--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
   </si>
   <si>
-    <t xml:space="preserve">Land &amp; Property</t>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Existing Land &amp; Property</t>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t xml:space="preserve">NEW FIXED ASSETS Bought AFTER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">New Land &amp; Property</t>
@@ -749,7 +752,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -934,6 +937,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -954,64 +969,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1927,45 +1934,24 @@
         <v>22</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="n">
-        <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
-      </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42"/>
-      <c r="B7" s="51" t="s">
+      <c r="D6" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52"/>
+      <c r="E6" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="45"/>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="48" t="n">
         <f aca="false">[1]Admin!$G$13</f>
         <v>0</v>
       </c>
@@ -1973,20 +1959,20 @@
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
-      <c r="M7" s="46"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="45"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="50"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1996,7 +1982,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="50" t="str">
+      <c r="G8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -2004,39 +1990,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="50" t="str">
+      <c r="I8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="50" t="str">
+      <c r="J8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="50" t="str">
+      <c r="K8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
         <v> </v>
       </c>
-      <c r="L8" s="50"/>
+      <c r="L8" s="53"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="50" t="str">
+      <c r="W8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="50" t="str">
+      <c r="X8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2046,7 +2032,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="50" t="str">
+      <c r="G9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -2054,39 +2040,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="50" t="str">
+      <c r="I9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="50" t="str">
+      <c r="J9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="50" t="str">
+      <c r="K9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
         <v> </v>
       </c>
-      <c r="L9" s="50"/>
+      <c r="L9" s="53"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
+      <c r="T9" s="50"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="50" t="str">
+      <c r="W9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="50" t="str">
+      <c r="X9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="50"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2096,7 +2082,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="50" t="str">
+      <c r="G10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -2104,39 +2090,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="50" t="str">
+      <c r="I10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="50" t="str">
+      <c r="J10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="50" t="str">
+      <c r="K10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
         <v> </v>
       </c>
-      <c r="L10" s="50"/>
+      <c r="L10" s="53"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="50" t="str">
+      <c r="W10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="50" t="str">
+      <c r="X10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
+      <c r="Y10" s="50"/>
+      <c r="Z10" s="50"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2171,9 +2157,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="50"/>
+      <c r="L11" s="53"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="50"/>
+      <c r="N11" s="53"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -2191,8 +2177,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="47"/>
-      <c r="U11" s="49"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="52"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2220,62 +2206,62 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="53"/>
+      <c r="W12" s="53"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="53"/>
+      <c r="Z12" s="53"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="66" t="n">
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="67" t="n">
         <f aca="false">[1]Admin!$G$14</f>
         <v>0.1</v>
       </c>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="52"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="53"/>
+      <c r="X13" s="53"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="50"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,7 +2271,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="50" t="str">
+      <c r="G14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2293,48 +2279,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="50" t="str">
+      <c r="I14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="50" t="str">
+      <c r="J14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="50" t="str">
+      <c r="K14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
         <v> </v>
       </c>
-      <c r="L14" s="50"/>
+      <c r="L14" s="53"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47" t="str">
+      <c r="N14" s="53"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="47" t="str">
+      <c r="S14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="47"/>
+      <c r="T14" s="50"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="50" t="str">
+      <c r="W14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="50" t="str">
+      <c r="X14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="47" t="str">
+      <c r="Y14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="47" t="str">
+      <c r="Z14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2347,7 +2333,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="50" t="str">
+      <c r="G15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2355,48 +2341,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="50" t="str">
+      <c r="I15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="50" t="str">
+      <c r="J15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="50" t="str">
+      <c r="K15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
         <v> </v>
       </c>
-      <c r="L15" s="50"/>
+      <c r="L15" s="53"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47" t="str">
+      <c r="N15" s="53"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="47" t="str">
+      <c r="S15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="47"/>
+      <c r="T15" s="50"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="50" t="str">
+      <c r="W15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="50" t="str">
+      <c r="X15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="47" t="str">
+      <c r="Y15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="47" t="str">
+      <c r="Z15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2409,7 +2395,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="50" t="str">
+      <c r="G16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2417,48 +2403,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="50" t="str">
+      <c r="I16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="50" t="str">
+      <c r="J16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="50" t="str">
+      <c r="K16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
         <v> </v>
       </c>
-      <c r="L16" s="50"/>
+      <c r="L16" s="53"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47" t="str">
+      <c r="N16" s="53"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="47" t="str">
+      <c r="S16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="47"/>
+      <c r="T16" s="50"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="50" t="str">
+      <c r="W16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="50" t="str">
+      <c r="X16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="47" t="str">
+      <c r="Y16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="47" t="str">
+      <c r="Z16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2471,7 +2457,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="50" t="str">
+      <c r="G17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2479,48 +2465,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="50" t="str">
+      <c r="I17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="50" t="str">
+      <c r="J17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="50" t="str">
+      <c r="K17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
         <v> </v>
       </c>
-      <c r="L17" s="50"/>
+      <c r="L17" s="53"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47" t="str">
+      <c r="N17" s="53"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="47" t="str">
+      <c r="S17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="47"/>
+      <c r="T17" s="50"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="50" t="str">
+      <c r="W17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="50" t="str">
+      <c r="X17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="47" t="str">
+      <c r="Y17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="47" t="str">
+      <c r="Z17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2533,7 +2519,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="50" t="str">
+      <c r="G18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2541,48 +2527,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="50" t="str">
+      <c r="I18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="50" t="str">
+      <c r="J18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="50" t="str">
+      <c r="K18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
         <v> </v>
       </c>
-      <c r="L18" s="50"/>
+      <c r="L18" s="53"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47" t="str">
+      <c r="N18" s="53"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="47" t="str">
+      <c r="S18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="47"/>
+      <c r="T18" s="50"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="50" t="str">
+      <c r="W18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="50" t="str">
+      <c r="X18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="47" t="str">
+      <c r="Y18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="47" t="str">
+      <c r="Z18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2620,9 +2606,9 @@
         <f aca="false">SUM(K14:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="50"/>
+      <c r="L19" s="53"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="50"/>
+      <c r="N19" s="53"/>
       <c r="O19" s="61" t="n">
         <f aca="false">SUM(O14:O18)</f>
         <v>0</v>
@@ -2640,8 +2626,8 @@
         <f aca="false">SUM(S14:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="47"/>
-      <c r="U19" s="49"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="52"/>
       <c r="V19" s="60" t="n">
         <f aca="false">SUM(V14:V18)</f>
         <v>0</v>
@@ -2669,62 +2655,62 @@
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
       <c r="H20" s="58"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
       <c r="P20" s="62"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="47"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="50"/>
-      <c r="Z20" s="50"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="50"/>
+      <c r="U20" s="52"/>
+      <c r="V20" s="53"/>
+      <c r="W20" s="53"/>
+      <c r="X20" s="53"/>
+      <c r="Y20" s="53"/>
+      <c r="Z20" s="53"/>
       <c r="AA20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="42"/>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="66"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="66" t="n">
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="67" t="n">
         <f aca="false">[1]Admin!$G$15</f>
         <v>0.2</v>
       </c>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="49"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="50"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="50"/>
+      <c r="T21" s="50"/>
+      <c r="U21" s="52"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="50"/>
+      <c r="Z21" s="50"/>
       <c r="AA21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2734,7 +2720,7 @@
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
       <c r="F22" s="57"/>
-      <c r="G22" s="50" t="str">
+      <c r="G22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,E22-F22," ")</f>
         <v> </v>
       </c>
@@ -2742,48 +2728,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I22" s="50" t="str">
+      <c r="I22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,MIN(E22*H22,G22)," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="50" t="str">
+      <c r="J22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,F22+I22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="50" t="str">
+      <c r="K22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,E22-J22," ")</f>
         <v> </v>
       </c>
-      <c r="L22" s="50"/>
+      <c r="L22" s="53"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47" t="str">
+      <c r="N22" s="53"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="50" t="str">
         <f aca="false">IF(O22&gt;0,O22*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S22" s="47" t="str">
+      <c r="S22" s="50" t="str">
         <f aca="false">IF(O22&gt;0,O22-R22," ")</f>
         <v> </v>
       </c>
-      <c r="T22" s="47"/>
+      <c r="T22" s="50"/>
       <c r="U22" s="54"/>
       <c r="V22" s="57"/>
-      <c r="W22" s="50" t="str">
+      <c r="W22" s="53" t="str">
         <f aca="false">IF(V22&gt;0,E22," ")</f>
         <v> </v>
       </c>
-      <c r="X22" s="50" t="str">
+      <c r="X22" s="53" t="str">
         <f aca="false">IF(V22&gt;0,J22," ")</f>
         <v> </v>
       </c>
-      <c r="Y22" s="47" t="str">
+      <c r="Y22" s="50" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&lt;S22,S22-V22," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z22" s="47" t="str">
+      <c r="Z22" s="50" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&gt;S22,V22-S22," ")," ")</f>
         <v> </v>
       </c>
@@ -2796,7 +2782,7 @@
       <c r="D23" s="56"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="50" t="str">
+      <c r="G23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,E23-F23," ")</f>
         <v> </v>
       </c>
@@ -2804,48 +2790,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I23" s="50" t="str">
+      <c r="I23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,MIN(E23*H23,G23)," ")</f>
         <v> </v>
       </c>
-      <c r="J23" s="50" t="str">
+      <c r="J23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,F23+I23," ")</f>
         <v> </v>
       </c>
-      <c r="K23" s="50" t="str">
+      <c r="K23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,E23-J23," ")</f>
         <v> </v>
       </c>
-      <c r="L23" s="50"/>
+      <c r="L23" s="53"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47" t="str">
+      <c r="N23" s="53"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="50" t="str">
         <f aca="false">IF(O23&gt;0,O23*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S23" s="47" t="str">
+      <c r="S23" s="50" t="str">
         <f aca="false">IF(O23&gt;0,O23-R23," ")</f>
         <v> </v>
       </c>
-      <c r="T23" s="47"/>
+      <c r="T23" s="50"/>
       <c r="U23" s="54"/>
       <c r="V23" s="57"/>
-      <c r="W23" s="50" t="str">
+      <c r="W23" s="53" t="str">
         <f aca="false">IF(V23&gt;0,E23," ")</f>
         <v> </v>
       </c>
-      <c r="X23" s="50" t="str">
+      <c r="X23" s="53" t="str">
         <f aca="false">IF(V23&gt;0,J23," ")</f>
         <v> </v>
       </c>
-      <c r="Y23" s="47" t="str">
+      <c r="Y23" s="50" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&lt;S23,S23-V23," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z23" s="47" t="str">
+      <c r="Z23" s="50" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&gt;S23,V23-S23," ")," ")</f>
         <v> </v>
       </c>
@@ -2858,7 +2844,7 @@
       <c r="D24" s="56"/>
       <c r="E24" s="57"/>
       <c r="F24" s="57"/>
-      <c r="G24" s="50" t="str">
+      <c r="G24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,E24-F24," ")</f>
         <v> </v>
       </c>
@@ -2866,48 +2852,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I24" s="50" t="str">
+      <c r="I24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,MIN(E24*H24,G24)," ")</f>
         <v> </v>
       </c>
-      <c r="J24" s="50" t="str">
+      <c r="J24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,F24+I24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="50" t="str">
+      <c r="K24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,E24-J24," ")</f>
         <v> </v>
       </c>
-      <c r="L24" s="50"/>
+      <c r="L24" s="53"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47" t="str">
+      <c r="N24" s="53"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="50" t="str">
         <f aca="false">IF(O24&gt;0,O24*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S24" s="47" t="str">
+      <c r="S24" s="50" t="str">
         <f aca="false">IF(O24&gt;0,O24-R24," ")</f>
         <v> </v>
       </c>
-      <c r="T24" s="47"/>
+      <c r="T24" s="50"/>
       <c r="U24" s="54"/>
       <c r="V24" s="57"/>
-      <c r="W24" s="50" t="str">
+      <c r="W24" s="53" t="str">
         <f aca="false">IF(V24&gt;0,E24," ")</f>
         <v> </v>
       </c>
-      <c r="X24" s="50" t="str">
+      <c r="X24" s="53" t="str">
         <f aca="false">IF(V24&gt;0,J24," ")</f>
         <v> </v>
       </c>
-      <c r="Y24" s="47" t="str">
+      <c r="Y24" s="50" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&lt;S24,S24-V24," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z24" s="47" t="str">
+      <c r="Z24" s="50" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&gt;S24,V24-S24," ")," ")</f>
         <v> </v>
       </c>
@@ -2920,7 +2906,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="50" t="str">
+      <c r="G25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2928,48 +2914,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="50" t="str">
+      <c r="I25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="50" t="str">
+      <c r="J25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="50" t="str">
+      <c r="K25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
         <v> </v>
       </c>
-      <c r="L25" s="50"/>
+      <c r="L25" s="53"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47" t="str">
+      <c r="N25" s="53"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="47" t="str">
+      <c r="S25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="47"/>
+      <c r="T25" s="50"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="50" t="str">
+      <c r="W25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="50" t="str">
+      <c r="X25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="47" t="str">
+      <c r="Y25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="47" t="str">
+      <c r="Z25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2982,7 +2968,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="50" t="str">
+      <c r="G26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -2990,48 +2976,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="50" t="str">
+      <c r="I26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="50" t="str">
+      <c r="J26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="50" t="str">
+      <c r="K26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
         <v> </v>
       </c>
-      <c r="L26" s="50"/>
+      <c r="L26" s="53"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47" t="str">
+      <c r="N26" s="53"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="47" t="str">
+      <c r="S26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="47"/>
+      <c r="T26" s="50"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="50" t="str">
+      <c r="W26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="50" t="str">
+      <c r="X26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="47" t="str">
+      <c r="Y26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="47" t="str">
+      <c r="Z26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -3069,9 +3055,9 @@
         <f aca="false">SUM(K22:K26)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="50"/>
+      <c r="L27" s="53"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="50"/>
+      <c r="N27" s="53"/>
       <c r="O27" s="61" t="n">
         <f aca="false">SUM(O22:O26)</f>
         <v>0</v>
@@ -3089,8 +3075,8 @@
         <f aca="false">SUM(S22:S26)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="47"/>
-      <c r="U27" s="49"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="52"/>
       <c r="V27" s="60" t="n">
         <f aca="false">SUM(V22:V26)</f>
         <v>0</v>
@@ -3118,62 +3104,62 @@
       <c r="B28" s="63"/>
       <c r="C28" s="64"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
       <c r="H28" s="58"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
       <c r="P28" s="62"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="47"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="53"/>
+      <c r="W28" s="53"/>
+      <c r="X28" s="53"/>
+      <c r="Y28" s="53"/>
+      <c r="Z28" s="53"/>
       <c r="AA28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="42"/>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="66" t="n">
+      <c r="C29" s="66"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="67" t="n">
         <f aca="false">[1]Admin!$G$16</f>
         <v>0.33</v>
       </c>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="47"/>
-      <c r="Z29" s="47"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="53"/>
+      <c r="X29" s="53"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="50"/>
       <c r="AA29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3183,7 +3169,7 @@
       <c r="D30" s="56"/>
       <c r="E30" s="57"/>
       <c r="F30" s="57"/>
-      <c r="G30" s="50" t="str">
+      <c r="G30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,E30-F30," ")</f>
         <v> </v>
       </c>
@@ -3191,48 +3177,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I30" s="50" t="str">
+      <c r="I30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,MIN(E30*H30,G30)," ")</f>
         <v> </v>
       </c>
-      <c r="J30" s="50" t="str">
+      <c r="J30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,F30+I30," ")</f>
         <v> </v>
       </c>
-      <c r="K30" s="50" t="str">
+      <c r="K30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,E30-J30," ")</f>
         <v> </v>
       </c>
-      <c r="L30" s="50"/>
+      <c r="L30" s="53"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47" t="str">
+      <c r="N30" s="53"/>
+      <c r="O30" s="68"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50" t="str">
         <f aca="false">IF(O30&gt;0,O30*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S30" s="47" t="str">
+      <c r="S30" s="50" t="str">
         <f aca="false">IF(O30&gt;0,O30-R30," ")</f>
         <v> </v>
       </c>
-      <c r="T30" s="47"/>
+      <c r="T30" s="50"/>
       <c r="U30" s="54"/>
       <c r="V30" s="57"/>
-      <c r="W30" s="50" t="str">
+      <c r="W30" s="53" t="str">
         <f aca="false">IF(V30&gt;0,E30," ")</f>
         <v> </v>
       </c>
-      <c r="X30" s="50" t="str">
+      <c r="X30" s="53" t="str">
         <f aca="false">IF(V30&gt;0,J30," ")</f>
         <v> </v>
       </c>
-      <c r="Y30" s="47" t="str">
+      <c r="Y30" s="50" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&lt;S30,S30-V30," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z30" s="47" t="str">
+      <c r="Z30" s="50" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&gt;S30,V30-S30," ")," ")</f>
         <v> </v>
       </c>
@@ -3245,7 +3231,7 @@
       <c r="D31" s="56"/>
       <c r="E31" s="57"/>
       <c r="F31" s="57"/>
-      <c r="G31" s="50" t="str">
+      <c r="G31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,E31-F31," ")</f>
         <v> </v>
       </c>
@@ -3253,48 +3239,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I31" s="50" t="str">
+      <c r="I31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,MIN(E31*H31,G31)," ")</f>
         <v> </v>
       </c>
-      <c r="J31" s="50" t="str">
+      <c r="J31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,F31+I31," ")</f>
         <v> </v>
       </c>
-      <c r="K31" s="50" t="str">
+      <c r="K31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,E31-J31," ")</f>
         <v> </v>
       </c>
-      <c r="L31" s="50"/>
+      <c r="L31" s="53"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="47"/>
-      <c r="R31" s="47" t="str">
+      <c r="N31" s="53"/>
+      <c r="O31" s="68"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50" t="str">
         <f aca="false">IF(O31&gt;0,O31*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S31" s="47" t="str">
+      <c r="S31" s="50" t="str">
         <f aca="false">IF(O31&gt;0,O31-R31," ")</f>
         <v> </v>
       </c>
-      <c r="T31" s="47"/>
+      <c r="T31" s="50"/>
       <c r="U31" s="54"/>
       <c r="V31" s="57"/>
-      <c r="W31" s="50" t="str">
+      <c r="W31" s="53" t="str">
         <f aca="false">IF(V31&gt;0,E31," ")</f>
         <v> </v>
       </c>
-      <c r="X31" s="50" t="str">
+      <c r="X31" s="53" t="str">
         <f aca="false">IF(V31&gt;0,J31," ")</f>
         <v> </v>
       </c>
-      <c r="Y31" s="47" t="str">
+      <c r="Y31" s="50" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&lt;S31,S31-V31," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z31" s="47" t="str">
+      <c r="Z31" s="50" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&gt;S31,V31-S31," ")," ")</f>
         <v> </v>
       </c>
@@ -3307,7 +3293,7 @@
       <c r="D32" s="56"/>
       <c r="E32" s="57"/>
       <c r="F32" s="57"/>
-      <c r="G32" s="50" t="str">
+      <c r="G32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,E32-F32," ")</f>
         <v> </v>
       </c>
@@ -3315,48 +3301,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I32" s="50" t="str">
+      <c r="I32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,MIN(E32*H32,G32)," ")</f>
         <v> </v>
       </c>
-      <c r="J32" s="50" t="str">
+      <c r="J32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,F32+I32," ")</f>
         <v> </v>
       </c>
-      <c r="K32" s="50" t="str">
+      <c r="K32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,E32-J32," ")</f>
         <v> </v>
       </c>
-      <c r="L32" s="50"/>
+      <c r="L32" s="53"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47" t="str">
+      <c r="N32" s="53"/>
+      <c r="O32" s="68"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50" t="str">
         <f aca="false">IF(O32&gt;0,O32*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S32" s="47" t="str">
+      <c r="S32" s="50" t="str">
         <f aca="false">IF(O32&gt;0,O32-R32," ")</f>
         <v> </v>
       </c>
-      <c r="T32" s="47"/>
+      <c r="T32" s="50"/>
       <c r="U32" s="54"/>
       <c r="V32" s="57"/>
-      <c r="W32" s="50" t="str">
+      <c r="W32" s="53" t="str">
         <f aca="false">IF(V32&gt;0,E32," ")</f>
         <v> </v>
       </c>
-      <c r="X32" s="50" t="str">
+      <c r="X32" s="53" t="str">
         <f aca="false">IF(V32&gt;0,J32," ")</f>
         <v> </v>
       </c>
-      <c r="Y32" s="47" t="str">
+      <c r="Y32" s="50" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&lt;S32,S32-V32," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z32" s="47" t="str">
+      <c r="Z32" s="50" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&gt;S32,V32-S32," ")," ")</f>
         <v> </v>
       </c>
@@ -3369,7 +3355,7 @@
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
       <c r="F33" s="57"/>
-      <c r="G33" s="50" t="str">
+      <c r="G33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
         <v> </v>
       </c>
@@ -3377,48 +3363,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="50" t="str">
+      <c r="I33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="50" t="str">
+      <c r="J33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="50" t="str">
+      <c r="K33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
         <v> </v>
       </c>
-      <c r="L33" s="50"/>
+      <c r="L33" s="53"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47" t="str">
+      <c r="N33" s="53"/>
+      <c r="O33" s="68"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="47" t="str">
+      <c r="S33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="47"/>
+      <c r="T33" s="50"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="50" t="str">
+      <c r="W33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="50" t="str">
+      <c r="X33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="47" t="str">
+      <c r="Y33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="47" t="str">
+      <c r="Z33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3431,7 +3417,7 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="50" t="str">
+      <c r="G34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
         <v> </v>
       </c>
@@ -3439,48 +3425,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="50" t="str">
+      <c r="I34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="50" t="str">
+      <c r="J34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="50" t="str">
+      <c r="K34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
         <v> </v>
       </c>
-      <c r="L34" s="50"/>
+      <c r="L34" s="53"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="67"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47" t="str">
+      <c r="N34" s="53"/>
+      <c r="O34" s="68"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="50"/>
+      <c r="R34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="47" t="str">
+      <c r="S34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="47"/>
+      <c r="T34" s="50"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="50" t="str">
+      <c r="W34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="50" t="str">
+      <c r="X34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="47" t="str">
+      <c r="Y34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="47" t="str">
+      <c r="Z34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3518,9 +3504,9 @@
         <f aca="false">SUM(K30:K34)</f>
         <v>0</v>
       </c>
-      <c r="L35" s="50"/>
+      <c r="L35" s="53"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="50"/>
+      <c r="N35" s="53"/>
       <c r="O35" s="61" t="n">
         <f aca="false">SUM(O30:O34)</f>
         <v>0</v>
@@ -3538,8 +3524,8 @@
         <f aca="false">SUM(S30:S34)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="47"/>
-      <c r="U35" s="49"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="52"/>
       <c r="V35" s="60" t="n">
         <f aca="false">SUM(V30:V34)</f>
         <v>0</v>
@@ -3567,65 +3553,65 @@
       <c r="B36" s="63"/>
       <c r="C36" s="64"/>
       <c r="D36" s="65"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
       <c r="H36" s="58"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
       <c r="P36" s="62"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="49"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="50"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
       <c r="AA36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="42"/>
-      <c r="B37" s="69" t="s">
+      <c r="B37" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="69"/>
-      <c r="D37" s="70" t="n">
+      <c r="C37" s="70"/>
+      <c r="D37" s="71" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="66" t="n">
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="67" t="n">
         <f aca="false">[1]Admin!$G$17</f>
         <v>0.25</v>
       </c>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
       <c r="P37" s="62"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="72"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="73"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="53"/>
+      <c r="W37" s="53"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
       <c r="AA37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3635,7 +3621,7 @@
       <c r="D38" s="56"/>
       <c r="E38" s="57"/>
       <c r="F38" s="57"/>
-      <c r="G38" s="50" t="str">
+      <c r="G38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
         <v> </v>
       </c>
@@ -3643,50 +3629,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I38" s="50" t="str">
+      <c r="I38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
         <v> </v>
       </c>
-      <c r="J38" s="50" t="str">
+      <c r="J38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
         <v> </v>
       </c>
-      <c r="K38" s="50" t="str">
+      <c r="K38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
         <v> </v>
       </c>
-      <c r="L38" s="50"/>
-      <c r="M38" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="50"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47" t="str">
+      <c r="L38" s="53"/>
+      <c r="M38" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="53"/>
+      <c r="O38" s="68"/>
+      <c r="P38" s="51"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
         <v> </v>
       </c>
-      <c r="S38" s="47" t="str">
+      <c r="S38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
         <v> </v>
       </c>
-      <c r="T38" s="47"/>
+      <c r="T38" s="50"/>
       <c r="U38" s="54"/>
       <c r="V38" s="57"/>
-      <c r="W38" s="50" t="str">
+      <c r="W38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
         <v> </v>
       </c>
-      <c r="X38" s="50" t="str">
+      <c r="X38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
         <v> </v>
       </c>
-      <c r="Y38" s="47" t="str">
+      <c r="Y38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z38" s="47" t="str">
+      <c r="Z38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
@@ -3699,7 +3685,7 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="50" t="str">
+      <c r="G39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
         <v> </v>
       </c>
@@ -3707,50 +3693,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I39" s="50" t="str">
+      <c r="I39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="50" t="str">
+      <c r="J39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="50" t="str">
+      <c r="K39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
         <v> </v>
       </c>
-      <c r="L39" s="50"/>
-      <c r="M39" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="50"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="47" t="str">
+      <c r="L39" s="53"/>
+      <c r="M39" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="53"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="47" t="str">
+      <c r="S39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="47"/>
+      <c r="T39" s="50"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="50" t="str">
+      <c r="W39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="50" t="str">
+      <c r="X39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="47" t="str">
+      <c r="Y39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,(S39-V39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="47" t="str">
+      <c r="Z39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,(V39-S39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
@@ -3763,7 +3749,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="50" t="str">
+      <c r="G40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
         <v> </v>
       </c>
@@ -3771,50 +3757,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I40" s="50" t="str">
+      <c r="I40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="50" t="str">
+      <c r="J40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="50" t="str">
+      <c r="K40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
         <v> </v>
       </c>
-      <c r="L40" s="50"/>
-      <c r="M40" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="50"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="47"/>
-      <c r="R40" s="47" t="str">
+      <c r="L40" s="53"/>
+      <c r="M40" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="53"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="47" t="str">
+      <c r="S40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="47"/>
+      <c r="T40" s="50"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="50" t="str">
+      <c r="W40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="50" t="str">
+      <c r="X40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="47" t="str">
+      <c r="Y40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,(S40-V40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="47" t="str">
+      <c r="Z40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,(V40-S40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
@@ -3827,7 +3813,7 @@
       <c r="D41" s="56"/>
       <c r="E41" s="57"/>
       <c r="F41" s="57"/>
-      <c r="G41" s="50" t="str">
+      <c r="G41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,E41-F41," ")</f>
         <v> </v>
       </c>
@@ -3835,50 +3821,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I41" s="50" t="str">
+      <c r="I41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,MIN(E41*H41,G41)," ")</f>
         <v> </v>
       </c>
-      <c r="J41" s="50" t="str">
+      <c r="J41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,F41+I41," ")</f>
         <v> </v>
       </c>
-      <c r="K41" s="50" t="str">
+      <c r="K41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,E41-J41," ")</f>
         <v> </v>
       </c>
-      <c r="L41" s="50"/>
-      <c r="M41" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="50"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="47"/>
-      <c r="R41" s="47" t="str">
+      <c r="L41" s="53"/>
+      <c r="M41" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="53"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="51"/>
+      <c r="Q41" s="50"/>
+      <c r="R41" s="50" t="str">
         <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
         <v> </v>
       </c>
-      <c r="S41" s="47" t="str">
+      <c r="S41" s="50" t="str">
         <f aca="false">IF(O41&gt;0,O41-R41," ")</f>
         <v> </v>
       </c>
-      <c r="T41" s="47"/>
+      <c r="T41" s="50"/>
       <c r="U41" s="54"/>
       <c r="V41" s="57"/>
-      <c r="W41" s="50" t="str">
+      <c r="W41" s="53" t="str">
         <f aca="false">IF(V41&gt;0,E41," ")</f>
         <v> </v>
       </c>
-      <c r="X41" s="50" t="str">
+      <c r="X41" s="53" t="str">
         <f aca="false">IF(V41&gt;0,J41," ")</f>
         <v> </v>
       </c>
-      <c r="Y41" s="47" t="str">
+      <c r="Y41" s="50" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&lt;S41,(S41-V41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z41" s="47" t="str">
+      <c r="Z41" s="50" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&gt;S41,(V41-S41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
@@ -3891,7 +3877,7 @@
       <c r="D42" s="56"/>
       <c r="E42" s="57"/>
       <c r="F42" s="57"/>
-      <c r="G42" s="50" t="str">
+      <c r="G42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,E42-F42," ")</f>
         <v> </v>
       </c>
@@ -3899,50 +3885,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I42" s="50" t="str">
+      <c r="I42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,MIN(E42*H42,G42)," ")</f>
         <v> </v>
       </c>
-      <c r="J42" s="50" t="str">
+      <c r="J42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,F42+I42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="50" t="str">
+      <c r="K42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,E42-J42," ")</f>
         <v> </v>
       </c>
-      <c r="L42" s="50"/>
-      <c r="M42" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="50"/>
-      <c r="O42" s="67"/>
-      <c r="P42" s="48"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47" t="str">
+      <c r="L42" s="53"/>
+      <c r="M42" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="53"/>
+      <c r="O42" s="68"/>
+      <c r="P42" s="51"/>
+      <c r="Q42" s="50"/>
+      <c r="R42" s="50" t="str">
         <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
         <v> </v>
       </c>
-      <c r="S42" s="47" t="str">
+      <c r="S42" s="50" t="str">
         <f aca="false">IF(O42&gt;0,O42-R42," ")</f>
         <v> </v>
       </c>
-      <c r="T42" s="47"/>
+      <c r="T42" s="50"/>
       <c r="U42" s="54"/>
       <c r="V42" s="57"/>
-      <c r="W42" s="50" t="str">
+      <c r="W42" s="53" t="str">
         <f aca="false">IF(V42&gt;0,E42," ")</f>
         <v> </v>
       </c>
-      <c r="X42" s="50" t="str">
+      <c r="X42" s="53" t="str">
         <f aca="false">IF(V42&gt;0,J42," ")</f>
         <v> </v>
       </c>
-      <c r="Y42" s="47" t="str">
+      <c r="Y42" s="50" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&lt;S42,(S42-V42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z42" s="47" t="str">
+      <c r="Z42" s="50" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&gt;S42,(V42-S42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
@@ -3950,36 +3936,36 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="69"/>
-      <c r="D43" s="70" t="n">
+      <c r="C43" s="70"/>
+      <c r="D43" s="71" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
       <c r="H43" s="58"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
       <c r="M43" s="58"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="47"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="47"/>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="47"/>
-      <c r="Z43" s="47"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="51"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="53"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="50"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3989,7 +3975,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="50" t="str">
+      <c r="G44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
         <v> </v>
       </c>
@@ -3997,50 +3983,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="50" t="str">
+      <c r="I44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="50" t="str">
+      <c r="J44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="50" t="str">
+      <c r="K44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
         <v> </v>
       </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="50"/>
-      <c r="O44" s="67"/>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47" t="str">
+      <c r="L44" s="53"/>
+      <c r="M44" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="53"/>
+      <c r="O44" s="68"/>
+      <c r="P44" s="51"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="47" t="str">
+      <c r="S44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="47"/>
+      <c r="T44" s="50"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="50" t="str">
+      <c r="W44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="50" t="str">
+      <c r="X44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="47" t="str">
+      <c r="Y44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="47" t="str">
+      <c r="Z44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -4053,7 +4039,7 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="50" t="str">
+      <c r="G45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
         <v> </v>
       </c>
@@ -4061,50 +4047,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="50" t="str">
+      <c r="I45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="50" t="str">
+      <c r="J45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="50" t="str">
+      <c r="K45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
         <v> </v>
       </c>
-      <c r="L45" s="50"/>
-      <c r="M45" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="50"/>
-      <c r="O45" s="67"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47" t="str">
+      <c r="L45" s="53"/>
+      <c r="M45" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="53"/>
+      <c r="O45" s="68"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="47" t="str">
+      <c r="S45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="47"/>
+      <c r="T45" s="50"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="50" t="str">
+      <c r="W45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="50" t="str">
+      <c r="X45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="47" t="str">
+      <c r="Y45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="47" t="str">
+      <c r="Z45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -4117,7 +4103,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="50" t="str">
+      <c r="G46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -4125,50 +4111,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="50" t="str">
+      <c r="I46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="50" t="str">
+      <c r="J46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="50" t="str">
+      <c r="K46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
         <v> </v>
       </c>
-      <c r="L46" s="50"/>
-      <c r="M46" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="50"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47" t="str">
+      <c r="L46" s="53"/>
+      <c r="M46" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="53"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="51"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="47" t="str">
+      <c r="S46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="47"/>
+      <c r="T46" s="50"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="50" t="str">
+      <c r="W46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="50" t="str">
+      <c r="X46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="47" t="str">
+      <c r="Y46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="47" t="str">
+      <c r="Z46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -4181,7 +4167,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="50" t="str">
+      <c r="G47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -4189,50 +4175,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="50" t="str">
+      <c r="I47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="50" t="str">
+      <c r="J47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="50" t="str">
+      <c r="K47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
         <v> </v>
       </c>
-      <c r="L47" s="50"/>
-      <c r="M47" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="50"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="48"/>
-      <c r="Q47" s="47"/>
-      <c r="R47" s="47" t="str">
+      <c r="L47" s="53"/>
+      <c r="M47" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="53"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="51"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="47" t="str">
+      <c r="S47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="47"/>
+      <c r="T47" s="50"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="50" t="str">
+      <c r="W47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="50" t="str">
+      <c r="X47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="47" t="str">
+      <c r="Y47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="47" t="str">
+      <c r="Z47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4245,7 +4231,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="50" t="str">
+      <c r="G48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4253,50 +4239,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="50" t="str">
+      <c r="I48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="50" t="str">
+      <c r="J48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="50" t="str">
+      <c r="K48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
         <v> </v>
       </c>
-      <c r="L48" s="50"/>
-      <c r="M48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="50"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47" t="str">
+      <c r="L48" s="53"/>
+      <c r="M48" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="53"/>
+      <c r="O48" s="68"/>
+      <c r="P48" s="51"/>
+      <c r="Q48" s="50"/>
+      <c r="R48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="47" t="str">
+      <c r="S48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="47"/>
+      <c r="T48" s="50"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="50" t="str">
+      <c r="W48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="50" t="str">
+      <c r="X48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="47" t="str">
+      <c r="Y48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="47" t="str">
+      <c r="Z48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4304,33 +4290,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="C49" s="51"/>
+      <c r="C49" s="66"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="47"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="47"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="49"/>
-      <c r="V49" s="50"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="50"/>
-      <c r="Y49" s="47"/>
-      <c r="Z49" s="47"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="50"/>
+      <c r="P49" s="51"/>
+      <c r="Q49" s="50"/>
+      <c r="R49" s="50"/>
+      <c r="S49" s="50"/>
+      <c r="T49" s="50"/>
+      <c r="U49" s="52"/>
+      <c r="V49" s="53"/>
+      <c r="W49" s="53"/>
+      <c r="X49" s="53"/>
+      <c r="Y49" s="50"/>
+      <c r="Z49" s="50"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4340,7 +4326,7 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="50" t="str">
+      <c r="G50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
         <v> </v>
       </c>
@@ -4348,50 +4334,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="50" t="str">
+      <c r="I50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="50" t="str">
+      <c r="J50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="50" t="str">
+      <c r="K50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
         <v> </v>
       </c>
-      <c r="L50" s="50"/>
-      <c r="M50" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="50"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47" t="str">
+      <c r="L50" s="53"/>
+      <c r="M50" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="53"/>
+      <c r="O50" s="68"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="50"/>
+      <c r="R50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,O50*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="47" t="str">
+      <c r="S50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="47"/>
+      <c r="T50" s="50"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="50" t="str">
+      <c r="W50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="50" t="str">
+      <c r="X50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="47" t="str">
+      <c r="Y50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="47" t="str">
+      <c r="Z50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4404,7 +4390,7 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="50" t="str">
+      <c r="G51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
         <v> </v>
       </c>
@@ -4412,50 +4398,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="50" t="str">
+      <c r="I51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="50" t="str">
+      <c r="J51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="50" t="str">
+      <c r="K51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
         <v> </v>
       </c>
-      <c r="L51" s="50"/>
-      <c r="M51" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="50"/>
-      <c r="O51" s="67"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47" t="str">
+      <c r="L51" s="53"/>
+      <c r="M51" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="53"/>
+      <c r="O51" s="68"/>
+      <c r="P51" s="51"/>
+      <c r="Q51" s="50"/>
+      <c r="R51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,O51*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="47" t="str">
+      <c r="S51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="47"/>
+      <c r="T51" s="50"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="50" t="str">
+      <c r="W51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="50" t="str">
+      <c r="X51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="47" t="str">
+      <c r="Y51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="47" t="str">
+      <c r="Z51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4468,7 +4454,7 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="50" t="str">
+      <c r="G52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
         <v> </v>
       </c>
@@ -4476,50 +4462,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="50" t="str">
+      <c r="I52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="50" t="str">
+      <c r="J52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="50" t="str">
+      <c r="K52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
         <v> </v>
       </c>
-      <c r="L52" s="50"/>
-      <c r="M52" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="50"/>
-      <c r="O52" s="67"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47" t="str">
+      <c r="L52" s="53"/>
+      <c r="M52" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="53"/>
+      <c r="O52" s="68"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="50"/>
+      <c r="R52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,O52*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="47" t="str">
+      <c r="S52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="47"/>
+      <c r="T52" s="50"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="50" t="str">
+      <c r="W52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="50" t="str">
+      <c r="X52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="47" t="str">
+      <c r="Y52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="47" t="str">
+      <c r="Z52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4532,7 +4518,7 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="50" t="str">
+      <c r="G53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
         <v> </v>
       </c>
@@ -4540,50 +4526,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="50" t="str">
+      <c r="I53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="50" t="str">
+      <c r="J53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="50" t="str">
+      <c r="K53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
         <v> </v>
       </c>
-      <c r="L53" s="50"/>
-      <c r="M53" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="50"/>
-      <c r="O53" s="67"/>
-      <c r="P53" s="48"/>
-      <c r="Q53" s="47"/>
-      <c r="R53" s="47" t="str">
+      <c r="L53" s="53"/>
+      <c r="M53" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="53"/>
+      <c r="O53" s="68"/>
+      <c r="P53" s="51"/>
+      <c r="Q53" s="50"/>
+      <c r="R53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,O53*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="47" t="str">
+      <c r="S53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="47"/>
+      <c r="T53" s="50"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="50" t="str">
+      <c r="W53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="50" t="str">
+      <c r="X53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="47" t="str">
+      <c r="Y53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="47" t="str">
+      <c r="Z53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4596,7 +4582,7 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="50" t="str">
+      <c r="G54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
         <v> </v>
       </c>
@@ -4604,50 +4590,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="50" t="str">
+      <c r="I54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="50" t="str">
+      <c r="J54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="50" t="str">
+      <c r="K54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
         <v> </v>
       </c>
-      <c r="L54" s="50"/>
-      <c r="M54" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="50"/>
-      <c r="O54" s="67"/>
-      <c r="P54" s="48"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47" t="str">
+      <c r="L54" s="53"/>
+      <c r="M54" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="53"/>
+      <c r="O54" s="68"/>
+      <c r="P54" s="51"/>
+      <c r="Q54" s="50"/>
+      <c r="R54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,O54*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="47" t="str">
+      <c r="S54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="47"/>
+      <c r="T54" s="50"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="50" t="str">
+      <c r="W54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="50" t="str">
+      <c r="X54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="47" t="str">
+      <c r="Y54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="47" t="str">
+      <c r="Z54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4685,9 +4671,9 @@
         <f aca="false">SUM(K38:K54)</f>
         <v>0</v>
       </c>
-      <c r="L55" s="50"/>
-      <c r="M55" s="71"/>
-      <c r="N55" s="50"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="72"/>
+      <c r="N55" s="53"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O38:O54)</f>
         <v>0</v>
@@ -4705,8 +4691,8 @@
         <f aca="false">SUM(S38:S54)</f>
         <v>0</v>
       </c>
-      <c r="T55" s="50"/>
-      <c r="U55" s="49"/>
+      <c r="T55" s="53"/>
+      <c r="U55" s="52"/>
       <c r="V55" s="61" t="n">
         <f aca="false">SUM(V38:V54)</f>
         <v>0</v>
@@ -4731,31 +4717,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="73"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="74"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="50"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="47"/>
-      <c r="P56" s="48"/>
-      <c r="Q56" s="47"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47"/>
-      <c r="T56" s="47"/>
-      <c r="U56" s="49"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="47"/>
-      <c r="X56" s="47"/>
-      <c r="Y56" s="47"/>
-      <c r="Z56" s="47"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="50"/>
+      <c r="P56" s="51"/>
+      <c r="Q56" s="50"/>
+      <c r="R56" s="50"/>
+      <c r="S56" s="50"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="52"/>
+      <c r="V56" s="53"/>
+      <c r="W56" s="50"/>
+      <c r="X56" s="50"/>
+      <c r="Y56" s="50"/>
+      <c r="Z56" s="50"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4765,74 +4751,74 @@
         <v>EXISTING FIXED ASSETS at </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="44" t="n">
+      <c r="D57" s="44" t="str">
         <f aca="false">D6</f>
-        <v>45753</v>
-      </c>
-      <c r="E57" s="74" t="n">
+        <v>Laptop (0.5 years old)</v>
+      </c>
+      <c r="E57" s="75" t="n">
         <f aca="false">E11+E19+E27+E35+E55</f>
         <v>0</v>
       </c>
-      <c r="F57" s="74" t="n">
+      <c r="F57" s="75" t="n">
         <f aca="false">F11+F19+F27+F35+F55</f>
         <v>0</v>
       </c>
-      <c r="G57" s="74" t="n">
+      <c r="G57" s="75" t="n">
         <f aca="false">G11+G19+G27+G35+G55</f>
         <v>0</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="74" t="n">
+      <c r="I57" s="75" t="n">
         <f aca="false">I11+I19+I27+I35+I55</f>
         <v>0</v>
       </c>
-      <c r="J57" s="74" t="n">
+      <c r="J57" s="75" t="n">
         <f aca="false">J11+J19+J27+J35+J55</f>
         <v>0</v>
       </c>
-      <c r="K57" s="74" t="n">
+      <c r="K57" s="75" t="n">
         <f aca="false">K11+K19+K27+K35+K55</f>
         <v>0</v>
       </c>
-      <c r="L57" s="50"/>
+      <c r="L57" s="53"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="74" t="n">
+      <c r="N57" s="53"/>
+      <c r="O57" s="75" t="n">
         <f aca="false">O11+O19+O27+O35+O55</f>
         <v>0</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="74" t="n">
+      <c r="Q57" s="75" t="n">
         <f aca="false">Q11+Q19+Q27+Q35+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="74" t="n">
+      <c r="R57" s="75" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
         <v>0</v>
       </c>
-      <c r="S57" s="74" t="n">
+      <c r="S57" s="75" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
         <v>0</v>
       </c>
-      <c r="T57" s="47"/>
-      <c r="U57" s="49"/>
-      <c r="V57" s="74" t="n">
+      <c r="T57" s="50"/>
+      <c r="U57" s="52"/>
+      <c r="V57" s="75" t="n">
         <f aca="false">V11+V19+V27+V35+V55</f>
         <v>0</v>
       </c>
-      <c r="W57" s="74" t="n">
+      <c r="W57" s="75" t="n">
         <f aca="false">W11+W19+W27+W35+W55</f>
         <v>0</v>
       </c>
-      <c r="X57" s="74" t="n">
+      <c r="X57" s="75" t="n">
         <f aca="false">X11+X19+X27+X35+X55</f>
         <v>0</v>
       </c>
-      <c r="Y57" s="74" t="n">
+      <c r="Y57" s="75" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="74" t="n">
+      <c r="Z57" s="75" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
         <v>0</v>
       </c>
@@ -4840,31 +4826,31 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="75"/>
-      <c r="C58" s="76"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="50"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="47"/>
-      <c r="P58" s="48"/>
-      <c r="Q58" s="47"/>
-      <c r="R58" s="47"/>
-      <c r="S58" s="47"/>
-      <c r="T58" s="47"/>
-      <c r="U58" s="49"/>
-      <c r="V58" s="50"/>
-      <c r="W58" s="50"/>
-      <c r="X58" s="50"/>
-      <c r="Y58" s="47"/>
-      <c r="Z58" s="47"/>
+      <c r="N58" s="53"/>
+      <c r="O58" s="50"/>
+      <c r="P58" s="51"/>
+      <c r="Q58" s="50"/>
+      <c r="R58" s="50"/>
+      <c r="S58" s="50"/>
+      <c r="T58" s="50"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="53"/>
+      <c r="W58" s="53"/>
+      <c r="X58" s="53"/>
+      <c r="Y58" s="50"/>
+      <c r="Z58" s="50"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4877,41 +4863,41 @@
         <f aca="false">[1]Admin!$B$4</f>
         <v>45753</v>
       </c>
-      <c r="E59" s="47"/>
-      <c r="F59" s="78"/>
-      <c r="G59" s="78"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
-      <c r="L59" s="47"/>
+      <c r="I59" s="50"/>
+      <c r="J59" s="50"/>
+      <c r="K59" s="50"/>
+      <c r="L59" s="50"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="47"/>
-      <c r="O59" s="47"/>
-      <c r="P59" s="48"/>
-      <c r="Q59" s="47"/>
-      <c r="R59" s="47"/>
-      <c r="S59" s="47"/>
-      <c r="T59" s="47"/>
-      <c r="U59" s="49"/>
-      <c r="V59" s="50"/>
-      <c r="W59" s="50"/>
-      <c r="X59" s="50"/>
-      <c r="Y59" s="47"/>
-      <c r="Z59" s="47"/>
+      <c r="N59" s="50"/>
+      <c r="O59" s="50"/>
+      <c r="P59" s="51"/>
+      <c r="Q59" s="50"/>
+      <c r="R59" s="50"/>
+      <c r="S59" s="50"/>
+      <c r="T59" s="50"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="53"/>
+      <c r="W59" s="53"/>
+      <c r="X59" s="53"/>
+      <c r="Y59" s="50"/>
+      <c r="Z59" s="50"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="51"/>
-      <c r="D60" s="52"/>
+      <c r="B60" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="66"/>
+      <c r="D60" s="47"/>
       <c r="E60" s="45"/>
-      <c r="F60" s="78"/>
-      <c r="G60" s="78"/>
-      <c r="H60" s="79" t="n">
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="80" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
@@ -4921,165 +4907,165 @@
       <c r="L60" s="45"/>
       <c r="M60" s="58"/>
       <c r="N60" s="45"/>
-      <c r="O60" s="47"/>
-      <c r="P60" s="48"/>
-      <c r="Q60" s="47"/>
-      <c r="R60" s="47"/>
-      <c r="S60" s="47"/>
-      <c r="T60" s="47"/>
-      <c r="U60" s="49"/>
-      <c r="V60" s="50"/>
-      <c r="W60" s="50"/>
-      <c r="X60" s="50"/>
-      <c r="Y60" s="47"/>
-      <c r="Z60" s="47"/>
+      <c r="O60" s="50"/>
+      <c r="P60" s="51"/>
+      <c r="Q60" s="50"/>
+      <c r="R60" s="50"/>
+      <c r="S60" s="50"/>
+      <c r="T60" s="50"/>
+      <c r="U60" s="52"/>
+      <c r="V60" s="53"/>
+      <c r="W60" s="53"/>
+      <c r="X60" s="53"/>
+      <c r="Y60" s="50"/>
+      <c r="Z60" s="50"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="80"/>
+      <c r="D61" s="81"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="50"/>
-      <c r="G61" s="50"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="50" t="str">
+      <c r="I61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="50" t="str">
+      <c r="J61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="50" t="str">
+      <c r="K61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
         <v> </v>
       </c>
-      <c r="L61" s="50"/>
+      <c r="L61" s="53"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="50"/>
-      <c r="O61" s="47"/>
-      <c r="P61" s="48"/>
-      <c r="Q61" s="47"/>
-      <c r="R61" s="47"/>
-      <c r="S61" s="47"/>
-      <c r="T61" s="47"/>
+      <c r="N61" s="53"/>
+      <c r="O61" s="50"/>
+      <c r="P61" s="51"/>
+      <c r="Q61" s="50"/>
+      <c r="R61" s="50"/>
+      <c r="S61" s="50"/>
+      <c r="T61" s="50"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="50" t="str">
+      <c r="W61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="50" t="str">
+      <c r="X61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="47"/>
-      <c r="Z61" s="47"/>
+      <c r="Y61" s="50"/>
+      <c r="Z61" s="50"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="80"/>
+      <c r="D62" s="81"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="50"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="50" t="str">
+      <c r="I62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="50" t="str">
+      <c r="J62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="50" t="str">
+      <c r="K62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
         <v> </v>
       </c>
-      <c r="L62" s="50"/>
+      <c r="L62" s="53"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="50"/>
-      <c r="O62" s="47"/>
-      <c r="P62" s="48"/>
-      <c r="Q62" s="47"/>
-      <c r="R62" s="47"/>
-      <c r="S62" s="47"/>
-      <c r="T62" s="47"/>
+      <c r="N62" s="53"/>
+      <c r="O62" s="50"/>
+      <c r="P62" s="51"/>
+      <c r="Q62" s="50"/>
+      <c r="R62" s="50"/>
+      <c r="S62" s="50"/>
+      <c r="T62" s="50"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="50" t="str">
+      <c r="W62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="50" t="str">
+      <c r="X62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="47"/>
-      <c r="Z62" s="47"/>
+      <c r="Y62" s="50"/>
+      <c r="Z62" s="50"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="80"/>
+      <c r="D63" s="81"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="50" t="str">
+      <c r="I63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="50" t="str">
+      <c r="J63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="50" t="str">
+      <c r="K63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
         <v> </v>
       </c>
-      <c r="L63" s="50"/>
+      <c r="L63" s="53"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="50"/>
-      <c r="O63" s="47"/>
-      <c r="P63" s="48"/>
-      <c r="Q63" s="47"/>
-      <c r="R63" s="47"/>
-      <c r="S63" s="47"/>
-      <c r="T63" s="47"/>
+      <c r="N63" s="53"/>
+      <c r="O63" s="50"/>
+      <c r="P63" s="51"/>
+      <c r="Q63" s="50"/>
+      <c r="R63" s="50"/>
+      <c r="S63" s="50"/>
+      <c r="T63" s="50"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="50" t="str">
+      <c r="W63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="50" t="str">
+      <c r="X63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="47"/>
-      <c r="Z63" s="47"/>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="50"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -5108,14 +5094,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="50"/>
+      <c r="L64" s="53"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="50"/>
+      <c r="N64" s="53"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="81"/>
+      <c r="P64" s="82"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -5128,8 +5114,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="47"/>
-      <c r="U64" s="49"/>
+      <c r="T64" s="50"/>
+      <c r="U64" s="52"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -5157,62 +5143,62 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="50"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="50"/>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="L65" s="50"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="53"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="50"/>
-      <c r="O65" s="50"/>
+      <c r="N65" s="53"/>
+      <c r="O65" s="53"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="50"/>
-      <c r="R65" s="50"/>
-      <c r="S65" s="50"/>
-      <c r="T65" s="47"/>
-      <c r="U65" s="49"/>
-      <c r="V65" s="50"/>
-      <c r="W65" s="50"/>
-      <c r="X65" s="50"/>
-      <c r="Y65" s="50"/>
-      <c r="Z65" s="50"/>
+      <c r="Q65" s="53"/>
+      <c r="R65" s="53"/>
+      <c r="S65" s="53"/>
+      <c r="T65" s="50"/>
+      <c r="U65" s="52"/>
+      <c r="V65" s="53"/>
+      <c r="W65" s="53"/>
+      <c r="X65" s="53"/>
+      <c r="Y65" s="53"/>
+      <c r="Z65" s="53"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="51"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="50"/>
-      <c r="H66" s="82" t="n">
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="83" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="50"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="53"/>
+      <c r="L66" s="53"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="47"/>
-      <c r="P66" s="48"/>
-      <c r="Q66" s="47"/>
-      <c r="R66" s="47"/>
-      <c r="S66" s="47"/>
-      <c r="T66" s="47"/>
-      <c r="U66" s="49"/>
-      <c r="V66" s="50"/>
-      <c r="W66" s="50"/>
-      <c r="X66" s="50"/>
-      <c r="Y66" s="47"/>
-      <c r="Z66" s="47"/>
+      <c r="N66" s="53"/>
+      <c r="O66" s="50"/>
+      <c r="P66" s="51"/>
+      <c r="Q66" s="50"/>
+      <c r="R66" s="50"/>
+      <c r="S66" s="50"/>
+      <c r="T66" s="50"/>
+      <c r="U66" s="52"/>
+      <c r="V66" s="53"/>
+      <c r="W66" s="53"/>
+      <c r="X66" s="53"/>
+      <c r="Y66" s="50"/>
+      <c r="Z66" s="50"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5221,57 +5207,57 @@
       <c r="C67" s="55"/>
       <c r="D67" s="56"/>
       <c r="E67" s="57"/>
-      <c r="F67" s="50"/>
-      <c r="G67" s="50"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="50" t="str">
+      <c r="I67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
         <v> </v>
       </c>
-      <c r="J67" s="50" t="str">
+      <c r="J67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
         <v> </v>
       </c>
-      <c r="K67" s="50" t="str">
+      <c r="K67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
         <v> </v>
       </c>
-      <c r="L67" s="50"/>
+      <c r="L67" s="53"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="50"/>
-      <c r="O67" s="47"/>
+      <c r="N67" s="53"/>
+      <c r="O67" s="50"/>
       <c r="P67" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q67" s="47" t="str">
+      <c r="Q67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67*P67," ")</f>
         <v> </v>
       </c>
-      <c r="R67" s="47"/>
-      <c r="S67" s="47" t="str">
+      <c r="R67" s="50"/>
+      <c r="S67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
         <v> </v>
       </c>
-      <c r="T67" s="47"/>
+      <c r="T67" s="50"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="50" t="str">
+      <c r="W67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="50" t="str">
+      <c r="X67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="47" t="str">
+      <c r="Y67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="47" t="str">
+      <c r="Z67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5283,57 +5269,57 @@
       <c r="C68" s="55"/>
       <c r="D68" s="56"/>
       <c r="E68" s="57"/>
-      <c r="F68" s="50"/>
-      <c r="G68" s="50"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="50" t="str">
+      <c r="I68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
         <v> </v>
       </c>
-      <c r="J68" s="50" t="str">
+      <c r="J68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
         <v> </v>
       </c>
-      <c r="K68" s="50" t="str">
+      <c r="K68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
         <v> </v>
       </c>
-      <c r="L68" s="50"/>
+      <c r="L68" s="53"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="47"/>
+      <c r="N68" s="53"/>
+      <c r="O68" s="50"/>
       <c r="P68" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q68" s="47" t="str">
+      <c r="Q68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68*P68," ")</f>
         <v> </v>
       </c>
-      <c r="R68" s="47"/>
-      <c r="S68" s="47" t="str">
+      <c r="R68" s="50"/>
+      <c r="S68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
         <v> </v>
       </c>
-      <c r="T68" s="47"/>
+      <c r="T68" s="50"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="50" t="str">
+      <c r="W68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="50" t="str">
+      <c r="X68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="47" t="str">
+      <c r="Y68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="47" t="str">
+      <c r="Z68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5345,57 +5331,57 @@
       <c r="C69" s="55"/>
       <c r="D69" s="56"/>
       <c r="E69" s="57"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="50" t="str">
+      <c r="I69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
         <v> </v>
       </c>
-      <c r="J69" s="50" t="str">
+      <c r="J69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
         <v> </v>
       </c>
-      <c r="K69" s="50" t="str">
+      <c r="K69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
         <v> </v>
       </c>
-      <c r="L69" s="50"/>
+      <c r="L69" s="53"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="47"/>
+      <c r="N69" s="53"/>
+      <c r="O69" s="50"/>
       <c r="P69" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q69" s="47" t="str">
+      <c r="Q69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69*P69," ")</f>
         <v> </v>
       </c>
-      <c r="R69" s="47"/>
-      <c r="S69" s="47" t="str">
+      <c r="R69" s="50"/>
+      <c r="S69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
         <v> </v>
       </c>
-      <c r="T69" s="47"/>
+      <c r="T69" s="50"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="50" t="str">
+      <c r="W69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="50" t="str">
+      <c r="X69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="47" t="str">
+      <c r="Y69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="47" t="str">
+      <c r="Z69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5407,57 +5393,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="50" t="str">
+      <c r="I70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="50" t="str">
+      <c r="J70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="50" t="str">
+      <c r="K70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
         <v> </v>
       </c>
-      <c r="L70" s="50"/>
+      <c r="L70" s="53"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="47"/>
+      <c r="N70" s="53"/>
+      <c r="O70" s="50"/>
       <c r="P70" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="47" t="str">
+      <c r="Q70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47" t="str">
+      <c r="R70" s="50"/>
+      <c r="S70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="47"/>
+      <c r="T70" s="50"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="50" t="str">
+      <c r="W70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="50" t="str">
+      <c r="X70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="47" t="str">
+      <c r="Y70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="47" t="str">
+      <c r="Z70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5469,57 +5455,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="50" t="str">
+      <c r="I71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="50" t="str">
+      <c r="J71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="50" t="str">
+      <c r="K71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
         <v> </v>
       </c>
-      <c r="L71" s="50"/>
+      <c r="L71" s="53"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="50"/>
-      <c r="O71" s="47"/>
+      <c r="N71" s="53"/>
+      <c r="O71" s="50"/>
       <c r="P71" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q71" s="47" t="str">
+      <c r="Q71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="47"/>
-      <c r="S71" s="47" t="str">
+      <c r="R71" s="50"/>
+      <c r="S71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="47"/>
+      <c r="T71" s="50"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="50" t="str">
+      <c r="W71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="50" t="str">
+      <c r="X71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="47" t="str">
+      <c r="Y71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="47" t="str">
+      <c r="Z71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5528,7 +5514,7 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="42"/>
       <c r="B72" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
@@ -5557,9 +5543,9 @@
         <f aca="false">SUM(K67:K71)</f>
         <v>0</v>
       </c>
-      <c r="L72" s="50"/>
+      <c r="L72" s="53"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="50"/>
+      <c r="N72" s="53"/>
       <c r="O72" s="61" t="n">
         <f aca="false">SUM(O67:O71)</f>
         <v>0</v>
@@ -5577,8 +5563,8 @@
         <f aca="false">SUM(S67:S71)</f>
         <v>0</v>
       </c>
-      <c r="T72" s="47"/>
-      <c r="U72" s="49"/>
+      <c r="T72" s="50"/>
+      <c r="U72" s="52"/>
       <c r="V72" s="60" t="n">
         <f aca="false">SUM(V67:V71)</f>
         <v>0</v>
@@ -5606,121 +5592,121 @@
       <c r="B73" s="63"/>
       <c r="C73" s="64"/>
       <c r="D73" s="65"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="50"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
       <c r="H73" s="58"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="L73" s="50"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="53"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="50"/>
-      <c r="O73" s="50"/>
+      <c r="N73" s="53"/>
+      <c r="O73" s="53"/>
       <c r="P73" s="62"/>
-      <c r="Q73" s="50"/>
-      <c r="R73" s="50"/>
-      <c r="S73" s="50"/>
-      <c r="T73" s="47"/>
-      <c r="U73" s="49"/>
-      <c r="V73" s="50"/>
-      <c r="W73" s="50"/>
-      <c r="X73" s="50"/>
-      <c r="Y73" s="50"/>
-      <c r="Z73" s="50"/>
+      <c r="Q73" s="53"/>
+      <c r="R73" s="53"/>
+      <c r="S73" s="53"/>
+      <c r="T73" s="50"/>
+      <c r="U73" s="52"/>
+      <c r="V73" s="53"/>
+      <c r="W73" s="53"/>
+      <c r="X73" s="53"/>
+      <c r="Y73" s="53"/>
+      <c r="Z73" s="53"/>
       <c r="AA73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="42"/>
-      <c r="B74" s="51" t="s">
+      <c r="B74" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="51"/>
+      <c r="C74" s="66"/>
       <c r="D74" s="62"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="50"/>
-      <c r="H74" s="82" t="n">
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="83" t="n">
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I74" s="50"/>
-      <c r="J74" s="50"/>
-      <c r="K74" s="50"/>
-      <c r="L74" s="50"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="50"/>
-      <c r="O74" s="47"/>
-      <c r="P74" s="48"/>
-      <c r="Q74" s="47"/>
-      <c r="R74" s="47"/>
-      <c r="S74" s="47"/>
-      <c r="T74" s="47"/>
-      <c r="U74" s="49"/>
-      <c r="V74" s="50"/>
-      <c r="W74" s="50"/>
-      <c r="X74" s="50"/>
-      <c r="Y74" s="47"/>
-      <c r="Z74" s="47"/>
+      <c r="N74" s="53"/>
+      <c r="O74" s="50"/>
+      <c r="P74" s="51"/>
+      <c r="Q74" s="50"/>
+      <c r="R74" s="50"/>
+      <c r="S74" s="50"/>
+      <c r="T74" s="50"/>
+      <c r="U74" s="52"/>
+      <c r="V74" s="53"/>
+      <c r="W74" s="53"/>
+      <c r="X74" s="53"/>
+      <c r="Y74" s="50"/>
+      <c r="Z74" s="50"/>
       <c r="AA74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
-      <c r="D75" s="80"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="57"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="50"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
       <c r="H75" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I75" s="50" t="str">
+      <c r="I75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,MIN(E75*H75,G75)," ")</f>
         <v> </v>
       </c>
-      <c r="J75" s="50" t="str">
+      <c r="J75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,F75+I75," ")</f>
         <v> </v>
       </c>
-      <c r="K75" s="50" t="str">
+      <c r="K75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,E75-J75," ")</f>
         <v> </v>
       </c>
-      <c r="L75" s="50"/>
+      <c r="L75" s="53"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="50"/>
-      <c r="O75" s="47"/>
+      <c r="N75" s="53"/>
+      <c r="O75" s="50"/>
       <c r="P75" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q75" s="47" t="str">
+      <c r="Q75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75*P75," ")</f>
         <v> </v>
       </c>
-      <c r="R75" s="47"/>
-      <c r="S75" s="47" t="str">
+      <c r="R75" s="50"/>
+      <c r="S75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75-Q75," ")</f>
         <v> </v>
       </c>
-      <c r="T75" s="47"/>
+      <c r="T75" s="50"/>
       <c r="U75" s="54"/>
       <c r="V75" s="57"/>
-      <c r="W75" s="50" t="str">
+      <c r="W75" s="53" t="str">
         <f aca="false">IF(V75&gt;0,E75," ")</f>
         <v> </v>
       </c>
-      <c r="X75" s="50" t="str">
+      <c r="X75" s="53" t="str">
         <f aca="false">IF(V75&gt;0,J75," ")</f>
         <v> </v>
       </c>
-      <c r="Y75" s="47" t="str">
+      <c r="Y75" s="50" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&lt;S75,S75-V75," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z75" s="47" t="str">
+      <c r="Z75" s="50" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&gt;S75,V75-S75," ")," ")</f>
         <v> </v>
       </c>
@@ -5730,59 +5716,59 @@
       <c r="A76" s="42"/>
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
-      <c r="D76" s="80"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="57"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
       <c r="H76" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I76" s="50" t="str">
+      <c r="I76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,MIN(E76*H76,G76)," ")</f>
         <v> </v>
       </c>
-      <c r="J76" s="50" t="str">
+      <c r="J76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,F76+I76," ")</f>
         <v> </v>
       </c>
-      <c r="K76" s="50" t="str">
+      <c r="K76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,E76-J76," ")</f>
         <v> </v>
       </c>
-      <c r="L76" s="50"/>
+      <c r="L76" s="53"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="50"/>
-      <c r="O76" s="47"/>
+      <c r="N76" s="53"/>
+      <c r="O76" s="50"/>
       <c r="P76" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q76" s="47" t="str">
+      <c r="Q76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76*P76," ")</f>
         <v> </v>
       </c>
-      <c r="R76" s="47"/>
-      <c r="S76" s="47" t="str">
+      <c r="R76" s="50"/>
+      <c r="S76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76-Q76," ")</f>
         <v> </v>
       </c>
-      <c r="T76" s="47"/>
+      <c r="T76" s="50"/>
       <c r="U76" s="54"/>
       <c r="V76" s="57"/>
-      <c r="W76" s="50" t="str">
+      <c r="W76" s="53" t="str">
         <f aca="false">IF(V76&gt;0,E76," ")</f>
         <v> </v>
       </c>
-      <c r="X76" s="50" t="str">
+      <c r="X76" s="53" t="str">
         <f aca="false">IF(V76&gt;0,J76," ")</f>
         <v> </v>
       </c>
-      <c r="Y76" s="47" t="str">
+      <c r="Y76" s="50" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&lt;S76,S76-V76," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z76" s="47" t="str">
+      <c r="Z76" s="50" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&gt;S76,V76-S76," ")," ")</f>
         <v> </v>
       </c>
@@ -5792,59 +5778,59 @@
       <c r="A77" s="42"/>
       <c r="B77" s="54"/>
       <c r="C77" s="55"/>
-      <c r="D77" s="80"/>
+      <c r="D77" s="81"/>
       <c r="E77" s="57"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
       <c r="H77" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="50" t="str">
+      <c r="I77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,MIN(E77*H77,G77)," ")</f>
         <v> </v>
       </c>
-      <c r="J77" s="50" t="str">
+      <c r="J77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,F77+I77," ")</f>
         <v> </v>
       </c>
-      <c r="K77" s="50" t="str">
+      <c r="K77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,E77-J77," ")</f>
         <v> </v>
       </c>
-      <c r="L77" s="50"/>
+      <c r="L77" s="53"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="50"/>
-      <c r="O77" s="47"/>
+      <c r="N77" s="53"/>
+      <c r="O77" s="50"/>
       <c r="P77" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="47" t="str">
+      <c r="Q77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77*P77," ")</f>
         <v> </v>
       </c>
-      <c r="R77" s="47"/>
-      <c r="S77" s="47" t="str">
+      <c r="R77" s="50"/>
+      <c r="S77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77-Q77," ")</f>
         <v> </v>
       </c>
-      <c r="T77" s="47"/>
+      <c r="T77" s="50"/>
       <c r="U77" s="54"/>
       <c r="V77" s="57"/>
-      <c r="W77" s="50" t="str">
+      <c r="W77" s="53" t="str">
         <f aca="false">IF(V77&gt;0,E77," ")</f>
         <v> </v>
       </c>
-      <c r="X77" s="50" t="str">
+      <c r="X77" s="53" t="str">
         <f aca="false">IF(V77&gt;0,J77," ")</f>
         <v> </v>
       </c>
-      <c r="Y77" s="47" t="str">
+      <c r="Y77" s="50" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&lt;S77,S77-V77," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z77" s="47" t="str">
+      <c r="Z77" s="50" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&gt;S77,V77-S77," ")," ")</f>
         <v> </v>
       </c>
@@ -5854,59 +5840,59 @@
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="80"/>
+      <c r="D78" s="81"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="50" t="str">
+      <c r="I78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="50" t="str">
+      <c r="J78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="50" t="str">
+      <c r="K78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
         <v> </v>
       </c>
-      <c r="L78" s="50"/>
+      <c r="L78" s="53"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="50"/>
-      <c r="O78" s="47"/>
+      <c r="N78" s="53"/>
+      <c r="O78" s="50"/>
       <c r="P78" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q78" s="47" t="str">
+      <c r="Q78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="47"/>
-      <c r="S78" s="47" t="str">
+      <c r="R78" s="50"/>
+      <c r="S78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="47"/>
+      <c r="T78" s="50"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="50" t="str">
+      <c r="W78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="50" t="str">
+      <c r="X78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="47" t="str">
+      <c r="Y78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="47" t="str">
+      <c r="Z78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5916,59 +5902,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="80"/>
+      <c r="D79" s="81"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="50" t="str">
+      <c r="I79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="50" t="str">
+      <c r="J79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="50" t="str">
+      <c r="K79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
         <v> </v>
       </c>
-      <c r="L79" s="50"/>
+      <c r="L79" s="53"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="50"/>
-      <c r="O79" s="47"/>
+      <c r="N79" s="53"/>
+      <c r="O79" s="50"/>
       <c r="P79" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q79" s="47" t="str">
+      <c r="Q79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="47"/>
-      <c r="S79" s="47" t="str">
+      <c r="R79" s="50"/>
+      <c r="S79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="47"/>
+      <c r="T79" s="50"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="50" t="str">
+      <c r="W79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="50" t="str">
+      <c r="X79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="47" t="str">
+      <c r="Y79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="47" t="str">
+      <c r="Z79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -5977,7 +5963,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="42"/>
       <c r="B80" s="59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C80" s="59"/>
       <c r="D80" s="59"/>
@@ -6006,9 +5992,9 @@
         <f aca="false">SUM(K75:K79)</f>
         <v>0</v>
       </c>
-      <c r="L80" s="50"/>
+      <c r="L80" s="53"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="50"/>
+      <c r="N80" s="53"/>
       <c r="O80" s="61" t="n">
         <f aca="false">SUM(O75:O79)</f>
         <v>0</v>
@@ -6026,8 +6012,8 @@
         <f aca="false">SUM(S75:S79)</f>
         <v>0</v>
       </c>
-      <c r="T80" s="47"/>
-      <c r="U80" s="49"/>
+      <c r="T80" s="50"/>
+      <c r="U80" s="52"/>
       <c r="V80" s="60" t="n">
         <f aca="false">SUM(V75:V79)</f>
         <v>0</v>
@@ -6055,121 +6041,121 @@
       <c r="B81" s="63"/>
       <c r="C81" s="64"/>
       <c r="D81" s="65"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
       <c r="H81" s="58"/>
-      <c r="I81" s="50"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
+      <c r="I81" s="53"/>
+      <c r="J81" s="53"/>
+      <c r="K81" s="53"/>
+      <c r="L81" s="53"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="50"/>
-      <c r="O81" s="50"/>
+      <c r="N81" s="53"/>
+      <c r="O81" s="53"/>
       <c r="P81" s="62"/>
-      <c r="Q81" s="50"/>
-      <c r="R81" s="50"/>
-      <c r="S81" s="50"/>
-      <c r="T81" s="47"/>
-      <c r="U81" s="49"/>
-      <c r="V81" s="50"/>
-      <c r="W81" s="50"/>
-      <c r="X81" s="50"/>
-      <c r="Y81" s="50"/>
-      <c r="Z81" s="50"/>
+      <c r="Q81" s="53"/>
+      <c r="R81" s="53"/>
+      <c r="S81" s="53"/>
+      <c r="T81" s="50"/>
+      <c r="U81" s="52"/>
+      <c r="V81" s="53"/>
+      <c r="W81" s="53"/>
+      <c r="X81" s="53"/>
+      <c r="Y81" s="53"/>
+      <c r="Z81" s="53"/>
       <c r="AA81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="42"/>
-      <c r="B82" s="51" t="s">
+      <c r="B82" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="51"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="82" t="n">
+      <c r="C82" s="66"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="83" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I82" s="50"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="53"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="50"/>
-      <c r="O82" s="47"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="47"/>
-      <c r="R82" s="47"/>
-      <c r="S82" s="47"/>
-      <c r="T82" s="47"/>
-      <c r="U82" s="49"/>
-      <c r="V82" s="50"/>
-      <c r="W82" s="50"/>
-      <c r="X82" s="50"/>
-      <c r="Y82" s="47"/>
-      <c r="Z82" s="47"/>
+      <c r="N82" s="53"/>
+      <c r="O82" s="50"/>
+      <c r="P82" s="51"/>
+      <c r="Q82" s="50"/>
+      <c r="R82" s="50"/>
+      <c r="S82" s="50"/>
+      <c r="T82" s="50"/>
+      <c r="U82" s="52"/>
+      <c r="V82" s="53"/>
+      <c r="W82" s="53"/>
+      <c r="X82" s="53"/>
+      <c r="Y82" s="50"/>
+      <c r="Z82" s="50"/>
       <c r="AA82" s="25"/>
     </row>
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="54"/>
       <c r="C83" s="55"/>
-      <c r="D83" s="80"/>
+      <c r="D83" s="81"/>
       <c r="E83" s="57"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
       <c r="H83" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I83" s="50" t="str">
+      <c r="I83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,MIN(E83*H83,G83)," ")</f>
         <v> </v>
       </c>
-      <c r="J83" s="50" t="str">
+      <c r="J83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,F83+I83," ")</f>
         <v> </v>
       </c>
-      <c r="K83" s="50" t="str">
+      <c r="K83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,E83-J83," ")</f>
         <v> </v>
       </c>
-      <c r="L83" s="50"/>
+      <c r="L83" s="53"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="50"/>
-      <c r="O83" s="47"/>
+      <c r="N83" s="53"/>
+      <c r="O83" s="50"/>
       <c r="P83" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q83" s="47" t="str">
+      <c r="Q83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83*P83," ")</f>
         <v> </v>
       </c>
-      <c r="R83" s="47"/>
-      <c r="S83" s="47" t="str">
+      <c r="R83" s="50"/>
+      <c r="S83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83-Q83," ")</f>
         <v> </v>
       </c>
-      <c r="T83" s="47"/>
+      <c r="T83" s="50"/>
       <c r="U83" s="54"/>
       <c r="V83" s="57"/>
-      <c r="W83" s="50" t="str">
+      <c r="W83" s="53" t="str">
         <f aca="false">IF(V83&gt;0,E83," ")</f>
         <v> </v>
       </c>
-      <c r="X83" s="50" t="str">
+      <c r="X83" s="53" t="str">
         <f aca="false">IF(V83&gt;0,J83," ")</f>
         <v> </v>
       </c>
-      <c r="Y83" s="47" t="str">
+      <c r="Y83" s="50" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&lt;S83,S83-V83," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z83" s="47" t="str">
+      <c r="Z83" s="50" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&gt;S83,V83-S83," ")," ")</f>
         <v> </v>
       </c>
@@ -6179,59 +6165,59 @@
       <c r="A84" s="42"/>
       <c r="B84" s="54"/>
       <c r="C84" s="55"/>
-      <c r="D84" s="80"/>
+      <c r="D84" s="81"/>
       <c r="E84" s="57"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
       <c r="H84" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I84" s="50" t="str">
+      <c r="I84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,MIN(E84*H84,G84)," ")</f>
         <v> </v>
       </c>
-      <c r="J84" s="50" t="str">
+      <c r="J84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,F84+I84," ")</f>
         <v> </v>
       </c>
-      <c r="K84" s="50" t="str">
+      <c r="K84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,E84-J84," ")</f>
         <v> </v>
       </c>
-      <c r="L84" s="50"/>
+      <c r="L84" s="53"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="50"/>
-      <c r="O84" s="47"/>
+      <c r="N84" s="53"/>
+      <c r="O84" s="50"/>
       <c r="P84" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q84" s="47" t="str">
+      <c r="Q84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84*P84," ")</f>
         <v> </v>
       </c>
-      <c r="R84" s="47"/>
-      <c r="S84" s="47" t="str">
+      <c r="R84" s="50"/>
+      <c r="S84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84-Q84," ")</f>
         <v> </v>
       </c>
-      <c r="T84" s="47"/>
+      <c r="T84" s="50"/>
       <c r="U84" s="54"/>
       <c r="V84" s="57"/>
-      <c r="W84" s="50" t="str">
+      <c r="W84" s="53" t="str">
         <f aca="false">IF(V84&gt;0,E84," ")</f>
         <v> </v>
       </c>
-      <c r="X84" s="50" t="str">
+      <c r="X84" s="53" t="str">
         <f aca="false">IF(V84&gt;0,J84," ")</f>
         <v> </v>
       </c>
-      <c r="Y84" s="47" t="str">
+      <c r="Y84" s="50" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&lt;S84,S84-V84," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z84" s="47" t="str">
+      <c r="Z84" s="50" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&gt;S84,V84-S84," ")," ")</f>
         <v> </v>
       </c>
@@ -6241,59 +6227,59 @@
       <c r="A85" s="42"/>
       <c r="B85" s="54"/>
       <c r="C85" s="55"/>
-      <c r="D85" s="80"/>
+      <c r="D85" s="81"/>
       <c r="E85" s="57"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
       <c r="H85" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="50" t="str">
+      <c r="I85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,MIN(E85*H85,G85)," ")</f>
         <v> </v>
       </c>
-      <c r="J85" s="50" t="str">
+      <c r="J85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,F85+I85," ")</f>
         <v> </v>
       </c>
-      <c r="K85" s="50" t="str">
+      <c r="K85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,E85-J85," ")</f>
         <v> </v>
       </c>
-      <c r="L85" s="50"/>
+      <c r="L85" s="53"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="50"/>
-      <c r="O85" s="47"/>
+      <c r="N85" s="53"/>
+      <c r="O85" s="50"/>
       <c r="P85" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q85" s="47" t="str">
+      <c r="Q85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85*P85," ")</f>
         <v> </v>
       </c>
-      <c r="R85" s="47"/>
-      <c r="S85" s="47" t="str">
+      <c r="R85" s="50"/>
+      <c r="S85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85-Q85," ")</f>
         <v> </v>
       </c>
-      <c r="T85" s="47"/>
+      <c r="T85" s="50"/>
       <c r="U85" s="54"/>
       <c r="V85" s="57"/>
-      <c r="W85" s="50" t="str">
+      <c r="W85" s="53" t="str">
         <f aca="false">IF(V85&gt;0,E85," ")</f>
         <v> </v>
       </c>
-      <c r="X85" s="50" t="str">
+      <c r="X85" s="53" t="str">
         <f aca="false">IF(V85&gt;0,J85," ")</f>
         <v> </v>
       </c>
-      <c r="Y85" s="47" t="str">
+      <c r="Y85" s="50" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&lt;S85,S85-V85," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z85" s="47" t="str">
+      <c r="Z85" s="50" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&gt;S85,V85-S85," ")," ")</f>
         <v> </v>
       </c>
@@ -6303,59 +6289,59 @@
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="80"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="50" t="str">
+      <c r="I86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="50" t="str">
+      <c r="J86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="50" t="str">
+      <c r="K86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
         <v> </v>
       </c>
-      <c r="L86" s="50"/>
+      <c r="L86" s="53"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="50"/>
-      <c r="O86" s="47"/>
+      <c r="N86" s="53"/>
+      <c r="O86" s="50"/>
       <c r="P86" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q86" s="47" t="str">
+      <c r="Q86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="47"/>
-      <c r="S86" s="47" t="str">
+      <c r="R86" s="50"/>
+      <c r="S86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="47"/>
+      <c r="T86" s="50"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="50" t="str">
+      <c r="W86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="50" t="str">
+      <c r="X86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="47" t="str">
+      <c r="Y86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="47" t="str">
+      <c r="Z86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6365,59 +6351,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="80"/>
+      <c r="D87" s="81"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="50" t="str">
+      <c r="I87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="50" t="str">
+      <c r="J87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="50" t="str">
+      <c r="K87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
         <v> </v>
       </c>
-      <c r="L87" s="50"/>
+      <c r="L87" s="53"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="50"/>
-      <c r="O87" s="47"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="50"/>
       <c r="P87" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q87" s="47" t="str">
+      <c r="Q87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="47"/>
-      <c r="S87" s="47" t="str">
+      <c r="R87" s="50"/>
+      <c r="S87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="47"/>
+      <c r="T87" s="50"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="50" t="str">
+      <c r="W87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="50" t="str">
+      <c r="X87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="47" t="str">
+      <c r="Y87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="47" t="str">
+      <c r="Z87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6426,7 +6412,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="42"/>
       <c r="B88" s="59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -6455,9 +6441,9 @@
         <f aca="false">SUM(K83:K87)</f>
         <v>0</v>
       </c>
-      <c r="L88" s="50"/>
+      <c r="L88" s="53"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="50"/>
+      <c r="N88" s="53"/>
       <c r="O88" s="61" t="n">
         <f aca="false">SUM(O83:O87)</f>
         <v>0</v>
@@ -6475,8 +6461,8 @@
         <f aca="false">SUM(S83:S87)</f>
         <v>0</v>
       </c>
-      <c r="T88" s="47"/>
-      <c r="U88" s="49"/>
+      <c r="T88" s="50"/>
+      <c r="U88" s="52"/>
       <c r="V88" s="60" t="n">
         <f aca="false">SUM(V83:V87)</f>
         <v>0</v>
@@ -6504,124 +6490,124 @@
       <c r="B89" s="63"/>
       <c r="C89" s="64"/>
       <c r="D89" s="65"/>
-      <c r="E89" s="50"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
       <c r="H89" s="58"/>
-      <c r="I89" s="50"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
-      <c r="L89" s="50"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="53"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="50"/>
-      <c r="O89" s="50"/>
+      <c r="N89" s="53"/>
+      <c r="O89" s="53"/>
       <c r="P89" s="62"/>
-      <c r="Q89" s="50"/>
-      <c r="R89" s="50"/>
-      <c r="S89" s="50"/>
-      <c r="T89" s="47"/>
-      <c r="U89" s="49"/>
-      <c r="V89" s="50"/>
-      <c r="W89" s="50"/>
-      <c r="X89" s="50"/>
-      <c r="Y89" s="50"/>
-      <c r="Z89" s="50"/>
+      <c r="Q89" s="53"/>
+      <c r="R89" s="53"/>
+      <c r="S89" s="53"/>
+      <c r="T89" s="50"/>
+      <c r="U89" s="52"/>
+      <c r="V89" s="53"/>
+      <c r="W89" s="53"/>
+      <c r="X89" s="53"/>
+      <c r="Y89" s="53"/>
+      <c r="Z89" s="53"/>
       <c r="AA89" s="25"/>
     </row>
     <row r="90" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="42"/>
-      <c r="B90" s="69" t="str">
+      <c r="B90" s="70" t="str">
         <f aca="false">B37</f>
         <v>Motor Vehicles - costing over £</v>
       </c>
-      <c r="C90" s="69"/>
-      <c r="D90" s="70" t="n">
+      <c r="C90" s="70"/>
+      <c r="D90" s="71" t="n">
         <f aca="false">D37</f>
         <v>12000</v>
       </c>
-      <c r="E90" s="50"/>
-      <c r="F90" s="50"/>
-      <c r="G90" s="50"/>
-      <c r="H90" s="82" t="n">
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="83" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I90" s="50"/>
-      <c r="J90" s="50"/>
-      <c r="K90" s="50"/>
-      <c r="L90" s="50"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="50"/>
-      <c r="O90" s="47"/>
+      <c r="N90" s="53"/>
+      <c r="O90" s="50"/>
       <c r="P90" s="62"/>
-      <c r="Q90" s="47"/>
-      <c r="R90" s="47"/>
-      <c r="S90" s="47"/>
-      <c r="T90" s="47"/>
-      <c r="U90" s="49"/>
-      <c r="V90" s="50"/>
-      <c r="W90" s="50"/>
-      <c r="X90" s="50"/>
-      <c r="Y90" s="47"/>
-      <c r="Z90" s="47"/>
+      <c r="Q90" s="50"/>
+      <c r="R90" s="50"/>
+      <c r="S90" s="50"/>
+      <c r="T90" s="50"/>
+      <c r="U90" s="52"/>
+      <c r="V90" s="53"/>
+      <c r="W90" s="53"/>
+      <c r="X90" s="53"/>
+      <c r="Y90" s="50"/>
+      <c r="Z90" s="50"/>
       <c r="AA90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="80"/>
+      <c r="D91" s="81"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I91" s="50" t="str">
+      <c r="I91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="50" t="str">
+      <c r="J91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="50" t="str">
+      <c r="K91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
         <v> </v>
       </c>
-      <c r="L91" s="50"/>
-      <c r="M91" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="50"/>
-      <c r="O91" s="47"/>
-      <c r="P91" s="48"/>
-      <c r="Q91" s="47"/>
-      <c r="R91" s="47" t="str">
+      <c r="L91" s="53"/>
+      <c r="M91" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="53"/>
+      <c r="O91" s="50"/>
+      <c r="P91" s="51"/>
+      <c r="Q91" s="50"/>
+      <c r="R91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
         <v> </v>
       </c>
-      <c r="S91" s="47" t="str">
+      <c r="S91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91-R91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="47"/>
+      <c r="T91" s="50"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="50" t="str">
+      <c r="W91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="50" t="str">
+      <c r="X91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="47" t="str">
+      <c r="Y91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,(S91-V91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="47" t="str">
+      <c r="Z91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,(V91-S91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
@@ -6631,58 +6617,58 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="80"/>
+      <c r="D92" s="81"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="50"/>
+      <c r="F92" s="53"/>
+      <c r="G92" s="53"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I92" s="50" t="str">
+      <c r="I92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="50" t="str">
+      <c r="J92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="50" t="str">
+      <c r="K92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
         <v> </v>
       </c>
-      <c r="L92" s="50"/>
-      <c r="M92" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="50"/>
-      <c r="O92" s="47"/>
-      <c r="P92" s="48"/>
-      <c r="Q92" s="47"/>
-      <c r="R92" s="47" t="str">
+      <c r="L92" s="53"/>
+      <c r="M92" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="53"/>
+      <c r="O92" s="50"/>
+      <c r="P92" s="51"/>
+      <c r="Q92" s="50"/>
+      <c r="R92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
         <v> </v>
       </c>
-      <c r="S92" s="47" t="str">
+      <c r="S92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92-R92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="47"/>
+      <c r="T92" s="50"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="50" t="str">
+      <c r="W92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="50" t="str">
+      <c r="X92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="47" t="str">
+      <c r="Y92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,(S92-V92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="47" t="str">
+      <c r="Z92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,(V92-S92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
@@ -6692,58 +6678,58 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="80"/>
+      <c r="D93" s="81"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
+      <c r="F93" s="53"/>
+      <c r="G93" s="53"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I93" s="50" t="str">
+      <c r="I93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="50" t="str">
+      <c r="J93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="50" t="str">
+      <c r="K93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
         <v> </v>
       </c>
-      <c r="L93" s="50"/>
-      <c r="M93" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="50"/>
-      <c r="O93" s="47"/>
-      <c r="P93" s="48"/>
-      <c r="Q93" s="47"/>
-      <c r="R93" s="47" t="str">
+      <c r="L93" s="53"/>
+      <c r="M93" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="53"/>
+      <c r="O93" s="50"/>
+      <c r="P93" s="51"/>
+      <c r="Q93" s="50"/>
+      <c r="R93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
         <v> </v>
       </c>
-      <c r="S93" s="47" t="str">
+      <c r="S93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93-R93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="47"/>
+      <c r="T93" s="50"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="50" t="str">
+      <c r="W93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="50" t="str">
+      <c r="X93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="47" t="str">
+      <c r="Y93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,(S93-V93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="47" t="str">
+      <c r="Z93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,(V93-S93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
@@ -6753,58 +6739,58 @@
       <c r="A94" s="42"/>
       <c r="B94" s="54"/>
       <c r="C94" s="55"/>
-      <c r="D94" s="80"/>
+      <c r="D94" s="81"/>
       <c r="E94" s="57"/>
-      <c r="F94" s="50"/>
-      <c r="G94" s="50"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
       <c r="H94" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I94" s="50" t="str">
+      <c r="I94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*H94,G94)," ")</f>
         <v> </v>
       </c>
-      <c r="J94" s="50" t="str">
+      <c r="J94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,F94+I94," ")</f>
         <v> </v>
       </c>
-      <c r="K94" s="50" t="str">
+      <c r="K94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,E94-J94," ")</f>
         <v> </v>
       </c>
-      <c r="L94" s="50"/>
-      <c r="M94" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="50"/>
-      <c r="O94" s="47"/>
-      <c r="P94" s="48"/>
-      <c r="Q94" s="47"/>
-      <c r="R94" s="47" t="str">
+      <c r="L94" s="53"/>
+      <c r="M94" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="53"/>
+      <c r="O94" s="50"/>
+      <c r="P94" s="51"/>
+      <c r="Q94" s="50"/>
+      <c r="R94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
         <v> </v>
       </c>
-      <c r="S94" s="47" t="str">
+      <c r="S94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,E94-R94," ")</f>
         <v> </v>
       </c>
-      <c r="T94" s="47"/>
+      <c r="T94" s="50"/>
       <c r="U94" s="54"/>
       <c r="V94" s="57"/>
-      <c r="W94" s="50" t="str">
+      <c r="W94" s="53" t="str">
         <f aca="false">IF(V94&gt;0,E94," ")</f>
         <v> </v>
       </c>
-      <c r="X94" s="50" t="str">
+      <c r="X94" s="53" t="str">
         <f aca="false">IF(V94&gt;0,J94," ")</f>
         <v> </v>
       </c>
-      <c r="Y94" s="47" t="str">
+      <c r="Y94" s="50" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&lt;S94,(S94-V94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z94" s="47" t="str">
+      <c r="Z94" s="50" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&gt;S94,(V94-S94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
@@ -6814,58 +6800,58 @@
       <c r="A95" s="42"/>
       <c r="B95" s="54"/>
       <c r="C95" s="55"/>
-      <c r="D95" s="80"/>
+      <c r="D95" s="81"/>
       <c r="E95" s="57"/>
-      <c r="F95" s="50"/>
-      <c r="G95" s="50"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="53"/>
       <c r="H95" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I95" s="50" t="str">
+      <c r="I95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*H95,G95)," ")</f>
         <v> </v>
       </c>
-      <c r="J95" s="50" t="str">
+      <c r="J95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,F95+I95," ")</f>
         <v> </v>
       </c>
-      <c r="K95" s="50" t="str">
+      <c r="K95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,E95-J95," ")</f>
         <v> </v>
       </c>
-      <c r="L95" s="50"/>
-      <c r="M95" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="50"/>
-      <c r="O95" s="47"/>
-      <c r="P95" s="48"/>
-      <c r="Q95" s="47"/>
-      <c r="R95" s="47" t="str">
+      <c r="L95" s="53"/>
+      <c r="M95" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="53"/>
+      <c r="O95" s="50"/>
+      <c r="P95" s="51"/>
+      <c r="Q95" s="50"/>
+      <c r="R95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
         <v> </v>
       </c>
-      <c r="S95" s="47" t="str">
+      <c r="S95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,E95-R95," ")</f>
         <v> </v>
       </c>
-      <c r="T95" s="47"/>
+      <c r="T95" s="50"/>
       <c r="U95" s="54"/>
       <c r="V95" s="57"/>
-      <c r="W95" s="50" t="str">
+      <c r="W95" s="53" t="str">
         <f aca="false">IF(V95&gt;0,E95," ")</f>
         <v> </v>
       </c>
-      <c r="X95" s="50" t="str">
+      <c r="X95" s="53" t="str">
         <f aca="false">IF(V95&gt;0,J95," ")</f>
         <v> </v>
       </c>
-      <c r="Y95" s="47" t="str">
+      <c r="Y95" s="50" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&lt;S95,(S95-V95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z95" s="47" t="str">
+      <c r="Z95" s="50" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&gt;S95,(V95-S95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
@@ -6873,95 +6859,95 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="83" t="str">
+      <c r="B96" s="84" t="str">
         <f aca="false">B43</f>
         <v>Motor Vehicles - costing under £</v>
       </c>
-      <c r="C96" s="83"/>
-      <c r="D96" s="70" t="n">
+      <c r="C96" s="84"/>
+      <c r="D96" s="71" t="n">
         <f aca="false">D43</f>
         <v>12000</v>
       </c>
-      <c r="E96" s="50"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53"/>
       <c r="H96" s="58"/>
-      <c r="I96" s="50"/>
-      <c r="J96" s="50"/>
-      <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="50"/>
-      <c r="O96" s="47"/>
-      <c r="P96" s="48"/>
-      <c r="Q96" s="47"/>
-      <c r="R96" s="47"/>
-      <c r="S96" s="47"/>
-      <c r="T96" s="47"/>
-      <c r="U96" s="49"/>
-      <c r="V96" s="50"/>
-      <c r="W96" s="50"/>
-      <c r="X96" s="50"/>
-      <c r="Y96" s="47"/>
-      <c r="Z96" s="47"/>
+      <c r="N96" s="53"/>
+      <c r="O96" s="50"/>
+      <c r="P96" s="51"/>
+      <c r="Q96" s="50"/>
+      <c r="R96" s="50"/>
+      <c r="S96" s="50"/>
+      <c r="T96" s="50"/>
+      <c r="U96" s="52"/>
+      <c r="V96" s="53"/>
+      <c r="W96" s="53"/>
+      <c r="X96" s="53"/>
+      <c r="Y96" s="50"/>
+      <c r="Z96" s="50"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="80"/>
+      <c r="D97" s="81"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
+      <c r="F97" s="53"/>
+      <c r="G97" s="53"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="50" t="str">
+      <c r="I97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="50" t="str">
+      <c r="J97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="50" t="str">
+      <c r="K97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
         <v> </v>
       </c>
-      <c r="L97" s="50"/>
-      <c r="M97" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="50"/>
-      <c r="O97" s="47"/>
-      <c r="P97" s="48"/>
-      <c r="Q97" s="47"/>
-      <c r="R97" s="47" t="str">
+      <c r="L97" s="53"/>
+      <c r="M97" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="53"/>
+      <c r="O97" s="50"/>
+      <c r="P97" s="51"/>
+      <c r="Q97" s="50"/>
+      <c r="R97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="47" t="str">
+      <c r="S97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="47"/>
+      <c r="T97" s="50"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="50" t="str">
+      <c r="W97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="50" t="str">
+      <c r="X97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="47" t="str">
+      <c r="Y97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="47" t="str">
+      <c r="Z97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -6971,58 +6957,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="80"/>
+      <c r="D98" s="81"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="50"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="50" t="str">
+      <c r="I98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="50" t="str">
+      <c r="J98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="50" t="str">
+      <c r="K98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
         <v> </v>
       </c>
-      <c r="L98" s="50"/>
-      <c r="M98" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="50"/>
-      <c r="O98" s="47"/>
-      <c r="P98" s="48"/>
-      <c r="Q98" s="47"/>
-      <c r="R98" s="47" t="str">
+      <c r="L98" s="53"/>
+      <c r="M98" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="53"/>
+      <c r="O98" s="50"/>
+      <c r="P98" s="51"/>
+      <c r="Q98" s="50"/>
+      <c r="R98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="47" t="str">
+      <c r="S98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="47"/>
+      <c r="T98" s="50"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="50" t="str">
+      <c r="W98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="50" t="str">
+      <c r="X98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="47" t="str">
+      <c r="Y98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="47" t="str">
+      <c r="Z98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -7032,58 +7018,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="80"/>
+      <c r="D99" s="81"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
+      <c r="F99" s="53"/>
+      <c r="G99" s="53"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="50" t="str">
+      <c r="I99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="50" t="str">
+      <c r="J99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="50" t="str">
+      <c r="K99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
         <v> </v>
       </c>
-      <c r="L99" s="50"/>
-      <c r="M99" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="50"/>
-      <c r="O99" s="47"/>
-      <c r="P99" s="48"/>
-      <c r="Q99" s="47"/>
-      <c r="R99" s="47" t="str">
+      <c r="L99" s="53"/>
+      <c r="M99" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="53"/>
+      <c r="O99" s="50"/>
+      <c r="P99" s="51"/>
+      <c r="Q99" s="50"/>
+      <c r="R99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="47" t="str">
+      <c r="S99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="47"/>
+      <c r="T99" s="50"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="50" t="str">
+      <c r="W99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="50" t="str">
+      <c r="X99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="47" t="str">
+      <c r="Y99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="47" t="str">
+      <c r="Z99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -7093,58 +7079,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="80"/>
+      <c r="D100" s="81"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="53"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="50" t="str">
+      <c r="I100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="50" t="str">
+      <c r="J100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="50" t="str">
+      <c r="K100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
         <v> </v>
       </c>
-      <c r="L100" s="50"/>
-      <c r="M100" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="50"/>
-      <c r="O100" s="47"/>
-      <c r="P100" s="48"/>
-      <c r="Q100" s="47"/>
-      <c r="R100" s="47" t="str">
+      <c r="L100" s="53"/>
+      <c r="M100" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="53"/>
+      <c r="O100" s="50"/>
+      <c r="P100" s="51"/>
+      <c r="Q100" s="50"/>
+      <c r="R100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="47" t="str">
+      <c r="S100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="47"/>
+      <c r="T100" s="50"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="50" t="str">
+      <c r="W100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="50" t="str">
+      <c r="X100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="47" t="str">
+      <c r="Y100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="47" t="str">
+      <c r="Z100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -7154,58 +7140,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="80"/>
+      <c r="D101" s="81"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
+      <c r="F101" s="53"/>
+      <c r="G101" s="53"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="50" t="str">
+      <c r="I101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="50" t="str">
+      <c r="J101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="50" t="str">
+      <c r="K101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
         <v> </v>
       </c>
-      <c r="L101" s="50"/>
-      <c r="M101" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="50"/>
-      <c r="O101" s="47"/>
-      <c r="P101" s="48"/>
-      <c r="Q101" s="47"/>
-      <c r="R101" s="47" t="str">
+      <c r="L101" s="53"/>
+      <c r="M101" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="53"/>
+      <c r="O101" s="50"/>
+      <c r="P101" s="51"/>
+      <c r="Q101" s="50"/>
+      <c r="R101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="47" t="str">
+      <c r="S101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="47"/>
+      <c r="T101" s="50"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="50" t="str">
+      <c r="W101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="50" t="str">
+      <c r="X101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="47" t="str">
+      <c r="Y101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="47" t="str">
+      <c r="Z101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7213,94 +7199,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="51" t="s">
+      <c r="B102" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="C102" s="51"/>
-      <c r="D102" s="68"/>
-      <c r="E102" s="50"/>
-      <c r="F102" s="50"/>
-      <c r="G102" s="50"/>
+      <c r="C102" s="66"/>
+      <c r="D102" s="69"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="50"/>
-      <c r="J102" s="50"/>
-      <c r="K102" s="50"/>
-      <c r="L102" s="50"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="53"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="50"/>
-      <c r="O102" s="47"/>
-      <c r="P102" s="48"/>
-      <c r="Q102" s="47"/>
-      <c r="R102" s="47"/>
-      <c r="S102" s="47"/>
-      <c r="T102" s="47"/>
-      <c r="U102" s="49"/>
-      <c r="V102" s="50"/>
-      <c r="W102" s="50"/>
-      <c r="X102" s="50"/>
-      <c r="Y102" s="47"/>
-      <c r="Z102" s="47"/>
+      <c r="N102" s="53"/>
+      <c r="O102" s="50"/>
+      <c r="P102" s="51"/>
+      <c r="Q102" s="50"/>
+      <c r="R102" s="50"/>
+      <c r="S102" s="50"/>
+      <c r="T102" s="50"/>
+      <c r="U102" s="52"/>
+      <c r="V102" s="53"/>
+      <c r="W102" s="53"/>
+      <c r="X102" s="53"/>
+      <c r="Y102" s="50"/>
+      <c r="Z102" s="50"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="80"/>
+      <c r="D103" s="81"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="50"/>
-      <c r="G103" s="50"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="50" t="str">
+      <c r="I103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="50" t="str">
+      <c r="J103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="50" t="str">
+      <c r="K103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
         <v> </v>
       </c>
-      <c r="L103" s="50"/>
-      <c r="M103" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="50"/>
-      <c r="O103" s="47"/>
+      <c r="L103" s="53"/>
+      <c r="M103" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="53"/>
+      <c r="O103" s="50"/>
       <c r="P103" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q103" s="47" t="str">
+      <c r="Q103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="47"/>
-      <c r="S103" s="47" t="str">
+      <c r="R103" s="50"/>
+      <c r="S103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="47"/>
+      <c r="T103" s="50"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="50" t="str">
+      <c r="W103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="50" t="str">
+      <c r="X103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="47" t="str">
+      <c r="Y103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="47" t="str">
+      <c r="Z103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7310,61 +7296,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="80"/>
+      <c r="D104" s="81"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="50"/>
-      <c r="G104" s="50"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="50" t="str">
+      <c r="I104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="50" t="str">
+      <c r="J104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="50" t="str">
+      <c r="K104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
         <v> </v>
       </c>
-      <c r="L104" s="50"/>
-      <c r="M104" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="50"/>
-      <c r="O104" s="47"/>
+      <c r="L104" s="53"/>
+      <c r="M104" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="53"/>
+      <c r="O104" s="50"/>
       <c r="P104" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q104" s="47" t="str">
+      <c r="Q104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="47"/>
-      <c r="S104" s="47" t="str">
+      <c r="R104" s="50"/>
+      <c r="S104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="47"/>
+      <c r="T104" s="50"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="50" t="str">
+      <c r="W104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="50" t="str">
+      <c r="X104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="47" t="str">
+      <c r="Y104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="47" t="str">
+      <c r="Z104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7374,61 +7360,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="80"/>
+      <c r="D105" s="81"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="50"/>
-      <c r="G105" s="50"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="50" t="str">
+      <c r="I105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="50" t="str">
+      <c r="J105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="50" t="str">
+      <c r="K105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
         <v> </v>
       </c>
-      <c r="L105" s="50"/>
-      <c r="M105" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="50"/>
-      <c r="O105" s="47"/>
+      <c r="L105" s="53"/>
+      <c r="M105" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="53"/>
+      <c r="O105" s="50"/>
       <c r="P105" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q105" s="47" t="str">
+      <c r="Q105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="47"/>
-      <c r="S105" s="47" t="str">
+      <c r="R105" s="50"/>
+      <c r="S105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="47"/>
+      <c r="T105" s="50"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="50" t="str">
+      <c r="W105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="50" t="str">
+      <c r="X105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="47" t="str">
+      <c r="Y105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="47" t="str">
+      <c r="Z105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7438,61 +7424,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="80"/>
+      <c r="D106" s="81"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="50"/>
-      <c r="G106" s="50"/>
+      <c r="F106" s="53"/>
+      <c r="G106" s="53"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="50" t="str">
+      <c r="I106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="50" t="str">
+      <c r="J106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="50" t="str">
+      <c r="K106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
         <v> </v>
       </c>
-      <c r="L106" s="50"/>
-      <c r="M106" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="50"/>
-      <c r="O106" s="47"/>
+      <c r="L106" s="53"/>
+      <c r="M106" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="53"/>
+      <c r="O106" s="50"/>
       <c r="P106" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q106" s="47" t="str">
+      <c r="Q106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="47"/>
-      <c r="S106" s="47" t="str">
+      <c r="R106" s="50"/>
+      <c r="S106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="47"/>
+      <c r="T106" s="50"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="50" t="str">
+      <c r="W106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="50" t="str">
+      <c r="X106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="47" t="str">
+      <c r="Y106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="47" t="str">
+      <c r="Z106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7502,61 +7488,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="80"/>
-      <c r="E107" s="84"/>
-      <c r="F107" s="50"/>
-      <c r="G107" s="50"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="85"/>
+      <c r="F107" s="53"/>
+      <c r="G107" s="53"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="50" t="str">
+      <c r="I107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="50" t="str">
+      <c r="J107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="50" t="str">
+      <c r="K107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
         <v> </v>
       </c>
-      <c r="L107" s="50"/>
-      <c r="M107" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="50"/>
-      <c r="O107" s="47"/>
+      <c r="L107" s="53"/>
+      <c r="M107" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="53"/>
+      <c r="O107" s="50"/>
       <c r="P107" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q107" s="47" t="str">
+      <c r="Q107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="47"/>
-      <c r="S107" s="47" t="str">
+      <c r="R107" s="50"/>
+      <c r="S107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="47"/>
+      <c r="T107" s="50"/>
       <c r="U107" s="54"/>
-      <c r="V107" s="84"/>
-      <c r="W107" s="50" t="str">
+      <c r="V107" s="85"/>
+      <c r="W107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="50" t="str">
+      <c r="X107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="47" t="str">
+      <c r="Y107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="47" t="str">
+      <c r="Z107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7565,7 +7551,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7594,9 +7580,9 @@
         <f aca="false">SUM(K91:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="50"/>
+      <c r="L108" s="53"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="50"/>
+      <c r="N108" s="53"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O91:O107)</f>
         <v>0</v>
@@ -7614,8 +7600,8 @@
         <f aca="false">SUM(S91:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="47"/>
-      <c r="U108" s="49"/>
+      <c r="T108" s="50"/>
+      <c r="U108" s="52"/>
       <c r="V108" s="61" t="n">
         <f aca="false">SUM(V91:V107)</f>
         <v>0</v>
@@ -7640,31 +7626,31 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="73"/>
-      <c r="D109" s="68"/>
-      <c r="E109" s="50"/>
-      <c r="F109" s="50"/>
-      <c r="G109" s="50"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="74"/>
+      <c r="D109" s="69"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="53"/>
+      <c r="G109" s="53"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="50"/>
-      <c r="J109" s="50"/>
-      <c r="K109" s="50"/>
-      <c r="L109" s="50"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="53"/>
+      <c r="L109" s="53"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="50"/>
-      <c r="O109" s="47"/>
-      <c r="P109" s="48"/>
-      <c r="Q109" s="47"/>
-      <c r="R109" s="47"/>
-      <c r="S109" s="47"/>
-      <c r="T109" s="47"/>
-      <c r="U109" s="49"/>
-      <c r="V109" s="50"/>
-      <c r="W109" s="47"/>
-      <c r="X109" s="47"/>
-      <c r="Y109" s="47"/>
-      <c r="Z109" s="47"/>
+      <c r="N109" s="53"/>
+      <c r="O109" s="50"/>
+      <c r="P109" s="51"/>
+      <c r="Q109" s="50"/>
+      <c r="R109" s="50"/>
+      <c r="S109" s="50"/>
+      <c r="T109" s="50"/>
+      <c r="U109" s="52"/>
+      <c r="V109" s="53"/>
+      <c r="W109" s="50"/>
+      <c r="X109" s="50"/>
+      <c r="Y109" s="50"/>
+      <c r="Z109" s="50"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7678,103 +7664,103 @@
         <f aca="false">D59</f>
         <v>45753</v>
       </c>
-      <c r="E110" s="74" t="n">
+      <c r="E110" s="75" t="n">
         <f aca="false">E64+E72+E80+E88+E108</f>
         <v>0</v>
       </c>
-      <c r="F110" s="74" t="n">
+      <c r="F110" s="75" t="n">
         <f aca="false">F64+F72+F80+F88+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="74" t="n">
+      <c r="G110" s="75" t="n">
         <f aca="false">G64+G72+G80+G88+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="74" t="n">
+      <c r="I110" s="75" t="n">
         <f aca="false">I64+I72+I80+I88+I108</f>
         <v>0</v>
       </c>
-      <c r="J110" s="74" t="n">
+      <c r="J110" s="75" t="n">
         <f aca="false">J64+J72+J80+J88+J108</f>
         <v>0</v>
       </c>
-      <c r="K110" s="74" t="n">
+      <c r="K110" s="75" t="n">
         <f aca="false">K64+K72+K80+K88+K108</f>
         <v>0</v>
       </c>
-      <c r="L110" s="50"/>
+      <c r="L110" s="53"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="50"/>
-      <c r="O110" s="74" t="n">
+      <c r="N110" s="53"/>
+      <c r="O110" s="75" t="n">
         <f aca="false">O64+O72+O80+O88+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="74" t="n">
+      <c r="Q110" s="75" t="n">
         <f aca="false">Q64+Q72+Q80+Q88+Q108</f>
         <v>0</v>
       </c>
-      <c r="R110" s="74" t="n">
+      <c r="R110" s="75" t="n">
         <f aca="false">R64+R72+R80+R88+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="74" t="n">
+      <c r="S110" s="75" t="n">
         <f aca="false">S64+S72+S80+S88+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="47"/>
-      <c r="U110" s="49"/>
-      <c r="V110" s="74" t="n">
+      <c r="T110" s="50"/>
+      <c r="U110" s="52"/>
+      <c r="V110" s="75" t="n">
         <f aca="false">V64+V72+V80+V88+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="74" t="n">
+      <c r="W110" s="75" t="n">
         <f aca="false">W64+W72+W80+W88+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="74" t="n">
+      <c r="X110" s="75" t="n">
         <f aca="false">X64+X72+X80+X88+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="74" t="n">
+      <c r="Y110" s="75" t="n">
         <f aca="false">Y64+Y72+Y80+Y88+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="74" t="n">
+      <c r="Z110" s="75" t="n">
         <f aca="false">Z64+Z72+Z80+Z88+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="85"/>
-      <c r="B111" s="86"/>
-      <c r="C111" s="87"/>
-      <c r="D111" s="88"/>
-      <c r="E111" s="89"/>
-      <c r="F111" s="89"/>
-      <c r="G111" s="89"/>
-      <c r="H111" s="90"/>
-      <c r="I111" s="89"/>
-      <c r="J111" s="89"/>
-      <c r="K111" s="89"/>
-      <c r="L111" s="89"/>
-      <c r="M111" s="90"/>
-      <c r="N111" s="89"/>
-      <c r="O111" s="91"/>
-      <c r="P111" s="92"/>
-      <c r="Q111" s="91"/>
-      <c r="R111" s="91"/>
-      <c r="S111" s="91"/>
-      <c r="T111" s="91"/>
-      <c r="U111" s="86"/>
-      <c r="V111" s="89"/>
-      <c r="W111" s="89"/>
-      <c r="X111" s="89"/>
-      <c r="Y111" s="91"/>
-      <c r="Z111" s="91"/>
-      <c r="AA111" s="93"/>
+      <c r="A111" s="86"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="88"/>
+      <c r="D111" s="89"/>
+      <c r="E111" s="90"/>
+      <c r="F111" s="90"/>
+      <c r="G111" s="90"/>
+      <c r="H111" s="91"/>
+      <c r="I111" s="90"/>
+      <c r="J111" s="90"/>
+      <c r="K111" s="90"/>
+      <c r="L111" s="90"/>
+      <c r="M111" s="91"/>
+      <c r="N111" s="90"/>
+      <c r="O111" s="92"/>
+      <c r="P111" s="93"/>
+      <c r="Q111" s="92"/>
+      <c r="R111" s="92"/>
+      <c r="S111" s="92"/>
+      <c r="T111" s="92"/>
+      <c r="U111" s="87"/>
+      <c r="V111" s="90"/>
+      <c r="W111" s="90"/>
+      <c r="X111" s="90"/>
+      <c r="Y111" s="92"/>
+      <c r="Z111" s="92"/>
+      <c r="AA111" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -7860,37 +7846,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="94" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="94" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="94" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="94" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="94" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="94" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="94" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="94" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="94" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="94" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="94" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="94" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="95" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="95" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="95" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="95" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="95" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="95" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="95" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="95" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="95" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="95" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="95"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="96"/>
+      <c r="A1" s="96"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7902,23 +7888,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="104"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="105"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7930,21 +7916,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="104"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="105"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -7956,31 +7942,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="97"/>
-      <c r="B4" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="108" t="s">
+      <c r="A4" s="98"/>
+      <c r="B4" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="102"/>
-      <c r="G4" s="109" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="108" t="s">
+      <c r="F4" s="103"/>
+      <c r="G4" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="102"/>
-      <c r="M4" s="110" t="s">
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="110"/>
-      <c r="O4" s="104"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="111" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="111"/>
+      <c r="O4" s="105"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -7992,25 +7978,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="97"/>
-      <c r="B5" s="98" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="98" t="s">
+      <c r="A5" s="98"/>
+      <c r="B5" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="99"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="104"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="100"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="105"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -8022,31 +8008,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="97"/>
-      <c r="B6" s="111" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112" t="n">
+      <c r="A6" s="98"/>
+      <c r="B6" s="112" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="113" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="111" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="112" t="n">
+      <c r="F6" s="103"/>
+      <c r="G6" s="112" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="113" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="102"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="104"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="105"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -8058,31 +8044,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="97"/>
-      <c r="B7" s="111" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="112" t="n">
+      <c r="A7" s="98"/>
+      <c r="B7" s="112" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="113" t="n">
         <f aca="false">Schedule!E72</f>
         <v>0</v>
       </c>
-      <c r="F7" s="102"/>
-      <c r="G7" s="111" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="112" t="n">
+      <c r="F7" s="103"/>
+      <c r="G7" s="112" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="113" t="n">
         <f aca="false">Schedule!V19+Schedule!V72</f>
         <v>0</v>
       </c>
-      <c r="L7" s="102"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="104"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="105"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -8094,31 +8080,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="97"/>
-      <c r="B8" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112" t="n">
+      <c r="A8" s="98"/>
+      <c r="B8" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="113" t="n">
         <f aca="false">Schedule!E80</f>
         <v>0</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="111" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="112" t="n">
+      <c r="F8" s="103"/>
+      <c r="G8" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="113" t="n">
         <f aca="false">Schedule!V27+Schedule!V80</f>
         <v>0</v>
       </c>
-      <c r="L8" s="102"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="104"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="105"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -8130,31 +8116,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="97"/>
-      <c r="B9" s="111" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="112" t="n">
+      <c r="A9" s="98"/>
+      <c r="B9" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113" t="n">
         <f aca="false">Schedule!E88</f>
         <v>0</v>
       </c>
-      <c r="F9" s="102"/>
-      <c r="G9" s="111" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="112" t="n">
+      <c r="F9" s="103"/>
+      <c r="G9" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="113" t="n">
         <f aca="false">Schedule!V35+Schedule!V88</f>
         <v>0</v>
       </c>
-      <c r="L9" s="102"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="104"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="105"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -8166,31 +8152,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="97"/>
-      <c r="B10" s="111" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112" t="n">
+      <c r="A10" s="98"/>
+      <c r="B10" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="111" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="112" t="n">
+      <c r="F10" s="103"/>
+      <c r="G10" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="113" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
         <v>0</v>
       </c>
-      <c r="L10" s="102"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="104"/>
+      <c r="L10" s="103"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="105"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8202,31 +8188,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="97"/>
-      <c r="B11" s="113" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="113"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114" t="n">
+      <c r="A11" s="98"/>
+      <c r="B11" s="114" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="115" t="n">
         <f aca="false">SUM(E6:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="102"/>
-      <c r="G11" s="115" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="115"/>
-      <c r="K11" s="114" t="n">
+      <c r="F11" s="103"/>
+      <c r="G11" s="116" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="115" t="n">
         <f aca="false">SUM(K6:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="104"/>
+      <c r="L11" s="103"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="111"/>
+      <c r="O11" s="105"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8238,21 +8224,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="97"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="102"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="104"/>
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="105"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8264,31 +8250,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="97"/>
-      <c r="B13" s="113" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="116" t="n">
+      <c r="A13" s="98"/>
+      <c r="B13" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="117" t="n">
         <f aca="false">[2]Mar!$AB$2</f>
         <v>0</v>
       </c>
-      <c r="F13" s="102"/>
-      <c r="G13" s="115" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="115"/>
-      <c r="K13" s="116" t="n">
+      <c r="F13" s="103"/>
+      <c r="G13" s="116" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="117" t="n">
         <f aca="false">[3]Mar!$V$2</f>
         <v>0</v>
       </c>
-      <c r="L13" s="102"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="104"/>
+      <c r="L13" s="103"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="105"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8300,21 +8286,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="97"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="104"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="105"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8326,33 +8312,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="97"/>
-      <c r="B15" s="117" t="str">
+      <c r="A15" s="98"/>
+      <c r="B15" s="118" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="118" t="n">
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="119" t="n">
         <f aca="false">E13-E11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="102"/>
-      <c r="G15" s="117" t="str">
+      <c r="F15" s="103"/>
+      <c r="G15" s="118" t="str">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="118" t="n">
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="119" t="n">
         <f aca="false">K13-K11</f>
         <v>0</v>
       </c>
-      <c r="L15" s="102"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="104"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="105"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8364,21 +8350,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="119"/>
-      <c r="B16" s="120"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="125"/>
+      <c r="A16" s="120"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="125"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="126"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8430,122 +8416,122 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="126" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="126" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="127" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="126" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="126" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="128"/>
-      <c r="B1" s="98"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="128"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="129"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="128"/>
-      <c r="B2" s="131"/>
-      <c r="C2" s="132" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133" t="n">
+      <c r="A2" s="129"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="n">
         <f aca="false">SUM(E8:E14)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="128"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="136" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="129"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="128"/>
-      <c r="B3" s="136" t="s">
-        <v>58</v>
+      <c r="A3" s="129"/>
+      <c r="B3" s="137" t="s">
+        <v>59</v>
       </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="128"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="129"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="128"/>
-      <c r="B4" s="49"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="128"/>
-    </row>
-    <row r="5" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="139"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="129"/>
+    </row>
+    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="140" t="s">
+      <c r="E5" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="140" t="s">
+      <c r="F5" s="141" t="s">
         <v>64</v>
       </c>
+      <c r="G5" s="141" t="s">
+        <v>65</v>
+      </c>
       <c r="H5" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="140" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
+      <c r="I5" s="141" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
       <c r="L5" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M5" s="139"/>
-    </row>
-    <row r="6" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="139"/>
+        <v>68</v>
+      </c>
+      <c r="M5" s="140"/>
+    </row>
+    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="140"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8553,273 +8539,273 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" s="140" t="s">
+      <c r="I6" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="140" t="s">
+      <c r="J6" s="141" t="s">
         <v>70</v>
       </c>
+      <c r="K6" s="141" t="s">
+        <v>71</v>
+      </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="139"/>
+      <c r="M6" s="140"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="128"/>
-      <c r="B7" s="49"/>
+      <c r="A7" s="129"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="128"/>
+      <c r="M7" s="129"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="128"/>
+      <c r="A8" s="129"/>
       <c r="B8" s="54"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="134" t="str">
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="135" t="str">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="134" t="str">
+      <c r="J8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="134" t="str">
+      <c r="K8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="128"/>
+      <c r="M8" s="129"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="128"/>
-      <c r="B9" s="49"/>
+      <c r="A9" s="129"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="128"/>
+      <c r="M9" s="129"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="128"/>
+      <c r="A10" s="129"/>
       <c r="B10" s="54"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="142"/>
-      <c r="I10" s="134" t="e">
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="134" t="str">
+      <c r="J10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="134" t="str">
+      <c r="K10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="128"/>
+      <c r="M10" s="129"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="128"/>
-      <c r="B11" s="49"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="52"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="128"/>
+      <c r="M11" s="129"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="128"/>
+      <c r="A12" s="129"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="134" t="e">
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="134" t="str">
+      <c r="J12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="134" t="str">
+      <c r="K12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="128"/>
+      <c r="M12" s="129"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="128"/>
-      <c r="B13" s="49"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="134"/>
-      <c r="J13" s="134"/>
-      <c r="K13" s="134"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="128"/>
+      <c r="M13" s="129"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="128"/>
+      <c r="A14" s="129"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="134" t="e">
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="134" t="str">
+      <c r="J14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="134" t="str">
+      <c r="K14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="128"/>
+      <c r="M14" s="129"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="128"/>
-      <c r="B15" s="49"/>
+      <c r="A15" s="129"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="128"/>
+      <c r="M15" s="129"/>
     </row>
     <row r="16" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="128"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="100"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="128"/>
+      <c r="A16" s="129"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="129"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="128"/>
-      <c r="B17" s="136" t="s">
-        <v>71</v>
+      <c r="A17" s="129"/>
+      <c r="B17" s="137" t="s">
+        <v>72</v>
       </c>
       <c r="C17" s="62"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
       <c r="H17" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="I17" s="131"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
+        <v>73</v>
+      </c>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="128"/>
+      <c r="M17" s="129"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="128"/>
-      <c r="B18" s="49"/>
+      <c r="A18" s="129"/>
+      <c r="B18" s="52"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
       <c r="L18" s="62"/>
-      <c r="M18" s="128"/>
-    </row>
-    <row r="19" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="139"/>
+      <c r="M18" s="129"/>
+    </row>
+    <row r="19" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="140"/>
       <c r="B19" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="140" t="s">
+      <c r="E19" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="140" t="s">
+      <c r="F19" s="141" t="s">
         <v>64</v>
       </c>
+      <c r="G19" s="141" t="s">
+        <v>65</v>
+      </c>
       <c r="H19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="140" t="s">
         <v>66</v>
       </c>
-      <c r="J19" s="140"/>
-      <c r="K19" s="140"/>
+      <c r="I19" s="141" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="141"/>
+      <c r="K19" s="141"/>
       <c r="L19" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M19" s="139"/>
-    </row>
-    <row r="20" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="139"/>
+        <v>68</v>
+      </c>
+      <c r="M19" s="140"/>
+    </row>
+    <row r="20" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="140"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8827,203 +8813,203 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
-      <c r="I20" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="J20" s="140" t="s">
+      <c r="I20" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="K20" s="140" t="s">
+      <c r="J20" s="141" t="s">
         <v>70</v>
       </c>
+      <c r="K20" s="141" t="s">
+        <v>71</v>
+      </c>
       <c r="L20" s="21"/>
-      <c r="M20" s="139"/>
-    </row>
-    <row r="21" s="141" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="139"/>
-      <c r="B21" s="143"/>
-      <c r="C21" s="143"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="139"/>
+      <c r="M20" s="140"/>
+    </row>
+    <row r="21" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="140"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="140"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="128"/>
+      <c r="A22" s="129"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="142"/>
-      <c r="I22" s="134" t="str">
+      <c r="E22" s="134"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="135" t="str">
         <f aca="false">IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="134" t="str">
+      <c r="J22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="134" t="str">
+      <c r="K22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="128"/>
+      <c r="M22" s="129"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="128"/>
-      <c r="B23" s="49"/>
+      <c r="A23" s="129"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="134"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="128"/>
+      <c r="M23" s="129"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="128"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="142"/>
-      <c r="I24" s="134" t="e">
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="134" t="str">
+      <c r="J24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="134" t="str">
+      <c r="K24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="128"/>
+      <c r="M24" s="129"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="128"/>
-      <c r="B25" s="49"/>
+      <c r="A25" s="129"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="134"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="135"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="128"/>
+      <c r="M25" s="129"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="128"/>
+      <c r="A26" s="129"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="142"/>
-      <c r="I26" s="134" t="e">
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="134" t="str">
+      <c r="J26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="134" t="str">
+      <c r="K26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="128"/>
+      <c r="M26" s="129"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="128"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="129"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="134"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="134"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="128"/>
+      <c r="M27" s="129"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="128"/>
+      <c r="A28" s="129"/>
       <c r="B28" s="54"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="142"/>
-      <c r="I28" s="134" t="e">
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="143"/>
+      <c r="I28" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="134" t="str">
+      <c r="J28" s="135" t="str">
         <f aca="false">IF(H28&gt;0,I28-K28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="134" t="str">
+      <c r="K28" s="135" t="str">
         <f aca="false">IF(H28&gt;0,G28/H28," ")</f>
         <v> </v>
       </c>
       <c r="L28" s="56"/>
-      <c r="M28" s="128"/>
+      <c r="M28" s="129"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="128"/>
-      <c r="B29" s="49"/>
+      <c r="A29" s="129"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="134"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="135"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="128"/>
+      <c r="M29" s="129"/>
     </row>
     <row r="30" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="128"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="128"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="128"/>
+      <c r="A30" s="129"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="129"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
   </si>
   <si>
-    <t xml:space="preserve">Laptop (0.5 years old)</t>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">Existing Land &amp; Property</t>
@@ -250,10 +250,16 @@
     <t xml:space="preserve">Computers</t>
   </si>
   <si>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Existing Computers</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing over £</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van (2.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing under £</t>
@@ -266,9 +272,6 @@
   </si>
   <si>
     <t xml:space="preserve">NEW FIXED ASSETS Bought AFTER </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">New Land &amp; Property</t>
@@ -752,7 +755,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -937,8 +940,28 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -949,26 +972,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1015,10 +1018,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1683,7 +1682,7 @@
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>0</v>
+        <v>10098</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
@@ -1934,24 +1933,45 @@
         <v>22</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="44" t="n">
+        <f aca="false">[1]Admin!$B$4</f>
+        <v>45753</v>
+      </c>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="50"/>
+      <c r="W6" s="50"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42"/>
+      <c r="B7" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="45" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y6" s="7" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="45"/>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">[1]Admin!$G$13</f>
         <v>0</v>
       </c>
@@ -1959,20 +1979,20 @@
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
-      <c r="M7" s="49"/>
+      <c r="M7" s="46"/>
       <c r="N7" s="45"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="50"/>
-      <c r="Z7" s="50"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1982,7 +2002,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="53" t="str">
+      <c r="G8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -1990,39 +2010,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="53" t="str">
+      <c r="I8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="53" t="str">
+      <c r="J8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="53" t="str">
+      <c r="K8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
         <v> </v>
       </c>
-      <c r="L8" s="53"/>
+      <c r="L8" s="50"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="53" t="str">
+      <c r="W8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="53" t="str">
+      <c r="X8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2032,7 +2052,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="53" t="str">
+      <c r="G9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -2040,39 +2060,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="53" t="str">
+      <c r="I9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="53" t="str">
+      <c r="J9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="53" t="str">
+      <c r="K9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
         <v> </v>
       </c>
-      <c r="L9" s="53"/>
+      <c r="L9" s="50"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="53" t="str">
+      <c r="W9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="53" t="str">
+      <c r="X9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="50"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2082,7 +2102,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="53" t="str">
+      <c r="G10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -2090,39 +2110,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="53" t="str">
+      <c r="I10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="53" t="str">
+      <c r="J10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="53" t="str">
+      <c r="K10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
         <v> </v>
       </c>
-      <c r="L10" s="53"/>
+      <c r="L10" s="50"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="53" t="str">
+      <c r="W10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="53" t="str">
+      <c r="X10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="50"/>
-      <c r="Z10" s="50"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="47"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2157,9 +2177,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="53"/>
+      <c r="L11" s="50"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="53"/>
+      <c r="N11" s="50"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -2177,8 +2197,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="50"/>
-      <c r="U11" s="52"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="49"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2206,62 +2226,62 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="53"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="53"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="66"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="67" t="n">
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="66" t="n">
         <f aca="false">[1]Admin!$G$14</f>
         <v>0.1</v>
       </c>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="50"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2271,7 +2291,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2279,48 +2299,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="53" t="str">
+      <c r="J14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="53" t="str">
+      <c r="K14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
         <v> </v>
       </c>
-      <c r="L14" s="53"/>
+      <c r="L14" s="50"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50" t="str">
+      <c r="N14" s="50"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="50" t="str">
+      <c r="S14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="50"/>
+      <c r="T14" s="47"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="53" t="str">
+      <c r="W14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="53" t="str">
+      <c r="X14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="50" t="str">
+      <c r="Y14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="50" t="str">
+      <c r="Z14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2333,7 +2353,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="53" t="str">
+      <c r="G15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2341,48 +2361,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="53" t="str">
+      <c r="I15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="53" t="str">
+      <c r="J15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="53" t="str">
+      <c r="K15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
         <v> </v>
       </c>
-      <c r="L15" s="53"/>
+      <c r="L15" s="50"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50" t="str">
+      <c r="N15" s="50"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="50" t="str">
+      <c r="S15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="50"/>
+      <c r="T15" s="47"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="53" t="str">
+      <c r="W15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="53" t="str">
+      <c r="X15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="50" t="str">
+      <c r="Y15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="50" t="str">
+      <c r="Z15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2395,7 +2415,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2403,48 +2423,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="53" t="str">
+      <c r="J16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="53" t="str">
+      <c r="K16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
         <v> </v>
       </c>
-      <c r="L16" s="53"/>
+      <c r="L16" s="50"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50" t="str">
+      <c r="N16" s="50"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="50" t="str">
+      <c r="S16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="50"/>
+      <c r="T16" s="47"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="53" t="str">
+      <c r="W16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="53" t="str">
+      <c r="X16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="50" t="str">
+      <c r="Y16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="50" t="str">
+      <c r="Z16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2457,7 +2477,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="53" t="str">
+      <c r="G17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2465,48 +2485,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="53" t="str">
+      <c r="I17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="53" t="str">
+      <c r="J17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="53" t="str">
+      <c r="K17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
         <v> </v>
       </c>
-      <c r="L17" s="53"/>
+      <c r="L17" s="50"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50" t="str">
+      <c r="N17" s="50"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="50" t="str">
+      <c r="S17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="50"/>
+      <c r="T17" s="47"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="53" t="str">
+      <c r="W17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="53" t="str">
+      <c r="X17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="50" t="str">
+      <c r="Y17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="50" t="str">
+      <c r="Z17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2519,7 +2539,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="53" t="str">
+      <c r="G18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2527,48 +2547,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="53" t="str">
+      <c r="J18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="53" t="str">
+      <c r="K18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
         <v> </v>
       </c>
-      <c r="L18" s="53"/>
+      <c r="L18" s="50"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50" t="str">
+      <c r="N18" s="50"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="50" t="str">
+      <c r="S18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="50"/>
+      <c r="T18" s="47"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="53" t="str">
+      <c r="W18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="53" t="str">
+      <c r="X18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="50" t="str">
+      <c r="Y18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="50" t="str">
+      <c r="Z18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2606,9 +2626,9 @@
         <f aca="false">SUM(K14:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="53"/>
+      <c r="L19" s="50"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="53"/>
+      <c r="N19" s="50"/>
       <c r="O19" s="61" t="n">
         <f aca="false">SUM(O14:O18)</f>
         <v>0</v>
@@ -2626,8 +2646,8 @@
         <f aca="false">SUM(S14:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="50"/>
-      <c r="U19" s="52"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="49"/>
       <c r="V19" s="60" t="n">
         <f aca="false">SUM(V14:V18)</f>
         <v>0</v>
@@ -2655,62 +2675,62 @@
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
       <c r="H20" s="58"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
       <c r="P20" s="62"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="52"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
+      <c r="Z20" s="50"/>
       <c r="AA20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="42"/>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="66"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="67" t="n">
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="66" t="n">
         <f aca="false">[1]Admin!$G$15</f>
         <v>0.2</v>
       </c>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="50"/>
-      <c r="Z21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="50"/>
+      <c r="W21" s="50"/>
+      <c r="X21" s="50"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="47"/>
       <c r="AA21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2720,7 +2740,7 @@
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
       <c r="F22" s="57"/>
-      <c r="G22" s="53" t="str">
+      <c r="G22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,E22-F22," ")</f>
         <v> </v>
       </c>
@@ -2728,48 +2748,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I22" s="53" t="str">
+      <c r="I22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,MIN(E22*H22,G22)," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="53" t="str">
+      <c r="J22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,F22+I22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="53" t="str">
+      <c r="K22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,E22-J22," ")</f>
         <v> </v>
       </c>
-      <c r="L22" s="53"/>
+      <c r="L22" s="50"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="68"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50" t="str">
+      <c r="N22" s="50"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47" t="str">
         <f aca="false">IF(O22&gt;0,O22*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S22" s="50" t="str">
+      <c r="S22" s="47" t="str">
         <f aca="false">IF(O22&gt;0,O22-R22," ")</f>
         <v> </v>
       </c>
-      <c r="T22" s="50"/>
+      <c r="T22" s="47"/>
       <c r="U22" s="54"/>
       <c r="V22" s="57"/>
-      <c r="W22" s="53" t="str">
+      <c r="W22" s="50" t="str">
         <f aca="false">IF(V22&gt;0,E22," ")</f>
         <v> </v>
       </c>
-      <c r="X22" s="53" t="str">
+      <c r="X22" s="50" t="str">
         <f aca="false">IF(V22&gt;0,J22," ")</f>
         <v> </v>
       </c>
-      <c r="Y22" s="50" t="str">
+      <c r="Y22" s="47" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&lt;S22,S22-V22," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z22" s="50" t="str">
+      <c r="Z22" s="47" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&gt;S22,V22-S22," ")," ")</f>
         <v> </v>
       </c>
@@ -2782,7 +2802,7 @@
       <c r="D23" s="56"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="53" t="str">
+      <c r="G23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,E23-F23," ")</f>
         <v> </v>
       </c>
@@ -2790,48 +2810,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I23" s="53" t="str">
+      <c r="I23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,MIN(E23*H23,G23)," ")</f>
         <v> </v>
       </c>
-      <c r="J23" s="53" t="str">
+      <c r="J23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,F23+I23," ")</f>
         <v> </v>
       </c>
-      <c r="K23" s="53" t="str">
+      <c r="K23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,E23-J23," ")</f>
         <v> </v>
       </c>
-      <c r="L23" s="53"/>
+      <c r="L23" s="50"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50" t="str">
+      <c r="N23" s="50"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="47" t="str">
         <f aca="false">IF(O23&gt;0,O23*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S23" s="50" t="str">
+      <c r="S23" s="47" t="str">
         <f aca="false">IF(O23&gt;0,O23-R23," ")</f>
         <v> </v>
       </c>
-      <c r="T23" s="50"/>
+      <c r="T23" s="47"/>
       <c r="U23" s="54"/>
       <c r="V23" s="57"/>
-      <c r="W23" s="53" t="str">
+      <c r="W23" s="50" t="str">
         <f aca="false">IF(V23&gt;0,E23," ")</f>
         <v> </v>
       </c>
-      <c r="X23" s="53" t="str">
+      <c r="X23" s="50" t="str">
         <f aca="false">IF(V23&gt;0,J23," ")</f>
         <v> </v>
       </c>
-      <c r="Y23" s="50" t="str">
+      <c r="Y23" s="47" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&lt;S23,S23-V23," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z23" s="50" t="str">
+      <c r="Z23" s="47" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&gt;S23,V23-S23," ")," ")</f>
         <v> </v>
       </c>
@@ -2844,7 +2864,7 @@
       <c r="D24" s="56"/>
       <c r="E24" s="57"/>
       <c r="F24" s="57"/>
-      <c r="G24" s="53" t="str">
+      <c r="G24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,E24-F24," ")</f>
         <v> </v>
       </c>
@@ -2852,48 +2872,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I24" s="53" t="str">
+      <c r="I24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,MIN(E24*H24,G24)," ")</f>
         <v> </v>
       </c>
-      <c r="J24" s="53" t="str">
+      <c r="J24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,F24+I24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="53" t="str">
+      <c r="K24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,E24-J24," ")</f>
         <v> </v>
       </c>
-      <c r="L24" s="53"/>
+      <c r="L24" s="50"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50" t="str">
+      <c r="N24" s="50"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47" t="str">
         <f aca="false">IF(O24&gt;0,O24*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S24" s="50" t="str">
+      <c r="S24" s="47" t="str">
         <f aca="false">IF(O24&gt;0,O24-R24," ")</f>
         <v> </v>
       </c>
-      <c r="T24" s="50"/>
+      <c r="T24" s="47"/>
       <c r="U24" s="54"/>
       <c r="V24" s="57"/>
-      <c r="W24" s="53" t="str">
+      <c r="W24" s="50" t="str">
         <f aca="false">IF(V24&gt;0,E24," ")</f>
         <v> </v>
       </c>
-      <c r="X24" s="53" t="str">
+      <c r="X24" s="50" t="str">
         <f aca="false">IF(V24&gt;0,J24," ")</f>
         <v> </v>
       </c>
-      <c r="Y24" s="50" t="str">
+      <c r="Y24" s="47" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&lt;S24,S24-V24," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z24" s="50" t="str">
+      <c r="Z24" s="47" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&gt;S24,V24-S24," ")," ")</f>
         <v> </v>
       </c>
@@ -2906,7 +2926,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="53" t="str">
+      <c r="G25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2914,48 +2934,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="53" t="str">
+      <c r="I25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="53" t="str">
+      <c r="J25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="53" t="str">
+      <c r="K25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
         <v> </v>
       </c>
-      <c r="L25" s="53"/>
+      <c r="L25" s="50"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50" t="str">
+      <c r="N25" s="50"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="50" t="str">
+      <c r="S25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="50"/>
+      <c r="T25" s="47"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="53" t="str">
+      <c r="W25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="53" t="str">
+      <c r="X25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="50" t="str">
+      <c r="Y25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="50" t="str">
+      <c r="Z25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2968,7 +2988,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="53" t="str">
+      <c r="G26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -2976,48 +2996,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="53" t="str">
+      <c r="I26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="53" t="str">
+      <c r="J26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="53" t="str">
+      <c r="K26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
         <v> </v>
       </c>
-      <c r="L26" s="53"/>
+      <c r="L26" s="50"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50" t="str">
+      <c r="N26" s="50"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="50" t="str">
+      <c r="S26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="50"/>
+      <c r="T26" s="47"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="53" t="str">
+      <c r="W26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="53" t="str">
+      <c r="X26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="50" t="str">
+      <c r="Y26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="50" t="str">
+      <c r="Z26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -3055,9 +3075,9 @@
         <f aca="false">SUM(K22:K26)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="53"/>
+      <c r="L27" s="50"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="53"/>
+      <c r="N27" s="50"/>
       <c r="O27" s="61" t="n">
         <f aca="false">SUM(O22:O26)</f>
         <v>0</v>
@@ -3075,8 +3095,8 @@
         <f aca="false">SUM(S22:S26)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="50"/>
-      <c r="U27" s="52"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="49"/>
       <c r="V27" s="60" t="n">
         <f aca="false">SUM(V22:V26)</f>
         <v>0</v>
@@ -3104,121 +3124,120 @@
       <c r="B28" s="63"/>
       <c r="C28" s="64"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
       <c r="H28" s="58"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
       <c r="P28" s="62"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="53"/>
-      <c r="X28" s="53"/>
-      <c r="Y28" s="53"/>
-      <c r="Z28" s="53"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="50"/>
+      <c r="W28" s="50"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
       <c r="AA28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="42"/>
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="66"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="67" t="n">
+      <c r="C29" s="51"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="66" t="n">
         <f aca="false">[1]Admin!$G$16</f>
         <v>0.33</v>
       </c>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="53"/>
-      <c r="W29" s="53"/>
-      <c r="X29" s="53"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="50"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="47"/>
+      <c r="Z29" s="47"/>
       <c r="AA29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="42"/>
       <c r="B30" s="54"/>
       <c r="C30" s="55"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="53" t="str">
-        <f aca="false">IF(E30&gt;0,E30-F30," ")</f>
-        <v> </v>
+      <c r="D30" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>270</v>
       </c>
       <c r="H30" s="58" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I30" s="53" t="str">
+      <c r="I30" s="50" t="str">
         <f aca="false">IF(E30&gt;0,MIN(E30*H30,G30)," ")</f>
         <v> </v>
       </c>
-      <c r="J30" s="53" t="str">
+      <c r="J30" s="50" t="str">
         <f aca="false">IF(E30&gt;0,F30+I30," ")</f>
         <v> </v>
       </c>
-      <c r="K30" s="53" t="str">
+      <c r="K30" s="50" t="str">
         <f aca="false">IF(E30&gt;0,E30-J30," ")</f>
         <v> </v>
       </c>
-      <c r="L30" s="53"/>
+      <c r="L30" s="50"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50" t="str">
+      <c r="N30" s="50"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="47"/>
+      <c r="R30" s="47" t="str">
         <f aca="false">IF(O30&gt;0,O30*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S30" s="50" t="str">
+      <c r="S30" s="47" t="str">
         <f aca="false">IF(O30&gt;0,O30-R30," ")</f>
         <v> </v>
       </c>
-      <c r="T30" s="50"/>
+      <c r="T30" s="47"/>
       <c r="U30" s="54"/>
       <c r="V30" s="57"/>
-      <c r="W30" s="53" t="str">
+      <c r="W30" s="50" t="str">
         <f aca="false">IF(V30&gt;0,E30," ")</f>
         <v> </v>
       </c>
-      <c r="X30" s="53" t="str">
+      <c r="X30" s="50" t="str">
         <f aca="false">IF(V30&gt;0,J30," ")</f>
         <v> </v>
       </c>
-      <c r="Y30" s="50" t="str">
+      <c r="Y30" s="47" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&lt;S30,S30-V30," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z30" s="50" t="str">
+      <c r="Z30" s="47" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&gt;S30,V30-S30," ")," ")</f>
         <v> </v>
       </c>
@@ -3231,7 +3250,7 @@
       <c r="D31" s="56"/>
       <c r="E31" s="57"/>
       <c r="F31" s="57"/>
-      <c r="G31" s="53" t="str">
+      <c r="G31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,E31-F31," ")</f>
         <v> </v>
       </c>
@@ -3239,48 +3258,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I31" s="53" t="str">
+      <c r="I31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,MIN(E31*H31,G31)," ")</f>
         <v> </v>
       </c>
-      <c r="J31" s="53" t="str">
+      <c r="J31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,F31+I31," ")</f>
         <v> </v>
       </c>
-      <c r="K31" s="53" t="str">
+      <c r="K31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,E31-J31," ")</f>
         <v> </v>
       </c>
-      <c r="L31" s="53"/>
+      <c r="L31" s="50"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="68"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50" t="str">
+      <c r="N31" s="50"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="47"/>
+      <c r="R31" s="47" t="str">
         <f aca="false">IF(O31&gt;0,O31*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S31" s="50" t="str">
+      <c r="S31" s="47" t="str">
         <f aca="false">IF(O31&gt;0,O31-R31," ")</f>
         <v> </v>
       </c>
-      <c r="T31" s="50"/>
+      <c r="T31" s="47"/>
       <c r="U31" s="54"/>
       <c r="V31" s="57"/>
-      <c r="W31" s="53" t="str">
+      <c r="W31" s="50" t="str">
         <f aca="false">IF(V31&gt;0,E31," ")</f>
         <v> </v>
       </c>
-      <c r="X31" s="53" t="str">
+      <c r="X31" s="50" t="str">
         <f aca="false">IF(V31&gt;0,J31," ")</f>
         <v> </v>
       </c>
-      <c r="Y31" s="50" t="str">
+      <c r="Y31" s="47" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&lt;S31,S31-V31," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z31" s="50" t="str">
+      <c r="Z31" s="47" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&gt;S31,V31-S31," ")," ")</f>
         <v> </v>
       </c>
@@ -3293,7 +3312,7 @@
       <c r="D32" s="56"/>
       <c r="E32" s="57"/>
       <c r="F32" s="57"/>
-      <c r="G32" s="53" t="str">
+      <c r="G32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,E32-F32," ")</f>
         <v> </v>
       </c>
@@ -3301,48 +3320,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I32" s="53" t="str">
+      <c r="I32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,MIN(E32*H32,G32)," ")</f>
         <v> </v>
       </c>
-      <c r="J32" s="53" t="str">
+      <c r="J32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,F32+I32," ")</f>
         <v> </v>
       </c>
-      <c r="K32" s="53" t="str">
+      <c r="K32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,E32-J32," ")</f>
         <v> </v>
       </c>
-      <c r="L32" s="53"/>
+      <c r="L32" s="50"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="68"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50" t="str">
+      <c r="N32" s="50"/>
+      <c r="O32" s="67"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="47"/>
+      <c r="R32" s="47" t="str">
         <f aca="false">IF(O32&gt;0,O32*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S32" s="50" t="str">
+      <c r="S32" s="47" t="str">
         <f aca="false">IF(O32&gt;0,O32-R32," ")</f>
         <v> </v>
       </c>
-      <c r="T32" s="50"/>
+      <c r="T32" s="47"/>
       <c r="U32" s="54"/>
       <c r="V32" s="57"/>
-      <c r="W32" s="53" t="str">
+      <c r="W32" s="50" t="str">
         <f aca="false">IF(V32&gt;0,E32," ")</f>
         <v> </v>
       </c>
-      <c r="X32" s="53" t="str">
+      <c r="X32" s="50" t="str">
         <f aca="false">IF(V32&gt;0,J32," ")</f>
         <v> </v>
       </c>
-      <c r="Y32" s="50" t="str">
+      <c r="Y32" s="47" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&lt;S32,S32-V32," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z32" s="50" t="str">
+      <c r="Z32" s="47" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&gt;S32,V32-S32," ")," ")</f>
         <v> </v>
       </c>
@@ -3355,7 +3374,7 @@
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
       <c r="F33" s="57"/>
-      <c r="G33" s="53" t="str">
+      <c r="G33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
         <v> </v>
       </c>
@@ -3363,48 +3382,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="53" t="str">
+      <c r="I33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="53" t="str">
+      <c r="J33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="53" t="str">
+      <c r="K33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
         <v> </v>
       </c>
-      <c r="L33" s="53"/>
+      <c r="L33" s="50"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="68"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50" t="str">
+      <c r="N33" s="50"/>
+      <c r="O33" s="67"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="47"/>
+      <c r="R33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="50" t="str">
+      <c r="S33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="50"/>
+      <c r="T33" s="47"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="53" t="str">
+      <c r="W33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="53" t="str">
+      <c r="X33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="50" t="str">
+      <c r="Y33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="50" t="str">
+      <c r="Z33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3417,7 +3436,7 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="53" t="str">
+      <c r="G34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
         <v> </v>
       </c>
@@ -3425,48 +3444,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="53" t="str">
+      <c r="I34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="53" t="str">
+      <c r="J34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="53" t="str">
+      <c r="K34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
         <v> </v>
       </c>
-      <c r="L34" s="53"/>
+      <c r="L34" s="50"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="68"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="50" t="str">
+      <c r="N34" s="50"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="50" t="str">
+      <c r="S34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="50"/>
+      <c r="T34" s="47"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="53" t="str">
+      <c r="W34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="53" t="str">
+      <c r="X34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="50" t="str">
+      <c r="Y34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="50" t="str">
+      <c r="Z34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3475,7 +3494,7 @@
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="42"/>
       <c r="B35" s="59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="59"/>
@@ -3485,7 +3504,7 @@
       </c>
       <c r="F35" s="60" t="n">
         <f aca="false">SUM(F30:F34)</f>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="G35" s="61" t="n">
         <f aca="false">SUM(G30:G34)</f>
@@ -3504,9 +3523,9 @@
         <f aca="false">SUM(K30:K34)</f>
         <v>0</v>
       </c>
-      <c r="L35" s="53"/>
+      <c r="L35" s="50"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="53"/>
+      <c r="N35" s="50"/>
       <c r="O35" s="61" t="n">
         <f aca="false">SUM(O30:O34)</f>
         <v>0</v>
@@ -3524,8 +3543,8 @@
         <f aca="false">SUM(S30:S34)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="50"/>
-      <c r="U35" s="52"/>
+      <c r="T35" s="47"/>
+      <c r="U35" s="49"/>
       <c r="V35" s="60" t="n">
         <f aca="false">SUM(V30:V34)</f>
         <v>0</v>
@@ -3553,126 +3572,125 @@
       <c r="B36" s="63"/>
       <c r="C36" s="64"/>
       <c r="D36" s="65"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
       <c r="H36" s="58"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="50"/>
       <c r="P36" s="62"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="53"/>
-      <c r="W36" s="53"/>
-      <c r="X36" s="53"/>
-      <c r="Y36" s="53"/>
-      <c r="Z36" s="53"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="50"/>
+      <c r="S36" s="50"/>
+      <c r="T36" s="47"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="50"/>
+      <c r="W36" s="50"/>
+      <c r="X36" s="50"/>
+      <c r="Y36" s="50"/>
+      <c r="Z36" s="50"/>
       <c r="AA36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="42"/>
-      <c r="B37" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="70"/>
-      <c r="D37" s="71" t="n">
+      <c r="B37" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="67" t="n">
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="66" t="n">
         <f aca="false">[1]Admin!$G$17</f>
         <v>0.25</v>
       </c>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="72"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
       <c r="P37" s="62"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="73"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="53"/>
-      <c r="W37" s="53"/>
-      <c r="X37" s="53"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="53"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="50"/>
+      <c r="S37" s="50"/>
+      <c r="T37" s="72"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="50"/>
+      <c r="W37" s="50"/>
+      <c r="X37" s="50"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
       <c r="AA37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="42"/>
       <c r="B38" s="54"/>
       <c r="C38" s="55"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="53" t="str">
-        <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
-        <v> </v>
+      <c r="D38" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>9828</v>
       </c>
       <c r="H38" s="58" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I38" s="53" t="str">
+      <c r="I38" s="50" t="str">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
         <v> </v>
       </c>
-      <c r="J38" s="53" t="str">
+      <c r="J38" s="50" t="str">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
         <v> </v>
       </c>
-      <c r="K38" s="53" t="str">
+      <c r="K38" s="50" t="str">
         <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
         <v> </v>
       </c>
-      <c r="L38" s="53"/>
-      <c r="M38" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="53"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50" t="str">
+      <c r="L38" s="50"/>
+      <c r="M38" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="50"/>
+      <c r="O38" s="67"/>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47" t="str">
         <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
         <v> </v>
       </c>
-      <c r="S38" s="50" t="str">
+      <c r="S38" s="47" t="str">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
         <v> </v>
       </c>
-      <c r="T38" s="50"/>
+      <c r="T38" s="47"/>
       <c r="U38" s="54"/>
       <c r="V38" s="57"/>
-      <c r="W38" s="53" t="str">
+      <c r="W38" s="50" t="str">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
         <v> </v>
       </c>
-      <c r="X38" s="53" t="str">
+      <c r="X38" s="50" t="str">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
         <v> </v>
       </c>
-      <c r="Y38" s="50" t="str">
+      <c r="Y38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z38" s="50" t="str">
+      <c r="Z38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
@@ -3685,7 +3703,7 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="53" t="str">
+      <c r="G39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
         <v> </v>
       </c>
@@ -3693,50 +3711,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I39" s="53" t="str">
+      <c r="I39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="53" t="str">
+      <c r="J39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="53" t="str">
+      <c r="K39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
         <v> </v>
       </c>
-      <c r="L39" s="53"/>
-      <c r="M39" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="53"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50" t="str">
+      <c r="L39" s="50"/>
+      <c r="M39" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="50"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="47"/>
+      <c r="R39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="50" t="str">
+      <c r="S39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="50"/>
+      <c r="T39" s="47"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="53" t="str">
+      <c r="W39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="53" t="str">
+      <c r="X39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="50" t="str">
+      <c r="Y39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,(S39-V39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="50" t="str">
+      <c r="Z39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,(V39-S39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
@@ -3749,7 +3767,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="53" t="str">
+      <c r="G40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
         <v> </v>
       </c>
@@ -3757,50 +3775,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I40" s="53" t="str">
+      <c r="I40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="53" t="str">
+      <c r="J40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="53" t="str">
+      <c r="K40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
         <v> </v>
       </c>
-      <c r="L40" s="53"/>
-      <c r="M40" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="53"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50" t="str">
+      <c r="L40" s="50"/>
+      <c r="M40" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="50"/>
+      <c r="O40" s="67"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="47"/>
+      <c r="R40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="50" t="str">
+      <c r="S40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="50"/>
+      <c r="T40" s="47"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="53" t="str">
+      <c r="W40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="53" t="str">
+      <c r="X40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="50" t="str">
+      <c r="Y40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,(S40-V40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="50" t="str">
+      <c r="Z40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,(V40-S40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
@@ -3813,7 +3831,7 @@
       <c r="D41" s="56"/>
       <c r="E41" s="57"/>
       <c r="F41" s="57"/>
-      <c r="G41" s="53" t="str">
+      <c r="G41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,E41-F41," ")</f>
         <v> </v>
       </c>
@@ -3821,50 +3839,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I41" s="53" t="str">
+      <c r="I41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,MIN(E41*H41,G41)," ")</f>
         <v> </v>
       </c>
-      <c r="J41" s="53" t="str">
+      <c r="J41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,F41+I41," ")</f>
         <v> </v>
       </c>
-      <c r="K41" s="53" t="str">
+      <c r="K41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,E41-J41," ")</f>
         <v> </v>
       </c>
-      <c r="L41" s="53"/>
-      <c r="M41" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="53"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50" t="str">
+      <c r="L41" s="50"/>
+      <c r="M41" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="50"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="47"/>
+      <c r="R41" s="47" t="str">
         <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
         <v> </v>
       </c>
-      <c r="S41" s="50" t="str">
+      <c r="S41" s="47" t="str">
         <f aca="false">IF(O41&gt;0,O41-R41," ")</f>
         <v> </v>
       </c>
-      <c r="T41" s="50"/>
+      <c r="T41" s="47"/>
       <c r="U41" s="54"/>
       <c r="V41" s="57"/>
-      <c r="W41" s="53" t="str">
+      <c r="W41" s="50" t="str">
         <f aca="false">IF(V41&gt;0,E41," ")</f>
         <v> </v>
       </c>
-      <c r="X41" s="53" t="str">
+      <c r="X41" s="50" t="str">
         <f aca="false">IF(V41&gt;0,J41," ")</f>
         <v> </v>
       </c>
-      <c r="Y41" s="50" t="str">
+      <c r="Y41" s="47" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&lt;S41,(S41-V41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z41" s="50" t="str">
+      <c r="Z41" s="47" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&gt;S41,(V41-S41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
@@ -3877,7 +3895,7 @@
       <c r="D42" s="56"/>
       <c r="E42" s="57"/>
       <c r="F42" s="57"/>
-      <c r="G42" s="53" t="str">
+      <c r="G42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,E42-F42," ")</f>
         <v> </v>
       </c>
@@ -3885,50 +3903,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I42" s="53" t="str">
+      <c r="I42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,MIN(E42*H42,G42)," ")</f>
         <v> </v>
       </c>
-      <c r="J42" s="53" t="str">
+      <c r="J42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,F42+I42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="53" t="str">
+      <c r="K42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,E42-J42," ")</f>
         <v> </v>
       </c>
-      <c r="L42" s="53"/>
-      <c r="M42" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="53"/>
-      <c r="O42" s="68"/>
-      <c r="P42" s="51"/>
-      <c r="Q42" s="50"/>
-      <c r="R42" s="50" t="str">
+      <c r="L42" s="50"/>
+      <c r="M42" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="50"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="48"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47" t="str">
         <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
         <v> </v>
       </c>
-      <c r="S42" s="50" t="str">
+      <c r="S42" s="47" t="str">
         <f aca="false">IF(O42&gt;0,O42-R42," ")</f>
         <v> </v>
       </c>
-      <c r="T42" s="50"/>
+      <c r="T42" s="47"/>
       <c r="U42" s="54"/>
       <c r="V42" s="57"/>
-      <c r="W42" s="53" t="str">
+      <c r="W42" s="50" t="str">
         <f aca="false">IF(V42&gt;0,E42," ")</f>
         <v> </v>
       </c>
-      <c r="X42" s="53" t="str">
+      <c r="X42" s="50" t="str">
         <f aca="false">IF(V42&gt;0,J42," ")</f>
         <v> </v>
       </c>
-      <c r="Y42" s="50" t="str">
+      <c r="Y42" s="47" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&lt;S42,(S42-V42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z42" s="50" t="str">
+      <c r="Z42" s="47" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&gt;S42,(V42-S42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
@@ -3936,36 +3954,36 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="71" t="n">
+      <c r="B43" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="69"/>
+      <c r="D43" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
       <c r="H43" s="58"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
       <c r="M43" s="58"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="53"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="47"/>
+      <c r="P43" s="48"/>
+      <c r="Q43" s="47"/>
+      <c r="R43" s="47"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="47"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="50"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="47"/>
+      <c r="Z43" s="47"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3975,7 +3993,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="53" t="str">
+      <c r="G44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
         <v> </v>
       </c>
@@ -3983,50 +4001,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="53" t="str">
+      <c r="I44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="53" t="str">
+      <c r="J44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="53" t="str">
+      <c r="K44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
         <v> </v>
       </c>
-      <c r="L44" s="53"/>
-      <c r="M44" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="53"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50" t="str">
+      <c r="L44" s="50"/>
+      <c r="M44" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="50"/>
+      <c r="O44" s="67"/>
+      <c r="P44" s="48"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="50" t="str">
+      <c r="S44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="50"/>
+      <c r="T44" s="47"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="53" t="str">
+      <c r="W44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="53" t="str">
+      <c r="X44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="50" t="str">
+      <c r="Y44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="50" t="str">
+      <c r="Z44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -4039,7 +4057,7 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="53" t="str">
+      <c r="G45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
         <v> </v>
       </c>
@@ -4047,50 +4065,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="53" t="str">
+      <c r="I45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="53" t="str">
+      <c r="J45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="53" t="str">
+      <c r="K45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
         <v> </v>
       </c>
-      <c r="L45" s="53"/>
-      <c r="M45" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="53"/>
-      <c r="O45" s="68"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50" t="str">
+      <c r="L45" s="50"/>
+      <c r="M45" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="50"/>
+      <c r="O45" s="67"/>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="50" t="str">
+      <c r="S45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="50"/>
+      <c r="T45" s="47"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="53" t="str">
+      <c r="W45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="53" t="str">
+      <c r="X45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="50" t="str">
+      <c r="Y45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="50" t="str">
+      <c r="Z45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -4103,7 +4121,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="53" t="str">
+      <c r="G46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -4111,50 +4129,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="53" t="str">
+      <c r="I46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="53" t="str">
+      <c r="J46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="53" t="str">
+      <c r="K46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
         <v> </v>
       </c>
-      <c r="L46" s="53"/>
-      <c r="M46" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="53"/>
-      <c r="O46" s="68"/>
-      <c r="P46" s="51"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50" t="str">
+      <c r="L46" s="50"/>
+      <c r="M46" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="50"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="47"/>
+      <c r="R46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="50" t="str">
+      <c r="S46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="50"/>
+      <c r="T46" s="47"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="53" t="str">
+      <c r="W46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="53" t="str">
+      <c r="X46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="50" t="str">
+      <c r="Y46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="50" t="str">
+      <c r="Z46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -4167,7 +4185,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="53" t="str">
+      <c r="G47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -4175,50 +4193,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="53" t="str">
+      <c r="I47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="53" t="str">
+      <c r="J47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="53" t="str">
+      <c r="K47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
         <v> </v>
       </c>
-      <c r="L47" s="53"/>
-      <c r="M47" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="53"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="51"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50" t="str">
+      <c r="L47" s="50"/>
+      <c r="M47" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="50"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="48"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="50" t="str">
+      <c r="S47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="50"/>
+      <c r="T47" s="47"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="53" t="str">
+      <c r="W47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="53" t="str">
+      <c r="X47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="50" t="str">
+      <c r="Y47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="50" t="str">
+      <c r="Z47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4231,7 +4249,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="53" t="str">
+      <c r="G48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4239,50 +4257,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="53" t="str">
+      <c r="I48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="53" t="str">
+      <c r="J48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="53" t="str">
+      <c r="K48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
         <v> </v>
       </c>
-      <c r="L48" s="53"/>
-      <c r="M48" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="53"/>
-      <c r="O48" s="68"/>
-      <c r="P48" s="51"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50" t="str">
+      <c r="L48" s="50"/>
+      <c r="M48" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="50"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="48"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="50" t="str">
+      <c r="S48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="50"/>
+      <c r="T48" s="47"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="53" t="str">
+      <c r="W48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="53" t="str">
+      <c r="X48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="50" t="str">
+      <c r="Y48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="50" t="str">
+      <c r="Z48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4290,33 +4308,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="66"/>
+      <c r="B49" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="51"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="50"/>
+      <c r="L49" s="50"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="51"/>
-      <c r="Q49" s="50"/>
-      <c r="R49" s="50"/>
-      <c r="S49" s="50"/>
-      <c r="T49" s="50"/>
-      <c r="U49" s="52"/>
-      <c r="V49" s="53"/>
-      <c r="W49" s="53"/>
-      <c r="X49" s="53"/>
-      <c r="Y49" s="50"/>
-      <c r="Z49" s="50"/>
+      <c r="N49" s="50"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="47"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="47"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="50"/>
+      <c r="W49" s="50"/>
+      <c r="X49" s="50"/>
+      <c r="Y49" s="47"/>
+      <c r="Z49" s="47"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4326,7 +4344,7 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="53" t="str">
+      <c r="G50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
         <v> </v>
       </c>
@@ -4334,50 +4352,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="53" t="str">
+      <c r="I50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="53" t="str">
+      <c r="J50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="53" t="str">
+      <c r="K50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
         <v> </v>
       </c>
-      <c r="L50" s="53"/>
-      <c r="M50" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="53"/>
-      <c r="O50" s="68"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="50"/>
-      <c r="R50" s="50" t="str">
+      <c r="L50" s="50"/>
+      <c r="M50" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="50"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,O50*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="50" t="str">
+      <c r="S50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="50"/>
+      <c r="T50" s="47"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="53" t="str">
+      <c r="W50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="53" t="str">
+      <c r="X50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="50" t="str">
+      <c r="Y50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="50" t="str">
+      <c r="Z50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4390,7 +4408,7 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="53" t="str">
+      <c r="G51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
         <v> </v>
       </c>
@@ -4398,50 +4416,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="53" t="str">
+      <c r="I51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="53" t="str">
+      <c r="J51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="53" t="str">
+      <c r="K51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
         <v> </v>
       </c>
-      <c r="L51" s="53"/>
-      <c r="M51" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="53"/>
-      <c r="O51" s="68"/>
-      <c r="P51" s="51"/>
-      <c r="Q51" s="50"/>
-      <c r="R51" s="50" t="str">
+      <c r="L51" s="50"/>
+      <c r="M51" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="50"/>
+      <c r="O51" s="67"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,O51*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="50" t="str">
+      <c r="S51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="50"/>
+      <c r="T51" s="47"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="53" t="str">
+      <c r="W51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="53" t="str">
+      <c r="X51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="50" t="str">
+      <c r="Y51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="50" t="str">
+      <c r="Z51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4454,7 +4472,7 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="53" t="str">
+      <c r="G52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
         <v> </v>
       </c>
@@ -4462,50 +4480,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="53" t="str">
+      <c r="I52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="53" t="str">
+      <c r="J52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="53" t="str">
+      <c r="K52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
         <v> </v>
       </c>
-      <c r="L52" s="53"/>
-      <c r="M52" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="53"/>
-      <c r="O52" s="68"/>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="50"/>
-      <c r="R52" s="50" t="str">
+      <c r="L52" s="50"/>
+      <c r="M52" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="50"/>
+      <c r="O52" s="67"/>
+      <c r="P52" s="48"/>
+      <c r="Q52" s="47"/>
+      <c r="R52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,O52*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="50" t="str">
+      <c r="S52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="50"/>
+      <c r="T52" s="47"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="53" t="str">
+      <c r="W52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="53" t="str">
+      <c r="X52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="50" t="str">
+      <c r="Y52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="50" t="str">
+      <c r="Z52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4518,7 +4536,7 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="53" t="str">
+      <c r="G53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
         <v> </v>
       </c>
@@ -4526,50 +4544,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="53" t="str">
+      <c r="I53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="53" t="str">
+      <c r="J53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="53" t="str">
+      <c r="K53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
         <v> </v>
       </c>
-      <c r="L53" s="53"/>
-      <c r="M53" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="53"/>
-      <c r="O53" s="68"/>
-      <c r="P53" s="51"/>
-      <c r="Q53" s="50"/>
-      <c r="R53" s="50" t="str">
+      <c r="L53" s="50"/>
+      <c r="M53" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="50"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="47"/>
+      <c r="R53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,O53*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="50" t="str">
+      <c r="S53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="50"/>
+      <c r="T53" s="47"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="53" t="str">
+      <c r="W53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="53" t="str">
+      <c r="X53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="50" t="str">
+      <c r="Y53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="50" t="str">
+      <c r="Z53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4582,7 +4600,7 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="53" t="str">
+      <c r="G54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
         <v> </v>
       </c>
@@ -4590,50 +4608,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="53" t="str">
+      <c r="I54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="53" t="str">
+      <c r="J54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="53" t="str">
+      <c r="K54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
         <v> </v>
       </c>
-      <c r="L54" s="53"/>
-      <c r="M54" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="53"/>
-      <c r="O54" s="68"/>
-      <c r="P54" s="51"/>
-      <c r="Q54" s="50"/>
-      <c r="R54" s="50" t="str">
+      <c r="L54" s="50"/>
+      <c r="M54" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="50"/>
+      <c r="O54" s="67"/>
+      <c r="P54" s="48"/>
+      <c r="Q54" s="47"/>
+      <c r="R54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,O54*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="50" t="str">
+      <c r="S54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="50"/>
+      <c r="T54" s="47"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="53" t="str">
+      <c r="W54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="53" t="str">
+      <c r="X54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="50" t="str">
+      <c r="Y54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="50" t="str">
+      <c r="Z54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4642,7 +4660,7 @@
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="42"/>
       <c r="B55" s="59" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C55" s="59"/>
       <c r="D55" s="59"/>
@@ -4652,7 +4670,7 @@
       </c>
       <c r="F55" s="61" t="n">
         <f aca="false">SUM(F38:F54)</f>
-        <v>0</v>
+        <v>9828</v>
       </c>
       <c r="G55" s="61" t="n">
         <f aca="false">SUM(G38:G54)</f>
@@ -4671,9 +4689,9 @@
         <f aca="false">SUM(K38:K54)</f>
         <v>0</v>
       </c>
-      <c r="L55" s="53"/>
-      <c r="M55" s="72"/>
-      <c r="N55" s="53"/>
+      <c r="L55" s="50"/>
+      <c r="M55" s="71"/>
+      <c r="N55" s="50"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O38:O54)</f>
         <v>0</v>
@@ -4691,8 +4709,8 @@
         <f aca="false">SUM(S38:S54)</f>
         <v>0</v>
       </c>
-      <c r="T55" s="53"/>
-      <c r="U55" s="52"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="49"/>
       <c r="V55" s="61" t="n">
         <f aca="false">SUM(V38:V54)</f>
         <v>0</v>
@@ -4717,31 +4735,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="74"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="73"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="50"/>
+      <c r="L56" s="50"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="50"/>
-      <c r="P56" s="51"/>
-      <c r="Q56" s="50"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="50"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="52"/>
-      <c r="V56" s="53"/>
-      <c r="W56" s="50"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="50"/>
-      <c r="Z56" s="50"/>
+      <c r="N56" s="50"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="48"/>
+      <c r="Q56" s="47"/>
+      <c r="R56" s="47"/>
+      <c r="S56" s="47"/>
+      <c r="T56" s="47"/>
+      <c r="U56" s="49"/>
+      <c r="V56" s="50"/>
+      <c r="W56" s="47"/>
+      <c r="X56" s="47"/>
+      <c r="Y56" s="47"/>
+      <c r="Z56" s="47"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4751,74 +4769,74 @@
         <v>EXISTING FIXED ASSETS at </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="44" t="str">
+      <c r="D57" s="44" t="n">
         <f aca="false">D6</f>
-        <v>Laptop (0.5 years old)</v>
-      </c>
-      <c r="E57" s="75" t="n">
+        <v>45753</v>
+      </c>
+      <c r="E57" s="74" t="n">
         <f aca="false">E11+E19+E27+E35+E55</f>
         <v>0</v>
       </c>
-      <c r="F57" s="75" t="n">
+      <c r="F57" s="74" t="n">
         <f aca="false">F11+F19+F27+F35+F55</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="75" t="n">
+        <v>10098</v>
+      </c>
+      <c r="G57" s="74" t="n">
         <f aca="false">G11+G19+G27+G35+G55</f>
         <v>0</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="75" t="n">
+      <c r="I57" s="74" t="n">
         <f aca="false">I11+I19+I27+I35+I55</f>
         <v>0</v>
       </c>
-      <c r="J57" s="75" t="n">
+      <c r="J57" s="74" t="n">
         <f aca="false">J11+J19+J27+J35+J55</f>
         <v>0</v>
       </c>
-      <c r="K57" s="75" t="n">
+      <c r="K57" s="74" t="n">
         <f aca="false">K11+K19+K27+K35+K55</f>
         <v>0</v>
       </c>
-      <c r="L57" s="53"/>
+      <c r="L57" s="50"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="75" t="n">
+      <c r="N57" s="50"/>
+      <c r="O57" s="74" t="n">
         <f aca="false">O11+O19+O27+O35+O55</f>
         <v>0</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="75" t="n">
+      <c r="Q57" s="74" t="n">
         <f aca="false">Q11+Q19+Q27+Q35+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="75" t="n">
+      <c r="R57" s="74" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
         <v>0</v>
       </c>
-      <c r="S57" s="75" t="n">
+      <c r="S57" s="74" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
         <v>0</v>
       </c>
-      <c r="T57" s="50"/>
-      <c r="U57" s="52"/>
-      <c r="V57" s="75" t="n">
+      <c r="T57" s="47"/>
+      <c r="U57" s="49"/>
+      <c r="V57" s="74" t="n">
         <f aca="false">V11+V19+V27+V35+V55</f>
         <v>0</v>
       </c>
-      <c r="W57" s="75" t="n">
+      <c r="W57" s="74" t="n">
         <f aca="false">W11+W19+W27+W35+W55</f>
         <v>0</v>
       </c>
-      <c r="X57" s="75" t="n">
+      <c r="X57" s="74" t="n">
         <f aca="false">X11+X19+X27+X35+X55</f>
         <v>0</v>
       </c>
-      <c r="Y57" s="75" t="n">
+      <c r="Y57" s="74" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="75" t="n">
+      <c r="Z57" s="74" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
         <v>0</v>
       </c>
@@ -4826,78 +4844,78 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="76"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="78"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="53"/>
-      <c r="K58" s="53"/>
-      <c r="L58" s="53"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="50"/>
+      <c r="L58" s="50"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="53"/>
-      <c r="O58" s="50"/>
-      <c r="P58" s="51"/>
-      <c r="Q58" s="50"/>
-      <c r="R58" s="50"/>
-      <c r="S58" s="50"/>
-      <c r="T58" s="50"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="53"/>
-      <c r="W58" s="53"/>
-      <c r="X58" s="53"/>
-      <c r="Y58" s="50"/>
-      <c r="Z58" s="50"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="47"/>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="47"/>
+      <c r="R58" s="47"/>
+      <c r="S58" s="47"/>
+      <c r="T58" s="47"/>
+      <c r="U58" s="49"/>
+      <c r="V58" s="50"/>
+      <c r="W58" s="50"/>
+      <c r="X58" s="50"/>
+      <c r="Y58" s="47"/>
+      <c r="Z58" s="47"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
       <c r="B59" s="43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="n">
         <f aca="false">[1]Admin!$B$4</f>
         <v>45753</v>
       </c>
-      <c r="E59" s="50"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="78"/>
+      <c r="G59" s="78"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="47"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="51"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="53"/>
-      <c r="W59" s="53"/>
-      <c r="X59" s="53"/>
-      <c r="Y59" s="50"/>
-      <c r="Z59" s="50"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="47"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="47"/>
+      <c r="R59" s="47"/>
+      <c r="S59" s="47"/>
+      <c r="T59" s="47"/>
+      <c r="U59" s="49"/>
+      <c r="V59" s="50"/>
+      <c r="W59" s="50"/>
+      <c r="X59" s="50"/>
+      <c r="Y59" s="47"/>
+      <c r="Z59" s="47"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="C60" s="66"/>
-      <c r="D60" s="47"/>
+      <c r="B60" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="51"/>
+      <c r="D60" s="52"/>
       <c r="E60" s="45"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
-      <c r="H60" s="80" t="n">
+      <c r="F60" s="78"/>
+      <c r="G60" s="78"/>
+      <c r="H60" s="79" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
@@ -4907,165 +4925,165 @@
       <c r="L60" s="45"/>
       <c r="M60" s="58"/>
       <c r="N60" s="45"/>
-      <c r="O60" s="50"/>
-      <c r="P60" s="51"/>
-      <c r="Q60" s="50"/>
-      <c r="R60" s="50"/>
-      <c r="S60" s="50"/>
-      <c r="T60" s="50"/>
-      <c r="U60" s="52"/>
-      <c r="V60" s="53"/>
-      <c r="W60" s="53"/>
-      <c r="X60" s="53"/>
-      <c r="Y60" s="50"/>
-      <c r="Z60" s="50"/>
+      <c r="O60" s="47"/>
+      <c r="P60" s="48"/>
+      <c r="Q60" s="47"/>
+      <c r="R60" s="47"/>
+      <c r="S60" s="47"/>
+      <c r="T60" s="47"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="50"/>
+      <c r="W60" s="50"/>
+      <c r="X60" s="50"/>
+      <c r="Y60" s="47"/>
+      <c r="Z60" s="47"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="81"/>
+      <c r="D61" s="80"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
+      <c r="F61" s="50"/>
+      <c r="G61" s="50"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="53" t="str">
+      <c r="I61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="53" t="str">
+      <c r="J61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="53" t="str">
+      <c r="K61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
         <v> </v>
       </c>
-      <c r="L61" s="53"/>
+      <c r="L61" s="50"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="53"/>
-      <c r="O61" s="50"/>
-      <c r="P61" s="51"/>
-      <c r="Q61" s="50"/>
-      <c r="R61" s="50"/>
-      <c r="S61" s="50"/>
-      <c r="T61" s="50"/>
+      <c r="N61" s="50"/>
+      <c r="O61" s="47"/>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="47"/>
+      <c r="R61" s="47"/>
+      <c r="S61" s="47"/>
+      <c r="T61" s="47"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="53" t="str">
+      <c r="W61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="53" t="str">
+      <c r="X61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="50"/>
-      <c r="Z61" s="50"/>
+      <c r="Y61" s="47"/>
+      <c r="Z61" s="47"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="81"/>
+      <c r="D62" s="80"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="53"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="50"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="53" t="str">
+      <c r="I62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="53" t="str">
+      <c r="J62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="53" t="str">
+      <c r="K62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
         <v> </v>
       </c>
-      <c r="L62" s="53"/>
+      <c r="L62" s="50"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="53"/>
-      <c r="O62" s="50"/>
-      <c r="P62" s="51"/>
-      <c r="Q62" s="50"/>
-      <c r="R62" s="50"/>
-      <c r="S62" s="50"/>
-      <c r="T62" s="50"/>
+      <c r="N62" s="50"/>
+      <c r="O62" s="47"/>
+      <c r="P62" s="48"/>
+      <c r="Q62" s="47"/>
+      <c r="R62" s="47"/>
+      <c r="S62" s="47"/>
+      <c r="T62" s="47"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="53" t="str">
+      <c r="W62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="53" t="str">
+      <c r="X62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="50"/>
-      <c r="Z62" s="50"/>
+      <c r="Y62" s="47"/>
+      <c r="Z62" s="47"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="81"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="53" t="str">
+      <c r="I63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="53" t="str">
+      <c r="J63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="53" t="str">
+      <c r="K63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
         <v> </v>
       </c>
-      <c r="L63" s="53"/>
+      <c r="L63" s="50"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="53"/>
-      <c r="O63" s="50"/>
-      <c r="P63" s="51"/>
-      <c r="Q63" s="50"/>
-      <c r="R63" s="50"/>
-      <c r="S63" s="50"/>
-      <c r="T63" s="50"/>
+      <c r="N63" s="50"/>
+      <c r="O63" s="47"/>
+      <c r="P63" s="48"/>
+      <c r="Q63" s="47"/>
+      <c r="R63" s="47"/>
+      <c r="S63" s="47"/>
+      <c r="T63" s="47"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="53" t="str">
+      <c r="W63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="53" t="str">
+      <c r="X63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="50"/>
-      <c r="Z63" s="50"/>
+      <c r="Y63" s="47"/>
+      <c r="Z63" s="47"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -5094,14 +5112,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="53"/>
+      <c r="L64" s="50"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="53"/>
+      <c r="N64" s="50"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="82"/>
+      <c r="P64" s="81"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -5114,8 +5132,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="50"/>
-      <c r="U64" s="52"/>
+      <c r="T64" s="47"/>
+      <c r="U64" s="49"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -5143,62 +5161,62 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="53"/>
-      <c r="F65" s="53"/>
-      <c r="G65" s="53"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="53"/>
-      <c r="J65" s="53"/>
-      <c r="K65" s="53"/>
-      <c r="L65" s="53"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="50"/>
+      <c r="L65" s="50"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="53"/>
-      <c r="O65" s="53"/>
+      <c r="N65" s="50"/>
+      <c r="O65" s="50"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="53"/>
-      <c r="R65" s="53"/>
-      <c r="S65" s="53"/>
-      <c r="T65" s="50"/>
-      <c r="U65" s="52"/>
-      <c r="V65" s="53"/>
-      <c r="W65" s="53"/>
-      <c r="X65" s="53"/>
-      <c r="Y65" s="53"/>
-      <c r="Z65" s="53"/>
+      <c r="Q65" s="50"/>
+      <c r="R65" s="50"/>
+      <c r="S65" s="50"/>
+      <c r="T65" s="47"/>
+      <c r="U65" s="49"/>
+      <c r="V65" s="50"/>
+      <c r="W65" s="50"/>
+      <c r="X65" s="50"/>
+      <c r="Y65" s="50"/>
+      <c r="Z65" s="50"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="66" t="s">
+      <c r="B66" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="66"/>
+      <c r="C66" s="51"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="53"/>
-      <c r="F66" s="53"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="83" t="n">
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="82" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="53"/>
-      <c r="J66" s="53"/>
-      <c r="K66" s="53"/>
-      <c r="L66" s="53"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="50"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="53"/>
-      <c r="O66" s="50"/>
-      <c r="P66" s="51"/>
-      <c r="Q66" s="50"/>
-      <c r="R66" s="50"/>
-      <c r="S66" s="50"/>
-      <c r="T66" s="50"/>
-      <c r="U66" s="52"/>
-      <c r="V66" s="53"/>
-      <c r="W66" s="53"/>
-      <c r="X66" s="53"/>
-      <c r="Y66" s="50"/>
-      <c r="Z66" s="50"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="47"/>
+      <c r="S66" s="47"/>
+      <c r="T66" s="47"/>
+      <c r="U66" s="49"/>
+      <c r="V66" s="50"/>
+      <c r="W66" s="50"/>
+      <c r="X66" s="50"/>
+      <c r="Y66" s="47"/>
+      <c r="Z66" s="47"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5207,57 +5225,57 @@
       <c r="C67" s="55"/>
       <c r="D67" s="56"/>
       <c r="E67" s="57"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="53" t="str">
+      <c r="I67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
         <v> </v>
       </c>
-      <c r="J67" s="53" t="str">
+      <c r="J67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
         <v> </v>
       </c>
-      <c r="K67" s="53" t="str">
+      <c r="K67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
         <v> </v>
       </c>
-      <c r="L67" s="53"/>
+      <c r="L67" s="50"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="53"/>
-      <c r="O67" s="50"/>
+      <c r="N67" s="50"/>
+      <c r="O67" s="47"/>
       <c r="P67" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q67" s="50" t="str">
+      <c r="Q67" s="47" t="str">
         <f aca="false">IF(E67&gt;0,E67*P67," ")</f>
         <v> </v>
       </c>
-      <c r="R67" s="50"/>
-      <c r="S67" s="50" t="str">
+      <c r="R67" s="47"/>
+      <c r="S67" s="47" t="str">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
         <v> </v>
       </c>
-      <c r="T67" s="50"/>
+      <c r="T67" s="47"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="53" t="str">
+      <c r="W67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="53" t="str">
+      <c r="X67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="50" t="str">
+      <c r="Y67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="50" t="str">
+      <c r="Z67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5269,57 +5287,57 @@
       <c r="C68" s="55"/>
       <c r="D68" s="56"/>
       <c r="E68" s="57"/>
-      <c r="F68" s="53"/>
-      <c r="G68" s="53"/>
+      <c r="F68" s="50"/>
+      <c r="G68" s="50"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="53" t="str">
+      <c r="I68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
         <v> </v>
       </c>
-      <c r="J68" s="53" t="str">
+      <c r="J68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
         <v> </v>
       </c>
-      <c r="K68" s="53" t="str">
+      <c r="K68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
         <v> </v>
       </c>
-      <c r="L68" s="53"/>
+      <c r="L68" s="50"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="53"/>
-      <c r="O68" s="50"/>
+      <c r="N68" s="50"/>
+      <c r="O68" s="47"/>
       <c r="P68" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q68" s="50" t="str">
+      <c r="Q68" s="47" t="str">
         <f aca="false">IF(E68&gt;0,E68*P68," ")</f>
         <v> </v>
       </c>
-      <c r="R68" s="50"/>
-      <c r="S68" s="50" t="str">
+      <c r="R68" s="47"/>
+      <c r="S68" s="47" t="str">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
         <v> </v>
       </c>
-      <c r="T68" s="50"/>
+      <c r="T68" s="47"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="53" t="str">
+      <c r="W68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="53" t="str">
+      <c r="X68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="50" t="str">
+      <c r="Y68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="50" t="str">
+      <c r="Z68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5331,57 +5349,57 @@
       <c r="C69" s="55"/>
       <c r="D69" s="56"/>
       <c r="E69" s="57"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="53" t="str">
+      <c r="I69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
         <v> </v>
       </c>
-      <c r="J69" s="53" t="str">
+      <c r="J69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
         <v> </v>
       </c>
-      <c r="K69" s="53" t="str">
+      <c r="K69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
         <v> </v>
       </c>
-      <c r="L69" s="53"/>
+      <c r="L69" s="50"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="53"/>
-      <c r="O69" s="50"/>
+      <c r="N69" s="50"/>
+      <c r="O69" s="47"/>
       <c r="P69" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q69" s="50" t="str">
+      <c r="Q69" s="47" t="str">
         <f aca="false">IF(E69&gt;0,E69*P69," ")</f>
         <v> </v>
       </c>
-      <c r="R69" s="50"/>
-      <c r="S69" s="50" t="str">
+      <c r="R69" s="47"/>
+      <c r="S69" s="47" t="str">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
         <v> </v>
       </c>
-      <c r="T69" s="50"/>
+      <c r="T69" s="47"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="53" t="str">
+      <c r="W69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="53" t="str">
+      <c r="X69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="50" t="str">
+      <c r="Y69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="50" t="str">
+      <c r="Z69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5393,57 +5411,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="53"/>
-      <c r="G70" s="53"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="53" t="str">
+      <c r="I70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="53" t="str">
+      <c r="J70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="53" t="str">
+      <c r="K70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
         <v> </v>
       </c>
-      <c r="L70" s="53"/>
+      <c r="L70" s="50"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="53"/>
-      <c r="O70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="47"/>
       <c r="P70" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="50" t="str">
+      <c r="Q70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="50"/>
-      <c r="S70" s="50" t="str">
+      <c r="R70" s="47"/>
+      <c r="S70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="50"/>
+      <c r="T70" s="47"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="53" t="str">
+      <c r="W70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="53" t="str">
+      <c r="X70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="50" t="str">
+      <c r="Y70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="50" t="str">
+      <c r="Z70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5455,57 +5473,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="53"/>
-      <c r="G71" s="53"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="53" t="str">
+      <c r="I71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="53" t="str">
+      <c r="J71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="53" t="str">
+      <c r="K71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
         <v> </v>
       </c>
-      <c r="L71" s="53"/>
+      <c r="L71" s="50"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="50"/>
+      <c r="N71" s="50"/>
+      <c r="O71" s="47"/>
       <c r="P71" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q71" s="50" t="str">
+      <c r="Q71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="50"/>
-      <c r="S71" s="50" t="str">
+      <c r="R71" s="47"/>
+      <c r="S71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="50"/>
+      <c r="T71" s="47"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="53" t="str">
+      <c r="W71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="53" t="str">
+      <c r="X71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="50" t="str">
+      <c r="Y71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="50" t="str">
+      <c r="Z71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5514,7 +5532,7 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="42"/>
       <c r="B72" s="59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
@@ -5543,9 +5561,9 @@
         <f aca="false">SUM(K67:K71)</f>
         <v>0</v>
       </c>
-      <c r="L72" s="53"/>
+      <c r="L72" s="50"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="53"/>
+      <c r="N72" s="50"/>
       <c r="O72" s="61" t="n">
         <f aca="false">SUM(O67:O71)</f>
         <v>0</v>
@@ -5563,8 +5581,8 @@
         <f aca="false">SUM(S67:S71)</f>
         <v>0</v>
       </c>
-      <c r="T72" s="50"/>
-      <c r="U72" s="52"/>
+      <c r="T72" s="47"/>
+      <c r="U72" s="49"/>
       <c r="V72" s="60" t="n">
         <f aca="false">SUM(V67:V71)</f>
         <v>0</v>
@@ -5592,121 +5610,121 @@
       <c r="B73" s="63"/>
       <c r="C73" s="64"/>
       <c r="D73" s="65"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
       <c r="H73" s="58"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-      <c r="L73" s="53"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="50"/>
+      <c r="K73" s="50"/>
+      <c r="L73" s="50"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="53"/>
-      <c r="O73" s="53"/>
+      <c r="N73" s="50"/>
+      <c r="O73" s="50"/>
       <c r="P73" s="62"/>
-      <c r="Q73" s="53"/>
-      <c r="R73" s="53"/>
-      <c r="S73" s="53"/>
-      <c r="T73" s="50"/>
-      <c r="U73" s="52"/>
-      <c r="V73" s="53"/>
-      <c r="W73" s="53"/>
-      <c r="X73" s="53"/>
-      <c r="Y73" s="53"/>
-      <c r="Z73" s="53"/>
+      <c r="Q73" s="50"/>
+      <c r="R73" s="50"/>
+      <c r="S73" s="50"/>
+      <c r="T73" s="47"/>
+      <c r="U73" s="49"/>
+      <c r="V73" s="50"/>
+      <c r="W73" s="50"/>
+      <c r="X73" s="50"/>
+      <c r="Y73" s="50"/>
+      <c r="Z73" s="50"/>
       <c r="AA73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="42"/>
-      <c r="B74" s="66" t="s">
+      <c r="B74" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="66"/>
+      <c r="C74" s="51"/>
       <c r="D74" s="62"/>
-      <c r="E74" s="53"/>
-      <c r="F74" s="53"/>
-      <c r="G74" s="53"/>
-      <c r="H74" s="83" t="n">
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="82" t="n">
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I74" s="53"/>
-      <c r="J74" s="53"/>
-      <c r="K74" s="53"/>
-      <c r="L74" s="53"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="K74" s="50"/>
+      <c r="L74" s="50"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="53"/>
-      <c r="O74" s="50"/>
-      <c r="P74" s="51"/>
-      <c r="Q74" s="50"/>
-      <c r="R74" s="50"/>
-      <c r="S74" s="50"/>
-      <c r="T74" s="50"/>
-      <c r="U74" s="52"/>
-      <c r="V74" s="53"/>
-      <c r="W74" s="53"/>
-      <c r="X74" s="53"/>
-      <c r="Y74" s="50"/>
-      <c r="Z74" s="50"/>
+      <c r="N74" s="50"/>
+      <c r="O74" s="47"/>
+      <c r="P74" s="48"/>
+      <c r="Q74" s="47"/>
+      <c r="R74" s="47"/>
+      <c r="S74" s="47"/>
+      <c r="T74" s="47"/>
+      <c r="U74" s="49"/>
+      <c r="V74" s="50"/>
+      <c r="W74" s="50"/>
+      <c r="X74" s="50"/>
+      <c r="Y74" s="47"/>
+      <c r="Z74" s="47"/>
       <c r="AA74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
-      <c r="D75" s="81"/>
+      <c r="D75" s="80"/>
       <c r="E75" s="57"/>
-      <c r="F75" s="53"/>
-      <c r="G75" s="53"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
       <c r="H75" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I75" s="53" t="str">
+      <c r="I75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,MIN(E75*H75,G75)," ")</f>
         <v> </v>
       </c>
-      <c r="J75" s="53" t="str">
+      <c r="J75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,F75+I75," ")</f>
         <v> </v>
       </c>
-      <c r="K75" s="53" t="str">
+      <c r="K75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75-J75," ")</f>
         <v> </v>
       </c>
-      <c r="L75" s="53"/>
+      <c r="L75" s="50"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="53"/>
-      <c r="O75" s="50"/>
+      <c r="N75" s="50"/>
+      <c r="O75" s="47"/>
       <c r="P75" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q75" s="50" t="str">
+      <c r="Q75" s="47" t="str">
         <f aca="false">IF(E75&gt;0,E75*P75," ")</f>
         <v> </v>
       </c>
-      <c r="R75" s="50"/>
-      <c r="S75" s="50" t="str">
+      <c r="R75" s="47"/>
+      <c r="S75" s="47" t="str">
         <f aca="false">IF(E75&gt;0,E75-Q75," ")</f>
         <v> </v>
       </c>
-      <c r="T75" s="50"/>
+      <c r="T75" s="47"/>
       <c r="U75" s="54"/>
       <c r="V75" s="57"/>
-      <c r="W75" s="53" t="str">
+      <c r="W75" s="50" t="str">
         <f aca="false">IF(V75&gt;0,E75," ")</f>
         <v> </v>
       </c>
-      <c r="X75" s="53" t="str">
+      <c r="X75" s="50" t="str">
         <f aca="false">IF(V75&gt;0,J75," ")</f>
         <v> </v>
       </c>
-      <c r="Y75" s="50" t="str">
+      <c r="Y75" s="47" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&lt;S75,S75-V75," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z75" s="50" t="str">
+      <c r="Z75" s="47" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&gt;S75,V75-S75," ")," ")</f>
         <v> </v>
       </c>
@@ -5716,59 +5734,59 @@
       <c r="A76" s="42"/>
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
-      <c r="D76" s="81"/>
+      <c r="D76" s="80"/>
       <c r="E76" s="57"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
       <c r="H76" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I76" s="53" t="str">
+      <c r="I76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,MIN(E76*H76,G76)," ")</f>
         <v> </v>
       </c>
-      <c r="J76" s="53" t="str">
+      <c r="J76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,F76+I76," ")</f>
         <v> </v>
       </c>
-      <c r="K76" s="53" t="str">
+      <c r="K76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76-J76," ")</f>
         <v> </v>
       </c>
-      <c r="L76" s="53"/>
+      <c r="L76" s="50"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="53"/>
-      <c r="O76" s="50"/>
+      <c r="N76" s="50"/>
+      <c r="O76" s="47"/>
       <c r="P76" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q76" s="50" t="str">
+      <c r="Q76" s="47" t="str">
         <f aca="false">IF(E76&gt;0,E76*P76," ")</f>
         <v> </v>
       </c>
-      <c r="R76" s="50"/>
-      <c r="S76" s="50" t="str">
+      <c r="R76" s="47"/>
+      <c r="S76" s="47" t="str">
         <f aca="false">IF(E76&gt;0,E76-Q76," ")</f>
         <v> </v>
       </c>
-      <c r="T76" s="50"/>
+      <c r="T76" s="47"/>
       <c r="U76" s="54"/>
       <c r="V76" s="57"/>
-      <c r="W76" s="53" t="str">
+      <c r="W76" s="50" t="str">
         <f aca="false">IF(V76&gt;0,E76," ")</f>
         <v> </v>
       </c>
-      <c r="X76" s="53" t="str">
+      <c r="X76" s="50" t="str">
         <f aca="false">IF(V76&gt;0,J76," ")</f>
         <v> </v>
       </c>
-      <c r="Y76" s="50" t="str">
+      <c r="Y76" s="47" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&lt;S76,S76-V76," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z76" s="50" t="str">
+      <c r="Z76" s="47" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&gt;S76,V76-S76," ")," ")</f>
         <v> </v>
       </c>
@@ -5778,59 +5796,59 @@
       <c r="A77" s="42"/>
       <c r="B77" s="54"/>
       <c r="C77" s="55"/>
-      <c r="D77" s="81"/>
+      <c r="D77" s="80"/>
       <c r="E77" s="57"/>
-      <c r="F77" s="53"/>
-      <c r="G77" s="53"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
       <c r="H77" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="53" t="str">
+      <c r="I77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,MIN(E77*H77,G77)," ")</f>
         <v> </v>
       </c>
-      <c r="J77" s="53" t="str">
+      <c r="J77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,F77+I77," ")</f>
         <v> </v>
       </c>
-      <c r="K77" s="53" t="str">
+      <c r="K77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77-J77," ")</f>
         <v> </v>
       </c>
-      <c r="L77" s="53"/>
+      <c r="L77" s="50"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="53"/>
-      <c r="O77" s="50"/>
+      <c r="N77" s="50"/>
+      <c r="O77" s="47"/>
       <c r="P77" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="50" t="str">
+      <c r="Q77" s="47" t="str">
         <f aca="false">IF(E77&gt;0,E77*P77," ")</f>
         <v> </v>
       </c>
-      <c r="R77" s="50"/>
-      <c r="S77" s="50" t="str">
+      <c r="R77" s="47"/>
+      <c r="S77" s="47" t="str">
         <f aca="false">IF(E77&gt;0,E77-Q77," ")</f>
         <v> </v>
       </c>
-      <c r="T77" s="50"/>
+      <c r="T77" s="47"/>
       <c r="U77" s="54"/>
       <c r="V77" s="57"/>
-      <c r="W77" s="53" t="str">
+      <c r="W77" s="50" t="str">
         <f aca="false">IF(V77&gt;0,E77," ")</f>
         <v> </v>
       </c>
-      <c r="X77" s="53" t="str">
+      <c r="X77" s="50" t="str">
         <f aca="false">IF(V77&gt;0,J77," ")</f>
         <v> </v>
       </c>
-      <c r="Y77" s="50" t="str">
+      <c r="Y77" s="47" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&lt;S77,S77-V77," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z77" s="50" t="str">
+      <c r="Z77" s="47" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&gt;S77,V77-S77," ")," ")</f>
         <v> </v>
       </c>
@@ -5840,59 +5858,59 @@
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="81"/>
+      <c r="D78" s="80"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="53" t="str">
+      <c r="I78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="53" t="str">
+      <c r="J78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="53" t="str">
+      <c r="K78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
         <v> </v>
       </c>
-      <c r="L78" s="53"/>
+      <c r="L78" s="50"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="53"/>
-      <c r="O78" s="50"/>
+      <c r="N78" s="50"/>
+      <c r="O78" s="47"/>
       <c r="P78" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q78" s="50" t="str">
+      <c r="Q78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="50"/>
-      <c r="S78" s="50" t="str">
+      <c r="R78" s="47"/>
+      <c r="S78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="50"/>
+      <c r="T78" s="47"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="53" t="str">
+      <c r="W78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="53" t="str">
+      <c r="X78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="50" t="str">
+      <c r="Y78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="50" t="str">
+      <c r="Z78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5902,59 +5920,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="81"/>
+      <c r="D79" s="80"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="53" t="str">
+      <c r="I79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="53" t="str">
+      <c r="J79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="53" t="str">
+      <c r="K79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
         <v> </v>
       </c>
-      <c r="L79" s="53"/>
+      <c r="L79" s="50"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="50"/>
+      <c r="N79" s="50"/>
+      <c r="O79" s="47"/>
       <c r="P79" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q79" s="50" t="str">
+      <c r="Q79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="50"/>
-      <c r="S79" s="50" t="str">
+      <c r="R79" s="47"/>
+      <c r="S79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="50"/>
+      <c r="T79" s="47"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="53" t="str">
+      <c r="W79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="53" t="str">
+      <c r="X79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="50" t="str">
+      <c r="Y79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="50" t="str">
+      <c r="Z79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -5963,7 +5981,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="42"/>
       <c r="B80" s="59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C80" s="59"/>
       <c r="D80" s="59"/>
@@ -5992,9 +6010,9 @@
         <f aca="false">SUM(K75:K79)</f>
         <v>0</v>
       </c>
-      <c r="L80" s="53"/>
+      <c r="L80" s="50"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="53"/>
+      <c r="N80" s="50"/>
       <c r="O80" s="61" t="n">
         <f aca="false">SUM(O75:O79)</f>
         <v>0</v>
@@ -6012,8 +6030,8 @@
         <f aca="false">SUM(S75:S79)</f>
         <v>0</v>
       </c>
-      <c r="T80" s="50"/>
-      <c r="U80" s="52"/>
+      <c r="T80" s="47"/>
+      <c r="U80" s="49"/>
       <c r="V80" s="60" t="n">
         <f aca="false">SUM(V75:V79)</f>
         <v>0</v>
@@ -6041,121 +6059,121 @@
       <c r="B81" s="63"/>
       <c r="C81" s="64"/>
       <c r="D81" s="65"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
       <c r="H81" s="58"/>
-      <c r="I81" s="53"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="53"/>
-      <c r="L81" s="53"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="53"/>
-      <c r="O81" s="53"/>
+      <c r="N81" s="50"/>
+      <c r="O81" s="50"/>
       <c r="P81" s="62"/>
-      <c r="Q81" s="53"/>
-      <c r="R81" s="53"/>
-      <c r="S81" s="53"/>
-      <c r="T81" s="50"/>
-      <c r="U81" s="52"/>
-      <c r="V81" s="53"/>
-      <c r="W81" s="53"/>
-      <c r="X81" s="53"/>
-      <c r="Y81" s="53"/>
-      <c r="Z81" s="53"/>
+      <c r="Q81" s="50"/>
+      <c r="R81" s="50"/>
+      <c r="S81" s="50"/>
+      <c r="T81" s="47"/>
+      <c r="U81" s="49"/>
+      <c r="V81" s="50"/>
+      <c r="W81" s="50"/>
+      <c r="X81" s="50"/>
+      <c r="Y81" s="50"/>
+      <c r="Z81" s="50"/>
       <c r="AA81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="42"/>
-      <c r="B82" s="66" t="s">
+      <c r="B82" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="66"/>
-      <c r="D82" s="69"/>
-      <c r="E82" s="53"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="83" t="n">
+      <c r="C82" s="51"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="82" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I82" s="53"/>
-      <c r="J82" s="53"/>
-      <c r="K82" s="53"/>
-      <c r="L82" s="53"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="53"/>
-      <c r="O82" s="50"/>
-      <c r="P82" s="51"/>
-      <c r="Q82" s="50"/>
-      <c r="R82" s="50"/>
-      <c r="S82" s="50"/>
-      <c r="T82" s="50"/>
-      <c r="U82" s="52"/>
-      <c r="V82" s="53"/>
-      <c r="W82" s="53"/>
-      <c r="X82" s="53"/>
-      <c r="Y82" s="50"/>
-      <c r="Z82" s="50"/>
+      <c r="N82" s="50"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="47"/>
+      <c r="R82" s="47"/>
+      <c r="S82" s="47"/>
+      <c r="T82" s="47"/>
+      <c r="U82" s="49"/>
+      <c r="V82" s="50"/>
+      <c r="W82" s="50"/>
+      <c r="X82" s="50"/>
+      <c r="Y82" s="47"/>
+      <c r="Z82" s="47"/>
       <c r="AA82" s="25"/>
     </row>
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="54"/>
       <c r="C83" s="55"/>
-      <c r="D83" s="81"/>
+      <c r="D83" s="80"/>
       <c r="E83" s="57"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
       <c r="H83" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I83" s="53" t="str">
+      <c r="I83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,MIN(E83*H83,G83)," ")</f>
         <v> </v>
       </c>
-      <c r="J83" s="53" t="str">
+      <c r="J83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,F83+I83," ")</f>
         <v> </v>
       </c>
-      <c r="K83" s="53" t="str">
+      <c r="K83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83-J83," ")</f>
         <v> </v>
       </c>
-      <c r="L83" s="53"/>
+      <c r="L83" s="50"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="53"/>
-      <c r="O83" s="50"/>
+      <c r="N83" s="50"/>
+      <c r="O83" s="47"/>
       <c r="P83" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q83" s="50" t="str">
+      <c r="Q83" s="47" t="str">
         <f aca="false">IF(E83&gt;0,E83*P83," ")</f>
         <v> </v>
       </c>
-      <c r="R83" s="50"/>
-      <c r="S83" s="50" t="str">
+      <c r="R83" s="47"/>
+      <c r="S83" s="47" t="str">
         <f aca="false">IF(E83&gt;0,E83-Q83," ")</f>
         <v> </v>
       </c>
-      <c r="T83" s="50"/>
+      <c r="T83" s="47"/>
       <c r="U83" s="54"/>
       <c r="V83" s="57"/>
-      <c r="W83" s="53" t="str">
+      <c r="W83" s="50" t="str">
         <f aca="false">IF(V83&gt;0,E83," ")</f>
         <v> </v>
       </c>
-      <c r="X83" s="53" t="str">
+      <c r="X83" s="50" t="str">
         <f aca="false">IF(V83&gt;0,J83," ")</f>
         <v> </v>
       </c>
-      <c r="Y83" s="50" t="str">
+      <c r="Y83" s="47" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&lt;S83,S83-V83," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z83" s="50" t="str">
+      <c r="Z83" s="47" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&gt;S83,V83-S83," ")," ")</f>
         <v> </v>
       </c>
@@ -6165,59 +6183,59 @@
       <c r="A84" s="42"/>
       <c r="B84" s="54"/>
       <c r="C84" s="55"/>
-      <c r="D84" s="81"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="57"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
       <c r="H84" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I84" s="53" t="str">
+      <c r="I84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,MIN(E84*H84,G84)," ")</f>
         <v> </v>
       </c>
-      <c r="J84" s="53" t="str">
+      <c r="J84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,F84+I84," ")</f>
         <v> </v>
       </c>
-      <c r="K84" s="53" t="str">
+      <c r="K84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84-J84," ")</f>
         <v> </v>
       </c>
-      <c r="L84" s="53"/>
+      <c r="L84" s="50"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="53"/>
-      <c r="O84" s="50"/>
+      <c r="N84" s="50"/>
+      <c r="O84" s="47"/>
       <c r="P84" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q84" s="50" t="str">
+      <c r="Q84" s="47" t="str">
         <f aca="false">IF(E84&gt;0,E84*P84," ")</f>
         <v> </v>
       </c>
-      <c r="R84" s="50"/>
-      <c r="S84" s="50" t="str">
+      <c r="R84" s="47"/>
+      <c r="S84" s="47" t="str">
         <f aca="false">IF(E84&gt;0,E84-Q84," ")</f>
         <v> </v>
       </c>
-      <c r="T84" s="50"/>
+      <c r="T84" s="47"/>
       <c r="U84" s="54"/>
       <c r="V84" s="57"/>
-      <c r="W84" s="53" t="str">
+      <c r="W84" s="50" t="str">
         <f aca="false">IF(V84&gt;0,E84," ")</f>
         <v> </v>
       </c>
-      <c r="X84" s="53" t="str">
+      <c r="X84" s="50" t="str">
         <f aca="false">IF(V84&gt;0,J84," ")</f>
         <v> </v>
       </c>
-      <c r="Y84" s="50" t="str">
+      <c r="Y84" s="47" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&lt;S84,S84-V84," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z84" s="50" t="str">
+      <c r="Z84" s="47" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&gt;S84,V84-S84," ")," ")</f>
         <v> </v>
       </c>
@@ -6227,59 +6245,59 @@
       <c r="A85" s="42"/>
       <c r="B85" s="54"/>
       <c r="C85" s="55"/>
-      <c r="D85" s="81"/>
+      <c r="D85" s="80"/>
       <c r="E85" s="57"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
       <c r="H85" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="53" t="str">
+      <c r="I85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,MIN(E85*H85,G85)," ")</f>
         <v> </v>
       </c>
-      <c r="J85" s="53" t="str">
+      <c r="J85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,F85+I85," ")</f>
         <v> </v>
       </c>
-      <c r="K85" s="53" t="str">
+      <c r="K85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85-J85," ")</f>
         <v> </v>
       </c>
-      <c r="L85" s="53"/>
+      <c r="L85" s="50"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="53"/>
-      <c r="O85" s="50"/>
+      <c r="N85" s="50"/>
+      <c r="O85" s="47"/>
       <c r="P85" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q85" s="50" t="str">
+      <c r="Q85" s="47" t="str">
         <f aca="false">IF(E85&gt;0,E85*P85," ")</f>
         <v> </v>
       </c>
-      <c r="R85" s="50"/>
-      <c r="S85" s="50" t="str">
+      <c r="R85" s="47"/>
+      <c r="S85" s="47" t="str">
         <f aca="false">IF(E85&gt;0,E85-Q85," ")</f>
         <v> </v>
       </c>
-      <c r="T85" s="50"/>
+      <c r="T85" s="47"/>
       <c r="U85" s="54"/>
       <c r="V85" s="57"/>
-      <c r="W85" s="53" t="str">
+      <c r="W85" s="50" t="str">
         <f aca="false">IF(V85&gt;0,E85," ")</f>
         <v> </v>
       </c>
-      <c r="X85" s="53" t="str">
+      <c r="X85" s="50" t="str">
         <f aca="false">IF(V85&gt;0,J85," ")</f>
         <v> </v>
       </c>
-      <c r="Y85" s="50" t="str">
+      <c r="Y85" s="47" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&lt;S85,S85-V85," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z85" s="50" t="str">
+      <c r="Z85" s="47" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&gt;S85,V85-S85," ")," ")</f>
         <v> </v>
       </c>
@@ -6289,59 +6307,59 @@
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="81"/>
+      <c r="D86" s="80"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="53" t="str">
+      <c r="I86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="53" t="str">
+      <c r="J86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="53" t="str">
+      <c r="K86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
         <v> </v>
       </c>
-      <c r="L86" s="53"/>
+      <c r="L86" s="50"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="53"/>
-      <c r="O86" s="50"/>
+      <c r="N86" s="50"/>
+      <c r="O86" s="47"/>
       <c r="P86" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q86" s="50" t="str">
+      <c r="Q86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="50"/>
-      <c r="S86" s="50" t="str">
+      <c r="R86" s="47"/>
+      <c r="S86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="50"/>
+      <c r="T86" s="47"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="53" t="str">
+      <c r="W86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="53" t="str">
+      <c r="X86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="50" t="str">
+      <c r="Y86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="50" t="str">
+      <c r="Z86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6351,59 +6369,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="81"/>
+      <c r="D87" s="80"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="53" t="str">
+      <c r="I87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="53" t="str">
+      <c r="J87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="53" t="str">
+      <c r="K87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
         <v> </v>
       </c>
-      <c r="L87" s="53"/>
+      <c r="L87" s="50"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="53"/>
-      <c r="O87" s="50"/>
+      <c r="N87" s="50"/>
+      <c r="O87" s="47"/>
       <c r="P87" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q87" s="50" t="str">
+      <c r="Q87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="50"/>
-      <c r="S87" s="50" t="str">
+      <c r="R87" s="47"/>
+      <c r="S87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="50"/>
+      <c r="T87" s="47"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="53" t="str">
+      <c r="W87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="53" t="str">
+      <c r="X87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="50" t="str">
+      <c r="Y87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="50" t="str">
+      <c r="Z87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6412,7 +6430,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="42"/>
       <c r="B88" s="59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -6441,9 +6459,9 @@
         <f aca="false">SUM(K83:K87)</f>
         <v>0</v>
       </c>
-      <c r="L88" s="53"/>
+      <c r="L88" s="50"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="53"/>
+      <c r="N88" s="50"/>
       <c r="O88" s="61" t="n">
         <f aca="false">SUM(O83:O87)</f>
         <v>0</v>
@@ -6461,8 +6479,8 @@
         <f aca="false">SUM(S83:S87)</f>
         <v>0</v>
       </c>
-      <c r="T88" s="50"/>
-      <c r="U88" s="52"/>
+      <c r="T88" s="47"/>
+      <c r="U88" s="49"/>
       <c r="V88" s="60" t="n">
         <f aca="false">SUM(V83:V87)</f>
         <v>0</v>
@@ -6490,124 +6508,124 @@
       <c r="B89" s="63"/>
       <c r="C89" s="64"/>
       <c r="D89" s="65"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
       <c r="H89" s="58"/>
-      <c r="I89" s="53"/>
-      <c r="J89" s="53"/>
-      <c r="K89" s="53"/>
-      <c r="L89" s="53"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
+      <c r="L89" s="50"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="53"/>
-      <c r="O89" s="53"/>
+      <c r="N89" s="50"/>
+      <c r="O89" s="50"/>
       <c r="P89" s="62"/>
-      <c r="Q89" s="53"/>
-      <c r="R89" s="53"/>
-      <c r="S89" s="53"/>
-      <c r="T89" s="50"/>
-      <c r="U89" s="52"/>
-      <c r="V89" s="53"/>
-      <c r="W89" s="53"/>
-      <c r="X89" s="53"/>
-      <c r="Y89" s="53"/>
-      <c r="Z89" s="53"/>
+      <c r="Q89" s="50"/>
+      <c r="R89" s="50"/>
+      <c r="S89" s="50"/>
+      <c r="T89" s="47"/>
+      <c r="U89" s="49"/>
+      <c r="V89" s="50"/>
+      <c r="W89" s="50"/>
+      <c r="X89" s="50"/>
+      <c r="Y89" s="50"/>
+      <c r="Z89" s="50"/>
       <c r="AA89" s="25"/>
     </row>
     <row r="90" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="42"/>
-      <c r="B90" s="70" t="str">
+      <c r="B90" s="69" t="str">
         <f aca="false">B37</f>
         <v>Motor Vehicles - costing over £</v>
       </c>
-      <c r="C90" s="70"/>
-      <c r="D90" s="71" t="n">
+      <c r="C90" s="69"/>
+      <c r="D90" s="70" t="n">
         <f aca="false">D37</f>
         <v>12000</v>
       </c>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="83" t="n">
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="82" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="53"/>
+      <c r="I90" s="50"/>
+      <c r="J90" s="50"/>
+      <c r="K90" s="50"/>
+      <c r="L90" s="50"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="53"/>
-      <c r="O90" s="50"/>
+      <c r="N90" s="50"/>
+      <c r="O90" s="47"/>
       <c r="P90" s="62"/>
-      <c r="Q90" s="50"/>
-      <c r="R90" s="50"/>
-      <c r="S90" s="50"/>
-      <c r="T90" s="50"/>
-      <c r="U90" s="52"/>
-      <c r="V90" s="53"/>
-      <c r="W90" s="53"/>
-      <c r="X90" s="53"/>
-      <c r="Y90" s="50"/>
-      <c r="Z90" s="50"/>
+      <c r="Q90" s="47"/>
+      <c r="R90" s="47"/>
+      <c r="S90" s="47"/>
+      <c r="T90" s="47"/>
+      <c r="U90" s="49"/>
+      <c r="V90" s="50"/>
+      <c r="W90" s="50"/>
+      <c r="X90" s="50"/>
+      <c r="Y90" s="47"/>
+      <c r="Z90" s="47"/>
       <c r="AA90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="81"/>
+      <c r="D91" s="80"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I91" s="53" t="str">
+      <c r="I91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="53" t="str">
+      <c r="J91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="53" t="str">
+      <c r="K91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
         <v> </v>
       </c>
-      <c r="L91" s="53"/>
-      <c r="M91" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="53"/>
-      <c r="O91" s="50"/>
-      <c r="P91" s="51"/>
-      <c r="Q91" s="50"/>
-      <c r="R91" s="50" t="str">
+      <c r="L91" s="50"/>
+      <c r="M91" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="50"/>
+      <c r="O91" s="47"/>
+      <c r="P91" s="48"/>
+      <c r="Q91" s="47"/>
+      <c r="R91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
         <v> </v>
       </c>
-      <c r="S91" s="50" t="str">
+      <c r="S91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,E91-R91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="50"/>
+      <c r="T91" s="47"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="53" t="str">
+      <c r="W91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="53" t="str">
+      <c r="X91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="50" t="str">
+      <c r="Y91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,(S91-V91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="50" t="str">
+      <c r="Z91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,(V91-S91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
@@ -6617,58 +6635,58 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="81"/>
+      <c r="D92" s="80"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I92" s="53" t="str">
+      <c r="I92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="53" t="str">
+      <c r="J92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="53" t="str">
+      <c r="K92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
         <v> </v>
       </c>
-      <c r="L92" s="53"/>
-      <c r="M92" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="53"/>
-      <c r="O92" s="50"/>
-      <c r="P92" s="51"/>
-      <c r="Q92" s="50"/>
-      <c r="R92" s="50" t="str">
+      <c r="L92" s="50"/>
+      <c r="M92" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="50"/>
+      <c r="O92" s="47"/>
+      <c r="P92" s="48"/>
+      <c r="Q92" s="47"/>
+      <c r="R92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
         <v> </v>
       </c>
-      <c r="S92" s="50" t="str">
+      <c r="S92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,E92-R92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="50"/>
+      <c r="T92" s="47"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="53" t="str">
+      <c r="W92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="53" t="str">
+      <c r="X92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="50" t="str">
+      <c r="Y92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,(S92-V92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="50" t="str">
+      <c r="Z92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,(V92-S92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
@@ -6678,58 +6696,58 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="81"/>
+      <c r="D93" s="80"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="53"/>
-      <c r="G93" s="53"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I93" s="53" t="str">
+      <c r="I93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="53" t="str">
+      <c r="J93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="53" t="str">
+      <c r="K93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
         <v> </v>
       </c>
-      <c r="L93" s="53"/>
-      <c r="M93" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="53"/>
-      <c r="O93" s="50"/>
-      <c r="P93" s="51"/>
-      <c r="Q93" s="50"/>
-      <c r="R93" s="50" t="str">
+      <c r="L93" s="50"/>
+      <c r="M93" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="50"/>
+      <c r="O93" s="47"/>
+      <c r="P93" s="48"/>
+      <c r="Q93" s="47"/>
+      <c r="R93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
         <v> </v>
       </c>
-      <c r="S93" s="50" t="str">
+      <c r="S93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,E93-R93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="50"/>
+      <c r="T93" s="47"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="53" t="str">
+      <c r="W93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="53" t="str">
+      <c r="X93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="50" t="str">
+      <c r="Y93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,(S93-V93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="50" t="str">
+      <c r="Z93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,(V93-S93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
@@ -6739,58 +6757,58 @@
       <c r="A94" s="42"/>
       <c r="B94" s="54"/>
       <c r="C94" s="55"/>
-      <c r="D94" s="81"/>
+      <c r="D94" s="80"/>
       <c r="E94" s="57"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
       <c r="H94" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I94" s="53" t="str">
+      <c r="I94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*H94,G94)," ")</f>
         <v> </v>
       </c>
-      <c r="J94" s="53" t="str">
+      <c r="J94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,F94+I94," ")</f>
         <v> </v>
       </c>
-      <c r="K94" s="53" t="str">
+      <c r="K94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,E94-J94," ")</f>
         <v> </v>
       </c>
-      <c r="L94" s="53"/>
-      <c r="M94" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="53"/>
-      <c r="O94" s="50"/>
-      <c r="P94" s="51"/>
-      <c r="Q94" s="50"/>
-      <c r="R94" s="50" t="str">
+      <c r="L94" s="50"/>
+      <c r="M94" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="50"/>
+      <c r="O94" s="47"/>
+      <c r="P94" s="48"/>
+      <c r="Q94" s="47"/>
+      <c r="R94" s="47" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
         <v> </v>
       </c>
-      <c r="S94" s="50" t="str">
+      <c r="S94" s="47" t="str">
         <f aca="false">IF(E94&gt;0,E94-R94," ")</f>
         <v> </v>
       </c>
-      <c r="T94" s="50"/>
+      <c r="T94" s="47"/>
       <c r="U94" s="54"/>
       <c r="V94" s="57"/>
-      <c r="W94" s="53" t="str">
+      <c r="W94" s="50" t="str">
         <f aca="false">IF(V94&gt;0,E94," ")</f>
         <v> </v>
       </c>
-      <c r="X94" s="53" t="str">
+      <c r="X94" s="50" t="str">
         <f aca="false">IF(V94&gt;0,J94," ")</f>
         <v> </v>
       </c>
-      <c r="Y94" s="50" t="str">
+      <c r="Y94" s="47" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&lt;S94,(S94-V94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z94" s="50" t="str">
+      <c r="Z94" s="47" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&gt;S94,(V94-S94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
@@ -6800,58 +6818,58 @@
       <c r="A95" s="42"/>
       <c r="B95" s="54"/>
       <c r="C95" s="55"/>
-      <c r="D95" s="81"/>
+      <c r="D95" s="80"/>
       <c r="E95" s="57"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50"/>
       <c r="H95" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I95" s="53" t="str">
+      <c r="I95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*H95,G95)," ")</f>
         <v> </v>
       </c>
-      <c r="J95" s="53" t="str">
+      <c r="J95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,F95+I95," ")</f>
         <v> </v>
       </c>
-      <c r="K95" s="53" t="str">
+      <c r="K95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,E95-J95," ")</f>
         <v> </v>
       </c>
-      <c r="L95" s="53"/>
-      <c r="M95" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="53"/>
-      <c r="O95" s="50"/>
-      <c r="P95" s="51"/>
-      <c r="Q95" s="50"/>
-      <c r="R95" s="50" t="str">
+      <c r="L95" s="50"/>
+      <c r="M95" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="50"/>
+      <c r="O95" s="47"/>
+      <c r="P95" s="48"/>
+      <c r="Q95" s="47"/>
+      <c r="R95" s="47" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
         <v> </v>
       </c>
-      <c r="S95" s="50" t="str">
+      <c r="S95" s="47" t="str">
         <f aca="false">IF(E95&gt;0,E95-R95," ")</f>
         <v> </v>
       </c>
-      <c r="T95" s="50"/>
+      <c r="T95" s="47"/>
       <c r="U95" s="54"/>
       <c r="V95" s="57"/>
-      <c r="W95" s="53" t="str">
+      <c r="W95" s="50" t="str">
         <f aca="false">IF(V95&gt;0,E95," ")</f>
         <v> </v>
       </c>
-      <c r="X95" s="53" t="str">
+      <c r="X95" s="50" t="str">
         <f aca="false">IF(V95&gt;0,J95," ")</f>
         <v> </v>
       </c>
-      <c r="Y95" s="50" t="str">
+      <c r="Y95" s="47" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&lt;S95,(S95-V95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z95" s="50" t="str">
+      <c r="Z95" s="47" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&gt;S95,(V95-S95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
@@ -6859,95 +6877,95 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="84" t="str">
+      <c r="B96" s="83" t="str">
         <f aca="false">B43</f>
         <v>Motor Vehicles - costing under £</v>
       </c>
-      <c r="C96" s="84"/>
-      <c r="D96" s="71" t="n">
+      <c r="C96" s="83"/>
+      <c r="D96" s="70" t="n">
         <f aca="false">D43</f>
         <v>12000</v>
       </c>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="53"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
       <c r="H96" s="58"/>
-      <c r="I96" s="53"/>
-      <c r="J96" s="53"/>
-      <c r="K96" s="53"/>
-      <c r="L96" s="53"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+      <c r="L96" s="50"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="53"/>
-      <c r="O96" s="50"/>
-      <c r="P96" s="51"/>
-      <c r="Q96" s="50"/>
-      <c r="R96" s="50"/>
-      <c r="S96" s="50"/>
-      <c r="T96" s="50"/>
-      <c r="U96" s="52"/>
-      <c r="V96" s="53"/>
-      <c r="W96" s="53"/>
-      <c r="X96" s="53"/>
-      <c r="Y96" s="50"/>
-      <c r="Z96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="47"/>
+      <c r="P96" s="48"/>
+      <c r="Q96" s="47"/>
+      <c r="R96" s="47"/>
+      <c r="S96" s="47"/>
+      <c r="T96" s="47"/>
+      <c r="U96" s="49"/>
+      <c r="V96" s="50"/>
+      <c r="W96" s="50"/>
+      <c r="X96" s="50"/>
+      <c r="Y96" s="47"/>
+      <c r="Z96" s="47"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="81"/>
+      <c r="D97" s="80"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="53"/>
-      <c r="G97" s="53"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="53" t="str">
+      <c r="I97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="53" t="str">
+      <c r="J97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="53" t="str">
+      <c r="K97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
         <v> </v>
       </c>
-      <c r="L97" s="53"/>
-      <c r="M97" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="53"/>
-      <c r="O97" s="50"/>
-      <c r="P97" s="51"/>
-      <c r="Q97" s="50"/>
-      <c r="R97" s="50" t="str">
+      <c r="L97" s="50"/>
+      <c r="M97" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="50"/>
+      <c r="O97" s="47"/>
+      <c r="P97" s="48"/>
+      <c r="Q97" s="47"/>
+      <c r="R97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="50" t="str">
+      <c r="S97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="50"/>
+      <c r="T97" s="47"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="53" t="str">
+      <c r="W97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="53" t="str">
+      <c r="X97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="50" t="str">
+      <c r="Y97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="50" t="str">
+      <c r="Z97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -6957,58 +6975,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="81"/>
+      <c r="D98" s="80"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="53"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="53" t="str">
+      <c r="I98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="53" t="str">
+      <c r="J98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="53" t="str">
+      <c r="K98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
         <v> </v>
       </c>
-      <c r="L98" s="53"/>
-      <c r="M98" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="53"/>
-      <c r="O98" s="50"/>
-      <c r="P98" s="51"/>
-      <c r="Q98" s="50"/>
-      <c r="R98" s="50" t="str">
+      <c r="L98" s="50"/>
+      <c r="M98" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="50"/>
+      <c r="O98" s="47"/>
+      <c r="P98" s="48"/>
+      <c r="Q98" s="47"/>
+      <c r="R98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="50" t="str">
+      <c r="S98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="50"/>
+      <c r="T98" s="47"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="53" t="str">
+      <c r="W98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="53" t="str">
+      <c r="X98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="50" t="str">
+      <c r="Y98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="50" t="str">
+      <c r="Z98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -7018,58 +7036,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="81"/>
+      <c r="D99" s="80"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="53"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="53" t="str">
+      <c r="I99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="53" t="str">
+      <c r="J99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="53" t="str">
+      <c r="K99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
         <v> </v>
       </c>
-      <c r="L99" s="53"/>
-      <c r="M99" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="53"/>
-      <c r="O99" s="50"/>
-      <c r="P99" s="51"/>
-      <c r="Q99" s="50"/>
-      <c r="R99" s="50" t="str">
+      <c r="L99" s="50"/>
+      <c r="M99" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="50"/>
+      <c r="O99" s="47"/>
+      <c r="P99" s="48"/>
+      <c r="Q99" s="47"/>
+      <c r="R99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="50" t="str">
+      <c r="S99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="50"/>
+      <c r="T99" s="47"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="53" t="str">
+      <c r="W99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="53" t="str">
+      <c r="X99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="50" t="str">
+      <c r="Y99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="50" t="str">
+      <c r="Z99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -7079,58 +7097,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="81"/>
+      <c r="D100" s="80"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="53"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="53" t="str">
+      <c r="I100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="53" t="str">
+      <c r="J100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="53" t="str">
+      <c r="K100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
         <v> </v>
       </c>
-      <c r="L100" s="53"/>
-      <c r="M100" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="53"/>
-      <c r="O100" s="50"/>
-      <c r="P100" s="51"/>
-      <c r="Q100" s="50"/>
-      <c r="R100" s="50" t="str">
+      <c r="L100" s="50"/>
+      <c r="M100" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="50"/>
+      <c r="O100" s="47"/>
+      <c r="P100" s="48"/>
+      <c r="Q100" s="47"/>
+      <c r="R100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="50" t="str">
+      <c r="S100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="50"/>
+      <c r="T100" s="47"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="53" t="str">
+      <c r="W100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="53" t="str">
+      <c r="X100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="50" t="str">
+      <c r="Y100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="50" t="str">
+      <c r="Z100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -7140,58 +7158,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="81"/>
+      <c r="D101" s="80"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="53"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="53" t="str">
+      <c r="I101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="53" t="str">
+      <c r="J101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="53" t="str">
+      <c r="K101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
         <v> </v>
       </c>
-      <c r="L101" s="53"/>
-      <c r="M101" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="53"/>
-      <c r="O101" s="50"/>
-      <c r="P101" s="51"/>
-      <c r="Q101" s="50"/>
-      <c r="R101" s="50" t="str">
+      <c r="L101" s="50"/>
+      <c r="M101" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="50"/>
+      <c r="O101" s="47"/>
+      <c r="P101" s="48"/>
+      <c r="Q101" s="47"/>
+      <c r="R101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="50" t="str">
+      <c r="S101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="50"/>
+      <c r="T101" s="47"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="53" t="str">
+      <c r="W101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="53" t="str">
+      <c r="X101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="50" t="str">
+      <c r="Y101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="50" t="str">
+      <c r="Z101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7199,94 +7217,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C102" s="66"/>
-      <c r="D102" s="69"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
+      <c r="B102" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" s="51"/>
+      <c r="D102" s="68"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
-      <c r="L102" s="53"/>
+      <c r="I102" s="50"/>
+      <c r="J102" s="50"/>
+      <c r="K102" s="50"/>
+      <c r="L102" s="50"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="53"/>
-      <c r="O102" s="50"/>
-      <c r="P102" s="51"/>
-      <c r="Q102" s="50"/>
-      <c r="R102" s="50"/>
-      <c r="S102" s="50"/>
-      <c r="T102" s="50"/>
-      <c r="U102" s="52"/>
-      <c r="V102" s="53"/>
-      <c r="W102" s="53"/>
-      <c r="X102" s="53"/>
-      <c r="Y102" s="50"/>
-      <c r="Z102" s="50"/>
+      <c r="N102" s="50"/>
+      <c r="O102" s="47"/>
+      <c r="P102" s="48"/>
+      <c r="Q102" s="47"/>
+      <c r="R102" s="47"/>
+      <c r="S102" s="47"/>
+      <c r="T102" s="47"/>
+      <c r="U102" s="49"/>
+      <c r="V102" s="50"/>
+      <c r="W102" s="50"/>
+      <c r="X102" s="50"/>
+      <c r="Y102" s="47"/>
+      <c r="Z102" s="47"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="81"/>
+      <c r="D103" s="80"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="53"/>
-      <c r="G103" s="53"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="53" t="str">
+      <c r="I103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="53" t="str">
+      <c r="J103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="53" t="str">
+      <c r="K103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
         <v> </v>
       </c>
-      <c r="L103" s="53"/>
-      <c r="M103" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="53"/>
-      <c r="O103" s="50"/>
+      <c r="L103" s="50"/>
+      <c r="M103" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="50"/>
+      <c r="O103" s="47"/>
       <c r="P103" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q103" s="50" t="str">
+      <c r="Q103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="50"/>
-      <c r="S103" s="50" t="str">
+      <c r="R103" s="47"/>
+      <c r="S103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="50"/>
+      <c r="T103" s="47"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="53" t="str">
+      <c r="W103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="53" t="str">
+      <c r="X103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="50" t="str">
+      <c r="Y103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="50" t="str">
+      <c r="Z103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7296,61 +7314,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="81"/>
+      <c r="D104" s="80"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="53"/>
-      <c r="G104" s="53"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="53" t="str">
+      <c r="I104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="53" t="str">
+      <c r="J104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="53" t="str">
+      <c r="K104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
         <v> </v>
       </c>
-      <c r="L104" s="53"/>
-      <c r="M104" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="53"/>
-      <c r="O104" s="50"/>
+      <c r="L104" s="50"/>
+      <c r="M104" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="50"/>
+      <c r="O104" s="47"/>
       <c r="P104" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q104" s="50" t="str">
+      <c r="Q104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="50"/>
-      <c r="S104" s="50" t="str">
+      <c r="R104" s="47"/>
+      <c r="S104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="50"/>
+      <c r="T104" s="47"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="53" t="str">
+      <c r="W104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="53" t="str">
+      <c r="X104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="50" t="str">
+      <c r="Y104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="50" t="str">
+      <c r="Z104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7360,61 +7378,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="81"/>
+      <c r="D105" s="80"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="53" t="str">
+      <c r="I105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="53" t="str">
+      <c r="J105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="53" t="str">
+      <c r="K105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
         <v> </v>
       </c>
-      <c r="L105" s="53"/>
-      <c r="M105" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="53"/>
-      <c r="O105" s="50"/>
+      <c r="L105" s="50"/>
+      <c r="M105" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="50"/>
+      <c r="O105" s="47"/>
       <c r="P105" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q105" s="50" t="str">
+      <c r="Q105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="50"/>
-      <c r="S105" s="50" t="str">
+      <c r="R105" s="47"/>
+      <c r="S105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="50"/>
+      <c r="T105" s="47"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="53" t="str">
+      <c r="W105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="53" t="str">
+      <c r="X105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="50" t="str">
+      <c r="Y105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="50" t="str">
+      <c r="Z105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7424,61 +7442,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="81"/>
+      <c r="D106" s="80"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="53"/>
-      <c r="G106" s="53"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="53" t="str">
+      <c r="I106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="53" t="str">
+      <c r="J106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="53" t="str">
+      <c r="K106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
         <v> </v>
       </c>
-      <c r="L106" s="53"/>
-      <c r="M106" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="53"/>
-      <c r="O106" s="50"/>
+      <c r="L106" s="50"/>
+      <c r="M106" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="50"/>
+      <c r="O106" s="47"/>
       <c r="P106" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q106" s="50" t="str">
+      <c r="Q106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="50"/>
-      <c r="S106" s="50" t="str">
+      <c r="R106" s="47"/>
+      <c r="S106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="50"/>
+      <c r="T106" s="47"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="53" t="str">
+      <c r="W106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="53" t="str">
+      <c r="X106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="50" t="str">
+      <c r="Y106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="50" t="str">
+      <c r="Z106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7488,61 +7506,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="81"/>
-      <c r="E107" s="85"/>
-      <c r="F107" s="53"/>
-      <c r="G107" s="53"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="84"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="53" t="str">
+      <c r="I107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="53" t="str">
+      <c r="J107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="53" t="str">
+      <c r="K107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
         <v> </v>
       </c>
-      <c r="L107" s="53"/>
-      <c r="M107" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="53"/>
-      <c r="O107" s="50"/>
+      <c r="L107" s="50"/>
+      <c r="M107" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="50"/>
+      <c r="O107" s="47"/>
       <c r="P107" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q107" s="50" t="str">
+      <c r="Q107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="50"/>
-      <c r="S107" s="50" t="str">
+      <c r="R107" s="47"/>
+      <c r="S107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="50"/>
+      <c r="T107" s="47"/>
       <c r="U107" s="54"/>
-      <c r="V107" s="85"/>
-      <c r="W107" s="53" t="str">
+      <c r="V107" s="84"/>
+      <c r="W107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="53" t="str">
+      <c r="X107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="50" t="str">
+      <c r="Y107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="50" t="str">
+      <c r="Z107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7551,7 +7569,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7580,9 +7598,9 @@
         <f aca="false">SUM(K91:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="53"/>
+      <c r="L108" s="50"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="53"/>
+      <c r="N108" s="50"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O91:O107)</f>
         <v>0</v>
@@ -7600,8 +7618,8 @@
         <f aca="false">SUM(S91:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="50"/>
-      <c r="U108" s="52"/>
+      <c r="T108" s="47"/>
+      <c r="U108" s="49"/>
       <c r="V108" s="61" t="n">
         <f aca="false">SUM(V91:V107)</f>
         <v>0</v>
@@ -7626,31 +7644,31 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="74"/>
-      <c r="D109" s="69"/>
-      <c r="E109" s="53"/>
-      <c r="F109" s="53"/>
-      <c r="G109" s="53"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="73"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="53"/>
+      <c r="I109" s="50"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="50"/>
+      <c r="L109" s="50"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="53"/>
-      <c r="O109" s="50"/>
-      <c r="P109" s="51"/>
-      <c r="Q109" s="50"/>
-      <c r="R109" s="50"/>
-      <c r="S109" s="50"/>
-      <c r="T109" s="50"/>
-      <c r="U109" s="52"/>
-      <c r="V109" s="53"/>
-      <c r="W109" s="50"/>
-      <c r="X109" s="50"/>
-      <c r="Y109" s="50"/>
-      <c r="Z109" s="50"/>
+      <c r="N109" s="50"/>
+      <c r="O109" s="47"/>
+      <c r="P109" s="48"/>
+      <c r="Q109" s="47"/>
+      <c r="R109" s="47"/>
+      <c r="S109" s="47"/>
+      <c r="T109" s="47"/>
+      <c r="U109" s="49"/>
+      <c r="V109" s="50"/>
+      <c r="W109" s="47"/>
+      <c r="X109" s="47"/>
+      <c r="Y109" s="47"/>
+      <c r="Z109" s="47"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7664,103 +7682,103 @@
         <f aca="false">D59</f>
         <v>45753</v>
       </c>
-      <c r="E110" s="75" t="n">
+      <c r="E110" s="74" t="n">
         <f aca="false">E64+E72+E80+E88+E108</f>
         <v>0</v>
       </c>
-      <c r="F110" s="75" t="n">
+      <c r="F110" s="74" t="n">
         <f aca="false">F64+F72+F80+F88+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="75" t="n">
+      <c r="G110" s="74" t="n">
         <f aca="false">G64+G72+G80+G88+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="75" t="n">
+      <c r="I110" s="74" t="n">
         <f aca="false">I64+I72+I80+I88+I108</f>
         <v>0</v>
       </c>
-      <c r="J110" s="75" t="n">
+      <c r="J110" s="74" t="n">
         <f aca="false">J64+J72+J80+J88+J108</f>
         <v>0</v>
       </c>
-      <c r="K110" s="75" t="n">
+      <c r="K110" s="74" t="n">
         <f aca="false">K64+K72+K80+K88+K108</f>
         <v>0</v>
       </c>
-      <c r="L110" s="53"/>
+      <c r="L110" s="50"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="53"/>
-      <c r="O110" s="75" t="n">
+      <c r="N110" s="50"/>
+      <c r="O110" s="74" t="n">
         <f aca="false">O64+O72+O80+O88+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="75" t="n">
+      <c r="Q110" s="74" t="n">
         <f aca="false">Q64+Q72+Q80+Q88+Q108</f>
         <v>0</v>
       </c>
-      <c r="R110" s="75" t="n">
+      <c r="R110" s="74" t="n">
         <f aca="false">R64+R72+R80+R88+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="75" t="n">
+      <c r="S110" s="74" t="n">
         <f aca="false">S64+S72+S80+S88+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="50"/>
-      <c r="U110" s="52"/>
-      <c r="V110" s="75" t="n">
+      <c r="T110" s="47"/>
+      <c r="U110" s="49"/>
+      <c r="V110" s="74" t="n">
         <f aca="false">V64+V72+V80+V88+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="75" t="n">
+      <c r="W110" s="74" t="n">
         <f aca="false">W64+W72+W80+W88+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="75" t="n">
+      <c r="X110" s="74" t="n">
         <f aca="false">X64+X72+X80+X88+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="75" t="n">
+      <c r="Y110" s="74" t="n">
         <f aca="false">Y64+Y72+Y80+Y88+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="75" t="n">
+      <c r="Z110" s="74" t="n">
         <f aca="false">Z64+Z72+Z80+Z88+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="86"/>
-      <c r="B111" s="87"/>
-      <c r="C111" s="88"/>
-      <c r="D111" s="89"/>
-      <c r="E111" s="90"/>
-      <c r="F111" s="90"/>
-      <c r="G111" s="90"/>
-      <c r="H111" s="91"/>
-      <c r="I111" s="90"/>
-      <c r="J111" s="90"/>
-      <c r="K111" s="90"/>
-      <c r="L111" s="90"/>
-      <c r="M111" s="91"/>
-      <c r="N111" s="90"/>
-      <c r="O111" s="92"/>
-      <c r="P111" s="93"/>
-      <c r="Q111" s="92"/>
-      <c r="R111" s="92"/>
-      <c r="S111" s="92"/>
-      <c r="T111" s="92"/>
-      <c r="U111" s="87"/>
-      <c r="V111" s="90"/>
-      <c r="W111" s="90"/>
-      <c r="X111" s="90"/>
-      <c r="Y111" s="92"/>
-      <c r="Z111" s="92"/>
-      <c r="AA111" s="94"/>
+      <c r="A111" s="85"/>
+      <c r="B111" s="86"/>
+      <c r="C111" s="87"/>
+      <c r="D111" s="88"/>
+      <c r="E111" s="89"/>
+      <c r="F111" s="89"/>
+      <c r="G111" s="89"/>
+      <c r="H111" s="90"/>
+      <c r="I111" s="89"/>
+      <c r="J111" s="89"/>
+      <c r="K111" s="89"/>
+      <c r="L111" s="89"/>
+      <c r="M111" s="90"/>
+      <c r="N111" s="89"/>
+      <c r="O111" s="91"/>
+      <c r="P111" s="92"/>
+      <c r="Q111" s="91"/>
+      <c r="R111" s="91"/>
+      <c r="S111" s="91"/>
+      <c r="T111" s="91"/>
+      <c r="U111" s="86"/>
+      <c r="V111" s="89"/>
+      <c r="W111" s="89"/>
+      <c r="X111" s="89"/>
+      <c r="Y111" s="91"/>
+      <c r="Z111" s="91"/>
+      <c r="AA111" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -7846,37 +7864,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="95" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="95" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="95" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="95" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="95" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="95" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="95" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="95" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="95" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="95" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="95" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="94" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="94" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="94" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="94" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="94" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="94" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="94" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="94" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="94" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="94" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="94" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="96"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7888,23 +7906,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="105"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="101" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="104"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7916,21 +7934,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="105"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="104"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -7942,31 +7960,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98"/>
-      <c r="B4" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="109" t="s">
+      <c r="A4" s="97"/>
+      <c r="B4" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="103"/>
-      <c r="G4" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="109" t="s">
+      <c r="F4" s="102"/>
+      <c r="G4" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="103"/>
-      <c r="M4" s="111" t="s">
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="111"/>
-      <c r="O4" s="105"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="110" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="110"/>
+      <c r="O4" s="104"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -7978,25 +7996,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="98"/>
-      <c r="B5" s="99" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="99" t="s">
+      <c r="A5" s="97"/>
+      <c r="B5" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="100"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="105"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="98" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="99"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="104"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -8008,31 +8026,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="98"/>
-      <c r="B6" s="112" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113" t="n">
+      <c r="A6" s="97"/>
+      <c r="B6" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="112" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="103"/>
-      <c r="G6" s="112" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="113" t="n">
+      <c r="F6" s="102"/>
+      <c r="G6" s="111" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="112" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="103"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="111"/>
-      <c r="O6" s="105"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="104"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -8044,31 +8062,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="98"/>
-      <c r="B7" s="112" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="113" t="n">
+      <c r="A7" s="97"/>
+      <c r="B7" s="111" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="112" t="n">
         <f aca="false">Schedule!E72</f>
         <v>0</v>
       </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="112" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="113" t="n">
+      <c r="F7" s="102"/>
+      <c r="G7" s="111" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="112" t="n">
         <f aca="false">Schedule!V19+Schedule!V72</f>
         <v>0</v>
       </c>
-      <c r="L7" s="103"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="105"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="104"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -8080,31 +8098,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="98"/>
-      <c r="B8" s="112" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="113" t="n">
+      <c r="A8" s="97"/>
+      <c r="B8" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112" t="n">
         <f aca="false">Schedule!E80</f>
         <v>0</v>
       </c>
-      <c r="F8" s="103"/>
-      <c r="G8" s="112" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="113" t="n">
+      <c r="F8" s="102"/>
+      <c r="G8" s="111" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="112" t="n">
         <f aca="false">Schedule!V27+Schedule!V80</f>
         <v>0</v>
       </c>
-      <c r="L8" s="103"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="105"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="104"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -8116,31 +8134,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="98"/>
-      <c r="B9" s="112" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113" t="n">
+      <c r="A9" s="97"/>
+      <c r="B9" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="112" t="n">
         <f aca="false">Schedule!E88</f>
         <v>0</v>
       </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="112" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="113" t="n">
+      <c r="F9" s="102"/>
+      <c r="G9" s="111" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="112" t="n">
         <f aca="false">Schedule!V35+Schedule!V88</f>
         <v>0</v>
       </c>
-      <c r="L9" s="103"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="105"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="104"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -8152,31 +8170,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="98"/>
-      <c r="B10" s="112" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113" t="n">
+      <c r="A10" s="97"/>
+      <c r="B10" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="103"/>
-      <c r="G10" s="112" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="113" t="n">
+      <c r="F10" s="102"/>
+      <c r="G10" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="112" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
         <v>0</v>
       </c>
-      <c r="L10" s="103"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="105"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="104"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8188,31 +8206,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="98"/>
-      <c r="B11" s="114" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="115" t="n">
+      <c r="A11" s="97"/>
+      <c r="B11" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="114" t="n">
         <f aca="false">SUM(E6:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="103"/>
-      <c r="G11" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="115" t="n">
+      <c r="F11" s="102"/>
+      <c r="G11" s="115" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="114" t="n">
         <f aca="false">SUM(K6:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="103"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="111"/>
-      <c r="O11" s="105"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="104"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8224,21 +8242,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="105"/>
+      <c r="A12" s="97"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="104"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8250,31 +8268,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="98"/>
-      <c r="B13" s="114" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="117" t="n">
+      <c r="A13" s="97"/>
+      <c r="B13" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="116" t="n">
         <f aca="false">[2]Mar!$AB$2</f>
         <v>0</v>
       </c>
-      <c r="F13" s="103"/>
-      <c r="G13" s="116" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="117" t="n">
+      <c r="F13" s="102"/>
+      <c r="G13" s="115" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="116" t="n">
         <f aca="false">[3]Mar!$V$2</f>
         <v>0</v>
       </c>
-      <c r="L13" s="103"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="105"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="104"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8286,21 +8304,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="105"/>
+      <c r="A14" s="97"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="104"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8312,33 +8330,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="98"/>
-      <c r="B15" s="118" t="str">
+      <c r="A15" s="97"/>
+      <c r="B15" s="117" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119" t="n">
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="118" t="n">
         <f aca="false">E13-E11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="103"/>
-      <c r="G15" s="118" t="str">
+      <c r="F15" s="102"/>
+      <c r="G15" s="117" t="str">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="119" t="n">
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="118" t="n">
         <f aca="false">K13-K11</f>
         <v>0</v>
       </c>
-      <c r="L15" s="103"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="105"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="104"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8350,21 +8368,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="120"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="125"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="126"/>
+      <c r="A16" s="119"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="124"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="125"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8416,122 +8434,122 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="126" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="126" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="127" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="126" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="126" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="129"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="129"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="128"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="129"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="133" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="n">
+      <c r="A2" s="128"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="132" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133" t="n">
         <f aca="false">SUM(E8:E14)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="129"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="128"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="129"/>
-      <c r="B3" s="137" t="s">
-        <v>59</v>
+      <c r="A3" s="128"/>
+      <c r="B3" s="136" t="s">
+        <v>60</v>
       </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="129"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="129"/>
-      <c r="B4" s="52"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="49"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="129"/>
-    </row>
-    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="140"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="128"/>
+    </row>
+    <row r="5" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="139"/>
       <c r="B5" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="141" t="s">
+      <c r="E5" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="141" t="s">
+      <c r="F5" s="140" t="s">
         <v>65</v>
       </c>
+      <c r="G5" s="140" t="s">
+        <v>66</v>
+      </c>
       <c r="H5" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
+      <c r="I5" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
       <c r="L5" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="140"/>
-    </row>
-    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="140"/>
+        <v>69</v>
+      </c>
+      <c r="M5" s="139"/>
+    </row>
+    <row r="6" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="139"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8539,273 +8557,273 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6" s="141" t="s">
+      <c r="I6" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="K6" s="141" t="s">
+      <c r="J6" s="140" t="s">
         <v>71</v>
       </c>
+      <c r="K6" s="140" t="s">
+        <v>72</v>
+      </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="140"/>
+      <c r="M6" s="139"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="129"/>
-      <c r="B7" s="52"/>
+      <c r="A7" s="128"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="134"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="129"/>
+      <c r="M7" s="128"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="129"/>
+      <c r="A8" s="128"/>
       <c r="B8" s="54"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="135" t="str">
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="134" t="str">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="135" t="str">
+      <c r="J8" s="134" t="str">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="135" t="str">
+      <c r="K8" s="134" t="str">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="129"/>
+      <c r="M8" s="128"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="129"/>
-      <c r="B9" s="52"/>
+      <c r="A9" s="128"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="129"/>
+      <c r="M9" s="128"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="129"/>
+      <c r="A10" s="128"/>
       <c r="B10" s="54"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="143"/>
-      <c r="I10" s="135" t="e">
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="135" t="str">
+      <c r="J10" s="134" t="str">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="135" t="str">
+      <c r="K10" s="134" t="str">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="129"/>
+      <c r="M10" s="128"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="129"/>
-      <c r="B11" s="52"/>
+      <c r="A11" s="128"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="129"/>
+      <c r="M11" s="128"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="129"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="135" t="e">
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="135" t="str">
+      <c r="J12" s="134" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="135" t="str">
+      <c r="K12" s="134" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="129"/>
+      <c r="M12" s="128"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="129"/>
-      <c r="B13" s="52"/>
+      <c r="A13" s="128"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="129"/>
+      <c r="M13" s="128"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="129"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="135" t="e">
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="135" t="str">
+      <c r="J14" s="134" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="135" t="str">
+      <c r="K14" s="134" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="129"/>
+      <c r="M14" s="128"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="129"/>
-      <c r="B15" s="52"/>
+      <c r="A15" s="128"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="129"/>
+      <c r="M15" s="128"/>
     </row>
     <row r="16" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="129"/>
-      <c r="B16" s="99"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="101"/>
-      <c r="M16" s="129"/>
+      <c r="A16" s="128"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="128"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="129"/>
-      <c r="B17" s="137" t="s">
-        <v>72</v>
+      <c r="A17" s="128"/>
+      <c r="B17" s="136" t="s">
+        <v>73</v>
       </c>
       <c r="C17" s="62"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
       <c r="H17" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" s="132"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
+        <v>74</v>
+      </c>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="129"/>
+      <c r="M17" s="128"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="129"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="128"/>
+      <c r="B18" s="49"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
       <c r="L18" s="62"/>
-      <c r="M18" s="129"/>
-    </row>
-    <row r="19" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="140"/>
+      <c r="M18" s="128"/>
+    </row>
+    <row r="19" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="139"/>
       <c r="B19" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="141" t="s">
+      <c r="E19" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="141" t="s">
+      <c r="F19" s="140" t="s">
         <v>65</v>
       </c>
+      <c r="G19" s="140" t="s">
+        <v>66</v>
+      </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
+      <c r="I19" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="J19" s="140"/>
+      <c r="K19" s="140"/>
       <c r="L19" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="M19" s="140"/>
-    </row>
-    <row r="20" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="140"/>
+        <v>69</v>
+      </c>
+      <c r="M19" s="139"/>
+    </row>
+    <row r="20" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="139"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8813,203 +8831,203 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
-      <c r="I20" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="J20" s="141" t="s">
+      <c r="I20" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="K20" s="141" t="s">
+      <c r="J20" s="140" t="s">
         <v>71</v>
       </c>
+      <c r="K20" s="140" t="s">
+        <v>72</v>
+      </c>
       <c r="L20" s="21"/>
-      <c r="M20" s="140"/>
-    </row>
-    <row r="21" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="140"/>
-      <c r="B21" s="144"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="144"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="145"/>
-      <c r="J21" s="145"/>
-      <c r="K21" s="145"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="140"/>
+      <c r="M20" s="139"/>
+    </row>
+    <row r="21" s="141" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="139"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="143"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="139"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="129"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="135" t="str">
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="134" t="str">
         <f aca="false">IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="135" t="str">
+      <c r="J22" s="134" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="135" t="str">
+      <c r="K22" s="134" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="129"/>
+      <c r="M22" s="128"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="129"/>
-      <c r="B23" s="52"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="49"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="135"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="129"/>
+      <c r="M23" s="128"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="129"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="135" t="e">
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="142"/>
+      <c r="I24" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="135" t="str">
+      <c r="J24" s="134" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="135" t="str">
+      <c r="K24" s="134" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="129"/>
+      <c r="M24" s="128"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="129"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="128"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="135"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="129"/>
+      <c r="M25" s="128"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="129"/>
+      <c r="A26" s="128"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="135" t="e">
+      <c r="E26" s="133"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="135" t="str">
+      <c r="J26" s="134" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="135" t="str">
+      <c r="K26" s="134" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="129"/>
+      <c r="M26" s="128"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="129"/>
-      <c r="B27" s="52"/>
+      <c r="A27" s="128"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="134"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="134"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="129"/>
+      <c r="M27" s="128"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="129"/>
+      <c r="A28" s="128"/>
       <c r="B28" s="54"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="134"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="143"/>
-      <c r="I28" s="135" t="e">
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="135" t="str">
+      <c r="J28" s="134" t="str">
         <f aca="false">IF(H28&gt;0,I28-K28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="135" t="str">
+      <c r="K28" s="134" t="str">
         <f aca="false">IF(H28&gt;0,G28/H28," ")</f>
         <v> </v>
       </c>
       <c r="L28" s="56"/>
-      <c r="M28" s="129"/>
+      <c r="M28" s="128"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="129"/>
-      <c r="B29" s="52"/>
+      <c r="A29" s="128"/>
+      <c r="B29" s="49"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="135"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="134"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="129"/>
+      <c r="M29" s="128"/>
     </row>
     <row r="30" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="129"/>
-      <c r="B30" s="99"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="131"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="129"/>
+      <c r="A30" s="128"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
   </si>
   <si>
-    <t xml:space="preserve">Land &amp; Property</t>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Existing Land &amp; Property</t>
@@ -250,16 +250,10 @@
     <t xml:space="preserve">Computers</t>
   </si>
   <si>
-    <t xml:space="preserve">Laptop (0.5 years old)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Existing Computers</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing over £</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Van (2.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing under £</t>
@@ -272,6 +266,9 @@
   </si>
   <si>
     <t xml:space="preserve">NEW FIXED ASSETS Bought AFTER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">New Land &amp; Property</t>
@@ -755,7 +752,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -940,6 +937,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -960,64 +969,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1682,7 +1683,7 @@
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>10098</v>
+        <v>0</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
@@ -1933,45 +1934,24 @@
         <v>22</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="n">
-        <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
-      </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42"/>
-      <c r="B7" s="51" t="s">
+      <c r="D6" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52"/>
+      <c r="E6" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="45"/>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="48" t="n">
         <f aca="false">[1]Admin!$G$13</f>
         <v>0</v>
       </c>
@@ -1979,20 +1959,20 @@
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
-      <c r="M7" s="46"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="45"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="50"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2002,7 +1982,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="50" t="str">
+      <c r="G8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -2010,39 +1990,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="50" t="str">
+      <c r="I8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="50" t="str">
+      <c r="J8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="50" t="str">
+      <c r="K8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
         <v> </v>
       </c>
-      <c r="L8" s="50"/>
+      <c r="L8" s="53"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="50" t="str">
+      <c r="W8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="50" t="str">
+      <c r="X8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2052,7 +2032,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="50" t="str">
+      <c r="G9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -2060,39 +2040,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="50" t="str">
+      <c r="I9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="50" t="str">
+      <c r="J9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="50" t="str">
+      <c r="K9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
         <v> </v>
       </c>
-      <c r="L9" s="50"/>
+      <c r="L9" s="53"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
+      <c r="T9" s="50"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="50" t="str">
+      <c r="W9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="50" t="str">
+      <c r="X9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="50"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2102,7 +2082,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="50" t="str">
+      <c r="G10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -2110,39 +2090,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="50" t="str">
+      <c r="I10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="50" t="str">
+      <c r="J10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="50" t="str">
+      <c r="K10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
         <v> </v>
       </c>
-      <c r="L10" s="50"/>
+      <c r="L10" s="53"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="50" t="str">
+      <c r="W10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="50" t="str">
+      <c r="X10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
+      <c r="Y10" s="50"/>
+      <c r="Z10" s="50"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2177,9 +2157,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="50"/>
+      <c r="L11" s="53"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="50"/>
+      <c r="N11" s="53"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -2197,8 +2177,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="47"/>
-      <c r="U11" s="49"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="52"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2226,62 +2206,62 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="53"/>
+      <c r="W12" s="53"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="53"/>
+      <c r="Z12" s="53"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="66" t="n">
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="67" t="n">
         <f aca="false">[1]Admin!$G$14</f>
         <v>0.1</v>
       </c>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="52"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="53"/>
+      <c r="X13" s="53"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="50"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2291,7 +2271,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="50" t="str">
+      <c r="G14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2299,48 +2279,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="50" t="str">
+      <c r="I14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="50" t="str">
+      <c r="J14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="50" t="str">
+      <c r="K14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
         <v> </v>
       </c>
-      <c r="L14" s="50"/>
+      <c r="L14" s="53"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47" t="str">
+      <c r="N14" s="53"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="47" t="str">
+      <c r="S14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="47"/>
+      <c r="T14" s="50"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="50" t="str">
+      <c r="W14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="50" t="str">
+      <c r="X14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="47" t="str">
+      <c r="Y14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="47" t="str">
+      <c r="Z14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2353,7 +2333,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="50" t="str">
+      <c r="G15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2361,48 +2341,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="50" t="str">
+      <c r="I15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="50" t="str">
+      <c r="J15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="50" t="str">
+      <c r="K15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
         <v> </v>
       </c>
-      <c r="L15" s="50"/>
+      <c r="L15" s="53"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47" t="str">
+      <c r="N15" s="53"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="47" t="str">
+      <c r="S15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="47"/>
+      <c r="T15" s="50"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="50" t="str">
+      <c r="W15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="50" t="str">
+      <c r="X15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="47" t="str">
+      <c r="Y15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="47" t="str">
+      <c r="Z15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2415,7 +2395,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="50" t="str">
+      <c r="G16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2423,48 +2403,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="50" t="str">
+      <c r="I16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="50" t="str">
+      <c r="J16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="50" t="str">
+      <c r="K16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
         <v> </v>
       </c>
-      <c r="L16" s="50"/>
+      <c r="L16" s="53"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47" t="str">
+      <c r="N16" s="53"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="47" t="str">
+      <c r="S16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="47"/>
+      <c r="T16" s="50"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="50" t="str">
+      <c r="W16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="50" t="str">
+      <c r="X16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="47" t="str">
+      <c r="Y16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="47" t="str">
+      <c r="Z16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2477,7 +2457,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="50" t="str">
+      <c r="G17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2485,48 +2465,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="50" t="str">
+      <c r="I17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="50" t="str">
+      <c r="J17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="50" t="str">
+      <c r="K17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
         <v> </v>
       </c>
-      <c r="L17" s="50"/>
+      <c r="L17" s="53"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47" t="str">
+      <c r="N17" s="53"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="47" t="str">
+      <c r="S17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="47"/>
+      <c r="T17" s="50"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="50" t="str">
+      <c r="W17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="50" t="str">
+      <c r="X17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="47" t="str">
+      <c r="Y17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="47" t="str">
+      <c r="Z17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2539,7 +2519,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="50" t="str">
+      <c r="G18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2547,48 +2527,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="50" t="str">
+      <c r="I18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="50" t="str">
+      <c r="J18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="50" t="str">
+      <c r="K18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
         <v> </v>
       </c>
-      <c r="L18" s="50"/>
+      <c r="L18" s="53"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47" t="str">
+      <c r="N18" s="53"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="47" t="str">
+      <c r="S18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="47"/>
+      <c r="T18" s="50"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="50" t="str">
+      <c r="W18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="50" t="str">
+      <c r="X18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="47" t="str">
+      <c r="Y18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="47" t="str">
+      <c r="Z18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2626,9 +2606,9 @@
         <f aca="false">SUM(K14:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="50"/>
+      <c r="L19" s="53"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="50"/>
+      <c r="N19" s="53"/>
       <c r="O19" s="61" t="n">
         <f aca="false">SUM(O14:O18)</f>
         <v>0</v>
@@ -2646,8 +2626,8 @@
         <f aca="false">SUM(S14:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="47"/>
-      <c r="U19" s="49"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="52"/>
       <c r="V19" s="60" t="n">
         <f aca="false">SUM(V14:V18)</f>
         <v>0</v>
@@ -2675,62 +2655,62 @@
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
       <c r="H20" s="58"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
       <c r="P20" s="62"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="47"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="50"/>
-      <c r="Z20" s="50"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="50"/>
+      <c r="U20" s="52"/>
+      <c r="V20" s="53"/>
+      <c r="W20" s="53"/>
+      <c r="X20" s="53"/>
+      <c r="Y20" s="53"/>
+      <c r="Z20" s="53"/>
       <c r="AA20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="42"/>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="66"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="66" t="n">
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="67" t="n">
         <f aca="false">[1]Admin!$G$15</f>
         <v>0.2</v>
       </c>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="49"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="50"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="50"/>
+      <c r="T21" s="50"/>
+      <c r="U21" s="52"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="50"/>
+      <c r="Z21" s="50"/>
       <c r="AA21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2740,7 +2720,7 @@
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
       <c r="F22" s="57"/>
-      <c r="G22" s="50" t="str">
+      <c r="G22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,E22-F22," ")</f>
         <v> </v>
       </c>
@@ -2748,48 +2728,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I22" s="50" t="str">
+      <c r="I22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,MIN(E22*H22,G22)," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="50" t="str">
+      <c r="J22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,F22+I22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="50" t="str">
+      <c r="K22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,E22-J22," ")</f>
         <v> </v>
       </c>
-      <c r="L22" s="50"/>
+      <c r="L22" s="53"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47" t="str">
+      <c r="N22" s="53"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="50" t="str">
         <f aca="false">IF(O22&gt;0,O22*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S22" s="47" t="str">
+      <c r="S22" s="50" t="str">
         <f aca="false">IF(O22&gt;0,O22-R22," ")</f>
         <v> </v>
       </c>
-      <c r="T22" s="47"/>
+      <c r="T22" s="50"/>
       <c r="U22" s="54"/>
       <c r="V22" s="57"/>
-      <c r="W22" s="50" t="str">
+      <c r="W22" s="53" t="str">
         <f aca="false">IF(V22&gt;0,E22," ")</f>
         <v> </v>
       </c>
-      <c r="X22" s="50" t="str">
+      <c r="X22" s="53" t="str">
         <f aca="false">IF(V22&gt;0,J22," ")</f>
         <v> </v>
       </c>
-      <c r="Y22" s="47" t="str">
+      <c r="Y22" s="50" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&lt;S22,S22-V22," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z22" s="47" t="str">
+      <c r="Z22" s="50" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&gt;S22,V22-S22," ")," ")</f>
         <v> </v>
       </c>
@@ -2802,7 +2782,7 @@
       <c r="D23" s="56"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="50" t="str">
+      <c r="G23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,E23-F23," ")</f>
         <v> </v>
       </c>
@@ -2810,48 +2790,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I23" s="50" t="str">
+      <c r="I23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,MIN(E23*H23,G23)," ")</f>
         <v> </v>
       </c>
-      <c r="J23" s="50" t="str">
+      <c r="J23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,F23+I23," ")</f>
         <v> </v>
       </c>
-      <c r="K23" s="50" t="str">
+      <c r="K23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,E23-J23," ")</f>
         <v> </v>
       </c>
-      <c r="L23" s="50"/>
+      <c r="L23" s="53"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47" t="str">
+      <c r="N23" s="53"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="50" t="str">
         <f aca="false">IF(O23&gt;0,O23*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S23" s="47" t="str">
+      <c r="S23" s="50" t="str">
         <f aca="false">IF(O23&gt;0,O23-R23," ")</f>
         <v> </v>
       </c>
-      <c r="T23" s="47"/>
+      <c r="T23" s="50"/>
       <c r="U23" s="54"/>
       <c r="V23" s="57"/>
-      <c r="W23" s="50" t="str">
+      <c r="W23" s="53" t="str">
         <f aca="false">IF(V23&gt;0,E23," ")</f>
         <v> </v>
       </c>
-      <c r="X23" s="50" t="str">
+      <c r="X23" s="53" t="str">
         <f aca="false">IF(V23&gt;0,J23," ")</f>
         <v> </v>
       </c>
-      <c r="Y23" s="47" t="str">
+      <c r="Y23" s="50" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&lt;S23,S23-V23," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z23" s="47" t="str">
+      <c r="Z23" s="50" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&gt;S23,V23-S23," ")," ")</f>
         <v> </v>
       </c>
@@ -2864,7 +2844,7 @@
       <c r="D24" s="56"/>
       <c r="E24" s="57"/>
       <c r="F24" s="57"/>
-      <c r="G24" s="50" t="str">
+      <c r="G24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,E24-F24," ")</f>
         <v> </v>
       </c>
@@ -2872,48 +2852,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I24" s="50" t="str">
+      <c r="I24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,MIN(E24*H24,G24)," ")</f>
         <v> </v>
       </c>
-      <c r="J24" s="50" t="str">
+      <c r="J24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,F24+I24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="50" t="str">
+      <c r="K24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,E24-J24," ")</f>
         <v> </v>
       </c>
-      <c r="L24" s="50"/>
+      <c r="L24" s="53"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47" t="str">
+      <c r="N24" s="53"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="50" t="str">
         <f aca="false">IF(O24&gt;0,O24*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S24" s="47" t="str">
+      <c r="S24" s="50" t="str">
         <f aca="false">IF(O24&gt;0,O24-R24," ")</f>
         <v> </v>
       </c>
-      <c r="T24" s="47"/>
+      <c r="T24" s="50"/>
       <c r="U24" s="54"/>
       <c r="V24" s="57"/>
-      <c r="W24" s="50" t="str">
+      <c r="W24" s="53" t="str">
         <f aca="false">IF(V24&gt;0,E24," ")</f>
         <v> </v>
       </c>
-      <c r="X24" s="50" t="str">
+      <c r="X24" s="53" t="str">
         <f aca="false">IF(V24&gt;0,J24," ")</f>
         <v> </v>
       </c>
-      <c r="Y24" s="47" t="str">
+      <c r="Y24" s="50" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&lt;S24,S24-V24," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z24" s="47" t="str">
+      <c r="Z24" s="50" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&gt;S24,V24-S24," ")," ")</f>
         <v> </v>
       </c>
@@ -2926,7 +2906,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="50" t="str">
+      <c r="G25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2934,48 +2914,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="50" t="str">
+      <c r="I25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="50" t="str">
+      <c r="J25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="50" t="str">
+      <c r="K25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
         <v> </v>
       </c>
-      <c r="L25" s="50"/>
+      <c r="L25" s="53"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47" t="str">
+      <c r="N25" s="53"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="47" t="str">
+      <c r="S25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="47"/>
+      <c r="T25" s="50"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="50" t="str">
+      <c r="W25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="50" t="str">
+      <c r="X25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="47" t="str">
+      <c r="Y25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="47" t="str">
+      <c r="Z25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2988,7 +2968,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="50" t="str">
+      <c r="G26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -2996,48 +2976,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="50" t="str">
+      <c r="I26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="50" t="str">
+      <c r="J26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="50" t="str">
+      <c r="K26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
         <v> </v>
       </c>
-      <c r="L26" s="50"/>
+      <c r="L26" s="53"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47" t="str">
+      <c r="N26" s="53"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="47" t="str">
+      <c r="S26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="47"/>
+      <c r="T26" s="50"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="50" t="str">
+      <c r="W26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="50" t="str">
+      <c r="X26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="47" t="str">
+      <c r="Y26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="47" t="str">
+      <c r="Z26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -3075,9 +3055,9 @@
         <f aca="false">SUM(K22:K26)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="50"/>
+      <c r="L27" s="53"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="50"/>
+      <c r="N27" s="53"/>
       <c r="O27" s="61" t="n">
         <f aca="false">SUM(O22:O26)</f>
         <v>0</v>
@@ -3095,8 +3075,8 @@
         <f aca="false">SUM(S22:S26)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="47"/>
-      <c r="U27" s="49"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="52"/>
       <c r="V27" s="60" t="n">
         <f aca="false">SUM(V22:V26)</f>
         <v>0</v>
@@ -3124,120 +3104,121 @@
       <c r="B28" s="63"/>
       <c r="C28" s="64"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
       <c r="H28" s="58"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
       <c r="P28" s="62"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="47"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="53"/>
+      <c r="W28" s="53"/>
+      <c r="X28" s="53"/>
+      <c r="Y28" s="53"/>
+      <c r="Z28" s="53"/>
       <c r="AA28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="42"/>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="66" t="n">
+      <c r="C29" s="66"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="67" t="n">
         <f aca="false">[1]Admin!$G$16</f>
         <v>0.33</v>
       </c>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="47"/>
-      <c r="Z29" s="47"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="53"/>
+      <c r="X29" s="53"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="50"/>
       <c r="AA29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="42"/>
       <c r="B30" s="54"/>
       <c r="C30" s="55"/>
-      <c r="D30" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>270</v>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="53" t="str">
+        <f aca="false">IF(E30&gt;0,E30-F30," ")</f>
+        <v> </v>
       </c>
       <c r="H30" s="58" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I30" s="50" t="str">
+      <c r="I30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,MIN(E30*H30,G30)," ")</f>
         <v> </v>
       </c>
-      <c r="J30" s="50" t="str">
+      <c r="J30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,F30+I30," ")</f>
         <v> </v>
       </c>
-      <c r="K30" s="50" t="str">
+      <c r="K30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,E30-J30," ")</f>
         <v> </v>
       </c>
-      <c r="L30" s="50"/>
+      <c r="L30" s="53"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47" t="str">
+      <c r="N30" s="53"/>
+      <c r="O30" s="68"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50" t="str">
         <f aca="false">IF(O30&gt;0,O30*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S30" s="47" t="str">
+      <c r="S30" s="50" t="str">
         <f aca="false">IF(O30&gt;0,O30-R30," ")</f>
         <v> </v>
       </c>
-      <c r="T30" s="47"/>
+      <c r="T30" s="50"/>
       <c r="U30" s="54"/>
       <c r="V30" s="57"/>
-      <c r="W30" s="50" t="str">
+      <c r="W30" s="53" t="str">
         <f aca="false">IF(V30&gt;0,E30," ")</f>
         <v> </v>
       </c>
-      <c r="X30" s="50" t="str">
+      <c r="X30" s="53" t="str">
         <f aca="false">IF(V30&gt;0,J30," ")</f>
         <v> </v>
       </c>
-      <c r="Y30" s="47" t="str">
+      <c r="Y30" s="50" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&lt;S30,S30-V30," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z30" s="47" t="str">
+      <c r="Z30" s="50" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&gt;S30,V30-S30," ")," ")</f>
         <v> </v>
       </c>
@@ -3250,7 +3231,7 @@
       <c r="D31" s="56"/>
       <c r="E31" s="57"/>
       <c r="F31" s="57"/>
-      <c r="G31" s="50" t="str">
+      <c r="G31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,E31-F31," ")</f>
         <v> </v>
       </c>
@@ -3258,48 +3239,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I31" s="50" t="str">
+      <c r="I31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,MIN(E31*H31,G31)," ")</f>
         <v> </v>
       </c>
-      <c r="J31" s="50" t="str">
+      <c r="J31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,F31+I31," ")</f>
         <v> </v>
       </c>
-      <c r="K31" s="50" t="str">
+      <c r="K31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,E31-J31," ")</f>
         <v> </v>
       </c>
-      <c r="L31" s="50"/>
+      <c r="L31" s="53"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="47"/>
-      <c r="R31" s="47" t="str">
+      <c r="N31" s="53"/>
+      <c r="O31" s="68"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50" t="str">
         <f aca="false">IF(O31&gt;0,O31*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S31" s="47" t="str">
+      <c r="S31" s="50" t="str">
         <f aca="false">IF(O31&gt;0,O31-R31," ")</f>
         <v> </v>
       </c>
-      <c r="T31" s="47"/>
+      <c r="T31" s="50"/>
       <c r="U31" s="54"/>
       <c r="V31" s="57"/>
-      <c r="W31" s="50" t="str">
+      <c r="W31" s="53" t="str">
         <f aca="false">IF(V31&gt;0,E31," ")</f>
         <v> </v>
       </c>
-      <c r="X31" s="50" t="str">
+      <c r="X31" s="53" t="str">
         <f aca="false">IF(V31&gt;0,J31," ")</f>
         <v> </v>
       </c>
-      <c r="Y31" s="47" t="str">
+      <c r="Y31" s="50" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&lt;S31,S31-V31," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z31" s="47" t="str">
+      <c r="Z31" s="50" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&gt;S31,V31-S31," ")," ")</f>
         <v> </v>
       </c>
@@ -3312,7 +3293,7 @@
       <c r="D32" s="56"/>
       <c r="E32" s="57"/>
       <c r="F32" s="57"/>
-      <c r="G32" s="50" t="str">
+      <c r="G32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,E32-F32," ")</f>
         <v> </v>
       </c>
@@ -3320,48 +3301,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I32" s="50" t="str">
+      <c r="I32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,MIN(E32*H32,G32)," ")</f>
         <v> </v>
       </c>
-      <c r="J32" s="50" t="str">
+      <c r="J32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,F32+I32," ")</f>
         <v> </v>
       </c>
-      <c r="K32" s="50" t="str">
+      <c r="K32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,E32-J32," ")</f>
         <v> </v>
       </c>
-      <c r="L32" s="50"/>
+      <c r="L32" s="53"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47" t="str">
+      <c r="N32" s="53"/>
+      <c r="O32" s="68"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50" t="str">
         <f aca="false">IF(O32&gt;0,O32*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S32" s="47" t="str">
+      <c r="S32" s="50" t="str">
         <f aca="false">IF(O32&gt;0,O32-R32," ")</f>
         <v> </v>
       </c>
-      <c r="T32" s="47"/>
+      <c r="T32" s="50"/>
       <c r="U32" s="54"/>
       <c r="V32" s="57"/>
-      <c r="W32" s="50" t="str">
+      <c r="W32" s="53" t="str">
         <f aca="false">IF(V32&gt;0,E32," ")</f>
         <v> </v>
       </c>
-      <c r="X32" s="50" t="str">
+      <c r="X32" s="53" t="str">
         <f aca="false">IF(V32&gt;0,J32," ")</f>
         <v> </v>
       </c>
-      <c r="Y32" s="47" t="str">
+      <c r="Y32" s="50" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&lt;S32,S32-V32," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z32" s="47" t="str">
+      <c r="Z32" s="50" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&gt;S32,V32-S32," ")," ")</f>
         <v> </v>
       </c>
@@ -3374,7 +3355,7 @@
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
       <c r="F33" s="57"/>
-      <c r="G33" s="50" t="str">
+      <c r="G33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
         <v> </v>
       </c>
@@ -3382,48 +3363,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="50" t="str">
+      <c r="I33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="50" t="str">
+      <c r="J33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="50" t="str">
+      <c r="K33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
         <v> </v>
       </c>
-      <c r="L33" s="50"/>
+      <c r="L33" s="53"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47" t="str">
+      <c r="N33" s="53"/>
+      <c r="O33" s="68"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="47" t="str">
+      <c r="S33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="47"/>
+      <c r="T33" s="50"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="50" t="str">
+      <c r="W33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="50" t="str">
+      <c r="X33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="47" t="str">
+      <c r="Y33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="47" t="str">
+      <c r="Z33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3436,7 +3417,7 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="50" t="str">
+      <c r="G34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
         <v> </v>
       </c>
@@ -3444,48 +3425,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="50" t="str">
+      <c r="I34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="50" t="str">
+      <c r="J34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="50" t="str">
+      <c r="K34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
         <v> </v>
       </c>
-      <c r="L34" s="50"/>
+      <c r="L34" s="53"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="67"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47" t="str">
+      <c r="N34" s="53"/>
+      <c r="O34" s="68"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="50"/>
+      <c r="R34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="47" t="str">
+      <c r="S34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="47"/>
+      <c r="T34" s="50"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="50" t="str">
+      <c r="W34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="50" t="str">
+      <c r="X34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="47" t="str">
+      <c r="Y34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="47" t="str">
+      <c r="Z34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3494,7 +3475,7 @@
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="42"/>
       <c r="B35" s="59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="59"/>
@@ -3504,7 +3485,7 @@
       </c>
       <c r="F35" s="60" t="n">
         <f aca="false">SUM(F30:F34)</f>
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="G35" s="61" t="n">
         <f aca="false">SUM(G30:G34)</f>
@@ -3523,9 +3504,9 @@
         <f aca="false">SUM(K30:K34)</f>
         <v>0</v>
       </c>
-      <c r="L35" s="50"/>
+      <c r="L35" s="53"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="50"/>
+      <c r="N35" s="53"/>
       <c r="O35" s="61" t="n">
         <f aca="false">SUM(O30:O34)</f>
         <v>0</v>
@@ -3543,8 +3524,8 @@
         <f aca="false">SUM(S30:S34)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="47"/>
-      <c r="U35" s="49"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="52"/>
       <c r="V35" s="60" t="n">
         <f aca="false">SUM(V30:V34)</f>
         <v>0</v>
@@ -3572,125 +3553,126 @@
       <c r="B36" s="63"/>
       <c r="C36" s="64"/>
       <c r="D36" s="65"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
       <c r="H36" s="58"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
       <c r="P36" s="62"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="49"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="50"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
       <c r="AA36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="42"/>
-      <c r="B37" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="69"/>
-      <c r="D37" s="70" t="n">
+      <c r="B37" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="70"/>
+      <c r="D37" s="71" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="66" t="n">
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="67" t="n">
         <f aca="false">[1]Admin!$G$17</f>
         <v>0.25</v>
       </c>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
       <c r="P37" s="62"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="72"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="73"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="53"/>
+      <c r="W37" s="53"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
       <c r="AA37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="42"/>
       <c r="B38" s="54"/>
       <c r="C38" s="55"/>
-      <c r="D38" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>9828</v>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="53" t="str">
+        <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
+        <v> </v>
       </c>
       <c r="H38" s="58" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I38" s="50" t="str">
+      <c r="I38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
         <v> </v>
       </c>
-      <c r="J38" s="50" t="str">
+      <c r="J38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
         <v> </v>
       </c>
-      <c r="K38" s="50" t="str">
+      <c r="K38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
         <v> </v>
       </c>
-      <c r="L38" s="50"/>
-      <c r="M38" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="50"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47" t="str">
+      <c r="L38" s="53"/>
+      <c r="M38" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="53"/>
+      <c r="O38" s="68"/>
+      <c r="P38" s="51"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
         <v> </v>
       </c>
-      <c r="S38" s="47" t="str">
+      <c r="S38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
         <v> </v>
       </c>
-      <c r="T38" s="47"/>
+      <c r="T38" s="50"/>
       <c r="U38" s="54"/>
       <c r="V38" s="57"/>
-      <c r="W38" s="50" t="str">
+      <c r="W38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
         <v> </v>
       </c>
-      <c r="X38" s="50" t="str">
+      <c r="X38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
         <v> </v>
       </c>
-      <c r="Y38" s="47" t="str">
+      <c r="Y38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z38" s="47" t="str">
+      <c r="Z38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
@@ -3703,7 +3685,7 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="50" t="str">
+      <c r="G39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
         <v> </v>
       </c>
@@ -3711,50 +3693,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I39" s="50" t="str">
+      <c r="I39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="50" t="str">
+      <c r="J39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="50" t="str">
+      <c r="K39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
         <v> </v>
       </c>
-      <c r="L39" s="50"/>
-      <c r="M39" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="50"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="47" t="str">
+      <c r="L39" s="53"/>
+      <c r="M39" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="53"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="47" t="str">
+      <c r="S39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="47"/>
+      <c r="T39" s="50"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="50" t="str">
+      <c r="W39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="50" t="str">
+      <c r="X39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="47" t="str">
+      <c r="Y39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,(S39-V39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="47" t="str">
+      <c r="Z39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,(V39-S39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
@@ -3767,7 +3749,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="50" t="str">
+      <c r="G40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
         <v> </v>
       </c>
@@ -3775,50 +3757,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I40" s="50" t="str">
+      <c r="I40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="50" t="str">
+      <c r="J40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="50" t="str">
+      <c r="K40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
         <v> </v>
       </c>
-      <c r="L40" s="50"/>
-      <c r="M40" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="50"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="47"/>
-      <c r="R40" s="47" t="str">
+      <c r="L40" s="53"/>
+      <c r="M40" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="53"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="47" t="str">
+      <c r="S40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="47"/>
+      <c r="T40" s="50"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="50" t="str">
+      <c r="W40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="50" t="str">
+      <c r="X40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="47" t="str">
+      <c r="Y40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,(S40-V40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="47" t="str">
+      <c r="Z40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,(V40-S40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
@@ -3831,7 +3813,7 @@
       <c r="D41" s="56"/>
       <c r="E41" s="57"/>
       <c r="F41" s="57"/>
-      <c r="G41" s="50" t="str">
+      <c r="G41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,E41-F41," ")</f>
         <v> </v>
       </c>
@@ -3839,50 +3821,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I41" s="50" t="str">
+      <c r="I41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,MIN(E41*H41,G41)," ")</f>
         <v> </v>
       </c>
-      <c r="J41" s="50" t="str">
+      <c r="J41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,F41+I41," ")</f>
         <v> </v>
       </c>
-      <c r="K41" s="50" t="str">
+      <c r="K41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,E41-J41," ")</f>
         <v> </v>
       </c>
-      <c r="L41" s="50"/>
-      <c r="M41" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="50"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="47"/>
-      <c r="R41" s="47" t="str">
+      <c r="L41" s="53"/>
+      <c r="M41" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="53"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="51"/>
+      <c r="Q41" s="50"/>
+      <c r="R41" s="50" t="str">
         <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
         <v> </v>
       </c>
-      <c r="S41" s="47" t="str">
+      <c r="S41" s="50" t="str">
         <f aca="false">IF(O41&gt;0,O41-R41," ")</f>
         <v> </v>
       </c>
-      <c r="T41" s="47"/>
+      <c r="T41" s="50"/>
       <c r="U41" s="54"/>
       <c r="V41" s="57"/>
-      <c r="W41" s="50" t="str">
+      <c r="W41" s="53" t="str">
         <f aca="false">IF(V41&gt;0,E41," ")</f>
         <v> </v>
       </c>
-      <c r="X41" s="50" t="str">
+      <c r="X41" s="53" t="str">
         <f aca="false">IF(V41&gt;0,J41," ")</f>
         <v> </v>
       </c>
-      <c r="Y41" s="47" t="str">
+      <c r="Y41" s="50" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&lt;S41,(S41-V41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z41" s="47" t="str">
+      <c r="Z41" s="50" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&gt;S41,(V41-S41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
@@ -3895,7 +3877,7 @@
       <c r="D42" s="56"/>
       <c r="E42" s="57"/>
       <c r="F42" s="57"/>
-      <c r="G42" s="50" t="str">
+      <c r="G42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,E42-F42," ")</f>
         <v> </v>
       </c>
@@ -3903,50 +3885,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I42" s="50" t="str">
+      <c r="I42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,MIN(E42*H42,G42)," ")</f>
         <v> </v>
       </c>
-      <c r="J42" s="50" t="str">
+      <c r="J42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,F42+I42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="50" t="str">
+      <c r="K42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,E42-J42," ")</f>
         <v> </v>
       </c>
-      <c r="L42" s="50"/>
-      <c r="M42" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="50"/>
-      <c r="O42" s="67"/>
-      <c r="P42" s="48"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47" t="str">
+      <c r="L42" s="53"/>
+      <c r="M42" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="53"/>
+      <c r="O42" s="68"/>
+      <c r="P42" s="51"/>
+      <c r="Q42" s="50"/>
+      <c r="R42" s="50" t="str">
         <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
         <v> </v>
       </c>
-      <c r="S42" s="47" t="str">
+      <c r="S42" s="50" t="str">
         <f aca="false">IF(O42&gt;0,O42-R42," ")</f>
         <v> </v>
       </c>
-      <c r="T42" s="47"/>
+      <c r="T42" s="50"/>
       <c r="U42" s="54"/>
       <c r="V42" s="57"/>
-      <c r="W42" s="50" t="str">
+      <c r="W42" s="53" t="str">
         <f aca="false">IF(V42&gt;0,E42," ")</f>
         <v> </v>
       </c>
-      <c r="X42" s="50" t="str">
+      <c r="X42" s="53" t="str">
         <f aca="false">IF(V42&gt;0,J42," ")</f>
         <v> </v>
       </c>
-      <c r="Y42" s="47" t="str">
+      <c r="Y42" s="50" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&lt;S42,(S42-V42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z42" s="47" t="str">
+      <c r="Z42" s="50" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&gt;S42,(V42-S42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
@@ -3954,36 +3936,36 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="69"/>
-      <c r="D43" s="70" t="n">
+      <c r="B43" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="70"/>
+      <c r="D43" s="71" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
       <c r="H43" s="58"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
       <c r="M43" s="58"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="47"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="47"/>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="47"/>
-      <c r="Z43" s="47"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="51"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="53"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="50"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3993,7 +3975,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="50" t="str">
+      <c r="G44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
         <v> </v>
       </c>
@@ -4001,50 +3983,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="50" t="str">
+      <c r="I44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="50" t="str">
+      <c r="J44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="50" t="str">
+      <c r="K44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
         <v> </v>
       </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="50"/>
-      <c r="O44" s="67"/>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47" t="str">
+      <c r="L44" s="53"/>
+      <c r="M44" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="53"/>
+      <c r="O44" s="68"/>
+      <c r="P44" s="51"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="47" t="str">
+      <c r="S44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="47"/>
+      <c r="T44" s="50"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="50" t="str">
+      <c r="W44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="50" t="str">
+      <c r="X44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="47" t="str">
+      <c r="Y44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="47" t="str">
+      <c r="Z44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -4057,7 +4039,7 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="50" t="str">
+      <c r="G45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
         <v> </v>
       </c>
@@ -4065,50 +4047,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="50" t="str">
+      <c r="I45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="50" t="str">
+      <c r="J45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="50" t="str">
+      <c r="K45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
         <v> </v>
       </c>
-      <c r="L45" s="50"/>
-      <c r="M45" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="50"/>
-      <c r="O45" s="67"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47" t="str">
+      <c r="L45" s="53"/>
+      <c r="M45" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="53"/>
+      <c r="O45" s="68"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="47" t="str">
+      <c r="S45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="47"/>
+      <c r="T45" s="50"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="50" t="str">
+      <c r="W45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="50" t="str">
+      <c r="X45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="47" t="str">
+      <c r="Y45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="47" t="str">
+      <c r="Z45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -4121,7 +4103,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="50" t="str">
+      <c r="G46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -4129,50 +4111,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="50" t="str">
+      <c r="I46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="50" t="str">
+      <c r="J46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="50" t="str">
+      <c r="K46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
         <v> </v>
       </c>
-      <c r="L46" s="50"/>
-      <c r="M46" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="50"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47" t="str">
+      <c r="L46" s="53"/>
+      <c r="M46" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="53"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="51"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="47" t="str">
+      <c r="S46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="47"/>
+      <c r="T46" s="50"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="50" t="str">
+      <c r="W46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="50" t="str">
+      <c r="X46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="47" t="str">
+      <c r="Y46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="47" t="str">
+      <c r="Z46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -4185,7 +4167,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="50" t="str">
+      <c r="G47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -4193,50 +4175,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="50" t="str">
+      <c r="I47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="50" t="str">
+      <c r="J47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="50" t="str">
+      <c r="K47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
         <v> </v>
       </c>
-      <c r="L47" s="50"/>
-      <c r="M47" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="50"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="48"/>
-      <c r="Q47" s="47"/>
-      <c r="R47" s="47" t="str">
+      <c r="L47" s="53"/>
+      <c r="M47" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="53"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="51"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="47" t="str">
+      <c r="S47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="47"/>
+      <c r="T47" s="50"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="50" t="str">
+      <c r="W47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="50" t="str">
+      <c r="X47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="47" t="str">
+      <c r="Y47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="47" t="str">
+      <c r="Z47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4249,7 +4231,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="50" t="str">
+      <c r="G48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4257,50 +4239,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="50" t="str">
+      <c r="I48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="50" t="str">
+      <c r="J48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="50" t="str">
+      <c r="K48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
         <v> </v>
       </c>
-      <c r="L48" s="50"/>
-      <c r="M48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="50"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47" t="str">
+      <c r="L48" s="53"/>
+      <c r="M48" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="53"/>
+      <c r="O48" s="68"/>
+      <c r="P48" s="51"/>
+      <c r="Q48" s="50"/>
+      <c r="R48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="47" t="str">
+      <c r="S48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="47"/>
+      <c r="T48" s="50"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="50" t="str">
+      <c r="W48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="50" t="str">
+      <c r="X48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="47" t="str">
+      <c r="Y48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="47" t="str">
+      <c r="Z48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4308,33 +4290,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="51"/>
+      <c r="B49" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="66"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="47"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="47"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="49"/>
-      <c r="V49" s="50"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="50"/>
-      <c r="Y49" s="47"/>
-      <c r="Z49" s="47"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="50"/>
+      <c r="P49" s="51"/>
+      <c r="Q49" s="50"/>
+      <c r="R49" s="50"/>
+      <c r="S49" s="50"/>
+      <c r="T49" s="50"/>
+      <c r="U49" s="52"/>
+      <c r="V49" s="53"/>
+      <c r="W49" s="53"/>
+      <c r="X49" s="53"/>
+      <c r="Y49" s="50"/>
+      <c r="Z49" s="50"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4344,7 +4326,7 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="50" t="str">
+      <c r="G50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
         <v> </v>
       </c>
@@ -4352,50 +4334,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="50" t="str">
+      <c r="I50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="50" t="str">
+      <c r="J50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="50" t="str">
+      <c r="K50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
         <v> </v>
       </c>
-      <c r="L50" s="50"/>
-      <c r="M50" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="50"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47" t="str">
+      <c r="L50" s="53"/>
+      <c r="M50" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="53"/>
+      <c r="O50" s="68"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="50"/>
+      <c r="R50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,O50*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="47" t="str">
+      <c r="S50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="47"/>
+      <c r="T50" s="50"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="50" t="str">
+      <c r="W50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="50" t="str">
+      <c r="X50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="47" t="str">
+      <c r="Y50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="47" t="str">
+      <c r="Z50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4408,7 +4390,7 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="50" t="str">
+      <c r="G51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
         <v> </v>
       </c>
@@ -4416,50 +4398,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="50" t="str">
+      <c r="I51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="50" t="str">
+      <c r="J51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="50" t="str">
+      <c r="K51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
         <v> </v>
       </c>
-      <c r="L51" s="50"/>
-      <c r="M51" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="50"/>
-      <c r="O51" s="67"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47" t="str">
+      <c r="L51" s="53"/>
+      <c r="M51" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="53"/>
+      <c r="O51" s="68"/>
+      <c r="P51" s="51"/>
+      <c r="Q51" s="50"/>
+      <c r="R51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,O51*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="47" t="str">
+      <c r="S51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="47"/>
+      <c r="T51" s="50"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="50" t="str">
+      <c r="W51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="50" t="str">
+      <c r="X51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="47" t="str">
+      <c r="Y51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="47" t="str">
+      <c r="Z51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4472,7 +4454,7 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="50" t="str">
+      <c r="G52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
         <v> </v>
       </c>
@@ -4480,50 +4462,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="50" t="str">
+      <c r="I52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="50" t="str">
+      <c r="J52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="50" t="str">
+      <c r="K52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
         <v> </v>
       </c>
-      <c r="L52" s="50"/>
-      <c r="M52" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="50"/>
-      <c r="O52" s="67"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47" t="str">
+      <c r="L52" s="53"/>
+      <c r="M52" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="53"/>
+      <c r="O52" s="68"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="50"/>
+      <c r="R52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,O52*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="47" t="str">
+      <c r="S52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="47"/>
+      <c r="T52" s="50"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="50" t="str">
+      <c r="W52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="50" t="str">
+      <c r="X52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="47" t="str">
+      <c r="Y52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="47" t="str">
+      <c r="Z52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4536,7 +4518,7 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="50" t="str">
+      <c r="G53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
         <v> </v>
       </c>
@@ -4544,50 +4526,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="50" t="str">
+      <c r="I53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="50" t="str">
+      <c r="J53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="50" t="str">
+      <c r="K53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
         <v> </v>
       </c>
-      <c r="L53" s="50"/>
-      <c r="M53" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="50"/>
-      <c r="O53" s="67"/>
-      <c r="P53" s="48"/>
-      <c r="Q53" s="47"/>
-      <c r="R53" s="47" t="str">
+      <c r="L53" s="53"/>
+      <c r="M53" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="53"/>
+      <c r="O53" s="68"/>
+      <c r="P53" s="51"/>
+      <c r="Q53" s="50"/>
+      <c r="R53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,O53*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="47" t="str">
+      <c r="S53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="47"/>
+      <c r="T53" s="50"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="50" t="str">
+      <c r="W53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="50" t="str">
+      <c r="X53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="47" t="str">
+      <c r="Y53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="47" t="str">
+      <c r="Z53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4600,7 +4582,7 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="50" t="str">
+      <c r="G54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
         <v> </v>
       </c>
@@ -4608,50 +4590,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="50" t="str">
+      <c r="I54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="50" t="str">
+      <c r="J54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="50" t="str">
+      <c r="K54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
         <v> </v>
       </c>
-      <c r="L54" s="50"/>
-      <c r="M54" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="50"/>
-      <c r="O54" s="67"/>
-      <c r="P54" s="48"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47" t="str">
+      <c r="L54" s="53"/>
+      <c r="M54" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="53"/>
+      <c r="O54" s="68"/>
+      <c r="P54" s="51"/>
+      <c r="Q54" s="50"/>
+      <c r="R54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,O54*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="47" t="str">
+      <c r="S54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="47"/>
+      <c r="T54" s="50"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="50" t="str">
+      <c r="W54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="50" t="str">
+      <c r="X54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="47" t="str">
+      <c r="Y54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="47" t="str">
+      <c r="Z54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4660,7 +4642,7 @@
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="42"/>
       <c r="B55" s="59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C55" s="59"/>
       <c r="D55" s="59"/>
@@ -4670,7 +4652,7 @@
       </c>
       <c r="F55" s="61" t="n">
         <f aca="false">SUM(F38:F54)</f>
-        <v>9828</v>
+        <v>0</v>
       </c>
       <c r="G55" s="61" t="n">
         <f aca="false">SUM(G38:G54)</f>
@@ -4689,9 +4671,9 @@
         <f aca="false">SUM(K38:K54)</f>
         <v>0</v>
       </c>
-      <c r="L55" s="50"/>
-      <c r="M55" s="71"/>
-      <c r="N55" s="50"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="72"/>
+      <c r="N55" s="53"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O38:O54)</f>
         <v>0</v>
@@ -4709,8 +4691,8 @@
         <f aca="false">SUM(S38:S54)</f>
         <v>0</v>
       </c>
-      <c r="T55" s="50"/>
-      <c r="U55" s="49"/>
+      <c r="T55" s="53"/>
+      <c r="U55" s="52"/>
       <c r="V55" s="61" t="n">
         <f aca="false">SUM(V38:V54)</f>
         <v>0</v>
@@ -4735,31 +4717,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="73"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="74"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="50"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="47"/>
-      <c r="P56" s="48"/>
-      <c r="Q56" s="47"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47"/>
-      <c r="T56" s="47"/>
-      <c r="U56" s="49"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="47"/>
-      <c r="X56" s="47"/>
-      <c r="Y56" s="47"/>
-      <c r="Z56" s="47"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="50"/>
+      <c r="P56" s="51"/>
+      <c r="Q56" s="50"/>
+      <c r="R56" s="50"/>
+      <c r="S56" s="50"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="52"/>
+      <c r="V56" s="53"/>
+      <c r="W56" s="50"/>
+      <c r="X56" s="50"/>
+      <c r="Y56" s="50"/>
+      <c r="Z56" s="50"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4769,74 +4751,74 @@
         <v>EXISTING FIXED ASSETS at </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="44" t="n">
+      <c r="D57" s="44" t="str">
         <f aca="false">D6</f>
-        <v>45753</v>
-      </c>
-      <c r="E57" s="74" t="n">
+        <v>Laptop (0.5 years old)</v>
+      </c>
+      <c r="E57" s="75" t="n">
         <f aca="false">E11+E19+E27+E35+E55</f>
         <v>0</v>
       </c>
-      <c r="F57" s="74" t="n">
+      <c r="F57" s="75" t="n">
         <f aca="false">F11+F19+F27+F35+F55</f>
-        <v>10098</v>
-      </c>
-      <c r="G57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="75" t="n">
         <f aca="false">G11+G19+G27+G35+G55</f>
         <v>0</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="74" t="n">
+      <c r="I57" s="75" t="n">
         <f aca="false">I11+I19+I27+I35+I55</f>
         <v>0</v>
       </c>
-      <c r="J57" s="74" t="n">
+      <c r="J57" s="75" t="n">
         <f aca="false">J11+J19+J27+J35+J55</f>
         <v>0</v>
       </c>
-      <c r="K57" s="74" t="n">
+      <c r="K57" s="75" t="n">
         <f aca="false">K11+K19+K27+K35+K55</f>
         <v>0</v>
       </c>
-      <c r="L57" s="50"/>
+      <c r="L57" s="53"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="74" t="n">
+      <c r="N57" s="53"/>
+      <c r="O57" s="75" t="n">
         <f aca="false">O11+O19+O27+O35+O55</f>
         <v>0</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="74" t="n">
+      <c r="Q57" s="75" t="n">
         <f aca="false">Q11+Q19+Q27+Q35+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="74" t="n">
+      <c r="R57" s="75" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
         <v>0</v>
       </c>
-      <c r="S57" s="74" t="n">
+      <c r="S57" s="75" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
         <v>0</v>
       </c>
-      <c r="T57" s="47"/>
-      <c r="U57" s="49"/>
-      <c r="V57" s="74" t="n">
+      <c r="T57" s="50"/>
+      <c r="U57" s="52"/>
+      <c r="V57" s="75" t="n">
         <f aca="false">V11+V19+V27+V35+V55</f>
         <v>0</v>
       </c>
-      <c r="W57" s="74" t="n">
+      <c r="W57" s="75" t="n">
         <f aca="false">W11+W19+W27+W35+W55</f>
         <v>0</v>
       </c>
-      <c r="X57" s="74" t="n">
+      <c r="X57" s="75" t="n">
         <f aca="false">X11+X19+X27+X35+X55</f>
         <v>0</v>
       </c>
-      <c r="Y57" s="74" t="n">
+      <c r="Y57" s="75" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="74" t="n">
+      <c r="Z57" s="75" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
         <v>0</v>
       </c>
@@ -4844,78 +4826,78 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="75"/>
-      <c r="C58" s="76"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="50"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="47"/>
-      <c r="P58" s="48"/>
-      <c r="Q58" s="47"/>
-      <c r="R58" s="47"/>
-      <c r="S58" s="47"/>
-      <c r="T58" s="47"/>
-      <c r="U58" s="49"/>
-      <c r="V58" s="50"/>
-      <c r="W58" s="50"/>
-      <c r="X58" s="50"/>
-      <c r="Y58" s="47"/>
-      <c r="Z58" s="47"/>
+      <c r="N58" s="53"/>
+      <c r="O58" s="50"/>
+      <c r="P58" s="51"/>
+      <c r="Q58" s="50"/>
+      <c r="R58" s="50"/>
+      <c r="S58" s="50"/>
+      <c r="T58" s="50"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="53"/>
+      <c r="W58" s="53"/>
+      <c r="X58" s="53"/>
+      <c r="Y58" s="50"/>
+      <c r="Z58" s="50"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
       <c r="B59" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="n">
         <f aca="false">[1]Admin!$B$4</f>
         <v>45753</v>
       </c>
-      <c r="E59" s="47"/>
-      <c r="F59" s="78"/>
-      <c r="G59" s="78"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
-      <c r="L59" s="47"/>
+      <c r="I59" s="50"/>
+      <c r="J59" s="50"/>
+      <c r="K59" s="50"/>
+      <c r="L59" s="50"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="47"/>
-      <c r="O59" s="47"/>
-      <c r="P59" s="48"/>
-      <c r="Q59" s="47"/>
-      <c r="R59" s="47"/>
-      <c r="S59" s="47"/>
-      <c r="T59" s="47"/>
-      <c r="U59" s="49"/>
-      <c r="V59" s="50"/>
-      <c r="W59" s="50"/>
-      <c r="X59" s="50"/>
-      <c r="Y59" s="47"/>
-      <c r="Z59" s="47"/>
+      <c r="N59" s="50"/>
+      <c r="O59" s="50"/>
+      <c r="P59" s="51"/>
+      <c r="Q59" s="50"/>
+      <c r="R59" s="50"/>
+      <c r="S59" s="50"/>
+      <c r="T59" s="50"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="53"/>
+      <c r="W59" s="53"/>
+      <c r="X59" s="53"/>
+      <c r="Y59" s="50"/>
+      <c r="Z59" s="50"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="51"/>
-      <c r="D60" s="52"/>
+      <c r="B60" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="66"/>
+      <c r="D60" s="47"/>
       <c r="E60" s="45"/>
-      <c r="F60" s="78"/>
-      <c r="G60" s="78"/>
-      <c r="H60" s="79" t="n">
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="80" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
@@ -4925,165 +4907,165 @@
       <c r="L60" s="45"/>
       <c r="M60" s="58"/>
       <c r="N60" s="45"/>
-      <c r="O60" s="47"/>
-      <c r="P60" s="48"/>
-      <c r="Q60" s="47"/>
-      <c r="R60" s="47"/>
-      <c r="S60" s="47"/>
-      <c r="T60" s="47"/>
-      <c r="U60" s="49"/>
-      <c r="V60" s="50"/>
-      <c r="W60" s="50"/>
-      <c r="X60" s="50"/>
-      <c r="Y60" s="47"/>
-      <c r="Z60" s="47"/>
+      <c r="O60" s="50"/>
+      <c r="P60" s="51"/>
+      <c r="Q60" s="50"/>
+      <c r="R60" s="50"/>
+      <c r="S60" s="50"/>
+      <c r="T60" s="50"/>
+      <c r="U60" s="52"/>
+      <c r="V60" s="53"/>
+      <c r="W60" s="53"/>
+      <c r="X60" s="53"/>
+      <c r="Y60" s="50"/>
+      <c r="Z60" s="50"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="80"/>
+      <c r="D61" s="81"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="50"/>
-      <c r="G61" s="50"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="50" t="str">
+      <c r="I61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="50" t="str">
+      <c r="J61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="50" t="str">
+      <c r="K61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
         <v> </v>
       </c>
-      <c r="L61" s="50"/>
+      <c r="L61" s="53"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="50"/>
-      <c r="O61" s="47"/>
-      <c r="P61" s="48"/>
-      <c r="Q61" s="47"/>
-      <c r="R61" s="47"/>
-      <c r="S61" s="47"/>
-      <c r="T61" s="47"/>
+      <c r="N61" s="53"/>
+      <c r="O61" s="50"/>
+      <c r="P61" s="51"/>
+      <c r="Q61" s="50"/>
+      <c r="R61" s="50"/>
+      <c r="S61" s="50"/>
+      <c r="T61" s="50"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="50" t="str">
+      <c r="W61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="50" t="str">
+      <c r="X61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="47"/>
-      <c r="Z61" s="47"/>
+      <c r="Y61" s="50"/>
+      <c r="Z61" s="50"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="80"/>
+      <c r="D62" s="81"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="50"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="50" t="str">
+      <c r="I62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="50" t="str">
+      <c r="J62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="50" t="str">
+      <c r="K62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
         <v> </v>
       </c>
-      <c r="L62" s="50"/>
+      <c r="L62" s="53"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="50"/>
-      <c r="O62" s="47"/>
-      <c r="P62" s="48"/>
-      <c r="Q62" s="47"/>
-      <c r="R62" s="47"/>
-      <c r="S62" s="47"/>
-      <c r="T62" s="47"/>
+      <c r="N62" s="53"/>
+      <c r="O62" s="50"/>
+      <c r="P62" s="51"/>
+      <c r="Q62" s="50"/>
+      <c r="R62" s="50"/>
+      <c r="S62" s="50"/>
+      <c r="T62" s="50"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="50" t="str">
+      <c r="W62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="50" t="str">
+      <c r="X62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="47"/>
-      <c r="Z62" s="47"/>
+      <c r="Y62" s="50"/>
+      <c r="Z62" s="50"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="80"/>
+      <c r="D63" s="81"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="50" t="str">
+      <c r="I63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="50" t="str">
+      <c r="J63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="50" t="str">
+      <c r="K63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
         <v> </v>
       </c>
-      <c r="L63" s="50"/>
+      <c r="L63" s="53"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="50"/>
-      <c r="O63" s="47"/>
-      <c r="P63" s="48"/>
-      <c r="Q63" s="47"/>
-      <c r="R63" s="47"/>
-      <c r="S63" s="47"/>
-      <c r="T63" s="47"/>
+      <c r="N63" s="53"/>
+      <c r="O63" s="50"/>
+      <c r="P63" s="51"/>
+      <c r="Q63" s="50"/>
+      <c r="R63" s="50"/>
+      <c r="S63" s="50"/>
+      <c r="T63" s="50"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="50" t="str">
+      <c r="W63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="50" t="str">
+      <c r="X63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="47"/>
-      <c r="Z63" s="47"/>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="50"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -5112,14 +5094,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="50"/>
+      <c r="L64" s="53"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="50"/>
+      <c r="N64" s="53"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="81"/>
+      <c r="P64" s="82"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -5132,8 +5114,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="47"/>
-      <c r="U64" s="49"/>
+      <c r="T64" s="50"/>
+      <c r="U64" s="52"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -5161,62 +5143,62 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="50"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="50"/>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="L65" s="50"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="53"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="50"/>
-      <c r="O65" s="50"/>
+      <c r="N65" s="53"/>
+      <c r="O65" s="53"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="50"/>
-      <c r="R65" s="50"/>
-      <c r="S65" s="50"/>
-      <c r="T65" s="47"/>
-      <c r="U65" s="49"/>
-      <c r="V65" s="50"/>
-      <c r="W65" s="50"/>
-      <c r="X65" s="50"/>
-      <c r="Y65" s="50"/>
-      <c r="Z65" s="50"/>
+      <c r="Q65" s="53"/>
+      <c r="R65" s="53"/>
+      <c r="S65" s="53"/>
+      <c r="T65" s="50"/>
+      <c r="U65" s="52"/>
+      <c r="V65" s="53"/>
+      <c r="W65" s="53"/>
+      <c r="X65" s="53"/>
+      <c r="Y65" s="53"/>
+      <c r="Z65" s="53"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="51"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="50"/>
-      <c r="H66" s="82" t="n">
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="83" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="50"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="53"/>
+      <c r="L66" s="53"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="47"/>
-      <c r="P66" s="48"/>
-      <c r="Q66" s="47"/>
-      <c r="R66" s="47"/>
-      <c r="S66" s="47"/>
-      <c r="T66" s="47"/>
-      <c r="U66" s="49"/>
-      <c r="V66" s="50"/>
-      <c r="W66" s="50"/>
-      <c r="X66" s="50"/>
-      <c r="Y66" s="47"/>
-      <c r="Z66" s="47"/>
+      <c r="N66" s="53"/>
+      <c r="O66" s="50"/>
+      <c r="P66" s="51"/>
+      <c r="Q66" s="50"/>
+      <c r="R66" s="50"/>
+      <c r="S66" s="50"/>
+      <c r="T66" s="50"/>
+      <c r="U66" s="52"/>
+      <c r="V66" s="53"/>
+      <c r="W66" s="53"/>
+      <c r="X66" s="53"/>
+      <c r="Y66" s="50"/>
+      <c r="Z66" s="50"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5225,57 +5207,57 @@
       <c r="C67" s="55"/>
       <c r="D67" s="56"/>
       <c r="E67" s="57"/>
-      <c r="F67" s="50"/>
-      <c r="G67" s="50"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="50" t="str">
+      <c r="I67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
         <v> </v>
       </c>
-      <c r="J67" s="50" t="str">
+      <c r="J67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
         <v> </v>
       </c>
-      <c r="K67" s="50" t="str">
+      <c r="K67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
         <v> </v>
       </c>
-      <c r="L67" s="50"/>
+      <c r="L67" s="53"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="50"/>
-      <c r="O67" s="47"/>
+      <c r="N67" s="53"/>
+      <c r="O67" s="50"/>
       <c r="P67" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q67" s="47" t="str">
+      <c r="Q67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67*P67," ")</f>
         <v> </v>
       </c>
-      <c r="R67" s="47"/>
-      <c r="S67" s="47" t="str">
+      <c r="R67" s="50"/>
+      <c r="S67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
         <v> </v>
       </c>
-      <c r="T67" s="47"/>
+      <c r="T67" s="50"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="50" t="str">
+      <c r="W67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="50" t="str">
+      <c r="X67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="47" t="str">
+      <c r="Y67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="47" t="str">
+      <c r="Z67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5287,57 +5269,57 @@
       <c r="C68" s="55"/>
       <c r="D68" s="56"/>
       <c r="E68" s="57"/>
-      <c r="F68" s="50"/>
-      <c r="G68" s="50"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="50" t="str">
+      <c r="I68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
         <v> </v>
       </c>
-      <c r="J68" s="50" t="str">
+      <c r="J68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
         <v> </v>
       </c>
-      <c r="K68" s="50" t="str">
+      <c r="K68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
         <v> </v>
       </c>
-      <c r="L68" s="50"/>
+      <c r="L68" s="53"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="47"/>
+      <c r="N68" s="53"/>
+      <c r="O68" s="50"/>
       <c r="P68" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q68" s="47" t="str">
+      <c r="Q68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68*P68," ")</f>
         <v> </v>
       </c>
-      <c r="R68" s="47"/>
-      <c r="S68" s="47" t="str">
+      <c r="R68" s="50"/>
+      <c r="S68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
         <v> </v>
       </c>
-      <c r="T68" s="47"/>
+      <c r="T68" s="50"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="50" t="str">
+      <c r="W68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="50" t="str">
+      <c r="X68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="47" t="str">
+      <c r="Y68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="47" t="str">
+      <c r="Z68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5349,57 +5331,57 @@
       <c r="C69" s="55"/>
       <c r="D69" s="56"/>
       <c r="E69" s="57"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="50" t="str">
+      <c r="I69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
         <v> </v>
       </c>
-      <c r="J69" s="50" t="str">
+      <c r="J69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
         <v> </v>
       </c>
-      <c r="K69" s="50" t="str">
+      <c r="K69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
         <v> </v>
       </c>
-      <c r="L69" s="50"/>
+      <c r="L69" s="53"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="47"/>
+      <c r="N69" s="53"/>
+      <c r="O69" s="50"/>
       <c r="P69" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q69" s="47" t="str">
+      <c r="Q69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69*P69," ")</f>
         <v> </v>
       </c>
-      <c r="R69" s="47"/>
-      <c r="S69" s="47" t="str">
+      <c r="R69" s="50"/>
+      <c r="S69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
         <v> </v>
       </c>
-      <c r="T69" s="47"/>
+      <c r="T69" s="50"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="50" t="str">
+      <c r="W69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="50" t="str">
+      <c r="X69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="47" t="str">
+      <c r="Y69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="47" t="str">
+      <c r="Z69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5411,57 +5393,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="50" t="str">
+      <c r="I70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="50" t="str">
+      <c r="J70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="50" t="str">
+      <c r="K70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
         <v> </v>
       </c>
-      <c r="L70" s="50"/>
+      <c r="L70" s="53"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="47"/>
+      <c r="N70" s="53"/>
+      <c r="O70" s="50"/>
       <c r="P70" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="47" t="str">
+      <c r="Q70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47" t="str">
+      <c r="R70" s="50"/>
+      <c r="S70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="47"/>
+      <c r="T70" s="50"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="50" t="str">
+      <c r="W70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="50" t="str">
+      <c r="X70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="47" t="str">
+      <c r="Y70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="47" t="str">
+      <c r="Z70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5473,57 +5455,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="50" t="str">
+      <c r="I71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="50" t="str">
+      <c r="J71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="50" t="str">
+      <c r="K71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
         <v> </v>
       </c>
-      <c r="L71" s="50"/>
+      <c r="L71" s="53"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="50"/>
-      <c r="O71" s="47"/>
+      <c r="N71" s="53"/>
+      <c r="O71" s="50"/>
       <c r="P71" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q71" s="47" t="str">
+      <c r="Q71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="47"/>
-      <c r="S71" s="47" t="str">
+      <c r="R71" s="50"/>
+      <c r="S71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="47"/>
+      <c r="T71" s="50"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="50" t="str">
+      <c r="W71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="50" t="str">
+      <c r="X71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="47" t="str">
+      <c r="Y71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="47" t="str">
+      <c r="Z71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5532,7 +5514,7 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="42"/>
       <c r="B72" s="59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
@@ -5561,9 +5543,9 @@
         <f aca="false">SUM(K67:K71)</f>
         <v>0</v>
       </c>
-      <c r="L72" s="50"/>
+      <c r="L72" s="53"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="50"/>
+      <c r="N72" s="53"/>
       <c r="O72" s="61" t="n">
         <f aca="false">SUM(O67:O71)</f>
         <v>0</v>
@@ -5581,8 +5563,8 @@
         <f aca="false">SUM(S67:S71)</f>
         <v>0</v>
       </c>
-      <c r="T72" s="47"/>
-      <c r="U72" s="49"/>
+      <c r="T72" s="50"/>
+      <c r="U72" s="52"/>
       <c r="V72" s="60" t="n">
         <f aca="false">SUM(V67:V71)</f>
         <v>0</v>
@@ -5610,121 +5592,121 @@
       <c r="B73" s="63"/>
       <c r="C73" s="64"/>
       <c r="D73" s="65"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="50"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
       <c r="H73" s="58"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="L73" s="50"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="53"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="50"/>
-      <c r="O73" s="50"/>
+      <c r="N73" s="53"/>
+      <c r="O73" s="53"/>
       <c r="P73" s="62"/>
-      <c r="Q73" s="50"/>
-      <c r="R73" s="50"/>
-      <c r="S73" s="50"/>
-      <c r="T73" s="47"/>
-      <c r="U73" s="49"/>
-      <c r="V73" s="50"/>
-      <c r="W73" s="50"/>
-      <c r="X73" s="50"/>
-      <c r="Y73" s="50"/>
-      <c r="Z73" s="50"/>
+      <c r="Q73" s="53"/>
+      <c r="R73" s="53"/>
+      <c r="S73" s="53"/>
+      <c r="T73" s="50"/>
+      <c r="U73" s="52"/>
+      <c r="V73" s="53"/>
+      <c r="W73" s="53"/>
+      <c r="X73" s="53"/>
+      <c r="Y73" s="53"/>
+      <c r="Z73" s="53"/>
       <c r="AA73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="42"/>
-      <c r="B74" s="51" t="s">
+      <c r="B74" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="51"/>
+      <c r="C74" s="66"/>
       <c r="D74" s="62"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="50"/>
-      <c r="H74" s="82" t="n">
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="83" t="n">
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I74" s="50"/>
-      <c r="J74" s="50"/>
-      <c r="K74" s="50"/>
-      <c r="L74" s="50"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="50"/>
-      <c r="O74" s="47"/>
-      <c r="P74" s="48"/>
-      <c r="Q74" s="47"/>
-      <c r="R74" s="47"/>
-      <c r="S74" s="47"/>
-      <c r="T74" s="47"/>
-      <c r="U74" s="49"/>
-      <c r="V74" s="50"/>
-      <c r="W74" s="50"/>
-      <c r="X74" s="50"/>
-      <c r="Y74" s="47"/>
-      <c r="Z74" s="47"/>
+      <c r="N74" s="53"/>
+      <c r="O74" s="50"/>
+      <c r="P74" s="51"/>
+      <c r="Q74" s="50"/>
+      <c r="R74" s="50"/>
+      <c r="S74" s="50"/>
+      <c r="T74" s="50"/>
+      <c r="U74" s="52"/>
+      <c r="V74" s="53"/>
+      <c r="W74" s="53"/>
+      <c r="X74" s="53"/>
+      <c r="Y74" s="50"/>
+      <c r="Z74" s="50"/>
       <c r="AA74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
-      <c r="D75" s="80"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="57"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="50"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
       <c r="H75" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I75" s="50" t="str">
+      <c r="I75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,MIN(E75*H75,G75)," ")</f>
         <v> </v>
       </c>
-      <c r="J75" s="50" t="str">
+      <c r="J75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,F75+I75," ")</f>
         <v> </v>
       </c>
-      <c r="K75" s="50" t="str">
+      <c r="K75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,E75-J75," ")</f>
         <v> </v>
       </c>
-      <c r="L75" s="50"/>
+      <c r="L75" s="53"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="50"/>
-      <c r="O75" s="47"/>
+      <c r="N75" s="53"/>
+      <c r="O75" s="50"/>
       <c r="P75" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q75" s="47" t="str">
+      <c r="Q75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75*P75," ")</f>
         <v> </v>
       </c>
-      <c r="R75" s="47"/>
-      <c r="S75" s="47" t="str">
+      <c r="R75" s="50"/>
+      <c r="S75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75-Q75," ")</f>
         <v> </v>
       </c>
-      <c r="T75" s="47"/>
+      <c r="T75" s="50"/>
       <c r="U75" s="54"/>
       <c r="V75" s="57"/>
-      <c r="W75" s="50" t="str">
+      <c r="W75" s="53" t="str">
         <f aca="false">IF(V75&gt;0,E75," ")</f>
         <v> </v>
       </c>
-      <c r="X75" s="50" t="str">
+      <c r="X75" s="53" t="str">
         <f aca="false">IF(V75&gt;0,J75," ")</f>
         <v> </v>
       </c>
-      <c r="Y75" s="47" t="str">
+      <c r="Y75" s="50" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&lt;S75,S75-V75," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z75" s="47" t="str">
+      <c r="Z75" s="50" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&gt;S75,V75-S75," ")," ")</f>
         <v> </v>
       </c>
@@ -5734,59 +5716,59 @@
       <c r="A76" s="42"/>
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
-      <c r="D76" s="80"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="57"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
       <c r="H76" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I76" s="50" t="str">
+      <c r="I76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,MIN(E76*H76,G76)," ")</f>
         <v> </v>
       </c>
-      <c r="J76" s="50" t="str">
+      <c r="J76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,F76+I76," ")</f>
         <v> </v>
       </c>
-      <c r="K76" s="50" t="str">
+      <c r="K76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,E76-J76," ")</f>
         <v> </v>
       </c>
-      <c r="L76" s="50"/>
+      <c r="L76" s="53"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="50"/>
-      <c r="O76" s="47"/>
+      <c r="N76" s="53"/>
+      <c r="O76" s="50"/>
       <c r="P76" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q76" s="47" t="str">
+      <c r="Q76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76*P76," ")</f>
         <v> </v>
       </c>
-      <c r="R76" s="47"/>
-      <c r="S76" s="47" t="str">
+      <c r="R76" s="50"/>
+      <c r="S76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76-Q76," ")</f>
         <v> </v>
       </c>
-      <c r="T76" s="47"/>
+      <c r="T76" s="50"/>
       <c r="U76" s="54"/>
       <c r="V76" s="57"/>
-      <c r="W76" s="50" t="str">
+      <c r="W76" s="53" t="str">
         <f aca="false">IF(V76&gt;0,E76," ")</f>
         <v> </v>
       </c>
-      <c r="X76" s="50" t="str">
+      <c r="X76" s="53" t="str">
         <f aca="false">IF(V76&gt;0,J76," ")</f>
         <v> </v>
       </c>
-      <c r="Y76" s="47" t="str">
+      <c r="Y76" s="50" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&lt;S76,S76-V76," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z76" s="47" t="str">
+      <c r="Z76" s="50" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&gt;S76,V76-S76," ")," ")</f>
         <v> </v>
       </c>
@@ -5796,59 +5778,59 @@
       <c r="A77" s="42"/>
       <c r="B77" s="54"/>
       <c r="C77" s="55"/>
-      <c r="D77" s="80"/>
+      <c r="D77" s="81"/>
       <c r="E77" s="57"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
       <c r="H77" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="50" t="str">
+      <c r="I77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,MIN(E77*H77,G77)," ")</f>
         <v> </v>
       </c>
-      <c r="J77" s="50" t="str">
+      <c r="J77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,F77+I77," ")</f>
         <v> </v>
       </c>
-      <c r="K77" s="50" t="str">
+      <c r="K77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,E77-J77," ")</f>
         <v> </v>
       </c>
-      <c r="L77" s="50"/>
+      <c r="L77" s="53"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="50"/>
-      <c r="O77" s="47"/>
+      <c r="N77" s="53"/>
+      <c r="O77" s="50"/>
       <c r="P77" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="47" t="str">
+      <c r="Q77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77*P77," ")</f>
         <v> </v>
       </c>
-      <c r="R77" s="47"/>
-      <c r="S77" s="47" t="str">
+      <c r="R77" s="50"/>
+      <c r="S77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77-Q77," ")</f>
         <v> </v>
       </c>
-      <c r="T77" s="47"/>
+      <c r="T77" s="50"/>
       <c r="U77" s="54"/>
       <c r="V77" s="57"/>
-      <c r="W77" s="50" t="str">
+      <c r="W77" s="53" t="str">
         <f aca="false">IF(V77&gt;0,E77," ")</f>
         <v> </v>
       </c>
-      <c r="X77" s="50" t="str">
+      <c r="X77" s="53" t="str">
         <f aca="false">IF(V77&gt;0,J77," ")</f>
         <v> </v>
       </c>
-      <c r="Y77" s="47" t="str">
+      <c r="Y77" s="50" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&lt;S77,S77-V77," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z77" s="47" t="str">
+      <c r="Z77" s="50" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&gt;S77,V77-S77," ")," ")</f>
         <v> </v>
       </c>
@@ -5858,59 +5840,59 @@
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="80"/>
+      <c r="D78" s="81"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="50" t="str">
+      <c r="I78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="50" t="str">
+      <c r="J78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="50" t="str">
+      <c r="K78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
         <v> </v>
       </c>
-      <c r="L78" s="50"/>
+      <c r="L78" s="53"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="50"/>
-      <c r="O78" s="47"/>
+      <c r="N78" s="53"/>
+      <c r="O78" s="50"/>
       <c r="P78" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q78" s="47" t="str">
+      <c r="Q78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="47"/>
-      <c r="S78" s="47" t="str">
+      <c r="R78" s="50"/>
+      <c r="S78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="47"/>
+      <c r="T78" s="50"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="50" t="str">
+      <c r="W78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="50" t="str">
+      <c r="X78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="47" t="str">
+      <c r="Y78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="47" t="str">
+      <c r="Z78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5920,59 +5902,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="80"/>
+      <c r="D79" s="81"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="50" t="str">
+      <c r="I79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="50" t="str">
+      <c r="J79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="50" t="str">
+      <c r="K79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
         <v> </v>
       </c>
-      <c r="L79" s="50"/>
+      <c r="L79" s="53"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="50"/>
-      <c r="O79" s="47"/>
+      <c r="N79" s="53"/>
+      <c r="O79" s="50"/>
       <c r="P79" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q79" s="47" t="str">
+      <c r="Q79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="47"/>
-      <c r="S79" s="47" t="str">
+      <c r="R79" s="50"/>
+      <c r="S79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="47"/>
+      <c r="T79" s="50"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="50" t="str">
+      <c r="W79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="50" t="str">
+      <c r="X79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="47" t="str">
+      <c r="Y79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="47" t="str">
+      <c r="Z79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -5981,7 +5963,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="42"/>
       <c r="B80" s="59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C80" s="59"/>
       <c r="D80" s="59"/>
@@ -6010,9 +5992,9 @@
         <f aca="false">SUM(K75:K79)</f>
         <v>0</v>
       </c>
-      <c r="L80" s="50"/>
+      <c r="L80" s="53"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="50"/>
+      <c r="N80" s="53"/>
       <c r="O80" s="61" t="n">
         <f aca="false">SUM(O75:O79)</f>
         <v>0</v>
@@ -6030,8 +6012,8 @@
         <f aca="false">SUM(S75:S79)</f>
         <v>0</v>
       </c>
-      <c r="T80" s="47"/>
-      <c r="U80" s="49"/>
+      <c r="T80" s="50"/>
+      <c r="U80" s="52"/>
       <c r="V80" s="60" t="n">
         <f aca="false">SUM(V75:V79)</f>
         <v>0</v>
@@ -6059,121 +6041,121 @@
       <c r="B81" s="63"/>
       <c r="C81" s="64"/>
       <c r="D81" s="65"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
       <c r="H81" s="58"/>
-      <c r="I81" s="50"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
+      <c r="I81" s="53"/>
+      <c r="J81" s="53"/>
+      <c r="K81" s="53"/>
+      <c r="L81" s="53"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="50"/>
-      <c r="O81" s="50"/>
+      <c r="N81" s="53"/>
+      <c r="O81" s="53"/>
       <c r="P81" s="62"/>
-      <c r="Q81" s="50"/>
-      <c r="R81" s="50"/>
-      <c r="S81" s="50"/>
-      <c r="T81" s="47"/>
-      <c r="U81" s="49"/>
-      <c r="V81" s="50"/>
-      <c r="W81" s="50"/>
-      <c r="X81" s="50"/>
-      <c r="Y81" s="50"/>
-      <c r="Z81" s="50"/>
+      <c r="Q81" s="53"/>
+      <c r="R81" s="53"/>
+      <c r="S81" s="53"/>
+      <c r="T81" s="50"/>
+      <c r="U81" s="52"/>
+      <c r="V81" s="53"/>
+      <c r="W81" s="53"/>
+      <c r="X81" s="53"/>
+      <c r="Y81" s="53"/>
+      <c r="Z81" s="53"/>
       <c r="AA81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="42"/>
-      <c r="B82" s="51" t="s">
+      <c r="B82" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="51"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="82" t="n">
+      <c r="C82" s="66"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="83" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I82" s="50"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="53"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="50"/>
-      <c r="O82" s="47"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="47"/>
-      <c r="R82" s="47"/>
-      <c r="S82" s="47"/>
-      <c r="T82" s="47"/>
-      <c r="U82" s="49"/>
-      <c r="V82" s="50"/>
-      <c r="W82" s="50"/>
-      <c r="X82" s="50"/>
-      <c r="Y82" s="47"/>
-      <c r="Z82" s="47"/>
+      <c r="N82" s="53"/>
+      <c r="O82" s="50"/>
+      <c r="P82" s="51"/>
+      <c r="Q82" s="50"/>
+      <c r="R82" s="50"/>
+      <c r="S82" s="50"/>
+      <c r="T82" s="50"/>
+      <c r="U82" s="52"/>
+      <c r="V82" s="53"/>
+      <c r="W82" s="53"/>
+      <c r="X82" s="53"/>
+      <c r="Y82" s="50"/>
+      <c r="Z82" s="50"/>
       <c r="AA82" s="25"/>
     </row>
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="54"/>
       <c r="C83" s="55"/>
-      <c r="D83" s="80"/>
+      <c r="D83" s="81"/>
       <c r="E83" s="57"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
       <c r="H83" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I83" s="50" t="str">
+      <c r="I83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,MIN(E83*H83,G83)," ")</f>
         <v> </v>
       </c>
-      <c r="J83" s="50" t="str">
+      <c r="J83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,F83+I83," ")</f>
         <v> </v>
       </c>
-      <c r="K83" s="50" t="str">
+      <c r="K83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,E83-J83," ")</f>
         <v> </v>
       </c>
-      <c r="L83" s="50"/>
+      <c r="L83" s="53"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="50"/>
-      <c r="O83" s="47"/>
+      <c r="N83" s="53"/>
+      <c r="O83" s="50"/>
       <c r="P83" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q83" s="47" t="str">
+      <c r="Q83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83*P83," ")</f>
         <v> </v>
       </c>
-      <c r="R83" s="47"/>
-      <c r="S83" s="47" t="str">
+      <c r="R83" s="50"/>
+      <c r="S83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83-Q83," ")</f>
         <v> </v>
       </c>
-      <c r="T83" s="47"/>
+      <c r="T83" s="50"/>
       <c r="U83" s="54"/>
       <c r="V83" s="57"/>
-      <c r="W83" s="50" t="str">
+      <c r="W83" s="53" t="str">
         <f aca="false">IF(V83&gt;0,E83," ")</f>
         <v> </v>
       </c>
-      <c r="X83" s="50" t="str">
+      <c r="X83" s="53" t="str">
         <f aca="false">IF(V83&gt;0,J83," ")</f>
         <v> </v>
       </c>
-      <c r="Y83" s="47" t="str">
+      <c r="Y83" s="50" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&lt;S83,S83-V83," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z83" s="47" t="str">
+      <c r="Z83" s="50" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&gt;S83,V83-S83," ")," ")</f>
         <v> </v>
       </c>
@@ -6183,59 +6165,59 @@
       <c r="A84" s="42"/>
       <c r="B84" s="54"/>
       <c r="C84" s="55"/>
-      <c r="D84" s="80"/>
+      <c r="D84" s="81"/>
       <c r="E84" s="57"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
       <c r="H84" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I84" s="50" t="str">
+      <c r="I84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,MIN(E84*H84,G84)," ")</f>
         <v> </v>
       </c>
-      <c r="J84" s="50" t="str">
+      <c r="J84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,F84+I84," ")</f>
         <v> </v>
       </c>
-      <c r="K84" s="50" t="str">
+      <c r="K84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,E84-J84," ")</f>
         <v> </v>
       </c>
-      <c r="L84" s="50"/>
+      <c r="L84" s="53"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="50"/>
-      <c r="O84" s="47"/>
+      <c r="N84" s="53"/>
+      <c r="O84" s="50"/>
       <c r="P84" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q84" s="47" t="str">
+      <c r="Q84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84*P84," ")</f>
         <v> </v>
       </c>
-      <c r="R84" s="47"/>
-      <c r="S84" s="47" t="str">
+      <c r="R84" s="50"/>
+      <c r="S84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84-Q84," ")</f>
         <v> </v>
       </c>
-      <c r="T84" s="47"/>
+      <c r="T84" s="50"/>
       <c r="U84" s="54"/>
       <c r="V84" s="57"/>
-      <c r="W84" s="50" t="str">
+      <c r="W84" s="53" t="str">
         <f aca="false">IF(V84&gt;0,E84," ")</f>
         <v> </v>
       </c>
-      <c r="X84" s="50" t="str">
+      <c r="X84" s="53" t="str">
         <f aca="false">IF(V84&gt;0,J84," ")</f>
         <v> </v>
       </c>
-      <c r="Y84" s="47" t="str">
+      <c r="Y84" s="50" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&lt;S84,S84-V84," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z84" s="47" t="str">
+      <c r="Z84" s="50" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&gt;S84,V84-S84," ")," ")</f>
         <v> </v>
       </c>
@@ -6245,59 +6227,59 @@
       <c r="A85" s="42"/>
       <c r="B85" s="54"/>
       <c r="C85" s="55"/>
-      <c r="D85" s="80"/>
+      <c r="D85" s="81"/>
       <c r="E85" s="57"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
       <c r="H85" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="50" t="str">
+      <c r="I85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,MIN(E85*H85,G85)," ")</f>
         <v> </v>
       </c>
-      <c r="J85" s="50" t="str">
+      <c r="J85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,F85+I85," ")</f>
         <v> </v>
       </c>
-      <c r="K85" s="50" t="str">
+      <c r="K85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,E85-J85," ")</f>
         <v> </v>
       </c>
-      <c r="L85" s="50"/>
+      <c r="L85" s="53"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="50"/>
-      <c r="O85" s="47"/>
+      <c r="N85" s="53"/>
+      <c r="O85" s="50"/>
       <c r="P85" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q85" s="47" t="str">
+      <c r="Q85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85*P85," ")</f>
         <v> </v>
       </c>
-      <c r="R85" s="47"/>
-      <c r="S85" s="47" t="str">
+      <c r="R85" s="50"/>
+      <c r="S85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85-Q85," ")</f>
         <v> </v>
       </c>
-      <c r="T85" s="47"/>
+      <c r="T85" s="50"/>
       <c r="U85" s="54"/>
       <c r="V85" s="57"/>
-      <c r="W85" s="50" t="str">
+      <c r="W85" s="53" t="str">
         <f aca="false">IF(V85&gt;0,E85," ")</f>
         <v> </v>
       </c>
-      <c r="X85" s="50" t="str">
+      <c r="X85" s="53" t="str">
         <f aca="false">IF(V85&gt;0,J85," ")</f>
         <v> </v>
       </c>
-      <c r="Y85" s="47" t="str">
+      <c r="Y85" s="50" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&lt;S85,S85-V85," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z85" s="47" t="str">
+      <c r="Z85" s="50" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&gt;S85,V85-S85," ")," ")</f>
         <v> </v>
       </c>
@@ -6307,59 +6289,59 @@
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="80"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="50" t="str">
+      <c r="I86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="50" t="str">
+      <c r="J86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="50" t="str">
+      <c r="K86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
         <v> </v>
       </c>
-      <c r="L86" s="50"/>
+      <c r="L86" s="53"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="50"/>
-      <c r="O86" s="47"/>
+      <c r="N86" s="53"/>
+      <c r="O86" s="50"/>
       <c r="P86" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q86" s="47" t="str">
+      <c r="Q86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="47"/>
-      <c r="S86" s="47" t="str">
+      <c r="R86" s="50"/>
+      <c r="S86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="47"/>
+      <c r="T86" s="50"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="50" t="str">
+      <c r="W86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="50" t="str">
+      <c r="X86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="47" t="str">
+      <c r="Y86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="47" t="str">
+      <c r="Z86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6369,59 +6351,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="80"/>
+      <c r="D87" s="81"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="50" t="str">
+      <c r="I87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="50" t="str">
+      <c r="J87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="50" t="str">
+      <c r="K87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
         <v> </v>
       </c>
-      <c r="L87" s="50"/>
+      <c r="L87" s="53"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="50"/>
-      <c r="O87" s="47"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="50"/>
       <c r="P87" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q87" s="47" t="str">
+      <c r="Q87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="47"/>
-      <c r="S87" s="47" t="str">
+      <c r="R87" s="50"/>
+      <c r="S87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="47"/>
+      <c r="T87" s="50"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="50" t="str">
+      <c r="W87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="50" t="str">
+      <c r="X87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="47" t="str">
+      <c r="Y87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="47" t="str">
+      <c r="Z87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6430,7 +6412,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="42"/>
       <c r="B88" s="59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -6459,9 +6441,9 @@
         <f aca="false">SUM(K83:K87)</f>
         <v>0</v>
       </c>
-      <c r="L88" s="50"/>
+      <c r="L88" s="53"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="50"/>
+      <c r="N88" s="53"/>
       <c r="O88" s="61" t="n">
         <f aca="false">SUM(O83:O87)</f>
         <v>0</v>
@@ -6479,8 +6461,8 @@
         <f aca="false">SUM(S83:S87)</f>
         <v>0</v>
       </c>
-      <c r="T88" s="47"/>
-      <c r="U88" s="49"/>
+      <c r="T88" s="50"/>
+      <c r="U88" s="52"/>
       <c r="V88" s="60" t="n">
         <f aca="false">SUM(V83:V87)</f>
         <v>0</v>
@@ -6508,124 +6490,124 @@
       <c r="B89" s="63"/>
       <c r="C89" s="64"/>
       <c r="D89" s="65"/>
-      <c r="E89" s="50"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
       <c r="H89" s="58"/>
-      <c r="I89" s="50"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
-      <c r="L89" s="50"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="53"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="50"/>
-      <c r="O89" s="50"/>
+      <c r="N89" s="53"/>
+      <c r="O89" s="53"/>
       <c r="P89" s="62"/>
-      <c r="Q89" s="50"/>
-      <c r="R89" s="50"/>
-      <c r="S89" s="50"/>
-      <c r="T89" s="47"/>
-      <c r="U89" s="49"/>
-      <c r="V89" s="50"/>
-      <c r="W89" s="50"/>
-      <c r="X89" s="50"/>
-      <c r="Y89" s="50"/>
-      <c r="Z89" s="50"/>
+      <c r="Q89" s="53"/>
+      <c r="R89" s="53"/>
+      <c r="S89" s="53"/>
+      <c r="T89" s="50"/>
+      <c r="U89" s="52"/>
+      <c r="V89" s="53"/>
+      <c r="W89" s="53"/>
+      <c r="X89" s="53"/>
+      <c r="Y89" s="53"/>
+      <c r="Z89" s="53"/>
       <c r="AA89" s="25"/>
     </row>
     <row r="90" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="42"/>
-      <c r="B90" s="69" t="str">
+      <c r="B90" s="70" t="str">
         <f aca="false">B37</f>
         <v>Motor Vehicles - costing over £</v>
       </c>
-      <c r="C90" s="69"/>
-      <c r="D90" s="70" t="n">
+      <c r="C90" s="70"/>
+      <c r="D90" s="71" t="n">
         <f aca="false">D37</f>
         <v>12000</v>
       </c>
-      <c r="E90" s="50"/>
-      <c r="F90" s="50"/>
-      <c r="G90" s="50"/>
-      <c r="H90" s="82" t="n">
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="83" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I90" s="50"/>
-      <c r="J90" s="50"/>
-      <c r="K90" s="50"/>
-      <c r="L90" s="50"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="50"/>
-      <c r="O90" s="47"/>
+      <c r="N90" s="53"/>
+      <c r="O90" s="50"/>
       <c r="P90" s="62"/>
-      <c r="Q90" s="47"/>
-      <c r="R90" s="47"/>
-      <c r="S90" s="47"/>
-      <c r="T90" s="47"/>
-      <c r="U90" s="49"/>
-      <c r="V90" s="50"/>
-      <c r="W90" s="50"/>
-      <c r="X90" s="50"/>
-      <c r="Y90" s="47"/>
-      <c r="Z90" s="47"/>
+      <c r="Q90" s="50"/>
+      <c r="R90" s="50"/>
+      <c r="S90" s="50"/>
+      <c r="T90" s="50"/>
+      <c r="U90" s="52"/>
+      <c r="V90" s="53"/>
+      <c r="W90" s="53"/>
+      <c r="X90" s="53"/>
+      <c r="Y90" s="50"/>
+      <c r="Z90" s="50"/>
       <c r="AA90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="80"/>
+      <c r="D91" s="81"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I91" s="50" t="str">
+      <c r="I91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="50" t="str">
+      <c r="J91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="50" t="str">
+      <c r="K91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
         <v> </v>
       </c>
-      <c r="L91" s="50"/>
-      <c r="M91" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="50"/>
-      <c r="O91" s="47"/>
-      <c r="P91" s="48"/>
-      <c r="Q91" s="47"/>
-      <c r="R91" s="47" t="str">
+      <c r="L91" s="53"/>
+      <c r="M91" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="53"/>
+      <c r="O91" s="50"/>
+      <c r="P91" s="51"/>
+      <c r="Q91" s="50"/>
+      <c r="R91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
         <v> </v>
       </c>
-      <c r="S91" s="47" t="str">
+      <c r="S91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91-R91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="47"/>
+      <c r="T91" s="50"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="50" t="str">
+      <c r="W91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="50" t="str">
+      <c r="X91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="47" t="str">
+      <c r="Y91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,(S91-V91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="47" t="str">
+      <c r="Z91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,(V91-S91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
@@ -6635,58 +6617,58 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="80"/>
+      <c r="D92" s="81"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="50"/>
+      <c r="F92" s="53"/>
+      <c r="G92" s="53"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I92" s="50" t="str">
+      <c r="I92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="50" t="str">
+      <c r="J92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="50" t="str">
+      <c r="K92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
         <v> </v>
       </c>
-      <c r="L92" s="50"/>
-      <c r="M92" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="50"/>
-      <c r="O92" s="47"/>
-      <c r="P92" s="48"/>
-      <c r="Q92" s="47"/>
-      <c r="R92" s="47" t="str">
+      <c r="L92" s="53"/>
+      <c r="M92" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="53"/>
+      <c r="O92" s="50"/>
+      <c r="P92" s="51"/>
+      <c r="Q92" s="50"/>
+      <c r="R92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
         <v> </v>
       </c>
-      <c r="S92" s="47" t="str">
+      <c r="S92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92-R92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="47"/>
+      <c r="T92" s="50"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="50" t="str">
+      <c r="W92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="50" t="str">
+      <c r="X92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="47" t="str">
+      <c r="Y92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,(S92-V92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="47" t="str">
+      <c r="Z92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,(V92-S92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
@@ -6696,58 +6678,58 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="80"/>
+      <c r="D93" s="81"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
+      <c r="F93" s="53"/>
+      <c r="G93" s="53"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I93" s="50" t="str">
+      <c r="I93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="50" t="str">
+      <c r="J93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="50" t="str">
+      <c r="K93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
         <v> </v>
       </c>
-      <c r="L93" s="50"/>
-      <c r="M93" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="50"/>
-      <c r="O93" s="47"/>
-      <c r="P93" s="48"/>
-      <c r="Q93" s="47"/>
-      <c r="R93" s="47" t="str">
+      <c r="L93" s="53"/>
+      <c r="M93" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="53"/>
+      <c r="O93" s="50"/>
+      <c r="P93" s="51"/>
+      <c r="Q93" s="50"/>
+      <c r="R93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
         <v> </v>
       </c>
-      <c r="S93" s="47" t="str">
+      <c r="S93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93-R93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="47"/>
+      <c r="T93" s="50"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="50" t="str">
+      <c r="W93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="50" t="str">
+      <c r="X93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="47" t="str">
+      <c r="Y93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,(S93-V93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="47" t="str">
+      <c r="Z93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,(V93-S93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
@@ -6757,58 +6739,58 @@
       <c r="A94" s="42"/>
       <c r="B94" s="54"/>
       <c r="C94" s="55"/>
-      <c r="D94" s="80"/>
+      <c r="D94" s="81"/>
       <c r="E94" s="57"/>
-      <c r="F94" s="50"/>
-      <c r="G94" s="50"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
       <c r="H94" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I94" s="50" t="str">
+      <c r="I94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*H94,G94)," ")</f>
         <v> </v>
       </c>
-      <c r="J94" s="50" t="str">
+      <c r="J94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,F94+I94," ")</f>
         <v> </v>
       </c>
-      <c r="K94" s="50" t="str">
+      <c r="K94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,E94-J94," ")</f>
         <v> </v>
       </c>
-      <c r="L94" s="50"/>
-      <c r="M94" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="50"/>
-      <c r="O94" s="47"/>
-      <c r="P94" s="48"/>
-      <c r="Q94" s="47"/>
-      <c r="R94" s="47" t="str">
+      <c r="L94" s="53"/>
+      <c r="M94" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="53"/>
+      <c r="O94" s="50"/>
+      <c r="P94" s="51"/>
+      <c r="Q94" s="50"/>
+      <c r="R94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
         <v> </v>
       </c>
-      <c r="S94" s="47" t="str">
+      <c r="S94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,E94-R94," ")</f>
         <v> </v>
       </c>
-      <c r="T94" s="47"/>
+      <c r="T94" s="50"/>
       <c r="U94" s="54"/>
       <c r="V94" s="57"/>
-      <c r="W94" s="50" t="str">
+      <c r="W94" s="53" t="str">
         <f aca="false">IF(V94&gt;0,E94," ")</f>
         <v> </v>
       </c>
-      <c r="X94" s="50" t="str">
+      <c r="X94" s="53" t="str">
         <f aca="false">IF(V94&gt;0,J94," ")</f>
         <v> </v>
       </c>
-      <c r="Y94" s="47" t="str">
+      <c r="Y94" s="50" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&lt;S94,(S94-V94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z94" s="47" t="str">
+      <c r="Z94" s="50" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&gt;S94,(V94-S94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
@@ -6818,58 +6800,58 @@
       <c r="A95" s="42"/>
       <c r="B95" s="54"/>
       <c r="C95" s="55"/>
-      <c r="D95" s="80"/>
+      <c r="D95" s="81"/>
       <c r="E95" s="57"/>
-      <c r="F95" s="50"/>
-      <c r="G95" s="50"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="53"/>
       <c r="H95" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I95" s="50" t="str">
+      <c r="I95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*H95,G95)," ")</f>
         <v> </v>
       </c>
-      <c r="J95" s="50" t="str">
+      <c r="J95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,F95+I95," ")</f>
         <v> </v>
       </c>
-      <c r="K95" s="50" t="str">
+      <c r="K95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,E95-J95," ")</f>
         <v> </v>
       </c>
-      <c r="L95" s="50"/>
-      <c r="M95" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="50"/>
-      <c r="O95" s="47"/>
-      <c r="P95" s="48"/>
-      <c r="Q95" s="47"/>
-      <c r="R95" s="47" t="str">
+      <c r="L95" s="53"/>
+      <c r="M95" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="53"/>
+      <c r="O95" s="50"/>
+      <c r="P95" s="51"/>
+      <c r="Q95" s="50"/>
+      <c r="R95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
         <v> </v>
       </c>
-      <c r="S95" s="47" t="str">
+      <c r="S95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,E95-R95," ")</f>
         <v> </v>
       </c>
-      <c r="T95" s="47"/>
+      <c r="T95" s="50"/>
       <c r="U95" s="54"/>
       <c r="V95" s="57"/>
-      <c r="W95" s="50" t="str">
+      <c r="W95" s="53" t="str">
         <f aca="false">IF(V95&gt;0,E95," ")</f>
         <v> </v>
       </c>
-      <c r="X95" s="50" t="str">
+      <c r="X95" s="53" t="str">
         <f aca="false">IF(V95&gt;0,J95," ")</f>
         <v> </v>
       </c>
-      <c r="Y95" s="47" t="str">
+      <c r="Y95" s="50" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&lt;S95,(S95-V95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z95" s="47" t="str">
+      <c r="Z95" s="50" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&gt;S95,(V95-S95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
@@ -6877,95 +6859,95 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="83" t="str">
+      <c r="B96" s="84" t="str">
         <f aca="false">B43</f>
         <v>Motor Vehicles - costing under £</v>
       </c>
-      <c r="C96" s="83"/>
-      <c r="D96" s="70" t="n">
+      <c r="C96" s="84"/>
+      <c r="D96" s="71" t="n">
         <f aca="false">D43</f>
         <v>12000</v>
       </c>
-      <c r="E96" s="50"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53"/>
       <c r="H96" s="58"/>
-      <c r="I96" s="50"/>
-      <c r="J96" s="50"/>
-      <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="50"/>
-      <c r="O96" s="47"/>
-      <c r="P96" s="48"/>
-      <c r="Q96" s="47"/>
-      <c r="R96" s="47"/>
-      <c r="S96" s="47"/>
-      <c r="T96" s="47"/>
-      <c r="U96" s="49"/>
-      <c r="V96" s="50"/>
-      <c r="W96" s="50"/>
-      <c r="X96" s="50"/>
-      <c r="Y96" s="47"/>
-      <c r="Z96" s="47"/>
+      <c r="N96" s="53"/>
+      <c r="O96" s="50"/>
+      <c r="P96" s="51"/>
+      <c r="Q96" s="50"/>
+      <c r="R96" s="50"/>
+      <c r="S96" s="50"/>
+      <c r="T96" s="50"/>
+      <c r="U96" s="52"/>
+      <c r="V96" s="53"/>
+      <c r="W96" s="53"/>
+      <c r="X96" s="53"/>
+      <c r="Y96" s="50"/>
+      <c r="Z96" s="50"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="80"/>
+      <c r="D97" s="81"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
+      <c r="F97" s="53"/>
+      <c r="G97" s="53"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="50" t="str">
+      <c r="I97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="50" t="str">
+      <c r="J97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="50" t="str">
+      <c r="K97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
         <v> </v>
       </c>
-      <c r="L97" s="50"/>
-      <c r="M97" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="50"/>
-      <c r="O97" s="47"/>
-      <c r="P97" s="48"/>
-      <c r="Q97" s="47"/>
-      <c r="R97" s="47" t="str">
+      <c r="L97" s="53"/>
+      <c r="M97" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="53"/>
+      <c r="O97" s="50"/>
+      <c r="P97" s="51"/>
+      <c r="Q97" s="50"/>
+      <c r="R97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="47" t="str">
+      <c r="S97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="47"/>
+      <c r="T97" s="50"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="50" t="str">
+      <c r="W97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="50" t="str">
+      <c r="X97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="47" t="str">
+      <c r="Y97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="47" t="str">
+      <c r="Z97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -6975,58 +6957,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="80"/>
+      <c r="D98" s="81"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="50"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="50" t="str">
+      <c r="I98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="50" t="str">
+      <c r="J98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="50" t="str">
+      <c r="K98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
         <v> </v>
       </c>
-      <c r="L98" s="50"/>
-      <c r="M98" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="50"/>
-      <c r="O98" s="47"/>
-      <c r="P98" s="48"/>
-      <c r="Q98" s="47"/>
-      <c r="R98" s="47" t="str">
+      <c r="L98" s="53"/>
+      <c r="M98" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="53"/>
+      <c r="O98" s="50"/>
+      <c r="P98" s="51"/>
+      <c r="Q98" s="50"/>
+      <c r="R98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="47" t="str">
+      <c r="S98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="47"/>
+      <c r="T98" s="50"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="50" t="str">
+      <c r="W98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="50" t="str">
+      <c r="X98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="47" t="str">
+      <c r="Y98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="47" t="str">
+      <c r="Z98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -7036,58 +7018,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="80"/>
+      <c r="D99" s="81"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
+      <c r="F99" s="53"/>
+      <c r="G99" s="53"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="50" t="str">
+      <c r="I99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="50" t="str">
+      <c r="J99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="50" t="str">
+      <c r="K99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
         <v> </v>
       </c>
-      <c r="L99" s="50"/>
-      <c r="M99" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="50"/>
-      <c r="O99" s="47"/>
-      <c r="P99" s="48"/>
-      <c r="Q99" s="47"/>
-      <c r="R99" s="47" t="str">
+      <c r="L99" s="53"/>
+      <c r="M99" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="53"/>
+      <c r="O99" s="50"/>
+      <c r="P99" s="51"/>
+      <c r="Q99" s="50"/>
+      <c r="R99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="47" t="str">
+      <c r="S99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="47"/>
+      <c r="T99" s="50"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="50" t="str">
+      <c r="W99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="50" t="str">
+      <c r="X99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="47" t="str">
+      <c r="Y99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="47" t="str">
+      <c r="Z99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -7097,58 +7079,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="80"/>
+      <c r="D100" s="81"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="53"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="50" t="str">
+      <c r="I100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="50" t="str">
+      <c r="J100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="50" t="str">
+      <c r="K100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
         <v> </v>
       </c>
-      <c r="L100" s="50"/>
-      <c r="M100" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="50"/>
-      <c r="O100" s="47"/>
-      <c r="P100" s="48"/>
-      <c r="Q100" s="47"/>
-      <c r="R100" s="47" t="str">
+      <c r="L100" s="53"/>
+      <c r="M100" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="53"/>
+      <c r="O100" s="50"/>
+      <c r="P100" s="51"/>
+      <c r="Q100" s="50"/>
+      <c r="R100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="47" t="str">
+      <c r="S100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="47"/>
+      <c r="T100" s="50"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="50" t="str">
+      <c r="W100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="50" t="str">
+      <c r="X100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="47" t="str">
+      <c r="Y100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="47" t="str">
+      <c r="Z100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -7158,58 +7140,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="80"/>
+      <c r="D101" s="81"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
+      <c r="F101" s="53"/>
+      <c r="G101" s="53"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="50" t="str">
+      <c r="I101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="50" t="str">
+      <c r="J101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="50" t="str">
+      <c r="K101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
         <v> </v>
       </c>
-      <c r="L101" s="50"/>
-      <c r="M101" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="50"/>
-      <c r="O101" s="47"/>
-      <c r="P101" s="48"/>
-      <c r="Q101" s="47"/>
-      <c r="R101" s="47" t="str">
+      <c r="L101" s="53"/>
+      <c r="M101" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="53"/>
+      <c r="O101" s="50"/>
+      <c r="P101" s="51"/>
+      <c r="Q101" s="50"/>
+      <c r="R101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="47" t="str">
+      <c r="S101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="47"/>
+      <c r="T101" s="50"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="50" t="str">
+      <c r="W101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="50" t="str">
+      <c r="X101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="47" t="str">
+      <c r="Y101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="47" t="str">
+      <c r="Z101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7217,94 +7199,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="C102" s="51"/>
-      <c r="D102" s="68"/>
-      <c r="E102" s="50"/>
-      <c r="F102" s="50"/>
-      <c r="G102" s="50"/>
+      <c r="B102" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102" s="66"/>
+      <c r="D102" s="69"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="50"/>
-      <c r="J102" s="50"/>
-      <c r="K102" s="50"/>
-      <c r="L102" s="50"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="53"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="50"/>
-      <c r="O102" s="47"/>
-      <c r="P102" s="48"/>
-      <c r="Q102" s="47"/>
-      <c r="R102" s="47"/>
-      <c r="S102" s="47"/>
-      <c r="T102" s="47"/>
-      <c r="U102" s="49"/>
-      <c r="V102" s="50"/>
-      <c r="W102" s="50"/>
-      <c r="X102" s="50"/>
-      <c r="Y102" s="47"/>
-      <c r="Z102" s="47"/>
+      <c r="N102" s="53"/>
+      <c r="O102" s="50"/>
+      <c r="P102" s="51"/>
+      <c r="Q102" s="50"/>
+      <c r="R102" s="50"/>
+      <c r="S102" s="50"/>
+      <c r="T102" s="50"/>
+      <c r="U102" s="52"/>
+      <c r="V102" s="53"/>
+      <c r="W102" s="53"/>
+      <c r="X102" s="53"/>
+      <c r="Y102" s="50"/>
+      <c r="Z102" s="50"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="80"/>
+      <c r="D103" s="81"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="50"/>
-      <c r="G103" s="50"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="50" t="str">
+      <c r="I103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="50" t="str">
+      <c r="J103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="50" t="str">
+      <c r="K103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
         <v> </v>
       </c>
-      <c r="L103" s="50"/>
-      <c r="M103" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="50"/>
-      <c r="O103" s="47"/>
+      <c r="L103" s="53"/>
+      <c r="M103" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="53"/>
+      <c r="O103" s="50"/>
       <c r="P103" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q103" s="47" t="str">
+      <c r="Q103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="47"/>
-      <c r="S103" s="47" t="str">
+      <c r="R103" s="50"/>
+      <c r="S103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="47"/>
+      <c r="T103" s="50"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="50" t="str">
+      <c r="W103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="50" t="str">
+      <c r="X103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="47" t="str">
+      <c r="Y103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="47" t="str">
+      <c r="Z103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7314,61 +7296,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="80"/>
+      <c r="D104" s="81"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="50"/>
-      <c r="G104" s="50"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="50" t="str">
+      <c r="I104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="50" t="str">
+      <c r="J104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="50" t="str">
+      <c r="K104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
         <v> </v>
       </c>
-      <c r="L104" s="50"/>
-      <c r="M104" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="50"/>
-      <c r="O104" s="47"/>
+      <c r="L104" s="53"/>
+      <c r="M104" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="53"/>
+      <c r="O104" s="50"/>
       <c r="P104" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q104" s="47" t="str">
+      <c r="Q104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="47"/>
-      <c r="S104" s="47" t="str">
+      <c r="R104" s="50"/>
+      <c r="S104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="47"/>
+      <c r="T104" s="50"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="50" t="str">
+      <c r="W104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="50" t="str">
+      <c r="X104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="47" t="str">
+      <c r="Y104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="47" t="str">
+      <c r="Z104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7378,61 +7360,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="80"/>
+      <c r="D105" s="81"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="50"/>
-      <c r="G105" s="50"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="50" t="str">
+      <c r="I105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="50" t="str">
+      <c r="J105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="50" t="str">
+      <c r="K105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
         <v> </v>
       </c>
-      <c r="L105" s="50"/>
-      <c r="M105" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="50"/>
-      <c r="O105" s="47"/>
+      <c r="L105" s="53"/>
+      <c r="M105" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="53"/>
+      <c r="O105" s="50"/>
       <c r="P105" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q105" s="47" t="str">
+      <c r="Q105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="47"/>
-      <c r="S105" s="47" t="str">
+      <c r="R105" s="50"/>
+      <c r="S105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="47"/>
+      <c r="T105" s="50"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="50" t="str">
+      <c r="W105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="50" t="str">
+      <c r="X105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="47" t="str">
+      <c r="Y105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="47" t="str">
+      <c r="Z105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7442,61 +7424,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="80"/>
+      <c r="D106" s="81"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="50"/>
-      <c r="G106" s="50"/>
+      <c r="F106" s="53"/>
+      <c r="G106" s="53"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="50" t="str">
+      <c r="I106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="50" t="str">
+      <c r="J106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="50" t="str">
+      <c r="K106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
         <v> </v>
       </c>
-      <c r="L106" s="50"/>
-      <c r="M106" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="50"/>
-      <c r="O106" s="47"/>
+      <c r="L106" s="53"/>
+      <c r="M106" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="53"/>
+      <c r="O106" s="50"/>
       <c r="P106" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q106" s="47" t="str">
+      <c r="Q106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="47"/>
-      <c r="S106" s="47" t="str">
+      <c r="R106" s="50"/>
+      <c r="S106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="47"/>
+      <c r="T106" s="50"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="50" t="str">
+      <c r="W106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="50" t="str">
+      <c r="X106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="47" t="str">
+      <c r="Y106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="47" t="str">
+      <c r="Z106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7506,61 +7488,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="80"/>
-      <c r="E107" s="84"/>
-      <c r="F107" s="50"/>
-      <c r="G107" s="50"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="85"/>
+      <c r="F107" s="53"/>
+      <c r="G107" s="53"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="50" t="str">
+      <c r="I107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="50" t="str">
+      <c r="J107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="50" t="str">
+      <c r="K107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
         <v> </v>
       </c>
-      <c r="L107" s="50"/>
-      <c r="M107" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="50"/>
-      <c r="O107" s="47"/>
+      <c r="L107" s="53"/>
+      <c r="M107" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="53"/>
+      <c r="O107" s="50"/>
       <c r="P107" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q107" s="47" t="str">
+      <c r="Q107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="47"/>
-      <c r="S107" s="47" t="str">
+      <c r="R107" s="50"/>
+      <c r="S107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="47"/>
+      <c r="T107" s="50"/>
       <c r="U107" s="54"/>
-      <c r="V107" s="84"/>
-      <c r="W107" s="50" t="str">
+      <c r="V107" s="85"/>
+      <c r="W107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="50" t="str">
+      <c r="X107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="47" t="str">
+      <c r="Y107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="47" t="str">
+      <c r="Z107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7569,7 +7551,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7598,9 +7580,9 @@
         <f aca="false">SUM(K91:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="50"/>
+      <c r="L108" s="53"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="50"/>
+      <c r="N108" s="53"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O91:O107)</f>
         <v>0</v>
@@ -7618,8 +7600,8 @@
         <f aca="false">SUM(S91:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="47"/>
-      <c r="U108" s="49"/>
+      <c r="T108" s="50"/>
+      <c r="U108" s="52"/>
       <c r="V108" s="61" t="n">
         <f aca="false">SUM(V91:V107)</f>
         <v>0</v>
@@ -7644,31 +7626,31 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="73"/>
-      <c r="D109" s="68"/>
-      <c r="E109" s="50"/>
-      <c r="F109" s="50"/>
-      <c r="G109" s="50"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="74"/>
+      <c r="D109" s="69"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="53"/>
+      <c r="G109" s="53"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="50"/>
-      <c r="J109" s="50"/>
-      <c r="K109" s="50"/>
-      <c r="L109" s="50"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="53"/>
+      <c r="L109" s="53"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="50"/>
-      <c r="O109" s="47"/>
-      <c r="P109" s="48"/>
-      <c r="Q109" s="47"/>
-      <c r="R109" s="47"/>
-      <c r="S109" s="47"/>
-      <c r="T109" s="47"/>
-      <c r="U109" s="49"/>
-      <c r="V109" s="50"/>
-      <c r="W109" s="47"/>
-      <c r="X109" s="47"/>
-      <c r="Y109" s="47"/>
-      <c r="Z109" s="47"/>
+      <c r="N109" s="53"/>
+      <c r="O109" s="50"/>
+      <c r="P109" s="51"/>
+      <c r="Q109" s="50"/>
+      <c r="R109" s="50"/>
+      <c r="S109" s="50"/>
+      <c r="T109" s="50"/>
+      <c r="U109" s="52"/>
+      <c r="V109" s="53"/>
+      <c r="W109" s="50"/>
+      <c r="X109" s="50"/>
+      <c r="Y109" s="50"/>
+      <c r="Z109" s="50"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7682,103 +7664,103 @@
         <f aca="false">D59</f>
         <v>45753</v>
       </c>
-      <c r="E110" s="74" t="n">
+      <c r="E110" s="75" t="n">
         <f aca="false">E64+E72+E80+E88+E108</f>
         <v>0</v>
       </c>
-      <c r="F110" s="74" t="n">
+      <c r="F110" s="75" t="n">
         <f aca="false">F64+F72+F80+F88+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="74" t="n">
+      <c r="G110" s="75" t="n">
         <f aca="false">G64+G72+G80+G88+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="74" t="n">
+      <c r="I110" s="75" t="n">
         <f aca="false">I64+I72+I80+I88+I108</f>
         <v>0</v>
       </c>
-      <c r="J110" s="74" t="n">
+      <c r="J110" s="75" t="n">
         <f aca="false">J64+J72+J80+J88+J108</f>
         <v>0</v>
       </c>
-      <c r="K110" s="74" t="n">
+      <c r="K110" s="75" t="n">
         <f aca="false">K64+K72+K80+K88+K108</f>
         <v>0</v>
       </c>
-      <c r="L110" s="50"/>
+      <c r="L110" s="53"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="50"/>
-      <c r="O110" s="74" t="n">
+      <c r="N110" s="53"/>
+      <c r="O110" s="75" t="n">
         <f aca="false">O64+O72+O80+O88+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="74" t="n">
+      <c r="Q110" s="75" t="n">
         <f aca="false">Q64+Q72+Q80+Q88+Q108</f>
         <v>0</v>
       </c>
-      <c r="R110" s="74" t="n">
+      <c r="R110" s="75" t="n">
         <f aca="false">R64+R72+R80+R88+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="74" t="n">
+      <c r="S110" s="75" t="n">
         <f aca="false">S64+S72+S80+S88+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="47"/>
-      <c r="U110" s="49"/>
-      <c r="V110" s="74" t="n">
+      <c r="T110" s="50"/>
+      <c r="U110" s="52"/>
+      <c r="V110" s="75" t="n">
         <f aca="false">V64+V72+V80+V88+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="74" t="n">
+      <c r="W110" s="75" t="n">
         <f aca="false">W64+W72+W80+W88+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="74" t="n">
+      <c r="X110" s="75" t="n">
         <f aca="false">X64+X72+X80+X88+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="74" t="n">
+      <c r="Y110" s="75" t="n">
         <f aca="false">Y64+Y72+Y80+Y88+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="74" t="n">
+      <c r="Z110" s="75" t="n">
         <f aca="false">Z64+Z72+Z80+Z88+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="85"/>
-      <c r="B111" s="86"/>
-      <c r="C111" s="87"/>
-      <c r="D111" s="88"/>
-      <c r="E111" s="89"/>
-      <c r="F111" s="89"/>
-      <c r="G111" s="89"/>
-      <c r="H111" s="90"/>
-      <c r="I111" s="89"/>
-      <c r="J111" s="89"/>
-      <c r="K111" s="89"/>
-      <c r="L111" s="89"/>
-      <c r="M111" s="90"/>
-      <c r="N111" s="89"/>
-      <c r="O111" s="91"/>
-      <c r="P111" s="92"/>
-      <c r="Q111" s="91"/>
-      <c r="R111" s="91"/>
-      <c r="S111" s="91"/>
-      <c r="T111" s="91"/>
-      <c r="U111" s="86"/>
-      <c r="V111" s="89"/>
-      <c r="W111" s="89"/>
-      <c r="X111" s="89"/>
-      <c r="Y111" s="91"/>
-      <c r="Z111" s="91"/>
-      <c r="AA111" s="93"/>
+      <c r="A111" s="86"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="88"/>
+      <c r="D111" s="89"/>
+      <c r="E111" s="90"/>
+      <c r="F111" s="90"/>
+      <c r="G111" s="90"/>
+      <c r="H111" s="91"/>
+      <c r="I111" s="90"/>
+      <c r="J111" s="90"/>
+      <c r="K111" s="90"/>
+      <c r="L111" s="90"/>
+      <c r="M111" s="91"/>
+      <c r="N111" s="90"/>
+      <c r="O111" s="92"/>
+      <c r="P111" s="93"/>
+      <c r="Q111" s="92"/>
+      <c r="R111" s="92"/>
+      <c r="S111" s="92"/>
+      <c r="T111" s="92"/>
+      <c r="U111" s="87"/>
+      <c r="V111" s="90"/>
+      <c r="W111" s="90"/>
+      <c r="X111" s="90"/>
+      <c r="Y111" s="92"/>
+      <c r="Z111" s="92"/>
+      <c r="AA111" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -7864,37 +7846,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="94" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="94" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="94" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="94" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="94" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="94" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="94" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="94" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="94" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="94" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="94" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="94" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="95" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="95" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="95" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="95" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="95" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="95" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="95" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="95" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="95" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="95" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="95"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="96"/>
+      <c r="A1" s="96"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7906,23 +7888,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="104"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="105"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7934,21 +7916,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="104"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="105"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -7960,31 +7942,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="97"/>
-      <c r="B4" s="107" t="s">
+      <c r="A4" s="98"/>
+      <c r="B4" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="109" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="103"/>
+      <c r="G4" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="108" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="102"/>
-      <c r="G4" s="109" t="s">
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="108" t="s">
+      <c r="L4" s="103"/>
+      <c r="M4" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="102"/>
-      <c r="M4" s="110" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="110"/>
-      <c r="O4" s="104"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="105"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -7996,25 +7978,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="97"/>
-      <c r="B5" s="98" t="s">
+      <c r="A5" s="98"/>
+      <c r="B5" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="98" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="99"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="104"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="105"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -8026,31 +8008,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="97"/>
-      <c r="B6" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112" t="n">
+      <c r="A6" s="98"/>
+      <c r="B6" s="112" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="113" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="111" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="112" t="n">
+      <c r="F6" s="103"/>
+      <c r="G6" s="112" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="113" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="102"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="104"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="105"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -8062,31 +8044,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="97"/>
-      <c r="B7" s="111" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="112" t="n">
+      <c r="A7" s="98"/>
+      <c r="B7" s="112" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="113" t="n">
         <f aca="false">Schedule!E72</f>
         <v>0</v>
       </c>
-      <c r="F7" s="102"/>
-      <c r="G7" s="111" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="112" t="n">
+      <c r="F7" s="103"/>
+      <c r="G7" s="112" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="113" t="n">
         <f aca="false">Schedule!V19+Schedule!V72</f>
         <v>0</v>
       </c>
-      <c r="L7" s="102"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="104"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="105"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -8098,31 +8080,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="97"/>
-      <c r="B8" s="111" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112" t="n">
+      <c r="A8" s="98"/>
+      <c r="B8" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="113" t="n">
         <f aca="false">Schedule!E80</f>
         <v>0</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="111" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="112" t="n">
+      <c r="F8" s="103"/>
+      <c r="G8" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="113" t="n">
         <f aca="false">Schedule!V27+Schedule!V80</f>
         <v>0</v>
       </c>
-      <c r="L8" s="102"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="104"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="105"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -8134,31 +8116,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="97"/>
-      <c r="B9" s="111" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="112" t="n">
+      <c r="A9" s="98"/>
+      <c r="B9" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113" t="n">
         <f aca="false">Schedule!E88</f>
         <v>0</v>
       </c>
-      <c r="F9" s="102"/>
-      <c r="G9" s="111" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="112" t="n">
+      <c r="F9" s="103"/>
+      <c r="G9" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="113" t="n">
         <f aca="false">Schedule!V35+Schedule!V88</f>
         <v>0</v>
       </c>
-      <c r="L9" s="102"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="104"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="105"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -8170,31 +8152,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="97"/>
-      <c r="B10" s="111" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112" t="n">
+      <c r="A10" s="98"/>
+      <c r="B10" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="112" t="n">
+      <c r="F10" s="103"/>
+      <c r="G10" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="113" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
         <v>0</v>
       </c>
-      <c r="L10" s="102"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="104"/>
+      <c r="L10" s="103"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="105"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8206,31 +8188,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="97"/>
-      <c r="B11" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="113"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114" t="n">
+      <c r="A11" s="98"/>
+      <c r="B11" s="114" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="115" t="n">
         <f aca="false">SUM(E6:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="102"/>
-      <c r="G11" s="115" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="115"/>
-      <c r="K11" s="114" t="n">
+      <c r="F11" s="103"/>
+      <c r="G11" s="116" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="115" t="n">
         <f aca="false">SUM(K6:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="104"/>
+      <c r="L11" s="103"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="111"/>
+      <c r="O11" s="105"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8242,21 +8224,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="97"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="102"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="104"/>
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="105"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8268,31 +8250,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="97"/>
-      <c r="B13" s="113" t="s">
+      <c r="A13" s="98"/>
+      <c r="B13" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="117" t="n">
+        <f aca="false">[2]Mar!$AB$2</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="103"/>
+      <c r="G13" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="116" t="n">
-        <f aca="false">[2]Mar!$AB$2</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="102"/>
-      <c r="G13" s="115" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="115"/>
-      <c r="K13" s="116" t="n">
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="117" t="n">
         <f aca="false">[3]Mar!$V$2</f>
         <v>0</v>
       </c>
-      <c r="L13" s="102"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="104"/>
+      <c r="L13" s="103"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="105"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8304,21 +8286,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="97"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="104"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="105"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8330,33 +8312,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="97"/>
-      <c r="B15" s="117" t="str">
+      <c r="A15" s="98"/>
+      <c r="B15" s="118" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="118" t="n">
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="119" t="n">
         <f aca="false">E13-E11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="102"/>
-      <c r="G15" s="117" t="str">
+      <c r="F15" s="103"/>
+      <c r="G15" s="118" t="str">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="118" t="n">
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="119" t="n">
         <f aca="false">K13-K11</f>
         <v>0</v>
       </c>
-      <c r="L15" s="102"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="104"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="105"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8368,21 +8350,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="119"/>
-      <c r="B16" s="120"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="125"/>
+      <c r="A16" s="120"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="125"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="126"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8434,122 +8416,122 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="126" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="126" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="127" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="126" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="126" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="128"/>
-      <c r="B1" s="98"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="128"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="129"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="128"/>
-      <c r="B2" s="131"/>
-      <c r="C2" s="132" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="n">
+        <f aca="false">SUM(E8:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="135"/>
+      <c r="G2" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133" t="n">
-        <f aca="false">SUM(E8:E14)</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135" t="s">
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="129"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="129"/>
+      <c r="B3" s="137" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="128"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="128"/>
-      <c r="B3" s="136" t="s">
-        <v>60</v>
-      </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="128"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="129"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="128"/>
-      <c r="B4" s="49"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="128"/>
-    </row>
-    <row r="5" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="139"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="129"/>
+    </row>
+    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="D5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="E5" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="140" t="s">
+      <c r="F5" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="140" t="s">
+      <c r="G5" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="140" t="s">
+      <c r="H5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="I5" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="140" t="s">
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M5" s="139"/>
-    </row>
-    <row r="6" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="139"/>
+      <c r="M5" s="140"/>
+    </row>
+    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="140"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8557,273 +8539,273 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="140" t="s">
+      <c r="I6" s="141" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="140" t="s">
+      <c r="K6" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="K6" s="140" t="s">
-        <v>72</v>
-      </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="139"/>
+      <c r="M6" s="140"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="128"/>
-      <c r="B7" s="49"/>
+      <c r="A7" s="129"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="128"/>
+      <c r="M7" s="129"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="128"/>
+      <c r="A8" s="129"/>
       <c r="B8" s="54"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="134" t="str">
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="135" t="str">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="134" t="str">
+      <c r="J8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="134" t="str">
+      <c r="K8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="128"/>
+      <c r="M8" s="129"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="128"/>
-      <c r="B9" s="49"/>
+      <c r="A9" s="129"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="128"/>
+      <c r="M9" s="129"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="128"/>
+      <c r="A10" s="129"/>
       <c r="B10" s="54"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="142"/>
-      <c r="I10" s="134" t="e">
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="134" t="str">
+      <c r="J10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="134" t="str">
+      <c r="K10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="128"/>
+      <c r="M10" s="129"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="128"/>
-      <c r="B11" s="49"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="52"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="128"/>
+      <c r="M11" s="129"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="128"/>
+      <c r="A12" s="129"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="134" t="e">
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="134" t="str">
+      <c r="J12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="134" t="str">
+      <c r="K12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="128"/>
+      <c r="M12" s="129"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="128"/>
-      <c r="B13" s="49"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="134"/>
-      <c r="J13" s="134"/>
-      <c r="K13" s="134"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="128"/>
+      <c r="M13" s="129"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="128"/>
+      <c r="A14" s="129"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="134" t="e">
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="134" t="str">
+      <c r="J14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="134" t="str">
+      <c r="K14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="128"/>
+      <c r="M14" s="129"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="128"/>
-      <c r="B15" s="49"/>
+      <c r="A15" s="129"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="128"/>
+      <c r="M15" s="129"/>
     </row>
     <row r="16" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="128"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="100"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="128"/>
+      <c r="A16" s="129"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="129"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="128"/>
-      <c r="B17" s="136" t="s">
+      <c r="A17" s="129"/>
+      <c r="B17" s="137" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="62"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="131"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="128"/>
+      <c r="M17" s="129"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="128"/>
-      <c r="B18" s="49"/>
+      <c r="A18" s="129"/>
+      <c r="B18" s="52"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
       <c r="L18" s="62"/>
-      <c r="M18" s="128"/>
-    </row>
-    <row r="19" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="139"/>
+      <c r="M18" s="129"/>
+    </row>
+    <row r="19" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="140"/>
       <c r="B19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="D19" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="E19" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="140" t="s">
+      <c r="F19" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="140" t="s">
+      <c r="G19" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="140" t="s">
+      <c r="H19" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="I19" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="I19" s="140" t="s">
+      <c r="J19" s="141"/>
+      <c r="K19" s="141"/>
+      <c r="L19" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="J19" s="140"/>
-      <c r="K19" s="140"/>
-      <c r="L19" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M19" s="139"/>
-    </row>
-    <row r="20" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="139"/>
+      <c r="M19" s="140"/>
+    </row>
+    <row r="20" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="140"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8831,203 +8813,203 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
-      <c r="I20" s="140" t="s">
+      <c r="I20" s="141" t="s">
+        <v>69</v>
+      </c>
+      <c r="J20" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="140" t="s">
+      <c r="K20" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="K20" s="140" t="s">
-        <v>72</v>
-      </c>
       <c r="L20" s="21"/>
-      <c r="M20" s="139"/>
-    </row>
-    <row r="21" s="141" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="139"/>
-      <c r="B21" s="143"/>
-      <c r="C21" s="143"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="139"/>
+      <c r="M20" s="140"/>
+    </row>
+    <row r="21" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="140"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="140"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="128"/>
+      <c r="A22" s="129"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="142"/>
-      <c r="I22" s="134" t="str">
+      <c r="E22" s="134"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="135" t="str">
         <f aca="false">IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="134" t="str">
+      <c r="J22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="134" t="str">
+      <c r="K22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="128"/>
+      <c r="M22" s="129"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="128"/>
-      <c r="B23" s="49"/>
+      <c r="A23" s="129"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="134"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="128"/>
+      <c r="M23" s="129"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="128"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="142"/>
-      <c r="I24" s="134" t="e">
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="134" t="str">
+      <c r="J24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="134" t="str">
+      <c r="K24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="128"/>
+      <c r="M24" s="129"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="128"/>
-      <c r="B25" s="49"/>
+      <c r="A25" s="129"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="134"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="135"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="128"/>
+      <c r="M25" s="129"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="128"/>
+      <c r="A26" s="129"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="142"/>
-      <c r="I26" s="134" t="e">
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="134" t="str">
+      <c r="J26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="134" t="str">
+      <c r="K26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="128"/>
+      <c r="M26" s="129"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="128"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="129"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="134"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="134"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="128"/>
+      <c r="M27" s="129"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="128"/>
+      <c r="A28" s="129"/>
       <c r="B28" s="54"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="142"/>
-      <c r="I28" s="134" t="e">
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="143"/>
+      <c r="I28" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="134" t="str">
+      <c r="J28" s="135" t="str">
         <f aca="false">IF(H28&gt;0,I28-K28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="134" t="str">
+      <c r="K28" s="135" t="str">
         <f aca="false">IF(H28&gt;0,G28/H28," ")</f>
         <v> </v>
       </c>
       <c r="L28" s="56"/>
-      <c r="M28" s="128"/>
+      <c r="M28" s="129"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="128"/>
-      <c r="B29" s="49"/>
+      <c r="A29" s="129"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="134"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="135"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="128"/>
+      <c r="M29" s="129"/>
     </row>
     <row r="30" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="128"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="128"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="128"/>
+      <c r="A30" s="129"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="129"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
   </si>
   <si>
-    <t xml:space="preserve">Laptop (0.5 years old)</t>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">Existing Land &amp; Property</t>
@@ -250,10 +250,16 @@
     <t xml:space="preserve">Computers</t>
   </si>
   <si>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Existing Computers</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing over £</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van (2.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing under £</t>
@@ -268,10 +274,16 @@
     <t xml:space="preserve">NEW FIXED ASSETS Bought AFTER </t>
   </si>
   <si>
-    <t xml:space="preserve">Land &amp; Property</t>
+    <t xml:space="preserve">New Land &amp; Property</t>
   </si>
   <si>
-    <t xml:space="preserve">New Land &amp; Property</t>
+    <t xml:space="preserve">Dell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IKEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
   </si>
   <si>
     <t xml:space="preserve">New Plant &amp; Machinery</t>
@@ -752,7 +764,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -937,8 +949,28 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -949,26 +981,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1015,10 +1027,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1377,7 +1385,7 @@
       <sheetData sheetId="9">
         <row r="4">
           <cell r="B4">
-            <v>45753</v>
+            <v>46118</v>
           </cell>
         </row>
         <row r="4">
@@ -1387,7 +1395,7 @@
         </row>
         <row r="5">
           <cell r="G5">
-            <v>0.18</v>
+            <v>0.14</v>
           </cell>
         </row>
         <row r="8">
@@ -1422,7 +1430,7 @@
         </row>
         <row r="17">
           <cell r="B17">
-            <v>46117</v>
+            <v>46482</v>
           </cell>
         </row>
         <row r="17">
@@ -1471,7 +1479,7 @@
       <sheetData sheetId="12">
         <row r="2">
           <cell r="AB2">
-            <v>0</v>
+            <v>32500</v>
           </cell>
         </row>
       </sheetData>
@@ -1516,7 +1524,7 @@
       <sheetData sheetId="12">
         <row r="2">
           <cell r="V2">
-            <v>0</v>
+            <v>12500</v>
           </cell>
         </row>
       </sheetData>
@@ -1679,30 +1687,30 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12" t="n">
         <f aca="false">E57+E110</f>
-        <v>0</v>
+        <v>65500</v>
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>0</v>
+        <v>10098</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
-        <v>0</v>
+        <v>22902</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="13" t="n">
         <f aca="false">I57+I110</f>
-        <v>0</v>
+        <v>11740</v>
       </c>
       <c r="J1" s="13" t="n">
         <f aca="false">J57+J110</f>
-        <v>0</v>
+        <v>21838</v>
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>0</v>
+        <v>43662</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1711,22 +1719,22 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13" t="n">
         <f aca="false">O57+O110</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="P1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="Q1" s="13" t="n">
         <f aca="false">Q57+Q110</f>
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="S1" s="13" t="n">
         <f aca="false">S57+S110</f>
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="T1" s="16"/>
       <c r="U1" s="17" t="s">
@@ -1734,19 +1742,19 @@
       </c>
       <c r="V1" s="13" t="n">
         <f aca="false">V57+V110</f>
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="W1" s="13" t="n">
         <f aca="false">W57+W110</f>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="X1" s="13" t="n">
         <f aca="false">X57+X110</f>
-        <v>0</v>
+        <v>17328</v>
       </c>
       <c r="Y1" s="13" t="n">
         <f aca="false">Y57+Y110</f>
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="Z1" s="13" t="n">
         <f aca="false">Z57+Z110</f>
@@ -1854,28 +1862,28 @@
       <c r="E4" s="22"/>
       <c r="F4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
+        <v>46118</v>
       </c>
       <c r="G4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
+        <v>46118</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="23"/>
       <c r="J4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46117</v>
+        <v>46482</v>
       </c>
       <c r="K4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46117</v>
+        <v>46482</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
       <c r="N4" s="13"/>
       <c r="O4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
+        <v>46118</v>
       </c>
       <c r="P4" s="27" t="n">
         <f aca="false">[1]Admin!$G$4</f>
@@ -1884,11 +1892,11 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="28" t="n">
         <f aca="false">[1]Admin!$G$5</f>
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="S4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46117</v>
+        <v>46482</v>
       </c>
       <c r="T4" s="16"/>
       <c r="U4" s="17"/>
@@ -1934,24 +1942,45 @@
         <v>22</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="44" t="n">
+        <f aca="false">[1]Admin!$B$4</f>
+        <v>46118</v>
+      </c>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="50"/>
+      <c r="W6" s="50"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42"/>
+      <c r="B7" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="45" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y6" s="7" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="45"/>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">[1]Admin!$G$13</f>
         <v>0</v>
       </c>
@@ -1959,20 +1988,20 @@
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
-      <c r="M7" s="49"/>
+      <c r="M7" s="46"/>
       <c r="N7" s="45"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="50"/>
-      <c r="Z7" s="50"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1982,7 +2011,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="53" t="str">
+      <c r="G8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -1990,39 +2019,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="53" t="str">
+      <c r="I8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="53" t="str">
+      <c r="J8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="53" t="str">
+      <c r="K8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
         <v> </v>
       </c>
-      <c r="L8" s="53"/>
+      <c r="L8" s="50"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="53" t="str">
+      <c r="W8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="53" t="str">
+      <c r="X8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2032,7 +2061,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="53" t="str">
+      <c r="G9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -2040,39 +2069,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="53" t="str">
+      <c r="I9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="53" t="str">
+      <c r="J9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="53" t="str">
+      <c r="K9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
         <v> </v>
       </c>
-      <c r="L9" s="53"/>
+      <c r="L9" s="50"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="53" t="str">
+      <c r="W9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="53" t="str">
+      <c r="X9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="50"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2082,7 +2111,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="53" t="str">
+      <c r="G10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -2090,39 +2119,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="53" t="str">
+      <c r="I10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="53" t="str">
+      <c r="J10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="53" t="str">
+      <c r="K10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
         <v> </v>
       </c>
-      <c r="L10" s="53"/>
+      <c r="L10" s="50"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="53" t="str">
+      <c r="W10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="53" t="str">
+      <c r="X10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="50"/>
-      <c r="Z10" s="50"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="47"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2157,9 +2186,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="53"/>
+      <c r="L11" s="50"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="53"/>
+      <c r="N11" s="50"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -2177,8 +2206,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="50"/>
-      <c r="U11" s="52"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="49"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2206,62 +2235,62 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="53"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="53"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="66"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="67" t="n">
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="66" t="n">
         <f aca="false">[1]Admin!$G$14</f>
         <v>0.1</v>
       </c>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="50"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2271,7 +2300,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2279,48 +2308,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="53" t="str">
+      <c r="J14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="53" t="str">
+      <c r="K14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
         <v> </v>
       </c>
-      <c r="L14" s="53"/>
+      <c r="L14" s="50"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50" t="str">
+      <c r="N14" s="50"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="50" t="str">
+      <c r="S14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="50"/>
+      <c r="T14" s="47"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="53" t="str">
+      <c r="W14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="53" t="str">
+      <c r="X14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="50" t="str">
+      <c r="Y14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="50" t="str">
+      <c r="Z14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2333,7 +2362,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="53" t="str">
+      <c r="G15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2341,48 +2370,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="53" t="str">
+      <c r="I15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="53" t="str">
+      <c r="J15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="53" t="str">
+      <c r="K15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
         <v> </v>
       </c>
-      <c r="L15" s="53"/>
+      <c r="L15" s="50"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50" t="str">
+      <c r="N15" s="50"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="50" t="str">
+      <c r="S15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="50"/>
+      <c r="T15" s="47"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="53" t="str">
+      <c r="W15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="53" t="str">
+      <c r="X15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="50" t="str">
+      <c r="Y15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="50" t="str">
+      <c r="Z15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2395,7 +2424,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2403,48 +2432,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="53" t="str">
+      <c r="J16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="53" t="str">
+      <c r="K16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
         <v> </v>
       </c>
-      <c r="L16" s="53"/>
+      <c r="L16" s="50"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50" t="str">
+      <c r="N16" s="50"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="50" t="str">
+      <c r="S16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="50"/>
+      <c r="T16" s="47"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="53" t="str">
+      <c r="W16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="53" t="str">
+      <c r="X16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="50" t="str">
+      <c r="Y16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="50" t="str">
+      <c r="Z16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2457,7 +2486,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="53" t="str">
+      <c r="G17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2465,48 +2494,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="53" t="str">
+      <c r="I17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="53" t="str">
+      <c r="J17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="53" t="str">
+      <c r="K17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
         <v> </v>
       </c>
-      <c r="L17" s="53"/>
+      <c r="L17" s="50"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50" t="str">
+      <c r="N17" s="50"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="50" t="str">
+      <c r="S17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="50"/>
+      <c r="T17" s="47"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="53" t="str">
+      <c r="W17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="53" t="str">
+      <c r="X17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="50" t="str">
+      <c r="Y17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="50" t="str">
+      <c r="Z17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2519,7 +2548,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="53" t="str">
+      <c r="G18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2527,48 +2556,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="53" t="str">
+      <c r="J18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="53" t="str">
+      <c r="K18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
         <v> </v>
       </c>
-      <c r="L18" s="53"/>
+      <c r="L18" s="50"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50" t="str">
+      <c r="N18" s="50"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="50" t="str">
+      <c r="S18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="50"/>
+      <c r="T18" s="47"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="53" t="str">
+      <c r="W18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="53" t="str">
+      <c r="X18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="50" t="str">
+      <c r="Y18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="50" t="str">
+      <c r="Z18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2606,9 +2635,9 @@
         <f aca="false">SUM(K14:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="53"/>
+      <c r="L19" s="50"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="53"/>
+      <c r="N19" s="50"/>
       <c r="O19" s="61" t="n">
         <f aca="false">SUM(O14:O18)</f>
         <v>0</v>
@@ -2626,8 +2655,8 @@
         <f aca="false">SUM(S14:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="50"/>
-      <c r="U19" s="52"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="49"/>
       <c r="V19" s="60" t="n">
         <f aca="false">SUM(V14:V18)</f>
         <v>0</v>
@@ -2655,62 +2684,62 @@
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
       <c r="H20" s="58"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
       <c r="P20" s="62"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="52"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
+      <c r="Z20" s="50"/>
       <c r="AA20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="42"/>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="66"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="67" t="n">
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="66" t="n">
         <f aca="false">[1]Admin!$G$15</f>
         <v>0.2</v>
       </c>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="50"/>
-      <c r="Z21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="50"/>
+      <c r="W21" s="50"/>
+      <c r="X21" s="50"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="47"/>
       <c r="AA21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2720,7 +2749,7 @@
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
       <c r="F22" s="57"/>
-      <c r="G22" s="53" t="str">
+      <c r="G22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,E22-F22," ")</f>
         <v> </v>
       </c>
@@ -2728,48 +2757,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I22" s="53" t="str">
+      <c r="I22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,MIN(E22*H22,G22)," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="53" t="str">
+      <c r="J22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,F22+I22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="53" t="str">
+      <c r="K22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,E22-J22," ")</f>
         <v> </v>
       </c>
-      <c r="L22" s="53"/>
+      <c r="L22" s="50"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="68"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50" t="str">
+      <c r="N22" s="50"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47" t="str">
         <f aca="false">IF(O22&gt;0,O22*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S22" s="50" t="str">
+      <c r="S22" s="47" t="str">
         <f aca="false">IF(O22&gt;0,O22-R22," ")</f>
         <v> </v>
       </c>
-      <c r="T22" s="50"/>
+      <c r="T22" s="47"/>
       <c r="U22" s="54"/>
       <c r="V22" s="57"/>
-      <c r="W22" s="53" t="str">
+      <c r="W22" s="50" t="str">
         <f aca="false">IF(V22&gt;0,E22," ")</f>
         <v> </v>
       </c>
-      <c r="X22" s="53" t="str">
+      <c r="X22" s="50" t="str">
         <f aca="false">IF(V22&gt;0,J22," ")</f>
         <v> </v>
       </c>
-      <c r="Y22" s="50" t="str">
+      <c r="Y22" s="47" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&lt;S22,S22-V22," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z22" s="50" t="str">
+      <c r="Z22" s="47" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&gt;S22,V22-S22," ")," ")</f>
         <v> </v>
       </c>
@@ -2782,7 +2811,7 @@
       <c r="D23" s="56"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="53" t="str">
+      <c r="G23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,E23-F23," ")</f>
         <v> </v>
       </c>
@@ -2790,48 +2819,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I23" s="53" t="str">
+      <c r="I23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,MIN(E23*H23,G23)," ")</f>
         <v> </v>
       </c>
-      <c r="J23" s="53" t="str">
+      <c r="J23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,F23+I23," ")</f>
         <v> </v>
       </c>
-      <c r="K23" s="53" t="str">
+      <c r="K23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,E23-J23," ")</f>
         <v> </v>
       </c>
-      <c r="L23" s="53"/>
+      <c r="L23" s="50"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50" t="str">
+      <c r="N23" s="50"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="47" t="str">
         <f aca="false">IF(O23&gt;0,O23*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S23" s="50" t="str">
+      <c r="S23" s="47" t="str">
         <f aca="false">IF(O23&gt;0,O23-R23," ")</f>
         <v> </v>
       </c>
-      <c r="T23" s="50"/>
+      <c r="T23" s="47"/>
       <c r="U23" s="54"/>
       <c r="V23" s="57"/>
-      <c r="W23" s="53" t="str">
+      <c r="W23" s="50" t="str">
         <f aca="false">IF(V23&gt;0,E23," ")</f>
         <v> </v>
       </c>
-      <c r="X23" s="53" t="str">
+      <c r="X23" s="50" t="str">
         <f aca="false">IF(V23&gt;0,J23," ")</f>
         <v> </v>
       </c>
-      <c r="Y23" s="50" t="str">
+      <c r="Y23" s="47" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&lt;S23,S23-V23," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z23" s="50" t="str">
+      <c r="Z23" s="47" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&gt;S23,V23-S23," ")," ")</f>
         <v> </v>
       </c>
@@ -2844,7 +2873,7 @@
       <c r="D24" s="56"/>
       <c r="E24" s="57"/>
       <c r="F24" s="57"/>
-      <c r="G24" s="53" t="str">
+      <c r="G24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,E24-F24," ")</f>
         <v> </v>
       </c>
@@ -2852,48 +2881,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I24" s="53" t="str">
+      <c r="I24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,MIN(E24*H24,G24)," ")</f>
         <v> </v>
       </c>
-      <c r="J24" s="53" t="str">
+      <c r="J24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,F24+I24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="53" t="str">
+      <c r="K24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,E24-J24," ")</f>
         <v> </v>
       </c>
-      <c r="L24" s="53"/>
+      <c r="L24" s="50"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50" t="str">
+      <c r="N24" s="50"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47" t="str">
         <f aca="false">IF(O24&gt;0,O24*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S24" s="50" t="str">
+      <c r="S24" s="47" t="str">
         <f aca="false">IF(O24&gt;0,O24-R24," ")</f>
         <v> </v>
       </c>
-      <c r="T24" s="50"/>
+      <c r="T24" s="47"/>
       <c r="U24" s="54"/>
       <c r="V24" s="57"/>
-      <c r="W24" s="53" t="str">
+      <c r="W24" s="50" t="str">
         <f aca="false">IF(V24&gt;0,E24," ")</f>
         <v> </v>
       </c>
-      <c r="X24" s="53" t="str">
+      <c r="X24" s="50" t="str">
         <f aca="false">IF(V24&gt;0,J24," ")</f>
         <v> </v>
       </c>
-      <c r="Y24" s="50" t="str">
+      <c r="Y24" s="47" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&lt;S24,S24-V24," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z24" s="50" t="str">
+      <c r="Z24" s="47" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&gt;S24,V24-S24," ")," ")</f>
         <v> </v>
       </c>
@@ -2906,7 +2935,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="53" t="str">
+      <c r="G25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2914,48 +2943,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="53" t="str">
+      <c r="I25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="53" t="str">
+      <c r="J25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="53" t="str">
+      <c r="K25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
         <v> </v>
       </c>
-      <c r="L25" s="53"/>
+      <c r="L25" s="50"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50" t="str">
+      <c r="N25" s="50"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="50" t="str">
+      <c r="S25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="50"/>
+      <c r="T25" s="47"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="53" t="str">
+      <c r="W25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="53" t="str">
+      <c r="X25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="50" t="str">
+      <c r="Y25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="50" t="str">
+      <c r="Z25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2968,7 +2997,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="53" t="str">
+      <c r="G26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -2976,48 +3005,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="53" t="str">
+      <c r="I26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="53" t="str">
+      <c r="J26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="53" t="str">
+      <c r="K26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
         <v> </v>
       </c>
-      <c r="L26" s="53"/>
+      <c r="L26" s="50"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50" t="str">
+      <c r="N26" s="50"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="50" t="str">
+      <c r="S26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="50"/>
+      <c r="T26" s="47"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="53" t="str">
+      <c r="W26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="53" t="str">
+      <c r="X26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="50" t="str">
+      <c r="Y26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="50" t="str">
+      <c r="Z26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -3055,9 +3084,9 @@
         <f aca="false">SUM(K22:K26)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="53"/>
+      <c r="L27" s="50"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="53"/>
+      <c r="N27" s="50"/>
       <c r="O27" s="61" t="n">
         <f aca="false">SUM(O22:O26)</f>
         <v>0</v>
@@ -3075,8 +3104,8 @@
         <f aca="false">SUM(S22:S26)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="50"/>
-      <c r="U27" s="52"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="49"/>
       <c r="V27" s="60" t="n">
         <f aca="false">SUM(V22:V26)</f>
         <v>0</v>
@@ -3104,121 +3133,127 @@
       <c r="B28" s="63"/>
       <c r="C28" s="64"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
       <c r="H28" s="58"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
       <c r="P28" s="62"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="53"/>
-      <c r="X28" s="53"/>
-      <c r="Y28" s="53"/>
-      <c r="Z28" s="53"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="50"/>
+      <c r="W28" s="50"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
       <c r="AA28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="42"/>
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="66"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="67" t="n">
+      <c r="C29" s="51"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="66" t="n">
         <f aca="false">[1]Admin!$G$16</f>
         <v>0.33</v>
       </c>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="53"/>
-      <c r="W29" s="53"/>
-      <c r="X29" s="53"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="50"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="47"/>
+      <c r="Z29" s="47"/>
       <c r="AA29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="42"/>
       <c r="B30" s="54"/>
-      <c r="C30" s="55"/>
+      <c r="C30" s="55" t="s">
+        <v>30</v>
+      </c>
       <c r="D30" s="56"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="53" t="str">
+      <c r="E30" s="57" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F30" s="57" t="n">
+        <v>270</v>
+      </c>
+      <c r="G30" s="50" t="n">
         <f aca="false">IF(E30&gt;0,E30-F30," ")</f>
-        <v> </v>
+        <v>2730</v>
       </c>
       <c r="H30" s="58" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I30" s="53" t="str">
+      <c r="I30" s="50" t="n">
         <f aca="false">IF(E30&gt;0,MIN(E30*H30,G30)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J30" s="53" t="str">
+        <v>990</v>
+      </c>
+      <c r="J30" s="50" t="n">
         <f aca="false">IF(E30&gt;0,F30+I30," ")</f>
-        <v> </v>
-      </c>
-      <c r="K30" s="53" t="str">
+        <v>1260</v>
+      </c>
+      <c r="K30" s="50" t="n">
         <f aca="false">IF(E30&gt;0,E30-J30," ")</f>
-        <v> </v>
-      </c>
-      <c r="L30" s="53"/>
+        <v>1740</v>
+      </c>
+      <c r="L30" s="50"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50" t="str">
+      <c r="N30" s="50"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="47"/>
+      <c r="R30" s="47" t="str">
         <f aca="false">IF(O30&gt;0,O30*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S30" s="50" t="str">
+      <c r="S30" s="47" t="str">
         <f aca="false">IF(O30&gt;0,O30-R30," ")</f>
         <v> </v>
       </c>
-      <c r="T30" s="50"/>
+      <c r="T30" s="47"/>
       <c r="U30" s="54"/>
       <c r="V30" s="57"/>
-      <c r="W30" s="53" t="str">
+      <c r="W30" s="50" t="str">
         <f aca="false">IF(V30&gt;0,E30," ")</f>
         <v> </v>
       </c>
-      <c r="X30" s="53" t="str">
+      <c r="X30" s="50" t="str">
         <f aca="false">IF(V30&gt;0,J30," ")</f>
         <v> </v>
       </c>
-      <c r="Y30" s="50" t="str">
+      <c r="Y30" s="47" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&lt;S30,S30-V30," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z30" s="50" t="str">
+      <c r="Z30" s="47" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&gt;S30,V30-S30," ")," ")</f>
         <v> </v>
       </c>
@@ -3231,7 +3266,7 @@
       <c r="D31" s="56"/>
       <c r="E31" s="57"/>
       <c r="F31" s="57"/>
-      <c r="G31" s="53" t="str">
+      <c r="G31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,E31-F31," ")</f>
         <v> </v>
       </c>
@@ -3239,48 +3274,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I31" s="53" t="str">
+      <c r="I31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,MIN(E31*H31,G31)," ")</f>
         <v> </v>
       </c>
-      <c r="J31" s="53" t="str">
+      <c r="J31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,F31+I31," ")</f>
         <v> </v>
       </c>
-      <c r="K31" s="53" t="str">
+      <c r="K31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,E31-J31," ")</f>
         <v> </v>
       </c>
-      <c r="L31" s="53"/>
+      <c r="L31" s="50"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="68"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50" t="str">
+      <c r="N31" s="50"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="47"/>
+      <c r="R31" s="47" t="str">
         <f aca="false">IF(O31&gt;0,O31*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S31" s="50" t="str">
+      <c r="S31" s="47" t="str">
         <f aca="false">IF(O31&gt;0,O31-R31," ")</f>
         <v> </v>
       </c>
-      <c r="T31" s="50"/>
+      <c r="T31" s="47"/>
       <c r="U31" s="54"/>
       <c r="V31" s="57"/>
-      <c r="W31" s="53" t="str">
+      <c r="W31" s="50" t="str">
         <f aca="false">IF(V31&gt;0,E31," ")</f>
         <v> </v>
       </c>
-      <c r="X31" s="53" t="str">
+      <c r="X31" s="50" t="str">
         <f aca="false">IF(V31&gt;0,J31," ")</f>
         <v> </v>
       </c>
-      <c r="Y31" s="50" t="str">
+      <c r="Y31" s="47" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&lt;S31,S31-V31," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z31" s="50" t="str">
+      <c r="Z31" s="47" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&gt;S31,V31-S31," ")," ")</f>
         <v> </v>
       </c>
@@ -3293,7 +3328,7 @@
       <c r="D32" s="56"/>
       <c r="E32" s="57"/>
       <c r="F32" s="57"/>
-      <c r="G32" s="53" t="str">
+      <c r="G32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,E32-F32," ")</f>
         <v> </v>
       </c>
@@ -3301,48 +3336,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I32" s="53" t="str">
+      <c r="I32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,MIN(E32*H32,G32)," ")</f>
         <v> </v>
       </c>
-      <c r="J32" s="53" t="str">
+      <c r="J32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,F32+I32," ")</f>
         <v> </v>
       </c>
-      <c r="K32" s="53" t="str">
+      <c r="K32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,E32-J32," ")</f>
         <v> </v>
       </c>
-      <c r="L32" s="53"/>
+      <c r="L32" s="50"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="68"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50" t="str">
+      <c r="N32" s="50"/>
+      <c r="O32" s="67"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="47"/>
+      <c r="R32" s="47" t="str">
         <f aca="false">IF(O32&gt;0,O32*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S32" s="50" t="str">
+      <c r="S32" s="47" t="str">
         <f aca="false">IF(O32&gt;0,O32-R32," ")</f>
         <v> </v>
       </c>
-      <c r="T32" s="50"/>
+      <c r="T32" s="47"/>
       <c r="U32" s="54"/>
       <c r="V32" s="57"/>
-      <c r="W32" s="53" t="str">
+      <c r="W32" s="50" t="str">
         <f aca="false">IF(V32&gt;0,E32," ")</f>
         <v> </v>
       </c>
-      <c r="X32" s="53" t="str">
+      <c r="X32" s="50" t="str">
         <f aca="false">IF(V32&gt;0,J32," ")</f>
         <v> </v>
       </c>
-      <c r="Y32" s="50" t="str">
+      <c r="Y32" s="47" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&lt;S32,S32-V32," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z32" s="50" t="str">
+      <c r="Z32" s="47" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&gt;S32,V32-S32," ")," ")</f>
         <v> </v>
       </c>
@@ -3355,7 +3390,7 @@
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
       <c r="F33" s="57"/>
-      <c r="G33" s="53" t="str">
+      <c r="G33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
         <v> </v>
       </c>
@@ -3363,48 +3398,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="53" t="str">
+      <c r="I33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="53" t="str">
+      <c r="J33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="53" t="str">
+      <c r="K33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
         <v> </v>
       </c>
-      <c r="L33" s="53"/>
+      <c r="L33" s="50"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="68"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50" t="str">
+      <c r="N33" s="50"/>
+      <c r="O33" s="67"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="47"/>
+      <c r="R33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="50" t="str">
+      <c r="S33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="50"/>
+      <c r="T33" s="47"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="53" t="str">
+      <c r="W33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="53" t="str">
+      <c r="X33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="50" t="str">
+      <c r="Y33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="50" t="str">
+      <c r="Z33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3417,7 +3452,7 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="53" t="str">
+      <c r="G34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
         <v> </v>
       </c>
@@ -3425,48 +3460,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="53" t="str">
+      <c r="I34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="53" t="str">
+      <c r="J34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="53" t="str">
+      <c r="K34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
         <v> </v>
       </c>
-      <c r="L34" s="53"/>
+      <c r="L34" s="50"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="68"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="50" t="str">
+      <c r="N34" s="50"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="50" t="str">
+      <c r="S34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="50"/>
+      <c r="T34" s="47"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="53" t="str">
+      <c r="W34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="53" t="str">
+      <c r="X34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="50" t="str">
+      <c r="Y34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="50" t="str">
+      <c r="Z34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3475,38 +3510,38 @@
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="42"/>
       <c r="B35" s="59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="59"/>
       <c r="E35" s="60" t="n">
         <f aca="false">SUM(E30:E34)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F35" s="60" t="n">
         <f aca="false">SUM(F30:F34)</f>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="G35" s="61" t="n">
         <f aca="false">SUM(G30:G34)</f>
-        <v>0</v>
+        <v>2730</v>
       </c>
       <c r="H35" s="58"/>
       <c r="I35" s="61" t="n">
         <f aca="false">SUM(I30:I34)</f>
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J35" s="61" t="n">
         <f aca="false">SUM(J30:J34)</f>
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="K35" s="61" t="n">
         <f aca="false">SUM(K30:K34)</f>
-        <v>0</v>
-      </c>
-      <c r="L35" s="53"/>
+        <v>1740</v>
+      </c>
+      <c r="L35" s="50"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="53"/>
+      <c r="N35" s="50"/>
       <c r="O35" s="61" t="n">
         <f aca="false">SUM(O30:O34)</f>
         <v>0</v>
@@ -3524,8 +3559,8 @@
         <f aca="false">SUM(S30:S34)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="50"/>
-      <c r="U35" s="52"/>
+      <c r="T35" s="47"/>
+      <c r="U35" s="49"/>
       <c r="V35" s="60" t="n">
         <f aca="false">SUM(V30:V34)</f>
         <v>0</v>
@@ -3553,126 +3588,138 @@
       <c r="B36" s="63"/>
       <c r="C36" s="64"/>
       <c r="D36" s="65"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
       <c r="H36" s="58"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="50"/>
       <c r="P36" s="62"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="53"/>
-      <c r="W36" s="53"/>
-      <c r="X36" s="53"/>
-      <c r="Y36" s="53"/>
-      <c r="Z36" s="53"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="50"/>
+      <c r="S36" s="50"/>
+      <c r="T36" s="47"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="50"/>
+      <c r="W36" s="50"/>
+      <c r="X36" s="50"/>
+      <c r="Y36" s="50"/>
+      <c r="Z36" s="50"/>
       <c r="AA36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="42"/>
-      <c r="B37" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="70"/>
-      <c r="D37" s="71" t="n">
+      <c r="B37" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="67" t="n">
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="66" t="n">
         <f aca="false">[1]Admin!$G$17</f>
         <v>0.25</v>
       </c>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="72"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
       <c r="P37" s="62"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="73"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="53"/>
-      <c r="W37" s="53"/>
-      <c r="X37" s="53"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="53"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="50"/>
+      <c r="S37" s="50"/>
+      <c r="T37" s="72"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="50"/>
+      <c r="W37" s="50"/>
+      <c r="X37" s="50"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
       <c r="AA37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="42"/>
       <c r="B38" s="54"/>
-      <c r="C38" s="55"/>
+      <c r="C38" s="55" t="s">
+        <v>33</v>
+      </c>
       <c r="D38" s="56"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="53" t="str">
+      <c r="E38" s="57" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F38" s="57" t="n">
+        <v>9828</v>
+      </c>
+      <c r="G38" s="50" t="n">
         <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
-        <v> </v>
+        <v>20172</v>
       </c>
       <c r="H38" s="58" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I38" s="53" t="str">
+      <c r="I38" s="50" t="n">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J38" s="53" t="str">
+        <v>7500</v>
+      </c>
+      <c r="J38" s="50" t="n">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
-        <v> </v>
-      </c>
-      <c r="K38" s="53" t="str">
+        <v>17328</v>
+      </c>
+      <c r="K38" s="50" t="n">
         <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
-        <v> </v>
-      </c>
-      <c r="L38" s="53"/>
-      <c r="M38" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="53"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50" t="str">
+        <v>12672</v>
+      </c>
+      <c r="L38" s="50"/>
+      <c r="M38" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="50"/>
+      <c r="O38" s="67" t="n">
+        <v>24000</v>
+      </c>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47" t="n">
         <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
-        <v> </v>
-      </c>
-      <c r="S38" s="50" t="str">
+        <v>3000</v>
+      </c>
+      <c r="S38" s="47" t="n">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
-        <v> </v>
-      </c>
-      <c r="T38" s="50"/>
-      <c r="U38" s="54"/>
-      <c r="V38" s="57"/>
-      <c r="W38" s="53" t="str">
+        <v>21000</v>
+      </c>
+      <c r="T38" s="47"/>
+      <c r="U38" s="54" t="n">
+        <v>45940</v>
+      </c>
+      <c r="V38" s="57" t="n">
+        <v>12500</v>
+      </c>
+      <c r="W38" s="50" t="n">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
-        <v> </v>
-      </c>
-      <c r="X38" s="53" t="str">
+        <v>30000</v>
+      </c>
+      <c r="X38" s="50" t="n">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
-        <v> </v>
-      </c>
-      <c r="Y38" s="50" t="str">
+        <v>17328</v>
+      </c>
+      <c r="Y38" s="47" t="n">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
-        <v> </v>
-      </c>
-      <c r="Z38" s="50" t="str">
+        <v>8500</v>
+      </c>
+      <c r="Z38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
@@ -3685,7 +3732,7 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="53" t="str">
+      <c r="G39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
         <v> </v>
       </c>
@@ -3693,50 +3740,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I39" s="53" t="str">
+      <c r="I39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="53" t="str">
+      <c r="J39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="53" t="str">
+      <c r="K39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
         <v> </v>
       </c>
-      <c r="L39" s="53"/>
-      <c r="M39" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="53"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50" t="str">
+      <c r="L39" s="50"/>
+      <c r="M39" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="50"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="47"/>
+      <c r="R39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="50" t="str">
+      <c r="S39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="50"/>
+      <c r="T39" s="47"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="53" t="str">
+      <c r="W39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="53" t="str">
+      <c r="X39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="50" t="str">
+      <c r="Y39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,(S39-V39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="50" t="str">
+      <c r="Z39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,(V39-S39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
@@ -3749,7 +3796,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="53" t="str">
+      <c r="G40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
         <v> </v>
       </c>
@@ -3757,50 +3804,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I40" s="53" t="str">
+      <c r="I40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="53" t="str">
+      <c r="J40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="53" t="str">
+      <c r="K40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
         <v> </v>
       </c>
-      <c r="L40" s="53"/>
-      <c r="M40" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="53"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50" t="str">
+      <c r="L40" s="50"/>
+      <c r="M40" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="50"/>
+      <c r="O40" s="67"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="47"/>
+      <c r="R40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="50" t="str">
+      <c r="S40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="50"/>
+      <c r="T40" s="47"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="53" t="str">
+      <c r="W40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="53" t="str">
+      <c r="X40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="50" t="str">
+      <c r="Y40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,(S40-V40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="50" t="str">
+      <c r="Z40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,(V40-S40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
@@ -3813,7 +3860,7 @@
       <c r="D41" s="56"/>
       <c r="E41" s="57"/>
       <c r="F41" s="57"/>
-      <c r="G41" s="53" t="str">
+      <c r="G41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,E41-F41," ")</f>
         <v> </v>
       </c>
@@ -3821,50 +3868,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I41" s="53" t="str">
+      <c r="I41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,MIN(E41*H41,G41)," ")</f>
         <v> </v>
       </c>
-      <c r="J41" s="53" t="str">
+      <c r="J41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,F41+I41," ")</f>
         <v> </v>
       </c>
-      <c r="K41" s="53" t="str">
+      <c r="K41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,E41-J41," ")</f>
         <v> </v>
       </c>
-      <c r="L41" s="53"/>
-      <c r="M41" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="53"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50" t="str">
+      <c r="L41" s="50"/>
+      <c r="M41" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="50"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="47"/>
+      <c r="R41" s="47" t="str">
         <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
         <v> </v>
       </c>
-      <c r="S41" s="50" t="str">
+      <c r="S41" s="47" t="str">
         <f aca="false">IF(O41&gt;0,O41-R41," ")</f>
         <v> </v>
       </c>
-      <c r="T41" s="50"/>
+      <c r="T41" s="47"/>
       <c r="U41" s="54"/>
       <c r="V41" s="57"/>
-      <c r="W41" s="53" t="str">
+      <c r="W41" s="50" t="str">
         <f aca="false">IF(V41&gt;0,E41," ")</f>
         <v> </v>
       </c>
-      <c r="X41" s="53" t="str">
+      <c r="X41" s="50" t="str">
         <f aca="false">IF(V41&gt;0,J41," ")</f>
         <v> </v>
       </c>
-      <c r="Y41" s="50" t="str">
+      <c r="Y41" s="47" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&lt;S41,(S41-V41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z41" s="50" t="str">
+      <c r="Z41" s="47" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&gt;S41,(V41-S41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
@@ -3877,7 +3924,7 @@
       <c r="D42" s="56"/>
       <c r="E42" s="57"/>
       <c r="F42" s="57"/>
-      <c r="G42" s="53" t="str">
+      <c r="G42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,E42-F42," ")</f>
         <v> </v>
       </c>
@@ -3885,50 +3932,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I42" s="53" t="str">
+      <c r="I42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,MIN(E42*H42,G42)," ")</f>
         <v> </v>
       </c>
-      <c r="J42" s="53" t="str">
+      <c r="J42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,F42+I42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="53" t="str">
+      <c r="K42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,E42-J42," ")</f>
         <v> </v>
       </c>
-      <c r="L42" s="53"/>
-      <c r="M42" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="53"/>
-      <c r="O42" s="68"/>
-      <c r="P42" s="51"/>
-      <c r="Q42" s="50"/>
-      <c r="R42" s="50" t="str">
+      <c r="L42" s="50"/>
+      <c r="M42" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="50"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="48"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47" t="str">
         <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
         <v> </v>
       </c>
-      <c r="S42" s="50" t="str">
+      <c r="S42" s="47" t="str">
         <f aca="false">IF(O42&gt;0,O42-R42," ")</f>
         <v> </v>
       </c>
-      <c r="T42" s="50"/>
+      <c r="T42" s="47"/>
       <c r="U42" s="54"/>
       <c r="V42" s="57"/>
-      <c r="W42" s="53" t="str">
+      <c r="W42" s="50" t="str">
         <f aca="false">IF(V42&gt;0,E42," ")</f>
         <v> </v>
       </c>
-      <c r="X42" s="53" t="str">
+      <c r="X42" s="50" t="str">
         <f aca="false">IF(V42&gt;0,J42," ")</f>
         <v> </v>
       </c>
-      <c r="Y42" s="50" t="str">
+      <c r="Y42" s="47" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&lt;S42,(S42-V42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z42" s="50" t="str">
+      <c r="Z42" s="47" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&gt;S42,(V42-S42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
@@ -3936,36 +3983,36 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="71" t="n">
+      <c r="B43" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="69"/>
+      <c r="D43" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
       <c r="H43" s="58"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
       <c r="M43" s="58"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="53"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="47"/>
+      <c r="P43" s="48"/>
+      <c r="Q43" s="47"/>
+      <c r="R43" s="47"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="47"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="50"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="47"/>
+      <c r="Z43" s="47"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3975,7 +4022,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="53" t="str">
+      <c r="G44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
         <v> </v>
       </c>
@@ -3983,50 +4030,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="53" t="str">
+      <c r="I44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="53" t="str">
+      <c r="J44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="53" t="str">
+      <c r="K44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
         <v> </v>
       </c>
-      <c r="L44" s="53"/>
-      <c r="M44" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="53"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50" t="str">
+      <c r="L44" s="50"/>
+      <c r="M44" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="50"/>
+      <c r="O44" s="67"/>
+      <c r="P44" s="48"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="50" t="str">
+      <c r="S44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="50"/>
+      <c r="T44" s="47"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="53" t="str">
+      <c r="W44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="53" t="str">
+      <c r="X44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="50" t="str">
+      <c r="Y44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="50" t="str">
+      <c r="Z44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -4039,7 +4086,7 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="53" t="str">
+      <c r="G45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
         <v> </v>
       </c>
@@ -4047,50 +4094,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="53" t="str">
+      <c r="I45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="53" t="str">
+      <c r="J45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="53" t="str">
+      <c r="K45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
         <v> </v>
       </c>
-      <c r="L45" s="53"/>
-      <c r="M45" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="53"/>
-      <c r="O45" s="68"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50" t="str">
+      <c r="L45" s="50"/>
+      <c r="M45" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="50"/>
+      <c r="O45" s="67"/>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="50" t="str">
+      <c r="S45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="50"/>
+      <c r="T45" s="47"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="53" t="str">
+      <c r="W45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="53" t="str">
+      <c r="X45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="50" t="str">
+      <c r="Y45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="50" t="str">
+      <c r="Z45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -4103,7 +4150,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="53" t="str">
+      <c r="G46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -4111,50 +4158,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="53" t="str">
+      <c r="I46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="53" t="str">
+      <c r="J46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="53" t="str">
+      <c r="K46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
         <v> </v>
       </c>
-      <c r="L46" s="53"/>
-      <c r="M46" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="53"/>
-      <c r="O46" s="68"/>
-      <c r="P46" s="51"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50" t="str">
+      <c r="L46" s="50"/>
+      <c r="M46" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="50"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="47"/>
+      <c r="R46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="50" t="str">
+      <c r="S46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="50"/>
+      <c r="T46" s="47"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="53" t="str">
+      <c r="W46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="53" t="str">
+      <c r="X46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="50" t="str">
+      <c r="Y46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="50" t="str">
+      <c r="Z46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -4167,7 +4214,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="53" t="str">
+      <c r="G47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -4175,50 +4222,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="53" t="str">
+      <c r="I47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="53" t="str">
+      <c r="J47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="53" t="str">
+      <c r="K47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
         <v> </v>
       </c>
-      <c r="L47" s="53"/>
-      <c r="M47" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="53"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="51"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50" t="str">
+      <c r="L47" s="50"/>
+      <c r="M47" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="50"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="48"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="50" t="str">
+      <c r="S47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="50"/>
+      <c r="T47" s="47"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="53" t="str">
+      <c r="W47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="53" t="str">
+      <c r="X47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="50" t="str">
+      <c r="Y47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="50" t="str">
+      <c r="Z47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4231,7 +4278,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="53" t="str">
+      <c r="G48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4239,50 +4286,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="53" t="str">
+      <c r="I48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="53" t="str">
+      <c r="J48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="53" t="str">
+      <c r="K48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
         <v> </v>
       </c>
-      <c r="L48" s="53"/>
-      <c r="M48" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="53"/>
-      <c r="O48" s="68"/>
-      <c r="P48" s="51"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50" t="str">
+      <c r="L48" s="50"/>
+      <c r="M48" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="50"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="48"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="50" t="str">
+      <c r="S48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="50"/>
+      <c r="T48" s="47"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="53" t="str">
+      <c r="W48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="53" t="str">
+      <c r="X48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="50" t="str">
+      <c r="Y48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="50" t="str">
+      <c r="Z48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4290,33 +4337,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="66"/>
+      <c r="B49" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="51"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="50"/>
+      <c r="L49" s="50"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="51"/>
-      <c r="Q49" s="50"/>
-      <c r="R49" s="50"/>
-      <c r="S49" s="50"/>
-      <c r="T49" s="50"/>
-      <c r="U49" s="52"/>
-      <c r="V49" s="53"/>
-      <c r="W49" s="53"/>
-      <c r="X49" s="53"/>
-      <c r="Y49" s="50"/>
-      <c r="Z49" s="50"/>
+      <c r="N49" s="50"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="47"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="47"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="50"/>
+      <c r="W49" s="50"/>
+      <c r="X49" s="50"/>
+      <c r="Y49" s="47"/>
+      <c r="Z49" s="47"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4326,7 +4373,7 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="53" t="str">
+      <c r="G50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
         <v> </v>
       </c>
@@ -4334,50 +4381,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="53" t="str">
+      <c r="I50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="53" t="str">
+      <c r="J50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="53" t="str">
+      <c r="K50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
         <v> </v>
       </c>
-      <c r="L50" s="53"/>
-      <c r="M50" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="53"/>
-      <c r="O50" s="68"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="50"/>
-      <c r="R50" s="50" t="str">
+      <c r="L50" s="50"/>
+      <c r="M50" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="50"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,O50*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="50" t="str">
+      <c r="S50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="50"/>
+      <c r="T50" s="47"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="53" t="str">
+      <c r="W50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="53" t="str">
+      <c r="X50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="50" t="str">
+      <c r="Y50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="50" t="str">
+      <c r="Z50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4390,7 +4437,7 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="53" t="str">
+      <c r="G51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
         <v> </v>
       </c>
@@ -4398,50 +4445,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="53" t="str">
+      <c r="I51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="53" t="str">
+      <c r="J51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="53" t="str">
+      <c r="K51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
         <v> </v>
       </c>
-      <c r="L51" s="53"/>
-      <c r="M51" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="53"/>
-      <c r="O51" s="68"/>
-      <c r="P51" s="51"/>
-      <c r="Q51" s="50"/>
-      <c r="R51" s="50" t="str">
+      <c r="L51" s="50"/>
+      <c r="M51" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="50"/>
+      <c r="O51" s="67"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,O51*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="50" t="str">
+      <c r="S51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="50"/>
+      <c r="T51" s="47"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="53" t="str">
+      <c r="W51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="53" t="str">
+      <c r="X51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="50" t="str">
+      <c r="Y51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="50" t="str">
+      <c r="Z51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4454,7 +4501,7 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="53" t="str">
+      <c r="G52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
         <v> </v>
       </c>
@@ -4462,50 +4509,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="53" t="str">
+      <c r="I52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="53" t="str">
+      <c r="J52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="53" t="str">
+      <c r="K52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
         <v> </v>
       </c>
-      <c r="L52" s="53"/>
-      <c r="M52" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="53"/>
-      <c r="O52" s="68"/>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="50"/>
-      <c r="R52" s="50" t="str">
+      <c r="L52" s="50"/>
+      <c r="M52" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="50"/>
+      <c r="O52" s="67"/>
+      <c r="P52" s="48"/>
+      <c r="Q52" s="47"/>
+      <c r="R52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,O52*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="50" t="str">
+      <c r="S52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="50"/>
+      <c r="T52" s="47"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="53" t="str">
+      <c r="W52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="53" t="str">
+      <c r="X52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="50" t="str">
+      <c r="Y52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="50" t="str">
+      <c r="Z52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4518,7 +4565,7 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="53" t="str">
+      <c r="G53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
         <v> </v>
       </c>
@@ -4526,50 +4573,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="53" t="str">
+      <c r="I53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="53" t="str">
+      <c r="J53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="53" t="str">
+      <c r="K53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
         <v> </v>
       </c>
-      <c r="L53" s="53"/>
-      <c r="M53" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="53"/>
-      <c r="O53" s="68"/>
-      <c r="P53" s="51"/>
-      <c r="Q53" s="50"/>
-      <c r="R53" s="50" t="str">
+      <c r="L53" s="50"/>
+      <c r="M53" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="50"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="47"/>
+      <c r="R53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,O53*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="50" t="str">
+      <c r="S53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="50"/>
+      <c r="T53" s="47"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="53" t="str">
+      <c r="W53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="53" t="str">
+      <c r="X53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="50" t="str">
+      <c r="Y53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="50" t="str">
+      <c r="Z53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4582,7 +4629,7 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="53" t="str">
+      <c r="G54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
         <v> </v>
       </c>
@@ -4590,50 +4637,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="53" t="str">
+      <c r="I54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="53" t="str">
+      <c r="J54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="53" t="str">
+      <c r="K54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
         <v> </v>
       </c>
-      <c r="L54" s="53"/>
-      <c r="M54" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="53"/>
-      <c r="O54" s="68"/>
-      <c r="P54" s="51"/>
-      <c r="Q54" s="50"/>
-      <c r="R54" s="50" t="str">
+      <c r="L54" s="50"/>
+      <c r="M54" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="50"/>
+      <c r="O54" s="67"/>
+      <c r="P54" s="48"/>
+      <c r="Q54" s="47"/>
+      <c r="R54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,O54*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="50" t="str">
+      <c r="S54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="50"/>
+      <c r="T54" s="47"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="53" t="str">
+      <c r="W54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="53" t="str">
+      <c r="X54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="50" t="str">
+      <c r="Y54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="50" t="str">
+      <c r="Z54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4642,41 +4689,41 @@
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="42"/>
       <c r="B55" s="59" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C55" s="59"/>
       <c r="D55" s="59"/>
       <c r="E55" s="61" t="n">
         <f aca="false">SUM(E38:E54)</f>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F55" s="61" t="n">
         <f aca="false">SUM(F38:F54)</f>
-        <v>0</v>
+        <v>9828</v>
       </c>
       <c r="G55" s="61" t="n">
         <f aca="false">SUM(G38:G54)</f>
-        <v>0</v>
+        <v>20172</v>
       </c>
       <c r="H55" s="58"/>
       <c r="I55" s="61" t="n">
         <f aca="false">SUM(I38:I54)</f>
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="J55" s="61" t="n">
         <f aca="false">SUM(J38:J54)</f>
-        <v>0</v>
+        <v>17328</v>
       </c>
       <c r="K55" s="61" t="n">
         <f aca="false">SUM(K38:K54)</f>
-        <v>0</v>
-      </c>
-      <c r="L55" s="53"/>
-      <c r="M55" s="72"/>
-      <c r="N55" s="53"/>
+        <v>12672</v>
+      </c>
+      <c r="L55" s="50"/>
+      <c r="M55" s="71"/>
+      <c r="N55" s="50"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O38:O54)</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="P55" s="62"/>
       <c r="Q55" s="61" t="n">
@@ -4685,29 +4732,29 @@
       </c>
       <c r="R55" s="61" t="n">
         <f aca="false">SUM(R38:R54)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="S55" s="61" t="n">
         <f aca="false">SUM(S38:S54)</f>
-        <v>0</v>
-      </c>
-      <c r="T55" s="53"/>
-      <c r="U55" s="52"/>
+        <v>21000</v>
+      </c>
+      <c r="T55" s="50"/>
+      <c r="U55" s="49"/>
       <c r="V55" s="61" t="n">
         <f aca="false">SUM(V38:V54)</f>
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="W55" s="61" t="n">
         <f aca="false">SUM(W38:W54)</f>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="X55" s="61" t="n">
         <f aca="false">SUM(X38:X54)</f>
-        <v>0</v>
+        <v>17328</v>
       </c>
       <c r="Y55" s="61" t="n">
         <f aca="false">SUM(Y38:Y54)</f>
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="Z55" s="61" t="n">
         <f aca="false">SUM(Z38:Z54)</f>
@@ -4717,31 +4764,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="74"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="73"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="50"/>
+      <c r="L56" s="50"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="50"/>
-      <c r="P56" s="51"/>
-      <c r="Q56" s="50"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="50"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="52"/>
-      <c r="V56" s="53"/>
-      <c r="W56" s="50"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="50"/>
-      <c r="Z56" s="50"/>
+      <c r="N56" s="50"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="48"/>
+      <c r="Q56" s="47"/>
+      <c r="R56" s="47"/>
+      <c r="S56" s="47"/>
+      <c r="T56" s="47"/>
+      <c r="U56" s="49"/>
+      <c r="V56" s="50"/>
+      <c r="W56" s="47"/>
+      <c r="X56" s="47"/>
+      <c r="Y56" s="47"/>
+      <c r="Z56" s="47"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4751,74 +4798,74 @@
         <v>EXISTING FIXED ASSETS at </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="44" t="str">
+      <c r="D57" s="44" t="n">
         <f aca="false">D6</f>
-        <v>Laptop (0.5 years old)</v>
-      </c>
-      <c r="E57" s="75" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E57" s="74" t="n">
         <f aca="false">E11+E19+E27+E35+E55</f>
-        <v>0</v>
-      </c>
-      <c r="F57" s="75" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F57" s="74" t="n">
         <f aca="false">F11+F19+F27+F35+F55</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="75" t="n">
+        <v>10098</v>
+      </c>
+      <c r="G57" s="74" t="n">
         <f aca="false">G11+G19+G27+G35+G55</f>
-        <v>0</v>
+        <v>22902</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="75" t="n">
+      <c r="I57" s="74" t="n">
         <f aca="false">I11+I19+I27+I35+I55</f>
-        <v>0</v>
-      </c>
-      <c r="J57" s="75" t="n">
+        <v>8490</v>
+      </c>
+      <c r="J57" s="74" t="n">
         <f aca="false">J11+J19+J27+J35+J55</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="75" t="n">
+        <v>18588</v>
+      </c>
+      <c r="K57" s="74" t="n">
         <f aca="false">K11+K19+K27+K35+K55</f>
-        <v>0</v>
-      </c>
-      <c r="L57" s="53"/>
+        <v>14412</v>
+      </c>
+      <c r="L57" s="50"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="75" t="n">
+      <c r="N57" s="50"/>
+      <c r="O57" s="74" t="n">
         <f aca="false">O11+O19+O27+O35+O55</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="75" t="n">
+      <c r="Q57" s="74" t="n">
         <f aca="false">Q11+Q19+Q27+Q35+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="75" t="n">
+      <c r="R57" s="74" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
-        <v>0</v>
-      </c>
-      <c r="S57" s="75" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S57" s="74" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
-        <v>0</v>
-      </c>
-      <c r="T57" s="50"/>
-      <c r="U57" s="52"/>
-      <c r="V57" s="75" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T57" s="47"/>
+      <c r="U57" s="49"/>
+      <c r="V57" s="74" t="n">
         <f aca="false">V11+V19+V27+V35+V55</f>
-        <v>0</v>
-      </c>
-      <c r="W57" s="75" t="n">
+        <v>12500</v>
+      </c>
+      <c r="W57" s="74" t="n">
         <f aca="false">W11+W19+W27+W35+W55</f>
-        <v>0</v>
-      </c>
-      <c r="X57" s="75" t="n">
+        <v>30000</v>
+      </c>
+      <c r="X57" s="74" t="n">
         <f aca="false">X11+X19+X27+X35+X55</f>
-        <v>0</v>
-      </c>
-      <c r="Y57" s="75" t="n">
+        <v>17328</v>
+      </c>
+      <c r="Y57" s="74" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
-        <v>0</v>
-      </c>
-      <c r="Z57" s="75" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Z57" s="74" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
         <v>0</v>
       </c>
@@ -4826,78 +4873,78 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="76"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="78"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="53"/>
-      <c r="K58" s="53"/>
-      <c r="L58" s="53"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="50"/>
+      <c r="L58" s="50"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="53"/>
-      <c r="O58" s="50"/>
-      <c r="P58" s="51"/>
-      <c r="Q58" s="50"/>
-      <c r="R58" s="50"/>
-      <c r="S58" s="50"/>
-      <c r="T58" s="50"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="53"/>
-      <c r="W58" s="53"/>
-      <c r="X58" s="53"/>
-      <c r="Y58" s="50"/>
-      <c r="Z58" s="50"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="47"/>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="47"/>
+      <c r="R58" s="47"/>
+      <c r="S58" s="47"/>
+      <c r="T58" s="47"/>
+      <c r="U58" s="49"/>
+      <c r="V58" s="50"/>
+      <c r="W58" s="50"/>
+      <c r="X58" s="50"/>
+      <c r="Y58" s="47"/>
+      <c r="Z58" s="47"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
       <c r="B59" s="43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
-      </c>
-      <c r="E59" s="50"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
+        <v>46118</v>
+      </c>
+      <c r="E59" s="47"/>
+      <c r="F59" s="78"/>
+      <c r="G59" s="78"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="47"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="51"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="53"/>
-      <c r="W59" s="53"/>
-      <c r="X59" s="53"/>
-      <c r="Y59" s="50"/>
-      <c r="Z59" s="50"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="47"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="47"/>
+      <c r="R59" s="47"/>
+      <c r="S59" s="47"/>
+      <c r="T59" s="47"/>
+      <c r="U59" s="49"/>
+      <c r="V59" s="50"/>
+      <c r="W59" s="50"/>
+      <c r="X59" s="50"/>
+      <c r="Y59" s="47"/>
+      <c r="Z59" s="47"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="C60" s="66"/>
-      <c r="D60" s="47"/>
+      <c r="B60" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="51"/>
+      <c r="D60" s="52"/>
       <c r="E60" s="45"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
-      <c r="H60" s="80" t="n">
+      <c r="F60" s="78"/>
+      <c r="G60" s="78"/>
+      <c r="H60" s="79" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
@@ -4907,165 +4954,165 @@
       <c r="L60" s="45"/>
       <c r="M60" s="58"/>
       <c r="N60" s="45"/>
-      <c r="O60" s="50"/>
-      <c r="P60" s="51"/>
-      <c r="Q60" s="50"/>
-      <c r="R60" s="50"/>
-      <c r="S60" s="50"/>
-      <c r="T60" s="50"/>
-      <c r="U60" s="52"/>
-      <c r="V60" s="53"/>
-      <c r="W60" s="53"/>
-      <c r="X60" s="53"/>
-      <c r="Y60" s="50"/>
-      <c r="Z60" s="50"/>
+      <c r="O60" s="47"/>
+      <c r="P60" s="48"/>
+      <c r="Q60" s="47"/>
+      <c r="R60" s="47"/>
+      <c r="S60" s="47"/>
+      <c r="T60" s="47"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="50"/>
+      <c r="W60" s="50"/>
+      <c r="X60" s="50"/>
+      <c r="Y60" s="47"/>
+      <c r="Z60" s="47"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="81"/>
+      <c r="D61" s="80"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
+      <c r="F61" s="50"/>
+      <c r="G61" s="50"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="53" t="str">
+      <c r="I61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="53" t="str">
+      <c r="J61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="53" t="str">
+      <c r="K61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
         <v> </v>
       </c>
-      <c r="L61" s="53"/>
+      <c r="L61" s="50"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="53"/>
-      <c r="O61" s="50"/>
-      <c r="P61" s="51"/>
-      <c r="Q61" s="50"/>
-      <c r="R61" s="50"/>
-      <c r="S61" s="50"/>
-      <c r="T61" s="50"/>
+      <c r="N61" s="50"/>
+      <c r="O61" s="47"/>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="47"/>
+      <c r="R61" s="47"/>
+      <c r="S61" s="47"/>
+      <c r="T61" s="47"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="53" t="str">
+      <c r="W61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="53" t="str">
+      <c r="X61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="50"/>
-      <c r="Z61" s="50"/>
+      <c r="Y61" s="47"/>
+      <c r="Z61" s="47"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="81"/>
+      <c r="D62" s="80"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="53"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="50"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="53" t="str">
+      <c r="I62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="53" t="str">
+      <c r="J62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="53" t="str">
+      <c r="K62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
         <v> </v>
       </c>
-      <c r="L62" s="53"/>
+      <c r="L62" s="50"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="53"/>
-      <c r="O62" s="50"/>
-      <c r="P62" s="51"/>
-      <c r="Q62" s="50"/>
-      <c r="R62" s="50"/>
-      <c r="S62" s="50"/>
-      <c r="T62" s="50"/>
+      <c r="N62" s="50"/>
+      <c r="O62" s="47"/>
+      <c r="P62" s="48"/>
+      <c r="Q62" s="47"/>
+      <c r="R62" s="47"/>
+      <c r="S62" s="47"/>
+      <c r="T62" s="47"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="53" t="str">
+      <c r="W62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="53" t="str">
+      <c r="X62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="50"/>
-      <c r="Z62" s="50"/>
+      <c r="Y62" s="47"/>
+      <c r="Z62" s="47"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="81"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="53" t="str">
+      <c r="I63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="53" t="str">
+      <c r="J63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="53" t="str">
+      <c r="K63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
         <v> </v>
       </c>
-      <c r="L63" s="53"/>
+      <c r="L63" s="50"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="53"/>
-      <c r="O63" s="50"/>
-      <c r="P63" s="51"/>
-      <c r="Q63" s="50"/>
-      <c r="R63" s="50"/>
-      <c r="S63" s="50"/>
-      <c r="T63" s="50"/>
+      <c r="N63" s="50"/>
+      <c r="O63" s="47"/>
+      <c r="P63" s="48"/>
+      <c r="Q63" s="47"/>
+      <c r="R63" s="47"/>
+      <c r="S63" s="47"/>
+      <c r="T63" s="47"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="53" t="str">
+      <c r="W63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="53" t="str">
+      <c r="X63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="50"/>
-      <c r="Z63" s="50"/>
+      <c r="Y63" s="47"/>
+      <c r="Z63" s="47"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -5094,14 +5141,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="53"/>
+      <c r="L64" s="50"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="53"/>
+      <c r="N64" s="50"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="82"/>
+      <c r="P64" s="81"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -5114,8 +5161,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="50"/>
-      <c r="U64" s="52"/>
+      <c r="T64" s="47"/>
+      <c r="U64" s="49"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -5143,121 +5190,127 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="53"/>
-      <c r="F65" s="53"/>
-      <c r="G65" s="53"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="53"/>
-      <c r="J65" s="53"/>
-      <c r="K65" s="53"/>
-      <c r="L65" s="53"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="50"/>
+      <c r="L65" s="50"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="53"/>
-      <c r="O65" s="53"/>
+      <c r="N65" s="50"/>
+      <c r="O65" s="50"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="53"/>
-      <c r="R65" s="53"/>
-      <c r="S65" s="53"/>
-      <c r="T65" s="50"/>
-      <c r="U65" s="52"/>
-      <c r="V65" s="53"/>
-      <c r="W65" s="53"/>
-      <c r="X65" s="53"/>
-      <c r="Y65" s="53"/>
-      <c r="Z65" s="53"/>
+      <c r="Q65" s="50"/>
+      <c r="R65" s="50"/>
+      <c r="S65" s="50"/>
+      <c r="T65" s="47"/>
+      <c r="U65" s="49"/>
+      <c r="V65" s="50"/>
+      <c r="W65" s="50"/>
+      <c r="X65" s="50"/>
+      <c r="Y65" s="50"/>
+      <c r="Z65" s="50"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="66" t="s">
+      <c r="B66" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="66"/>
+      <c r="C66" s="51"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="53"/>
-      <c r="F66" s="53"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="83" t="n">
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="82" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="53"/>
-      <c r="J66" s="53"/>
-      <c r="K66" s="53"/>
-      <c r="L66" s="53"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="50"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="53"/>
-      <c r="O66" s="50"/>
-      <c r="P66" s="51"/>
-      <c r="Q66" s="50"/>
-      <c r="R66" s="50"/>
-      <c r="S66" s="50"/>
-      <c r="T66" s="50"/>
-      <c r="U66" s="52"/>
-      <c r="V66" s="53"/>
-      <c r="W66" s="53"/>
-      <c r="X66" s="53"/>
-      <c r="Y66" s="50"/>
-      <c r="Z66" s="50"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="47"/>
+      <c r="S66" s="47"/>
+      <c r="T66" s="47"/>
+      <c r="U66" s="49"/>
+      <c r="V66" s="50"/>
+      <c r="W66" s="50"/>
+      <c r="X66" s="50"/>
+      <c r="Y66" s="47"/>
+      <c r="Z66" s="47"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42"/>
-      <c r="B67" s="54"/>
-      <c r="C67" s="55"/>
+      <c r="B67" s="54" t="n">
+        <v>45792</v>
+      </c>
+      <c r="C67" s="55" t="s">
+        <v>39</v>
+      </c>
       <c r="D67" s="56"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
+      <c r="E67" s="57" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="53" t="str">
+      <c r="I67" s="50" t="n">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J67" s="53" t="str">
+        <v>150</v>
+      </c>
+      <c r="J67" s="50" t="n">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
-        <v> </v>
-      </c>
-      <c r="K67" s="53" t="str">
+        <v>150</v>
+      </c>
+      <c r="K67" s="50" t="n">
         <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
-        <v> </v>
-      </c>
-      <c r="L67" s="53"/>
+        <v>1350</v>
+      </c>
+      <c r="L67" s="50"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="53"/>
-      <c r="O67" s="50"/>
+      <c r="N67" s="50"/>
+      <c r="O67" s="47"/>
       <c r="P67" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q67" s="50" t="str">
+      <c r="Q67" s="47" t="n">
         <f aca="false">IF(E67&gt;0,E67*P67," ")</f>
-        <v> </v>
-      </c>
-      <c r="R67" s="50"/>
-      <c r="S67" s="50" t="str">
+        <v>1500</v>
+      </c>
+      <c r="R67" s="47"/>
+      <c r="S67" s="47" t="n">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
-        <v> </v>
-      </c>
-      <c r="T67" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="T67" s="47"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="53" t="str">
+      <c r="W67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="53" t="str">
+      <c r="X67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="50" t="str">
+      <c r="Y67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="50" t="str">
+      <c r="Z67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5265,61 +5318,67 @@
     </row>
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
-      <c r="B68" s="54"/>
-      <c r="C68" s="55"/>
+      <c r="B68" s="54" t="n">
+        <v>45853</v>
+      </c>
+      <c r="C68" s="55" t="s">
+        <v>40</v>
+      </c>
       <c r="D68" s="56"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="53"/>
-      <c r="G68" s="53"/>
+      <c r="E68" s="57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F68" s="50"/>
+      <c r="G68" s="50"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="53" t="str">
+      <c r="I68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J68" s="53" t="str">
+        <v>100</v>
+      </c>
+      <c r="J68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
-        <v> </v>
-      </c>
-      <c r="K68" s="53" t="str">
+        <v>100</v>
+      </c>
+      <c r="K68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
-        <v> </v>
-      </c>
-      <c r="L68" s="53"/>
+        <v>900</v>
+      </c>
+      <c r="L68" s="50"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="53"/>
-      <c r="O68" s="50"/>
+      <c r="N68" s="50"/>
+      <c r="O68" s="47"/>
       <c r="P68" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q68" s="50" t="str">
+      <c r="Q68" s="47" t="n">
         <f aca="false">IF(E68&gt;0,E68*P68," ")</f>
-        <v> </v>
-      </c>
-      <c r="R68" s="50"/>
-      <c r="S68" s="50" t="str">
+        <v>1000</v>
+      </c>
+      <c r="R68" s="47"/>
+      <c r="S68" s="47" t="n">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
-        <v> </v>
-      </c>
-      <c r="T68" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="T68" s="47"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="53" t="str">
+      <c r="W68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="53" t="str">
+      <c r="X68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="50" t="str">
+      <c r="Y68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="50" t="str">
+      <c r="Z68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5327,61 +5386,67 @@
     </row>
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
-      <c r="B69" s="54"/>
-      <c r="C69" s="55"/>
+      <c r="B69" s="54" t="n">
+        <v>45955</v>
+      </c>
+      <c r="C69" s="55" t="s">
+        <v>41</v>
+      </c>
       <c r="D69" s="56"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
+      <c r="E69" s="57" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="53" t="str">
+      <c r="I69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J69" s="53" t="str">
+        <v>3000</v>
+      </c>
+      <c r="J69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
-        <v> </v>
-      </c>
-      <c r="K69" s="53" t="str">
+        <v>3000</v>
+      </c>
+      <c r="K69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
-        <v> </v>
-      </c>
-      <c r="L69" s="53"/>
+        <v>27000</v>
+      </c>
+      <c r="L69" s="50"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="53"/>
-      <c r="O69" s="50"/>
+      <c r="N69" s="50"/>
+      <c r="O69" s="47"/>
       <c r="P69" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q69" s="50" t="str">
+      <c r="Q69" s="47" t="n">
         <f aca="false">IF(E69&gt;0,E69*P69," ")</f>
-        <v> </v>
-      </c>
-      <c r="R69" s="50"/>
-      <c r="S69" s="50" t="str">
+        <v>30000</v>
+      </c>
+      <c r="R69" s="47"/>
+      <c r="S69" s="47" t="n">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
-        <v> </v>
-      </c>
-      <c r="T69" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="T69" s="47"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="53" t="str">
+      <c r="W69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="53" t="str">
+      <c r="X69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="50" t="str">
+      <c r="Y69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="50" t="str">
+      <c r="Z69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5393,57 +5458,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="53"/>
-      <c r="G70" s="53"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="53" t="str">
+      <c r="I70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="53" t="str">
+      <c r="J70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="53" t="str">
+      <c r="K70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
         <v> </v>
       </c>
-      <c r="L70" s="53"/>
+      <c r="L70" s="50"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="53"/>
-      <c r="O70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="47"/>
       <c r="P70" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="50" t="str">
+      <c r="Q70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="50"/>
-      <c r="S70" s="50" t="str">
+      <c r="R70" s="47"/>
+      <c r="S70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="50"/>
+      <c r="T70" s="47"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="53" t="str">
+      <c r="W70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="53" t="str">
+      <c r="X70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="50" t="str">
+      <c r="Y70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="50" t="str">
+      <c r="Z70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5455,57 +5520,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="53"/>
-      <c r="G71" s="53"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="53" t="str">
+      <c r="I71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="53" t="str">
+      <c r="J71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="53" t="str">
+      <c r="K71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
         <v> </v>
       </c>
-      <c r="L71" s="53"/>
+      <c r="L71" s="50"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="50"/>
+      <c r="N71" s="50"/>
+      <c r="O71" s="47"/>
       <c r="P71" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q71" s="50" t="str">
+      <c r="Q71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="50"/>
-      <c r="S71" s="50" t="str">
+      <c r="R71" s="47"/>
+      <c r="S71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="50"/>
+      <c r="T71" s="47"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="53" t="str">
+      <c r="W71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="53" t="str">
+      <c r="X71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="50" t="str">
+      <c r="Y71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="50" t="str">
+      <c r="Z71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5514,13 +5579,13 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="42"/>
       <c r="B72" s="59" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
       <c r="E72" s="60" t="n">
         <f aca="false">SUM(E67:E71)</f>
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="F72" s="61" t="n">
         <f aca="false">SUM(F67:F71)</f>
@@ -5533,19 +5598,19 @@
       <c r="H72" s="58"/>
       <c r="I72" s="61" t="n">
         <f aca="false">SUM(I67:I71)</f>
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="J72" s="61" t="n">
         <f aca="false">SUM(J67:J71)</f>
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="K72" s="61" t="n">
         <f aca="false">SUM(K67:K71)</f>
-        <v>0</v>
-      </c>
-      <c r="L72" s="53"/>
+        <v>29250</v>
+      </c>
+      <c r="L72" s="50"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="53"/>
+      <c r="N72" s="50"/>
       <c r="O72" s="61" t="n">
         <f aca="false">SUM(O67:O71)</f>
         <v>0</v>
@@ -5553,7 +5618,7 @@
       <c r="P72" s="62"/>
       <c r="Q72" s="61" t="n">
         <f aca="false">SUM(Q67:Q71)</f>
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="R72" s="61" t="n">
         <f aca="false">SUM(R67:R71)</f>
@@ -5563,8 +5628,8 @@
         <f aca="false">SUM(S67:S71)</f>
         <v>0</v>
       </c>
-      <c r="T72" s="50"/>
-      <c r="U72" s="52"/>
+      <c r="T72" s="47"/>
+      <c r="U72" s="49"/>
       <c r="V72" s="60" t="n">
         <f aca="false">SUM(V67:V71)</f>
         <v>0</v>
@@ -5592,121 +5657,121 @@
       <c r="B73" s="63"/>
       <c r="C73" s="64"/>
       <c r="D73" s="65"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
       <c r="H73" s="58"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-      <c r="L73" s="53"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="50"/>
+      <c r="K73" s="50"/>
+      <c r="L73" s="50"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="53"/>
-      <c r="O73" s="53"/>
+      <c r="N73" s="50"/>
+      <c r="O73" s="50"/>
       <c r="P73" s="62"/>
-      <c r="Q73" s="53"/>
-      <c r="R73" s="53"/>
-      <c r="S73" s="53"/>
-      <c r="T73" s="50"/>
-      <c r="U73" s="52"/>
-      <c r="V73" s="53"/>
-      <c r="W73" s="53"/>
-      <c r="X73" s="53"/>
-      <c r="Y73" s="53"/>
-      <c r="Z73" s="53"/>
+      <c r="Q73" s="50"/>
+      <c r="R73" s="50"/>
+      <c r="S73" s="50"/>
+      <c r="T73" s="47"/>
+      <c r="U73" s="49"/>
+      <c r="V73" s="50"/>
+      <c r="W73" s="50"/>
+      <c r="X73" s="50"/>
+      <c r="Y73" s="50"/>
+      <c r="Z73" s="50"/>
       <c r="AA73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="42"/>
-      <c r="B74" s="66" t="s">
+      <c r="B74" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="66"/>
+      <c r="C74" s="51"/>
       <c r="D74" s="62"/>
-      <c r="E74" s="53"/>
-      <c r="F74" s="53"/>
-      <c r="G74" s="53"/>
-      <c r="H74" s="83" t="n">
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="82" t="n">
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I74" s="53"/>
-      <c r="J74" s="53"/>
-      <c r="K74" s="53"/>
-      <c r="L74" s="53"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="K74" s="50"/>
+      <c r="L74" s="50"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="53"/>
-      <c r="O74" s="50"/>
-      <c r="P74" s="51"/>
-      <c r="Q74" s="50"/>
-      <c r="R74" s="50"/>
-      <c r="S74" s="50"/>
-      <c r="T74" s="50"/>
-      <c r="U74" s="52"/>
-      <c r="V74" s="53"/>
-      <c r="W74" s="53"/>
-      <c r="X74" s="53"/>
-      <c r="Y74" s="50"/>
-      <c r="Z74" s="50"/>
+      <c r="N74" s="50"/>
+      <c r="O74" s="47"/>
+      <c r="P74" s="48"/>
+      <c r="Q74" s="47"/>
+      <c r="R74" s="47"/>
+      <c r="S74" s="47"/>
+      <c r="T74" s="47"/>
+      <c r="U74" s="49"/>
+      <c r="V74" s="50"/>
+      <c r="W74" s="50"/>
+      <c r="X74" s="50"/>
+      <c r="Y74" s="47"/>
+      <c r="Z74" s="47"/>
       <c r="AA74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
-      <c r="D75" s="81"/>
+      <c r="D75" s="80"/>
       <c r="E75" s="57"/>
-      <c r="F75" s="53"/>
-      <c r="G75" s="53"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
       <c r="H75" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I75" s="53" t="str">
+      <c r="I75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,MIN(E75*H75,G75)," ")</f>
         <v> </v>
       </c>
-      <c r="J75" s="53" t="str">
+      <c r="J75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,F75+I75," ")</f>
         <v> </v>
       </c>
-      <c r="K75" s="53" t="str">
+      <c r="K75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75-J75," ")</f>
         <v> </v>
       </c>
-      <c r="L75" s="53"/>
+      <c r="L75" s="50"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="53"/>
-      <c r="O75" s="50"/>
+      <c r="N75" s="50"/>
+      <c r="O75" s="47"/>
       <c r="P75" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q75" s="50" t="str">
+      <c r="Q75" s="47" t="str">
         <f aca="false">IF(E75&gt;0,E75*P75," ")</f>
         <v> </v>
       </c>
-      <c r="R75" s="50"/>
-      <c r="S75" s="50" t="str">
+      <c r="R75" s="47"/>
+      <c r="S75" s="47" t="str">
         <f aca="false">IF(E75&gt;0,E75-Q75," ")</f>
         <v> </v>
       </c>
-      <c r="T75" s="50"/>
+      <c r="T75" s="47"/>
       <c r="U75" s="54"/>
       <c r="V75" s="57"/>
-      <c r="W75" s="53" t="str">
+      <c r="W75" s="50" t="str">
         <f aca="false">IF(V75&gt;0,E75," ")</f>
         <v> </v>
       </c>
-      <c r="X75" s="53" t="str">
+      <c r="X75" s="50" t="str">
         <f aca="false">IF(V75&gt;0,J75," ")</f>
         <v> </v>
       </c>
-      <c r="Y75" s="50" t="str">
+      <c r="Y75" s="47" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&lt;S75,S75-V75," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z75" s="50" t="str">
+      <c r="Z75" s="47" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&gt;S75,V75-S75," ")," ")</f>
         <v> </v>
       </c>
@@ -5716,59 +5781,59 @@
       <c r="A76" s="42"/>
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
-      <c r="D76" s="81"/>
+      <c r="D76" s="80"/>
       <c r="E76" s="57"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
       <c r="H76" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I76" s="53" t="str">
+      <c r="I76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,MIN(E76*H76,G76)," ")</f>
         <v> </v>
       </c>
-      <c r="J76" s="53" t="str">
+      <c r="J76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,F76+I76," ")</f>
         <v> </v>
       </c>
-      <c r="K76" s="53" t="str">
+      <c r="K76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76-J76," ")</f>
         <v> </v>
       </c>
-      <c r="L76" s="53"/>
+      <c r="L76" s="50"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="53"/>
-      <c r="O76" s="50"/>
+      <c r="N76" s="50"/>
+      <c r="O76" s="47"/>
       <c r="P76" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q76" s="50" t="str">
+      <c r="Q76" s="47" t="str">
         <f aca="false">IF(E76&gt;0,E76*P76," ")</f>
         <v> </v>
       </c>
-      <c r="R76" s="50"/>
-      <c r="S76" s="50" t="str">
+      <c r="R76" s="47"/>
+      <c r="S76" s="47" t="str">
         <f aca="false">IF(E76&gt;0,E76-Q76," ")</f>
         <v> </v>
       </c>
-      <c r="T76" s="50"/>
+      <c r="T76" s="47"/>
       <c r="U76" s="54"/>
       <c r="V76" s="57"/>
-      <c r="W76" s="53" t="str">
+      <c r="W76" s="50" t="str">
         <f aca="false">IF(V76&gt;0,E76," ")</f>
         <v> </v>
       </c>
-      <c r="X76" s="53" t="str">
+      <c r="X76" s="50" t="str">
         <f aca="false">IF(V76&gt;0,J76," ")</f>
         <v> </v>
       </c>
-      <c r="Y76" s="50" t="str">
+      <c r="Y76" s="47" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&lt;S76,S76-V76," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z76" s="50" t="str">
+      <c r="Z76" s="47" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&gt;S76,V76-S76," ")," ")</f>
         <v> </v>
       </c>
@@ -5778,59 +5843,59 @@
       <c r="A77" s="42"/>
       <c r="B77" s="54"/>
       <c r="C77" s="55"/>
-      <c r="D77" s="81"/>
+      <c r="D77" s="80"/>
       <c r="E77" s="57"/>
-      <c r="F77" s="53"/>
-      <c r="G77" s="53"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
       <c r="H77" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="53" t="str">
+      <c r="I77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,MIN(E77*H77,G77)," ")</f>
         <v> </v>
       </c>
-      <c r="J77" s="53" t="str">
+      <c r="J77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,F77+I77," ")</f>
         <v> </v>
       </c>
-      <c r="K77" s="53" t="str">
+      <c r="K77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77-J77," ")</f>
         <v> </v>
       </c>
-      <c r="L77" s="53"/>
+      <c r="L77" s="50"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="53"/>
-      <c r="O77" s="50"/>
+      <c r="N77" s="50"/>
+      <c r="O77" s="47"/>
       <c r="P77" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="50" t="str">
+      <c r="Q77" s="47" t="str">
         <f aca="false">IF(E77&gt;0,E77*P77," ")</f>
         <v> </v>
       </c>
-      <c r="R77" s="50"/>
-      <c r="S77" s="50" t="str">
+      <c r="R77" s="47"/>
+      <c r="S77" s="47" t="str">
         <f aca="false">IF(E77&gt;0,E77-Q77," ")</f>
         <v> </v>
       </c>
-      <c r="T77" s="50"/>
+      <c r="T77" s="47"/>
       <c r="U77" s="54"/>
       <c r="V77" s="57"/>
-      <c r="W77" s="53" t="str">
+      <c r="W77" s="50" t="str">
         <f aca="false">IF(V77&gt;0,E77," ")</f>
         <v> </v>
       </c>
-      <c r="X77" s="53" t="str">
+      <c r="X77" s="50" t="str">
         <f aca="false">IF(V77&gt;0,J77," ")</f>
         <v> </v>
       </c>
-      <c r="Y77" s="50" t="str">
+      <c r="Y77" s="47" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&lt;S77,S77-V77," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z77" s="50" t="str">
+      <c r="Z77" s="47" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&gt;S77,V77-S77," ")," ")</f>
         <v> </v>
       </c>
@@ -5840,59 +5905,59 @@
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="81"/>
+      <c r="D78" s="80"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="53" t="str">
+      <c r="I78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="53" t="str">
+      <c r="J78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="53" t="str">
+      <c r="K78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
         <v> </v>
       </c>
-      <c r="L78" s="53"/>
+      <c r="L78" s="50"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="53"/>
-      <c r="O78" s="50"/>
+      <c r="N78" s="50"/>
+      <c r="O78" s="47"/>
       <c r="P78" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q78" s="50" t="str">
+      <c r="Q78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="50"/>
-      <c r="S78" s="50" t="str">
+      <c r="R78" s="47"/>
+      <c r="S78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="50"/>
+      <c r="T78" s="47"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="53" t="str">
+      <c r="W78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="53" t="str">
+      <c r="X78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="50" t="str">
+      <c r="Y78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="50" t="str">
+      <c r="Z78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5902,59 +5967,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="81"/>
+      <c r="D79" s="80"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="53" t="str">
+      <c r="I79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="53" t="str">
+      <c r="J79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="53" t="str">
+      <c r="K79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
         <v> </v>
       </c>
-      <c r="L79" s="53"/>
+      <c r="L79" s="50"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="50"/>
+      <c r="N79" s="50"/>
+      <c r="O79" s="47"/>
       <c r="P79" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q79" s="50" t="str">
+      <c r="Q79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="50"/>
-      <c r="S79" s="50" t="str">
+      <c r="R79" s="47"/>
+      <c r="S79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="50"/>
+      <c r="T79" s="47"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="53" t="str">
+      <c r="W79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="53" t="str">
+      <c r="X79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="50" t="str">
+      <c r="Y79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="50" t="str">
+      <c r="Z79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -5963,7 +6028,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="42"/>
       <c r="B80" s="59" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C80" s="59"/>
       <c r="D80" s="59"/>
@@ -5992,9 +6057,9 @@
         <f aca="false">SUM(K75:K79)</f>
         <v>0</v>
       </c>
-      <c r="L80" s="53"/>
+      <c r="L80" s="50"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="53"/>
+      <c r="N80" s="50"/>
       <c r="O80" s="61" t="n">
         <f aca="false">SUM(O75:O79)</f>
         <v>0</v>
@@ -6012,8 +6077,8 @@
         <f aca="false">SUM(S75:S79)</f>
         <v>0</v>
       </c>
-      <c r="T80" s="50"/>
-      <c r="U80" s="52"/>
+      <c r="T80" s="47"/>
+      <c r="U80" s="49"/>
       <c r="V80" s="60" t="n">
         <f aca="false">SUM(V75:V79)</f>
         <v>0</v>
@@ -6041,121 +6106,121 @@
       <c r="B81" s="63"/>
       <c r="C81" s="64"/>
       <c r="D81" s="65"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
       <c r="H81" s="58"/>
-      <c r="I81" s="53"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="53"/>
-      <c r="L81" s="53"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="53"/>
-      <c r="O81" s="53"/>
+      <c r="N81" s="50"/>
+      <c r="O81" s="50"/>
       <c r="P81" s="62"/>
-      <c r="Q81" s="53"/>
-      <c r="R81" s="53"/>
-      <c r="S81" s="53"/>
-      <c r="T81" s="50"/>
-      <c r="U81" s="52"/>
-      <c r="V81" s="53"/>
-      <c r="W81" s="53"/>
-      <c r="X81" s="53"/>
-      <c r="Y81" s="53"/>
-      <c r="Z81" s="53"/>
+      <c r="Q81" s="50"/>
+      <c r="R81" s="50"/>
+      <c r="S81" s="50"/>
+      <c r="T81" s="47"/>
+      <c r="U81" s="49"/>
+      <c r="V81" s="50"/>
+      <c r="W81" s="50"/>
+      <c r="X81" s="50"/>
+      <c r="Y81" s="50"/>
+      <c r="Z81" s="50"/>
       <c r="AA81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="42"/>
-      <c r="B82" s="66" t="s">
+      <c r="B82" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="66"/>
-      <c r="D82" s="69"/>
-      <c r="E82" s="53"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="83" t="n">
+      <c r="C82" s="51"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="82" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I82" s="53"/>
-      <c r="J82" s="53"/>
-      <c r="K82" s="53"/>
-      <c r="L82" s="53"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="53"/>
-      <c r="O82" s="50"/>
-      <c r="P82" s="51"/>
-      <c r="Q82" s="50"/>
-      <c r="R82" s="50"/>
-      <c r="S82" s="50"/>
-      <c r="T82" s="50"/>
-      <c r="U82" s="52"/>
-      <c r="V82" s="53"/>
-      <c r="W82" s="53"/>
-      <c r="X82" s="53"/>
-      <c r="Y82" s="50"/>
-      <c r="Z82" s="50"/>
+      <c r="N82" s="50"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="47"/>
+      <c r="R82" s="47"/>
+      <c r="S82" s="47"/>
+      <c r="T82" s="47"/>
+      <c r="U82" s="49"/>
+      <c r="V82" s="50"/>
+      <c r="W82" s="50"/>
+      <c r="X82" s="50"/>
+      <c r="Y82" s="47"/>
+      <c r="Z82" s="47"/>
       <c r="AA82" s="25"/>
     </row>
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="54"/>
       <c r="C83" s="55"/>
-      <c r="D83" s="81"/>
+      <c r="D83" s="80"/>
       <c r="E83" s="57"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
       <c r="H83" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I83" s="53" t="str">
+      <c r="I83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,MIN(E83*H83,G83)," ")</f>
         <v> </v>
       </c>
-      <c r="J83" s="53" t="str">
+      <c r="J83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,F83+I83," ")</f>
         <v> </v>
       </c>
-      <c r="K83" s="53" t="str">
+      <c r="K83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83-J83," ")</f>
         <v> </v>
       </c>
-      <c r="L83" s="53"/>
+      <c r="L83" s="50"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="53"/>
-      <c r="O83" s="50"/>
+      <c r="N83" s="50"/>
+      <c r="O83" s="47"/>
       <c r="P83" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q83" s="50" t="str">
+      <c r="Q83" s="47" t="str">
         <f aca="false">IF(E83&gt;0,E83*P83," ")</f>
         <v> </v>
       </c>
-      <c r="R83" s="50"/>
-      <c r="S83" s="50" t="str">
+      <c r="R83" s="47"/>
+      <c r="S83" s="47" t="str">
         <f aca="false">IF(E83&gt;0,E83-Q83," ")</f>
         <v> </v>
       </c>
-      <c r="T83" s="50"/>
+      <c r="T83" s="47"/>
       <c r="U83" s="54"/>
       <c r="V83" s="57"/>
-      <c r="W83" s="53" t="str">
+      <c r="W83" s="50" t="str">
         <f aca="false">IF(V83&gt;0,E83," ")</f>
         <v> </v>
       </c>
-      <c r="X83" s="53" t="str">
+      <c r="X83" s="50" t="str">
         <f aca="false">IF(V83&gt;0,J83," ")</f>
         <v> </v>
       </c>
-      <c r="Y83" s="50" t="str">
+      <c r="Y83" s="47" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&lt;S83,S83-V83," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z83" s="50" t="str">
+      <c r="Z83" s="47" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&gt;S83,V83-S83," ")," ")</f>
         <v> </v>
       </c>
@@ -6165,59 +6230,59 @@
       <c r="A84" s="42"/>
       <c r="B84" s="54"/>
       <c r="C84" s="55"/>
-      <c r="D84" s="81"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="57"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
       <c r="H84" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I84" s="53" t="str">
+      <c r="I84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,MIN(E84*H84,G84)," ")</f>
         <v> </v>
       </c>
-      <c r="J84" s="53" t="str">
+      <c r="J84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,F84+I84," ")</f>
         <v> </v>
       </c>
-      <c r="K84" s="53" t="str">
+      <c r="K84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84-J84," ")</f>
         <v> </v>
       </c>
-      <c r="L84" s="53"/>
+      <c r="L84" s="50"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="53"/>
-      <c r="O84" s="50"/>
+      <c r="N84" s="50"/>
+      <c r="O84" s="47"/>
       <c r="P84" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q84" s="50" t="str">
+      <c r="Q84" s="47" t="str">
         <f aca="false">IF(E84&gt;0,E84*P84," ")</f>
         <v> </v>
       </c>
-      <c r="R84" s="50"/>
-      <c r="S84" s="50" t="str">
+      <c r="R84" s="47"/>
+      <c r="S84" s="47" t="str">
         <f aca="false">IF(E84&gt;0,E84-Q84," ")</f>
         <v> </v>
       </c>
-      <c r="T84" s="50"/>
+      <c r="T84" s="47"/>
       <c r="U84" s="54"/>
       <c r="V84" s="57"/>
-      <c r="W84" s="53" t="str">
+      <c r="W84" s="50" t="str">
         <f aca="false">IF(V84&gt;0,E84," ")</f>
         <v> </v>
       </c>
-      <c r="X84" s="53" t="str">
+      <c r="X84" s="50" t="str">
         <f aca="false">IF(V84&gt;0,J84," ")</f>
         <v> </v>
       </c>
-      <c r="Y84" s="50" t="str">
+      <c r="Y84" s="47" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&lt;S84,S84-V84," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z84" s="50" t="str">
+      <c r="Z84" s="47" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&gt;S84,V84-S84," ")," ")</f>
         <v> </v>
       </c>
@@ -6227,59 +6292,59 @@
       <c r="A85" s="42"/>
       <c r="B85" s="54"/>
       <c r="C85" s="55"/>
-      <c r="D85" s="81"/>
+      <c r="D85" s="80"/>
       <c r="E85" s="57"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
       <c r="H85" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="53" t="str">
+      <c r="I85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,MIN(E85*H85,G85)," ")</f>
         <v> </v>
       </c>
-      <c r="J85" s="53" t="str">
+      <c r="J85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,F85+I85," ")</f>
         <v> </v>
       </c>
-      <c r="K85" s="53" t="str">
+      <c r="K85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85-J85," ")</f>
         <v> </v>
       </c>
-      <c r="L85" s="53"/>
+      <c r="L85" s="50"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="53"/>
-      <c r="O85" s="50"/>
+      <c r="N85" s="50"/>
+      <c r="O85" s="47"/>
       <c r="P85" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q85" s="50" t="str">
+      <c r="Q85" s="47" t="str">
         <f aca="false">IF(E85&gt;0,E85*P85," ")</f>
         <v> </v>
       </c>
-      <c r="R85" s="50"/>
-      <c r="S85" s="50" t="str">
+      <c r="R85" s="47"/>
+      <c r="S85" s="47" t="str">
         <f aca="false">IF(E85&gt;0,E85-Q85," ")</f>
         <v> </v>
       </c>
-      <c r="T85" s="50"/>
+      <c r="T85" s="47"/>
       <c r="U85" s="54"/>
       <c r="V85" s="57"/>
-      <c r="W85" s="53" t="str">
+      <c r="W85" s="50" t="str">
         <f aca="false">IF(V85&gt;0,E85," ")</f>
         <v> </v>
       </c>
-      <c r="X85" s="53" t="str">
+      <c r="X85" s="50" t="str">
         <f aca="false">IF(V85&gt;0,J85," ")</f>
         <v> </v>
       </c>
-      <c r="Y85" s="50" t="str">
+      <c r="Y85" s="47" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&lt;S85,S85-V85," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z85" s="50" t="str">
+      <c r="Z85" s="47" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&gt;S85,V85-S85," ")," ")</f>
         <v> </v>
       </c>
@@ -6289,59 +6354,59 @@
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="81"/>
+      <c r="D86" s="80"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="53" t="str">
+      <c r="I86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="53" t="str">
+      <c r="J86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="53" t="str">
+      <c r="K86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
         <v> </v>
       </c>
-      <c r="L86" s="53"/>
+      <c r="L86" s="50"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="53"/>
-      <c r="O86" s="50"/>
+      <c r="N86" s="50"/>
+      <c r="O86" s="47"/>
       <c r="P86" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q86" s="50" t="str">
+      <c r="Q86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="50"/>
-      <c r="S86" s="50" t="str">
+      <c r="R86" s="47"/>
+      <c r="S86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="50"/>
+      <c r="T86" s="47"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="53" t="str">
+      <c r="W86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="53" t="str">
+      <c r="X86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="50" t="str">
+      <c r="Y86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="50" t="str">
+      <c r="Z86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6351,59 +6416,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="81"/>
+      <c r="D87" s="80"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="53" t="str">
+      <c r="I87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="53" t="str">
+      <c r="J87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="53" t="str">
+      <c r="K87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
         <v> </v>
       </c>
-      <c r="L87" s="53"/>
+      <c r="L87" s="50"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="53"/>
-      <c r="O87" s="50"/>
+      <c r="N87" s="50"/>
+      <c r="O87" s="47"/>
       <c r="P87" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q87" s="50" t="str">
+      <c r="Q87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="50"/>
-      <c r="S87" s="50" t="str">
+      <c r="R87" s="47"/>
+      <c r="S87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="50"/>
+      <c r="T87" s="47"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="53" t="str">
+      <c r="W87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="53" t="str">
+      <c r="X87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="50" t="str">
+      <c r="Y87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="50" t="str">
+      <c r="Z87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6412,7 +6477,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="42"/>
       <c r="B88" s="59" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -6441,9 +6506,9 @@
         <f aca="false">SUM(K83:K87)</f>
         <v>0</v>
       </c>
-      <c r="L88" s="53"/>
+      <c r="L88" s="50"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="53"/>
+      <c r="N88" s="50"/>
       <c r="O88" s="61" t="n">
         <f aca="false">SUM(O83:O87)</f>
         <v>0</v>
@@ -6461,8 +6526,8 @@
         <f aca="false">SUM(S83:S87)</f>
         <v>0</v>
       </c>
-      <c r="T88" s="50"/>
-      <c r="U88" s="52"/>
+      <c r="T88" s="47"/>
+      <c r="U88" s="49"/>
       <c r="V88" s="60" t="n">
         <f aca="false">SUM(V83:V87)</f>
         <v>0</v>
@@ -6490,124 +6555,124 @@
       <c r="B89" s="63"/>
       <c r="C89" s="64"/>
       <c r="D89" s="65"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
       <c r="H89" s="58"/>
-      <c r="I89" s="53"/>
-      <c r="J89" s="53"/>
-      <c r="K89" s="53"/>
-      <c r="L89" s="53"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
+      <c r="L89" s="50"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="53"/>
-      <c r="O89" s="53"/>
+      <c r="N89" s="50"/>
+      <c r="O89" s="50"/>
       <c r="P89" s="62"/>
-      <c r="Q89" s="53"/>
-      <c r="R89" s="53"/>
-      <c r="S89" s="53"/>
-      <c r="T89" s="50"/>
-      <c r="U89" s="52"/>
-      <c r="V89" s="53"/>
-      <c r="W89" s="53"/>
-      <c r="X89" s="53"/>
-      <c r="Y89" s="53"/>
-      <c r="Z89" s="53"/>
+      <c r="Q89" s="50"/>
+      <c r="R89" s="50"/>
+      <c r="S89" s="50"/>
+      <c r="T89" s="47"/>
+      <c r="U89" s="49"/>
+      <c r="V89" s="50"/>
+      <c r="W89" s="50"/>
+      <c r="X89" s="50"/>
+      <c r="Y89" s="50"/>
+      <c r="Z89" s="50"/>
       <c r="AA89" s="25"/>
     </row>
     <row r="90" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="42"/>
-      <c r="B90" s="70" t="str">
+      <c r="B90" s="69" t="str">
         <f aca="false">B37</f>
         <v>Motor Vehicles - costing over £</v>
       </c>
-      <c r="C90" s="70"/>
-      <c r="D90" s="71" t="n">
+      <c r="C90" s="69"/>
+      <c r="D90" s="70" t="n">
         <f aca="false">D37</f>
         <v>12000</v>
       </c>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="83" t="n">
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="82" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="53"/>
+      <c r="I90" s="50"/>
+      <c r="J90" s="50"/>
+      <c r="K90" s="50"/>
+      <c r="L90" s="50"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="53"/>
-      <c r="O90" s="50"/>
+      <c r="N90" s="50"/>
+      <c r="O90" s="47"/>
       <c r="P90" s="62"/>
-      <c r="Q90" s="50"/>
-      <c r="R90" s="50"/>
-      <c r="S90" s="50"/>
-      <c r="T90" s="50"/>
-      <c r="U90" s="52"/>
-      <c r="V90" s="53"/>
-      <c r="W90" s="53"/>
-      <c r="X90" s="53"/>
-      <c r="Y90" s="50"/>
-      <c r="Z90" s="50"/>
+      <c r="Q90" s="47"/>
+      <c r="R90" s="47"/>
+      <c r="S90" s="47"/>
+      <c r="T90" s="47"/>
+      <c r="U90" s="49"/>
+      <c r="V90" s="50"/>
+      <c r="W90" s="50"/>
+      <c r="X90" s="50"/>
+      <c r="Y90" s="47"/>
+      <c r="Z90" s="47"/>
       <c r="AA90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="81"/>
+      <c r="D91" s="80"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I91" s="53" t="str">
+      <c r="I91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="53" t="str">
+      <c r="J91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="53" t="str">
+      <c r="K91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
         <v> </v>
       </c>
-      <c r="L91" s="53"/>
-      <c r="M91" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="53"/>
-      <c r="O91" s="50"/>
-      <c r="P91" s="51"/>
-      <c r="Q91" s="50"/>
-      <c r="R91" s="50" t="str">
+      <c r="L91" s="50"/>
+      <c r="M91" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="50"/>
+      <c r="O91" s="47"/>
+      <c r="P91" s="48"/>
+      <c r="Q91" s="47"/>
+      <c r="R91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
         <v> </v>
       </c>
-      <c r="S91" s="50" t="str">
+      <c r="S91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,E91-R91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="50"/>
+      <c r="T91" s="47"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="53" t="str">
+      <c r="W91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="53" t="str">
+      <c r="X91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="50" t="str">
+      <c r="Y91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,(S91-V91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="50" t="str">
+      <c r="Z91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,(V91-S91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
@@ -6617,58 +6682,58 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="81"/>
+      <c r="D92" s="80"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I92" s="53" t="str">
+      <c r="I92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="53" t="str">
+      <c r="J92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="53" t="str">
+      <c r="K92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
         <v> </v>
       </c>
-      <c r="L92" s="53"/>
-      <c r="M92" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="53"/>
-      <c r="O92" s="50"/>
-      <c r="P92" s="51"/>
-      <c r="Q92" s="50"/>
-      <c r="R92" s="50" t="str">
+      <c r="L92" s="50"/>
+      <c r="M92" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="50"/>
+      <c r="O92" s="47"/>
+      <c r="P92" s="48"/>
+      <c r="Q92" s="47"/>
+      <c r="R92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
         <v> </v>
       </c>
-      <c r="S92" s="50" t="str">
+      <c r="S92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,E92-R92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="50"/>
+      <c r="T92" s="47"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="53" t="str">
+      <c r="W92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="53" t="str">
+      <c r="X92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="50" t="str">
+      <c r="Y92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,(S92-V92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="50" t="str">
+      <c r="Z92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,(V92-S92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
@@ -6678,58 +6743,58 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="81"/>
+      <c r="D93" s="80"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="53"/>
-      <c r="G93" s="53"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I93" s="53" t="str">
+      <c r="I93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="53" t="str">
+      <c r="J93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="53" t="str">
+      <c r="K93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
         <v> </v>
       </c>
-      <c r="L93" s="53"/>
-      <c r="M93" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="53"/>
-      <c r="O93" s="50"/>
-      <c r="P93" s="51"/>
-      <c r="Q93" s="50"/>
-      <c r="R93" s="50" t="str">
+      <c r="L93" s="50"/>
+      <c r="M93" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="50"/>
+      <c r="O93" s="47"/>
+      <c r="P93" s="48"/>
+      <c r="Q93" s="47"/>
+      <c r="R93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
         <v> </v>
       </c>
-      <c r="S93" s="50" t="str">
+      <c r="S93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,E93-R93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="50"/>
+      <c r="T93" s="47"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="53" t="str">
+      <c r="W93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="53" t="str">
+      <c r="X93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="50" t="str">
+      <c r="Y93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,(S93-V93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="50" t="str">
+      <c r="Z93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,(V93-S93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
@@ -6739,58 +6804,58 @@
       <c r="A94" s="42"/>
       <c r="B94" s="54"/>
       <c r="C94" s="55"/>
-      <c r="D94" s="81"/>
+      <c r="D94" s="80"/>
       <c r="E94" s="57"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
       <c r="H94" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I94" s="53" t="str">
+      <c r="I94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*H94,G94)," ")</f>
         <v> </v>
       </c>
-      <c r="J94" s="53" t="str">
+      <c r="J94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,F94+I94," ")</f>
         <v> </v>
       </c>
-      <c r="K94" s="53" t="str">
+      <c r="K94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,E94-J94," ")</f>
         <v> </v>
       </c>
-      <c r="L94" s="53"/>
-      <c r="M94" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="53"/>
-      <c r="O94" s="50"/>
-      <c r="P94" s="51"/>
-      <c r="Q94" s="50"/>
-      <c r="R94" s="50" t="str">
+      <c r="L94" s="50"/>
+      <c r="M94" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="50"/>
+      <c r="O94" s="47"/>
+      <c r="P94" s="48"/>
+      <c r="Q94" s="47"/>
+      <c r="R94" s="47" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
         <v> </v>
       </c>
-      <c r="S94" s="50" t="str">
+      <c r="S94" s="47" t="str">
         <f aca="false">IF(E94&gt;0,E94-R94," ")</f>
         <v> </v>
       </c>
-      <c r="T94" s="50"/>
+      <c r="T94" s="47"/>
       <c r="U94" s="54"/>
       <c r="V94" s="57"/>
-      <c r="W94" s="53" t="str">
+      <c r="W94" s="50" t="str">
         <f aca="false">IF(V94&gt;0,E94," ")</f>
         <v> </v>
       </c>
-      <c r="X94" s="53" t="str">
+      <c r="X94" s="50" t="str">
         <f aca="false">IF(V94&gt;0,J94," ")</f>
         <v> </v>
       </c>
-      <c r="Y94" s="50" t="str">
+      <c r="Y94" s="47" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&lt;S94,(S94-V94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z94" s="50" t="str">
+      <c r="Z94" s="47" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&gt;S94,(V94-S94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
@@ -6800,58 +6865,58 @@
       <c r="A95" s="42"/>
       <c r="B95" s="54"/>
       <c r="C95" s="55"/>
-      <c r="D95" s="81"/>
+      <c r="D95" s="80"/>
       <c r="E95" s="57"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50"/>
       <c r="H95" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I95" s="53" t="str">
+      <c r="I95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*H95,G95)," ")</f>
         <v> </v>
       </c>
-      <c r="J95" s="53" t="str">
+      <c r="J95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,F95+I95," ")</f>
         <v> </v>
       </c>
-      <c r="K95" s="53" t="str">
+      <c r="K95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,E95-J95," ")</f>
         <v> </v>
       </c>
-      <c r="L95" s="53"/>
-      <c r="M95" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="53"/>
-      <c r="O95" s="50"/>
-      <c r="P95" s="51"/>
-      <c r="Q95" s="50"/>
-      <c r="R95" s="50" t="str">
+      <c r="L95" s="50"/>
+      <c r="M95" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="50"/>
+      <c r="O95" s="47"/>
+      <c r="P95" s="48"/>
+      <c r="Q95" s="47"/>
+      <c r="R95" s="47" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
         <v> </v>
       </c>
-      <c r="S95" s="50" t="str">
+      <c r="S95" s="47" t="str">
         <f aca="false">IF(E95&gt;0,E95-R95," ")</f>
         <v> </v>
       </c>
-      <c r="T95" s="50"/>
+      <c r="T95" s="47"/>
       <c r="U95" s="54"/>
       <c r="V95" s="57"/>
-      <c r="W95" s="53" t="str">
+      <c r="W95" s="50" t="str">
         <f aca="false">IF(V95&gt;0,E95," ")</f>
         <v> </v>
       </c>
-      <c r="X95" s="53" t="str">
+      <c r="X95" s="50" t="str">
         <f aca="false">IF(V95&gt;0,J95," ")</f>
         <v> </v>
       </c>
-      <c r="Y95" s="50" t="str">
+      <c r="Y95" s="47" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&lt;S95,(S95-V95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z95" s="50" t="str">
+      <c r="Z95" s="47" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&gt;S95,(V95-S95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
@@ -6859,95 +6924,95 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="84" t="str">
+      <c r="B96" s="83" t="str">
         <f aca="false">B43</f>
         <v>Motor Vehicles - costing under £</v>
       </c>
-      <c r="C96" s="84"/>
-      <c r="D96" s="71" t="n">
+      <c r="C96" s="83"/>
+      <c r="D96" s="70" t="n">
         <f aca="false">D43</f>
         <v>12000</v>
       </c>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="53"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
       <c r="H96" s="58"/>
-      <c r="I96" s="53"/>
-      <c r="J96" s="53"/>
-      <c r="K96" s="53"/>
-      <c r="L96" s="53"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+      <c r="L96" s="50"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="53"/>
-      <c r="O96" s="50"/>
-      <c r="P96" s="51"/>
-      <c r="Q96" s="50"/>
-      <c r="R96" s="50"/>
-      <c r="S96" s="50"/>
-      <c r="T96" s="50"/>
-      <c r="U96" s="52"/>
-      <c r="V96" s="53"/>
-      <c r="W96" s="53"/>
-      <c r="X96" s="53"/>
-      <c r="Y96" s="50"/>
-      <c r="Z96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="47"/>
+      <c r="P96" s="48"/>
+      <c r="Q96" s="47"/>
+      <c r="R96" s="47"/>
+      <c r="S96" s="47"/>
+      <c r="T96" s="47"/>
+      <c r="U96" s="49"/>
+      <c r="V96" s="50"/>
+      <c r="W96" s="50"/>
+      <c r="X96" s="50"/>
+      <c r="Y96" s="47"/>
+      <c r="Z96" s="47"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="81"/>
+      <c r="D97" s="80"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="53"/>
-      <c r="G97" s="53"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="53" t="str">
+      <c r="I97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="53" t="str">
+      <c r="J97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="53" t="str">
+      <c r="K97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
         <v> </v>
       </c>
-      <c r="L97" s="53"/>
-      <c r="M97" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="53"/>
-      <c r="O97" s="50"/>
-      <c r="P97" s="51"/>
-      <c r="Q97" s="50"/>
-      <c r="R97" s="50" t="str">
+      <c r="L97" s="50"/>
+      <c r="M97" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="50"/>
+      <c r="O97" s="47"/>
+      <c r="P97" s="48"/>
+      <c r="Q97" s="47"/>
+      <c r="R97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="50" t="str">
+      <c r="S97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="50"/>
+      <c r="T97" s="47"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="53" t="str">
+      <c r="W97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="53" t="str">
+      <c r="X97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="50" t="str">
+      <c r="Y97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="50" t="str">
+      <c r="Z97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -6957,58 +7022,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="81"/>
+      <c r="D98" s="80"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="53"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="53" t="str">
+      <c r="I98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="53" t="str">
+      <c r="J98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="53" t="str">
+      <c r="K98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
         <v> </v>
       </c>
-      <c r="L98" s="53"/>
-      <c r="M98" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="53"/>
-      <c r="O98" s="50"/>
-      <c r="P98" s="51"/>
-      <c r="Q98" s="50"/>
-      <c r="R98" s="50" t="str">
+      <c r="L98" s="50"/>
+      <c r="M98" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="50"/>
+      <c r="O98" s="47"/>
+      <c r="P98" s="48"/>
+      <c r="Q98" s="47"/>
+      <c r="R98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="50" t="str">
+      <c r="S98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="50"/>
+      <c r="T98" s="47"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="53" t="str">
+      <c r="W98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="53" t="str">
+      <c r="X98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="50" t="str">
+      <c r="Y98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="50" t="str">
+      <c r="Z98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -7018,58 +7083,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="81"/>
+      <c r="D99" s="80"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="53"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="53" t="str">
+      <c r="I99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="53" t="str">
+      <c r="J99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="53" t="str">
+      <c r="K99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
         <v> </v>
       </c>
-      <c r="L99" s="53"/>
-      <c r="M99" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="53"/>
-      <c r="O99" s="50"/>
-      <c r="P99" s="51"/>
-      <c r="Q99" s="50"/>
-      <c r="R99" s="50" t="str">
+      <c r="L99" s="50"/>
+      <c r="M99" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="50"/>
+      <c r="O99" s="47"/>
+      <c r="P99" s="48"/>
+      <c r="Q99" s="47"/>
+      <c r="R99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="50" t="str">
+      <c r="S99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="50"/>
+      <c r="T99" s="47"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="53" t="str">
+      <c r="W99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="53" t="str">
+      <c r="X99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="50" t="str">
+      <c r="Y99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="50" t="str">
+      <c r="Z99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -7079,58 +7144,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="81"/>
+      <c r="D100" s="80"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="53"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="53" t="str">
+      <c r="I100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="53" t="str">
+      <c r="J100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="53" t="str">
+      <c r="K100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
         <v> </v>
       </c>
-      <c r="L100" s="53"/>
-      <c r="M100" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="53"/>
-      <c r="O100" s="50"/>
-      <c r="P100" s="51"/>
-      <c r="Q100" s="50"/>
-      <c r="R100" s="50" t="str">
+      <c r="L100" s="50"/>
+      <c r="M100" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="50"/>
+      <c r="O100" s="47"/>
+      <c r="P100" s="48"/>
+      <c r="Q100" s="47"/>
+      <c r="R100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="50" t="str">
+      <c r="S100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="50"/>
+      <c r="T100" s="47"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="53" t="str">
+      <c r="W100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="53" t="str">
+      <c r="X100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="50" t="str">
+      <c r="Y100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="50" t="str">
+      <c r="Z100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -7140,58 +7205,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="81"/>
+      <c r="D101" s="80"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="53"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="53" t="str">
+      <c r="I101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="53" t="str">
+      <c r="J101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="53" t="str">
+      <c r="K101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
         <v> </v>
       </c>
-      <c r="L101" s="53"/>
-      <c r="M101" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="53"/>
-      <c r="O101" s="50"/>
-      <c r="P101" s="51"/>
-      <c r="Q101" s="50"/>
-      <c r="R101" s="50" t="str">
+      <c r="L101" s="50"/>
+      <c r="M101" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="50"/>
+      <c r="O101" s="47"/>
+      <c r="P101" s="48"/>
+      <c r="Q101" s="47"/>
+      <c r="R101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="50" t="str">
+      <c r="S101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="50"/>
+      <c r="T101" s="47"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="53" t="str">
+      <c r="W101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="53" t="str">
+      <c r="X101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="50" t="str">
+      <c r="Y101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="50" t="str">
+      <c r="Z101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7199,94 +7264,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C102" s="66"/>
-      <c r="D102" s="69"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
+      <c r="B102" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" s="51"/>
+      <c r="D102" s="68"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
-      <c r="L102" s="53"/>
+      <c r="I102" s="50"/>
+      <c r="J102" s="50"/>
+      <c r="K102" s="50"/>
+      <c r="L102" s="50"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="53"/>
-      <c r="O102" s="50"/>
-      <c r="P102" s="51"/>
-      <c r="Q102" s="50"/>
-      <c r="R102" s="50"/>
-      <c r="S102" s="50"/>
-      <c r="T102" s="50"/>
-      <c r="U102" s="52"/>
-      <c r="V102" s="53"/>
-      <c r="W102" s="53"/>
-      <c r="X102" s="53"/>
-      <c r="Y102" s="50"/>
-      <c r="Z102" s="50"/>
+      <c r="N102" s="50"/>
+      <c r="O102" s="47"/>
+      <c r="P102" s="48"/>
+      <c r="Q102" s="47"/>
+      <c r="R102" s="47"/>
+      <c r="S102" s="47"/>
+      <c r="T102" s="47"/>
+      <c r="U102" s="49"/>
+      <c r="V102" s="50"/>
+      <c r="W102" s="50"/>
+      <c r="X102" s="50"/>
+      <c r="Y102" s="47"/>
+      <c r="Z102" s="47"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="81"/>
+      <c r="D103" s="80"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="53"/>
-      <c r="G103" s="53"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="53" t="str">
+      <c r="I103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="53" t="str">
+      <c r="J103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="53" t="str">
+      <c r="K103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
         <v> </v>
       </c>
-      <c r="L103" s="53"/>
-      <c r="M103" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="53"/>
-      <c r="O103" s="50"/>
+      <c r="L103" s="50"/>
+      <c r="M103" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="50"/>
+      <c r="O103" s="47"/>
       <c r="P103" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q103" s="50" t="str">
+      <c r="Q103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="50"/>
-      <c r="S103" s="50" t="str">
+      <c r="R103" s="47"/>
+      <c r="S103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="50"/>
+      <c r="T103" s="47"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="53" t="str">
+      <c r="W103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="53" t="str">
+      <c r="X103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="50" t="str">
+      <c r="Y103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="50" t="str">
+      <c r="Z103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7296,61 +7361,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="81"/>
+      <c r="D104" s="80"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="53"/>
-      <c r="G104" s="53"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="53" t="str">
+      <c r="I104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="53" t="str">
+      <c r="J104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="53" t="str">
+      <c r="K104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
         <v> </v>
       </c>
-      <c r="L104" s="53"/>
-      <c r="M104" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="53"/>
-      <c r="O104" s="50"/>
+      <c r="L104" s="50"/>
+      <c r="M104" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="50"/>
+      <c r="O104" s="47"/>
       <c r="P104" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q104" s="50" t="str">
+      <c r="Q104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="50"/>
-      <c r="S104" s="50" t="str">
+      <c r="R104" s="47"/>
+      <c r="S104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="50"/>
+      <c r="T104" s="47"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="53" t="str">
+      <c r="W104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="53" t="str">
+      <c r="X104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="50" t="str">
+      <c r="Y104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="50" t="str">
+      <c r="Z104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7360,61 +7425,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="81"/>
+      <c r="D105" s="80"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="53" t="str">
+      <c r="I105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="53" t="str">
+      <c r="J105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="53" t="str">
+      <c r="K105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
         <v> </v>
       </c>
-      <c r="L105" s="53"/>
-      <c r="M105" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="53"/>
-      <c r="O105" s="50"/>
+      <c r="L105" s="50"/>
+      <c r="M105" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="50"/>
+      <c r="O105" s="47"/>
       <c r="P105" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q105" s="50" t="str">
+      <c r="Q105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="50"/>
-      <c r="S105" s="50" t="str">
+      <c r="R105" s="47"/>
+      <c r="S105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="50"/>
+      <c r="T105" s="47"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="53" t="str">
+      <c r="W105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="53" t="str">
+      <c r="X105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="50" t="str">
+      <c r="Y105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="50" t="str">
+      <c r="Z105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7424,61 +7489,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="81"/>
+      <c r="D106" s="80"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="53"/>
-      <c r="G106" s="53"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="53" t="str">
+      <c r="I106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="53" t="str">
+      <c r="J106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="53" t="str">
+      <c r="K106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
         <v> </v>
       </c>
-      <c r="L106" s="53"/>
-      <c r="M106" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="53"/>
-      <c r="O106" s="50"/>
+      <c r="L106" s="50"/>
+      <c r="M106" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="50"/>
+      <c r="O106" s="47"/>
       <c r="P106" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q106" s="50" t="str">
+      <c r="Q106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="50"/>
-      <c r="S106" s="50" t="str">
+      <c r="R106" s="47"/>
+      <c r="S106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="50"/>
+      <c r="T106" s="47"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="53" t="str">
+      <c r="W106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="53" t="str">
+      <c r="X106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="50" t="str">
+      <c r="Y106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="50" t="str">
+      <c r="Z106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7488,61 +7553,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="81"/>
-      <c r="E107" s="85"/>
-      <c r="F107" s="53"/>
-      <c r="G107" s="53"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="84"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="53" t="str">
+      <c r="I107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="53" t="str">
+      <c r="J107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="53" t="str">
+      <c r="K107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
         <v> </v>
       </c>
-      <c r="L107" s="53"/>
-      <c r="M107" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="53"/>
-      <c r="O107" s="50"/>
+      <c r="L107" s="50"/>
+      <c r="M107" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="50"/>
+      <c r="O107" s="47"/>
       <c r="P107" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q107" s="50" t="str">
+      <c r="Q107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="50"/>
-      <c r="S107" s="50" t="str">
+      <c r="R107" s="47"/>
+      <c r="S107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="50"/>
+      <c r="T107" s="47"/>
       <c r="U107" s="54"/>
-      <c r="V107" s="85"/>
-      <c r="W107" s="53" t="str">
+      <c r="V107" s="84"/>
+      <c r="W107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="53" t="str">
+      <c r="X107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="50" t="str">
+      <c r="Y107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="50" t="str">
+      <c r="Z107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7551,7 +7616,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7580,9 +7645,9 @@
         <f aca="false">SUM(K91:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="53"/>
+      <c r="L108" s="50"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="53"/>
+      <c r="N108" s="50"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O91:O107)</f>
         <v>0</v>
@@ -7600,8 +7665,8 @@
         <f aca="false">SUM(S91:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="50"/>
-      <c r="U108" s="52"/>
+      <c r="T108" s="47"/>
+      <c r="U108" s="49"/>
       <c r="V108" s="61" t="n">
         <f aca="false">SUM(V91:V107)</f>
         <v>0</v>
@@ -7626,31 +7691,31 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="74"/>
-      <c r="D109" s="69"/>
-      <c r="E109" s="53"/>
-      <c r="F109" s="53"/>
-      <c r="G109" s="53"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="73"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="53"/>
+      <c r="I109" s="50"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="50"/>
+      <c r="L109" s="50"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="53"/>
-      <c r="O109" s="50"/>
-      <c r="P109" s="51"/>
-      <c r="Q109" s="50"/>
-      <c r="R109" s="50"/>
-      <c r="S109" s="50"/>
-      <c r="T109" s="50"/>
-      <c r="U109" s="52"/>
-      <c r="V109" s="53"/>
-      <c r="W109" s="50"/>
-      <c r="X109" s="50"/>
-      <c r="Y109" s="50"/>
-      <c r="Z109" s="50"/>
+      <c r="N109" s="50"/>
+      <c r="O109" s="47"/>
+      <c r="P109" s="48"/>
+      <c r="Q109" s="47"/>
+      <c r="R109" s="47"/>
+      <c r="S109" s="47"/>
+      <c r="T109" s="47"/>
+      <c r="U109" s="49"/>
+      <c r="V109" s="50"/>
+      <c r="W109" s="47"/>
+      <c r="X109" s="47"/>
+      <c r="Y109" s="47"/>
+      <c r="Z109" s="47"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7662,105 +7727,105 @@
       <c r="C110" s="43"/>
       <c r="D110" s="44" t="n">
         <f aca="false">D59</f>
-        <v>45753</v>
-      </c>
-      <c r="E110" s="75" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E110" s="74" t="n">
         <f aca="false">E64+E72+E80+E88+E108</f>
-        <v>0</v>
-      </c>
-      <c r="F110" s="75" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F110" s="74" t="n">
         <f aca="false">F64+F72+F80+F88+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="75" t="n">
+      <c r="G110" s="74" t="n">
         <f aca="false">G64+G72+G80+G88+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="75" t="n">
+      <c r="I110" s="74" t="n">
         <f aca="false">I64+I72+I80+I88+I108</f>
-        <v>0</v>
-      </c>
-      <c r="J110" s="75" t="n">
+        <v>3250</v>
+      </c>
+      <c r="J110" s="74" t="n">
         <f aca="false">J64+J72+J80+J88+J108</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="75" t="n">
+        <v>3250</v>
+      </c>
+      <c r="K110" s="74" t="n">
         <f aca="false">K64+K72+K80+K88+K108</f>
-        <v>0</v>
-      </c>
-      <c r="L110" s="53"/>
+        <v>29250</v>
+      </c>
+      <c r="L110" s="50"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="53"/>
-      <c r="O110" s="75" t="n">
+      <c r="N110" s="50"/>
+      <c r="O110" s="74" t="n">
         <f aca="false">O64+O72+O80+O88+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="75" t="n">
+      <c r="Q110" s="74" t="n">
         <f aca="false">Q64+Q72+Q80+Q88+Q108</f>
-        <v>0</v>
-      </c>
-      <c r="R110" s="75" t="n">
+        <v>32500</v>
+      </c>
+      <c r="R110" s="74" t="n">
         <f aca="false">R64+R72+R80+R88+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="75" t="n">
+      <c r="S110" s="74" t="n">
         <f aca="false">S64+S72+S80+S88+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="50"/>
-      <c r="U110" s="52"/>
-      <c r="V110" s="75" t="n">
+      <c r="T110" s="47"/>
+      <c r="U110" s="49"/>
+      <c r="V110" s="74" t="n">
         <f aca="false">V64+V72+V80+V88+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="75" t="n">
+      <c r="W110" s="74" t="n">
         <f aca="false">W64+W72+W80+W88+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="75" t="n">
+      <c r="X110" s="74" t="n">
         <f aca="false">X64+X72+X80+X88+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="75" t="n">
+      <c r="Y110" s="74" t="n">
         <f aca="false">Y64+Y72+Y80+Y88+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="75" t="n">
+      <c r="Z110" s="74" t="n">
         <f aca="false">Z64+Z72+Z80+Z88+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="86"/>
-      <c r="B111" s="87"/>
-      <c r="C111" s="88"/>
-      <c r="D111" s="89"/>
-      <c r="E111" s="90"/>
-      <c r="F111" s="90"/>
-      <c r="G111" s="90"/>
-      <c r="H111" s="91"/>
-      <c r="I111" s="90"/>
-      <c r="J111" s="90"/>
-      <c r="K111" s="90"/>
-      <c r="L111" s="90"/>
-      <c r="M111" s="91"/>
-      <c r="N111" s="90"/>
-      <c r="O111" s="92"/>
-      <c r="P111" s="93"/>
-      <c r="Q111" s="92"/>
-      <c r="R111" s="92"/>
-      <c r="S111" s="92"/>
-      <c r="T111" s="92"/>
-      <c r="U111" s="87"/>
-      <c r="V111" s="90"/>
-      <c r="W111" s="90"/>
-      <c r="X111" s="90"/>
-      <c r="Y111" s="92"/>
-      <c r="Z111" s="92"/>
-      <c r="AA111" s="94"/>
+      <c r="A111" s="85"/>
+      <c r="B111" s="86"/>
+      <c r="C111" s="87"/>
+      <c r="D111" s="88"/>
+      <c r="E111" s="89"/>
+      <c r="F111" s="89"/>
+      <c r="G111" s="89"/>
+      <c r="H111" s="90"/>
+      <c r="I111" s="89"/>
+      <c r="J111" s="89"/>
+      <c r="K111" s="89"/>
+      <c r="L111" s="89"/>
+      <c r="M111" s="90"/>
+      <c r="N111" s="89"/>
+      <c r="O111" s="91"/>
+      <c r="P111" s="92"/>
+      <c r="Q111" s="91"/>
+      <c r="R111" s="91"/>
+      <c r="S111" s="91"/>
+      <c r="T111" s="91"/>
+      <c r="U111" s="86"/>
+      <c r="V111" s="89"/>
+      <c r="W111" s="89"/>
+      <c r="X111" s="89"/>
+      <c r="Y111" s="91"/>
+      <c r="Z111" s="91"/>
+      <c r="AA111" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -7846,37 +7911,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="95" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="95" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="95" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="95" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="95" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="95" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="95" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="95" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="95" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="95" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="95" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="94" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="94" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="94" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="94" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="94" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="94" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="94" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="94" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="94" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="94" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="94" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="96"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7888,23 +7953,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="105"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="104"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7916,21 +7981,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="105"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="104"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -7942,31 +8007,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98"/>
-      <c r="B4" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="109" t="s">
+      <c r="A4" s="97"/>
+      <c r="B4" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="103"/>
-      <c r="G4" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="109" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="103"/>
-      <c r="M4" s="111" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="111"/>
-      <c r="O4" s="105"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="109" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="108" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="102"/>
+      <c r="M4" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="110"/>
+      <c r="O4" s="104"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -7978,25 +8043,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="98"/>
-      <c r="B5" s="99" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="99" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="100"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="105"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="99"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="99"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="104"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -8008,31 +8073,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="98"/>
-      <c r="B6" s="112" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113" t="n">
+      <c r="A6" s="97"/>
+      <c r="B6" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="112" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="103"/>
-      <c r="G6" s="112" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="113" t="n">
+      <c r="F6" s="102"/>
+      <c r="G6" s="111" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="112" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="103"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="111"/>
-      <c r="O6" s="105"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="104"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -8044,31 +8109,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="98"/>
-      <c r="B7" s="112" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="113" t="n">
+      <c r="A7" s="97"/>
+      <c r="B7" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="112" t="n">
         <f aca="false">Schedule!E72</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="112" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="113" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F7" s="102"/>
+      <c r="G7" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="112" t="n">
         <f aca="false">Schedule!V19+Schedule!V72</f>
         <v>0</v>
       </c>
-      <c r="L7" s="103"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="105"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="104"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -8080,31 +8145,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="98"/>
-      <c r="B8" s="112" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="113" t="n">
+      <c r="A8" s="97"/>
+      <c r="B8" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112" t="n">
         <f aca="false">Schedule!E80</f>
         <v>0</v>
       </c>
-      <c r="F8" s="103"/>
-      <c r="G8" s="112" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="113" t="n">
+      <c r="F8" s="102"/>
+      <c r="G8" s="111" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="112" t="n">
         <f aca="false">Schedule!V27+Schedule!V80</f>
         <v>0</v>
       </c>
-      <c r="L8" s="103"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="105"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="104"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -8116,31 +8181,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="98"/>
-      <c r="B9" s="112" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113" t="n">
+      <c r="A9" s="97"/>
+      <c r="B9" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="112" t="n">
         <f aca="false">Schedule!E88</f>
         <v>0</v>
       </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="112" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="113" t="n">
+      <c r="F9" s="102"/>
+      <c r="G9" s="111" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="112" t="n">
         <f aca="false">Schedule!V35+Schedule!V88</f>
         <v>0</v>
       </c>
-      <c r="L9" s="103"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="105"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="104"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -8152,31 +8217,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="98"/>
-      <c r="B10" s="112" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113" t="n">
+      <c r="A10" s="97"/>
+      <c r="B10" s="111" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="103"/>
-      <c r="G10" s="112" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="113" t="n">
+      <c r="F10" s="102"/>
+      <c r="G10" s="111" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="112" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="103"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="105"/>
+        <v>12500</v>
+      </c>
+      <c r="L10" s="102"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="104"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8188,31 +8253,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="98"/>
-      <c r="B11" s="114" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="115" t="n">
+      <c r="A11" s="97"/>
+      <c r="B11" s="113" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="114" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="103"/>
-      <c r="G11" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="115" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F11" s="102"/>
+      <c r="G11" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="114" t="n">
         <f aca="false">SUM(K6:K10)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="103"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="111"/>
-      <c r="O11" s="105"/>
+        <v>12500</v>
+      </c>
+      <c r="L11" s="102"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="104"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8224,21 +8289,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="105"/>
+      <c r="A12" s="97"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="104"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8250,31 +8315,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="98"/>
-      <c r="B13" s="114" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="117" t="n">
+      <c r="A13" s="97"/>
+      <c r="B13" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="116" t="n">
         <f aca="false">[2]Mar!$AB$2</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="103"/>
-      <c r="G13" s="116" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="117" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F13" s="102"/>
+      <c r="G13" s="115" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="116" t="n">
         <f aca="false">[3]Mar!$V$2</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="103"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="105"/>
+        <v>12500</v>
+      </c>
+      <c r="L13" s="102"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="104"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8286,21 +8351,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="105"/>
+      <c r="A14" s="97"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="104"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8312,33 +8377,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="98"/>
-      <c r="B15" s="118" t="str">
+      <c r="A15" s="97"/>
+      <c r="B15" s="117" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119" t="n">
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="118" t="n">
         <f aca="false">E13-E11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="103"/>
-      <c r="G15" s="118" t="str">
+      <c r="F15" s="102"/>
+      <c r="G15" s="117" t="str">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="119" t="n">
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="118" t="n">
         <f aca="false">K13-K11</f>
         <v>0</v>
       </c>
-      <c r="L15" s="103"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="105"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="104"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8350,21 +8415,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="120"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="125"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="126"/>
+      <c r="A16" s="119"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="124"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="125"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8416,122 +8481,122 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="126" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="126" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="127" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="126" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="126" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="129"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="129"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="128"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="129"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="133" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="n">
+      <c r="A2" s="128"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="132" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133" t="n">
         <f aca="false">SUM(E8:E14)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="129"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="128"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="129"/>
-      <c r="B3" s="137" t="s">
-        <v>59</v>
+      <c r="A3" s="128"/>
+      <c r="B3" s="136" t="s">
+        <v>63</v>
       </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="129"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="129"/>
-      <c r="B4" s="52"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="49"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="129"/>
-    </row>
-    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="140"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="128"/>
+    </row>
+    <row r="5" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="139"/>
       <c r="B5" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="141" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="141" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="141" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E5" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="140" t="s">
+        <v>69</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="141" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
+        <v>70</v>
+      </c>
+      <c r="I5" s="140" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
       <c r="L5" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="140"/>
-    </row>
-    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="140"/>
+        <v>72</v>
+      </c>
+      <c r="M5" s="139"/>
+    </row>
+    <row r="6" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="139"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8539,273 +8604,273 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6" s="141" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" s="141" t="s">
-        <v>71</v>
+      <c r="I6" s="140" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="140" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="140" t="s">
+        <v>75</v>
       </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="140"/>
+      <c r="M6" s="139"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="129"/>
-      <c r="B7" s="52"/>
+      <c r="A7" s="128"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="134"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="129"/>
+      <c r="M7" s="128"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="129"/>
+      <c r="A8" s="128"/>
       <c r="B8" s="54"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="135" t="str">
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="134" t="str">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="135" t="str">
+      <c r="J8" s="134" t="str">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="135" t="str">
+      <c r="K8" s="134" t="str">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="129"/>
+      <c r="M8" s="128"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="129"/>
-      <c r="B9" s="52"/>
+      <c r="A9" s="128"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="129"/>
+      <c r="M9" s="128"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="129"/>
+      <c r="A10" s="128"/>
       <c r="B10" s="54"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="143"/>
-      <c r="I10" s="135" t="e">
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="135" t="str">
+      <c r="J10" s="134" t="str">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="135" t="str">
+      <c r="K10" s="134" t="str">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="129"/>
+      <c r="M10" s="128"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="129"/>
-      <c r="B11" s="52"/>
+      <c r="A11" s="128"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="129"/>
+      <c r="M11" s="128"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="129"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="135" t="e">
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="135" t="str">
+      <c r="J12" s="134" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="135" t="str">
+      <c r="K12" s="134" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="129"/>
+      <c r="M12" s="128"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="129"/>
-      <c r="B13" s="52"/>
+      <c r="A13" s="128"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="129"/>
+      <c r="M13" s="128"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="129"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="135" t="e">
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="135" t="str">
+      <c r="J14" s="134" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="135" t="str">
+      <c r="K14" s="134" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="129"/>
+      <c r="M14" s="128"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="129"/>
-      <c r="B15" s="52"/>
+      <c r="A15" s="128"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="129"/>
+      <c r="M15" s="128"/>
     </row>
     <row r="16" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="129"/>
-      <c r="B16" s="99"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="101"/>
-      <c r="M16" s="129"/>
+      <c r="A16" s="128"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="128"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="129"/>
-      <c r="B17" s="137" t="s">
-        <v>72</v>
+      <c r="A17" s="128"/>
+      <c r="B17" s="136" t="s">
+        <v>76</v>
       </c>
       <c r="C17" s="62"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
       <c r="H17" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" s="132"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
+        <v>77</v>
+      </c>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="129"/>
+      <c r="M17" s="128"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="129"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="128"/>
+      <c r="B18" s="49"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
       <c r="L18" s="62"/>
-      <c r="M18" s="129"/>
-    </row>
-    <row r="19" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="140"/>
+      <c r="M18" s="128"/>
+    </row>
+    <row r="19" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="139"/>
       <c r="B19" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="141" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="141" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19" s="141" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E19" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="140" t="s">
+        <v>69</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" s="141" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
+        <v>70</v>
+      </c>
+      <c r="I19" s="140" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="140"/>
+      <c r="K19" s="140"/>
       <c r="L19" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="M19" s="140"/>
-    </row>
-    <row r="20" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="140"/>
+        <v>72</v>
+      </c>
+      <c r="M19" s="139"/>
+    </row>
+    <row r="20" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="139"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8813,203 +8878,203 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
-      <c r="I20" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="J20" s="141" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="141" t="s">
-        <v>71</v>
+      <c r="I20" s="140" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="140" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" s="140" t="s">
+        <v>75</v>
       </c>
       <c r="L20" s="21"/>
-      <c r="M20" s="140"/>
-    </row>
-    <row r="21" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="140"/>
-      <c r="B21" s="144"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="144"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="145"/>
-      <c r="J21" s="145"/>
-      <c r="K21" s="145"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="140"/>
+      <c r="M20" s="139"/>
+    </row>
+    <row r="21" s="141" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="139"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="143"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="139"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="129"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="135" t="str">
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="134" t="str">
         <f aca="false">IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="135" t="str">
+      <c r="J22" s="134" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="135" t="str">
+      <c r="K22" s="134" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="129"/>
+      <c r="M22" s="128"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="129"/>
-      <c r="B23" s="52"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="49"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="135"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="129"/>
+      <c r="M23" s="128"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="129"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="135" t="e">
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="142"/>
+      <c r="I24" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="135" t="str">
+      <c r="J24" s="134" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="135" t="str">
+      <c r="K24" s="134" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="129"/>
+      <c r="M24" s="128"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="129"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="128"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="135"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="129"/>
+      <c r="M25" s="128"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="129"/>
+      <c r="A26" s="128"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="135" t="e">
+      <c r="E26" s="133"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="135" t="str">
+      <c r="J26" s="134" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="135" t="str">
+      <c r="K26" s="134" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="129"/>
+      <c r="M26" s="128"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="129"/>
-      <c r="B27" s="52"/>
+      <c r="A27" s="128"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="134"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="134"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="129"/>
+      <c r="M27" s="128"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="129"/>
+      <c r="A28" s="128"/>
       <c r="B28" s="54"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="134"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="143"/>
-      <c r="I28" s="135" t="e">
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="134" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="135" t="str">
+      <c r="J28" s="134" t="str">
         <f aca="false">IF(H28&gt;0,I28-K28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="135" t="str">
+      <c r="K28" s="134" t="str">
         <f aca="false">IF(H28&gt;0,G28/H28," ")</f>
         <v> </v>
       </c>
       <c r="L28" s="56"/>
-      <c r="M28" s="129"/>
+      <c r="M28" s="128"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="129"/>
-      <c r="B29" s="52"/>
+      <c r="A29" s="128"/>
+      <c r="B29" s="49"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="135"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="134"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="129"/>
+      <c r="M29" s="128"/>
     </row>
     <row r="30" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="129"/>
-      <c r="B30" s="99"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="131"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="129"/>
+      <c r="A30" s="128"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
   </si>
   <si>
-    <t xml:space="preserve">Land &amp; Property</t>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Existing Land &amp; Property</t>
@@ -250,16 +250,10 @@
     <t xml:space="preserve">Computers</t>
   </si>
   <si>
-    <t xml:space="preserve">Laptop (0.5 years old)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Existing Computers</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing over £</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Van (2.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing under £</t>
@@ -274,16 +268,10 @@
     <t xml:space="preserve">NEW FIXED ASSETS Bought AFTER </t>
   </si>
   <si>
-    <t xml:space="preserve">New Land &amp; Property</t>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
-    <t xml:space="preserve">Dell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IKEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ford</t>
+    <t xml:space="preserve">New Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">New Plant &amp; Machinery</t>
@@ -764,7 +752,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -949,6 +937,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -969,64 +969,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1385,7 +1377,7 @@
       <sheetData sheetId="9">
         <row r="4">
           <cell r="B4">
-            <v>46118</v>
+            <v>45753</v>
           </cell>
         </row>
         <row r="4">
@@ -1395,7 +1387,7 @@
         </row>
         <row r="5">
           <cell r="G5">
-            <v>0.14</v>
+            <v>0.18</v>
           </cell>
         </row>
         <row r="8">
@@ -1430,7 +1422,7 @@
         </row>
         <row r="17">
           <cell r="B17">
-            <v>46482</v>
+            <v>46117</v>
           </cell>
         </row>
         <row r="17">
@@ -1479,7 +1471,7 @@
       <sheetData sheetId="12">
         <row r="2">
           <cell r="AB2">
-            <v>32500</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -1524,7 +1516,7 @@
       <sheetData sheetId="12">
         <row r="2">
           <cell r="V2">
-            <v>12500</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -1687,30 +1679,30 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12" t="n">
         <f aca="false">E57+E110</f>
-        <v>65500</v>
+        <v>0</v>
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>10098</v>
+        <v>0</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
-        <v>22902</v>
+        <v>0</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="13" t="n">
         <f aca="false">I57+I110</f>
-        <v>11740</v>
+        <v>0</v>
       </c>
       <c r="J1" s="13" t="n">
         <f aca="false">J57+J110</f>
-        <v>21838</v>
+        <v>0</v>
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>43662</v>
+        <v>0</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1719,22 +1711,22 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13" t="n">
         <f aca="false">O57+O110</f>
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="P1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="Q1" s="13" t="n">
         <f aca="false">Q57+Q110</f>
-        <v>32500</v>
+        <v>0</v>
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="S1" s="13" t="n">
         <f aca="false">S57+S110</f>
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="T1" s="16"/>
       <c r="U1" s="17" t="s">
@@ -1742,19 +1734,19 @@
       </c>
       <c r="V1" s="13" t="n">
         <f aca="false">V57+V110</f>
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="W1" s="13" t="n">
         <f aca="false">W57+W110</f>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="X1" s="13" t="n">
         <f aca="false">X57+X110</f>
-        <v>17328</v>
+        <v>0</v>
       </c>
       <c r="Y1" s="13" t="n">
         <f aca="false">Y57+Y110</f>
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="Z1" s="13" t="n">
         <f aca="false">Z57+Z110</f>
@@ -1862,28 +1854,28 @@
       <c r="E4" s="22"/>
       <c r="F4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>46118</v>
+        <v>45753</v>
       </c>
       <c r="G4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>46118</v>
+        <v>45753</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="23"/>
       <c r="J4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46482</v>
+        <v>46117</v>
       </c>
       <c r="K4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46482</v>
+        <v>46117</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
       <c r="N4" s="13"/>
       <c r="O4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>46118</v>
+        <v>45753</v>
       </c>
       <c r="P4" s="27" t="n">
         <f aca="false">[1]Admin!$G$4</f>
@@ -1892,11 +1884,11 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="28" t="n">
         <f aca="false">[1]Admin!$G$5</f>
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="S4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46482</v>
+        <v>46117</v>
       </c>
       <c r="T4" s="16"/>
       <c r="U4" s="17"/>
@@ -1942,45 +1934,24 @@
         <v>22</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="n">
-        <f aca="false">[1]Admin!$B$4</f>
-        <v>46118</v>
-      </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42"/>
-      <c r="B7" s="51" t="s">
+      <c r="D6" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52"/>
+      <c r="E6" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="45"/>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="48" t="n">
         <f aca="false">[1]Admin!$G$13</f>
         <v>0</v>
       </c>
@@ -1988,20 +1959,20 @@
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
-      <c r="M7" s="46"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="45"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="50"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2011,7 +1982,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="50" t="str">
+      <c r="G8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -2019,39 +1990,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="50" t="str">
+      <c r="I8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="50" t="str">
+      <c r="J8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="50" t="str">
+      <c r="K8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
         <v> </v>
       </c>
-      <c r="L8" s="50"/>
+      <c r="L8" s="53"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="50" t="str">
+      <c r="W8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="50" t="str">
+      <c r="X8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2061,7 +2032,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="50" t="str">
+      <c r="G9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -2069,39 +2040,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="50" t="str">
+      <c r="I9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="50" t="str">
+      <c r="J9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="50" t="str">
+      <c r="K9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
         <v> </v>
       </c>
-      <c r="L9" s="50"/>
+      <c r="L9" s="53"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
+      <c r="T9" s="50"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="50" t="str">
+      <c r="W9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="50" t="str">
+      <c r="X9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="50"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2111,7 +2082,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="50" t="str">
+      <c r="G10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -2119,39 +2090,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="50" t="str">
+      <c r="I10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="50" t="str">
+      <c r="J10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="50" t="str">
+      <c r="K10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
         <v> </v>
       </c>
-      <c r="L10" s="50"/>
+      <c r="L10" s="53"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="50" t="str">
+      <c r="W10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="50" t="str">
+      <c r="X10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
+      <c r="Y10" s="50"/>
+      <c r="Z10" s="50"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2186,9 +2157,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="50"/>
+      <c r="L11" s="53"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="50"/>
+      <c r="N11" s="53"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -2206,8 +2177,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="47"/>
-      <c r="U11" s="49"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="52"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2235,62 +2206,62 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="53"/>
+      <c r="W12" s="53"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="53"/>
+      <c r="Z12" s="53"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="66" t="n">
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="67" t="n">
         <f aca="false">[1]Admin!$G$14</f>
         <v>0.1</v>
       </c>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="52"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="53"/>
+      <c r="X13" s="53"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="50"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2300,7 +2271,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="50" t="str">
+      <c r="G14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2308,48 +2279,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="50" t="str">
+      <c r="I14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="50" t="str">
+      <c r="J14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="50" t="str">
+      <c r="K14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
         <v> </v>
       </c>
-      <c r="L14" s="50"/>
+      <c r="L14" s="53"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47" t="str">
+      <c r="N14" s="53"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="47" t="str">
+      <c r="S14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="47"/>
+      <c r="T14" s="50"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="50" t="str">
+      <c r="W14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="50" t="str">
+      <c r="X14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="47" t="str">
+      <c r="Y14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="47" t="str">
+      <c r="Z14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2362,7 +2333,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="50" t="str">
+      <c r="G15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2370,48 +2341,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="50" t="str">
+      <c r="I15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="50" t="str">
+      <c r="J15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="50" t="str">
+      <c r="K15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
         <v> </v>
       </c>
-      <c r="L15" s="50"/>
+      <c r="L15" s="53"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47" t="str">
+      <c r="N15" s="53"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="47" t="str">
+      <c r="S15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="47"/>
+      <c r="T15" s="50"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="50" t="str">
+      <c r="W15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="50" t="str">
+      <c r="X15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="47" t="str">
+      <c r="Y15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="47" t="str">
+      <c r="Z15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2424,7 +2395,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="50" t="str">
+      <c r="G16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2432,48 +2403,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="50" t="str">
+      <c r="I16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="50" t="str">
+      <c r="J16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="50" t="str">
+      <c r="K16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
         <v> </v>
       </c>
-      <c r="L16" s="50"/>
+      <c r="L16" s="53"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47" t="str">
+      <c r="N16" s="53"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="47" t="str">
+      <c r="S16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="47"/>
+      <c r="T16" s="50"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="50" t="str">
+      <c r="W16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="50" t="str">
+      <c r="X16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="47" t="str">
+      <c r="Y16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="47" t="str">
+      <c r="Z16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2486,7 +2457,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="50" t="str">
+      <c r="G17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2494,48 +2465,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="50" t="str">
+      <c r="I17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="50" t="str">
+      <c r="J17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="50" t="str">
+      <c r="K17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
         <v> </v>
       </c>
-      <c r="L17" s="50"/>
+      <c r="L17" s="53"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47" t="str">
+      <c r="N17" s="53"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="47" t="str">
+      <c r="S17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="47"/>
+      <c r="T17" s="50"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="50" t="str">
+      <c r="W17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="50" t="str">
+      <c r="X17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="47" t="str">
+      <c r="Y17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="47" t="str">
+      <c r="Z17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2548,7 +2519,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="50" t="str">
+      <c r="G18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2556,48 +2527,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="50" t="str">
+      <c r="I18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="50" t="str">
+      <c r="J18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="50" t="str">
+      <c r="K18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
         <v> </v>
       </c>
-      <c r="L18" s="50"/>
+      <c r="L18" s="53"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47" t="str">
+      <c r="N18" s="53"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="47" t="str">
+      <c r="S18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="47"/>
+      <c r="T18" s="50"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="50" t="str">
+      <c r="W18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="50" t="str">
+      <c r="X18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="47" t="str">
+      <c r="Y18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="47" t="str">
+      <c r="Z18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2635,9 +2606,9 @@
         <f aca="false">SUM(K14:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="50"/>
+      <c r="L19" s="53"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="50"/>
+      <c r="N19" s="53"/>
       <c r="O19" s="61" t="n">
         <f aca="false">SUM(O14:O18)</f>
         <v>0</v>
@@ -2655,8 +2626,8 @@
         <f aca="false">SUM(S14:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="47"/>
-      <c r="U19" s="49"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="52"/>
       <c r="V19" s="60" t="n">
         <f aca="false">SUM(V14:V18)</f>
         <v>0</v>
@@ -2684,62 +2655,62 @@
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
       <c r="H20" s="58"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
       <c r="P20" s="62"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="47"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="50"/>
-      <c r="Z20" s="50"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="50"/>
+      <c r="U20" s="52"/>
+      <c r="V20" s="53"/>
+      <c r="W20" s="53"/>
+      <c r="X20" s="53"/>
+      <c r="Y20" s="53"/>
+      <c r="Z20" s="53"/>
       <c r="AA20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="42"/>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="66"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="66" t="n">
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="67" t="n">
         <f aca="false">[1]Admin!$G$15</f>
         <v>0.2</v>
       </c>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="49"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="50"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="50"/>
+      <c r="T21" s="50"/>
+      <c r="U21" s="52"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="50"/>
+      <c r="Z21" s="50"/>
       <c r="AA21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2749,7 +2720,7 @@
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
       <c r="F22" s="57"/>
-      <c r="G22" s="50" t="str">
+      <c r="G22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,E22-F22," ")</f>
         <v> </v>
       </c>
@@ -2757,48 +2728,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I22" s="50" t="str">
+      <c r="I22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,MIN(E22*H22,G22)," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="50" t="str">
+      <c r="J22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,F22+I22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="50" t="str">
+      <c r="K22" s="53" t="str">
         <f aca="false">IF(E22&gt;0,E22-J22," ")</f>
         <v> </v>
       </c>
-      <c r="L22" s="50"/>
+      <c r="L22" s="53"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47" t="str">
+      <c r="N22" s="53"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="50" t="str">
         <f aca="false">IF(O22&gt;0,O22*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S22" s="47" t="str">
+      <c r="S22" s="50" t="str">
         <f aca="false">IF(O22&gt;0,O22-R22," ")</f>
         <v> </v>
       </c>
-      <c r="T22" s="47"/>
+      <c r="T22" s="50"/>
       <c r="U22" s="54"/>
       <c r="V22" s="57"/>
-      <c r="W22" s="50" t="str">
+      <c r="W22" s="53" t="str">
         <f aca="false">IF(V22&gt;0,E22," ")</f>
         <v> </v>
       </c>
-      <c r="X22" s="50" t="str">
+      <c r="X22" s="53" t="str">
         <f aca="false">IF(V22&gt;0,J22," ")</f>
         <v> </v>
       </c>
-      <c r="Y22" s="47" t="str">
+      <c r="Y22" s="50" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&lt;S22,S22-V22," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z22" s="47" t="str">
+      <c r="Z22" s="50" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&gt;S22,V22-S22," ")," ")</f>
         <v> </v>
       </c>
@@ -2811,7 +2782,7 @@
       <c r="D23" s="56"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="50" t="str">
+      <c r="G23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,E23-F23," ")</f>
         <v> </v>
       </c>
@@ -2819,48 +2790,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I23" s="50" t="str">
+      <c r="I23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,MIN(E23*H23,G23)," ")</f>
         <v> </v>
       </c>
-      <c r="J23" s="50" t="str">
+      <c r="J23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,F23+I23," ")</f>
         <v> </v>
       </c>
-      <c r="K23" s="50" t="str">
+      <c r="K23" s="53" t="str">
         <f aca="false">IF(E23&gt;0,E23-J23," ")</f>
         <v> </v>
       </c>
-      <c r="L23" s="50"/>
+      <c r="L23" s="53"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47" t="str">
+      <c r="N23" s="53"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="50" t="str">
         <f aca="false">IF(O23&gt;0,O23*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S23" s="47" t="str">
+      <c r="S23" s="50" t="str">
         <f aca="false">IF(O23&gt;0,O23-R23," ")</f>
         <v> </v>
       </c>
-      <c r="T23" s="47"/>
+      <c r="T23" s="50"/>
       <c r="U23" s="54"/>
       <c r="V23" s="57"/>
-      <c r="W23" s="50" t="str">
+      <c r="W23" s="53" t="str">
         <f aca="false">IF(V23&gt;0,E23," ")</f>
         <v> </v>
       </c>
-      <c r="X23" s="50" t="str">
+      <c r="X23" s="53" t="str">
         <f aca="false">IF(V23&gt;0,J23," ")</f>
         <v> </v>
       </c>
-      <c r="Y23" s="47" t="str">
+      <c r="Y23" s="50" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&lt;S23,S23-V23," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z23" s="47" t="str">
+      <c r="Z23" s="50" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&gt;S23,V23-S23," ")," ")</f>
         <v> </v>
       </c>
@@ -2873,7 +2844,7 @@
       <c r="D24" s="56"/>
       <c r="E24" s="57"/>
       <c r="F24" s="57"/>
-      <c r="G24" s="50" t="str">
+      <c r="G24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,E24-F24," ")</f>
         <v> </v>
       </c>
@@ -2881,48 +2852,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I24" s="50" t="str">
+      <c r="I24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,MIN(E24*H24,G24)," ")</f>
         <v> </v>
       </c>
-      <c r="J24" s="50" t="str">
+      <c r="J24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,F24+I24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="50" t="str">
+      <c r="K24" s="53" t="str">
         <f aca="false">IF(E24&gt;0,E24-J24," ")</f>
         <v> </v>
       </c>
-      <c r="L24" s="50"/>
+      <c r="L24" s="53"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47" t="str">
+      <c r="N24" s="53"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="50" t="str">
         <f aca="false">IF(O24&gt;0,O24*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S24" s="47" t="str">
+      <c r="S24" s="50" t="str">
         <f aca="false">IF(O24&gt;0,O24-R24," ")</f>
         <v> </v>
       </c>
-      <c r="T24" s="47"/>
+      <c r="T24" s="50"/>
       <c r="U24" s="54"/>
       <c r="V24" s="57"/>
-      <c r="W24" s="50" t="str">
+      <c r="W24" s="53" t="str">
         <f aca="false">IF(V24&gt;0,E24," ")</f>
         <v> </v>
       </c>
-      <c r="X24" s="50" t="str">
+      <c r="X24" s="53" t="str">
         <f aca="false">IF(V24&gt;0,J24," ")</f>
         <v> </v>
       </c>
-      <c r="Y24" s="47" t="str">
+      <c r="Y24" s="50" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&lt;S24,S24-V24," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z24" s="47" t="str">
+      <c r="Z24" s="50" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&gt;S24,V24-S24," ")," ")</f>
         <v> </v>
       </c>
@@ -2935,7 +2906,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="50" t="str">
+      <c r="G25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2943,48 +2914,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="50" t="str">
+      <c r="I25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="50" t="str">
+      <c r="J25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="50" t="str">
+      <c r="K25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
         <v> </v>
       </c>
-      <c r="L25" s="50"/>
+      <c r="L25" s="53"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47" t="str">
+      <c r="N25" s="53"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="47" t="str">
+      <c r="S25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="47"/>
+      <c r="T25" s="50"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="50" t="str">
+      <c r="W25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="50" t="str">
+      <c r="X25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="47" t="str">
+      <c r="Y25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="47" t="str">
+      <c r="Z25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2997,7 +2968,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="50" t="str">
+      <c r="G26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -3005,48 +2976,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="50" t="str">
+      <c r="I26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="50" t="str">
+      <c r="J26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="50" t="str">
+      <c r="K26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
         <v> </v>
       </c>
-      <c r="L26" s="50"/>
+      <c r="L26" s="53"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47" t="str">
+      <c r="N26" s="53"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="47" t="str">
+      <c r="S26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="47"/>
+      <c r="T26" s="50"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="50" t="str">
+      <c r="W26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="50" t="str">
+      <c r="X26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="47" t="str">
+      <c r="Y26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="47" t="str">
+      <c r="Z26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -3084,9 +3055,9 @@
         <f aca="false">SUM(K22:K26)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="50"/>
+      <c r="L27" s="53"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="50"/>
+      <c r="N27" s="53"/>
       <c r="O27" s="61" t="n">
         <f aca="false">SUM(O22:O26)</f>
         <v>0</v>
@@ -3104,8 +3075,8 @@
         <f aca="false">SUM(S22:S26)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="47"/>
-      <c r="U27" s="49"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="52"/>
       <c r="V27" s="60" t="n">
         <f aca="false">SUM(V22:V26)</f>
         <v>0</v>
@@ -3133,127 +3104,121 @@
       <c r="B28" s="63"/>
       <c r="C28" s="64"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
       <c r="H28" s="58"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
       <c r="P28" s="62"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="47"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="53"/>
+      <c r="W28" s="53"/>
+      <c r="X28" s="53"/>
+      <c r="Y28" s="53"/>
+      <c r="Z28" s="53"/>
       <c r="AA28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="42"/>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="66" t="n">
+      <c r="C29" s="66"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="67" t="n">
         <f aca="false">[1]Admin!$G$16</f>
         <v>0.33</v>
       </c>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="47"/>
-      <c r="Z29" s="47"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="53"/>
+      <c r="X29" s="53"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="50"/>
       <c r="AA29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="42"/>
       <c r="B30" s="54"/>
-      <c r="C30" s="55" t="s">
-        <v>30</v>
-      </c>
+      <c r="C30" s="55"/>
       <c r="D30" s="56"/>
-      <c r="E30" s="57" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F30" s="57" t="n">
-        <v>270</v>
-      </c>
-      <c r="G30" s="50" t="n">
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,E30-F30," ")</f>
-        <v>2730</v>
+        <v> </v>
       </c>
       <c r="H30" s="58" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I30" s="50" t="n">
+      <c r="I30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,MIN(E30*H30,G30)," ")</f>
-        <v>990</v>
-      </c>
-      <c r="J30" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="J30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,F30+I30," ")</f>
-        <v>1260</v>
-      </c>
-      <c r="K30" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="K30" s="53" t="str">
         <f aca="false">IF(E30&gt;0,E30-J30," ")</f>
-        <v>1740</v>
-      </c>
-      <c r="L30" s="50"/>
+        <v> </v>
+      </c>
+      <c r="L30" s="53"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47" t="str">
+      <c r="N30" s="53"/>
+      <c r="O30" s="68"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50" t="str">
         <f aca="false">IF(O30&gt;0,O30*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S30" s="47" t="str">
+      <c r="S30" s="50" t="str">
         <f aca="false">IF(O30&gt;0,O30-R30," ")</f>
         <v> </v>
       </c>
-      <c r="T30" s="47"/>
+      <c r="T30" s="50"/>
       <c r="U30" s="54"/>
       <c r="V30" s="57"/>
-      <c r="W30" s="50" t="str">
+      <c r="W30" s="53" t="str">
         <f aca="false">IF(V30&gt;0,E30," ")</f>
         <v> </v>
       </c>
-      <c r="X30" s="50" t="str">
+      <c r="X30" s="53" t="str">
         <f aca="false">IF(V30&gt;0,J30," ")</f>
         <v> </v>
       </c>
-      <c r="Y30" s="47" t="str">
+      <c r="Y30" s="50" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&lt;S30,S30-V30," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z30" s="47" t="str">
+      <c r="Z30" s="50" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&gt;S30,V30-S30," ")," ")</f>
         <v> </v>
       </c>
@@ -3266,7 +3231,7 @@
       <c r="D31" s="56"/>
       <c r="E31" s="57"/>
       <c r="F31" s="57"/>
-      <c r="G31" s="50" t="str">
+      <c r="G31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,E31-F31," ")</f>
         <v> </v>
       </c>
@@ -3274,48 +3239,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I31" s="50" t="str">
+      <c r="I31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,MIN(E31*H31,G31)," ")</f>
         <v> </v>
       </c>
-      <c r="J31" s="50" t="str">
+      <c r="J31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,F31+I31," ")</f>
         <v> </v>
       </c>
-      <c r="K31" s="50" t="str">
+      <c r="K31" s="53" t="str">
         <f aca="false">IF(E31&gt;0,E31-J31," ")</f>
         <v> </v>
       </c>
-      <c r="L31" s="50"/>
+      <c r="L31" s="53"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="47"/>
-      <c r="R31" s="47" t="str">
+      <c r="N31" s="53"/>
+      <c r="O31" s="68"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50" t="str">
         <f aca="false">IF(O31&gt;0,O31*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S31" s="47" t="str">
+      <c r="S31" s="50" t="str">
         <f aca="false">IF(O31&gt;0,O31-R31," ")</f>
         <v> </v>
       </c>
-      <c r="T31" s="47"/>
+      <c r="T31" s="50"/>
       <c r="U31" s="54"/>
       <c r="V31" s="57"/>
-      <c r="W31" s="50" t="str">
+      <c r="W31" s="53" t="str">
         <f aca="false">IF(V31&gt;0,E31," ")</f>
         <v> </v>
       </c>
-      <c r="X31" s="50" t="str">
+      <c r="X31" s="53" t="str">
         <f aca="false">IF(V31&gt;0,J31," ")</f>
         <v> </v>
       </c>
-      <c r="Y31" s="47" t="str">
+      <c r="Y31" s="50" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&lt;S31,S31-V31," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z31" s="47" t="str">
+      <c r="Z31" s="50" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&gt;S31,V31-S31," ")," ")</f>
         <v> </v>
       </c>
@@ -3328,7 +3293,7 @@
       <c r="D32" s="56"/>
       <c r="E32" s="57"/>
       <c r="F32" s="57"/>
-      <c r="G32" s="50" t="str">
+      <c r="G32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,E32-F32," ")</f>
         <v> </v>
       </c>
@@ -3336,48 +3301,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I32" s="50" t="str">
+      <c r="I32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,MIN(E32*H32,G32)," ")</f>
         <v> </v>
       </c>
-      <c r="J32" s="50" t="str">
+      <c r="J32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,F32+I32," ")</f>
         <v> </v>
       </c>
-      <c r="K32" s="50" t="str">
+      <c r="K32" s="53" t="str">
         <f aca="false">IF(E32&gt;0,E32-J32," ")</f>
         <v> </v>
       </c>
-      <c r="L32" s="50"/>
+      <c r="L32" s="53"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47" t="str">
+      <c r="N32" s="53"/>
+      <c r="O32" s="68"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50" t="str">
         <f aca="false">IF(O32&gt;0,O32*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S32" s="47" t="str">
+      <c r="S32" s="50" t="str">
         <f aca="false">IF(O32&gt;0,O32-R32," ")</f>
         <v> </v>
       </c>
-      <c r="T32" s="47"/>
+      <c r="T32" s="50"/>
       <c r="U32" s="54"/>
       <c r="V32" s="57"/>
-      <c r="W32" s="50" t="str">
+      <c r="W32" s="53" t="str">
         <f aca="false">IF(V32&gt;0,E32," ")</f>
         <v> </v>
       </c>
-      <c r="X32" s="50" t="str">
+      <c r="X32" s="53" t="str">
         <f aca="false">IF(V32&gt;0,J32," ")</f>
         <v> </v>
       </c>
-      <c r="Y32" s="47" t="str">
+      <c r="Y32" s="50" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&lt;S32,S32-V32," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z32" s="47" t="str">
+      <c r="Z32" s="50" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&gt;S32,V32-S32," ")," ")</f>
         <v> </v>
       </c>
@@ -3390,7 +3355,7 @@
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
       <c r="F33" s="57"/>
-      <c r="G33" s="50" t="str">
+      <c r="G33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
         <v> </v>
       </c>
@@ -3398,48 +3363,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="50" t="str">
+      <c r="I33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="50" t="str">
+      <c r="J33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="50" t="str">
+      <c r="K33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
         <v> </v>
       </c>
-      <c r="L33" s="50"/>
+      <c r="L33" s="53"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47" t="str">
+      <c r="N33" s="53"/>
+      <c r="O33" s="68"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="47" t="str">
+      <c r="S33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="47"/>
+      <c r="T33" s="50"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="50" t="str">
+      <c r="W33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="50" t="str">
+      <c r="X33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="47" t="str">
+      <c r="Y33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="47" t="str">
+      <c r="Z33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3452,7 +3417,7 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="50" t="str">
+      <c r="G34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
         <v> </v>
       </c>
@@ -3460,48 +3425,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="50" t="str">
+      <c r="I34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="50" t="str">
+      <c r="J34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="50" t="str">
+      <c r="K34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
         <v> </v>
       </c>
-      <c r="L34" s="50"/>
+      <c r="L34" s="53"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="67"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47" t="str">
+      <c r="N34" s="53"/>
+      <c r="O34" s="68"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="50"/>
+      <c r="R34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="47" t="str">
+      <c r="S34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="47"/>
+      <c r="T34" s="50"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="50" t="str">
+      <c r="W34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="50" t="str">
+      <c r="X34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="47" t="str">
+      <c r="Y34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="47" t="str">
+      <c r="Z34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3510,38 +3475,38 @@
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="42"/>
       <c r="B35" s="59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="59"/>
       <c r="E35" s="60" t="n">
         <f aca="false">SUM(E30:E34)</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F35" s="60" t="n">
         <f aca="false">SUM(F30:F34)</f>
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="G35" s="61" t="n">
         <f aca="false">SUM(G30:G34)</f>
-        <v>2730</v>
+        <v>0</v>
       </c>
       <c r="H35" s="58"/>
       <c r="I35" s="61" t="n">
         <f aca="false">SUM(I30:I34)</f>
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="J35" s="61" t="n">
         <f aca="false">SUM(J30:J34)</f>
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="K35" s="61" t="n">
         <f aca="false">SUM(K30:K34)</f>
-        <v>1740</v>
-      </c>
-      <c r="L35" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="53"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="50"/>
+      <c r="N35" s="53"/>
       <c r="O35" s="61" t="n">
         <f aca="false">SUM(O30:O34)</f>
         <v>0</v>
@@ -3559,8 +3524,8 @@
         <f aca="false">SUM(S30:S34)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="47"/>
-      <c r="U35" s="49"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="52"/>
       <c r="V35" s="60" t="n">
         <f aca="false">SUM(V30:V34)</f>
         <v>0</v>
@@ -3588,138 +3553,126 @@
       <c r="B36" s="63"/>
       <c r="C36" s="64"/>
       <c r="D36" s="65"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
       <c r="H36" s="58"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
       <c r="P36" s="62"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="49"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
-      <c r="Y36" s="50"/>
-      <c r="Z36" s="50"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="50"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
       <c r="AA36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="42"/>
-      <c r="B37" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="69"/>
-      <c r="D37" s="70" t="n">
+      <c r="B37" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="70"/>
+      <c r="D37" s="71" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="66" t="n">
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="67" t="n">
         <f aca="false">[1]Admin!$G$17</f>
         <v>0.25</v>
       </c>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
       <c r="P37" s="62"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="72"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="73"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="53"/>
+      <c r="W37" s="53"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
       <c r="AA37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="42"/>
       <c r="B38" s="54"/>
-      <c r="C38" s="55" t="s">
-        <v>33</v>
-      </c>
+      <c r="C38" s="55"/>
       <c r="D38" s="56"/>
-      <c r="E38" s="57" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F38" s="57" t="n">
-        <v>9828</v>
-      </c>
-      <c r="G38" s="50" t="n">
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
-        <v>20172</v>
+        <v> </v>
       </c>
       <c r="H38" s="58" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I38" s="50" t="n">
+      <c r="I38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
-        <v>7500</v>
-      </c>
-      <c r="J38" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="J38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
-        <v>17328</v>
-      </c>
-      <c r="K38" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="K38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
-        <v>12672</v>
-      </c>
-      <c r="L38" s="50"/>
-      <c r="M38" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="50"/>
-      <c r="O38" s="67" t="n">
-        <v>24000</v>
-      </c>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47" t="n">
+        <v> </v>
+      </c>
+      <c r="L38" s="53"/>
+      <c r="M38" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="53"/>
+      <c r="O38" s="68"/>
+      <c r="P38" s="51"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
-        <v>3000</v>
-      </c>
-      <c r="S38" s="47" t="n">
+        <v> </v>
+      </c>
+      <c r="S38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
-        <v>21000</v>
-      </c>
-      <c r="T38" s="47"/>
-      <c r="U38" s="54" t="n">
-        <v>45940</v>
-      </c>
-      <c r="V38" s="57" t="n">
-        <v>12500</v>
-      </c>
-      <c r="W38" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="T38" s="50"/>
+      <c r="U38" s="54"/>
+      <c r="V38" s="57"/>
+      <c r="W38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
-        <v>30000</v>
-      </c>
-      <c r="X38" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="X38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
-        <v>17328</v>
-      </c>
-      <c r="Y38" s="47" t="n">
+        <v> </v>
+      </c>
+      <c r="Y38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
-        <v>8500</v>
-      </c>
-      <c r="Z38" s="47" t="str">
+        <v> </v>
+      </c>
+      <c r="Z38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
@@ -3732,7 +3685,7 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="50" t="str">
+      <c r="G39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
         <v> </v>
       </c>
@@ -3740,50 +3693,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I39" s="50" t="str">
+      <c r="I39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="50" t="str">
+      <c r="J39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="50" t="str">
+      <c r="K39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
         <v> </v>
       </c>
-      <c r="L39" s="50"/>
-      <c r="M39" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="50"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="47" t="str">
+      <c r="L39" s="53"/>
+      <c r="M39" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="53"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="47" t="str">
+      <c r="S39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="47"/>
+      <c r="T39" s="50"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="50" t="str">
+      <c r="W39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="50" t="str">
+      <c r="X39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="47" t="str">
+      <c r="Y39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,(S39-V39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="47" t="str">
+      <c r="Z39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,(V39-S39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
@@ -3796,7 +3749,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="50" t="str">
+      <c r="G40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
         <v> </v>
       </c>
@@ -3804,50 +3757,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I40" s="50" t="str">
+      <c r="I40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="50" t="str">
+      <c r="J40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="50" t="str">
+      <c r="K40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
         <v> </v>
       </c>
-      <c r="L40" s="50"/>
-      <c r="M40" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="50"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="47"/>
-      <c r="R40" s="47" t="str">
+      <c r="L40" s="53"/>
+      <c r="M40" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="53"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="47" t="str">
+      <c r="S40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="47"/>
+      <c r="T40" s="50"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="50" t="str">
+      <c r="W40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="50" t="str">
+      <c r="X40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="47" t="str">
+      <c r="Y40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,(S40-V40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="47" t="str">
+      <c r="Z40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,(V40-S40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
@@ -3860,7 +3813,7 @@
       <c r="D41" s="56"/>
       <c r="E41" s="57"/>
       <c r="F41" s="57"/>
-      <c r="G41" s="50" t="str">
+      <c r="G41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,E41-F41," ")</f>
         <v> </v>
       </c>
@@ -3868,50 +3821,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I41" s="50" t="str">
+      <c r="I41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,MIN(E41*H41,G41)," ")</f>
         <v> </v>
       </c>
-      <c r="J41" s="50" t="str">
+      <c r="J41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,F41+I41," ")</f>
         <v> </v>
       </c>
-      <c r="K41" s="50" t="str">
+      <c r="K41" s="53" t="str">
         <f aca="false">IF(E41&gt;0,E41-J41," ")</f>
         <v> </v>
       </c>
-      <c r="L41" s="50"/>
-      <c r="M41" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="50"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="47"/>
-      <c r="R41" s="47" t="str">
+      <c r="L41" s="53"/>
+      <c r="M41" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="53"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="51"/>
+      <c r="Q41" s="50"/>
+      <c r="R41" s="50" t="str">
         <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
         <v> </v>
       </c>
-      <c r="S41" s="47" t="str">
+      <c r="S41" s="50" t="str">
         <f aca="false">IF(O41&gt;0,O41-R41," ")</f>
         <v> </v>
       </c>
-      <c r="T41" s="47"/>
+      <c r="T41" s="50"/>
       <c r="U41" s="54"/>
       <c r="V41" s="57"/>
-      <c r="W41" s="50" t="str">
+      <c r="W41" s="53" t="str">
         <f aca="false">IF(V41&gt;0,E41," ")</f>
         <v> </v>
       </c>
-      <c r="X41" s="50" t="str">
+      <c r="X41" s="53" t="str">
         <f aca="false">IF(V41&gt;0,J41," ")</f>
         <v> </v>
       </c>
-      <c r="Y41" s="47" t="str">
+      <c r="Y41" s="50" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&lt;S41,(S41-V41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z41" s="47" t="str">
+      <c r="Z41" s="50" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&gt;S41,(V41-S41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
@@ -3924,7 +3877,7 @@
       <c r="D42" s="56"/>
       <c r="E42" s="57"/>
       <c r="F42" s="57"/>
-      <c r="G42" s="50" t="str">
+      <c r="G42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,E42-F42," ")</f>
         <v> </v>
       </c>
@@ -3932,50 +3885,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I42" s="50" t="str">
+      <c r="I42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,MIN(E42*H42,G42)," ")</f>
         <v> </v>
       </c>
-      <c r="J42" s="50" t="str">
+      <c r="J42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,F42+I42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="50" t="str">
+      <c r="K42" s="53" t="str">
         <f aca="false">IF(E42&gt;0,E42-J42," ")</f>
         <v> </v>
       </c>
-      <c r="L42" s="50"/>
-      <c r="M42" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="50"/>
-      <c r="O42" s="67"/>
-      <c r="P42" s="48"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47" t="str">
+      <c r="L42" s="53"/>
+      <c r="M42" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="53"/>
+      <c r="O42" s="68"/>
+      <c r="P42" s="51"/>
+      <c r="Q42" s="50"/>
+      <c r="R42" s="50" t="str">
         <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
         <v> </v>
       </c>
-      <c r="S42" s="47" t="str">
+      <c r="S42" s="50" t="str">
         <f aca="false">IF(O42&gt;0,O42-R42," ")</f>
         <v> </v>
       </c>
-      <c r="T42" s="47"/>
+      <c r="T42" s="50"/>
       <c r="U42" s="54"/>
       <c r="V42" s="57"/>
-      <c r="W42" s="50" t="str">
+      <c r="W42" s="53" t="str">
         <f aca="false">IF(V42&gt;0,E42," ")</f>
         <v> </v>
       </c>
-      <c r="X42" s="50" t="str">
+      <c r="X42" s="53" t="str">
         <f aca="false">IF(V42&gt;0,J42," ")</f>
         <v> </v>
       </c>
-      <c r="Y42" s="47" t="str">
+      <c r="Y42" s="50" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&lt;S42,(S42-V42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z42" s="47" t="str">
+      <c r="Z42" s="50" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&gt;S42,(V42-S42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
@@ -3983,36 +3936,36 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="69"/>
-      <c r="D43" s="70" t="n">
+      <c r="B43" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="70"/>
+      <c r="D43" s="71" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
       <c r="H43" s="58"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
       <c r="M43" s="58"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="47"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="47"/>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="47"/>
-      <c r="Z43" s="47"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="51"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="53"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="50"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4022,7 +3975,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="50" t="str">
+      <c r="G44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
         <v> </v>
       </c>
@@ -4030,50 +3983,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="50" t="str">
+      <c r="I44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="50" t="str">
+      <c r="J44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="50" t="str">
+      <c r="K44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
         <v> </v>
       </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="50"/>
-      <c r="O44" s="67"/>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47" t="str">
+      <c r="L44" s="53"/>
+      <c r="M44" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="53"/>
+      <c r="O44" s="68"/>
+      <c r="P44" s="51"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="47" t="str">
+      <c r="S44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="47"/>
+      <c r="T44" s="50"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="50" t="str">
+      <c r="W44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="50" t="str">
+      <c r="X44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="47" t="str">
+      <c r="Y44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="47" t="str">
+      <c r="Z44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -4086,7 +4039,7 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="50" t="str">
+      <c r="G45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
         <v> </v>
       </c>
@@ -4094,50 +4047,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="50" t="str">
+      <c r="I45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="50" t="str">
+      <c r="J45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="50" t="str">
+      <c r="K45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
         <v> </v>
       </c>
-      <c r="L45" s="50"/>
-      <c r="M45" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="50"/>
-      <c r="O45" s="67"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47" t="str">
+      <c r="L45" s="53"/>
+      <c r="M45" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="53"/>
+      <c r="O45" s="68"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="47" t="str">
+      <c r="S45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="47"/>
+      <c r="T45" s="50"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="50" t="str">
+      <c r="W45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="50" t="str">
+      <c r="X45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="47" t="str">
+      <c r="Y45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="47" t="str">
+      <c r="Z45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -4150,7 +4103,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="50" t="str">
+      <c r="G46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -4158,50 +4111,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="50" t="str">
+      <c r="I46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="50" t="str">
+      <c r="J46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="50" t="str">
+      <c r="K46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
         <v> </v>
       </c>
-      <c r="L46" s="50"/>
-      <c r="M46" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="50"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47" t="str">
+      <c r="L46" s="53"/>
+      <c r="M46" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="53"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="51"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="47" t="str">
+      <c r="S46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="47"/>
+      <c r="T46" s="50"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="50" t="str">
+      <c r="W46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="50" t="str">
+      <c r="X46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="47" t="str">
+      <c r="Y46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="47" t="str">
+      <c r="Z46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -4214,7 +4167,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="50" t="str">
+      <c r="G47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -4222,50 +4175,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="50" t="str">
+      <c r="I47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="50" t="str">
+      <c r="J47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="50" t="str">
+      <c r="K47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
         <v> </v>
       </c>
-      <c r="L47" s="50"/>
-      <c r="M47" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="50"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="48"/>
-      <c r="Q47" s="47"/>
-      <c r="R47" s="47" t="str">
+      <c r="L47" s="53"/>
+      <c r="M47" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="53"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="51"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="47" t="str">
+      <c r="S47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="47"/>
+      <c r="T47" s="50"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="50" t="str">
+      <c r="W47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="50" t="str">
+      <c r="X47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="47" t="str">
+      <c r="Y47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="47" t="str">
+      <c r="Z47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4278,7 +4231,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="50" t="str">
+      <c r="G48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4286,50 +4239,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="50" t="str">
+      <c r="I48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="50" t="str">
+      <c r="J48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="50" t="str">
+      <c r="K48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
         <v> </v>
       </c>
-      <c r="L48" s="50"/>
-      <c r="M48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="50"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47" t="str">
+      <c r="L48" s="53"/>
+      <c r="M48" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="53"/>
+      <c r="O48" s="68"/>
+      <c r="P48" s="51"/>
+      <c r="Q48" s="50"/>
+      <c r="R48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="47" t="str">
+      <c r="S48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="47"/>
+      <c r="T48" s="50"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="50" t="str">
+      <c r="W48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="50" t="str">
+      <c r="X48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="47" t="str">
+      <c r="Y48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="47" t="str">
+      <c r="Z48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4337,33 +4290,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="51"/>
+      <c r="B49" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="66"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="47"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="47"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="49"/>
-      <c r="V49" s="50"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="50"/>
-      <c r="Y49" s="47"/>
-      <c r="Z49" s="47"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="50"/>
+      <c r="P49" s="51"/>
+      <c r="Q49" s="50"/>
+      <c r="R49" s="50"/>
+      <c r="S49" s="50"/>
+      <c r="T49" s="50"/>
+      <c r="U49" s="52"/>
+      <c r="V49" s="53"/>
+      <c r="W49" s="53"/>
+      <c r="X49" s="53"/>
+      <c r="Y49" s="50"/>
+      <c r="Z49" s="50"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4373,7 +4326,7 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="50" t="str">
+      <c r="G50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
         <v> </v>
       </c>
@@ -4381,50 +4334,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="50" t="str">
+      <c r="I50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="50" t="str">
+      <c r="J50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="50" t="str">
+      <c r="K50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
         <v> </v>
       </c>
-      <c r="L50" s="50"/>
-      <c r="M50" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="50"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47" t="str">
+      <c r="L50" s="53"/>
+      <c r="M50" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="53"/>
+      <c r="O50" s="68"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="50"/>
+      <c r="R50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,O50*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="47" t="str">
+      <c r="S50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="47"/>
+      <c r="T50" s="50"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="50" t="str">
+      <c r="W50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="50" t="str">
+      <c r="X50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="47" t="str">
+      <c r="Y50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="47" t="str">
+      <c r="Z50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4437,7 +4390,7 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="50" t="str">
+      <c r="G51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
         <v> </v>
       </c>
@@ -4445,50 +4398,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="50" t="str">
+      <c r="I51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="50" t="str">
+      <c r="J51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="50" t="str">
+      <c r="K51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
         <v> </v>
       </c>
-      <c r="L51" s="50"/>
-      <c r="M51" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="50"/>
-      <c r="O51" s="67"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47" t="str">
+      <c r="L51" s="53"/>
+      <c r="M51" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="53"/>
+      <c r="O51" s="68"/>
+      <c r="P51" s="51"/>
+      <c r="Q51" s="50"/>
+      <c r="R51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,O51*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="47" t="str">
+      <c r="S51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="47"/>
+      <c r="T51" s="50"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="50" t="str">
+      <c r="W51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="50" t="str">
+      <c r="X51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="47" t="str">
+      <c r="Y51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="47" t="str">
+      <c r="Z51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4501,7 +4454,7 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="50" t="str">
+      <c r="G52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
         <v> </v>
       </c>
@@ -4509,50 +4462,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="50" t="str">
+      <c r="I52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="50" t="str">
+      <c r="J52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="50" t="str">
+      <c r="K52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
         <v> </v>
       </c>
-      <c r="L52" s="50"/>
-      <c r="M52" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="50"/>
-      <c r="O52" s="67"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47" t="str">
+      <c r="L52" s="53"/>
+      <c r="M52" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="53"/>
+      <c r="O52" s="68"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="50"/>
+      <c r="R52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,O52*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="47" t="str">
+      <c r="S52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="47"/>
+      <c r="T52" s="50"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="50" t="str">
+      <c r="W52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="50" t="str">
+      <c r="X52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="47" t="str">
+      <c r="Y52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="47" t="str">
+      <c r="Z52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4565,7 +4518,7 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="50" t="str">
+      <c r="G53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
         <v> </v>
       </c>
@@ -4573,50 +4526,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="50" t="str">
+      <c r="I53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="50" t="str">
+      <c r="J53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="50" t="str">
+      <c r="K53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
         <v> </v>
       </c>
-      <c r="L53" s="50"/>
-      <c r="M53" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="50"/>
-      <c r="O53" s="67"/>
-      <c r="P53" s="48"/>
-      <c r="Q53" s="47"/>
-      <c r="R53" s="47" t="str">
+      <c r="L53" s="53"/>
+      <c r="M53" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="53"/>
+      <c r="O53" s="68"/>
+      <c r="P53" s="51"/>
+      <c r="Q53" s="50"/>
+      <c r="R53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,O53*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="47" t="str">
+      <c r="S53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="47"/>
+      <c r="T53" s="50"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="50" t="str">
+      <c r="W53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="50" t="str">
+      <c r="X53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="47" t="str">
+      <c r="Y53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="47" t="str">
+      <c r="Z53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4629,7 +4582,7 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="50" t="str">
+      <c r="G54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
         <v> </v>
       </c>
@@ -4637,50 +4590,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="50" t="str">
+      <c r="I54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="50" t="str">
+      <c r="J54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="50" t="str">
+      <c r="K54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
         <v> </v>
       </c>
-      <c r="L54" s="50"/>
-      <c r="M54" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="50"/>
-      <c r="O54" s="67"/>
-      <c r="P54" s="48"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47" t="str">
+      <c r="L54" s="53"/>
+      <c r="M54" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="53"/>
+      <c r="O54" s="68"/>
+      <c r="P54" s="51"/>
+      <c r="Q54" s="50"/>
+      <c r="R54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,O54*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="47" t="str">
+      <c r="S54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="47"/>
+      <c r="T54" s="50"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="50" t="str">
+      <c r="W54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="50" t="str">
+      <c r="X54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="47" t="str">
+      <c r="Y54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="47" t="str">
+      <c r="Z54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4689,41 +4642,41 @@
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="42"/>
       <c r="B55" s="59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C55" s="59"/>
       <c r="D55" s="59"/>
       <c r="E55" s="61" t="n">
         <f aca="false">SUM(E38:E54)</f>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="F55" s="61" t="n">
         <f aca="false">SUM(F38:F54)</f>
-        <v>9828</v>
+        <v>0</v>
       </c>
       <c r="G55" s="61" t="n">
         <f aca="false">SUM(G38:G54)</f>
-        <v>20172</v>
+        <v>0</v>
       </c>
       <c r="H55" s="58"/>
       <c r="I55" s="61" t="n">
         <f aca="false">SUM(I38:I54)</f>
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="J55" s="61" t="n">
         <f aca="false">SUM(J38:J54)</f>
-        <v>17328</v>
+        <v>0</v>
       </c>
       <c r="K55" s="61" t="n">
         <f aca="false">SUM(K38:K54)</f>
-        <v>12672</v>
-      </c>
-      <c r="L55" s="50"/>
-      <c r="M55" s="71"/>
-      <c r="N55" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="53"/>
+      <c r="M55" s="72"/>
+      <c r="N55" s="53"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O38:O54)</f>
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="P55" s="62"/>
       <c r="Q55" s="61" t="n">
@@ -4732,29 +4685,29 @@
       </c>
       <c r="R55" s="61" t="n">
         <f aca="false">SUM(R38:R54)</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="S55" s="61" t="n">
         <f aca="false">SUM(S38:S54)</f>
-        <v>21000</v>
-      </c>
-      <c r="T55" s="50"/>
-      <c r="U55" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="53"/>
+      <c r="U55" s="52"/>
       <c r="V55" s="61" t="n">
         <f aca="false">SUM(V38:V54)</f>
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="W55" s="61" t="n">
         <f aca="false">SUM(W38:W54)</f>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="X55" s="61" t="n">
         <f aca="false">SUM(X38:X54)</f>
-        <v>17328</v>
+        <v>0</v>
       </c>
       <c r="Y55" s="61" t="n">
         <f aca="false">SUM(Y38:Y54)</f>
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="61" t="n">
         <f aca="false">SUM(Z38:Z54)</f>
@@ -4764,31 +4717,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="73"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="74"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="50"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="47"/>
-      <c r="P56" s="48"/>
-      <c r="Q56" s="47"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47"/>
-      <c r="T56" s="47"/>
-      <c r="U56" s="49"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="47"/>
-      <c r="X56" s="47"/>
-      <c r="Y56" s="47"/>
-      <c r="Z56" s="47"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="50"/>
+      <c r="P56" s="51"/>
+      <c r="Q56" s="50"/>
+      <c r="R56" s="50"/>
+      <c r="S56" s="50"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="52"/>
+      <c r="V56" s="53"/>
+      <c r="W56" s="50"/>
+      <c r="X56" s="50"/>
+      <c r="Y56" s="50"/>
+      <c r="Z56" s="50"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4798,74 +4751,74 @@
         <v>EXISTING FIXED ASSETS at </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="44" t="n">
+      <c r="D57" s="44" t="str">
         <f aca="false">D6</f>
-        <v>46118</v>
-      </c>
-      <c r="E57" s="74" t="n">
+        <v>Laptop (0.5 years old)</v>
+      </c>
+      <c r="E57" s="75" t="n">
         <f aca="false">E11+E19+E27+E35+E55</f>
-        <v>33000</v>
-      </c>
-      <c r="F57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="75" t="n">
         <f aca="false">F11+F19+F27+F35+F55</f>
-        <v>10098</v>
-      </c>
-      <c r="G57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="75" t="n">
         <f aca="false">G11+G19+G27+G35+G55</f>
-        <v>22902</v>
+        <v>0</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="74" t="n">
+      <c r="I57" s="75" t="n">
         <f aca="false">I11+I19+I27+I35+I55</f>
-        <v>8490</v>
-      </c>
-      <c r="J57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="75" t="n">
         <f aca="false">J11+J19+J27+J35+J55</f>
-        <v>18588</v>
-      </c>
-      <c r="K57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="75" t="n">
         <f aca="false">K11+K19+K27+K35+K55</f>
-        <v>14412</v>
-      </c>
-      <c r="L57" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="53"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="74" t="n">
+      <c r="N57" s="53"/>
+      <c r="O57" s="75" t="n">
         <f aca="false">O11+O19+O27+O35+O55</f>
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="74" t="n">
+      <c r="Q57" s="75" t="n">
         <f aca="false">Q11+Q19+Q27+Q35+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="74" t="n">
+      <c r="R57" s="75" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
-        <v>3000</v>
-      </c>
-      <c r="S57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="75" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
-        <v>21000</v>
-      </c>
-      <c r="T57" s="47"/>
-      <c r="U57" s="49"/>
-      <c r="V57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="50"/>
+      <c r="U57" s="52"/>
+      <c r="V57" s="75" t="n">
         <f aca="false">V11+V19+V27+V35+V55</f>
-        <v>12500</v>
-      </c>
-      <c r="W57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="75" t="n">
         <f aca="false">W11+W19+W27+W35+W55</f>
-        <v>30000</v>
-      </c>
-      <c r="X57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="75" t="n">
         <f aca="false">X11+X19+X27+X35+X55</f>
-        <v>17328</v>
-      </c>
-      <c r="Y57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="75" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
-        <v>8500</v>
-      </c>
-      <c r="Z57" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="75" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
         <v>0</v>
       </c>
@@ -4873,78 +4826,78 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="75"/>
-      <c r="C58" s="76"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="50"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="47"/>
-      <c r="P58" s="48"/>
-      <c r="Q58" s="47"/>
-      <c r="R58" s="47"/>
-      <c r="S58" s="47"/>
-      <c r="T58" s="47"/>
-      <c r="U58" s="49"/>
-      <c r="V58" s="50"/>
-      <c r="W58" s="50"/>
-      <c r="X58" s="50"/>
-      <c r="Y58" s="47"/>
-      <c r="Z58" s="47"/>
+      <c r="N58" s="53"/>
+      <c r="O58" s="50"/>
+      <c r="P58" s="51"/>
+      <c r="Q58" s="50"/>
+      <c r="R58" s="50"/>
+      <c r="S58" s="50"/>
+      <c r="T58" s="50"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="53"/>
+      <c r="W58" s="53"/>
+      <c r="X58" s="53"/>
+      <c r="Y58" s="50"/>
+      <c r="Z58" s="50"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
       <c r="B59" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>46118</v>
-      </c>
-      <c r="E59" s="47"/>
-      <c r="F59" s="78"/>
-      <c r="G59" s="78"/>
+        <v>45753</v>
+      </c>
+      <c r="E59" s="50"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
-      <c r="L59" s="47"/>
+      <c r="I59" s="50"/>
+      <c r="J59" s="50"/>
+      <c r="K59" s="50"/>
+      <c r="L59" s="50"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="47"/>
-      <c r="O59" s="47"/>
-      <c r="P59" s="48"/>
-      <c r="Q59" s="47"/>
-      <c r="R59" s="47"/>
-      <c r="S59" s="47"/>
-      <c r="T59" s="47"/>
-      <c r="U59" s="49"/>
-      <c r="V59" s="50"/>
-      <c r="W59" s="50"/>
-      <c r="X59" s="50"/>
-      <c r="Y59" s="47"/>
-      <c r="Z59" s="47"/>
+      <c r="N59" s="50"/>
+      <c r="O59" s="50"/>
+      <c r="P59" s="51"/>
+      <c r="Q59" s="50"/>
+      <c r="R59" s="50"/>
+      <c r="S59" s="50"/>
+      <c r="T59" s="50"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="53"/>
+      <c r="W59" s="53"/>
+      <c r="X59" s="53"/>
+      <c r="Y59" s="50"/>
+      <c r="Z59" s="50"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="51"/>
-      <c r="D60" s="52"/>
+      <c r="B60" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="66"/>
+      <c r="D60" s="47"/>
       <c r="E60" s="45"/>
-      <c r="F60" s="78"/>
-      <c r="G60" s="78"/>
-      <c r="H60" s="79" t="n">
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="80" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
@@ -4954,165 +4907,165 @@
       <c r="L60" s="45"/>
       <c r="M60" s="58"/>
       <c r="N60" s="45"/>
-      <c r="O60" s="47"/>
-      <c r="P60" s="48"/>
-      <c r="Q60" s="47"/>
-      <c r="R60" s="47"/>
-      <c r="S60" s="47"/>
-      <c r="T60" s="47"/>
-      <c r="U60" s="49"/>
-      <c r="V60" s="50"/>
-      <c r="W60" s="50"/>
-      <c r="X60" s="50"/>
-      <c r="Y60" s="47"/>
-      <c r="Z60" s="47"/>
+      <c r="O60" s="50"/>
+      <c r="P60" s="51"/>
+      <c r="Q60" s="50"/>
+      <c r="R60" s="50"/>
+      <c r="S60" s="50"/>
+      <c r="T60" s="50"/>
+      <c r="U60" s="52"/>
+      <c r="V60" s="53"/>
+      <c r="W60" s="53"/>
+      <c r="X60" s="53"/>
+      <c r="Y60" s="50"/>
+      <c r="Z60" s="50"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="80"/>
+      <c r="D61" s="81"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="50"/>
-      <c r="G61" s="50"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="50" t="str">
+      <c r="I61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="50" t="str">
+      <c r="J61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="50" t="str">
+      <c r="K61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
         <v> </v>
       </c>
-      <c r="L61" s="50"/>
+      <c r="L61" s="53"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="50"/>
-      <c r="O61" s="47"/>
-      <c r="P61" s="48"/>
-      <c r="Q61" s="47"/>
-      <c r="R61" s="47"/>
-      <c r="S61" s="47"/>
-      <c r="T61" s="47"/>
+      <c r="N61" s="53"/>
+      <c r="O61" s="50"/>
+      <c r="P61" s="51"/>
+      <c r="Q61" s="50"/>
+      <c r="R61" s="50"/>
+      <c r="S61" s="50"/>
+      <c r="T61" s="50"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="50" t="str">
+      <c r="W61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="50" t="str">
+      <c r="X61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="47"/>
-      <c r="Z61" s="47"/>
+      <c r="Y61" s="50"/>
+      <c r="Z61" s="50"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="80"/>
+      <c r="D62" s="81"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="50"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="50" t="str">
+      <c r="I62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="50" t="str">
+      <c r="J62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="50" t="str">
+      <c r="K62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
         <v> </v>
       </c>
-      <c r="L62" s="50"/>
+      <c r="L62" s="53"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="50"/>
-      <c r="O62" s="47"/>
-      <c r="P62" s="48"/>
-      <c r="Q62" s="47"/>
-      <c r="R62" s="47"/>
-      <c r="S62" s="47"/>
-      <c r="T62" s="47"/>
+      <c r="N62" s="53"/>
+      <c r="O62" s="50"/>
+      <c r="P62" s="51"/>
+      <c r="Q62" s="50"/>
+      <c r="R62" s="50"/>
+      <c r="S62" s="50"/>
+      <c r="T62" s="50"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="50" t="str">
+      <c r="W62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="50" t="str">
+      <c r="X62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="47"/>
-      <c r="Z62" s="47"/>
+      <c r="Y62" s="50"/>
+      <c r="Z62" s="50"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="80"/>
+      <c r="D63" s="81"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="50" t="str">
+      <c r="I63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="50" t="str">
+      <c r="J63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="50" t="str">
+      <c r="K63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
         <v> </v>
       </c>
-      <c r="L63" s="50"/>
+      <c r="L63" s="53"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="50"/>
-      <c r="O63" s="47"/>
-      <c r="P63" s="48"/>
-      <c r="Q63" s="47"/>
-      <c r="R63" s="47"/>
-      <c r="S63" s="47"/>
-      <c r="T63" s="47"/>
+      <c r="N63" s="53"/>
+      <c r="O63" s="50"/>
+      <c r="P63" s="51"/>
+      <c r="Q63" s="50"/>
+      <c r="R63" s="50"/>
+      <c r="S63" s="50"/>
+      <c r="T63" s="50"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="50" t="str">
+      <c r="W63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="50" t="str">
+      <c r="X63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="47"/>
-      <c r="Z63" s="47"/>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="50"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -5141,14 +5094,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="50"/>
+      <c r="L64" s="53"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="50"/>
+      <c r="N64" s="53"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="81"/>
+      <c r="P64" s="82"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -5161,8 +5114,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="47"/>
-      <c r="U64" s="49"/>
+      <c r="T64" s="50"/>
+      <c r="U64" s="52"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -5190,127 +5143,121 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="50"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="50"/>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="L65" s="50"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="53"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="50"/>
-      <c r="O65" s="50"/>
+      <c r="N65" s="53"/>
+      <c r="O65" s="53"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="50"/>
-      <c r="R65" s="50"/>
-      <c r="S65" s="50"/>
-      <c r="T65" s="47"/>
-      <c r="U65" s="49"/>
-      <c r="V65" s="50"/>
-      <c r="W65" s="50"/>
-      <c r="X65" s="50"/>
-      <c r="Y65" s="50"/>
-      <c r="Z65" s="50"/>
+      <c r="Q65" s="53"/>
+      <c r="R65" s="53"/>
+      <c r="S65" s="53"/>
+      <c r="T65" s="50"/>
+      <c r="U65" s="52"/>
+      <c r="V65" s="53"/>
+      <c r="W65" s="53"/>
+      <c r="X65" s="53"/>
+      <c r="Y65" s="53"/>
+      <c r="Z65" s="53"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="51"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="50"/>
-      <c r="H66" s="82" t="n">
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="83" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="50"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="53"/>
+      <c r="L66" s="53"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="47"/>
-      <c r="P66" s="48"/>
-      <c r="Q66" s="47"/>
-      <c r="R66" s="47"/>
-      <c r="S66" s="47"/>
-      <c r="T66" s="47"/>
-      <c r="U66" s="49"/>
-      <c r="V66" s="50"/>
-      <c r="W66" s="50"/>
-      <c r="X66" s="50"/>
-      <c r="Y66" s="47"/>
-      <c r="Z66" s="47"/>
+      <c r="N66" s="53"/>
+      <c r="O66" s="50"/>
+      <c r="P66" s="51"/>
+      <c r="Q66" s="50"/>
+      <c r="R66" s="50"/>
+      <c r="S66" s="50"/>
+      <c r="T66" s="50"/>
+      <c r="U66" s="52"/>
+      <c r="V66" s="53"/>
+      <c r="W66" s="53"/>
+      <c r="X66" s="53"/>
+      <c r="Y66" s="50"/>
+      <c r="Z66" s="50"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42"/>
-      <c r="B67" s="54" t="n">
-        <v>45792</v>
-      </c>
-      <c r="C67" s="55" t="s">
-        <v>39</v>
-      </c>
+      <c r="B67" s="54"/>
+      <c r="C67" s="55"/>
       <c r="D67" s="56"/>
-      <c r="E67" s="57" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F67" s="50"/>
-      <c r="G67" s="50"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="50" t="n">
+      <c r="I67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
-        <v>150</v>
-      </c>
-      <c r="J67" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="J67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
-        <v>150</v>
-      </c>
-      <c r="K67" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="K67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
-        <v>1350</v>
-      </c>
-      <c r="L67" s="50"/>
+        <v> </v>
+      </c>
+      <c r="L67" s="53"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="50"/>
-      <c r="O67" s="47"/>
+      <c r="N67" s="53"/>
+      <c r="O67" s="50"/>
       <c r="P67" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q67" s="47" t="n">
+      <c r="Q67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67*P67," ")</f>
-        <v>1500</v>
-      </c>
-      <c r="R67" s="47"/>
-      <c r="S67" s="47" t="n">
+        <v> </v>
+      </c>
+      <c r="R67" s="50"/>
+      <c r="S67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
-        <v>0</v>
-      </c>
-      <c r="T67" s="47"/>
+        <v> </v>
+      </c>
+      <c r="T67" s="50"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="50" t="str">
+      <c r="W67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="50" t="str">
+      <c r="X67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="47" t="str">
+      <c r="Y67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="47" t="str">
+      <c r="Z67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5318,67 +5265,61 @@
     </row>
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
-      <c r="B68" s="54" t="n">
-        <v>45853</v>
-      </c>
-      <c r="C68" s="55" t="s">
-        <v>40</v>
-      </c>
+      <c r="B68" s="54"/>
+      <c r="C68" s="55"/>
       <c r="D68" s="56"/>
-      <c r="E68" s="57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F68" s="50"/>
-      <c r="G68" s="50"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="50" t="n">
+      <c r="I68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
-        <v>100</v>
-      </c>
-      <c r="J68" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="J68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
-        <v>100</v>
-      </c>
-      <c r="K68" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="K68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
-        <v>900</v>
-      </c>
-      <c r="L68" s="50"/>
+        <v> </v>
+      </c>
+      <c r="L68" s="53"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="47"/>
+      <c r="N68" s="53"/>
+      <c r="O68" s="50"/>
       <c r="P68" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q68" s="47" t="n">
+      <c r="Q68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68*P68," ")</f>
-        <v>1000</v>
-      </c>
-      <c r="R68" s="47"/>
-      <c r="S68" s="47" t="n">
+        <v> </v>
+      </c>
+      <c r="R68" s="50"/>
+      <c r="S68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
-        <v>0</v>
-      </c>
-      <c r="T68" s="47"/>
+        <v> </v>
+      </c>
+      <c r="T68" s="50"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="50" t="str">
+      <c r="W68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="50" t="str">
+      <c r="X68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="47" t="str">
+      <c r="Y68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="47" t="str">
+      <c r="Z68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5386,67 +5327,61 @@
     </row>
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
-      <c r="B69" s="54" t="n">
-        <v>45955</v>
-      </c>
-      <c r="C69" s="55" t="s">
-        <v>41</v>
-      </c>
+      <c r="B69" s="54"/>
+      <c r="C69" s="55"/>
       <c r="D69" s="56"/>
-      <c r="E69" s="57" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="50" t="n">
+      <c r="I69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
-        <v>3000</v>
-      </c>
-      <c r="J69" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="J69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
-        <v>3000</v>
-      </c>
-      <c r="K69" s="50" t="n">
+        <v> </v>
+      </c>
+      <c r="K69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
-        <v>27000</v>
-      </c>
-      <c r="L69" s="50"/>
+        <v> </v>
+      </c>
+      <c r="L69" s="53"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="47"/>
+      <c r="N69" s="53"/>
+      <c r="O69" s="50"/>
       <c r="P69" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q69" s="47" t="n">
+      <c r="Q69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69*P69," ")</f>
-        <v>30000</v>
-      </c>
-      <c r="R69" s="47"/>
-      <c r="S69" s="47" t="n">
+        <v> </v>
+      </c>
+      <c r="R69" s="50"/>
+      <c r="S69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
-        <v>0</v>
-      </c>
-      <c r="T69" s="47"/>
+        <v> </v>
+      </c>
+      <c r="T69" s="50"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="50" t="str">
+      <c r="W69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="50" t="str">
+      <c r="X69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="47" t="str">
+      <c r="Y69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="47" t="str">
+      <c r="Z69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5458,57 +5393,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="50" t="str">
+      <c r="I70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="50" t="str">
+      <c r="J70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="50" t="str">
+      <c r="K70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
         <v> </v>
       </c>
-      <c r="L70" s="50"/>
+      <c r="L70" s="53"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="47"/>
+      <c r="N70" s="53"/>
+      <c r="O70" s="50"/>
       <c r="P70" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="47" t="str">
+      <c r="Q70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47" t="str">
+      <c r="R70" s="50"/>
+      <c r="S70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="47"/>
+      <c r="T70" s="50"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="50" t="str">
+      <c r="W70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="50" t="str">
+      <c r="X70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="47" t="str">
+      <c r="Y70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="47" t="str">
+      <c r="Z70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5520,57 +5455,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="50" t="str">
+      <c r="I71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="50" t="str">
+      <c r="J71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="50" t="str">
+      <c r="K71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
         <v> </v>
       </c>
-      <c r="L71" s="50"/>
+      <c r="L71" s="53"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="50"/>
-      <c r="O71" s="47"/>
+      <c r="N71" s="53"/>
+      <c r="O71" s="50"/>
       <c r="P71" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q71" s="47" t="str">
+      <c r="Q71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="47"/>
-      <c r="S71" s="47" t="str">
+      <c r="R71" s="50"/>
+      <c r="S71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="47"/>
+      <c r="T71" s="50"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="50" t="str">
+      <c r="W71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="50" t="str">
+      <c r="X71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="47" t="str">
+      <c r="Y71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="47" t="str">
+      <c r="Z71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5579,13 +5514,13 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="42"/>
       <c r="B72" s="59" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
       <c r="E72" s="60" t="n">
         <f aca="false">SUM(E67:E71)</f>
-        <v>32500</v>
+        <v>0</v>
       </c>
       <c r="F72" s="61" t="n">
         <f aca="false">SUM(F67:F71)</f>
@@ -5598,19 +5533,19 @@
       <c r="H72" s="58"/>
       <c r="I72" s="61" t="n">
         <f aca="false">SUM(I67:I71)</f>
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="J72" s="61" t="n">
         <f aca="false">SUM(J67:J71)</f>
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="K72" s="61" t="n">
         <f aca="false">SUM(K67:K71)</f>
-        <v>29250</v>
-      </c>
-      <c r="L72" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="53"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="50"/>
+      <c r="N72" s="53"/>
       <c r="O72" s="61" t="n">
         <f aca="false">SUM(O67:O71)</f>
         <v>0</v>
@@ -5618,7 +5553,7 @@
       <c r="P72" s="62"/>
       <c r="Q72" s="61" t="n">
         <f aca="false">SUM(Q67:Q71)</f>
-        <v>32500</v>
+        <v>0</v>
       </c>
       <c r="R72" s="61" t="n">
         <f aca="false">SUM(R67:R71)</f>
@@ -5628,8 +5563,8 @@
         <f aca="false">SUM(S67:S71)</f>
         <v>0</v>
       </c>
-      <c r="T72" s="47"/>
-      <c r="U72" s="49"/>
+      <c r="T72" s="50"/>
+      <c r="U72" s="52"/>
       <c r="V72" s="60" t="n">
         <f aca="false">SUM(V67:V71)</f>
         <v>0</v>
@@ -5657,121 +5592,121 @@
       <c r="B73" s="63"/>
       <c r="C73" s="64"/>
       <c r="D73" s="65"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="50"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
       <c r="H73" s="58"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="L73" s="50"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="53"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="50"/>
-      <c r="O73" s="50"/>
+      <c r="N73" s="53"/>
+      <c r="O73" s="53"/>
       <c r="P73" s="62"/>
-      <c r="Q73" s="50"/>
-      <c r="R73" s="50"/>
-      <c r="S73" s="50"/>
-      <c r="T73" s="47"/>
-      <c r="U73" s="49"/>
-      <c r="V73" s="50"/>
-      <c r="W73" s="50"/>
-      <c r="X73" s="50"/>
-      <c r="Y73" s="50"/>
-      <c r="Z73" s="50"/>
+      <c r="Q73" s="53"/>
+      <c r="R73" s="53"/>
+      <c r="S73" s="53"/>
+      <c r="T73" s="50"/>
+      <c r="U73" s="52"/>
+      <c r="V73" s="53"/>
+      <c r="W73" s="53"/>
+      <c r="X73" s="53"/>
+      <c r="Y73" s="53"/>
+      <c r="Z73" s="53"/>
       <c r="AA73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="42"/>
-      <c r="B74" s="51" t="s">
+      <c r="B74" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="51"/>
+      <c r="C74" s="66"/>
       <c r="D74" s="62"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="50"/>
-      <c r="H74" s="82" t="n">
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="83" t="n">
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I74" s="50"/>
-      <c r="J74" s="50"/>
-      <c r="K74" s="50"/>
-      <c r="L74" s="50"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="50"/>
-      <c r="O74" s="47"/>
-      <c r="P74" s="48"/>
-      <c r="Q74" s="47"/>
-      <c r="R74" s="47"/>
-      <c r="S74" s="47"/>
-      <c r="T74" s="47"/>
-      <c r="U74" s="49"/>
-      <c r="V74" s="50"/>
-      <c r="W74" s="50"/>
-      <c r="X74" s="50"/>
-      <c r="Y74" s="47"/>
-      <c r="Z74" s="47"/>
+      <c r="N74" s="53"/>
+      <c r="O74" s="50"/>
+      <c r="P74" s="51"/>
+      <c r="Q74" s="50"/>
+      <c r="R74" s="50"/>
+      <c r="S74" s="50"/>
+      <c r="T74" s="50"/>
+      <c r="U74" s="52"/>
+      <c r="V74" s="53"/>
+      <c r="W74" s="53"/>
+      <c r="X74" s="53"/>
+      <c r="Y74" s="50"/>
+      <c r="Z74" s="50"/>
       <c r="AA74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
-      <c r="D75" s="80"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="57"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="50"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
       <c r="H75" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I75" s="50" t="str">
+      <c r="I75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,MIN(E75*H75,G75)," ")</f>
         <v> </v>
       </c>
-      <c r="J75" s="50" t="str">
+      <c r="J75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,F75+I75," ")</f>
         <v> </v>
       </c>
-      <c r="K75" s="50" t="str">
+      <c r="K75" s="53" t="str">
         <f aca="false">IF(E75&gt;0,E75-J75," ")</f>
         <v> </v>
       </c>
-      <c r="L75" s="50"/>
+      <c r="L75" s="53"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="50"/>
-      <c r="O75" s="47"/>
+      <c r="N75" s="53"/>
+      <c r="O75" s="50"/>
       <c r="P75" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q75" s="47" t="str">
+      <c r="Q75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75*P75," ")</f>
         <v> </v>
       </c>
-      <c r="R75" s="47"/>
-      <c r="S75" s="47" t="str">
+      <c r="R75" s="50"/>
+      <c r="S75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,E75-Q75," ")</f>
         <v> </v>
       </c>
-      <c r="T75" s="47"/>
+      <c r="T75" s="50"/>
       <c r="U75" s="54"/>
       <c r="V75" s="57"/>
-      <c r="W75" s="50" t="str">
+      <c r="W75" s="53" t="str">
         <f aca="false">IF(V75&gt;0,E75," ")</f>
         <v> </v>
       </c>
-      <c r="X75" s="50" t="str">
+      <c r="X75" s="53" t="str">
         <f aca="false">IF(V75&gt;0,J75," ")</f>
         <v> </v>
       </c>
-      <c r="Y75" s="47" t="str">
+      <c r="Y75" s="50" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&lt;S75,S75-V75," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z75" s="47" t="str">
+      <c r="Z75" s="50" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&gt;S75,V75-S75," ")," ")</f>
         <v> </v>
       </c>
@@ -5781,59 +5716,59 @@
       <c r="A76" s="42"/>
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
-      <c r="D76" s="80"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="57"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
       <c r="H76" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I76" s="50" t="str">
+      <c r="I76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,MIN(E76*H76,G76)," ")</f>
         <v> </v>
       </c>
-      <c r="J76" s="50" t="str">
+      <c r="J76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,F76+I76," ")</f>
         <v> </v>
       </c>
-      <c r="K76" s="50" t="str">
+      <c r="K76" s="53" t="str">
         <f aca="false">IF(E76&gt;0,E76-J76," ")</f>
         <v> </v>
       </c>
-      <c r="L76" s="50"/>
+      <c r="L76" s="53"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="50"/>
-      <c r="O76" s="47"/>
+      <c r="N76" s="53"/>
+      <c r="O76" s="50"/>
       <c r="P76" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q76" s="47" t="str">
+      <c r="Q76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76*P76," ")</f>
         <v> </v>
       </c>
-      <c r="R76" s="47"/>
-      <c r="S76" s="47" t="str">
+      <c r="R76" s="50"/>
+      <c r="S76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,E76-Q76," ")</f>
         <v> </v>
       </c>
-      <c r="T76" s="47"/>
+      <c r="T76" s="50"/>
       <c r="U76" s="54"/>
       <c r="V76" s="57"/>
-      <c r="W76" s="50" t="str">
+      <c r="W76" s="53" t="str">
         <f aca="false">IF(V76&gt;0,E76," ")</f>
         <v> </v>
       </c>
-      <c r="X76" s="50" t="str">
+      <c r="X76" s="53" t="str">
         <f aca="false">IF(V76&gt;0,J76," ")</f>
         <v> </v>
       </c>
-      <c r="Y76" s="47" t="str">
+      <c r="Y76" s="50" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&lt;S76,S76-V76," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z76" s="47" t="str">
+      <c r="Z76" s="50" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&gt;S76,V76-S76," ")," ")</f>
         <v> </v>
       </c>
@@ -5843,59 +5778,59 @@
       <c r="A77" s="42"/>
       <c r="B77" s="54"/>
       <c r="C77" s="55"/>
-      <c r="D77" s="80"/>
+      <c r="D77" s="81"/>
       <c r="E77" s="57"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
       <c r="H77" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="50" t="str">
+      <c r="I77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,MIN(E77*H77,G77)," ")</f>
         <v> </v>
       </c>
-      <c r="J77" s="50" t="str">
+      <c r="J77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,F77+I77," ")</f>
         <v> </v>
       </c>
-      <c r="K77" s="50" t="str">
+      <c r="K77" s="53" t="str">
         <f aca="false">IF(E77&gt;0,E77-J77," ")</f>
         <v> </v>
       </c>
-      <c r="L77" s="50"/>
+      <c r="L77" s="53"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="50"/>
-      <c r="O77" s="47"/>
+      <c r="N77" s="53"/>
+      <c r="O77" s="50"/>
       <c r="P77" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="47" t="str">
+      <c r="Q77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77*P77," ")</f>
         <v> </v>
       </c>
-      <c r="R77" s="47"/>
-      <c r="S77" s="47" t="str">
+      <c r="R77" s="50"/>
+      <c r="S77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,E77-Q77," ")</f>
         <v> </v>
       </c>
-      <c r="T77" s="47"/>
+      <c r="T77" s="50"/>
       <c r="U77" s="54"/>
       <c r="V77" s="57"/>
-      <c r="W77" s="50" t="str">
+      <c r="W77" s="53" t="str">
         <f aca="false">IF(V77&gt;0,E77," ")</f>
         <v> </v>
       </c>
-      <c r="X77" s="50" t="str">
+      <c r="X77" s="53" t="str">
         <f aca="false">IF(V77&gt;0,J77," ")</f>
         <v> </v>
       </c>
-      <c r="Y77" s="47" t="str">
+      <c r="Y77" s="50" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&lt;S77,S77-V77," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z77" s="47" t="str">
+      <c r="Z77" s="50" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&gt;S77,V77-S77," ")," ")</f>
         <v> </v>
       </c>
@@ -5905,59 +5840,59 @@
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="80"/>
+      <c r="D78" s="81"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="50" t="str">
+      <c r="I78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="50" t="str">
+      <c r="J78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="50" t="str">
+      <c r="K78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
         <v> </v>
       </c>
-      <c r="L78" s="50"/>
+      <c r="L78" s="53"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="50"/>
-      <c r="O78" s="47"/>
+      <c r="N78" s="53"/>
+      <c r="O78" s="50"/>
       <c r="P78" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q78" s="47" t="str">
+      <c r="Q78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="47"/>
-      <c r="S78" s="47" t="str">
+      <c r="R78" s="50"/>
+      <c r="S78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="47"/>
+      <c r="T78" s="50"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="50" t="str">
+      <c r="W78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="50" t="str">
+      <c r="X78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="47" t="str">
+      <c r="Y78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="47" t="str">
+      <c r="Z78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5967,59 +5902,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="80"/>
+      <c r="D79" s="81"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="50" t="str">
+      <c r="I79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="50" t="str">
+      <c r="J79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="50" t="str">
+      <c r="K79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
         <v> </v>
       </c>
-      <c r="L79" s="50"/>
+      <c r="L79" s="53"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="50"/>
-      <c r="O79" s="47"/>
+      <c r="N79" s="53"/>
+      <c r="O79" s="50"/>
       <c r="P79" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q79" s="47" t="str">
+      <c r="Q79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="47"/>
-      <c r="S79" s="47" t="str">
+      <c r="R79" s="50"/>
+      <c r="S79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="47"/>
+      <c r="T79" s="50"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="50" t="str">
+      <c r="W79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="50" t="str">
+      <c r="X79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="47" t="str">
+      <c r="Y79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="47" t="str">
+      <c r="Z79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -6028,7 +5963,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="42"/>
       <c r="B80" s="59" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C80" s="59"/>
       <c r="D80" s="59"/>
@@ -6057,9 +5992,9 @@
         <f aca="false">SUM(K75:K79)</f>
         <v>0</v>
       </c>
-      <c r="L80" s="50"/>
+      <c r="L80" s="53"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="50"/>
+      <c r="N80" s="53"/>
       <c r="O80" s="61" t="n">
         <f aca="false">SUM(O75:O79)</f>
         <v>0</v>
@@ -6077,8 +6012,8 @@
         <f aca="false">SUM(S75:S79)</f>
         <v>0</v>
       </c>
-      <c r="T80" s="47"/>
-      <c r="U80" s="49"/>
+      <c r="T80" s="50"/>
+      <c r="U80" s="52"/>
       <c r="V80" s="60" t="n">
         <f aca="false">SUM(V75:V79)</f>
         <v>0</v>
@@ -6106,121 +6041,121 @@
       <c r="B81" s="63"/>
       <c r="C81" s="64"/>
       <c r="D81" s="65"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
       <c r="H81" s="58"/>
-      <c r="I81" s="50"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
+      <c r="I81" s="53"/>
+      <c r="J81" s="53"/>
+      <c r="K81" s="53"/>
+      <c r="L81" s="53"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="50"/>
-      <c r="O81" s="50"/>
+      <c r="N81" s="53"/>
+      <c r="O81" s="53"/>
       <c r="P81" s="62"/>
-      <c r="Q81" s="50"/>
-      <c r="R81" s="50"/>
-      <c r="S81" s="50"/>
-      <c r="T81" s="47"/>
-      <c r="U81" s="49"/>
-      <c r="V81" s="50"/>
-      <c r="W81" s="50"/>
-      <c r="X81" s="50"/>
-      <c r="Y81" s="50"/>
-      <c r="Z81" s="50"/>
+      <c r="Q81" s="53"/>
+      <c r="R81" s="53"/>
+      <c r="S81" s="53"/>
+      <c r="T81" s="50"/>
+      <c r="U81" s="52"/>
+      <c r="V81" s="53"/>
+      <c r="W81" s="53"/>
+      <c r="X81" s="53"/>
+      <c r="Y81" s="53"/>
+      <c r="Z81" s="53"/>
       <c r="AA81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="42"/>
-      <c r="B82" s="51" t="s">
+      <c r="B82" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="51"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="82" t="n">
+      <c r="C82" s="66"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="83" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I82" s="50"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="53"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="50"/>
-      <c r="O82" s="47"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="47"/>
-      <c r="R82" s="47"/>
-      <c r="S82" s="47"/>
-      <c r="T82" s="47"/>
-      <c r="U82" s="49"/>
-      <c r="V82" s="50"/>
-      <c r="W82" s="50"/>
-      <c r="X82" s="50"/>
-      <c r="Y82" s="47"/>
-      <c r="Z82" s="47"/>
+      <c r="N82" s="53"/>
+      <c r="O82" s="50"/>
+      <c r="P82" s="51"/>
+      <c r="Q82" s="50"/>
+      <c r="R82" s="50"/>
+      <c r="S82" s="50"/>
+      <c r="T82" s="50"/>
+      <c r="U82" s="52"/>
+      <c r="V82" s="53"/>
+      <c r="W82" s="53"/>
+      <c r="X82" s="53"/>
+      <c r="Y82" s="50"/>
+      <c r="Z82" s="50"/>
       <c r="AA82" s="25"/>
     </row>
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="54"/>
       <c r="C83" s="55"/>
-      <c r="D83" s="80"/>
+      <c r="D83" s="81"/>
       <c r="E83" s="57"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
       <c r="H83" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I83" s="50" t="str">
+      <c r="I83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,MIN(E83*H83,G83)," ")</f>
         <v> </v>
       </c>
-      <c r="J83" s="50" t="str">
+      <c r="J83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,F83+I83," ")</f>
         <v> </v>
       </c>
-      <c r="K83" s="50" t="str">
+      <c r="K83" s="53" t="str">
         <f aca="false">IF(E83&gt;0,E83-J83," ")</f>
         <v> </v>
       </c>
-      <c r="L83" s="50"/>
+      <c r="L83" s="53"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="50"/>
-      <c r="O83" s="47"/>
+      <c r="N83" s="53"/>
+      <c r="O83" s="50"/>
       <c r="P83" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q83" s="47" t="str">
+      <c r="Q83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83*P83," ")</f>
         <v> </v>
       </c>
-      <c r="R83" s="47"/>
-      <c r="S83" s="47" t="str">
+      <c r="R83" s="50"/>
+      <c r="S83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,E83-Q83," ")</f>
         <v> </v>
       </c>
-      <c r="T83" s="47"/>
+      <c r="T83" s="50"/>
       <c r="U83" s="54"/>
       <c r="V83" s="57"/>
-      <c r="W83" s="50" t="str">
+      <c r="W83" s="53" t="str">
         <f aca="false">IF(V83&gt;0,E83," ")</f>
         <v> </v>
       </c>
-      <c r="X83" s="50" t="str">
+      <c r="X83" s="53" t="str">
         <f aca="false">IF(V83&gt;0,J83," ")</f>
         <v> </v>
       </c>
-      <c r="Y83" s="47" t="str">
+      <c r="Y83" s="50" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&lt;S83,S83-V83," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z83" s="47" t="str">
+      <c r="Z83" s="50" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&gt;S83,V83-S83," ")," ")</f>
         <v> </v>
       </c>
@@ -6230,59 +6165,59 @@
       <c r="A84" s="42"/>
       <c r="B84" s="54"/>
       <c r="C84" s="55"/>
-      <c r="D84" s="80"/>
+      <c r="D84" s="81"/>
       <c r="E84" s="57"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
       <c r="H84" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I84" s="50" t="str">
+      <c r="I84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,MIN(E84*H84,G84)," ")</f>
         <v> </v>
       </c>
-      <c r="J84" s="50" t="str">
+      <c r="J84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,F84+I84," ")</f>
         <v> </v>
       </c>
-      <c r="K84" s="50" t="str">
+      <c r="K84" s="53" t="str">
         <f aca="false">IF(E84&gt;0,E84-J84," ")</f>
         <v> </v>
       </c>
-      <c r="L84" s="50"/>
+      <c r="L84" s="53"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="50"/>
-      <c r="O84" s="47"/>
+      <c r="N84" s="53"/>
+      <c r="O84" s="50"/>
       <c r="P84" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q84" s="47" t="str">
+      <c r="Q84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84*P84," ")</f>
         <v> </v>
       </c>
-      <c r="R84" s="47"/>
-      <c r="S84" s="47" t="str">
+      <c r="R84" s="50"/>
+      <c r="S84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,E84-Q84," ")</f>
         <v> </v>
       </c>
-      <c r="T84" s="47"/>
+      <c r="T84" s="50"/>
       <c r="U84" s="54"/>
       <c r="V84" s="57"/>
-      <c r="W84" s="50" t="str">
+      <c r="W84" s="53" t="str">
         <f aca="false">IF(V84&gt;0,E84," ")</f>
         <v> </v>
       </c>
-      <c r="X84" s="50" t="str">
+      <c r="X84" s="53" t="str">
         <f aca="false">IF(V84&gt;0,J84," ")</f>
         <v> </v>
       </c>
-      <c r="Y84" s="47" t="str">
+      <c r="Y84" s="50" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&lt;S84,S84-V84," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z84" s="47" t="str">
+      <c r="Z84" s="50" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&gt;S84,V84-S84," ")," ")</f>
         <v> </v>
       </c>
@@ -6292,59 +6227,59 @@
       <c r="A85" s="42"/>
       <c r="B85" s="54"/>
       <c r="C85" s="55"/>
-      <c r="D85" s="80"/>
+      <c r="D85" s="81"/>
       <c r="E85" s="57"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
       <c r="H85" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="50" t="str">
+      <c r="I85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,MIN(E85*H85,G85)," ")</f>
         <v> </v>
       </c>
-      <c r="J85" s="50" t="str">
+      <c r="J85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,F85+I85," ")</f>
         <v> </v>
       </c>
-      <c r="K85" s="50" t="str">
+      <c r="K85" s="53" t="str">
         <f aca="false">IF(E85&gt;0,E85-J85," ")</f>
         <v> </v>
       </c>
-      <c r="L85" s="50"/>
+      <c r="L85" s="53"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="50"/>
-      <c r="O85" s="47"/>
+      <c r="N85" s="53"/>
+      <c r="O85" s="50"/>
       <c r="P85" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q85" s="47" t="str">
+      <c r="Q85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85*P85," ")</f>
         <v> </v>
       </c>
-      <c r="R85" s="47"/>
-      <c r="S85" s="47" t="str">
+      <c r="R85" s="50"/>
+      <c r="S85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,E85-Q85," ")</f>
         <v> </v>
       </c>
-      <c r="T85" s="47"/>
+      <c r="T85" s="50"/>
       <c r="U85" s="54"/>
       <c r="V85" s="57"/>
-      <c r="W85" s="50" t="str">
+      <c r="W85" s="53" t="str">
         <f aca="false">IF(V85&gt;0,E85," ")</f>
         <v> </v>
       </c>
-      <c r="X85" s="50" t="str">
+      <c r="X85" s="53" t="str">
         <f aca="false">IF(V85&gt;0,J85," ")</f>
         <v> </v>
       </c>
-      <c r="Y85" s="47" t="str">
+      <c r="Y85" s="50" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&lt;S85,S85-V85," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z85" s="47" t="str">
+      <c r="Z85" s="50" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&gt;S85,V85-S85," ")," ")</f>
         <v> </v>
       </c>
@@ -6354,59 +6289,59 @@
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="80"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="50" t="str">
+      <c r="I86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="50" t="str">
+      <c r="J86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="50" t="str">
+      <c r="K86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
         <v> </v>
       </c>
-      <c r="L86" s="50"/>
+      <c r="L86" s="53"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="50"/>
-      <c r="O86" s="47"/>
+      <c r="N86" s="53"/>
+      <c r="O86" s="50"/>
       <c r="P86" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q86" s="47" t="str">
+      <c r="Q86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="47"/>
-      <c r="S86" s="47" t="str">
+      <c r="R86" s="50"/>
+      <c r="S86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="47"/>
+      <c r="T86" s="50"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="50" t="str">
+      <c r="W86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="50" t="str">
+      <c r="X86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="47" t="str">
+      <c r="Y86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="47" t="str">
+      <c r="Z86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6416,59 +6351,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="80"/>
+      <c r="D87" s="81"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="50" t="str">
+      <c r="I87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="50" t="str">
+      <c r="J87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="50" t="str">
+      <c r="K87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
         <v> </v>
       </c>
-      <c r="L87" s="50"/>
+      <c r="L87" s="53"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="50"/>
-      <c r="O87" s="47"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="50"/>
       <c r="P87" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q87" s="47" t="str">
+      <c r="Q87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="47"/>
-      <c r="S87" s="47" t="str">
+      <c r="R87" s="50"/>
+      <c r="S87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="47"/>
+      <c r="T87" s="50"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="50" t="str">
+      <c r="W87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="50" t="str">
+      <c r="X87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="47" t="str">
+      <c r="Y87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="47" t="str">
+      <c r="Z87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6477,7 +6412,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="42"/>
       <c r="B88" s="59" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -6506,9 +6441,9 @@
         <f aca="false">SUM(K83:K87)</f>
         <v>0</v>
       </c>
-      <c r="L88" s="50"/>
+      <c r="L88" s="53"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="50"/>
+      <c r="N88" s="53"/>
       <c r="O88" s="61" t="n">
         <f aca="false">SUM(O83:O87)</f>
         <v>0</v>
@@ -6526,8 +6461,8 @@
         <f aca="false">SUM(S83:S87)</f>
         <v>0</v>
       </c>
-      <c r="T88" s="47"/>
-      <c r="U88" s="49"/>
+      <c r="T88" s="50"/>
+      <c r="U88" s="52"/>
       <c r="V88" s="60" t="n">
         <f aca="false">SUM(V83:V87)</f>
         <v>0</v>
@@ -6555,124 +6490,124 @@
       <c r="B89" s="63"/>
       <c r="C89" s="64"/>
       <c r="D89" s="65"/>
-      <c r="E89" s="50"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
       <c r="H89" s="58"/>
-      <c r="I89" s="50"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
-      <c r="L89" s="50"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="53"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="50"/>
-      <c r="O89" s="50"/>
+      <c r="N89" s="53"/>
+      <c r="O89" s="53"/>
       <c r="P89" s="62"/>
-      <c r="Q89" s="50"/>
-      <c r="R89" s="50"/>
-      <c r="S89" s="50"/>
-      <c r="T89" s="47"/>
-      <c r="U89" s="49"/>
-      <c r="V89" s="50"/>
-      <c r="W89" s="50"/>
-      <c r="X89" s="50"/>
-      <c r="Y89" s="50"/>
-      <c r="Z89" s="50"/>
+      <c r="Q89" s="53"/>
+      <c r="R89" s="53"/>
+      <c r="S89" s="53"/>
+      <c r="T89" s="50"/>
+      <c r="U89" s="52"/>
+      <c r="V89" s="53"/>
+      <c r="W89" s="53"/>
+      <c r="X89" s="53"/>
+      <c r="Y89" s="53"/>
+      <c r="Z89" s="53"/>
       <c r="AA89" s="25"/>
     </row>
     <row r="90" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="42"/>
-      <c r="B90" s="69" t="str">
+      <c r="B90" s="70" t="str">
         <f aca="false">B37</f>
         <v>Motor Vehicles - costing over £</v>
       </c>
-      <c r="C90" s="69"/>
-      <c r="D90" s="70" t="n">
+      <c r="C90" s="70"/>
+      <c r="D90" s="71" t="n">
         <f aca="false">D37</f>
         <v>12000</v>
       </c>
-      <c r="E90" s="50"/>
-      <c r="F90" s="50"/>
-      <c r="G90" s="50"/>
-      <c r="H90" s="82" t="n">
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="83" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I90" s="50"/>
-      <c r="J90" s="50"/>
-      <c r="K90" s="50"/>
-      <c r="L90" s="50"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="50"/>
-      <c r="O90" s="47"/>
+      <c r="N90" s="53"/>
+      <c r="O90" s="50"/>
       <c r="P90" s="62"/>
-      <c r="Q90" s="47"/>
-      <c r="R90" s="47"/>
-      <c r="S90" s="47"/>
-      <c r="T90" s="47"/>
-      <c r="U90" s="49"/>
-      <c r="V90" s="50"/>
-      <c r="W90" s="50"/>
-      <c r="X90" s="50"/>
-      <c r="Y90" s="47"/>
-      <c r="Z90" s="47"/>
+      <c r="Q90" s="50"/>
+      <c r="R90" s="50"/>
+      <c r="S90" s="50"/>
+      <c r="T90" s="50"/>
+      <c r="U90" s="52"/>
+      <c r="V90" s="53"/>
+      <c r="W90" s="53"/>
+      <c r="X90" s="53"/>
+      <c r="Y90" s="50"/>
+      <c r="Z90" s="50"/>
       <c r="AA90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="80"/>
+      <c r="D91" s="81"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I91" s="50" t="str">
+      <c r="I91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="50" t="str">
+      <c r="J91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="50" t="str">
+      <c r="K91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
         <v> </v>
       </c>
-      <c r="L91" s="50"/>
-      <c r="M91" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="50"/>
-      <c r="O91" s="47"/>
-      <c r="P91" s="48"/>
-      <c r="Q91" s="47"/>
-      <c r="R91" s="47" t="str">
+      <c r="L91" s="53"/>
+      <c r="M91" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="53"/>
+      <c r="O91" s="50"/>
+      <c r="P91" s="51"/>
+      <c r="Q91" s="50"/>
+      <c r="R91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
         <v> </v>
       </c>
-      <c r="S91" s="47" t="str">
+      <c r="S91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91-R91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="47"/>
+      <c r="T91" s="50"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="50" t="str">
+      <c r="W91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="50" t="str">
+      <c r="X91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="47" t="str">
+      <c r="Y91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,(S91-V91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="47" t="str">
+      <c r="Z91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,(V91-S91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
@@ -6682,58 +6617,58 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="80"/>
+      <c r="D92" s="81"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="50"/>
+      <c r="F92" s="53"/>
+      <c r="G92" s="53"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I92" s="50" t="str">
+      <c r="I92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="50" t="str">
+      <c r="J92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="50" t="str">
+      <c r="K92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
         <v> </v>
       </c>
-      <c r="L92" s="50"/>
-      <c r="M92" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="50"/>
-      <c r="O92" s="47"/>
-      <c r="P92" s="48"/>
-      <c r="Q92" s="47"/>
-      <c r="R92" s="47" t="str">
+      <c r="L92" s="53"/>
+      <c r="M92" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="53"/>
+      <c r="O92" s="50"/>
+      <c r="P92" s="51"/>
+      <c r="Q92" s="50"/>
+      <c r="R92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
         <v> </v>
       </c>
-      <c r="S92" s="47" t="str">
+      <c r="S92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92-R92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="47"/>
+      <c r="T92" s="50"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="50" t="str">
+      <c r="W92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="50" t="str">
+      <c r="X92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="47" t="str">
+      <c r="Y92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,(S92-V92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="47" t="str">
+      <c r="Z92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,(V92-S92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
@@ -6743,58 +6678,58 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="80"/>
+      <c r="D93" s="81"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
+      <c r="F93" s="53"/>
+      <c r="G93" s="53"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I93" s="50" t="str">
+      <c r="I93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="50" t="str">
+      <c r="J93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="50" t="str">
+      <c r="K93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
         <v> </v>
       </c>
-      <c r="L93" s="50"/>
-      <c r="M93" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="50"/>
-      <c r="O93" s="47"/>
-      <c r="P93" s="48"/>
-      <c r="Q93" s="47"/>
-      <c r="R93" s="47" t="str">
+      <c r="L93" s="53"/>
+      <c r="M93" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="53"/>
+      <c r="O93" s="50"/>
+      <c r="P93" s="51"/>
+      <c r="Q93" s="50"/>
+      <c r="R93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
         <v> </v>
       </c>
-      <c r="S93" s="47" t="str">
+      <c r="S93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93-R93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="47"/>
+      <c r="T93" s="50"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="50" t="str">
+      <c r="W93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="50" t="str">
+      <c r="X93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="47" t="str">
+      <c r="Y93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,(S93-V93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="47" t="str">
+      <c r="Z93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,(V93-S93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
@@ -6804,58 +6739,58 @@
       <c r="A94" s="42"/>
       <c r="B94" s="54"/>
       <c r="C94" s="55"/>
-      <c r="D94" s="80"/>
+      <c r="D94" s="81"/>
       <c r="E94" s="57"/>
-      <c r="F94" s="50"/>
-      <c r="G94" s="50"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
       <c r="H94" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I94" s="50" t="str">
+      <c r="I94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*H94,G94)," ")</f>
         <v> </v>
       </c>
-      <c r="J94" s="50" t="str">
+      <c r="J94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,F94+I94," ")</f>
         <v> </v>
       </c>
-      <c r="K94" s="50" t="str">
+      <c r="K94" s="53" t="str">
         <f aca="false">IF(E94&gt;0,E94-J94," ")</f>
         <v> </v>
       </c>
-      <c r="L94" s="50"/>
-      <c r="M94" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="50"/>
-      <c r="O94" s="47"/>
-      <c r="P94" s="48"/>
-      <c r="Q94" s="47"/>
-      <c r="R94" s="47" t="str">
+      <c r="L94" s="53"/>
+      <c r="M94" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="53"/>
+      <c r="O94" s="50"/>
+      <c r="P94" s="51"/>
+      <c r="Q94" s="50"/>
+      <c r="R94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
         <v> </v>
       </c>
-      <c r="S94" s="47" t="str">
+      <c r="S94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,E94-R94," ")</f>
         <v> </v>
       </c>
-      <c r="T94" s="47"/>
+      <c r="T94" s="50"/>
       <c r="U94" s="54"/>
       <c r="V94" s="57"/>
-      <c r="W94" s="50" t="str">
+      <c r="W94" s="53" t="str">
         <f aca="false">IF(V94&gt;0,E94," ")</f>
         <v> </v>
       </c>
-      <c r="X94" s="50" t="str">
+      <c r="X94" s="53" t="str">
         <f aca="false">IF(V94&gt;0,J94," ")</f>
         <v> </v>
       </c>
-      <c r="Y94" s="47" t="str">
+      <c r="Y94" s="50" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&lt;S94,(S94-V94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z94" s="47" t="str">
+      <c r="Z94" s="50" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&gt;S94,(V94-S94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
@@ -6865,58 +6800,58 @@
       <c r="A95" s="42"/>
       <c r="B95" s="54"/>
       <c r="C95" s="55"/>
-      <c r="D95" s="80"/>
+      <c r="D95" s="81"/>
       <c r="E95" s="57"/>
-      <c r="F95" s="50"/>
-      <c r="G95" s="50"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="53"/>
       <c r="H95" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I95" s="50" t="str">
+      <c r="I95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*H95,G95)," ")</f>
         <v> </v>
       </c>
-      <c r="J95" s="50" t="str">
+      <c r="J95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,F95+I95," ")</f>
         <v> </v>
       </c>
-      <c r="K95" s="50" t="str">
+      <c r="K95" s="53" t="str">
         <f aca="false">IF(E95&gt;0,E95-J95," ")</f>
         <v> </v>
       </c>
-      <c r="L95" s="50"/>
-      <c r="M95" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="50"/>
-      <c r="O95" s="47"/>
-      <c r="P95" s="48"/>
-      <c r="Q95" s="47"/>
-      <c r="R95" s="47" t="str">
+      <c r="L95" s="53"/>
+      <c r="M95" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="53"/>
+      <c r="O95" s="50"/>
+      <c r="P95" s="51"/>
+      <c r="Q95" s="50"/>
+      <c r="R95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
         <v> </v>
       </c>
-      <c r="S95" s="47" t="str">
+      <c r="S95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,E95-R95," ")</f>
         <v> </v>
       </c>
-      <c r="T95" s="47"/>
+      <c r="T95" s="50"/>
       <c r="U95" s="54"/>
       <c r="V95" s="57"/>
-      <c r="W95" s="50" t="str">
+      <c r="W95" s="53" t="str">
         <f aca="false">IF(V95&gt;0,E95," ")</f>
         <v> </v>
       </c>
-      <c r="X95" s="50" t="str">
+      <c r="X95" s="53" t="str">
         <f aca="false">IF(V95&gt;0,J95," ")</f>
         <v> </v>
       </c>
-      <c r="Y95" s="47" t="str">
+      <c r="Y95" s="50" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&lt;S95,(S95-V95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z95" s="47" t="str">
+      <c r="Z95" s="50" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&gt;S95,(V95-S95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
@@ -6924,95 +6859,95 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="83" t="str">
+      <c r="B96" s="84" t="str">
         <f aca="false">B43</f>
         <v>Motor Vehicles - costing under £</v>
       </c>
-      <c r="C96" s="83"/>
-      <c r="D96" s="70" t="n">
+      <c r="C96" s="84"/>
+      <c r="D96" s="71" t="n">
         <f aca="false">D43</f>
         <v>12000</v>
       </c>
-      <c r="E96" s="50"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53"/>
       <c r="H96" s="58"/>
-      <c r="I96" s="50"/>
-      <c r="J96" s="50"/>
-      <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="50"/>
-      <c r="O96" s="47"/>
-      <c r="P96" s="48"/>
-      <c r="Q96" s="47"/>
-      <c r="R96" s="47"/>
-      <c r="S96" s="47"/>
-      <c r="T96" s="47"/>
-      <c r="U96" s="49"/>
-      <c r="V96" s="50"/>
-      <c r="W96" s="50"/>
-      <c r="X96" s="50"/>
-      <c r="Y96" s="47"/>
-      <c r="Z96" s="47"/>
+      <c r="N96" s="53"/>
+      <c r="O96" s="50"/>
+      <c r="P96" s="51"/>
+      <c r="Q96" s="50"/>
+      <c r="R96" s="50"/>
+      <c r="S96" s="50"/>
+      <c r="T96" s="50"/>
+      <c r="U96" s="52"/>
+      <c r="V96" s="53"/>
+      <c r="W96" s="53"/>
+      <c r="X96" s="53"/>
+      <c r="Y96" s="50"/>
+      <c r="Z96" s="50"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="80"/>
+      <c r="D97" s="81"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
+      <c r="F97" s="53"/>
+      <c r="G97" s="53"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="50" t="str">
+      <c r="I97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="50" t="str">
+      <c r="J97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="50" t="str">
+      <c r="K97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
         <v> </v>
       </c>
-      <c r="L97" s="50"/>
-      <c r="M97" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="50"/>
-      <c r="O97" s="47"/>
-      <c r="P97" s="48"/>
-      <c r="Q97" s="47"/>
-      <c r="R97" s="47" t="str">
+      <c r="L97" s="53"/>
+      <c r="M97" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="53"/>
+      <c r="O97" s="50"/>
+      <c r="P97" s="51"/>
+      <c r="Q97" s="50"/>
+      <c r="R97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="47" t="str">
+      <c r="S97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="47"/>
+      <c r="T97" s="50"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="50" t="str">
+      <c r="W97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="50" t="str">
+      <c r="X97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="47" t="str">
+      <c r="Y97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="47" t="str">
+      <c r="Z97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -7022,58 +6957,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="80"/>
+      <c r="D98" s="81"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="50"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="50" t="str">
+      <c r="I98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="50" t="str">
+      <c r="J98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="50" t="str">
+      <c r="K98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
         <v> </v>
       </c>
-      <c r="L98" s="50"/>
-      <c r="M98" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="50"/>
-      <c r="O98" s="47"/>
-      <c r="P98" s="48"/>
-      <c r="Q98" s="47"/>
-      <c r="R98" s="47" t="str">
+      <c r="L98" s="53"/>
+      <c r="M98" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="53"/>
+      <c r="O98" s="50"/>
+      <c r="P98" s="51"/>
+      <c r="Q98" s="50"/>
+      <c r="R98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="47" t="str">
+      <c r="S98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="47"/>
+      <c r="T98" s="50"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="50" t="str">
+      <c r="W98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="50" t="str">
+      <c r="X98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="47" t="str">
+      <c r="Y98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="47" t="str">
+      <c r="Z98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -7083,58 +7018,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="80"/>
+      <c r="D99" s="81"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
+      <c r="F99" s="53"/>
+      <c r="G99" s="53"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="50" t="str">
+      <c r="I99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="50" t="str">
+      <c r="J99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="50" t="str">
+      <c r="K99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
         <v> </v>
       </c>
-      <c r="L99" s="50"/>
-      <c r="M99" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="50"/>
-      <c r="O99" s="47"/>
-      <c r="P99" s="48"/>
-      <c r="Q99" s="47"/>
-      <c r="R99" s="47" t="str">
+      <c r="L99" s="53"/>
+      <c r="M99" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="53"/>
+      <c r="O99" s="50"/>
+      <c r="P99" s="51"/>
+      <c r="Q99" s="50"/>
+      <c r="R99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="47" t="str">
+      <c r="S99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="47"/>
+      <c r="T99" s="50"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="50" t="str">
+      <c r="W99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="50" t="str">
+      <c r="X99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="47" t="str">
+      <c r="Y99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="47" t="str">
+      <c r="Z99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -7144,58 +7079,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="80"/>
+      <c r="D100" s="81"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="53"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="50" t="str">
+      <c r="I100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="50" t="str">
+      <c r="J100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="50" t="str">
+      <c r="K100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
         <v> </v>
       </c>
-      <c r="L100" s="50"/>
-      <c r="M100" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="50"/>
-      <c r="O100" s="47"/>
-      <c r="P100" s="48"/>
-      <c r="Q100" s="47"/>
-      <c r="R100" s="47" t="str">
+      <c r="L100" s="53"/>
+      <c r="M100" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="53"/>
+      <c r="O100" s="50"/>
+      <c r="P100" s="51"/>
+      <c r="Q100" s="50"/>
+      <c r="R100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="47" t="str">
+      <c r="S100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="47"/>
+      <c r="T100" s="50"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="50" t="str">
+      <c r="W100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="50" t="str">
+      <c r="X100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="47" t="str">
+      <c r="Y100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="47" t="str">
+      <c r="Z100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -7205,58 +7140,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="80"/>
+      <c r="D101" s="81"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
+      <c r="F101" s="53"/>
+      <c r="G101" s="53"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="50" t="str">
+      <c r="I101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="50" t="str">
+      <c r="J101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="50" t="str">
+      <c r="K101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
         <v> </v>
       </c>
-      <c r="L101" s="50"/>
-      <c r="M101" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="50"/>
-      <c r="O101" s="47"/>
-      <c r="P101" s="48"/>
-      <c r="Q101" s="47"/>
-      <c r="R101" s="47" t="str">
+      <c r="L101" s="53"/>
+      <c r="M101" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="53"/>
+      <c r="O101" s="50"/>
+      <c r="P101" s="51"/>
+      <c r="Q101" s="50"/>
+      <c r="R101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="47" t="str">
+      <c r="S101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="47"/>
+      <c r="T101" s="50"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="50" t="str">
+      <c r="W101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="50" t="str">
+      <c r="X101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="47" t="str">
+      <c r="Y101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="47" t="str">
+      <c r="Z101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7264,94 +7199,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="C102" s="51"/>
-      <c r="D102" s="68"/>
-      <c r="E102" s="50"/>
-      <c r="F102" s="50"/>
-      <c r="G102" s="50"/>
+      <c r="B102" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102" s="66"/>
+      <c r="D102" s="69"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="50"/>
-      <c r="J102" s="50"/>
-      <c r="K102" s="50"/>
-      <c r="L102" s="50"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="53"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="50"/>
-      <c r="O102" s="47"/>
-      <c r="P102" s="48"/>
-      <c r="Q102" s="47"/>
-      <c r="R102" s="47"/>
-      <c r="S102" s="47"/>
-      <c r="T102" s="47"/>
-      <c r="U102" s="49"/>
-      <c r="V102" s="50"/>
-      <c r="W102" s="50"/>
-      <c r="X102" s="50"/>
-      <c r="Y102" s="47"/>
-      <c r="Z102" s="47"/>
+      <c r="N102" s="53"/>
+      <c r="O102" s="50"/>
+      <c r="P102" s="51"/>
+      <c r="Q102" s="50"/>
+      <c r="R102" s="50"/>
+      <c r="S102" s="50"/>
+      <c r="T102" s="50"/>
+      <c r="U102" s="52"/>
+      <c r="V102" s="53"/>
+      <c r="W102" s="53"/>
+      <c r="X102" s="53"/>
+      <c r="Y102" s="50"/>
+      <c r="Z102" s="50"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="80"/>
+      <c r="D103" s="81"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="50"/>
-      <c r="G103" s="50"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="50" t="str">
+      <c r="I103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="50" t="str">
+      <c r="J103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="50" t="str">
+      <c r="K103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
         <v> </v>
       </c>
-      <c r="L103" s="50"/>
-      <c r="M103" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="50"/>
-      <c r="O103" s="47"/>
+      <c r="L103" s="53"/>
+      <c r="M103" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="53"/>
+      <c r="O103" s="50"/>
       <c r="P103" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q103" s="47" t="str">
+      <c r="Q103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="47"/>
-      <c r="S103" s="47" t="str">
+      <c r="R103" s="50"/>
+      <c r="S103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="47"/>
+      <c r="T103" s="50"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="50" t="str">
+      <c r="W103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="50" t="str">
+      <c r="X103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="47" t="str">
+      <c r="Y103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="47" t="str">
+      <c r="Z103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7361,61 +7296,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="80"/>
+      <c r="D104" s="81"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="50"/>
-      <c r="G104" s="50"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="50" t="str">
+      <c r="I104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="50" t="str">
+      <c r="J104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="50" t="str">
+      <c r="K104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
         <v> </v>
       </c>
-      <c r="L104" s="50"/>
-      <c r="M104" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="50"/>
-      <c r="O104" s="47"/>
+      <c r="L104" s="53"/>
+      <c r="M104" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="53"/>
+      <c r="O104" s="50"/>
       <c r="P104" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q104" s="47" t="str">
+      <c r="Q104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="47"/>
-      <c r="S104" s="47" t="str">
+      <c r="R104" s="50"/>
+      <c r="S104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="47"/>
+      <c r="T104" s="50"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="50" t="str">
+      <c r="W104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="50" t="str">
+      <c r="X104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="47" t="str">
+      <c r="Y104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="47" t="str">
+      <c r="Z104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7425,61 +7360,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="80"/>
+      <c r="D105" s="81"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="50"/>
-      <c r="G105" s="50"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="50" t="str">
+      <c r="I105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="50" t="str">
+      <c r="J105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="50" t="str">
+      <c r="K105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
         <v> </v>
       </c>
-      <c r="L105" s="50"/>
-      <c r="M105" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="50"/>
-      <c r="O105" s="47"/>
+      <c r="L105" s="53"/>
+      <c r="M105" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="53"/>
+      <c r="O105" s="50"/>
       <c r="P105" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q105" s="47" t="str">
+      <c r="Q105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="47"/>
-      <c r="S105" s="47" t="str">
+      <c r="R105" s="50"/>
+      <c r="S105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="47"/>
+      <c r="T105" s="50"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="50" t="str">
+      <c r="W105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="50" t="str">
+      <c r="X105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="47" t="str">
+      <c r="Y105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="47" t="str">
+      <c r="Z105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7489,61 +7424,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="80"/>
+      <c r="D106" s="81"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="50"/>
-      <c r="G106" s="50"/>
+      <c r="F106" s="53"/>
+      <c r="G106" s="53"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="50" t="str">
+      <c r="I106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="50" t="str">
+      <c r="J106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="50" t="str">
+      <c r="K106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
         <v> </v>
       </c>
-      <c r="L106" s="50"/>
-      <c r="M106" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="50"/>
-      <c r="O106" s="47"/>
+      <c r="L106" s="53"/>
+      <c r="M106" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="53"/>
+      <c r="O106" s="50"/>
       <c r="P106" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q106" s="47" t="str">
+      <c r="Q106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="47"/>
-      <c r="S106" s="47" t="str">
+      <c r="R106" s="50"/>
+      <c r="S106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="47"/>
+      <c r="T106" s="50"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="50" t="str">
+      <c r="W106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="50" t="str">
+      <c r="X106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="47" t="str">
+      <c r="Y106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="47" t="str">
+      <c r="Z106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7553,61 +7488,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="80"/>
-      <c r="E107" s="84"/>
-      <c r="F107" s="50"/>
-      <c r="G107" s="50"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="85"/>
+      <c r="F107" s="53"/>
+      <c r="G107" s="53"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="50" t="str">
+      <c r="I107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="50" t="str">
+      <c r="J107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="50" t="str">
+      <c r="K107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
         <v> </v>
       </c>
-      <c r="L107" s="50"/>
-      <c r="M107" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="50"/>
-      <c r="O107" s="47"/>
+      <c r="L107" s="53"/>
+      <c r="M107" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="53"/>
+      <c r="O107" s="50"/>
       <c r="P107" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q107" s="47" t="str">
+      <c r="Q107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="47"/>
-      <c r="S107" s="47" t="str">
+      <c r="R107" s="50"/>
+      <c r="S107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="47"/>
+      <c r="T107" s="50"/>
       <c r="U107" s="54"/>
-      <c r="V107" s="84"/>
-      <c r="W107" s="50" t="str">
+      <c r="V107" s="85"/>
+      <c r="W107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="50" t="str">
+      <c r="X107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="47" t="str">
+      <c r="Y107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="47" t="str">
+      <c r="Z107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7616,7 +7551,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7645,9 +7580,9 @@
         <f aca="false">SUM(K91:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="50"/>
+      <c r="L108" s="53"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="50"/>
+      <c r="N108" s="53"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O91:O107)</f>
         <v>0</v>
@@ -7665,8 +7600,8 @@
         <f aca="false">SUM(S91:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="47"/>
-      <c r="U108" s="49"/>
+      <c r="T108" s="50"/>
+      <c r="U108" s="52"/>
       <c r="V108" s="61" t="n">
         <f aca="false">SUM(V91:V107)</f>
         <v>0</v>
@@ -7691,31 +7626,31 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="73"/>
-      <c r="D109" s="68"/>
-      <c r="E109" s="50"/>
-      <c r="F109" s="50"/>
-      <c r="G109" s="50"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="74"/>
+      <c r="D109" s="69"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="53"/>
+      <c r="G109" s="53"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="50"/>
-      <c r="J109" s="50"/>
-      <c r="K109" s="50"/>
-      <c r="L109" s="50"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="53"/>
+      <c r="L109" s="53"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="50"/>
-      <c r="O109" s="47"/>
-      <c r="P109" s="48"/>
-      <c r="Q109" s="47"/>
-      <c r="R109" s="47"/>
-      <c r="S109" s="47"/>
-      <c r="T109" s="47"/>
-      <c r="U109" s="49"/>
-      <c r="V109" s="50"/>
-      <c r="W109" s="47"/>
-      <c r="X109" s="47"/>
-      <c r="Y109" s="47"/>
-      <c r="Z109" s="47"/>
+      <c r="N109" s="53"/>
+      <c r="O109" s="50"/>
+      <c r="P109" s="51"/>
+      <c r="Q109" s="50"/>
+      <c r="R109" s="50"/>
+      <c r="S109" s="50"/>
+      <c r="T109" s="50"/>
+      <c r="U109" s="52"/>
+      <c r="V109" s="53"/>
+      <c r="W109" s="50"/>
+      <c r="X109" s="50"/>
+      <c r="Y109" s="50"/>
+      <c r="Z109" s="50"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7727,105 +7662,105 @@
       <c r="C110" s="43"/>
       <c r="D110" s="44" t="n">
         <f aca="false">D59</f>
-        <v>46118</v>
-      </c>
-      <c r="E110" s="74" t="n">
+        <v>45753</v>
+      </c>
+      <c r="E110" s="75" t="n">
         <f aca="false">E64+E72+E80+E88+E108</f>
-        <v>32500</v>
-      </c>
-      <c r="F110" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="75" t="n">
         <f aca="false">F64+F72+F80+F88+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="74" t="n">
+      <c r="G110" s="75" t="n">
         <f aca="false">G64+G72+G80+G88+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="74" t="n">
+      <c r="I110" s="75" t="n">
         <f aca="false">I64+I72+I80+I88+I108</f>
-        <v>3250</v>
-      </c>
-      <c r="J110" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="75" t="n">
         <f aca="false">J64+J72+J80+J88+J108</f>
-        <v>3250</v>
-      </c>
-      <c r="K110" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="75" t="n">
         <f aca="false">K64+K72+K80+K88+K108</f>
-        <v>29250</v>
-      </c>
-      <c r="L110" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="53"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="50"/>
-      <c r="O110" s="74" t="n">
+      <c r="N110" s="53"/>
+      <c r="O110" s="75" t="n">
         <f aca="false">O64+O72+O80+O88+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="74" t="n">
+      <c r="Q110" s="75" t="n">
         <f aca="false">Q64+Q72+Q80+Q88+Q108</f>
-        <v>32500</v>
-      </c>
-      <c r="R110" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="75" t="n">
         <f aca="false">R64+R72+R80+R88+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="74" t="n">
+      <c r="S110" s="75" t="n">
         <f aca="false">S64+S72+S80+S88+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="47"/>
-      <c r="U110" s="49"/>
-      <c r="V110" s="74" t="n">
+      <c r="T110" s="50"/>
+      <c r="U110" s="52"/>
+      <c r="V110" s="75" t="n">
         <f aca="false">V64+V72+V80+V88+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="74" t="n">
+      <c r="W110" s="75" t="n">
         <f aca="false">W64+W72+W80+W88+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="74" t="n">
+      <c r="X110" s="75" t="n">
         <f aca="false">X64+X72+X80+X88+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="74" t="n">
+      <c r="Y110" s="75" t="n">
         <f aca="false">Y64+Y72+Y80+Y88+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="74" t="n">
+      <c r="Z110" s="75" t="n">
         <f aca="false">Z64+Z72+Z80+Z88+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="85"/>
-      <c r="B111" s="86"/>
-      <c r="C111" s="87"/>
-      <c r="D111" s="88"/>
-      <c r="E111" s="89"/>
-      <c r="F111" s="89"/>
-      <c r="G111" s="89"/>
-      <c r="H111" s="90"/>
-      <c r="I111" s="89"/>
-      <c r="J111" s="89"/>
-      <c r="K111" s="89"/>
-      <c r="L111" s="89"/>
-      <c r="M111" s="90"/>
-      <c r="N111" s="89"/>
-      <c r="O111" s="91"/>
-      <c r="P111" s="92"/>
-      <c r="Q111" s="91"/>
-      <c r="R111" s="91"/>
-      <c r="S111" s="91"/>
-      <c r="T111" s="91"/>
-      <c r="U111" s="86"/>
-      <c r="V111" s="89"/>
-      <c r="W111" s="89"/>
-      <c r="X111" s="89"/>
-      <c r="Y111" s="91"/>
-      <c r="Z111" s="91"/>
-      <c r="AA111" s="93"/>
+      <c r="A111" s="86"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="88"/>
+      <c r="D111" s="89"/>
+      <c r="E111" s="90"/>
+      <c r="F111" s="90"/>
+      <c r="G111" s="90"/>
+      <c r="H111" s="91"/>
+      <c r="I111" s="90"/>
+      <c r="J111" s="90"/>
+      <c r="K111" s="90"/>
+      <c r="L111" s="90"/>
+      <c r="M111" s="91"/>
+      <c r="N111" s="90"/>
+      <c r="O111" s="92"/>
+      <c r="P111" s="93"/>
+      <c r="Q111" s="92"/>
+      <c r="R111" s="92"/>
+      <c r="S111" s="92"/>
+      <c r="T111" s="92"/>
+      <c r="U111" s="87"/>
+      <c r="V111" s="90"/>
+      <c r="W111" s="90"/>
+      <c r="X111" s="90"/>
+      <c r="Y111" s="92"/>
+      <c r="Z111" s="92"/>
+      <c r="AA111" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -7911,37 +7846,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="94" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="94" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="94" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="94" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="94" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="94" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="94" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="94" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="94" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="94" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="94" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="94" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="95" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="95" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="95" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="95" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="95" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="95" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="95" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="95" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="95" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="95" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="95"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="96"/>
+      <c r="A1" s="96"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7953,23 +7888,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="104"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="105"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7981,21 +7916,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="104"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="105"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -8007,31 +7942,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="97"/>
-      <c r="B4" s="107" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="108" t="s">
+      <c r="A4" s="98"/>
+      <c r="B4" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="102"/>
-      <c r="G4" s="109" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="108" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="102"/>
-      <c r="M4" s="110" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" s="110"/>
-      <c r="O4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="110" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="103"/>
+      <c r="M4" s="111" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="111"/>
+      <c r="O4" s="105"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -8043,25 +7978,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="97"/>
-      <c r="B5" s="98" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="98" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="99"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="104"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="100"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="105"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -8073,31 +8008,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="97"/>
-      <c r="B6" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112" t="n">
+      <c r="A6" s="98"/>
+      <c r="B6" s="112" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="113" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="111" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="112" t="n">
+      <c r="F6" s="103"/>
+      <c r="G6" s="112" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="113" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="102"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="104"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="105"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -8109,31 +8044,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="97"/>
-      <c r="B7" s="111" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="112" t="n">
+      <c r="A7" s="98"/>
+      <c r="B7" s="112" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="113" t="n">
         <f aca="false">Schedule!E72</f>
-        <v>32500</v>
-      </c>
-      <c r="F7" s="102"/>
-      <c r="G7" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="103"/>
+      <c r="G7" s="112" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="113" t="n">
         <f aca="false">Schedule!V19+Schedule!V72</f>
         <v>0</v>
       </c>
-      <c r="L7" s="102"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="104"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="105"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -8145,31 +8080,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="97"/>
-      <c r="B8" s="111" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112" t="n">
+      <c r="A8" s="98"/>
+      <c r="B8" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="113" t="n">
         <f aca="false">Schedule!E80</f>
         <v>0</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="111" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="112" t="n">
+      <c r="F8" s="103"/>
+      <c r="G8" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="113" t="n">
         <f aca="false">Schedule!V27+Schedule!V80</f>
         <v>0</v>
       </c>
-      <c r="L8" s="102"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="104"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="105"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -8181,31 +8116,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="97"/>
-      <c r="B9" s="111" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="112" t="n">
+      <c r="A9" s="98"/>
+      <c r="B9" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113" t="n">
         <f aca="false">Schedule!E88</f>
         <v>0</v>
       </c>
-      <c r="F9" s="102"/>
-      <c r="G9" s="111" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="112" t="n">
+      <c r="F9" s="103"/>
+      <c r="G9" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="113" t="n">
         <f aca="false">Schedule!V35+Schedule!V88</f>
         <v>0</v>
       </c>
-      <c r="L9" s="102"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="104"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="105"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -8217,31 +8152,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="97"/>
-      <c r="B10" s="111" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112" t="n">
+      <c r="A10" s="98"/>
+      <c r="B10" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="111" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="112" t="n">
+      <c r="F10" s="103"/>
+      <c r="G10" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="113" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
-        <v>12500</v>
-      </c>
-      <c r="L10" s="102"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="104"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="103"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="105"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8253,31 +8188,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="97"/>
-      <c r="B11" s="113" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="113"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114" t="n">
+      <c r="A11" s="98"/>
+      <c r="B11" s="114" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="115" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>32500</v>
-      </c>
-      <c r="F11" s="102"/>
-      <c r="G11" s="115" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="115"/>
-      <c r="K11" s="114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="103"/>
+      <c r="G11" s="116" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="115" t="n">
         <f aca="false">SUM(K6:K10)</f>
-        <v>12500</v>
-      </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="104"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="103"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="111"/>
+      <c r="O11" s="105"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8289,21 +8224,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="97"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="102"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="104"/>
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="105"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8315,31 +8250,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="97"/>
-      <c r="B13" s="113" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="116" t="n">
+      <c r="A13" s="98"/>
+      <c r="B13" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="117" t="n">
         <f aca="false">[2]Mar!$AB$2</f>
-        <v>32500</v>
-      </c>
-      <c r="F13" s="102"/>
-      <c r="G13" s="115" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="115"/>
-      <c r="K13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="103"/>
+      <c r="G13" s="116" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="117" t="n">
         <f aca="false">[3]Mar!$V$2</f>
-        <v>12500</v>
-      </c>
-      <c r="L13" s="102"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="104"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="103"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="105"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8351,21 +8286,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="97"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="104"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="105"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8377,33 +8312,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="97"/>
-      <c r="B15" s="117" t="str">
+      <c r="A15" s="98"/>
+      <c r="B15" s="118" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="118" t="n">
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="119" t="n">
         <f aca="false">E13-E11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="102"/>
-      <c r="G15" s="117" t="str">
+      <c r="F15" s="103"/>
+      <c r="G15" s="118" t="str">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="118" t="n">
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="119" t="n">
         <f aca="false">K13-K11</f>
         <v>0</v>
       </c>
-      <c r="L15" s="102"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="104"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="105"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8415,21 +8350,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="119"/>
-      <c r="B16" s="120"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="125"/>
+      <c r="A16" s="120"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="125"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="126"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8481,122 +8416,122 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="126" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="126" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="127" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="126" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="126" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="128"/>
-      <c r="B1" s="98"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="128"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="129"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="128"/>
-      <c r="B2" s="131"/>
-      <c r="C2" s="132" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133" t="n">
+      <c r="A2" s="129"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="n">
         <f aca="false">SUM(E8:E14)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="128"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="136" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="129"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="128"/>
-      <c r="B3" s="136" t="s">
-        <v>63</v>
+      <c r="A3" s="129"/>
+      <c r="B3" s="137" t="s">
+        <v>59</v>
       </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="128"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="129"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="128"/>
-      <c r="B4" s="49"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="128"/>
-    </row>
-    <row r="5" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="139"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="129"/>
+    </row>
+    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="141" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="G5" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="H5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="140" t="s">
+      <c r="I5" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="140" t="s">
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="140" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="140" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="M5" s="139"/>
-    </row>
-    <row r="6" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="139"/>
+      <c r="M5" s="140"/>
+    </row>
+    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="140"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8604,273 +8539,273 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="140" t="s">
-        <v>73</v>
-      </c>
-      <c r="J6" s="140" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="140" t="s">
-        <v>75</v>
+      <c r="I6" s="141" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="141" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="141" t="s">
+        <v>71</v>
       </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="139"/>
+      <c r="M6" s="140"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="128"/>
-      <c r="B7" s="49"/>
+      <c r="A7" s="129"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="128"/>
+      <c r="M7" s="129"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="128"/>
+      <c r="A8" s="129"/>
       <c r="B8" s="54"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="134" t="str">
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="135" t="str">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="134" t="str">
+      <c r="J8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="134" t="str">
+      <c r="K8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="128"/>
+      <c r="M8" s="129"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="128"/>
-      <c r="B9" s="49"/>
+      <c r="A9" s="129"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="128"/>
+      <c r="M9" s="129"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="128"/>
+      <c r="A10" s="129"/>
       <c r="B10" s="54"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="142"/>
-      <c r="I10" s="134" t="e">
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="134" t="str">
+      <c r="J10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="134" t="str">
+      <c r="K10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="128"/>
+      <c r="M10" s="129"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="128"/>
-      <c r="B11" s="49"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="52"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="128"/>
+      <c r="M11" s="129"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="128"/>
+      <c r="A12" s="129"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="134" t="e">
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="134" t="str">
+      <c r="J12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="134" t="str">
+      <c r="K12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="128"/>
+      <c r="M12" s="129"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="128"/>
-      <c r="B13" s="49"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="134"/>
-      <c r="J13" s="134"/>
-      <c r="K13" s="134"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="128"/>
+      <c r="M13" s="129"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="128"/>
+      <c r="A14" s="129"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="134" t="e">
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="134" t="str">
+      <c r="J14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="134" t="str">
+      <c r="K14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="128"/>
+      <c r="M14" s="129"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="128"/>
-      <c r="B15" s="49"/>
+      <c r="A15" s="129"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="128"/>
+      <c r="M15" s="129"/>
     </row>
     <row r="16" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="128"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="100"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="100"/>
-      <c r="M16" s="128"/>
+      <c r="A16" s="129"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="129"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="128"/>
-      <c r="B17" s="136" t="s">
-        <v>76</v>
+      <c r="A17" s="129"/>
+      <c r="B17" s="137" t="s">
+        <v>72</v>
       </c>
       <c r="C17" s="62"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
       <c r="H17" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17" s="131"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
+        <v>73</v>
+      </c>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="128"/>
+      <c r="M17" s="129"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="128"/>
-      <c r="B18" s="49"/>
+      <c r="A18" s="129"/>
+      <c r="B18" s="52"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
       <c r="L18" s="62"/>
-      <c r="M18" s="128"/>
-    </row>
-    <row r="19" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="139"/>
+      <c r="M18" s="129"/>
+    </row>
+    <row r="19" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="140"/>
       <c r="B19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="141" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="G19" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="H19" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="140" t="s">
+      <c r="I19" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="140" t="s">
+      <c r="J19" s="141"/>
+      <c r="K19" s="141"/>
+      <c r="L19" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="140" t="s">
-        <v>69</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="I19" s="140" t="s">
-        <v>71</v>
-      </c>
-      <c r="J19" s="140"/>
-      <c r="K19" s="140"/>
-      <c r="L19" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="M19" s="139"/>
-    </row>
-    <row r="20" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="139"/>
+      <c r="M19" s="140"/>
+    </row>
+    <row r="20" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="140"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8878,203 +8813,203 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
-      <c r="I20" s="140" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" s="140" t="s">
-        <v>74</v>
-      </c>
-      <c r="K20" s="140" t="s">
-        <v>75</v>
+      <c r="I20" s="141" t="s">
+        <v>69</v>
+      </c>
+      <c r="J20" s="141" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20" s="141" t="s">
+        <v>71</v>
       </c>
       <c r="L20" s="21"/>
-      <c r="M20" s="139"/>
-    </row>
-    <row r="21" s="141" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="139"/>
-      <c r="B21" s="143"/>
-      <c r="C21" s="143"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="139"/>
+      <c r="M20" s="140"/>
+    </row>
+    <row r="21" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="140"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="140"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="128"/>
+      <c r="A22" s="129"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="142"/>
-      <c r="I22" s="134" t="str">
+      <c r="E22" s="134"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="135" t="str">
         <f aca="false">IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="134" t="str">
+      <c r="J22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="134" t="str">
+      <c r="K22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="128"/>
+      <c r="M22" s="129"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="128"/>
-      <c r="B23" s="49"/>
+      <c r="A23" s="129"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="134"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="128"/>
+      <c r="M23" s="129"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="128"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="142"/>
-      <c r="I24" s="134" t="e">
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="134" t="str">
+      <c r="J24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="134" t="str">
+      <c r="K24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="128"/>
+      <c r="M24" s="129"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="128"/>
-      <c r="B25" s="49"/>
+      <c r="A25" s="129"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="134"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="135"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="128"/>
+      <c r="M25" s="129"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="128"/>
+      <c r="A26" s="129"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="142"/>
-      <c r="I26" s="134" t="e">
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="134" t="str">
+      <c r="J26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="134" t="str">
+      <c r="K26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="128"/>
+      <c r="M26" s="129"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="128"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="129"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="134"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="134"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="128"/>
+      <c r="M27" s="129"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="128"/>
+      <c r="A28" s="129"/>
       <c r="B28" s="54"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="142"/>
-      <c r="I28" s="134" t="e">
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="143"/>
+      <c r="I28" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="134" t="str">
+      <c r="J28" s="135" t="str">
         <f aca="false">IF(H28&gt;0,I28-K28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="134" t="str">
+      <c r="K28" s="135" t="str">
         <f aca="false">IF(H28&gt;0,G28/H28," ")</f>
         <v> </v>
       </c>
       <c r="L28" s="56"/>
-      <c r="M28" s="128"/>
+      <c r="M28" s="129"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="128"/>
-      <c r="B29" s="49"/>
+      <c r="A29" s="129"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="134"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="135"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="128"/>
+      <c r="M29" s="129"/>
     </row>
     <row r="30" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="128"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="128"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="128"/>
+      <c r="A30" s="129"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="129"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
   </si>
   <si>
-    <t xml:space="preserve">Laptop (0.5 years old)</t>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">Existing Land &amp; Property</t>
@@ -250,10 +250,16 @@
     <t xml:space="preserve">Computers</t>
   </si>
   <si>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Existing Computers</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing over £</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van (2.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing under £</t>
@@ -268,10 +274,16 @@
     <t xml:space="preserve">NEW FIXED ASSETS Bought AFTER </t>
   </si>
   <si>
-    <t xml:space="preserve">Land &amp; Property</t>
+    <t xml:space="preserve">New Land &amp; Property</t>
   </si>
   <si>
-    <t xml:space="preserve">New Land &amp; Property</t>
+    <t xml:space="preserve">Dell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IKEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
   </si>
   <si>
     <t xml:space="preserve">New Plant &amp; Machinery</t>
@@ -415,6 +427,18 @@
   </si>
   <si>
     <t xml:space="preserve">Monthly Interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close Brothers Asset Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP-2025-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precision Tooling Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP-2025-02</t>
   </si>
   <si>
     <t xml:space="preserve">Hire Purchase Agreements existing at start of financial year</t>
@@ -752,7 +776,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -937,8 +961,28 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -949,26 +993,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1015,10 +1039,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1377,7 +1397,7 @@
       <sheetData sheetId="9">
         <row r="4">
           <cell r="B4">
-            <v>45753</v>
+            <v>46118</v>
           </cell>
         </row>
         <row r="4">
@@ -1387,7 +1407,7 @@
         </row>
         <row r="5">
           <cell r="G5">
-            <v>0.18</v>
+            <v>0.14</v>
           </cell>
         </row>
         <row r="8">
@@ -1422,7 +1442,7 @@
         </row>
         <row r="17">
           <cell r="B17">
-            <v>46117</v>
+            <v>46482</v>
           </cell>
         </row>
         <row r="17">
@@ -1471,7 +1491,7 @@
       <sheetData sheetId="12">
         <row r="2">
           <cell r="AB2">
-            <v>0</v>
+            <v>32500</v>
           </cell>
         </row>
       </sheetData>
@@ -1516,7 +1536,7 @@
       <sheetData sheetId="12">
         <row r="2">
           <cell r="V2">
-            <v>0</v>
+            <v>12500</v>
           </cell>
         </row>
       </sheetData>
@@ -1679,30 +1699,30 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12" t="n">
         <f aca="false">E57+E110</f>
-        <v>0</v>
+        <v>65500</v>
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>0</v>
+        <v>10098</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
-        <v>0</v>
+        <v>22902</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="13" t="n">
         <f aca="false">I57+I110</f>
-        <v>0</v>
+        <v>11740</v>
       </c>
       <c r="J1" s="13" t="n">
         <f aca="false">J57+J110</f>
-        <v>0</v>
+        <v>21838</v>
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>0</v>
+        <v>30990</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1711,22 +1731,22 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13" t="n">
         <f aca="false">O57+O110</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="P1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="Q1" s="13" t="n">
         <f aca="false">Q57+Q110</f>
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="S1" s="13" t="n">
         <f aca="false">S57+S110</f>
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="T1" s="16"/>
       <c r="U1" s="17" t="s">
@@ -1734,19 +1754,19 @@
       </c>
       <c r="V1" s="13" t="n">
         <f aca="false">V57+V110</f>
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="W1" s="13" t="n">
         <f aca="false">W57+W110</f>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="X1" s="13" t="n">
         <f aca="false">X57+X110</f>
-        <v>0</v>
+        <v>17328</v>
       </c>
       <c r="Y1" s="13" t="n">
         <f aca="false">Y57+Y110</f>
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="Z1" s="13" t="n">
         <f aca="false">Z57+Z110</f>
@@ -1854,28 +1874,28 @@
       <c r="E4" s="22"/>
       <c r="F4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
+        <v>46118</v>
       </c>
       <c r="G4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
+        <v>46118</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="23"/>
       <c r="J4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46117</v>
+        <v>46482</v>
       </c>
       <c r="K4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46117</v>
+        <v>46482</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
       <c r="N4" s="13"/>
       <c r="O4" s="26" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
+        <v>46118</v>
       </c>
       <c r="P4" s="27" t="n">
         <f aca="false">[1]Admin!$G$4</f>
@@ -1884,11 +1904,11 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="28" t="n">
         <f aca="false">[1]Admin!$G$5</f>
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="S4" s="26" t="n">
         <f aca="false">[1]Admin!$B$17</f>
-        <v>46117</v>
+        <v>46482</v>
       </c>
       <c r="T4" s="16"/>
       <c r="U4" s="17"/>
@@ -1934,24 +1954,45 @@
         <v>22</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="44" t="n">
+        <f aca="false">[1]Admin!$B$4</f>
+        <v>46118</v>
+      </c>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="50"/>
+      <c r="W6" s="50"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42"/>
+      <c r="B7" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="45" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y6" s="7" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="45"/>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">[1]Admin!$G$13</f>
         <v>0</v>
       </c>
@@ -1959,20 +2000,20 @@
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
-      <c r="M7" s="49"/>
+      <c r="M7" s="46"/>
       <c r="N7" s="45"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="50"/>
-      <c r="Z7" s="50"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1982,7 +2023,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="53" t="str">
+      <c r="G8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -1990,39 +2031,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="53" t="str">
+      <c r="I8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="53" t="str">
+      <c r="J8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="53" t="str">
-        <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
-        <v> </v>
-      </c>
-      <c r="L8" s="53"/>
+      <c r="K8" s="50" t="str">
+        <f aca="false">IF(E8&gt;0,IF(V8&gt;0,0,E8-J8)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L8" s="50"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="53" t="str">
+      <c r="W8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="53" t="str">
+      <c r="X8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2032,7 +2073,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="53" t="str">
+      <c r="G9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -2040,39 +2081,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="53" t="str">
+      <c r="I9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="53" t="str">
+      <c r="J9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="53" t="str">
-        <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
-        <v> </v>
-      </c>
-      <c r="L9" s="53"/>
+      <c r="K9" s="50" t="str">
+        <f aca="false">IF(E9&gt;0,IF(V9&gt;0,0,E9-J9)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L9" s="50"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="53" t="str">
+      <c r="W9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="53" t="str">
+      <c r="X9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="50"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2082,7 +2123,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="53" t="str">
+      <c r="G10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -2090,39 +2131,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="53" t="str">
+      <c r="I10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="53" t="str">
+      <c r="J10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="53" t="str">
-        <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
-        <v> </v>
-      </c>
-      <c r="L10" s="53"/>
+      <c r="K10" s="50" t="str">
+        <f aca="false">IF(E10&gt;0,IF(V10&gt;0,0,E10-J10)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L10" s="50"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="53" t="str">
+      <c r="W10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="53" t="str">
+      <c r="X10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="50"/>
-      <c r="Z10" s="50"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="47"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2157,9 +2198,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="53"/>
+      <c r="L11" s="50"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="53"/>
+      <c r="N11" s="50"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -2177,8 +2218,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="50"/>
-      <c r="U11" s="52"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="49"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2206,62 +2247,62 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="53"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="53"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="66"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="67" t="n">
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="66" t="n">
         <f aca="false">[1]Admin!$G$14</f>
         <v>0.1</v>
       </c>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="50"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2271,7 +2312,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2279,48 +2320,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="53" t="str">
+      <c r="J14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="53" t="str">
-        <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
-        <v> </v>
-      </c>
-      <c r="L14" s="53"/>
+      <c r="K14" s="50" t="str">
+        <f aca="false">IF(E14&gt;0,IF(V14&gt;0,0,E14-J14)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L14" s="50"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50" t="str">
+      <c r="N14" s="50"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="50" t="str">
+      <c r="S14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="50"/>
+      <c r="T14" s="47"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="53" t="str">
+      <c r="W14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="53" t="str">
+      <c r="X14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="50" t="str">
+      <c r="Y14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="50" t="str">
+      <c r="Z14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2333,7 +2374,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="53" t="str">
+      <c r="G15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2341,48 +2382,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="53" t="str">
+      <c r="I15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="53" t="str">
+      <c r="J15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="53" t="str">
-        <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
-        <v> </v>
-      </c>
-      <c r="L15" s="53"/>
+      <c r="K15" s="50" t="str">
+        <f aca="false">IF(E15&gt;0,IF(V15&gt;0,0,E15-J15)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L15" s="50"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50" t="str">
+      <c r="N15" s="50"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="50" t="str">
+      <c r="S15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="50"/>
+      <c r="T15" s="47"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="53" t="str">
+      <c r="W15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="53" t="str">
+      <c r="X15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="50" t="str">
+      <c r="Y15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="50" t="str">
+      <c r="Z15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2395,7 +2436,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2403,48 +2444,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="53" t="str">
+      <c r="J16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="53" t="str">
-        <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
-        <v> </v>
-      </c>
-      <c r="L16" s="53"/>
+      <c r="K16" s="50" t="str">
+        <f aca="false">IF(E16&gt;0,IF(V16&gt;0,0,E16-J16)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L16" s="50"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50" t="str">
+      <c r="N16" s="50"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="50" t="str">
+      <c r="S16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="50"/>
+      <c r="T16" s="47"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="53" t="str">
+      <c r="W16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="53" t="str">
+      <c r="X16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="50" t="str">
+      <c r="Y16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="50" t="str">
+      <c r="Z16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2457,7 +2498,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="53" t="str">
+      <c r="G17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2465,48 +2506,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="53" t="str">
+      <c r="I17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="53" t="str">
+      <c r="J17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="53" t="str">
-        <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
-        <v> </v>
-      </c>
-      <c r="L17" s="53"/>
+      <c r="K17" s="50" t="str">
+        <f aca="false">IF(E17&gt;0,IF(V17&gt;0,0,E17-J17)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L17" s="50"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50" t="str">
+      <c r="N17" s="50"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="50" t="str">
+      <c r="S17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="50"/>
+      <c r="T17" s="47"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="53" t="str">
+      <c r="W17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="53" t="str">
+      <c r="X17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="50" t="str">
+      <c r="Y17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="50" t="str">
+      <c r="Z17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2519,7 +2560,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="53" t="str">
+      <c r="G18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2527,48 +2568,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="53" t="str">
+      <c r="J18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="53" t="str">
-        <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
-        <v> </v>
-      </c>
-      <c r="L18" s="53"/>
+      <c r="K18" s="50" t="str">
+        <f aca="false">IF(E18&gt;0,IF(V18&gt;0,0,E18-J18)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L18" s="50"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50" t="str">
+      <c r="N18" s="50"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="50" t="str">
+      <c r="S18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="50"/>
+      <c r="T18" s="47"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="53" t="str">
+      <c r="W18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="53" t="str">
+      <c r="X18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="50" t="str">
+      <c r="Y18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="50" t="str">
+      <c r="Z18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2606,9 +2647,9 @@
         <f aca="false">SUM(K14:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="53"/>
+      <c r="L19" s="50"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="53"/>
+      <c r="N19" s="50"/>
       <c r="O19" s="61" t="n">
         <f aca="false">SUM(O14:O18)</f>
         <v>0</v>
@@ -2626,8 +2667,8 @@
         <f aca="false">SUM(S14:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="50"/>
-      <c r="U19" s="52"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="49"/>
       <c r="V19" s="60" t="n">
         <f aca="false">SUM(V14:V18)</f>
         <v>0</v>
@@ -2655,62 +2696,62 @@
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
       <c r="H20" s="58"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
       <c r="P20" s="62"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="52"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
+      <c r="Z20" s="50"/>
       <c r="AA20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="42"/>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="66"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="67" t="n">
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="66" t="n">
         <f aca="false">[1]Admin!$G$15</f>
         <v>0.2</v>
       </c>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="50"/>
-      <c r="Z21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="50"/>
+      <c r="W21" s="50"/>
+      <c r="X21" s="50"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="47"/>
       <c r="AA21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2720,7 +2761,7 @@
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
       <c r="F22" s="57"/>
-      <c r="G22" s="53" t="str">
+      <c r="G22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,E22-F22," ")</f>
         <v> </v>
       </c>
@@ -2728,48 +2769,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I22" s="53" t="str">
+      <c r="I22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,MIN(E22*H22,G22)," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="53" t="str">
+      <c r="J22" s="50" t="str">
         <f aca="false">IF(E22&gt;0,F22+I22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="53" t="str">
-        <f aca="false">IF(E22&gt;0,E22-J22," ")</f>
-        <v> </v>
-      </c>
-      <c r="L22" s="53"/>
+      <c r="K22" s="50" t="str">
+        <f aca="false">IF(E22&gt;0,IF(V22&gt;0,0,E22-J22)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L22" s="50"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="68"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50" t="str">
+      <c r="N22" s="50"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47" t="str">
         <f aca="false">IF(O22&gt;0,O22*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S22" s="50" t="str">
+      <c r="S22" s="47" t="str">
         <f aca="false">IF(O22&gt;0,O22-R22," ")</f>
         <v> </v>
       </c>
-      <c r="T22" s="50"/>
+      <c r="T22" s="47"/>
       <c r="U22" s="54"/>
       <c r="V22" s="57"/>
-      <c r="W22" s="53" t="str">
+      <c r="W22" s="50" t="str">
         <f aca="false">IF(V22&gt;0,E22," ")</f>
         <v> </v>
       </c>
-      <c r="X22" s="53" t="str">
+      <c r="X22" s="50" t="str">
         <f aca="false">IF(V22&gt;0,J22," ")</f>
         <v> </v>
       </c>
-      <c r="Y22" s="50" t="str">
+      <c r="Y22" s="47" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&lt;S22,S22-V22," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z22" s="50" t="str">
+      <c r="Z22" s="47" t="str">
         <f aca="false">IF((U22+V22)&gt;0,IF(V22&gt;S22,V22-S22," ")," ")</f>
         <v> </v>
       </c>
@@ -2782,7 +2823,7 @@
       <c r="D23" s="56"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="53" t="str">
+      <c r="G23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,E23-F23," ")</f>
         <v> </v>
       </c>
@@ -2790,48 +2831,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I23" s="53" t="str">
+      <c r="I23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,MIN(E23*H23,G23)," ")</f>
         <v> </v>
       </c>
-      <c r="J23" s="53" t="str">
+      <c r="J23" s="50" t="str">
         <f aca="false">IF(E23&gt;0,F23+I23," ")</f>
         <v> </v>
       </c>
-      <c r="K23" s="53" t="str">
-        <f aca="false">IF(E23&gt;0,E23-J23," ")</f>
-        <v> </v>
-      </c>
-      <c r="L23" s="53"/>
+      <c r="K23" s="50" t="str">
+        <f aca="false">IF(E23&gt;0,IF(V23&gt;0,0,E23-J23)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L23" s="50"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50" t="str">
+      <c r="N23" s="50"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="47" t="str">
         <f aca="false">IF(O23&gt;0,O23*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S23" s="50" t="str">
+      <c r="S23" s="47" t="str">
         <f aca="false">IF(O23&gt;0,O23-R23," ")</f>
         <v> </v>
       </c>
-      <c r="T23" s="50"/>
+      <c r="T23" s="47"/>
       <c r="U23" s="54"/>
       <c r="V23" s="57"/>
-      <c r="W23" s="53" t="str">
+      <c r="W23" s="50" t="str">
         <f aca="false">IF(V23&gt;0,E23," ")</f>
         <v> </v>
       </c>
-      <c r="X23" s="53" t="str">
+      <c r="X23" s="50" t="str">
         <f aca="false">IF(V23&gt;0,J23," ")</f>
         <v> </v>
       </c>
-      <c r="Y23" s="50" t="str">
+      <c r="Y23" s="47" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&lt;S23,S23-V23," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z23" s="50" t="str">
+      <c r="Z23" s="47" t="str">
         <f aca="false">IF((U23+V23)&gt;0,IF(V23&gt;S23,V23-S23," ")," ")</f>
         <v> </v>
       </c>
@@ -2844,7 +2885,7 @@
       <c r="D24" s="56"/>
       <c r="E24" s="57"/>
       <c r="F24" s="57"/>
-      <c r="G24" s="53" t="str">
+      <c r="G24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,E24-F24," ")</f>
         <v> </v>
       </c>
@@ -2852,48 +2893,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I24" s="53" t="str">
+      <c r="I24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,MIN(E24*H24,G24)," ")</f>
         <v> </v>
       </c>
-      <c r="J24" s="53" t="str">
+      <c r="J24" s="50" t="str">
         <f aca="false">IF(E24&gt;0,F24+I24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="53" t="str">
-        <f aca="false">IF(E24&gt;0,E24-J24," ")</f>
-        <v> </v>
-      </c>
-      <c r="L24" s="53"/>
+      <c r="K24" s="50" t="str">
+        <f aca="false">IF(E24&gt;0,IF(V24&gt;0,0,E24-J24)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L24" s="50"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50" t="str">
+      <c r="N24" s="50"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47" t="str">
         <f aca="false">IF(O24&gt;0,O24*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S24" s="50" t="str">
+      <c r="S24" s="47" t="str">
         <f aca="false">IF(O24&gt;0,O24-R24," ")</f>
         <v> </v>
       </c>
-      <c r="T24" s="50"/>
+      <c r="T24" s="47"/>
       <c r="U24" s="54"/>
       <c r="V24" s="57"/>
-      <c r="W24" s="53" t="str">
+      <c r="W24" s="50" t="str">
         <f aca="false">IF(V24&gt;0,E24," ")</f>
         <v> </v>
       </c>
-      <c r="X24" s="53" t="str">
+      <c r="X24" s="50" t="str">
         <f aca="false">IF(V24&gt;0,J24," ")</f>
         <v> </v>
       </c>
-      <c r="Y24" s="50" t="str">
+      <c r="Y24" s="47" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&lt;S24,S24-V24," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z24" s="50" t="str">
+      <c r="Z24" s="47" t="str">
         <f aca="false">IF((U24+V24)&gt;0,IF(V24&gt;S24,V24-S24," ")," ")</f>
         <v> </v>
       </c>
@@ -2906,7 +2947,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="53" t="str">
+      <c r="G25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2914,48 +2955,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="53" t="str">
+      <c r="I25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="53" t="str">
+      <c r="J25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="53" t="str">
-        <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
-        <v> </v>
-      </c>
-      <c r="L25" s="53"/>
+      <c r="K25" s="50" t="str">
+        <f aca="false">IF(E25&gt;0,IF(V25&gt;0,0,E25-J25)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L25" s="50"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50" t="str">
+      <c r="N25" s="50"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="50" t="str">
+      <c r="S25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="50"/>
+      <c r="T25" s="47"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="53" t="str">
+      <c r="W25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="53" t="str">
+      <c r="X25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="50" t="str">
+      <c r="Y25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="50" t="str">
+      <c r="Z25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2968,7 +3009,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="53" t="str">
+      <c r="G26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -2976,48 +3017,48 @@
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="53" t="str">
+      <c r="I26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="53" t="str">
+      <c r="J26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="53" t="str">
-        <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
-        <v> </v>
-      </c>
-      <c r="L26" s="53"/>
+      <c r="K26" s="50" t="str">
+        <f aca="false">IF(E26&gt;0,IF(V26&gt;0,0,E26-J26)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L26" s="50"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50" t="str">
+      <c r="N26" s="50"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="50" t="str">
+      <c r="S26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="50"/>
+      <c r="T26" s="47"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="53" t="str">
+      <c r="W26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="53" t="str">
+      <c r="X26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="50" t="str">
+      <c r="Y26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="50" t="str">
+      <c r="Z26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -3055,9 +3096,9 @@
         <f aca="false">SUM(K22:K26)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="53"/>
+      <c r="L27" s="50"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="53"/>
+      <c r="N27" s="50"/>
       <c r="O27" s="61" t="n">
         <f aca="false">SUM(O22:O26)</f>
         <v>0</v>
@@ -3075,8 +3116,8 @@
         <f aca="false">SUM(S22:S26)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="50"/>
-      <c r="U27" s="52"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="49"/>
       <c r="V27" s="60" t="n">
         <f aca="false">SUM(V22:V26)</f>
         <v>0</v>
@@ -3104,121 +3145,127 @@
       <c r="B28" s="63"/>
       <c r="C28" s="64"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
       <c r="H28" s="58"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
       <c r="P28" s="62"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="53"/>
-      <c r="X28" s="53"/>
-      <c r="Y28" s="53"/>
-      <c r="Z28" s="53"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="50"/>
+      <c r="W28" s="50"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
       <c r="AA28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="42"/>
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="66"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="67" t="n">
+      <c r="C29" s="51"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="66" t="n">
         <f aca="false">[1]Admin!$G$16</f>
         <v>0.33</v>
       </c>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="53"/>
-      <c r="W29" s="53"/>
-      <c r="X29" s="53"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="50"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="47"/>
+      <c r="Z29" s="47"/>
       <c r="AA29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="42"/>
       <c r="B30" s="54"/>
-      <c r="C30" s="55"/>
+      <c r="C30" s="55" t="s">
+        <v>30</v>
+      </c>
       <c r="D30" s="56"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="53" t="str">
+      <c r="E30" s="57" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F30" s="57" t="n">
+        <v>270</v>
+      </c>
+      <c r="G30" s="50" t="n">
         <f aca="false">IF(E30&gt;0,E30-F30," ")</f>
-        <v> </v>
+        <v>2730</v>
       </c>
       <c r="H30" s="58" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I30" s="53" t="str">
+      <c r="I30" s="50" t="n">
         <f aca="false">IF(E30&gt;0,MIN(E30*H30,G30)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J30" s="53" t="str">
+        <v>990</v>
+      </c>
+      <c r="J30" s="50" t="n">
         <f aca="false">IF(E30&gt;0,F30+I30," ")</f>
-        <v> </v>
-      </c>
-      <c r="K30" s="53" t="str">
-        <f aca="false">IF(E30&gt;0,E30-J30," ")</f>
-        <v> </v>
-      </c>
-      <c r="L30" s="53"/>
+        <v>1260</v>
+      </c>
+      <c r="K30" s="50" t="n">
+        <f aca="false">IF(E30&gt;0,IF(V30&gt;0,0,E30-J30)," ")</f>
+        <v>1740</v>
+      </c>
+      <c r="L30" s="50"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50" t="str">
+      <c r="N30" s="50"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="47"/>
+      <c r="R30" s="47" t="str">
         <f aca="false">IF(O30&gt;0,O30*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S30" s="50" t="str">
+      <c r="S30" s="47" t="str">
         <f aca="false">IF(O30&gt;0,O30-R30," ")</f>
         <v> </v>
       </c>
-      <c r="T30" s="50"/>
+      <c r="T30" s="47"/>
       <c r="U30" s="54"/>
       <c r="V30" s="57"/>
-      <c r="W30" s="53" t="str">
+      <c r="W30" s="50" t="str">
         <f aca="false">IF(V30&gt;0,E30," ")</f>
         <v> </v>
       </c>
-      <c r="X30" s="53" t="str">
+      <c r="X30" s="50" t="str">
         <f aca="false">IF(V30&gt;0,J30," ")</f>
         <v> </v>
       </c>
-      <c r="Y30" s="50" t="str">
+      <c r="Y30" s="47" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&lt;S30,S30-V30," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z30" s="50" t="str">
+      <c r="Z30" s="47" t="str">
         <f aca="false">IF((U30+V30)&gt;0,IF(V30&gt;S30,V30-S30," ")," ")</f>
         <v> </v>
       </c>
@@ -3231,7 +3278,7 @@
       <c r="D31" s="56"/>
       <c r="E31" s="57"/>
       <c r="F31" s="57"/>
-      <c r="G31" s="53" t="str">
+      <c r="G31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,E31-F31," ")</f>
         <v> </v>
       </c>
@@ -3239,48 +3286,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I31" s="53" t="str">
+      <c r="I31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,MIN(E31*H31,G31)," ")</f>
         <v> </v>
       </c>
-      <c r="J31" s="53" t="str">
+      <c r="J31" s="50" t="str">
         <f aca="false">IF(E31&gt;0,F31+I31," ")</f>
         <v> </v>
       </c>
-      <c r="K31" s="53" t="str">
-        <f aca="false">IF(E31&gt;0,E31-J31," ")</f>
-        <v> </v>
-      </c>
-      <c r="L31" s="53"/>
+      <c r="K31" s="50" t="str">
+        <f aca="false">IF(E31&gt;0,IF(V31&gt;0,0,E31-J31)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L31" s="50"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="68"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50" t="str">
+      <c r="N31" s="50"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="47"/>
+      <c r="R31" s="47" t="str">
         <f aca="false">IF(O31&gt;0,O31*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S31" s="50" t="str">
+      <c r="S31" s="47" t="str">
         <f aca="false">IF(O31&gt;0,O31-R31," ")</f>
         <v> </v>
       </c>
-      <c r="T31" s="50"/>
+      <c r="T31" s="47"/>
       <c r="U31" s="54"/>
       <c r="V31" s="57"/>
-      <c r="W31" s="53" t="str">
+      <c r="W31" s="50" t="str">
         <f aca="false">IF(V31&gt;0,E31," ")</f>
         <v> </v>
       </c>
-      <c r="X31" s="53" t="str">
+      <c r="X31" s="50" t="str">
         <f aca="false">IF(V31&gt;0,J31," ")</f>
         <v> </v>
       </c>
-      <c r="Y31" s="50" t="str">
+      <c r="Y31" s="47" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&lt;S31,S31-V31," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z31" s="50" t="str">
+      <c r="Z31" s="47" t="str">
         <f aca="false">IF((U31+V31)&gt;0,IF(V31&gt;S31,V31-S31," ")," ")</f>
         <v> </v>
       </c>
@@ -3293,7 +3340,7 @@
       <c r="D32" s="56"/>
       <c r="E32" s="57"/>
       <c r="F32" s="57"/>
-      <c r="G32" s="53" t="str">
+      <c r="G32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,E32-F32," ")</f>
         <v> </v>
       </c>
@@ -3301,48 +3348,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I32" s="53" t="str">
+      <c r="I32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,MIN(E32*H32,G32)," ")</f>
         <v> </v>
       </c>
-      <c r="J32" s="53" t="str">
+      <c r="J32" s="50" t="str">
         <f aca="false">IF(E32&gt;0,F32+I32," ")</f>
         <v> </v>
       </c>
-      <c r="K32" s="53" t="str">
-        <f aca="false">IF(E32&gt;0,E32-J32," ")</f>
-        <v> </v>
-      </c>
-      <c r="L32" s="53"/>
+      <c r="K32" s="50" t="str">
+        <f aca="false">IF(E32&gt;0,IF(V32&gt;0,0,E32-J32)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L32" s="50"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="68"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50" t="str">
+      <c r="N32" s="50"/>
+      <c r="O32" s="67"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="47"/>
+      <c r="R32" s="47" t="str">
         <f aca="false">IF(O32&gt;0,O32*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S32" s="50" t="str">
+      <c r="S32" s="47" t="str">
         <f aca="false">IF(O32&gt;0,O32-R32," ")</f>
         <v> </v>
       </c>
-      <c r="T32" s="50"/>
+      <c r="T32" s="47"/>
       <c r="U32" s="54"/>
       <c r="V32" s="57"/>
-      <c r="W32" s="53" t="str">
+      <c r="W32" s="50" t="str">
         <f aca="false">IF(V32&gt;0,E32," ")</f>
         <v> </v>
       </c>
-      <c r="X32" s="53" t="str">
+      <c r="X32" s="50" t="str">
         <f aca="false">IF(V32&gt;0,J32," ")</f>
         <v> </v>
       </c>
-      <c r="Y32" s="50" t="str">
+      <c r="Y32" s="47" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&lt;S32,S32-V32," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z32" s="50" t="str">
+      <c r="Z32" s="47" t="str">
         <f aca="false">IF((U32+V32)&gt;0,IF(V32&gt;S32,V32-S32," ")," ")</f>
         <v> </v>
       </c>
@@ -3355,7 +3402,7 @@
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
       <c r="F33" s="57"/>
-      <c r="G33" s="53" t="str">
+      <c r="G33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
         <v> </v>
       </c>
@@ -3363,48 +3410,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="53" t="str">
+      <c r="I33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="53" t="str">
+      <c r="J33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="53" t="str">
-        <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
-        <v> </v>
-      </c>
-      <c r="L33" s="53"/>
+      <c r="K33" s="50" t="str">
+        <f aca="false">IF(E33&gt;0,IF(V33&gt;0,0,E33-J33)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L33" s="50"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="68"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50" t="str">
+      <c r="N33" s="50"/>
+      <c r="O33" s="67"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="47"/>
+      <c r="R33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="50" t="str">
+      <c r="S33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="50"/>
+      <c r="T33" s="47"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="53" t="str">
+      <c r="W33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="53" t="str">
+      <c r="X33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="50" t="str">
+      <c r="Y33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="50" t="str">
+      <c r="Z33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3417,7 +3464,7 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="53" t="str">
+      <c r="G34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
         <v> </v>
       </c>
@@ -3425,48 +3472,48 @@
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="53" t="str">
+      <c r="I34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="53" t="str">
+      <c r="J34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="53" t="str">
-        <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
-        <v> </v>
-      </c>
-      <c r="L34" s="53"/>
+      <c r="K34" s="50" t="str">
+        <f aca="false">IF(E34&gt;0,IF(V34&gt;0,0,E34-J34)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L34" s="50"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="68"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="50" t="str">
+      <c r="N34" s="50"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="50" t="str">
+      <c r="S34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="50"/>
+      <c r="T34" s="47"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="53" t="str">
+      <c r="W34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="53" t="str">
+      <c r="X34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="50" t="str">
+      <c r="Y34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="50" t="str">
+      <c r="Z34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3475,38 +3522,38 @@
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="42"/>
       <c r="B35" s="59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="59"/>
       <c r="E35" s="60" t="n">
         <f aca="false">SUM(E30:E34)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F35" s="60" t="n">
         <f aca="false">SUM(F30:F34)</f>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="G35" s="61" t="n">
         <f aca="false">SUM(G30:G34)</f>
-        <v>0</v>
+        <v>2730</v>
       </c>
       <c r="H35" s="58"/>
       <c r="I35" s="61" t="n">
         <f aca="false">SUM(I30:I34)</f>
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J35" s="61" t="n">
         <f aca="false">SUM(J30:J34)</f>
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="K35" s="61" t="n">
         <f aca="false">SUM(K30:K34)</f>
-        <v>0</v>
-      </c>
-      <c r="L35" s="53"/>
+        <v>1740</v>
+      </c>
+      <c r="L35" s="50"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="53"/>
+      <c r="N35" s="50"/>
       <c r="O35" s="61" t="n">
         <f aca="false">SUM(O30:O34)</f>
         <v>0</v>
@@ -3524,8 +3571,8 @@
         <f aca="false">SUM(S30:S34)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="50"/>
-      <c r="U35" s="52"/>
+      <c r="T35" s="47"/>
+      <c r="U35" s="49"/>
       <c r="V35" s="60" t="n">
         <f aca="false">SUM(V30:V34)</f>
         <v>0</v>
@@ -3553,126 +3600,138 @@
       <c r="B36" s="63"/>
       <c r="C36" s="64"/>
       <c r="D36" s="65"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
       <c r="H36" s="58"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="50"/>
       <c r="P36" s="62"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="53"/>
-      <c r="W36" s="53"/>
-      <c r="X36" s="53"/>
-      <c r="Y36" s="53"/>
-      <c r="Z36" s="53"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="50"/>
+      <c r="S36" s="50"/>
+      <c r="T36" s="47"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="50"/>
+      <c r="W36" s="50"/>
+      <c r="X36" s="50"/>
+      <c r="Y36" s="50"/>
+      <c r="Z36" s="50"/>
       <c r="AA36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="42"/>
-      <c r="B37" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="70"/>
-      <c r="D37" s="71" t="n">
+      <c r="B37" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="67" t="n">
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="66" t="n">
         <f aca="false">[1]Admin!$G$17</f>
         <v>0.25</v>
       </c>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="72"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
       <c r="P37" s="62"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="73"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="53"/>
-      <c r="W37" s="53"/>
-      <c r="X37" s="53"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="53"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="50"/>
+      <c r="S37" s="50"/>
+      <c r="T37" s="72"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="50"/>
+      <c r="W37" s="50"/>
+      <c r="X37" s="50"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
       <c r="AA37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="42"/>
       <c r="B38" s="54"/>
-      <c r="C38" s="55"/>
+      <c r="C38" s="55" t="s">
+        <v>33</v>
+      </c>
       <c r="D38" s="56"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="53" t="str">
+      <c r="E38" s="57" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F38" s="57" t="n">
+        <v>9828</v>
+      </c>
+      <c r="G38" s="50" t="n">
         <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
-        <v> </v>
+        <v>20172</v>
       </c>
       <c r="H38" s="58" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I38" s="53" t="str">
+      <c r="I38" s="50" t="n">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J38" s="53" t="str">
+        <v>7500</v>
+      </c>
+      <c r="J38" s="50" t="n">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
-        <v> </v>
-      </c>
-      <c r="K38" s="53" t="str">
-        <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
-        <v> </v>
-      </c>
-      <c r="L38" s="53"/>
-      <c r="M38" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="53"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50" t="str">
+        <v>17328</v>
+      </c>
+      <c r="K38" s="50" t="n">
+        <f aca="false">IF(E38&gt;0,IF(V38&gt;0,0,E38-J38)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="50"/>
+      <c r="M38" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="50"/>
+      <c r="O38" s="67" t="n">
+        <v>24000</v>
+      </c>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47" t="n">
         <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
-        <v> </v>
-      </c>
-      <c r="S38" s="50" t="str">
+        <v>3000</v>
+      </c>
+      <c r="S38" s="47" t="n">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
-        <v> </v>
-      </c>
-      <c r="T38" s="50"/>
-      <c r="U38" s="54"/>
-      <c r="V38" s="57"/>
-      <c r="W38" s="53" t="str">
+        <v>21000</v>
+      </c>
+      <c r="T38" s="47"/>
+      <c r="U38" s="54" t="n">
+        <v>45940</v>
+      </c>
+      <c r="V38" s="57" t="n">
+        <v>12500</v>
+      </c>
+      <c r="W38" s="50" t="n">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
-        <v> </v>
-      </c>
-      <c r="X38" s="53" t="str">
+        <v>30000</v>
+      </c>
+      <c r="X38" s="50" t="n">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
-        <v> </v>
-      </c>
-      <c r="Y38" s="50" t="str">
+        <v>17328</v>
+      </c>
+      <c r="Y38" s="47" t="n">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
-        <v> </v>
-      </c>
-      <c r="Z38" s="50" t="str">
+        <v>8500</v>
+      </c>
+      <c r="Z38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
         <v> </v>
       </c>
@@ -3685,7 +3744,7 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="53" t="str">
+      <c r="G39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
         <v> </v>
       </c>
@@ -3693,50 +3752,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I39" s="53" t="str">
+      <c r="I39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="53" t="str">
+      <c r="J39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="53" t="str">
-        <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
-        <v> </v>
-      </c>
-      <c r="L39" s="53"/>
-      <c r="M39" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="53"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50" t="str">
+      <c r="K39" s="50" t="str">
+        <f aca="false">IF(E39&gt;0,IF(V39&gt;0,0,E39-J39)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L39" s="50"/>
+      <c r="M39" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="50"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="47"/>
+      <c r="R39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="50" t="str">
+      <c r="S39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="50"/>
+      <c r="T39" s="47"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="53" t="str">
+      <c r="W39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="53" t="str">
+      <c r="X39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="50" t="str">
+      <c r="Y39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,(S39-V39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="50" t="str">
+      <c r="Z39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,(V39-S39)*(1-M39)," ")," ")</f>
         <v> </v>
       </c>
@@ -3749,7 +3808,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="53" t="str">
+      <c r="G40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
         <v> </v>
       </c>
@@ -3757,50 +3816,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I40" s="53" t="str">
+      <c r="I40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="53" t="str">
+      <c r="J40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="53" t="str">
-        <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
-        <v> </v>
-      </c>
-      <c r="L40" s="53"/>
-      <c r="M40" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="53"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50" t="str">
+      <c r="K40" s="50" t="str">
+        <f aca="false">IF(E40&gt;0,IF(V40&gt;0,0,E40-J40)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L40" s="50"/>
+      <c r="M40" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="50"/>
+      <c r="O40" s="67"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="47"/>
+      <c r="R40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="50" t="str">
+      <c r="S40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="50"/>
+      <c r="T40" s="47"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="53" t="str">
+      <c r="W40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="53" t="str">
+      <c r="X40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="50" t="str">
+      <c r="Y40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,(S40-V40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="50" t="str">
+      <c r="Z40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,(V40-S40)*(1-M40)," ")," ")</f>
         <v> </v>
       </c>
@@ -3813,7 +3872,7 @@
       <c r="D41" s="56"/>
       <c r="E41" s="57"/>
       <c r="F41" s="57"/>
-      <c r="G41" s="53" t="str">
+      <c r="G41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,E41-F41," ")</f>
         <v> </v>
       </c>
@@ -3821,50 +3880,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I41" s="53" t="str">
+      <c r="I41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,MIN(E41*H41,G41)," ")</f>
         <v> </v>
       </c>
-      <c r="J41" s="53" t="str">
+      <c r="J41" s="50" t="str">
         <f aca="false">IF(E41&gt;0,F41+I41," ")</f>
         <v> </v>
       </c>
-      <c r="K41" s="53" t="str">
-        <f aca="false">IF(E41&gt;0,E41-J41," ")</f>
-        <v> </v>
-      </c>
-      <c r="L41" s="53"/>
-      <c r="M41" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="53"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50" t="str">
+      <c r="K41" s="50" t="str">
+        <f aca="false">IF(E41&gt;0,IF(V41&gt;0,0,E41-J41)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L41" s="50"/>
+      <c r="M41" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="50"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="47"/>
+      <c r="R41" s="47" t="str">
         <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
         <v> </v>
       </c>
-      <c r="S41" s="50" t="str">
+      <c r="S41" s="47" t="str">
         <f aca="false">IF(O41&gt;0,O41-R41," ")</f>
         <v> </v>
       </c>
-      <c r="T41" s="50"/>
+      <c r="T41" s="47"/>
       <c r="U41" s="54"/>
       <c r="V41" s="57"/>
-      <c r="W41" s="53" t="str">
+      <c r="W41" s="50" t="str">
         <f aca="false">IF(V41&gt;0,E41," ")</f>
         <v> </v>
       </c>
-      <c r="X41" s="53" t="str">
+      <c r="X41" s="50" t="str">
         <f aca="false">IF(V41&gt;0,J41," ")</f>
         <v> </v>
       </c>
-      <c r="Y41" s="50" t="str">
+      <c r="Y41" s="47" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&lt;S41,(S41-V41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z41" s="50" t="str">
+      <c r="Z41" s="47" t="str">
         <f aca="false">IF((U41+V41)&gt;0,IF(V41&gt;S41,(V41-S41)*(1-M41)," ")," ")</f>
         <v> </v>
       </c>
@@ -3877,7 +3936,7 @@
       <c r="D42" s="56"/>
       <c r="E42" s="57"/>
       <c r="F42" s="57"/>
-      <c r="G42" s="53" t="str">
+      <c r="G42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,E42-F42," ")</f>
         <v> </v>
       </c>
@@ -3885,50 +3944,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I42" s="53" t="str">
+      <c r="I42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,MIN(E42*H42,G42)," ")</f>
         <v> </v>
       </c>
-      <c r="J42" s="53" t="str">
+      <c r="J42" s="50" t="str">
         <f aca="false">IF(E42&gt;0,F42+I42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="53" t="str">
-        <f aca="false">IF(E42&gt;0,E42-J42," ")</f>
-        <v> </v>
-      </c>
-      <c r="L42" s="53"/>
-      <c r="M42" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="53"/>
-      <c r="O42" s="68"/>
-      <c r="P42" s="51"/>
-      <c r="Q42" s="50"/>
-      <c r="R42" s="50" t="str">
+      <c r="K42" s="50" t="str">
+        <f aca="false">IF(E42&gt;0,IF(V42&gt;0,0,E42-J42)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L42" s="50"/>
+      <c r="M42" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="50"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="48"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47" t="str">
         <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
         <v> </v>
       </c>
-      <c r="S42" s="50" t="str">
+      <c r="S42" s="47" t="str">
         <f aca="false">IF(O42&gt;0,O42-R42," ")</f>
         <v> </v>
       </c>
-      <c r="T42" s="50"/>
+      <c r="T42" s="47"/>
       <c r="U42" s="54"/>
       <c r="V42" s="57"/>
-      <c r="W42" s="53" t="str">
+      <c r="W42" s="50" t="str">
         <f aca="false">IF(V42&gt;0,E42," ")</f>
         <v> </v>
       </c>
-      <c r="X42" s="53" t="str">
+      <c r="X42" s="50" t="str">
         <f aca="false">IF(V42&gt;0,J42," ")</f>
         <v> </v>
       </c>
-      <c r="Y42" s="50" t="str">
+      <c r="Y42" s="47" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&lt;S42,(S42-V42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z42" s="50" t="str">
+      <c r="Z42" s="47" t="str">
         <f aca="false">IF((U42+V42)&gt;0,IF(V42&gt;S42,(V42-S42)*(1-M42)," ")," ")</f>
         <v> </v>
       </c>
@@ -3936,36 +3995,36 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="71" t="n">
+      <c r="B43" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="69"/>
+      <c r="D43" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
         <v>12000</v>
       </c>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
       <c r="H43" s="58"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
       <c r="M43" s="58"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="53"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="47"/>
+      <c r="P43" s="48"/>
+      <c r="Q43" s="47"/>
+      <c r="R43" s="47"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="47"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="50"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="47"/>
+      <c r="Z43" s="47"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3975,7 +4034,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="53" t="str">
+      <c r="G44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
         <v> </v>
       </c>
@@ -3983,50 +4042,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="53" t="str">
+      <c r="I44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="53" t="str">
+      <c r="J44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="53" t="str">
-        <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
-        <v> </v>
-      </c>
-      <c r="L44" s="53"/>
-      <c r="M44" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="53"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50" t="str">
+      <c r="K44" s="50" t="str">
+        <f aca="false">IF(E44&gt;0,IF(V44&gt;0,0,E44-J44)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L44" s="50"/>
+      <c r="M44" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="50"/>
+      <c r="O44" s="67"/>
+      <c r="P44" s="48"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="50" t="str">
+      <c r="S44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="50"/>
+      <c r="T44" s="47"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="53" t="str">
+      <c r="W44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="53" t="str">
+      <c r="X44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="50" t="str">
+      <c r="Y44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="50" t="str">
+      <c r="Z44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -4039,7 +4098,7 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="53" t="str">
+      <c r="G45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
         <v> </v>
       </c>
@@ -4047,50 +4106,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="53" t="str">
+      <c r="I45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="53" t="str">
+      <c r="J45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="53" t="str">
-        <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
-        <v> </v>
-      </c>
-      <c r="L45" s="53"/>
-      <c r="M45" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="53"/>
-      <c r="O45" s="68"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50" t="str">
+      <c r="K45" s="50" t="str">
+        <f aca="false">IF(E45&gt;0,IF(V45&gt;0,0,E45-J45)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L45" s="50"/>
+      <c r="M45" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="50"/>
+      <c r="O45" s="67"/>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="50" t="str">
+      <c r="S45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="50"/>
+      <c r="T45" s="47"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="53" t="str">
+      <c r="W45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="53" t="str">
+      <c r="X45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="50" t="str">
+      <c r="Y45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="50" t="str">
+      <c r="Z45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -4103,7 +4162,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="53" t="str">
+      <c r="G46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -4111,50 +4170,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="53" t="str">
+      <c r="I46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="53" t="str">
+      <c r="J46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="53" t="str">
-        <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
-        <v> </v>
-      </c>
-      <c r="L46" s="53"/>
-      <c r="M46" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="53"/>
-      <c r="O46" s="68"/>
-      <c r="P46" s="51"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50" t="str">
+      <c r="K46" s="50" t="str">
+        <f aca="false">IF(E46&gt;0,IF(V46&gt;0,0,E46-J46)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L46" s="50"/>
+      <c r="M46" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="50"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="47"/>
+      <c r="R46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="50" t="str">
+      <c r="S46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="50"/>
+      <c r="T46" s="47"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="53" t="str">
+      <c r="W46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="53" t="str">
+      <c r="X46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="50" t="str">
+      <c r="Y46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="50" t="str">
+      <c r="Z46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -4167,7 +4226,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="53" t="str">
+      <c r="G47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -4175,50 +4234,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="53" t="str">
+      <c r="I47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="53" t="str">
+      <c r="J47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="53" t="str">
-        <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
-        <v> </v>
-      </c>
-      <c r="L47" s="53"/>
-      <c r="M47" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="53"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="51"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50" t="str">
+      <c r="K47" s="50" t="str">
+        <f aca="false">IF(E47&gt;0,IF(V47&gt;0,0,E47-J47)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L47" s="50"/>
+      <c r="M47" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="50"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="48"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="50" t="str">
+      <c r="S47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="50"/>
+      <c r="T47" s="47"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="53" t="str">
+      <c r="W47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="53" t="str">
+      <c r="X47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="50" t="str">
+      <c r="Y47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="50" t="str">
+      <c r="Z47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4231,7 +4290,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="53" t="str">
+      <c r="G48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4239,50 +4298,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="53" t="str">
+      <c r="I48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="53" t="str">
+      <c r="J48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="53" t="str">
-        <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
-        <v> </v>
-      </c>
-      <c r="L48" s="53"/>
-      <c r="M48" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="53"/>
-      <c r="O48" s="68"/>
-      <c r="P48" s="51"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50" t="str">
+      <c r="K48" s="50" t="str">
+        <f aca="false">IF(E48&gt;0,IF(V48&gt;0,0,E48-J48)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L48" s="50"/>
+      <c r="M48" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="50"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="48"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="50" t="str">
+      <c r="S48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="50"/>
+      <c r="T48" s="47"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="53" t="str">
+      <c r="W48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="53" t="str">
+      <c r="X48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="50" t="str">
+      <c r="Y48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="50" t="str">
+      <c r="Z48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4290,33 +4349,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="66"/>
+      <c r="B49" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="51"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="50"/>
+      <c r="L49" s="50"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="51"/>
-      <c r="Q49" s="50"/>
-      <c r="R49" s="50"/>
-      <c r="S49" s="50"/>
-      <c r="T49" s="50"/>
-      <c r="U49" s="52"/>
-      <c r="V49" s="53"/>
-      <c r="W49" s="53"/>
-      <c r="X49" s="53"/>
-      <c r="Y49" s="50"/>
-      <c r="Z49" s="50"/>
+      <c r="N49" s="50"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="47"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="47"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="50"/>
+      <c r="W49" s="50"/>
+      <c r="X49" s="50"/>
+      <c r="Y49" s="47"/>
+      <c r="Z49" s="47"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4326,7 +4385,7 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="53" t="str">
+      <c r="G50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
         <v> </v>
       </c>
@@ -4334,50 +4393,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="53" t="str">
+      <c r="I50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="53" t="str">
+      <c r="J50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="53" t="str">
-        <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
-        <v> </v>
-      </c>
-      <c r="L50" s="53"/>
-      <c r="M50" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="53"/>
-      <c r="O50" s="68"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="50"/>
-      <c r="R50" s="50" t="str">
+      <c r="K50" s="50" t="str">
+        <f aca="false">IF(E50&gt;0,IF(V50&gt;0,0,E50-J50)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L50" s="50"/>
+      <c r="M50" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="50"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,O50*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="50" t="str">
+      <c r="S50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="50"/>
+      <c r="T50" s="47"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="53" t="str">
+      <c r="W50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="53" t="str">
+      <c r="X50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="50" t="str">
+      <c r="Y50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="50" t="str">
+      <c r="Z50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4390,7 +4449,7 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="53" t="str">
+      <c r="G51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
         <v> </v>
       </c>
@@ -4398,50 +4457,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="53" t="str">
+      <c r="I51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="53" t="str">
+      <c r="J51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="53" t="str">
-        <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
-        <v> </v>
-      </c>
-      <c r="L51" s="53"/>
-      <c r="M51" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="53"/>
-      <c r="O51" s="68"/>
-      <c r="P51" s="51"/>
-      <c r="Q51" s="50"/>
-      <c r="R51" s="50" t="str">
+      <c r="K51" s="50" t="str">
+        <f aca="false">IF(E51&gt;0,IF(V51&gt;0,0,E51-J51)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L51" s="50"/>
+      <c r="M51" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="50"/>
+      <c r="O51" s="67"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,O51*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="50" t="str">
+      <c r="S51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="50"/>
+      <c r="T51" s="47"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="53" t="str">
+      <c r="W51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="53" t="str">
+      <c r="X51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="50" t="str">
+      <c r="Y51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="50" t="str">
+      <c r="Z51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4454,7 +4513,7 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="53" t="str">
+      <c r="G52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
         <v> </v>
       </c>
@@ -4462,50 +4521,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="53" t="str">
+      <c r="I52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="53" t="str">
+      <c r="J52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="53" t="str">
-        <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
-        <v> </v>
-      </c>
-      <c r="L52" s="53"/>
-      <c r="M52" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="53"/>
-      <c r="O52" s="68"/>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="50"/>
-      <c r="R52" s="50" t="str">
+      <c r="K52" s="50" t="str">
+        <f aca="false">IF(E52&gt;0,IF(V52&gt;0,0,E52-J52)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L52" s="50"/>
+      <c r="M52" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="50"/>
+      <c r="O52" s="67"/>
+      <c r="P52" s="48"/>
+      <c r="Q52" s="47"/>
+      <c r="R52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,O52*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="50" t="str">
+      <c r="S52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="50"/>
+      <c r="T52" s="47"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="53" t="str">
+      <c r="W52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="53" t="str">
+      <c r="X52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="50" t="str">
+      <c r="Y52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="50" t="str">
+      <c r="Z52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4518,7 +4577,7 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="53" t="str">
+      <c r="G53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
         <v> </v>
       </c>
@@ -4526,50 +4585,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="53" t="str">
+      <c r="I53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="53" t="str">
+      <c r="J53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="53" t="str">
-        <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
-        <v> </v>
-      </c>
-      <c r="L53" s="53"/>
-      <c r="M53" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="53"/>
-      <c r="O53" s="68"/>
-      <c r="P53" s="51"/>
-      <c r="Q53" s="50"/>
-      <c r="R53" s="50" t="str">
+      <c r="K53" s="50" t="str">
+        <f aca="false">IF(E53&gt;0,IF(V53&gt;0,0,E53-J53)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L53" s="50"/>
+      <c r="M53" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="50"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="47"/>
+      <c r="R53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,O53*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="50" t="str">
+      <c r="S53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="50"/>
+      <c r="T53" s="47"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="53" t="str">
+      <c r="W53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="53" t="str">
+      <c r="X53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="50" t="str">
+      <c r="Y53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="50" t="str">
+      <c r="Z53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4582,7 +4641,7 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="53" t="str">
+      <c r="G54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
         <v> </v>
       </c>
@@ -4590,50 +4649,50 @@
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="53" t="str">
+      <c r="I54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="53" t="str">
+      <c r="J54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="53" t="str">
-        <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
-        <v> </v>
-      </c>
-      <c r="L54" s="53"/>
-      <c r="M54" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="53"/>
-      <c r="O54" s="68"/>
-      <c r="P54" s="51"/>
-      <c r="Q54" s="50"/>
-      <c r="R54" s="50" t="str">
+      <c r="K54" s="50" t="str">
+        <f aca="false">IF(E54&gt;0,IF(V54&gt;0,0,E54-J54)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L54" s="50"/>
+      <c r="M54" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="50"/>
+      <c r="O54" s="67"/>
+      <c r="P54" s="48"/>
+      <c r="Q54" s="47"/>
+      <c r="R54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,O54*R$4," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="50" t="str">
+      <c r="S54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="50"/>
+      <c r="T54" s="47"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="53" t="str">
+      <c r="W54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="53" t="str">
+      <c r="X54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="50" t="str">
+      <c r="Y54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="50" t="str">
+      <c r="Z54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4642,41 +4701,41 @@
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="42"/>
       <c r="B55" s="59" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C55" s="59"/>
       <c r="D55" s="59"/>
       <c r="E55" s="61" t="n">
         <f aca="false">SUM(E38:E54)</f>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F55" s="61" t="n">
         <f aca="false">SUM(F38:F54)</f>
-        <v>0</v>
+        <v>9828</v>
       </c>
       <c r="G55" s="61" t="n">
         <f aca="false">SUM(G38:G54)</f>
-        <v>0</v>
+        <v>20172</v>
       </c>
       <c r="H55" s="58"/>
       <c r="I55" s="61" t="n">
         <f aca="false">SUM(I38:I54)</f>
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="J55" s="61" t="n">
         <f aca="false">SUM(J38:J54)</f>
-        <v>0</v>
+        <v>17328</v>
       </c>
       <c r="K55" s="61" t="n">
         <f aca="false">SUM(K38:K54)</f>
         <v>0</v>
       </c>
-      <c r="L55" s="53"/>
-      <c r="M55" s="72"/>
-      <c r="N55" s="53"/>
+      <c r="L55" s="50"/>
+      <c r="M55" s="71"/>
+      <c r="N55" s="50"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O38:O54)</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="P55" s="62"/>
       <c r="Q55" s="61" t="n">
@@ -4685,29 +4744,29 @@
       </c>
       <c r="R55" s="61" t="n">
         <f aca="false">SUM(R38:R54)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="S55" s="61" t="n">
         <f aca="false">SUM(S38:S54)</f>
-        <v>0</v>
-      </c>
-      <c r="T55" s="53"/>
-      <c r="U55" s="52"/>
+        <v>21000</v>
+      </c>
+      <c r="T55" s="50"/>
+      <c r="U55" s="49"/>
       <c r="V55" s="61" t="n">
         <f aca="false">SUM(V38:V54)</f>
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="W55" s="61" t="n">
         <f aca="false">SUM(W38:W54)</f>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="X55" s="61" t="n">
         <f aca="false">SUM(X38:X54)</f>
-        <v>0</v>
+        <v>17328</v>
       </c>
       <c r="Y55" s="61" t="n">
         <f aca="false">SUM(Y38:Y54)</f>
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="Z55" s="61" t="n">
         <f aca="false">SUM(Z38:Z54)</f>
@@ -4717,31 +4776,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="74"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="73"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="50"/>
+      <c r="L56" s="50"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="50"/>
-      <c r="P56" s="51"/>
-      <c r="Q56" s="50"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="50"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="52"/>
-      <c r="V56" s="53"/>
-      <c r="W56" s="50"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="50"/>
-      <c r="Z56" s="50"/>
+      <c r="N56" s="50"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="48"/>
+      <c r="Q56" s="47"/>
+      <c r="R56" s="47"/>
+      <c r="S56" s="47"/>
+      <c r="T56" s="47"/>
+      <c r="U56" s="49"/>
+      <c r="V56" s="50"/>
+      <c r="W56" s="47"/>
+      <c r="X56" s="47"/>
+      <c r="Y56" s="47"/>
+      <c r="Z56" s="47"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4751,74 +4810,74 @@
         <v>EXISTING FIXED ASSETS at </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="44" t="str">
+      <c r="D57" s="44" t="n">
         <f aca="false">D6</f>
-        <v>Laptop (0.5 years old)</v>
-      </c>
-      <c r="E57" s="75" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E57" s="74" t="n">
         <f aca="false">E11+E19+E27+E35+E55</f>
-        <v>0</v>
-      </c>
-      <c r="F57" s="75" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F57" s="74" t="n">
         <f aca="false">F11+F19+F27+F35+F55</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="75" t="n">
+        <v>10098</v>
+      </c>
+      <c r="G57" s="74" t="n">
         <f aca="false">G11+G19+G27+G35+G55</f>
-        <v>0</v>
+        <v>22902</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="75" t="n">
+      <c r="I57" s="74" t="n">
         <f aca="false">I11+I19+I27+I35+I55</f>
-        <v>0</v>
-      </c>
-      <c r="J57" s="75" t="n">
+        <v>8490</v>
+      </c>
+      <c r="J57" s="74" t="n">
         <f aca="false">J11+J19+J27+J35+J55</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="75" t="n">
+        <v>18588</v>
+      </c>
+      <c r="K57" s="74" t="n">
         <f aca="false">K11+K19+K27+K35+K55</f>
-        <v>0</v>
-      </c>
-      <c r="L57" s="53"/>
+        <v>1740</v>
+      </c>
+      <c r="L57" s="50"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="75" t="n">
+      <c r="N57" s="50"/>
+      <c r="O57" s="74" t="n">
         <f aca="false">O11+O19+O27+O35+O55</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="75" t="n">
+      <c r="Q57" s="74" t="n">
         <f aca="false">Q11+Q19+Q27+Q35+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="75" t="n">
+      <c r="R57" s="74" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
-        <v>0</v>
-      </c>
-      <c r="S57" s="75" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S57" s="74" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
-        <v>0</v>
-      </c>
-      <c r="T57" s="50"/>
-      <c r="U57" s="52"/>
-      <c r="V57" s="75" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T57" s="47"/>
+      <c r="U57" s="49"/>
+      <c r="V57" s="74" t="n">
         <f aca="false">V11+V19+V27+V35+V55</f>
-        <v>0</v>
-      </c>
-      <c r="W57" s="75" t="n">
+        <v>12500</v>
+      </c>
+      <c r="W57" s="74" t="n">
         <f aca="false">W11+W19+W27+W35+W55</f>
-        <v>0</v>
-      </c>
-      <c r="X57" s="75" t="n">
+        <v>30000</v>
+      </c>
+      <c r="X57" s="74" t="n">
         <f aca="false">X11+X19+X27+X35+X55</f>
-        <v>0</v>
-      </c>
-      <c r="Y57" s="75" t="n">
+        <v>17328</v>
+      </c>
+      <c r="Y57" s="74" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
-        <v>0</v>
-      </c>
-      <c r="Z57" s="75" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Z57" s="74" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
         <v>0</v>
       </c>
@@ -4826,78 +4885,78 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="76"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="78"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="53"/>
-      <c r="K58" s="53"/>
-      <c r="L58" s="53"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="50"/>
+      <c r="L58" s="50"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="53"/>
-      <c r="O58" s="50"/>
-      <c r="P58" s="51"/>
-      <c r="Q58" s="50"/>
-      <c r="R58" s="50"/>
-      <c r="S58" s="50"/>
-      <c r="T58" s="50"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="53"/>
-      <c r="W58" s="53"/>
-      <c r="X58" s="53"/>
-      <c r="Y58" s="50"/>
-      <c r="Z58" s="50"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="47"/>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="47"/>
+      <c r="R58" s="47"/>
+      <c r="S58" s="47"/>
+      <c r="T58" s="47"/>
+      <c r="U58" s="49"/>
+      <c r="V58" s="50"/>
+      <c r="W58" s="50"/>
+      <c r="X58" s="50"/>
+      <c r="Y58" s="47"/>
+      <c r="Z58" s="47"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
       <c r="B59" s="43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="n">
         <f aca="false">[1]Admin!$B$4</f>
-        <v>45753</v>
-      </c>
-      <c r="E59" s="50"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
+        <v>46118</v>
+      </c>
+      <c r="E59" s="47"/>
+      <c r="F59" s="78"/>
+      <c r="G59" s="78"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="47"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="51"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="53"/>
-      <c r="W59" s="53"/>
-      <c r="X59" s="53"/>
-      <c r="Y59" s="50"/>
-      <c r="Z59" s="50"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="47"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="47"/>
+      <c r="R59" s="47"/>
+      <c r="S59" s="47"/>
+      <c r="T59" s="47"/>
+      <c r="U59" s="49"/>
+      <c r="V59" s="50"/>
+      <c r="W59" s="50"/>
+      <c r="X59" s="50"/>
+      <c r="Y59" s="47"/>
+      <c r="Z59" s="47"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="C60" s="66"/>
-      <c r="D60" s="47"/>
+      <c r="B60" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="51"/>
+      <c r="D60" s="52"/>
       <c r="E60" s="45"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
-      <c r="H60" s="80" t="n">
+      <c r="F60" s="78"/>
+      <c r="G60" s="78"/>
+      <c r="H60" s="79" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
@@ -4907,165 +4966,165 @@
       <c r="L60" s="45"/>
       <c r="M60" s="58"/>
       <c r="N60" s="45"/>
-      <c r="O60" s="50"/>
-      <c r="P60" s="51"/>
-      <c r="Q60" s="50"/>
-      <c r="R60" s="50"/>
-      <c r="S60" s="50"/>
-      <c r="T60" s="50"/>
-      <c r="U60" s="52"/>
-      <c r="V60" s="53"/>
-      <c r="W60" s="53"/>
-      <c r="X60" s="53"/>
-      <c r="Y60" s="50"/>
-      <c r="Z60" s="50"/>
+      <c r="O60" s="47"/>
+      <c r="P60" s="48"/>
+      <c r="Q60" s="47"/>
+      <c r="R60" s="47"/>
+      <c r="S60" s="47"/>
+      <c r="T60" s="47"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="50"/>
+      <c r="W60" s="50"/>
+      <c r="X60" s="50"/>
+      <c r="Y60" s="47"/>
+      <c r="Z60" s="47"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="81"/>
+      <c r="D61" s="80"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
+      <c r="F61" s="50"/>
+      <c r="G61" s="50"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="53" t="str">
+      <c r="I61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="53" t="str">
+      <c r="J61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="53" t="str">
-        <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
-        <v> </v>
-      </c>
-      <c r="L61" s="53"/>
+      <c r="K61" s="50" t="str">
+        <f aca="false">IF(E61&gt;0,IF(V61&gt;0,0,E61-J61)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L61" s="50"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="53"/>
-      <c r="O61" s="50"/>
-      <c r="P61" s="51"/>
-      <c r="Q61" s="50"/>
-      <c r="R61" s="50"/>
-      <c r="S61" s="50"/>
-      <c r="T61" s="50"/>
+      <c r="N61" s="50"/>
+      <c r="O61" s="47"/>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="47"/>
+      <c r="R61" s="47"/>
+      <c r="S61" s="47"/>
+      <c r="T61" s="47"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="53" t="str">
+      <c r="W61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="53" t="str">
+      <c r="X61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="50"/>
-      <c r="Z61" s="50"/>
+      <c r="Y61" s="47"/>
+      <c r="Z61" s="47"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="81"/>
+      <c r="D62" s="80"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="53"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="50"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="53" t="str">
+      <c r="I62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="53" t="str">
+      <c r="J62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="53" t="str">
-        <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
-        <v> </v>
-      </c>
-      <c r="L62" s="53"/>
+      <c r="K62" s="50" t="str">
+        <f aca="false">IF(E62&gt;0,IF(V62&gt;0,0,E62-J62)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L62" s="50"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="53"/>
-      <c r="O62" s="50"/>
-      <c r="P62" s="51"/>
-      <c r="Q62" s="50"/>
-      <c r="R62" s="50"/>
-      <c r="S62" s="50"/>
-      <c r="T62" s="50"/>
+      <c r="N62" s="50"/>
+      <c r="O62" s="47"/>
+      <c r="P62" s="48"/>
+      <c r="Q62" s="47"/>
+      <c r="R62" s="47"/>
+      <c r="S62" s="47"/>
+      <c r="T62" s="47"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="53" t="str">
+      <c r="W62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="53" t="str">
+      <c r="X62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="50"/>
-      <c r="Z62" s="50"/>
+      <c r="Y62" s="47"/>
+      <c r="Z62" s="47"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="81"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="53" t="str">
+      <c r="I63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="53" t="str">
+      <c r="J63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="53" t="str">
-        <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
-        <v> </v>
-      </c>
-      <c r="L63" s="53"/>
+      <c r="K63" s="50" t="str">
+        <f aca="false">IF(E63&gt;0,IF(V63&gt;0,0,E63-J63)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L63" s="50"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="53"/>
-      <c r="O63" s="50"/>
-      <c r="P63" s="51"/>
-      <c r="Q63" s="50"/>
-      <c r="R63" s="50"/>
-      <c r="S63" s="50"/>
-      <c r="T63" s="50"/>
+      <c r="N63" s="50"/>
+      <c r="O63" s="47"/>
+      <c r="P63" s="48"/>
+      <c r="Q63" s="47"/>
+      <c r="R63" s="47"/>
+      <c r="S63" s="47"/>
+      <c r="T63" s="47"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="53" t="str">
+      <c r="W63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="53" t="str">
+      <c r="X63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="50"/>
-      <c r="Z63" s="50"/>
+      <c r="Y63" s="47"/>
+      <c r="Z63" s="47"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -5094,14 +5153,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="53"/>
+      <c r="L64" s="50"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="53"/>
+      <c r="N64" s="50"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="82"/>
+      <c r="P64" s="81"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -5114,8 +5173,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="50"/>
-      <c r="U64" s="52"/>
+      <c r="T64" s="47"/>
+      <c r="U64" s="49"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -5143,121 +5202,127 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="53"/>
-      <c r="F65" s="53"/>
-      <c r="G65" s="53"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="53"/>
-      <c r="J65" s="53"/>
-      <c r="K65" s="53"/>
-      <c r="L65" s="53"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="50"/>
+      <c r="L65" s="50"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="53"/>
-      <c r="O65" s="53"/>
+      <c r="N65" s="50"/>
+      <c r="O65" s="50"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="53"/>
-      <c r="R65" s="53"/>
-      <c r="S65" s="53"/>
-      <c r="T65" s="50"/>
-      <c r="U65" s="52"/>
-      <c r="V65" s="53"/>
-      <c r="W65" s="53"/>
-      <c r="X65" s="53"/>
-      <c r="Y65" s="53"/>
-      <c r="Z65" s="53"/>
+      <c r="Q65" s="50"/>
+      <c r="R65" s="50"/>
+      <c r="S65" s="50"/>
+      <c r="T65" s="47"/>
+      <c r="U65" s="49"/>
+      <c r="V65" s="50"/>
+      <c r="W65" s="50"/>
+      <c r="X65" s="50"/>
+      <c r="Y65" s="50"/>
+      <c r="Z65" s="50"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="66" t="s">
+      <c r="B66" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="66"/>
+      <c r="C66" s="51"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="53"/>
-      <c r="F66" s="53"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="83" t="n">
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="82" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="53"/>
-      <c r="J66" s="53"/>
-      <c r="K66" s="53"/>
-      <c r="L66" s="53"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="50"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="53"/>
-      <c r="O66" s="50"/>
-      <c r="P66" s="51"/>
-      <c r="Q66" s="50"/>
-      <c r="R66" s="50"/>
-      <c r="S66" s="50"/>
-      <c r="T66" s="50"/>
-      <c r="U66" s="52"/>
-      <c r="V66" s="53"/>
-      <c r="W66" s="53"/>
-      <c r="X66" s="53"/>
-      <c r="Y66" s="50"/>
-      <c r="Z66" s="50"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="47"/>
+      <c r="S66" s="47"/>
+      <c r="T66" s="47"/>
+      <c r="U66" s="49"/>
+      <c r="V66" s="50"/>
+      <c r="W66" s="50"/>
+      <c r="X66" s="50"/>
+      <c r="Y66" s="47"/>
+      <c r="Z66" s="47"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42"/>
-      <c r="B67" s="54"/>
-      <c r="C67" s="55"/>
+      <c r="B67" s="54" t="n">
+        <v>45792</v>
+      </c>
+      <c r="C67" s="55" t="s">
+        <v>39</v>
+      </c>
       <c r="D67" s="56"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
+      <c r="E67" s="57" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="53" t="str">
+      <c r="I67" s="50" t="n">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J67" s="53" t="str">
+        <v>150</v>
+      </c>
+      <c r="J67" s="50" t="n">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
-        <v> </v>
-      </c>
-      <c r="K67" s="53" t="str">
-        <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
-        <v> </v>
-      </c>
-      <c r="L67" s="53"/>
+        <v>150</v>
+      </c>
+      <c r="K67" s="50" t="n">
+        <f aca="false">IF(E67&gt;0,IF(V67&gt;0,0,E67-J67)," ")</f>
+        <v>1350</v>
+      </c>
+      <c r="L67" s="50"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="53"/>
-      <c r="O67" s="50"/>
+      <c r="N67" s="50"/>
+      <c r="O67" s="47"/>
       <c r="P67" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q67" s="50" t="str">
+      <c r="Q67" s="47" t="n">
         <f aca="false">IF(E67&gt;0,E67*P67," ")</f>
-        <v> </v>
-      </c>
-      <c r="R67" s="50"/>
-      <c r="S67" s="50" t="str">
+        <v>1500</v>
+      </c>
+      <c r="R67" s="47"/>
+      <c r="S67" s="47" t="n">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
-        <v> </v>
-      </c>
-      <c r="T67" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="T67" s="47"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="53" t="str">
+      <c r="W67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="53" t="str">
+      <c r="X67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="50" t="str">
+      <c r="Y67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="50" t="str">
+      <c r="Z67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5265,61 +5330,67 @@
     </row>
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
-      <c r="B68" s="54"/>
-      <c r="C68" s="55"/>
+      <c r="B68" s="54" t="n">
+        <v>45853</v>
+      </c>
+      <c r="C68" s="55" t="s">
+        <v>40</v>
+      </c>
       <c r="D68" s="56"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="53"/>
-      <c r="G68" s="53"/>
+      <c r="E68" s="57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F68" s="50"/>
+      <c r="G68" s="50"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="53" t="str">
+      <c r="I68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J68" s="53" t="str">
+        <v>100</v>
+      </c>
+      <c r="J68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
-        <v> </v>
-      </c>
-      <c r="K68" s="53" t="str">
-        <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
-        <v> </v>
-      </c>
-      <c r="L68" s="53"/>
+        <v>100</v>
+      </c>
+      <c r="K68" s="50" t="n">
+        <f aca="false">IF(E68&gt;0,IF(V68&gt;0,0,E68-J68)," ")</f>
+        <v>900</v>
+      </c>
+      <c r="L68" s="50"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="53"/>
-      <c r="O68" s="50"/>
+      <c r="N68" s="50"/>
+      <c r="O68" s="47"/>
       <c r="P68" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q68" s="50" t="str">
+      <c r="Q68" s="47" t="n">
         <f aca="false">IF(E68&gt;0,E68*P68," ")</f>
-        <v> </v>
-      </c>
-      <c r="R68" s="50"/>
-      <c r="S68" s="50" t="str">
+        <v>1000</v>
+      </c>
+      <c r="R68" s="47"/>
+      <c r="S68" s="47" t="n">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
-        <v> </v>
-      </c>
-      <c r="T68" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="T68" s="47"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="53" t="str">
+      <c r="W68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="53" t="str">
+      <c r="X68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="50" t="str">
+      <c r="Y68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="50" t="str">
+      <c r="Z68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5327,61 +5398,67 @@
     </row>
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
-      <c r="B69" s="54"/>
-      <c r="C69" s="55"/>
+      <c r="B69" s="54" t="n">
+        <v>45955</v>
+      </c>
+      <c r="C69" s="55" t="s">
+        <v>41</v>
+      </c>
       <c r="D69" s="56"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
+      <c r="E69" s="57" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="53" t="str">
+      <c r="I69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J69" s="53" t="str">
+        <v>3000</v>
+      </c>
+      <c r="J69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
-        <v> </v>
-      </c>
-      <c r="K69" s="53" t="str">
-        <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
-        <v> </v>
-      </c>
-      <c r="L69" s="53"/>
+        <v>3000</v>
+      </c>
+      <c r="K69" s="50" t="n">
+        <f aca="false">IF(E69&gt;0,IF(V69&gt;0,0,E69-J69)," ")</f>
+        <v>27000</v>
+      </c>
+      <c r="L69" s="50"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="53"/>
-      <c r="O69" s="50"/>
+      <c r="N69" s="50"/>
+      <c r="O69" s="47"/>
       <c r="P69" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q69" s="50" t="str">
+      <c r="Q69" s="47" t="n">
         <f aca="false">IF(E69&gt;0,E69*P69," ")</f>
-        <v> </v>
-      </c>
-      <c r="R69" s="50"/>
-      <c r="S69" s="50" t="str">
+        <v>30000</v>
+      </c>
+      <c r="R69" s="47"/>
+      <c r="S69" s="47" t="n">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
-        <v> </v>
-      </c>
-      <c r="T69" s="50"/>
+        <v>0</v>
+      </c>
+      <c r="T69" s="47"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="53" t="str">
+      <c r="W69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="53" t="str">
+      <c r="X69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="50" t="str">
+      <c r="Y69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="50" t="str">
+      <c r="Z69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5393,57 +5470,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="53"/>
-      <c r="G70" s="53"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="53" t="str">
+      <c r="I70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="53" t="str">
+      <c r="J70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="53" t="str">
-        <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
-        <v> </v>
-      </c>
-      <c r="L70" s="53"/>
+      <c r="K70" s="50" t="str">
+        <f aca="false">IF(E70&gt;0,IF(V70&gt;0,0,E70-J70)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L70" s="50"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="53"/>
-      <c r="O70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="47"/>
       <c r="P70" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="50" t="str">
+      <c r="Q70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="50"/>
-      <c r="S70" s="50" t="str">
+      <c r="R70" s="47"/>
+      <c r="S70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="50"/>
+      <c r="T70" s="47"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="53" t="str">
+      <c r="W70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="53" t="str">
+      <c r="X70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="50" t="str">
+      <c r="Y70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="50" t="str">
+      <c r="Z70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5455,57 +5532,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="53"/>
-      <c r="G71" s="53"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="53" t="str">
+      <c r="I71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="53" t="str">
+      <c r="J71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="53" t="str">
-        <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
-        <v> </v>
-      </c>
-      <c r="L71" s="53"/>
+      <c r="K71" s="50" t="str">
+        <f aca="false">IF(E71&gt;0,IF(V71&gt;0,0,E71-J71)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L71" s="50"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="50"/>
+      <c r="N71" s="50"/>
+      <c r="O71" s="47"/>
       <c r="P71" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q71" s="50" t="str">
+      <c r="Q71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="50"/>
-      <c r="S71" s="50" t="str">
+      <c r="R71" s="47"/>
+      <c r="S71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="50"/>
+      <c r="T71" s="47"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="53" t="str">
+      <c r="W71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="53" t="str">
+      <c r="X71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="50" t="str">
+      <c r="Y71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="50" t="str">
+      <c r="Z71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5514,13 +5591,13 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="42"/>
       <c r="B72" s="59" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
       <c r="E72" s="60" t="n">
         <f aca="false">SUM(E67:E71)</f>
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="F72" s="61" t="n">
         <f aca="false">SUM(F67:F71)</f>
@@ -5533,19 +5610,19 @@
       <c r="H72" s="58"/>
       <c r="I72" s="61" t="n">
         <f aca="false">SUM(I67:I71)</f>
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="J72" s="61" t="n">
         <f aca="false">SUM(J67:J71)</f>
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="K72" s="61" t="n">
         <f aca="false">SUM(K67:K71)</f>
-        <v>0</v>
-      </c>
-      <c r="L72" s="53"/>
+        <v>29250</v>
+      </c>
+      <c r="L72" s="50"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="53"/>
+      <c r="N72" s="50"/>
       <c r="O72" s="61" t="n">
         <f aca="false">SUM(O67:O71)</f>
         <v>0</v>
@@ -5553,7 +5630,7 @@
       <c r="P72" s="62"/>
       <c r="Q72" s="61" t="n">
         <f aca="false">SUM(Q67:Q71)</f>
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="R72" s="61" t="n">
         <f aca="false">SUM(R67:R71)</f>
@@ -5563,8 +5640,8 @@
         <f aca="false">SUM(S67:S71)</f>
         <v>0</v>
       </c>
-      <c r="T72" s="50"/>
-      <c r="U72" s="52"/>
+      <c r="T72" s="47"/>
+      <c r="U72" s="49"/>
       <c r="V72" s="60" t="n">
         <f aca="false">SUM(V67:V71)</f>
         <v>0</v>
@@ -5592,121 +5669,121 @@
       <c r="B73" s="63"/>
       <c r="C73" s="64"/>
       <c r="D73" s="65"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
       <c r="H73" s="58"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-      <c r="L73" s="53"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="50"/>
+      <c r="K73" s="50"/>
+      <c r="L73" s="50"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="53"/>
-      <c r="O73" s="53"/>
+      <c r="N73" s="50"/>
+      <c r="O73" s="50"/>
       <c r="P73" s="62"/>
-      <c r="Q73" s="53"/>
-      <c r="R73" s="53"/>
-      <c r="S73" s="53"/>
-      <c r="T73" s="50"/>
-      <c r="U73" s="52"/>
-      <c r="V73" s="53"/>
-      <c r="W73" s="53"/>
-      <c r="X73" s="53"/>
-      <c r="Y73" s="53"/>
-      <c r="Z73" s="53"/>
+      <c r="Q73" s="50"/>
+      <c r="R73" s="50"/>
+      <c r="S73" s="50"/>
+      <c r="T73" s="47"/>
+      <c r="U73" s="49"/>
+      <c r="V73" s="50"/>
+      <c r="W73" s="50"/>
+      <c r="X73" s="50"/>
+      <c r="Y73" s="50"/>
+      <c r="Z73" s="50"/>
       <c r="AA73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="42"/>
-      <c r="B74" s="66" t="s">
+      <c r="B74" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="66"/>
+      <c r="C74" s="51"/>
       <c r="D74" s="62"/>
-      <c r="E74" s="53"/>
-      <c r="F74" s="53"/>
-      <c r="G74" s="53"/>
-      <c r="H74" s="83" t="n">
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="82" t="n">
         <f aca="false">H$21</f>
         <v>0.2</v>
       </c>
-      <c r="I74" s="53"/>
-      <c r="J74" s="53"/>
-      <c r="K74" s="53"/>
-      <c r="L74" s="53"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="K74" s="50"/>
+      <c r="L74" s="50"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="53"/>
-      <c r="O74" s="50"/>
-      <c r="P74" s="51"/>
-      <c r="Q74" s="50"/>
-      <c r="R74" s="50"/>
-      <c r="S74" s="50"/>
-      <c r="T74" s="50"/>
-      <c r="U74" s="52"/>
-      <c r="V74" s="53"/>
-      <c r="W74" s="53"/>
-      <c r="X74" s="53"/>
-      <c r="Y74" s="50"/>
-      <c r="Z74" s="50"/>
+      <c r="N74" s="50"/>
+      <c r="O74" s="47"/>
+      <c r="P74" s="48"/>
+      <c r="Q74" s="47"/>
+      <c r="R74" s="47"/>
+      <c r="S74" s="47"/>
+      <c r="T74" s="47"/>
+      <c r="U74" s="49"/>
+      <c r="V74" s="50"/>
+      <c r="W74" s="50"/>
+      <c r="X74" s="50"/>
+      <c r="Y74" s="47"/>
+      <c r="Z74" s="47"/>
       <c r="AA74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
-      <c r="D75" s="81"/>
+      <c r="D75" s="80"/>
       <c r="E75" s="57"/>
-      <c r="F75" s="53"/>
-      <c r="G75" s="53"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
       <c r="H75" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I75" s="53" t="str">
+      <c r="I75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,MIN(E75*H75,G75)," ")</f>
         <v> </v>
       </c>
-      <c r="J75" s="53" t="str">
+      <c r="J75" s="50" t="str">
         <f aca="false">IF(E75&gt;0,F75+I75," ")</f>
         <v> </v>
       </c>
-      <c r="K75" s="53" t="str">
-        <f aca="false">IF(E75&gt;0,E75-J75," ")</f>
-        <v> </v>
-      </c>
-      <c r="L75" s="53"/>
+      <c r="K75" s="50" t="str">
+        <f aca="false">IF(E75&gt;0,IF(V75&gt;0,0,E75-J75)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L75" s="50"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="53"/>
-      <c r="O75" s="50"/>
+      <c r="N75" s="50"/>
+      <c r="O75" s="47"/>
       <c r="P75" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q75" s="50" t="str">
+      <c r="Q75" s="47" t="str">
         <f aca="false">IF(E75&gt;0,E75*P75," ")</f>
         <v> </v>
       </c>
-      <c r="R75" s="50"/>
-      <c r="S75" s="50" t="str">
+      <c r="R75" s="47"/>
+      <c r="S75" s="47" t="str">
         <f aca="false">IF(E75&gt;0,E75-Q75," ")</f>
         <v> </v>
       </c>
-      <c r="T75" s="50"/>
+      <c r="T75" s="47"/>
       <c r="U75" s="54"/>
       <c r="V75" s="57"/>
-      <c r="W75" s="53" t="str">
+      <c r="W75" s="50" t="str">
         <f aca="false">IF(V75&gt;0,E75," ")</f>
         <v> </v>
       </c>
-      <c r="X75" s="53" t="str">
+      <c r="X75" s="50" t="str">
         <f aca="false">IF(V75&gt;0,J75," ")</f>
         <v> </v>
       </c>
-      <c r="Y75" s="50" t="str">
+      <c r="Y75" s="47" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&lt;S75,S75-V75," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z75" s="50" t="str">
+      <c r="Z75" s="47" t="str">
         <f aca="false">IF((U75+V75)&gt;0,IF(V75&gt;S75,V75-S75," ")," ")</f>
         <v> </v>
       </c>
@@ -5716,59 +5793,59 @@
       <c r="A76" s="42"/>
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
-      <c r="D76" s="81"/>
+      <c r="D76" s="80"/>
       <c r="E76" s="57"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
       <c r="H76" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I76" s="53" t="str">
+      <c r="I76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,MIN(E76*H76,G76)," ")</f>
         <v> </v>
       </c>
-      <c r="J76" s="53" t="str">
+      <c r="J76" s="50" t="str">
         <f aca="false">IF(E76&gt;0,F76+I76," ")</f>
         <v> </v>
       </c>
-      <c r="K76" s="53" t="str">
-        <f aca="false">IF(E76&gt;0,E76-J76," ")</f>
-        <v> </v>
-      </c>
-      <c r="L76" s="53"/>
+      <c r="K76" s="50" t="str">
+        <f aca="false">IF(E76&gt;0,IF(V76&gt;0,0,E76-J76)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L76" s="50"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="53"/>
-      <c r="O76" s="50"/>
+      <c r="N76" s="50"/>
+      <c r="O76" s="47"/>
       <c r="P76" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q76" s="50" t="str">
+      <c r="Q76" s="47" t="str">
         <f aca="false">IF(E76&gt;0,E76*P76," ")</f>
         <v> </v>
       </c>
-      <c r="R76" s="50"/>
-      <c r="S76" s="50" t="str">
+      <c r="R76" s="47"/>
+      <c r="S76" s="47" t="str">
         <f aca="false">IF(E76&gt;0,E76-Q76," ")</f>
         <v> </v>
       </c>
-      <c r="T76" s="50"/>
+      <c r="T76" s="47"/>
       <c r="U76" s="54"/>
       <c r="V76" s="57"/>
-      <c r="W76" s="53" t="str">
+      <c r="W76" s="50" t="str">
         <f aca="false">IF(V76&gt;0,E76," ")</f>
         <v> </v>
       </c>
-      <c r="X76" s="53" t="str">
+      <c r="X76" s="50" t="str">
         <f aca="false">IF(V76&gt;0,J76," ")</f>
         <v> </v>
       </c>
-      <c r="Y76" s="50" t="str">
+      <c r="Y76" s="47" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&lt;S76,S76-V76," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z76" s="50" t="str">
+      <c r="Z76" s="47" t="str">
         <f aca="false">IF((U76+V76)&gt;0,IF(V76&gt;S76,V76-S76," ")," ")</f>
         <v> </v>
       </c>
@@ -5778,59 +5855,59 @@
       <c r="A77" s="42"/>
       <c r="B77" s="54"/>
       <c r="C77" s="55"/>
-      <c r="D77" s="81"/>
+      <c r="D77" s="80"/>
       <c r="E77" s="57"/>
-      <c r="F77" s="53"/>
-      <c r="G77" s="53"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
       <c r="H77" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="53" t="str">
+      <c r="I77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,MIN(E77*H77,G77)," ")</f>
         <v> </v>
       </c>
-      <c r="J77" s="53" t="str">
+      <c r="J77" s="50" t="str">
         <f aca="false">IF(E77&gt;0,F77+I77," ")</f>
         <v> </v>
       </c>
-      <c r="K77" s="53" t="str">
-        <f aca="false">IF(E77&gt;0,E77-J77," ")</f>
-        <v> </v>
-      </c>
-      <c r="L77" s="53"/>
+      <c r="K77" s="50" t="str">
+        <f aca="false">IF(E77&gt;0,IF(V77&gt;0,0,E77-J77)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L77" s="50"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="53"/>
-      <c r="O77" s="50"/>
+      <c r="N77" s="50"/>
+      <c r="O77" s="47"/>
       <c r="P77" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="50" t="str">
+      <c r="Q77" s="47" t="str">
         <f aca="false">IF(E77&gt;0,E77*P77," ")</f>
         <v> </v>
       </c>
-      <c r="R77" s="50"/>
-      <c r="S77" s="50" t="str">
+      <c r="R77" s="47"/>
+      <c r="S77" s="47" t="str">
         <f aca="false">IF(E77&gt;0,E77-Q77," ")</f>
         <v> </v>
       </c>
-      <c r="T77" s="50"/>
+      <c r="T77" s="47"/>
       <c r="U77" s="54"/>
       <c r="V77" s="57"/>
-      <c r="W77" s="53" t="str">
+      <c r="W77" s="50" t="str">
         <f aca="false">IF(V77&gt;0,E77," ")</f>
         <v> </v>
       </c>
-      <c r="X77" s="53" t="str">
+      <c r="X77" s="50" t="str">
         <f aca="false">IF(V77&gt;0,J77," ")</f>
         <v> </v>
       </c>
-      <c r="Y77" s="50" t="str">
+      <c r="Y77" s="47" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&lt;S77,S77-V77," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z77" s="50" t="str">
+      <c r="Z77" s="47" t="str">
         <f aca="false">IF((U77+V77)&gt;0,IF(V77&gt;S77,V77-S77," ")," ")</f>
         <v> </v>
       </c>
@@ -5840,59 +5917,59 @@
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="81"/>
+      <c r="D78" s="80"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="53" t="str">
+      <c r="I78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="53" t="str">
+      <c r="J78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="53" t="str">
-        <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
-        <v> </v>
-      </c>
-      <c r="L78" s="53"/>
+      <c r="K78" s="50" t="str">
+        <f aca="false">IF(E78&gt;0,IF(V78&gt;0,0,E78-J78)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L78" s="50"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="53"/>
-      <c r="O78" s="50"/>
+      <c r="N78" s="50"/>
+      <c r="O78" s="47"/>
       <c r="P78" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q78" s="50" t="str">
+      <c r="Q78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="50"/>
-      <c r="S78" s="50" t="str">
+      <c r="R78" s="47"/>
+      <c r="S78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="50"/>
+      <c r="T78" s="47"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="53" t="str">
+      <c r="W78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="53" t="str">
+      <c r="X78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="50" t="str">
+      <c r="Y78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="50" t="str">
+      <c r="Z78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5902,59 +5979,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="81"/>
+      <c r="D79" s="80"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$74</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="53" t="str">
+      <c r="I79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="53" t="str">
+      <c r="J79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="53" t="str">
-        <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
-        <v> </v>
-      </c>
-      <c r="L79" s="53"/>
+      <c r="K79" s="50" t="str">
+        <f aca="false">IF(E79&gt;0,IF(V79&gt;0,0,E79-J79)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L79" s="50"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="50"/>
+      <c r="N79" s="50"/>
+      <c r="O79" s="47"/>
       <c r="P79" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q79" s="50" t="str">
+      <c r="Q79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="50"/>
-      <c r="S79" s="50" t="str">
+      <c r="R79" s="47"/>
+      <c r="S79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="50"/>
+      <c r="T79" s="47"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="53" t="str">
+      <c r="W79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="53" t="str">
+      <c r="X79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="50" t="str">
+      <c r="Y79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="50" t="str">
+      <c r="Z79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -5963,7 +6040,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="42"/>
       <c r="B80" s="59" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C80" s="59"/>
       <c r="D80" s="59"/>
@@ -5992,9 +6069,9 @@
         <f aca="false">SUM(K75:K79)</f>
         <v>0</v>
       </c>
-      <c r="L80" s="53"/>
+      <c r="L80" s="50"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="53"/>
+      <c r="N80" s="50"/>
       <c r="O80" s="61" t="n">
         <f aca="false">SUM(O75:O79)</f>
         <v>0</v>
@@ -6012,8 +6089,8 @@
         <f aca="false">SUM(S75:S79)</f>
         <v>0</v>
       </c>
-      <c r="T80" s="50"/>
-      <c r="U80" s="52"/>
+      <c r="T80" s="47"/>
+      <c r="U80" s="49"/>
       <c r="V80" s="60" t="n">
         <f aca="false">SUM(V75:V79)</f>
         <v>0</v>
@@ -6041,121 +6118,121 @@
       <c r="B81" s="63"/>
       <c r="C81" s="64"/>
       <c r="D81" s="65"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
       <c r="H81" s="58"/>
-      <c r="I81" s="53"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="53"/>
-      <c r="L81" s="53"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="53"/>
-      <c r="O81" s="53"/>
+      <c r="N81" s="50"/>
+      <c r="O81" s="50"/>
       <c r="P81" s="62"/>
-      <c r="Q81" s="53"/>
-      <c r="R81" s="53"/>
-      <c r="S81" s="53"/>
-      <c r="T81" s="50"/>
-      <c r="U81" s="52"/>
-      <c r="V81" s="53"/>
-      <c r="W81" s="53"/>
-      <c r="X81" s="53"/>
-      <c r="Y81" s="53"/>
-      <c r="Z81" s="53"/>
+      <c r="Q81" s="50"/>
+      <c r="R81" s="50"/>
+      <c r="S81" s="50"/>
+      <c r="T81" s="47"/>
+      <c r="U81" s="49"/>
+      <c r="V81" s="50"/>
+      <c r="W81" s="50"/>
+      <c r="X81" s="50"/>
+      <c r="Y81" s="50"/>
+      <c r="Z81" s="50"/>
       <c r="AA81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="42"/>
-      <c r="B82" s="66" t="s">
+      <c r="B82" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="66"/>
-      <c r="D82" s="69"/>
-      <c r="E82" s="53"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="83" t="n">
+      <c r="C82" s="51"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="82" t="n">
         <f aca="false">H$29</f>
         <v>0.33</v>
       </c>
-      <c r="I82" s="53"/>
-      <c r="J82" s="53"/>
-      <c r="K82" s="53"/>
-      <c r="L82" s="53"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="53"/>
-      <c r="O82" s="50"/>
-      <c r="P82" s="51"/>
-      <c r="Q82" s="50"/>
-      <c r="R82" s="50"/>
-      <c r="S82" s="50"/>
-      <c r="T82" s="50"/>
-      <c r="U82" s="52"/>
-      <c r="V82" s="53"/>
-      <c r="W82" s="53"/>
-      <c r="X82" s="53"/>
-      <c r="Y82" s="50"/>
-      <c r="Z82" s="50"/>
+      <c r="N82" s="50"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="47"/>
+      <c r="R82" s="47"/>
+      <c r="S82" s="47"/>
+      <c r="T82" s="47"/>
+      <c r="U82" s="49"/>
+      <c r="V82" s="50"/>
+      <c r="W82" s="50"/>
+      <c r="X82" s="50"/>
+      <c r="Y82" s="47"/>
+      <c r="Z82" s="47"/>
       <c r="AA82" s="25"/>
     </row>
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="54"/>
       <c r="C83" s="55"/>
-      <c r="D83" s="81"/>
+      <c r="D83" s="80"/>
       <c r="E83" s="57"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
       <c r="H83" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I83" s="53" t="str">
+      <c r="I83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,MIN(E83*H83,G83)," ")</f>
         <v> </v>
       </c>
-      <c r="J83" s="53" t="str">
+      <c r="J83" s="50" t="str">
         <f aca="false">IF(E83&gt;0,F83+I83," ")</f>
         <v> </v>
       </c>
-      <c r="K83" s="53" t="str">
-        <f aca="false">IF(E83&gt;0,E83-J83," ")</f>
-        <v> </v>
-      </c>
-      <c r="L83" s="53"/>
+      <c r="K83" s="50" t="str">
+        <f aca="false">IF(E83&gt;0,IF(V83&gt;0,0,E83-J83)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L83" s="50"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="53"/>
-      <c r="O83" s="50"/>
+      <c r="N83" s="50"/>
+      <c r="O83" s="47"/>
       <c r="P83" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q83" s="50" t="str">
+      <c r="Q83" s="47" t="str">
         <f aca="false">IF(E83&gt;0,E83*P83," ")</f>
         <v> </v>
       </c>
-      <c r="R83" s="50"/>
-      <c r="S83" s="50" t="str">
+      <c r="R83" s="47"/>
+      <c r="S83" s="47" t="str">
         <f aca="false">IF(E83&gt;0,E83-Q83," ")</f>
         <v> </v>
       </c>
-      <c r="T83" s="50"/>
+      <c r="T83" s="47"/>
       <c r="U83" s="54"/>
       <c r="V83" s="57"/>
-      <c r="W83" s="53" t="str">
+      <c r="W83" s="50" t="str">
         <f aca="false">IF(V83&gt;0,E83," ")</f>
         <v> </v>
       </c>
-      <c r="X83" s="53" t="str">
+      <c r="X83" s="50" t="str">
         <f aca="false">IF(V83&gt;0,J83," ")</f>
         <v> </v>
       </c>
-      <c r="Y83" s="50" t="str">
+      <c r="Y83" s="47" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&lt;S83,S83-V83," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z83" s="50" t="str">
+      <c r="Z83" s="47" t="str">
         <f aca="false">IF((U83+V83)&gt;0,IF(V83&gt;S83,V83-S83," ")," ")</f>
         <v> </v>
       </c>
@@ -6165,59 +6242,59 @@
       <c r="A84" s="42"/>
       <c r="B84" s="54"/>
       <c r="C84" s="55"/>
-      <c r="D84" s="81"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="57"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
       <c r="H84" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I84" s="53" t="str">
+      <c r="I84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,MIN(E84*H84,G84)," ")</f>
         <v> </v>
       </c>
-      <c r="J84" s="53" t="str">
+      <c r="J84" s="50" t="str">
         <f aca="false">IF(E84&gt;0,F84+I84," ")</f>
         <v> </v>
       </c>
-      <c r="K84" s="53" t="str">
-        <f aca="false">IF(E84&gt;0,E84-J84," ")</f>
-        <v> </v>
-      </c>
-      <c r="L84" s="53"/>
+      <c r="K84" s="50" t="str">
+        <f aca="false">IF(E84&gt;0,IF(V84&gt;0,0,E84-J84)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L84" s="50"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="53"/>
-      <c r="O84" s="50"/>
+      <c r="N84" s="50"/>
+      <c r="O84" s="47"/>
       <c r="P84" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q84" s="50" t="str">
+      <c r="Q84" s="47" t="str">
         <f aca="false">IF(E84&gt;0,E84*P84," ")</f>
         <v> </v>
       </c>
-      <c r="R84" s="50"/>
-      <c r="S84" s="50" t="str">
+      <c r="R84" s="47"/>
+      <c r="S84" s="47" t="str">
         <f aca="false">IF(E84&gt;0,E84-Q84," ")</f>
         <v> </v>
       </c>
-      <c r="T84" s="50"/>
+      <c r="T84" s="47"/>
       <c r="U84" s="54"/>
       <c r="V84" s="57"/>
-      <c r="W84" s="53" t="str">
+      <c r="W84" s="50" t="str">
         <f aca="false">IF(V84&gt;0,E84," ")</f>
         <v> </v>
       </c>
-      <c r="X84" s="53" t="str">
+      <c r="X84" s="50" t="str">
         <f aca="false">IF(V84&gt;0,J84," ")</f>
         <v> </v>
       </c>
-      <c r="Y84" s="50" t="str">
+      <c r="Y84" s="47" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&lt;S84,S84-V84," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z84" s="50" t="str">
+      <c r="Z84" s="47" t="str">
         <f aca="false">IF((U84+V84)&gt;0,IF(V84&gt;S84,V84-S84," ")," ")</f>
         <v> </v>
       </c>
@@ -6227,59 +6304,59 @@
       <c r="A85" s="42"/>
       <c r="B85" s="54"/>
       <c r="C85" s="55"/>
-      <c r="D85" s="81"/>
+      <c r="D85" s="80"/>
       <c r="E85" s="57"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
       <c r="H85" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="53" t="str">
+      <c r="I85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,MIN(E85*H85,G85)," ")</f>
         <v> </v>
       </c>
-      <c r="J85" s="53" t="str">
+      <c r="J85" s="50" t="str">
         <f aca="false">IF(E85&gt;0,F85+I85," ")</f>
         <v> </v>
       </c>
-      <c r="K85" s="53" t="str">
-        <f aca="false">IF(E85&gt;0,E85-J85," ")</f>
-        <v> </v>
-      </c>
-      <c r="L85" s="53"/>
+      <c r="K85" s="50" t="str">
+        <f aca="false">IF(E85&gt;0,IF(V85&gt;0,0,E85-J85)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L85" s="50"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="53"/>
-      <c r="O85" s="50"/>
+      <c r="N85" s="50"/>
+      <c r="O85" s="47"/>
       <c r="P85" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q85" s="50" t="str">
+      <c r="Q85" s="47" t="str">
         <f aca="false">IF(E85&gt;0,E85*P85," ")</f>
         <v> </v>
       </c>
-      <c r="R85" s="50"/>
-      <c r="S85" s="50" t="str">
+      <c r="R85" s="47"/>
+      <c r="S85" s="47" t="str">
         <f aca="false">IF(E85&gt;0,E85-Q85," ")</f>
         <v> </v>
       </c>
-      <c r="T85" s="50"/>
+      <c r="T85" s="47"/>
       <c r="U85" s="54"/>
       <c r="V85" s="57"/>
-      <c r="W85" s="53" t="str">
+      <c r="W85" s="50" t="str">
         <f aca="false">IF(V85&gt;0,E85," ")</f>
         <v> </v>
       </c>
-      <c r="X85" s="53" t="str">
+      <c r="X85" s="50" t="str">
         <f aca="false">IF(V85&gt;0,J85," ")</f>
         <v> </v>
       </c>
-      <c r="Y85" s="50" t="str">
+      <c r="Y85" s="47" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&lt;S85,S85-V85," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z85" s="50" t="str">
+      <c r="Z85" s="47" t="str">
         <f aca="false">IF((U85+V85)&gt;0,IF(V85&gt;S85,V85-S85," ")," ")</f>
         <v> </v>
       </c>
@@ -6289,59 +6366,59 @@
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="81"/>
+      <c r="D86" s="80"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="53" t="str">
+      <c r="I86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="53" t="str">
+      <c r="J86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="53" t="str">
-        <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
-        <v> </v>
-      </c>
-      <c r="L86" s="53"/>
+      <c r="K86" s="50" t="str">
+        <f aca="false">IF(E86&gt;0,IF(V86&gt;0,0,E86-J86)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L86" s="50"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="53"/>
-      <c r="O86" s="50"/>
+      <c r="N86" s="50"/>
+      <c r="O86" s="47"/>
       <c r="P86" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q86" s="50" t="str">
+      <c r="Q86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="50"/>
-      <c r="S86" s="50" t="str">
+      <c r="R86" s="47"/>
+      <c r="S86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="50"/>
+      <c r="T86" s="47"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="53" t="str">
+      <c r="W86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="53" t="str">
+      <c r="X86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="50" t="str">
+      <c r="Y86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="50" t="str">
+      <c r="Z86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6351,59 +6428,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="81"/>
+      <c r="D87" s="80"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$82</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="53" t="str">
+      <c r="I87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="53" t="str">
+      <c r="J87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="53" t="str">
-        <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
-        <v> </v>
-      </c>
-      <c r="L87" s="53"/>
+      <c r="K87" s="50" t="str">
+        <f aca="false">IF(E87&gt;0,IF(V87&gt;0,0,E87-J87)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L87" s="50"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="53"/>
-      <c r="O87" s="50"/>
+      <c r="N87" s="50"/>
+      <c r="O87" s="47"/>
       <c r="P87" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q87" s="50" t="str">
+      <c r="Q87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="50"/>
-      <c r="S87" s="50" t="str">
+      <c r="R87" s="47"/>
+      <c r="S87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="50"/>
+      <c r="T87" s="47"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="53" t="str">
+      <c r="W87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="53" t="str">
+      <c r="X87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="50" t="str">
+      <c r="Y87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="50" t="str">
+      <c r="Z87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6412,7 +6489,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="42"/>
       <c r="B88" s="59" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -6441,9 +6518,9 @@
         <f aca="false">SUM(K83:K87)</f>
         <v>0</v>
       </c>
-      <c r="L88" s="53"/>
+      <c r="L88" s="50"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="53"/>
+      <c r="N88" s="50"/>
       <c r="O88" s="61" t="n">
         <f aca="false">SUM(O83:O87)</f>
         <v>0</v>
@@ -6461,8 +6538,8 @@
         <f aca="false">SUM(S83:S87)</f>
         <v>0</v>
       </c>
-      <c r="T88" s="50"/>
-      <c r="U88" s="52"/>
+      <c r="T88" s="47"/>
+      <c r="U88" s="49"/>
       <c r="V88" s="60" t="n">
         <f aca="false">SUM(V83:V87)</f>
         <v>0</v>
@@ -6490,124 +6567,124 @@
       <c r="B89" s="63"/>
       <c r="C89" s="64"/>
       <c r="D89" s="65"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
       <c r="H89" s="58"/>
-      <c r="I89" s="53"/>
-      <c r="J89" s="53"/>
-      <c r="K89" s="53"/>
-      <c r="L89" s="53"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
+      <c r="L89" s="50"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="53"/>
-      <c r="O89" s="53"/>
+      <c r="N89" s="50"/>
+      <c r="O89" s="50"/>
       <c r="P89" s="62"/>
-      <c r="Q89" s="53"/>
-      <c r="R89" s="53"/>
-      <c r="S89" s="53"/>
-      <c r="T89" s="50"/>
-      <c r="U89" s="52"/>
-      <c r="V89" s="53"/>
-      <c r="W89" s="53"/>
-      <c r="X89" s="53"/>
-      <c r="Y89" s="53"/>
-      <c r="Z89" s="53"/>
+      <c r="Q89" s="50"/>
+      <c r="R89" s="50"/>
+      <c r="S89" s="50"/>
+      <c r="T89" s="47"/>
+      <c r="U89" s="49"/>
+      <c r="V89" s="50"/>
+      <c r="W89" s="50"/>
+      <c r="X89" s="50"/>
+      <c r="Y89" s="50"/>
+      <c r="Z89" s="50"/>
       <c r="AA89" s="25"/>
     </row>
     <row r="90" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="42"/>
-      <c r="B90" s="70" t="str">
+      <c r="B90" s="69" t="str">
         <f aca="false">B37</f>
         <v>Motor Vehicles - costing over £</v>
       </c>
-      <c r="C90" s="70"/>
-      <c r="D90" s="71" t="n">
+      <c r="C90" s="69"/>
+      <c r="D90" s="70" t="n">
         <f aca="false">D37</f>
         <v>12000</v>
       </c>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="83" t="n">
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="82" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="53"/>
+      <c r="I90" s="50"/>
+      <c r="J90" s="50"/>
+      <c r="K90" s="50"/>
+      <c r="L90" s="50"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="53"/>
-      <c r="O90" s="50"/>
+      <c r="N90" s="50"/>
+      <c r="O90" s="47"/>
       <c r="P90" s="62"/>
-      <c r="Q90" s="50"/>
-      <c r="R90" s="50"/>
-      <c r="S90" s="50"/>
-      <c r="T90" s="50"/>
-      <c r="U90" s="52"/>
-      <c r="V90" s="53"/>
-      <c r="W90" s="53"/>
-      <c r="X90" s="53"/>
-      <c r="Y90" s="50"/>
-      <c r="Z90" s="50"/>
+      <c r="Q90" s="47"/>
+      <c r="R90" s="47"/>
+      <c r="S90" s="47"/>
+      <c r="T90" s="47"/>
+      <c r="U90" s="49"/>
+      <c r="V90" s="50"/>
+      <c r="W90" s="50"/>
+      <c r="X90" s="50"/>
+      <c r="Y90" s="47"/>
+      <c r="Z90" s="47"/>
       <c r="AA90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="81"/>
+      <c r="D91" s="80"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I91" s="53" t="str">
+      <c r="I91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="53" t="str">
+      <c r="J91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="53" t="str">
-        <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
-        <v> </v>
-      </c>
-      <c r="L91" s="53"/>
-      <c r="M91" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="53"/>
-      <c r="O91" s="50"/>
-      <c r="P91" s="51"/>
-      <c r="Q91" s="50"/>
-      <c r="R91" s="50" t="str">
+      <c r="K91" s="50" t="str">
+        <f aca="false">IF(E91&gt;0,IF(V91&gt;0,0,E91-J91)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L91" s="50"/>
+      <c r="M91" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="50"/>
+      <c r="O91" s="47"/>
+      <c r="P91" s="48"/>
+      <c r="Q91" s="47"/>
+      <c r="R91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
         <v> </v>
       </c>
-      <c r="S91" s="50" t="str">
+      <c r="S91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,E91-R91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="50"/>
+      <c r="T91" s="47"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="53" t="str">
+      <c r="W91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="53" t="str">
+      <c r="X91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="50" t="str">
+      <c r="Y91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,(S91-V91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="50" t="str">
+      <c r="Z91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,(V91-S91)*(1-M91)," ")," ")</f>
         <v> </v>
       </c>
@@ -6617,58 +6694,58 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="81"/>
+      <c r="D92" s="80"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I92" s="53" t="str">
+      <c r="I92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="53" t="str">
+      <c r="J92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="53" t="str">
-        <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
-        <v> </v>
-      </c>
-      <c r="L92" s="53"/>
-      <c r="M92" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="53"/>
-      <c r="O92" s="50"/>
-      <c r="P92" s="51"/>
-      <c r="Q92" s="50"/>
-      <c r="R92" s="50" t="str">
+      <c r="K92" s="50" t="str">
+        <f aca="false">IF(E92&gt;0,IF(V92&gt;0,0,E92-J92)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L92" s="50"/>
+      <c r="M92" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="50"/>
+      <c r="O92" s="47"/>
+      <c r="P92" s="48"/>
+      <c r="Q92" s="47"/>
+      <c r="R92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
         <v> </v>
       </c>
-      <c r="S92" s="50" t="str">
+      <c r="S92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,E92-R92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="50"/>
+      <c r="T92" s="47"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="53" t="str">
+      <c r="W92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="53" t="str">
+      <c r="X92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="50" t="str">
+      <c r="Y92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,(S92-V92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="50" t="str">
+      <c r="Z92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,(V92-S92)*(1-M92)," ")," ")</f>
         <v> </v>
       </c>
@@ -6678,58 +6755,58 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="81"/>
+      <c r="D93" s="80"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="53"/>
-      <c r="G93" s="53"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I93" s="53" t="str">
+      <c r="I93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="53" t="str">
+      <c r="J93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="53" t="str">
-        <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
-        <v> </v>
-      </c>
-      <c r="L93" s="53"/>
-      <c r="M93" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="53"/>
-      <c r="O93" s="50"/>
-      <c r="P93" s="51"/>
-      <c r="Q93" s="50"/>
-      <c r="R93" s="50" t="str">
+      <c r="K93" s="50" t="str">
+        <f aca="false">IF(E93&gt;0,IF(V93&gt;0,0,E93-J93)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L93" s="50"/>
+      <c r="M93" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="50"/>
+      <c r="O93" s="47"/>
+      <c r="P93" s="48"/>
+      <c r="Q93" s="47"/>
+      <c r="R93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
         <v> </v>
       </c>
-      <c r="S93" s="50" t="str">
+      <c r="S93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,E93-R93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="50"/>
+      <c r="T93" s="47"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="53" t="str">
+      <c r="W93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="53" t="str">
+      <c r="X93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="50" t="str">
+      <c r="Y93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,(S93-V93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="50" t="str">
+      <c r="Z93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,(V93-S93)*(1-M93)," ")," ")</f>
         <v> </v>
       </c>
@@ -6739,58 +6816,58 @@
       <c r="A94" s="42"/>
       <c r="B94" s="54"/>
       <c r="C94" s="55"/>
-      <c r="D94" s="81"/>
+      <c r="D94" s="80"/>
       <c r="E94" s="57"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
       <c r="H94" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I94" s="53" t="str">
+      <c r="I94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*H94,G94)," ")</f>
         <v> </v>
       </c>
-      <c r="J94" s="53" t="str">
+      <c r="J94" s="50" t="str">
         <f aca="false">IF(E94&gt;0,F94+I94," ")</f>
         <v> </v>
       </c>
-      <c r="K94" s="53" t="str">
-        <f aca="false">IF(E94&gt;0,E94-J94," ")</f>
-        <v> </v>
-      </c>
-      <c r="L94" s="53"/>
-      <c r="M94" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="53"/>
-      <c r="O94" s="50"/>
-      <c r="P94" s="51"/>
-      <c r="Q94" s="50"/>
-      <c r="R94" s="50" t="str">
+      <c r="K94" s="50" t="str">
+        <f aca="false">IF(E94&gt;0,IF(V94&gt;0,0,E94-J94)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L94" s="50"/>
+      <c r="M94" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="50"/>
+      <c r="O94" s="47"/>
+      <c r="P94" s="48"/>
+      <c r="Q94" s="47"/>
+      <c r="R94" s="47" t="str">
         <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
         <v> </v>
       </c>
-      <c r="S94" s="50" t="str">
+      <c r="S94" s="47" t="str">
         <f aca="false">IF(E94&gt;0,E94-R94," ")</f>
         <v> </v>
       </c>
-      <c r="T94" s="50"/>
+      <c r="T94" s="47"/>
       <c r="U94" s="54"/>
       <c r="V94" s="57"/>
-      <c r="W94" s="53" t="str">
+      <c r="W94" s="50" t="str">
         <f aca="false">IF(V94&gt;0,E94," ")</f>
         <v> </v>
       </c>
-      <c r="X94" s="53" t="str">
+      <c r="X94" s="50" t="str">
         <f aca="false">IF(V94&gt;0,J94," ")</f>
         <v> </v>
       </c>
-      <c r="Y94" s="50" t="str">
+      <c r="Y94" s="47" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&lt;S94,(S94-V94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z94" s="50" t="str">
+      <c r="Z94" s="47" t="str">
         <f aca="false">IF((U94+V94)&gt;0,IF(V94&gt;S94,(V94-S94)*(1-M94)," ")," ")</f>
         <v> </v>
       </c>
@@ -6800,58 +6877,58 @@
       <c r="A95" s="42"/>
       <c r="B95" s="54"/>
       <c r="C95" s="55"/>
-      <c r="D95" s="81"/>
+      <c r="D95" s="80"/>
       <c r="E95" s="57"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50"/>
       <c r="H95" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I95" s="53" t="str">
+      <c r="I95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*H95,G95)," ")</f>
         <v> </v>
       </c>
-      <c r="J95" s="53" t="str">
+      <c r="J95" s="50" t="str">
         <f aca="false">IF(E95&gt;0,F95+I95," ")</f>
         <v> </v>
       </c>
-      <c r="K95" s="53" t="str">
-        <f aca="false">IF(E95&gt;0,E95-J95," ")</f>
-        <v> </v>
-      </c>
-      <c r="L95" s="53"/>
-      <c r="M95" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="53"/>
-      <c r="O95" s="50"/>
-      <c r="P95" s="51"/>
-      <c r="Q95" s="50"/>
-      <c r="R95" s="50" t="str">
+      <c r="K95" s="50" t="str">
+        <f aca="false">IF(E95&gt;0,IF(V95&gt;0,0,E95-J95)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L95" s="50"/>
+      <c r="M95" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="50"/>
+      <c r="O95" s="47"/>
+      <c r="P95" s="48"/>
+      <c r="Q95" s="47"/>
+      <c r="R95" s="47" t="str">
         <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
         <v> </v>
       </c>
-      <c r="S95" s="50" t="str">
+      <c r="S95" s="47" t="str">
         <f aca="false">IF(E95&gt;0,E95-R95," ")</f>
         <v> </v>
       </c>
-      <c r="T95" s="50"/>
+      <c r="T95" s="47"/>
       <c r="U95" s="54"/>
       <c r="V95" s="57"/>
-      <c r="W95" s="53" t="str">
+      <c r="W95" s="50" t="str">
         <f aca="false">IF(V95&gt;0,E95," ")</f>
         <v> </v>
       </c>
-      <c r="X95" s="53" t="str">
+      <c r="X95" s="50" t="str">
         <f aca="false">IF(V95&gt;0,J95," ")</f>
         <v> </v>
       </c>
-      <c r="Y95" s="50" t="str">
+      <c r="Y95" s="47" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&lt;S95,(S95-V95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z95" s="50" t="str">
+      <c r="Z95" s="47" t="str">
         <f aca="false">IF((U95+V95)&gt;0,IF(V95&gt;S95,(V95-S95)*(1-M95)," ")," ")</f>
         <v> </v>
       </c>
@@ -6859,95 +6936,95 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="84" t="str">
+      <c r="B96" s="83" t="str">
         <f aca="false">B43</f>
         <v>Motor Vehicles - costing under £</v>
       </c>
-      <c r="C96" s="84"/>
-      <c r="D96" s="71" t="n">
+      <c r="C96" s="83"/>
+      <c r="D96" s="70" t="n">
         <f aca="false">D43</f>
         <v>12000</v>
       </c>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="53"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
       <c r="H96" s="58"/>
-      <c r="I96" s="53"/>
-      <c r="J96" s="53"/>
-      <c r="K96" s="53"/>
-      <c r="L96" s="53"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+      <c r="L96" s="50"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="53"/>
-      <c r="O96" s="50"/>
-      <c r="P96" s="51"/>
-      <c r="Q96" s="50"/>
-      <c r="R96" s="50"/>
-      <c r="S96" s="50"/>
-      <c r="T96" s="50"/>
-      <c r="U96" s="52"/>
-      <c r="V96" s="53"/>
-      <c r="W96" s="53"/>
-      <c r="X96" s="53"/>
-      <c r="Y96" s="50"/>
-      <c r="Z96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="47"/>
+      <c r="P96" s="48"/>
+      <c r="Q96" s="47"/>
+      <c r="R96" s="47"/>
+      <c r="S96" s="47"/>
+      <c r="T96" s="47"/>
+      <c r="U96" s="49"/>
+      <c r="V96" s="50"/>
+      <c r="W96" s="50"/>
+      <c r="X96" s="50"/>
+      <c r="Y96" s="47"/>
+      <c r="Z96" s="47"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="81"/>
+      <c r="D97" s="80"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="53"/>
-      <c r="G97" s="53"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="53" t="str">
+      <c r="I97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="53" t="str">
+      <c r="J97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="53" t="str">
-        <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
-        <v> </v>
-      </c>
-      <c r="L97" s="53"/>
-      <c r="M97" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="53"/>
-      <c r="O97" s="50"/>
-      <c r="P97" s="51"/>
-      <c r="Q97" s="50"/>
-      <c r="R97" s="50" t="str">
+      <c r="K97" s="50" t="str">
+        <f aca="false">IF(E97&gt;0,IF(V97&gt;0,0,E97-J97)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L97" s="50"/>
+      <c r="M97" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="50"/>
+      <c r="O97" s="47"/>
+      <c r="P97" s="48"/>
+      <c r="Q97" s="47"/>
+      <c r="R97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="50" t="str">
+      <c r="S97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="50"/>
+      <c r="T97" s="47"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="53" t="str">
+      <c r="W97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="53" t="str">
+      <c r="X97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="50" t="str">
+      <c r="Y97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="50" t="str">
+      <c r="Z97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -6957,58 +7034,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="81"/>
+      <c r="D98" s="80"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="53"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="53" t="str">
+      <c r="I98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="53" t="str">
+      <c r="J98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="53" t="str">
-        <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
-        <v> </v>
-      </c>
-      <c r="L98" s="53"/>
-      <c r="M98" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="53"/>
-      <c r="O98" s="50"/>
-      <c r="P98" s="51"/>
-      <c r="Q98" s="50"/>
-      <c r="R98" s="50" t="str">
+      <c r="K98" s="50" t="str">
+        <f aca="false">IF(E98&gt;0,IF(V98&gt;0,0,E98-J98)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L98" s="50"/>
+      <c r="M98" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="50"/>
+      <c r="O98" s="47"/>
+      <c r="P98" s="48"/>
+      <c r="Q98" s="47"/>
+      <c r="R98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="50" t="str">
+      <c r="S98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="50"/>
+      <c r="T98" s="47"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="53" t="str">
+      <c r="W98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="53" t="str">
+      <c r="X98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="50" t="str">
+      <c r="Y98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="50" t="str">
+      <c r="Z98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -7018,58 +7095,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="81"/>
+      <c r="D99" s="80"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="53"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="53" t="str">
+      <c r="I99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="53" t="str">
+      <c r="J99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="53" t="str">
-        <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
-        <v> </v>
-      </c>
-      <c r="L99" s="53"/>
-      <c r="M99" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="53"/>
-      <c r="O99" s="50"/>
-      <c r="P99" s="51"/>
-      <c r="Q99" s="50"/>
-      <c r="R99" s="50" t="str">
+      <c r="K99" s="50" t="str">
+        <f aca="false">IF(E99&gt;0,IF(V99&gt;0,0,E99-J99)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L99" s="50"/>
+      <c r="M99" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="50"/>
+      <c r="O99" s="47"/>
+      <c r="P99" s="48"/>
+      <c r="Q99" s="47"/>
+      <c r="R99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="50" t="str">
+      <c r="S99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="50"/>
+      <c r="T99" s="47"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="53" t="str">
+      <c r="W99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="53" t="str">
+      <c r="X99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="50" t="str">
+      <c r="Y99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="50" t="str">
+      <c r="Z99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -7079,58 +7156,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="81"/>
+      <c r="D100" s="80"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="53"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="53" t="str">
+      <c r="I100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="53" t="str">
+      <c r="J100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="53" t="str">
-        <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
-        <v> </v>
-      </c>
-      <c r="L100" s="53"/>
-      <c r="M100" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="53"/>
-      <c r="O100" s="50"/>
-      <c r="P100" s="51"/>
-      <c r="Q100" s="50"/>
-      <c r="R100" s="50" t="str">
+      <c r="K100" s="50" t="str">
+        <f aca="false">IF(E100&gt;0,IF(V100&gt;0,0,E100-J100)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L100" s="50"/>
+      <c r="M100" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="50"/>
+      <c r="O100" s="47"/>
+      <c r="P100" s="48"/>
+      <c r="Q100" s="47"/>
+      <c r="R100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="50" t="str">
+      <c r="S100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="50"/>
+      <c r="T100" s="47"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="53" t="str">
+      <c r="W100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="53" t="str">
+      <c r="X100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="50" t="str">
+      <c r="Y100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="50" t="str">
+      <c r="Z100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -7140,58 +7217,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="81"/>
+      <c r="D101" s="80"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="53"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="53" t="str">
+      <c r="I101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="53" t="str">
+      <c r="J101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="53" t="str">
-        <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
-        <v> </v>
-      </c>
-      <c r="L101" s="53"/>
-      <c r="M101" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="53"/>
-      <c r="O101" s="50"/>
-      <c r="P101" s="51"/>
-      <c r="Q101" s="50"/>
-      <c r="R101" s="50" t="str">
+      <c r="K101" s="50" t="str">
+        <f aca="false">IF(E101&gt;0,IF(V101&gt;0,0,E101-J101)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L101" s="50"/>
+      <c r="M101" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="50"/>
+      <c r="O101" s="47"/>
+      <c r="P101" s="48"/>
+      <c r="Q101" s="47"/>
+      <c r="R101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="50" t="str">
+      <c r="S101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="50"/>
+      <c r="T101" s="47"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="53" t="str">
+      <c r="W101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="53" t="str">
+      <c r="X101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="50" t="str">
+      <c r="Y101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="50" t="str">
+      <c r="Z101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7199,94 +7276,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C102" s="66"/>
-      <c r="D102" s="69"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
+      <c r="B102" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" s="51"/>
+      <c r="D102" s="68"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
-      <c r="L102" s="53"/>
+      <c r="I102" s="50"/>
+      <c r="J102" s="50"/>
+      <c r="K102" s="50"/>
+      <c r="L102" s="50"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="53"/>
-      <c r="O102" s="50"/>
-      <c r="P102" s="51"/>
-      <c r="Q102" s="50"/>
-      <c r="R102" s="50"/>
-      <c r="S102" s="50"/>
-      <c r="T102" s="50"/>
-      <c r="U102" s="52"/>
-      <c r="V102" s="53"/>
-      <c r="W102" s="53"/>
-      <c r="X102" s="53"/>
-      <c r="Y102" s="50"/>
-      <c r="Z102" s="50"/>
+      <c r="N102" s="50"/>
+      <c r="O102" s="47"/>
+      <c r="P102" s="48"/>
+      <c r="Q102" s="47"/>
+      <c r="R102" s="47"/>
+      <c r="S102" s="47"/>
+      <c r="T102" s="47"/>
+      <c r="U102" s="49"/>
+      <c r="V102" s="50"/>
+      <c r="W102" s="50"/>
+      <c r="X102" s="50"/>
+      <c r="Y102" s="47"/>
+      <c r="Z102" s="47"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="81"/>
+      <c r="D103" s="80"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="53"/>
-      <c r="G103" s="53"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="53" t="str">
+      <c r="I103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="53" t="str">
+      <c r="J103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="53" t="str">
-        <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
-        <v> </v>
-      </c>
-      <c r="L103" s="53"/>
-      <c r="M103" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="53"/>
-      <c r="O103" s="50"/>
+      <c r="K103" s="50" t="str">
+        <f aca="false">IF(E103&gt;0,IF(V103&gt;0,0,E103-J103)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L103" s="50"/>
+      <c r="M103" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="50"/>
+      <c r="O103" s="47"/>
       <c r="P103" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q103" s="50" t="str">
+      <c r="Q103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="50"/>
-      <c r="S103" s="50" t="str">
+      <c r="R103" s="47"/>
+      <c r="S103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="50"/>
+      <c r="T103" s="47"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="53" t="str">
+      <c r="W103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="53" t="str">
+      <c r="X103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="50" t="str">
+      <c r="Y103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="50" t="str">
+      <c r="Z103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7296,61 +7373,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="81"/>
+      <c r="D104" s="80"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="53"/>
-      <c r="G104" s="53"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="53" t="str">
+      <c r="I104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="53" t="str">
+      <c r="J104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="53" t="str">
-        <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
-        <v> </v>
-      </c>
-      <c r="L104" s="53"/>
-      <c r="M104" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="53"/>
-      <c r="O104" s="50"/>
+      <c r="K104" s="50" t="str">
+        <f aca="false">IF(E104&gt;0,IF(V104&gt;0,0,E104-J104)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L104" s="50"/>
+      <c r="M104" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="50"/>
+      <c r="O104" s="47"/>
       <c r="P104" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q104" s="50" t="str">
+      <c r="Q104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="50"/>
-      <c r="S104" s="50" t="str">
+      <c r="R104" s="47"/>
+      <c r="S104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="50"/>
+      <c r="T104" s="47"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="53" t="str">
+      <c r="W104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="53" t="str">
+      <c r="X104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="50" t="str">
+      <c r="Y104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="50" t="str">
+      <c r="Z104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7360,61 +7437,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="81"/>
+      <c r="D105" s="80"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="53" t="str">
+      <c r="I105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="53" t="str">
+      <c r="J105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="53" t="str">
-        <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
-        <v> </v>
-      </c>
-      <c r="L105" s="53"/>
-      <c r="M105" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="53"/>
-      <c r="O105" s="50"/>
+      <c r="K105" s="50" t="str">
+        <f aca="false">IF(E105&gt;0,IF(V105&gt;0,0,E105-J105)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L105" s="50"/>
+      <c r="M105" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="50"/>
+      <c r="O105" s="47"/>
       <c r="P105" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q105" s="50" t="str">
+      <c r="Q105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="50"/>
-      <c r="S105" s="50" t="str">
+      <c r="R105" s="47"/>
+      <c r="S105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="50"/>
+      <c r="T105" s="47"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="53" t="str">
+      <c r="W105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="53" t="str">
+      <c r="X105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="50" t="str">
+      <c r="Y105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="50" t="str">
+      <c r="Z105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7424,61 +7501,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="81"/>
+      <c r="D106" s="80"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="53"/>
-      <c r="G106" s="53"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="53" t="str">
+      <c r="I106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="53" t="str">
+      <c r="J106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="53" t="str">
-        <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
-        <v> </v>
-      </c>
-      <c r="L106" s="53"/>
-      <c r="M106" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="53"/>
-      <c r="O106" s="50"/>
+      <c r="K106" s="50" t="str">
+        <f aca="false">IF(E106&gt;0,IF(V106&gt;0,0,E106-J106)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L106" s="50"/>
+      <c r="M106" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="50"/>
+      <c r="O106" s="47"/>
       <c r="P106" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q106" s="50" t="str">
+      <c r="Q106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="50"/>
-      <c r="S106" s="50" t="str">
+      <c r="R106" s="47"/>
+      <c r="S106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="50"/>
+      <c r="T106" s="47"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="53" t="str">
+      <c r="W106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="53" t="str">
+      <c r="X106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="50" t="str">
+      <c r="Y106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="50" t="str">
+      <c r="Z106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7488,61 +7565,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="81"/>
-      <c r="E107" s="85"/>
-      <c r="F107" s="53"/>
-      <c r="G107" s="53"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="84"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$90</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="53" t="str">
+      <c r="I107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="53" t="str">
+      <c r="J107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="53" t="str">
-        <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
-        <v> </v>
-      </c>
-      <c r="L107" s="53"/>
-      <c r="M107" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="53"/>
-      <c r="O107" s="50"/>
+      <c r="K107" s="50" t="str">
+        <f aca="false">IF(E107&gt;0,IF(V107&gt;0,0,E107-J107)," ")</f>
+        <v> </v>
+      </c>
+      <c r="L107" s="50"/>
+      <c r="M107" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="50"/>
+      <c r="O107" s="47"/>
       <c r="P107" s="58" t="n">
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q107" s="50" t="str">
+      <c r="Q107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="50"/>
-      <c r="S107" s="50" t="str">
+      <c r="R107" s="47"/>
+      <c r="S107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="50"/>
+      <c r="T107" s="47"/>
       <c r="U107" s="54"/>
-      <c r="V107" s="85"/>
-      <c r="W107" s="53" t="str">
+      <c r="V107" s="84"/>
+      <c r="W107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="53" t="str">
+      <c r="X107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="50" t="str">
+      <c r="Y107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="50" t="str">
+      <c r="Z107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7551,7 +7628,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7580,9 +7657,9 @@
         <f aca="false">SUM(K91:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="53"/>
+      <c r="L108" s="50"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="53"/>
+      <c r="N108" s="50"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O91:O107)</f>
         <v>0</v>
@@ -7600,8 +7677,8 @@
         <f aca="false">SUM(S91:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="50"/>
-      <c r="U108" s="52"/>
+      <c r="T108" s="47"/>
+      <c r="U108" s="49"/>
       <c r="V108" s="61" t="n">
         <f aca="false">SUM(V91:V107)</f>
         <v>0</v>
@@ -7626,31 +7703,31 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="74"/>
-      <c r="D109" s="69"/>
-      <c r="E109" s="53"/>
-      <c r="F109" s="53"/>
-      <c r="G109" s="53"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="73"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="53"/>
+      <c r="I109" s="50"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="50"/>
+      <c r="L109" s="50"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="53"/>
-      <c r="O109" s="50"/>
-      <c r="P109" s="51"/>
-      <c r="Q109" s="50"/>
-      <c r="R109" s="50"/>
-      <c r="S109" s="50"/>
-      <c r="T109" s="50"/>
-      <c r="U109" s="52"/>
-      <c r="V109" s="53"/>
-      <c r="W109" s="50"/>
-      <c r="X109" s="50"/>
-      <c r="Y109" s="50"/>
-      <c r="Z109" s="50"/>
+      <c r="N109" s="50"/>
+      <c r="O109" s="47"/>
+      <c r="P109" s="48"/>
+      <c r="Q109" s="47"/>
+      <c r="R109" s="47"/>
+      <c r="S109" s="47"/>
+      <c r="T109" s="47"/>
+      <c r="U109" s="49"/>
+      <c r="V109" s="50"/>
+      <c r="W109" s="47"/>
+      <c r="X109" s="47"/>
+      <c r="Y109" s="47"/>
+      <c r="Z109" s="47"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7662,105 +7739,105 @@
       <c r="C110" s="43"/>
       <c r="D110" s="44" t="n">
         <f aca="false">D59</f>
-        <v>45753</v>
-      </c>
-      <c r="E110" s="75" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E110" s="74" t="n">
         <f aca="false">E64+E72+E80+E88+E108</f>
-        <v>0</v>
-      </c>
-      <c r="F110" s="75" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F110" s="74" t="n">
         <f aca="false">F64+F72+F80+F88+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="75" t="n">
+      <c r="G110" s="74" t="n">
         <f aca="false">G64+G72+G80+G88+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="75" t="n">
+      <c r="I110" s="74" t="n">
         <f aca="false">I64+I72+I80+I88+I108</f>
-        <v>0</v>
-      </c>
-      <c r="J110" s="75" t="n">
+        <v>3250</v>
+      </c>
+      <c r="J110" s="74" t="n">
         <f aca="false">J64+J72+J80+J88+J108</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="75" t="n">
+        <v>3250</v>
+      </c>
+      <c r="K110" s="74" t="n">
         <f aca="false">K64+K72+K80+K88+K108</f>
-        <v>0</v>
-      </c>
-      <c r="L110" s="53"/>
+        <v>29250</v>
+      </c>
+      <c r="L110" s="50"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="53"/>
-      <c r="O110" s="75" t="n">
+      <c r="N110" s="50"/>
+      <c r="O110" s="74" t="n">
         <f aca="false">O64+O72+O80+O88+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="75" t="n">
+      <c r="Q110" s="74" t="n">
         <f aca="false">Q64+Q72+Q80+Q88+Q108</f>
-        <v>0</v>
-      </c>
-      <c r="R110" s="75" t="n">
+        <v>32500</v>
+      </c>
+      <c r="R110" s="74" t="n">
         <f aca="false">R64+R72+R80+R88+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="75" t="n">
+      <c r="S110" s="74" t="n">
         <f aca="false">S64+S72+S80+S88+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="50"/>
-      <c r="U110" s="52"/>
-      <c r="V110" s="75" t="n">
+      <c r="T110" s="47"/>
+      <c r="U110" s="49"/>
+      <c r="V110" s="74" t="n">
         <f aca="false">V64+V72+V80+V88+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="75" t="n">
+      <c r="W110" s="74" t="n">
         <f aca="false">W64+W72+W80+W88+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="75" t="n">
+      <c r="X110" s="74" t="n">
         <f aca="false">X64+X72+X80+X88+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="75" t="n">
+      <c r="Y110" s="74" t="n">
         <f aca="false">Y64+Y72+Y80+Y88+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="75" t="n">
+      <c r="Z110" s="74" t="n">
         <f aca="false">Z64+Z72+Z80+Z88+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="86"/>
-      <c r="B111" s="87"/>
-      <c r="C111" s="88"/>
-      <c r="D111" s="89"/>
-      <c r="E111" s="90"/>
-      <c r="F111" s="90"/>
-      <c r="G111" s="90"/>
-      <c r="H111" s="91"/>
-      <c r="I111" s="90"/>
-      <c r="J111" s="90"/>
-      <c r="K111" s="90"/>
-      <c r="L111" s="90"/>
-      <c r="M111" s="91"/>
-      <c r="N111" s="90"/>
-      <c r="O111" s="92"/>
-      <c r="P111" s="93"/>
-      <c r="Q111" s="92"/>
-      <c r="R111" s="92"/>
-      <c r="S111" s="92"/>
-      <c r="T111" s="92"/>
-      <c r="U111" s="87"/>
-      <c r="V111" s="90"/>
-      <c r="W111" s="90"/>
-      <c r="X111" s="90"/>
-      <c r="Y111" s="92"/>
-      <c r="Z111" s="92"/>
-      <c r="AA111" s="94"/>
+      <c r="A111" s="85"/>
+      <c r="B111" s="86"/>
+      <c r="C111" s="87"/>
+      <c r="D111" s="88"/>
+      <c r="E111" s="89"/>
+      <c r="F111" s="89"/>
+      <c r="G111" s="89"/>
+      <c r="H111" s="90"/>
+      <c r="I111" s="89"/>
+      <c r="J111" s="89"/>
+      <c r="K111" s="89"/>
+      <c r="L111" s="89"/>
+      <c r="M111" s="90"/>
+      <c r="N111" s="89"/>
+      <c r="O111" s="91"/>
+      <c r="P111" s="92"/>
+      <c r="Q111" s="91"/>
+      <c r="R111" s="91"/>
+      <c r="S111" s="91"/>
+      <c r="T111" s="91"/>
+      <c r="U111" s="86"/>
+      <c r="V111" s="89"/>
+      <c r="W111" s="89"/>
+      <c r="X111" s="89"/>
+      <c r="Y111" s="91"/>
+      <c r="Z111" s="91"/>
+      <c r="AA111" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -7846,37 +7923,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="95" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="95" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="95" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="95" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="95" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="95" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="95" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="95" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="95" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="95" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="95" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="95" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="94" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="94" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="94" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="94" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="94" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="94" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="94" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="94" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="94" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="94" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="94" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="94" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="96"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7888,23 +7965,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="105"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="104"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7916,21 +7993,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="105"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="104"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -7942,31 +8019,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98"/>
-      <c r="B4" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="109" t="s">
+      <c r="A4" s="97"/>
+      <c r="B4" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="103"/>
-      <c r="G4" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="109" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="103"/>
-      <c r="M4" s="111" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="111"/>
-      <c r="O4" s="105"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="109" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="108" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="102"/>
+      <c r="M4" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="110"/>
+      <c r="O4" s="104"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -7978,25 +8055,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="98"/>
-      <c r="B5" s="99" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="99" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="100"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="105"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="99"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="99"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="104"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -8008,31 +8085,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="98"/>
-      <c r="B6" s="112" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113" t="n">
+      <c r="A6" s="97"/>
+      <c r="B6" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="112" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="103"/>
-      <c r="G6" s="112" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="113" t="n">
+      <c r="F6" s="102"/>
+      <c r="G6" s="111" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="112" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="103"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="111"/>
-      <c r="O6" s="105"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="104"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -8044,31 +8121,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="98"/>
-      <c r="B7" s="112" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="113" t="n">
+      <c r="A7" s="97"/>
+      <c r="B7" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="112" t="n">
         <f aca="false">Schedule!E72</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="112" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="113" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F7" s="102"/>
+      <c r="G7" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="112" t="n">
         <f aca="false">Schedule!V19+Schedule!V72</f>
         <v>0</v>
       </c>
-      <c r="L7" s="103"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="105"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="104"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -8080,31 +8157,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="98"/>
-      <c r="B8" s="112" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="113" t="n">
+      <c r="A8" s="97"/>
+      <c r="B8" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112" t="n">
         <f aca="false">Schedule!E80</f>
         <v>0</v>
       </c>
-      <c r="F8" s="103"/>
-      <c r="G8" s="112" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="113" t="n">
+      <c r="F8" s="102"/>
+      <c r="G8" s="111" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="112" t="n">
         <f aca="false">Schedule!V27+Schedule!V80</f>
         <v>0</v>
       </c>
-      <c r="L8" s="103"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="105"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="104"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -8116,31 +8193,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="98"/>
-      <c r="B9" s="112" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113" t="n">
+      <c r="A9" s="97"/>
+      <c r="B9" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="112" t="n">
         <f aca="false">Schedule!E88</f>
         <v>0</v>
       </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="112" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="113" t="n">
+      <c r="F9" s="102"/>
+      <c r="G9" s="111" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="112" t="n">
         <f aca="false">Schedule!V35+Schedule!V88</f>
         <v>0</v>
       </c>
-      <c r="L9" s="103"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="105"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="104"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -8152,31 +8229,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="98"/>
-      <c r="B10" s="112" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113" t="n">
+      <c r="A10" s="97"/>
+      <c r="B10" s="111" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="103"/>
-      <c r="G10" s="112" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="113" t="n">
+      <c r="F10" s="102"/>
+      <c r="G10" s="111" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="112" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="103"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="105"/>
+        <v>12500</v>
+      </c>
+      <c r="L10" s="102"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="104"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8188,31 +8265,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="98"/>
-      <c r="B11" s="114" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="115" t="n">
+      <c r="A11" s="97"/>
+      <c r="B11" s="113" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="114" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="103"/>
-      <c r="G11" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="115" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F11" s="102"/>
+      <c r="G11" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="114" t="n">
         <f aca="false">SUM(K6:K10)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="103"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="111"/>
-      <c r="O11" s="105"/>
+        <v>12500</v>
+      </c>
+      <c r="L11" s="102"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="104"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8224,21 +8301,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="105"/>
+      <c r="A12" s="97"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="104"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8250,31 +8327,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="98"/>
-      <c r="B13" s="114" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="117" t="n">
+      <c r="A13" s="97"/>
+      <c r="B13" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="116" t="n">
         <f aca="false">[2]Mar!$AB$2</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="103"/>
-      <c r="G13" s="116" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="117" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F13" s="102"/>
+      <c r="G13" s="115" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="116" t="n">
         <f aca="false">[3]Mar!$V$2</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="103"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="105"/>
+        <v>12500</v>
+      </c>
+      <c r="L13" s="102"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="104"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8286,21 +8363,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="105"/>
+      <c r="A14" s="97"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="104"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8312,33 +8389,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="98"/>
-      <c r="B15" s="118" t="str">
+      <c r="A15" s="97"/>
+      <c r="B15" s="117" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119" t="n">
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="118" t="n">
         <f aca="false">E13-E11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="103"/>
-      <c r="G15" s="118" t="str">
+      <c r="F15" s="102"/>
+      <c r="G15" s="117" t="str">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="119" t="n">
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="118" t="n">
         <f aca="false">K13-K11</f>
         <v>0</v>
       </c>
-      <c r="L15" s="103"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="105"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="104"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8350,21 +8427,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="120"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="125"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="126"/>
+      <c r="A16" s="119"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="124"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="125"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8416,122 +8493,122 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="126" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="126" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="127" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="126" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="126" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="129"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="129"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="128"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="129"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="133" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="n">
+      <c r="A2" s="128"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="132" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133" t="n">
         <f aca="false">SUM(E8:E14)</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="129"/>
+        <v>20000</v>
+      </c>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="128"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="129"/>
-      <c r="B3" s="137" t="s">
-        <v>59</v>
+      <c r="A3" s="128"/>
+      <c r="B3" s="136" t="s">
+        <v>63</v>
       </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="129"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="129"/>
-      <c r="B4" s="52"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="49"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="129"/>
-    </row>
-    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="140"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="128"/>
+    </row>
+    <row r="5" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="139"/>
       <c r="B5" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="141" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="141" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="141" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E5" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="140" t="s">
+        <v>69</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="141" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
+        <v>70</v>
+      </c>
+      <c r="I5" s="140" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
       <c r="L5" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="140"/>
-    </row>
-    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="140"/>
+        <v>72</v>
+      </c>
+      <c r="M5" s="139"/>
+    </row>
+    <row r="6" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="139"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8539,273 +8616,305 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6" s="141" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" s="141" t="s">
-        <v>71</v>
+      <c r="I6" s="140" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="140" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="140" t="s">
+        <v>75</v>
       </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="140"/>
+      <c r="M6" s="139"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="129"/>
-      <c r="B7" s="52"/>
+      <c r="A7" s="128"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="134"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="129"/>
+      <c r="M7" s="128"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="129"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="135" t="str">
+      <c r="A8" s="128"/>
+      <c r="B8" s="54" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="133" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F8" s="133" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" s="133" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H8" s="142" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="134" t="n">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
-        <v> </v>
-      </c>
-      <c r="J8" s="135" t="str">
+        <v>750</v>
+      </c>
+      <c r="J8" s="134" t="n">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
-        <v> </v>
-      </c>
-      <c r="K8" s="135" t="str">
+        <v>660</v>
+      </c>
+      <c r="K8" s="134" t="n">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
-        <v> </v>
-      </c>
-      <c r="L8" s="56"/>
-      <c r="M8" s="129"/>
+        <v>90</v>
+      </c>
+      <c r="L8" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="128"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="129"/>
-      <c r="B9" s="52"/>
+      <c r="A9" s="128"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="129"/>
+      <c r="M9" s="128"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="129"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="143"/>
-      <c r="I10" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J10" s="135" t="str">
+      <c r="A10" s="128"/>
+      <c r="B10" s="54" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="133" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F10" s="133" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" s="133" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" s="142" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="134" t="n">
+        <f aca="false">IF(E10&gt;0,(E10+F10+G10)/H10," ")</f>
+        <v>405</v>
+      </c>
+      <c r="J10" s="134" t="n">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
-        <v> </v>
-      </c>
-      <c r="K10" s="135" t="str">
+        <v>355</v>
+      </c>
+      <c r="K10" s="134" t="n">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
-        <v> </v>
-      </c>
-      <c r="L10" s="56"/>
-      <c r="M10" s="129"/>
+        <v>50</v>
+      </c>
+      <c r="L10" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" s="128"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="129"/>
-      <c r="B11" s="52"/>
+      <c r="A11" s="128"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="129"/>
+      <c r="M11" s="128"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="129"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J12" s="135" t="str">
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="134" t="str">
+        <f aca="false">IF(E12&gt;0,(E12+F12+G12)/H12," ")</f>
+        <v> </v>
+      </c>
+      <c r="J12" s="134" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="135" t="str">
+      <c r="K12" s="134" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="129"/>
+      <c r="M12" s="128"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="129"/>
-      <c r="B13" s="52"/>
+      <c r="A13" s="128"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="129"/>
+      <c r="M13" s="128"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="129"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J14" s="135" t="str">
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="134" t="str">
+        <f aca="false">IF(E14&gt;0,(E14+F14+G14)/H14," ")</f>
+        <v> </v>
+      </c>
+      <c r="J14" s="134" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="135" t="str">
+      <c r="K14" s="134" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="129"/>
+      <c r="M14" s="128"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="129"/>
-      <c r="B15" s="52"/>
+      <c r="A15" s="128"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="129"/>
+      <c r="M15" s="128"/>
     </row>
     <row r="16" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="129"/>
-      <c r="B16" s="99"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="101"/>
-      <c r="M16" s="129"/>
+      <c r="A16" s="128"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="100"/>
+      <c r="M16" s="128"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="129"/>
-      <c r="B17" s="137" t="s">
-        <v>72</v>
+      <c r="A17" s="128"/>
+      <c r="B17" s="136" t="s">
+        <v>80</v>
       </c>
       <c r="C17" s="62"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
       <c r="H17" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" s="132"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
+        <v>81</v>
+      </c>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="129"/>
+      <c r="M17" s="128"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="129"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="128"/>
+      <c r="B18" s="49"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
       <c r="L18" s="62"/>
-      <c r="M18" s="129"/>
-    </row>
-    <row r="19" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="140"/>
+      <c r="M18" s="128"/>
+    </row>
+    <row r="19" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="139"/>
       <c r="B19" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="141" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="141" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19" s="141" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E19" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="140" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="140" t="s">
+        <v>69</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" s="141" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
+        <v>70</v>
+      </c>
+      <c r="I19" s="140" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="140"/>
+      <c r="K19" s="140"/>
       <c r="L19" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="M19" s="140"/>
-    </row>
-    <row r="20" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="140"/>
+        <v>72</v>
+      </c>
+      <c r="M19" s="139"/>
+    </row>
+    <row r="20" s="141" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="139"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -8813,203 +8922,203 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
-      <c r="I20" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="J20" s="141" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="141" t="s">
-        <v>71</v>
+      <c r="I20" s="140" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="140" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" s="140" t="s">
+        <v>75</v>
       </c>
       <c r="L20" s="21"/>
-      <c r="M20" s="140"/>
-    </row>
-    <row r="21" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="140"/>
-      <c r="B21" s="144"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="144"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="145"/>
-      <c r="J21" s="145"/>
-      <c r="K21" s="145"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="140"/>
+      <c r="M20" s="139"/>
+    </row>
+    <row r="21" s="141" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="139"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="143"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="139"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="129"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="135" t="str">
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="134" t="str">
         <f aca="false">IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
         <v> </v>
       </c>
-      <c r="J22" s="135" t="str">
+      <c r="J22" s="134" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="135" t="str">
+      <c r="K22" s="134" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="129"/>
+      <c r="M22" s="128"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="129"/>
-      <c r="B23" s="52"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="49"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="135"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="129"/>
+      <c r="M23" s="128"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="129"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J24" s="135" t="str">
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="142"/>
+      <c r="I24" s="134" t="str">
+        <f aca="false">IF(E24&gt;0,(E24+F24+G24)/H24," ")</f>
+        <v> </v>
+      </c>
+      <c r="J24" s="134" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="135" t="str">
+      <c r="K24" s="134" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="129"/>
+      <c r="M24" s="128"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="129"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="128"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="135"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="129"/>
+      <c r="M25" s="128"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="129"/>
+      <c r="A26" s="128"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J26" s="135" t="str">
+      <c r="E26" s="133"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="134" t="str">
+        <f aca="false">IF(E26&gt;0,(E26+F26+G26)/H26," ")</f>
+        <v> </v>
+      </c>
+      <c r="J26" s="134" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="135" t="str">
+      <c r="K26" s="134" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="129"/>
+      <c r="M26" s="128"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="129"/>
-      <c r="B27" s="52"/>
+      <c r="A27" s="128"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="134"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="134"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="129"/>
+      <c r="M27" s="128"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="129"/>
+      <c r="A28" s="128"/>
       <c r="B28" s="54"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="134"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="143"/>
-      <c r="I28" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J28" s="135" t="str">
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="134" t="str">
+        <f aca="false">IF(E28&gt;0,(E28+F28+G28)/H28," ")</f>
+        <v> </v>
+      </c>
+      <c r="J28" s="134" t="str">
         <f aca="false">IF(H28&gt;0,I28-K28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="135" t="str">
+      <c r="K28" s="134" t="str">
         <f aca="false">IF(H28&gt;0,G28/H28," ")</f>
         <v> </v>
       </c>
       <c r="L28" s="56"/>
-      <c r="M28" s="129"/>
+      <c r="M28" s="128"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="129"/>
-      <c r="B29" s="52"/>
+      <c r="A29" s="128"/>
+      <c r="B29" s="49"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="135"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="134"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="129"/>
+      <c r="M29" s="128"/>
     </row>
     <row r="30" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="129"/>
-      <c r="B30" s="99"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="131"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="129"/>
+      <c r="A30" s="128"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -280,6 +280,9 @@
     <t xml:space="preserve">Dell</t>
   </si>
   <si>
+    <t xml:space="preserve">Precision Tooling Supplies</t>
+  </si>
+  <si>
     <t xml:space="preserve">IKEA</t>
   </si>
   <si>
@@ -433,9 +436,6 @@
   </si>
   <si>
     <t xml:space="preserve">HP-2025-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precision Tooling Supplies</t>
   </si>
   <si>
     <t xml:space="preserve">HP-2025-02</t>
@@ -1491,7 +1491,7 @@
       <sheetData sheetId="12">
         <row r="2">
           <cell r="AB2">
-            <v>32500</v>
+            <v>52500</v>
           </cell>
         </row>
       </sheetData>
@@ -1699,7 +1699,7 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12" t="n">
         <f aca="false">E57+E110</f>
-        <v>65500</v>
+        <v>85500</v>
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
@@ -1714,15 +1714,15 @@
       </c>
       <c r="I1" s="13" t="n">
         <f aca="false">I57+I110</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="J1" s="13" t="n">
         <f aca="false">J57+J110</f>
-        <v>21838</v>
+        <v>23838</v>
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>30990</v>
+        <v>48990</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Q1" s="13" t="n">
         <f aca="false">Q57+Q110</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
@@ -5331,14 +5331,14 @@
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
       <c r="B68" s="54" t="n">
-        <v>45853</v>
+        <v>45809</v>
       </c>
       <c r="C68" s="55" t="s">
         <v>40</v>
       </c>
       <c r="D68" s="56"/>
       <c r="E68" s="57" t="n">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="F68" s="50"/>
       <c r="G68" s="50"/>
@@ -5348,15 +5348,15 @@
       </c>
       <c r="I68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="J68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="K68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,IF(V68&gt;0,0,E68-J68)," ")</f>
-        <v>900</v>
+        <v>11700</v>
       </c>
       <c r="L68" s="50"/>
       <c r="M68" s="58"/>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="Q68" s="47" t="n">
         <f aca="false">IF(E68&gt;0,E68*P68," ")</f>
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="R68" s="47"/>
       <c r="S68" s="47" t="n">
@@ -5399,14 +5399,14 @@
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
       <c r="B69" s="54" t="n">
-        <v>45955</v>
+        <v>45853</v>
       </c>
       <c r="C69" s="55" t="s">
         <v>41</v>
       </c>
       <c r="D69" s="56"/>
       <c r="E69" s="57" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="F69" s="50"/>
       <c r="G69" s="50"/>
@@ -5416,15 +5416,15 @@
       </c>
       <c r="I69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="J69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="K69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,IF(V69&gt;0,0,E69-J69)," ")</f>
-        <v>27000</v>
+        <v>900</v>
       </c>
       <c r="L69" s="50"/>
       <c r="M69" s="58"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="Q69" s="47" t="n">
         <f aca="false">IF(E69&gt;0,E69*P69," ")</f>
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="R69" s="47"/>
       <c r="S69" s="47" t="n">
@@ -5466,27 +5466,33 @@
     </row>
     <row r="70" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="42"/>
-      <c r="B70" s="54"/>
-      <c r="C70" s="55"/>
+      <c r="B70" s="54" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C70" s="55" t="s">
+        <v>40</v>
+      </c>
       <c r="D70" s="56"/>
-      <c r="E70" s="57"/>
+      <c r="E70" s="57" t="n">
+        <v>7000</v>
+      </c>
       <c r="F70" s="50"/>
       <c r="G70" s="50"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="50" t="str">
+      <c r="I70" s="50" t="n">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J70" s="50" t="str">
+        <v>700</v>
+      </c>
+      <c r="J70" s="50" t="n">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
-        <v> </v>
-      </c>
-      <c r="K70" s="50" t="str">
+        <v>700</v>
+      </c>
+      <c r="K70" s="50" t="n">
         <f aca="false">IF(E70&gt;0,IF(V70&gt;0,0,E70-J70)," ")</f>
-        <v> </v>
+        <v>6300</v>
       </c>
       <c r="L70" s="50"/>
       <c r="M70" s="58"/>
@@ -5496,14 +5502,14 @@
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="47" t="str">
+      <c r="Q70" s="47" t="n">
         <f aca="false">IF(E70&gt;0,E70*P70," ")</f>
-        <v> </v>
+        <v>7000</v>
       </c>
       <c r="R70" s="47"/>
-      <c r="S70" s="47" t="str">
+      <c r="S70" s="47" t="n">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="T70" s="47"/>
       <c r="U70" s="54"/>
@@ -5528,27 +5534,33 @@
     </row>
     <row r="71" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="42"/>
-      <c r="B71" s="54"/>
-      <c r="C71" s="55"/>
+      <c r="B71" s="54" t="n">
+        <v>45955</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>42</v>
+      </c>
       <c r="D71" s="56"/>
-      <c r="E71" s="57"/>
+      <c r="E71" s="57" t="n">
+        <v>30000</v>
+      </c>
       <c r="F71" s="50"/>
       <c r="G71" s="50"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="50" t="str">
+      <c r="I71" s="50" t="n">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J71" s="50" t="str">
+        <v>3000</v>
+      </c>
+      <c r="J71" s="50" t="n">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
-        <v> </v>
-      </c>
-      <c r="K71" s="50" t="str">
+        <v>3000</v>
+      </c>
+      <c r="K71" s="50" t="n">
         <f aca="false">IF(E71&gt;0,IF(V71&gt;0,0,E71-J71)," ")</f>
-        <v> </v>
+        <v>27000</v>
       </c>
       <c r="L71" s="50"/>
       <c r="M71" s="58"/>
@@ -5558,14 +5570,14 @@
         <f aca="false">P$4</f>
         <v>1</v>
       </c>
-      <c r="Q71" s="47" t="str">
+      <c r="Q71" s="47" t="n">
         <f aca="false">IF(E71&gt;0,E71*P71," ")</f>
-        <v> </v>
+        <v>30000</v>
       </c>
       <c r="R71" s="47"/>
-      <c r="S71" s="47" t="str">
+      <c r="S71" s="47" t="n">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="T71" s="47"/>
       <c r="U71" s="54"/>
@@ -5591,13 +5603,13 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="42"/>
       <c r="B72" s="59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
       <c r="E72" s="60" t="n">
         <f aca="false">SUM(E67:E71)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F72" s="61" t="n">
         <f aca="false">SUM(F67:F71)</f>
@@ -5610,15 +5622,15 @@
       <c r="H72" s="58"/>
       <c r="I72" s="61" t="n">
         <f aca="false">SUM(I67:I71)</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="J72" s="61" t="n">
         <f aca="false">SUM(J67:J71)</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="K72" s="61" t="n">
         <f aca="false">SUM(K67:K71)</f>
-        <v>29250</v>
+        <v>47250</v>
       </c>
       <c r="L72" s="50"/>
       <c r="M72" s="58"/>
@@ -5630,7 +5642,7 @@
       <c r="P72" s="62"/>
       <c r="Q72" s="61" t="n">
         <f aca="false">SUM(Q67:Q71)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="R72" s="61" t="n">
         <f aca="false">SUM(R67:R71)</f>
@@ -6040,7 +6052,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="42"/>
       <c r="B80" s="59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C80" s="59"/>
       <c r="D80" s="59"/>
@@ -6489,7 +6501,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="42"/>
       <c r="B88" s="59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -7628,7 +7640,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7743,7 +7755,7 @@
       </c>
       <c r="E110" s="74" t="n">
         <f aca="false">E64+E72+E80+E88+E108</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F110" s="74" t="n">
         <f aca="false">F64+F72+F80+F88+F108</f>
@@ -7756,15 +7768,15 @@
       <c r="H110" s="58"/>
       <c r="I110" s="74" t="n">
         <f aca="false">I64+I72+I80+I88+I108</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="J110" s="74" t="n">
         <f aca="false">J64+J72+J80+J88+J108</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="K110" s="74" t="n">
         <f aca="false">K64+K72+K80+K88+K108</f>
-        <v>29250</v>
+        <v>47250</v>
       </c>
       <c r="L110" s="50"/>
       <c r="M110" s="58"/>
@@ -7776,7 +7788,7 @@
       <c r="P110" s="62"/>
       <c r="Q110" s="74" t="n">
         <f aca="false">Q64+Q72+Q80+Q88+Q108</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="R110" s="74" t="n">
         <f aca="false">R64+R72+R80+R88+R108</f>
@@ -7970,7 +7982,7 @@
       <c r="C2" s="99"/>
       <c r="D2" s="100"/>
       <c r="E2" s="101" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" s="101"/>
       <c r="G2" s="101"/>
@@ -8021,7 +8033,7 @@
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="97"/>
       <c r="B4" s="107" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="99"/>
       <c r="D4" s="100"/>
@@ -8030,17 +8042,17 @@
       </c>
       <c r="F4" s="102"/>
       <c r="G4" s="109" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="109"/>
       <c r="I4" s="109"/>
       <c r="J4" s="102"/>
       <c r="K4" s="108" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L4" s="102"/>
       <c r="M4" s="110" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N4" s="110"/>
       <c r="O4" s="104"/>
@@ -8057,14 +8069,14 @@
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="97"/>
       <c r="B5" s="98" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="99"/>
       <c r="D5" s="100"/>
       <c r="E5" s="102"/>
       <c r="F5" s="102"/>
       <c r="G5" s="98" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100"/>
@@ -8097,7 +8109,7 @@
       </c>
       <c r="F6" s="102"/>
       <c r="G6" s="111" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H6" s="111"/>
       <c r="I6" s="111"/>
@@ -8123,17 +8135,17 @@
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="97"/>
       <c r="B7" s="111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="111"/>
       <c r="D7" s="111"/>
       <c r="E7" s="112" t="n">
         <f aca="false">Schedule!E72</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F7" s="102"/>
       <c r="G7" s="111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="111"/>
@@ -8159,7 +8171,7 @@
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="97"/>
       <c r="B8" s="111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="111"/>
       <c r="D8" s="111"/>
@@ -8169,7 +8181,7 @@
       </c>
       <c r="F8" s="102"/>
       <c r="G8" s="111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8" s="111"/>
       <c r="I8" s="111"/>
@@ -8195,7 +8207,7 @@
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="97"/>
       <c r="B9" s="111" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="111"/>
       <c r="D9" s="111"/>
@@ -8205,7 +8217,7 @@
       </c>
       <c r="F9" s="102"/>
       <c r="G9" s="111" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H9" s="111"/>
       <c r="I9" s="111"/>
@@ -8231,7 +8243,7 @@
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="97"/>
       <c r="B10" s="111" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="111"/>
       <c r="D10" s="111"/>
@@ -8241,7 +8253,7 @@
       </c>
       <c r="F10" s="102"/>
       <c r="G10" s="111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -8267,17 +8279,17 @@
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="97"/>
       <c r="B11" s="113" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="113"/>
       <c r="D11" s="113"/>
       <c r="E11" s="114" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F11" s="102"/>
       <c r="G11" s="115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="115"/>
       <c r="I11" s="115"/>
@@ -8329,17 +8341,17 @@
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="97"/>
       <c r="B13" s="113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="113"/>
       <c r="D13" s="113"/>
       <c r="E13" s="116" t="n">
         <f aca="false">[2]Mar!$AB$2</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F13" s="102"/>
       <c r="G13" s="115" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13" s="115"/>
       <c r="I13" s="115"/>
@@ -8524,7 +8536,7 @@
       <c r="A2" s="128"/>
       <c r="B2" s="131"/>
       <c r="C2" s="132" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" s="132"/>
       <c r="E2" s="133" t="n">
@@ -8533,7 +8545,7 @@
       </c>
       <c r="F2" s="134"/>
       <c r="G2" s="135" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H2" s="135"/>
       <c r="I2" s="135"/>
@@ -8545,7 +8557,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="128"/>
       <c r="B3" s="136" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="137"/>
@@ -8577,33 +8589,33 @@
     <row r="5" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="139"/>
       <c r="B5" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" s="140" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" s="140" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="140" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I5" s="140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J5" s="140"/>
       <c r="K5" s="140"/>
       <c r="L5" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M5" s="139"/>
     </row>
@@ -8617,13 +8629,13 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="140" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J6" s="140" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K6" s="140" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="139"/>
@@ -8649,10 +8661,10 @@
         <v>45809</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="133" t="n">
         <v>13000</v>
@@ -8679,7 +8691,7 @@
         <v>90</v>
       </c>
       <c r="L8" s="56" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="M8" s="128"/>
     </row>
@@ -8704,7 +8716,7 @@
         <v>45901</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" s="56" t="s">
         <v>79</v>
@@ -8734,7 +8746,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="56" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="M10" s="128"/>
     </row>
@@ -8883,33 +8895,33 @@
     <row r="19" s="141" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="139"/>
       <c r="B19" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="140" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" s="140" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="140" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J19" s="140"/>
       <c r="K19" s="140"/>
       <c r="L19" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M19" s="139"/>
     </row>
@@ -8923,13 +8935,13 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="140" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J20" s="140" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K20" s="140" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L20" s="21"/>
       <c r="M20" s="139"/>

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -1410,16 +1410,6 @@
             <v>0.14</v>
           </cell>
         </row>
-        <row r="8">
-          <cell r="E8">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="G8">
-            <v>3000</v>
-          </cell>
-        </row>
         <row r="13">
           <cell r="G13">
             <v>0</v>
@@ -1742,11 +1732,11 @@
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="S1" s="13" t="n">
         <f aca="false">S57+S110</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T1" s="16"/>
       <c r="U1" s="17" t="s">
@@ -1766,7 +1756,7 @@
       </c>
       <c r="Y1" s="13" t="n">
         <f aca="false">Y57+Y110</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z1" s="13" t="n">
         <f aca="false">Z57+Z110</f>
@@ -3632,7 +3622,7 @@
       <c r="C37" s="69"/>
       <c r="D37" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="E37" s="50"/>
       <c r="F37" s="50"/>
@@ -3705,12 +3695,12 @@
       <c r="P38" s="48"/>
       <c r="Q38" s="47"/>
       <c r="R38" s="47" t="n">
-        <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
-        <v>3000</v>
+        <f aca="false">IF(O38&gt;0,O38*R$4*(1-M38)," ")</f>
+        <v>3360</v>
       </c>
       <c r="S38" s="47" t="n">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T38" s="47"/>
       <c r="U38" s="54" t="n">
@@ -3729,7 +3719,7 @@
       </c>
       <c r="Y38" s="47" t="n">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
@@ -3773,7 +3763,7 @@
       <c r="P39" s="48"/>
       <c r="Q39" s="47"/>
       <c r="R39" s="47" t="str">
-        <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
+        <f aca="false">IF(O39&gt;0,O39*R$4*(1-M39)," ")</f>
         <v> </v>
       </c>
       <c r="S39" s="47" t="str">
@@ -3837,7 +3827,7 @@
       <c r="P40" s="48"/>
       <c r="Q40" s="47"/>
       <c r="R40" s="47" t="str">
-        <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
+        <f aca="false">IF(O40&gt;0,O40*R$4*(1-M40)," ")</f>
         <v> </v>
       </c>
       <c r="S40" s="47" t="str">
@@ -3901,7 +3891,7 @@
       <c r="P41" s="48"/>
       <c r="Q41" s="47"/>
       <c r="R41" s="47" t="str">
-        <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
+        <f aca="false">IF(O41&gt;0,O41*R$4*(1-M41)," ")</f>
         <v> </v>
       </c>
       <c r="S41" s="47" t="str">
@@ -3965,7 +3955,7 @@
       <c r="P42" s="48"/>
       <c r="Q42" s="47"/>
       <c r="R42" s="47" t="str">
-        <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
+        <f aca="false">IF(O42&gt;0,O42*R$4*(1-M42)," ")</f>
         <v> </v>
       </c>
       <c r="S42" s="47" t="str">
@@ -4001,7 +3991,7 @@
       <c r="C43" s="69"/>
       <c r="D43" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="E43" s="50"/>
       <c r="F43" s="50"/>
@@ -4063,7 +4053,7 @@
       <c r="P44" s="48"/>
       <c r="Q44" s="47"/>
       <c r="R44" s="47" t="str">
-        <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
+        <f aca="false">IF(O44&gt;0,O44*R$4*(1-M44)," ")</f>
         <v> </v>
       </c>
       <c r="S44" s="47" t="str">
@@ -4127,7 +4117,7 @@
       <c r="P45" s="48"/>
       <c r="Q45" s="47"/>
       <c r="R45" s="47" t="str">
-        <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
+        <f aca="false">IF(O45&gt;0,O45*R$4*(1-M45)," ")</f>
         <v> </v>
       </c>
       <c r="S45" s="47" t="str">
@@ -4191,7 +4181,7 @@
       <c r="P46" s="48"/>
       <c r="Q46" s="47"/>
       <c r="R46" s="47" t="str">
-        <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
+        <f aca="false">IF(O46&gt;0,O46*R$4*(1-M46)," ")</f>
         <v> </v>
       </c>
       <c r="S46" s="47" t="str">
@@ -4255,7 +4245,7 @@
       <c r="P47" s="48"/>
       <c r="Q47" s="47"/>
       <c r="R47" s="47" t="str">
-        <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
+        <f aca="false">IF(O47&gt;0,O47*R$4*(1-M47)," ")</f>
         <v> </v>
       </c>
       <c r="S47" s="47" t="str">
@@ -4319,7 +4309,7 @@
       <c r="P48" s="48"/>
       <c r="Q48" s="47"/>
       <c r="R48" s="47" t="str">
-        <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
+        <f aca="false">IF(O48&gt;0,O48*R$4*(1-M48)," ")</f>
         <v> </v>
       </c>
       <c r="S48" s="47" t="str">
@@ -4744,11 +4734,11 @@
       </c>
       <c r="R55" s="61" t="n">
         <f aca="false">SUM(R38:R54)</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="S55" s="61" t="n">
         <f aca="false">SUM(S38:S54)</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T55" s="50"/>
       <c r="U55" s="49"/>
@@ -4766,7 +4756,7 @@
       </c>
       <c r="Y55" s="61" t="n">
         <f aca="false">SUM(Y38:Y54)</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z55" s="61" t="n">
         <f aca="false">SUM(Z38:Z54)</f>
@@ -4853,11 +4843,11 @@
       </c>
       <c r="R57" s="74" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="S57" s="74" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T57" s="47"/>
       <c r="U57" s="49"/>
@@ -4875,7 +4865,7 @@
       </c>
       <c r="Y57" s="74" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z57" s="74" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
@@ -6612,7 +6602,7 @@
       <c r="C90" s="69"/>
       <c r="D90" s="70" t="n">
         <f aca="false">D37</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
@@ -6674,7 +6664,7 @@
       <c r="P91" s="48"/>
       <c r="Q91" s="47"/>
       <c r="R91" s="47" t="str">
-        <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
+        <f aca="false">IF(E91&gt;0,E91*R$4*(1-M91)," ")</f>
         <v> </v>
       </c>
       <c r="S91" s="47" t="str">
@@ -6735,7 +6725,7 @@
       <c r="P92" s="48"/>
       <c r="Q92" s="47"/>
       <c r="R92" s="47" t="str">
-        <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
+        <f aca="false">IF(E92&gt;0,E92*R$4*(1-M92)," ")</f>
         <v> </v>
       </c>
       <c r="S92" s="47" t="str">
@@ -6796,7 +6786,7 @@
       <c r="P93" s="48"/>
       <c r="Q93" s="47"/>
       <c r="R93" s="47" t="str">
-        <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
+        <f aca="false">IF(E93&gt;0,E93*R$4*(1-M93)," ")</f>
         <v> </v>
       </c>
       <c r="S93" s="47" t="str">
@@ -6857,7 +6847,7 @@
       <c r="P94" s="48"/>
       <c r="Q94" s="47"/>
       <c r="R94" s="47" t="str">
-        <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
+        <f aca="false">IF(E94&gt;0,E94*R$4*(1-M94)," ")</f>
         <v> </v>
       </c>
       <c r="S94" s="47" t="str">
@@ -6918,7 +6908,7 @@
       <c r="P95" s="48"/>
       <c r="Q95" s="47"/>
       <c r="R95" s="47" t="str">
-        <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
+        <f aca="false">IF(E95&gt;0,E95*R$4*(1-M95)," ")</f>
         <v> </v>
       </c>
       <c r="S95" s="47" t="str">
@@ -6955,7 +6945,7 @@
       <c r="C96" s="83"/>
       <c r="D96" s="70" t="n">
         <f aca="false">D43</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="50"/>
       <c r="F96" s="50"/>
@@ -7014,7 +7004,7 @@
       <c r="P97" s="48"/>
       <c r="Q97" s="47"/>
       <c r="R97" s="47" t="str">
-        <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
+        <f aca="false">IF(E97&gt;0,E97*R$4*(1-M97)," ")</f>
         <v> </v>
       </c>
       <c r="S97" s="47" t="str">
@@ -7075,7 +7065,7 @@
       <c r="P98" s="48"/>
       <c r="Q98" s="47"/>
       <c r="R98" s="47" t="str">
-        <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
+        <f aca="false">IF(E98&gt;0,E98*R$4*(1-M98)," ")</f>
         <v> </v>
       </c>
       <c r="S98" s="47" t="str">
@@ -7136,7 +7126,7 @@
       <c r="P99" s="48"/>
       <c r="Q99" s="47"/>
       <c r="R99" s="47" t="str">
-        <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
+        <f aca="false">IF(E99&gt;0,E99*R$4*(1-M99)," ")</f>
         <v> </v>
       </c>
       <c r="S99" s="47" t="str">
@@ -7197,7 +7187,7 @@
       <c r="P100" s="48"/>
       <c r="Q100" s="47"/>
       <c r="R100" s="47" t="str">
-        <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
+        <f aca="false">IF(E100&gt;0,E100*R$4*(1-M100)," ")</f>
         <v> </v>
       </c>
       <c r="S100" s="47" t="str">
@@ -7258,7 +7248,7 @@
       <c r="P101" s="48"/>
       <c r="Q101" s="47"/>
       <c r="R101" s="47" t="str">
-        <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
+        <f aca="false">IF(E101&gt;0,E101*R$4*(1-M101)," ")</f>
         <v> </v>
       </c>
       <c r="S101" s="47" t="str">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -1410,6 +1410,16 @@
             <v>0.14</v>
           </cell>
         </row>
+        <row r="8">
+          <cell r="E8">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="G8">
+            <v>3000</v>
+          </cell>
+        </row>
         <row r="13">
           <cell r="G13">
             <v>0</v>
@@ -1732,11 +1742,11 @@
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
-        <v>3360</v>
+        <v>3000</v>
       </c>
       <c r="S1" s="13" t="n">
         <f aca="false">S57+S110</f>
-        <v>20640</v>
+        <v>21000</v>
       </c>
       <c r="T1" s="16"/>
       <c r="U1" s="17" t="s">
@@ -1756,7 +1766,7 @@
       </c>
       <c r="Y1" s="13" t="n">
         <f aca="false">Y57+Y110</f>
-        <v>8140</v>
+        <v>8500</v>
       </c>
       <c r="Z1" s="13" t="n">
         <f aca="false">Z57+Z110</f>
@@ -3622,7 +3632,7 @@
       <c r="C37" s="69"/>
       <c r="D37" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E37" s="50"/>
       <c r="F37" s="50"/>
@@ -3695,12 +3705,12 @@
       <c r="P38" s="48"/>
       <c r="Q38" s="47"/>
       <c r="R38" s="47" t="n">
-        <f aca="false">IF(O38&gt;0,O38*R$4*(1-M38)," ")</f>
-        <v>3360</v>
+        <f aca="false">IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
+        <v>3000</v>
       </c>
       <c r="S38" s="47" t="n">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
-        <v>20640</v>
+        <v>21000</v>
       </c>
       <c r="T38" s="47"/>
       <c r="U38" s="54" t="n">
@@ -3719,7 +3729,7 @@
       </c>
       <c r="Y38" s="47" t="n">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,(S38-V38)*(1-M38)," ")," ")</f>
-        <v>8140</v>
+        <v>8500</v>
       </c>
       <c r="Z38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,(V38-S38)*(1-M38)," ")," ")</f>
@@ -3763,7 +3773,7 @@
       <c r="P39" s="48"/>
       <c r="Q39" s="47"/>
       <c r="R39" s="47" t="str">
-        <f aca="false">IF(O39&gt;0,O39*R$4*(1-M39)," ")</f>
+        <f aca="false">IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
         <v> </v>
       </c>
       <c r="S39" s="47" t="str">
@@ -3827,7 +3837,7 @@
       <c r="P40" s="48"/>
       <c r="Q40" s="47"/>
       <c r="R40" s="47" t="str">
-        <f aca="false">IF(O40&gt;0,O40*R$4*(1-M40)," ")</f>
+        <f aca="false">IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
         <v> </v>
       </c>
       <c r="S40" s="47" t="str">
@@ -3891,7 +3901,7 @@
       <c r="P41" s="48"/>
       <c r="Q41" s="47"/>
       <c r="R41" s="47" t="str">
-        <f aca="false">IF(O41&gt;0,O41*R$4*(1-M41)," ")</f>
+        <f aca="false">IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
         <v> </v>
       </c>
       <c r="S41" s="47" t="str">
@@ -3955,7 +3965,7 @@
       <c r="P42" s="48"/>
       <c r="Q42" s="47"/>
       <c r="R42" s="47" t="str">
-        <f aca="false">IF(O42&gt;0,O42*R$4*(1-M42)," ")</f>
+        <f aca="false">IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
         <v> </v>
       </c>
       <c r="S42" s="47" t="str">
@@ -3991,7 +4001,7 @@
       <c r="C43" s="69"/>
       <c r="D43" s="70" t="n">
         <f aca="false">[1]Admin!$E$8</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E43" s="50"/>
       <c r="F43" s="50"/>
@@ -4053,7 +4063,7 @@
       <c r="P44" s="48"/>
       <c r="Q44" s="47"/>
       <c r="R44" s="47" t="str">
-        <f aca="false">IF(O44&gt;0,O44*R$4*(1-M44)," ")</f>
+        <f aca="false">IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
         <v> </v>
       </c>
       <c r="S44" s="47" t="str">
@@ -4117,7 +4127,7 @@
       <c r="P45" s="48"/>
       <c r="Q45" s="47"/>
       <c r="R45" s="47" t="str">
-        <f aca="false">IF(O45&gt;0,O45*R$4*(1-M45)," ")</f>
+        <f aca="false">IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
         <v> </v>
       </c>
       <c r="S45" s="47" t="str">
@@ -4181,7 +4191,7 @@
       <c r="P46" s="48"/>
       <c r="Q46" s="47"/>
       <c r="R46" s="47" t="str">
-        <f aca="false">IF(O46&gt;0,O46*R$4*(1-M46)," ")</f>
+        <f aca="false">IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
         <v> </v>
       </c>
       <c r="S46" s="47" t="str">
@@ -4245,7 +4255,7 @@
       <c r="P47" s="48"/>
       <c r="Q47" s="47"/>
       <c r="R47" s="47" t="str">
-        <f aca="false">IF(O47&gt;0,O47*R$4*(1-M47)," ")</f>
+        <f aca="false">IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
         <v> </v>
       </c>
       <c r="S47" s="47" t="str">
@@ -4309,7 +4319,7 @@
       <c r="P48" s="48"/>
       <c r="Q48" s="47"/>
       <c r="R48" s="47" t="str">
-        <f aca="false">IF(O48&gt;0,O48*R$4*(1-M48)," ")</f>
+        <f aca="false">IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
         <v> </v>
       </c>
       <c r="S48" s="47" t="str">
@@ -4734,11 +4744,11 @@
       </c>
       <c r="R55" s="61" t="n">
         <f aca="false">SUM(R38:R54)</f>
-        <v>3360</v>
+        <v>3000</v>
       </c>
       <c r="S55" s="61" t="n">
         <f aca="false">SUM(S38:S54)</f>
-        <v>20640</v>
+        <v>21000</v>
       </c>
       <c r="T55" s="50"/>
       <c r="U55" s="49"/>
@@ -4756,7 +4766,7 @@
       </c>
       <c r="Y55" s="61" t="n">
         <f aca="false">SUM(Y38:Y54)</f>
-        <v>8140</v>
+        <v>8500</v>
       </c>
       <c r="Z55" s="61" t="n">
         <f aca="false">SUM(Z38:Z54)</f>
@@ -4843,11 +4853,11 @@
       </c>
       <c r="R57" s="74" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
-        <v>3360</v>
+        <v>3000</v>
       </c>
       <c r="S57" s="74" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
-        <v>20640</v>
+        <v>21000</v>
       </c>
       <c r="T57" s="47"/>
       <c r="U57" s="49"/>
@@ -4865,7 +4875,7 @@
       </c>
       <c r="Y57" s="74" t="n">
         <f aca="false">Y11+Y19+Y27+Y35+Y55</f>
-        <v>8140</v>
+        <v>8500</v>
       </c>
       <c r="Z57" s="74" t="n">
         <f aca="false">Z11+Z19+Z27+Z35+Z55</f>
@@ -6602,7 +6612,7 @@
       <c r="C90" s="69"/>
       <c r="D90" s="70" t="n">
         <f aca="false">D37</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
@@ -6664,7 +6674,7 @@
       <c r="P91" s="48"/>
       <c r="Q91" s="47"/>
       <c r="R91" s="47" t="str">
-        <f aca="false">IF(E91&gt;0,E91*R$4*(1-M91)," ")</f>
+        <f aca="false">IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
         <v> </v>
       </c>
       <c r="S91" s="47" t="str">
@@ -6725,7 +6735,7 @@
       <c r="P92" s="48"/>
       <c r="Q92" s="47"/>
       <c r="R92" s="47" t="str">
-        <f aca="false">IF(E92&gt;0,E92*R$4*(1-M92)," ")</f>
+        <f aca="false">IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
         <v> </v>
       </c>
       <c r="S92" s="47" t="str">
@@ -6786,7 +6796,7 @@
       <c r="P93" s="48"/>
       <c r="Q93" s="47"/>
       <c r="R93" s="47" t="str">
-        <f aca="false">IF(E93&gt;0,E93*R$4*(1-M93)," ")</f>
+        <f aca="false">IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
         <v> </v>
       </c>
       <c r="S93" s="47" t="str">
@@ -6847,7 +6857,7 @@
       <c r="P94" s="48"/>
       <c r="Q94" s="47"/>
       <c r="R94" s="47" t="str">
-        <f aca="false">IF(E94&gt;0,E94*R$4*(1-M94)," ")</f>
+        <f aca="false">IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
         <v> </v>
       </c>
       <c r="S94" s="47" t="str">
@@ -6908,7 +6918,7 @@
       <c r="P95" s="48"/>
       <c r="Q95" s="47"/>
       <c r="R95" s="47" t="str">
-        <f aca="false">IF(E95&gt;0,E95*R$4*(1-M95)," ")</f>
+        <f aca="false">IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
         <v> </v>
       </c>
       <c r="S95" s="47" t="str">
@@ -6945,7 +6955,7 @@
       <c r="C96" s="83"/>
       <c r="D96" s="70" t="n">
         <f aca="false">D43</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E96" s="50"/>
       <c r="F96" s="50"/>
@@ -7004,7 +7014,7 @@
       <c r="P97" s="48"/>
       <c r="Q97" s="47"/>
       <c r="R97" s="47" t="str">
-        <f aca="false">IF(E97&gt;0,E97*R$4*(1-M97)," ")</f>
+        <f aca="false">IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
         <v> </v>
       </c>
       <c r="S97" s="47" t="str">
@@ -7065,7 +7075,7 @@
       <c r="P98" s="48"/>
       <c r="Q98" s="47"/>
       <c r="R98" s="47" t="str">
-        <f aca="false">IF(E98&gt;0,E98*R$4*(1-M98)," ")</f>
+        <f aca="false">IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
         <v> </v>
       </c>
       <c r="S98" s="47" t="str">
@@ -7126,7 +7136,7 @@
       <c r="P99" s="48"/>
       <c r="Q99" s="47"/>
       <c r="R99" s="47" t="str">
-        <f aca="false">IF(E99&gt;0,E99*R$4*(1-M99)," ")</f>
+        <f aca="false">IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
         <v> </v>
       </c>
       <c r="S99" s="47" t="str">
@@ -7187,7 +7197,7 @@
       <c r="P100" s="48"/>
       <c r="Q100" s="47"/>
       <c r="R100" s="47" t="str">
-        <f aca="false">IF(E100&gt;0,E100*R$4*(1-M100)," ")</f>
+        <f aca="false">IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
         <v> </v>
       </c>
       <c r="S100" s="47" t="str">
@@ -7248,7 +7258,7 @@
       <c r="P101" s="48"/>
       <c r="Q101" s="47"/>
       <c r="R101" s="47" t="str">
-        <f aca="false">IF(E101&gt;0,E101*R$4*(1-M101)," ")</f>
+        <f aca="false">IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
         <v> </v>
       </c>
       <c r="S101" s="47" t="str">

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -3704,7 +3704,7 @@
       </c>
       <c r="T38" s="47"/>
       <c r="U38" s="54" t="n">
-        <v>45940</v>
+        <v>46305</v>
       </c>
       <c r="V38" s="57" t="n">
         <v>12500</v>
@@ -5253,7 +5253,7 @@
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42"/>
       <c r="B67" s="54" t="n">
-        <v>45792</v>
+        <v>46157</v>
       </c>
       <c r="C67" s="55" t="s">
         <v>39</v>
@@ -5321,7 +5321,7 @@
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
       <c r="B68" s="54" t="n">
-        <v>45809</v>
+        <v>46174</v>
       </c>
       <c r="C68" s="55" t="s">
         <v>40</v>
@@ -5389,7 +5389,7 @@
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
       <c r="B69" s="54" t="n">
-        <v>45853</v>
+        <v>46218</v>
       </c>
       <c r="C69" s="55" t="s">
         <v>41</v>
@@ -5457,7 +5457,7 @@
     <row r="70" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="42"/>
       <c r="B70" s="54" t="n">
-        <v>45901</v>
+        <v>46266</v>
       </c>
       <c r="C70" s="55" t="s">
         <v>40</v>
@@ -5525,7 +5525,7 @@
     <row r="71" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="42"/>
       <c r="B71" s="54" t="n">
-        <v>45955</v>
+        <v>46320</v>
       </c>
       <c r="C71" s="55" t="s">
         <v>42</v>
@@ -8648,7 +8648,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="128"/>
       <c r="B8" s="54" t="n">
-        <v>45809</v>
+        <v>46174</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>77</v>
@@ -8703,7 +8703,7 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="128"/>
       <c r="B10" s="54" t="n">
-        <v>45901</v>
+        <v>46266</v>
       </c>
       <c r="C10" s="56" t="s">
         <v>77</v>
